--- a/docs/Climate_Atlas_Fields_Dictionary_AR_EN_Units.xlsx
+++ b/docs/Climate_Atlas_Fields_Dictionary_AR_EN_Units.xlsx
@@ -1858,7 +1858,7 @@
       </c>
       <c r="E36" s="14" t="inlineStr">
         <is>
-          <t>المعدل الشهري لتساقط الأمطار (المتوسط السنوي مقسوماً على 12 شهراً).</t>
+          <t>المتوسط الشهري لتساقط الأمطار (المتوسط السنوي مقسوماً على 12 شهراً).</t>
         </is>
       </c>
       <c r="F36" s="15" t="inlineStr">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="G36" s="16" t="inlineStr">
         <is>
-          <t>خريطة المعدل الشهري لتساقط الأمطار (ملم)</t>
+          <t>خريطة المتوسط الشهري لتساقط الأمطار (ملم)</t>
         </is>
       </c>
     </row>

--- a/docs/Climate_Atlas_Fields_Dictionary_AR_EN_Units.xlsx
+++ b/docs/Climate_Atlas_Fields_Dictionary_AR_EN_Units.xlsx
@@ -7,12 +7,13 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Climate_Fields" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Modules_18_Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_عن_القاموس_About_Dictionary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Climate_Fields" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Modules_18_Summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Climate_Fields'!$A$1:$G$116</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Modules_18_Summary'!$A$1:$H$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Climate_Fields'!$A$1:$G$116</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Modules_18_Summary'!$A$1:$H$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -21,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,6 +34,12 @@
       <name val="Segoe UI"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
       <sz val="11"/>
     </font>
     <font>
@@ -55,6 +62,12 @@
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
       <color rgb="007F3F98"/>
       <sz val="10"/>
     </font>
@@ -64,14 +77,8 @@
       <color rgb="00165B33"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Segoe UI"/>
-      <b val="1"/>
-      <color rgb="001F4E79"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -86,8 +93,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F6FA"/>
+        <bgColor rgb="00F2F6FA"/>
       </patternFill>
     </fill>
     <fill>
@@ -98,14 +111,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F6FA"/>
-        <bgColor rgb="00F2F6FA"/>
+        <fgColor rgb="002F5597"/>
+        <bgColor rgb="002F5597"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002F5597"/>
-        <bgColor rgb="002F5597"/>
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -135,96 +148,104 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -592,6 +613,1062 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G39"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="48" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="45" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>القاموس المرجعي الشامل لحقول ومؤشرات أطلس المناخ الرقمي
+Comprehensive Data Dictionary — NASA POWER Climate Atlas Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>1. بطاقة الهوية الفنية ومصدر البيانات المناخية (Technical Engine &amp; Data Source Profile)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>اسم الأداة والمنصة البرمجية (Software Platform)</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>NASA POWER Climate Atlas Generator (ArcGIS 10.8 &amp; Pro)</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>أداة المعالجة الكارتوجرافية والتحليل المناخي الآلي لمنظومة ArcGIS</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>مزود ونماذج البيانات المناخية (Data Source &amp; Models)</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>NASA POWER API (CERES &amp; MERRA-2 Gridded Reanalysis)</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="n"/>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>نماذج الاستشعار الفضائي وإعادة التحليل المناخي المعتمدة لوكالة ناسا</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="n"/>
+      <c r="G5" s="11" t="n"/>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>الفترة الزمنية المناخية القياسية (Climate Normal Period)</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>1996 – 2025 (سلسلة مناخية قياسية مكتملة 30 عاماً)</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>تطابق المعيار الدولي للمعدلات المناخية القياسية (WMO 30-Year Normal)</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="6" t="n"/>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>المعايير العلمية والمرجعيات الدولية (Scientific Standards)</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>WMO-No. 1203 / FAO-56 Irrigation / Steadman &amp; ISO 7243</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>المنهجيات المعتمدة عالمياً لحساب الراحة الحرارية والقحولة والتبخر</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="11" t="n"/>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>التغطية الجغرافية ونظام الإحداثيات (Spatial Scope &amp; Coordinate System)</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Global Coverage (WGS 1984 / EPSG:4326)</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>تغطية عالمية شاملة بدقة شبكية منتظمة وقابلة للقص على أي دولة أو إقليم</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="6" t="n"/>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>إجمالي الحقول الموصوفة في القاموس (Total Defined Fields)</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>116 حقلاً معيارياً (Standard Fields)</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="n"/>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>تشمل الحقول الإدارية والفيزيائية والفصلية ومتجهات الرياح والموديلات</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="n"/>
+      <c r="G9" s="11" t="n"/>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>عدد الحزم والعناصر المناخية (Climate Modules)</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>18 حزمة موديولية متكاملة (18 Complete Modules)</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>مجلدات راسترات وطبقات معالم بقاعدة البيانات الجغرافية متطابقة 1:1</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="n"/>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2. هيكل حزم البيانات والموديلات الـ 18 المتطابقة 1:1 (The 18 Climate Modules Architecture)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>م</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>كود الموديول في الأداة
+Module Code</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>الاسم باللغة العربية
+Arabic Module Name</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>الاسم بالإنجليزية
+English Module Name</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>المؤشرات
+Indicators</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="inlineStr">
+        <is>
+          <t>الوحدة الرئيسية
+Main Unit</t>
+        </is>
+      </c>
+      <c r="G13" s="13" t="inlineStr">
+        <is>
+          <t>المنهجية والمعيار العلمي المعتمد
+Scientific Methodology &amp; Standards</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>01_Temperature</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>درجة الحرارة</t>
+        </is>
+      </c>
+      <c r="D14" s="15" t="inlineStr">
+        <is>
+          <t>01_Temperature</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" s="16" t="inlineStr">
+        <is>
+          <t>°C</t>
+        </is>
+      </c>
+      <c r="G14" s="15" t="inlineStr">
+        <is>
+          <t>NASA POWER T2M, T2M_MAX, T2M_MIN / WMO Climatological Normals</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>02_Precipitation</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>الأمطار والتساقط</t>
+        </is>
+      </c>
+      <c r="D15" s="18" t="inlineStr">
+        <is>
+          <t>02_Precipitation</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F15" s="19" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="G15" s="18" t="inlineStr">
+        <is>
+          <t>NASA POWER PRECTOTCORR / Annual, Seasonal Totals &amp; Ranges</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>03_Sea_Level_Pressure</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>ضغط مستوى سطح البحر</t>
+        </is>
+      </c>
+      <c r="D16" s="15" t="inlineStr">
+        <is>
+          <t>03_Sea_Level_Pressure</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F16" s="16" t="inlineStr">
+        <is>
+          <t>hPa / mbar</t>
+        </is>
+      </c>
+      <c r="G16" s="15" t="inlineStr">
+        <is>
+          <t>NASA POWER SLP / Reduced to Standard Mean Sea Level</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>04_Surface_Pressure</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>الضغط السطحي الفعلي</t>
+        </is>
+      </c>
+      <c r="D17" s="18" t="inlineStr">
+        <is>
+          <t>04_Surface_Pressure</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F17" s="19" t="inlineStr">
+        <is>
+          <t>hPa / mbar</t>
+        </is>
+      </c>
+      <c r="G17" s="18" t="inlineStr">
+        <is>
+          <t>NASA POWER PS / Actual Local Topographic Station Pressure</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>05_Wind</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>الرياح السطحية (سرعة واتجاه)</t>
+        </is>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>05_Wind</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F18" s="16" t="inlineStr">
+        <is>
+          <t>m/s, °</t>
+        </is>
+      </c>
+      <c r="G18" s="15" t="inlineStr">
+        <is>
+          <t>NASA POWER WS10M, WD10M / Circular Mean Vector atan2</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>06_Relative_Humidity</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>الرطوبة النسبية</t>
+        </is>
+      </c>
+      <c r="D19" s="18" t="inlineStr">
+        <is>
+          <t>06_Relative_Humidity</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F19" s="19" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="G19" s="18" t="inlineStr">
+        <is>
+          <t>NASA POWER RH2M / Climatological Relative Humidity at 2m</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>07_Dew_Point</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>نقطة الندى</t>
+        </is>
+      </c>
+      <c r="D20" s="15" t="inlineStr">
+        <is>
+          <t>07_Dew_Point</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F20" s="16" t="inlineStr">
+        <is>
+          <t>°C</t>
+        </is>
+      </c>
+      <c r="G20" s="15" t="inlineStr">
+        <is>
+          <t>NASA POWER T2MDEW / Dew Point Temperature at 2m</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>08_Solar_Radiation</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>الإشعاع الشمسي والطاقة</t>
+        </is>
+      </c>
+      <c r="D21" s="18" t="inlineStr">
+        <is>
+          <t>08_Solar_Radiation</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F21" s="19" t="inlineStr">
+        <is>
+          <t>kWh/m²/day</t>
+        </is>
+      </c>
+      <c r="G21" s="18" t="inlineStr">
+        <is>
+          <t>NASA POWER ALLSKY_SFC_SW_DWN / Daily Mean &amp; Cumulative Annual</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>09_UV_Index</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>مؤشر الأشعة فوق البنفسجية</t>
+        </is>
+      </c>
+      <c r="D22" s="15" t="inlineStr">
+        <is>
+          <t>09_UV_Index</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F22" s="16" t="inlineStr">
+        <is>
+          <t>Index (0–16+)</t>
+        </is>
+      </c>
+      <c r="G22" s="15" t="inlineStr">
+        <is>
+          <t>WHO / WMO Global Solar UV Index Standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="inlineStr">
+        <is>
+          <t>10_Cloud_Cover</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>الغطاء السحابي</t>
+        </is>
+      </c>
+      <c r="D23" s="18" t="inlineStr">
+        <is>
+          <t>10_Cloud_Cover</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F23" s="19" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="G23" s="18" t="inlineStr">
+        <is>
+          <t>NASA POWER CLOUD_AMT / Total Sky Cloud Fraction</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>11_Heat_Index</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>مؤشر الحرارة والإجهاد الحراري</t>
+        </is>
+      </c>
+      <c r="D24" s="15" t="inlineStr">
+        <is>
+          <t>11_Heat_Index</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F24" s="16" t="inlineStr">
+        <is>
+          <t>°C</t>
+        </is>
+      </c>
+      <c r="G24" s="15" t="inlineStr">
+        <is>
+          <t>Steadman-Rothfusz NWS Formula + Humidex + ISO 7243 WBGT</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="inlineStr">
+        <is>
+          <t>12_Wind_Chill</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>مبرد الرياح</t>
+        </is>
+      </c>
+      <c r="D25" s="18" t="inlineStr">
+        <is>
+          <t>12_Wind_Chill</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F25" s="19" t="inlineStr">
+        <is>
+          <t>°C</t>
+        </is>
+      </c>
+      <c r="G25" s="18" t="inlineStr">
+        <is>
+          <t>US National Weather Service (NWS) Wind Chill Equivalent</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>13_De_Martonne_Aridity</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>دليل الجفاف لدي مارتون</t>
+        </is>
+      </c>
+      <c r="D26" s="15" t="inlineStr">
+        <is>
+          <t>13_De_Martonne_Aridity</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="16" t="inlineStr">
+        <is>
+          <t>Index</t>
+        </is>
+      </c>
+      <c r="G26" s="15" t="inlineStr">
+        <is>
+          <t>De Martonne (1926) Aridity Index: I = P / (T + 10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="inlineStr">
+        <is>
+          <t>14_Evapotranspiration</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>البخر والنتح المرجعي (ET)</t>
+        </is>
+      </c>
+      <c r="D27" s="18" t="inlineStr">
+        <is>
+          <t>14_Evapotranspiration</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="F27" s="19" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="G27" s="18" t="inlineStr">
+        <is>
+          <t>FAO-56 Hargreaves-Samani (1985) Extraterrestrial Radiation Ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>15_UNEP_Aridity</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>مؤشر القحولة UNEP</t>
+        </is>
+      </c>
+      <c r="D28" s="15" t="inlineStr">
+        <is>
+          <t>15_UNEP_Aridity</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="16" t="inlineStr">
+        <is>
+          <t>Ratio</t>
+        </is>
+      </c>
+      <c r="G28" s="15" t="inlineStr">
+        <is>
+          <t>UNEP Global Aridity Index: AI = P / ETo</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="inlineStr">
+        <is>
+          <t>16_Water_Deficit</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>الموازنة والعجز المائي</t>
+        </is>
+      </c>
+      <c r="D29" s="18" t="inlineStr">
+        <is>
+          <t>16_Water_Deficit</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" s="19" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="G29" s="18" t="inlineStr">
+        <is>
+          <t>Climatic Water Balance: WD = P - ETo (Negative = Deficit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B30" s="14" t="inlineStr">
+        <is>
+          <t>17_Dry_Months</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>عدد الأشهر الجافة بيولوجياً</t>
+        </is>
+      </c>
+      <c r="D30" s="15" t="inlineStr">
+        <is>
+          <t>17_Dry_Months</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" s="16" t="inlineStr">
+        <is>
+          <t>Months (0–12)</t>
+        </is>
+      </c>
+      <c r="G30" s="15" t="inlineStr">
+        <is>
+          <t>Walter-Lieth Bioclimatic Standard: P &lt; 2 * T</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B31" s="17" t="inlineStr">
+        <is>
+          <t>18_Trends_And_Anomalies</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>الاتجاهات والشذوذ المناخي</t>
+        </is>
+      </c>
+      <c r="D31" s="18" t="inlineStr">
+        <is>
+          <t>18_Trends_And_Anomalies</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="F31" s="19" t="inlineStr">
+        <is>
+          <t>°C, mm, %</t>
+        </is>
+      </c>
+      <c r="G31" s="18" t="inlineStr">
+        <is>
+          <t>OLS Linear Regression Trends &amp; WMO 1991–2020 Baseline Anomalies</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="24" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>3. دليل قراءة أعمدة القاموس المرجعي واستخدامها في نظم المعلومات الجغرافية (Field Dictionary Columns Guide)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>اسم الحقل المختصر (Short Field Name)</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>صيغة Shapefile / DBF (حتى 10 أحرف)</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="n"/>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>متوافق 100% مع طبقات الشيب فايل لمنع اقتطاع الأسماء وتشوهها عند التصدير.</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="n"/>
+      <c r="G34" s="6" t="n"/>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>اسم الحقل الكامل (Full Field Name)</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>صيغة Geodatabase و NASA POWER API</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="n"/>
+      <c r="E35" s="12" t="inlineStr">
+        <is>
+          <t>الاسم المعياري الشامل المعتمد في قواعد البيانات الجغرافية (GDB) وبرمجية الأداة.</t>
+        </is>
+      </c>
+      <c r="F35" s="11" t="n"/>
+      <c r="G35" s="11" t="n"/>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>الموديول / العنصر المناخي (Climate Module)</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>الحزمة المناخية (1 من 18 موديول)</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="n"/>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>يتطابق بنسبة 1:1 مع اسم مجلد الراستر واسم طبقة المعالم في قاعدة البيانات.</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="n"/>
+      <c r="G36" s="6" t="n"/>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>الشرح والتوصيف العلمي (Scientific Description)</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t>البيان الفيزيائي والمعادلة الرياضية</t>
+        </is>
+      </c>
+      <c r="D37" s="11" t="n"/>
+      <c r="E37" s="12" t="inlineStr">
+        <is>
+          <t>التوصيف الرياضي والفيزيائي الدقيق لكيفية حساب المؤشر وفترته الزمنية المعتمدة.</t>
+        </is>
+      </c>
+      <c r="F37" s="11" t="n"/>
+      <c r="G37" s="11" t="n"/>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>وحدة القياس القياسية (Measurement Unit)</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>الوحدات الدولية المعتمدة (SI Units)</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="n"/>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>درجات مئوية (°C)، ملم، هيكتوباسكال (hPa)، م/ث، ميجاجول/م²، نسب مئوية (%).</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="n"/>
+      <c r="G38" s="6" t="n"/>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>اسم الخريطة المقترح (Suggested Map Title)</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="inlineStr">
+        <is>
+          <t>الصياغة الكارتوجرافية الاحترافية</t>
+        </is>
+      </c>
+      <c r="D39" s="11" t="n"/>
+      <c r="E39" s="12" t="inlineStr">
+        <is>
+          <t>العنوان الكارتوجرافي الرسمي المعتمد لوضعه في عنوان الخريطة ومفتاح المصطلحات (Legend).</t>
+        </is>
+      </c>
+      <c r="F39" s="11" t="n"/>
+      <c r="G39" s="11" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="30">
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="E10:G10"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E34:G34"/>
+    <mergeCell ref="E9:G9"/>
+    <mergeCell ref="E6:G6"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="E36:G36"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E7:G7"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="E37:G37"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="E39:G39"/>
+    <mergeCell ref="E8:G8"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="E35:G35"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="E38:G38"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -605,42 +1682,42 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="20" t="inlineStr">
         <is>
           <t>م</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="20" t="inlineStr">
         <is>
           <t>اسم الحقل المختصر (Shapefile)
 Short Field Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="20" t="inlineStr">
         <is>
           <t>اسم الحقل الكامل (Geodatabase / API)
 Full Field Name (EN)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="20" t="inlineStr">
         <is>
           <t>الموديول / العنصر المناخي
 Climate Module</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="20" t="inlineStr">
         <is>
           <t>الشرح والتوصيف العلمي باللغة العربية
 Scientific Description (AR)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="20" t="inlineStr">
         <is>
           <t>وحدة القياس
 Unit</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="20" t="inlineStr">
         <is>
           <t>اسم الخريطة المقترح
 Suggested Map Title (AR)</t>
@@ -648,4025 +1725,4025 @@
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="22" t="inlineStr">
         <is>
           <t>OBJECTID</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="23" t="inlineStr">
         <is>
           <t>OBJECTID</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="24" t="inlineStr">
         <is>
           <t>Admin / بيانات إدارية</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="E2" s="25" t="inlineStr">
         <is>
           <t>المعرف الرقمي التسلسلي الفريد للظاهرة في قاعدة البيانات الجغرافية (Geodatabase OID).</t>
         </is>
       </c>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="F2" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G2" s="8" t="inlineStr">
+      <c r="G2" s="27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="22" t="inlineStr">
         <is>
           <t>Source_ID</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="23" t="inlineStr">
         <is>
           <t>Source_ID</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="24" t="inlineStr">
         <is>
           <t>Admin / بيانات إدارية</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="25" t="inlineStr">
         <is>
           <t>المعرف الفريد لمحطة الرصد أو النقطة المناخية المصدرية المدخلة في المعالجة.</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="F3" s="26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="22" t="inlineStr">
         <is>
           <t>Point_Lat</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="23" t="inlineStr">
         <is>
           <t>Point_Lat</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="24" t="inlineStr">
         <is>
           <t>Admin / بيانات إدارية</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" s="25" t="inlineStr">
         <is>
           <t>دائرة العرض الجغرافية للنقطة بالنظام الإحداثي العالمي WGS 1984 بالدرجات العشرية.</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="F4" s="26" t="inlineStr">
         <is>
           <t>درجة (°)</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="G4" s="28" t="inlineStr">
         <is>
           <t>خريطة توزيع دوائر العرض للمحطات</t>
         </is>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="22" t="inlineStr">
         <is>
           <t>Point_Lon</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="23" t="inlineStr">
         <is>
           <t>Point_Lon</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="24" t="inlineStr">
         <is>
           <t>Admin / بيانات إدارية</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="25" t="inlineStr">
         <is>
           <t>خط الطول الجغرافي للنقطة بالنظام الإحداثي العالمي WGS 1984 بالدرجات العشرية.</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="26" t="inlineStr">
         <is>
           <t>درجة (°)</t>
         </is>
       </c>
-      <c r="G5" s="9" t="inlineStr">
+      <c r="G5" s="28" t="inlineStr">
         <is>
           <t>خريطة توزيع خطوط الطول للمحطات</t>
         </is>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>Data_Start</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="23" t="inlineStr">
         <is>
           <t>Data_Start</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="24" t="inlineStr">
         <is>
           <t>Admin / بيانات إدارية</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="25" t="inlineStr">
         <is>
           <t>سنة أو تاريخ بداية السلسلة الزمنية المناخية المسحوبة من وكالة ناسا POWER.</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F6" s="26" t="inlineStr">
         <is>
           <t>سنة / تاريخ</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="G6" s="27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>Data_End</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t>Data_End</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="24" t="inlineStr">
         <is>
           <t>Admin / بيانات إدارية</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="25" t="inlineStr">
         <is>
           <t>سنة أو تاريخ نهاية السلسلة الزمنية المناخية المسحوبة من وكالة ناسا POWER.</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="F7" s="26" t="inlineStr">
         <is>
           <t>سنة / تاريخ</t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="G7" s="27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="21" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>Temporal</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="23" t="inlineStr">
         <is>
           <t>Temporal</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="24" t="inlineStr">
         <is>
           <t>Admin / بيانات إدارية</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E8" s="25" t="inlineStr">
         <is>
           <t>الدقة الزمنية للبيانات المدخلة في المعالجة (Daily يومي / Monthly شهري / Precalc محسوب مسبقاً).</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="F8" s="26" t="inlineStr">
         <is>
           <t>نص</t>
         </is>
       </c>
-      <c r="G8" s="8" t="inlineStr">
+      <c r="G8" s="27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>Intrp_Meth</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t>Interp_Meth</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="24" t="inlineStr">
         <is>
           <t>Admin / بيانات إدارية</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="25" t="inlineStr">
         <is>
           <t>خوارزمية الاستيفاء المكاني المستخدمة في توليد أسطح الراستر (IDW / Kriging / Spline).</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="F9" s="26" t="inlineStr">
         <is>
           <t>نص</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="G9" s="27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="21" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>Cell_Size</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>Cell_Size</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="24" t="inlineStr">
         <is>
           <t>Admin / بيانات إدارية</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E10" s="25" t="inlineStr">
         <is>
           <t>حجم ودقة خلية الراستر الناتجة عن الاستيفاء المكاني بوحدات الإسقاط المعتمد.</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="F10" s="26" t="inlineStr">
         <is>
           <t>متر / درجات</t>
         </is>
       </c>
-      <c r="G10" s="8" t="inlineStr">
+      <c r="G10" s="27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="21" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>Wind_Cell</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="23" t="inlineStr">
         <is>
           <t>Wind_Cell</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="24" t="inlineStr">
         <is>
           <t>Admin / بيانات إدارية</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E11" s="25" t="inlineStr">
         <is>
           <t>المسافة التباعدية بين خلايا شبكة متجهات وأسهم اتجاه وسرعة الرياح.</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="F11" s="26" t="inlineStr">
         <is>
           <t>متر / درجات</t>
         </is>
       </c>
-      <c r="G11" s="8" t="inlineStr">
+      <c r="G11" s="27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="21" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="23" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="24" t="inlineStr">
         <is>
           <t>Admin / بيانات إدارية</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E12" s="25" t="inlineStr">
         <is>
           <t>حالة إتمام المعالجة الحسابية المناخية للنقطة بنجاح (OK أو FAILED).</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F12" s="26" t="inlineStr">
         <is>
           <t>نص</t>
         </is>
       </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="G12" s="27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="21" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>Error_Msg</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>Error_Msg</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" s="24" t="inlineStr">
         <is>
           <t>Admin / بيانات إدارية</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E13" s="25" t="inlineStr">
         <is>
           <t>نص رسالة الخطأ أو التشخيص التحذيري في حال تعثر معالجة بيانات النقطة.</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F13" s="26" t="inlineStr">
         <is>
           <t>نص</t>
         </is>
       </c>
-      <c r="G13" s="8" t="inlineStr">
+      <c r="G13" s="27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="10" t="n">
+      <c r="A14" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>T_AnnMean</t>
         </is>
       </c>
-      <c r="C14" s="12" t="inlineStr">
+      <c r="C14" s="29" t="inlineStr">
         <is>
           <t>T_Annual_Mean</t>
         </is>
       </c>
-      <c r="D14" s="13" t="inlineStr">
+      <c r="D14" s="18" t="inlineStr">
         <is>
           <t>01_Temperature (درجة الحرارة)</t>
         </is>
       </c>
-      <c r="E14" s="14" t="inlineStr">
+      <c r="E14" s="12" t="inlineStr">
         <is>
           <t>المتوسط الحسابي السنوي لدرجة حرارة الهواء عند ارتفاع 2 متر لجميع شهور السنة.</t>
         </is>
       </c>
-      <c r="F14" s="15" t="inlineStr">
+      <c r="F14" s="19" t="inlineStr">
         <is>
           <t>°C</t>
         </is>
       </c>
-      <c r="G14" s="16" t="inlineStr">
+      <c r="G14" s="30" t="inlineStr">
         <is>
           <t>خريطة المتوسط السنوي لدرجة الحرارة (°C)</t>
         </is>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="17" t="n">
+      <c r="A15" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="18" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>T_WinMean</t>
         </is>
       </c>
-      <c r="C15" s="19" t="inlineStr">
+      <c r="C15" s="31" t="inlineStr">
         <is>
           <t>T_Winter_Mean</t>
         </is>
       </c>
-      <c r="D15" s="20" t="inlineStr">
+      <c r="D15" s="15" t="inlineStr">
         <is>
           <t>01_Temperature (درجة الحرارة)</t>
         </is>
       </c>
-      <c r="E15" s="21" t="inlineStr">
+      <c r="E15" s="7" t="inlineStr">
         <is>
           <t>متوسط درجة حرارة الهواء لفصل الشتاء الأرصادي (شهور ديسمبر، يناير، فبراير - DJF).</t>
         </is>
       </c>
-      <c r="F15" s="22" t="inlineStr">
+      <c r="F15" s="16" t="inlineStr">
         <is>
           <t>°C</t>
         </is>
       </c>
-      <c r="G15" s="23" t="inlineStr">
+      <c r="G15" s="32" t="inlineStr">
         <is>
           <t>خريطة متوسط درجة الحرارة خلال فصل الشتاء (°C)</t>
         </is>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="10" t="n">
+      <c r="A16" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>T_SprMean</t>
         </is>
       </c>
-      <c r="C16" s="12" t="inlineStr">
+      <c r="C16" s="29" t="inlineStr">
         <is>
           <t>T_Spring_Mean</t>
         </is>
       </c>
-      <c r="D16" s="13" t="inlineStr">
+      <c r="D16" s="18" t="inlineStr">
         <is>
           <t>01_Temperature (درجة الحرارة)</t>
         </is>
       </c>
-      <c r="E16" s="14" t="inlineStr">
+      <c r="E16" s="12" t="inlineStr">
         <is>
           <t>متوسط درجة حرارة الهواء لفصل الربيع الأرصادي (شهور مارس، أبريل، مايو - MAM).</t>
         </is>
       </c>
-      <c r="F16" s="15" t="inlineStr">
+      <c r="F16" s="19" t="inlineStr">
         <is>
           <t>°C</t>
         </is>
       </c>
-      <c r="G16" s="16" t="inlineStr">
+      <c r="G16" s="30" t="inlineStr">
         <is>
           <t>خريطة متوسط درجة الحرارة خلال فصل الربيع (°C)</t>
         </is>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="17" t="n">
+      <c r="A17" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="18" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>T_SumMean</t>
         </is>
       </c>
-      <c r="C17" s="19" t="inlineStr">
+      <c r="C17" s="31" t="inlineStr">
         <is>
           <t>T_Summer_Mean</t>
         </is>
       </c>
-      <c r="D17" s="20" t="inlineStr">
+      <c r="D17" s="15" t="inlineStr">
         <is>
           <t>01_Temperature (درجة الحرارة)</t>
         </is>
       </c>
-      <c r="E17" s="21" t="inlineStr">
+      <c r="E17" s="7" t="inlineStr">
         <is>
           <t>متوسط درجة حرارة الهواء لفصل الصيف الأرصادي (شهور يونيو، يوليو، أغسطس - JJA).</t>
         </is>
       </c>
-      <c r="F17" s="22" t="inlineStr">
+      <c r="F17" s="16" t="inlineStr">
         <is>
           <t>°C</t>
         </is>
       </c>
-      <c r="G17" s="23" t="inlineStr">
+      <c r="G17" s="32" t="inlineStr">
         <is>
           <t>خريطة متوسط درجة الحرارة خلال فصل الصيف (°C)</t>
         </is>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="10" t="n">
+      <c r="A18" s="8" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>T_AutMean</t>
         </is>
       </c>
-      <c r="C18" s="12" t="inlineStr">
+      <c r="C18" s="29" t="inlineStr">
         <is>
           <t>T_Autumn_Mean</t>
         </is>
       </c>
-      <c r="D18" s="13" t="inlineStr">
+      <c r="D18" s="18" t="inlineStr">
         <is>
           <t>01_Temperature (درجة الحرارة)</t>
         </is>
       </c>
-      <c r="E18" s="14" t="inlineStr">
+      <c r="E18" s="12" t="inlineStr">
         <is>
           <t>متوسط درجة حرارة الهواء لفصل الخريف الأرصادي (شهور سبتمبر، أكتوبر، نوفمبر - SON).</t>
         </is>
       </c>
-      <c r="F18" s="15" t="inlineStr">
+      <c r="F18" s="19" t="inlineStr">
         <is>
           <t>°C</t>
         </is>
       </c>
-      <c r="G18" s="16" t="inlineStr">
+      <c r="G18" s="30" t="inlineStr">
         <is>
           <t>خريطة متوسط درجة الحرارة خلال فصل الخريف (°C)</t>
         </is>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="17" t="n">
+      <c r="A19" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="18" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>T_AnnRng</t>
         </is>
       </c>
-      <c r="C19" s="19" t="inlineStr">
+      <c r="C19" s="31" t="inlineStr">
         <is>
           <t>T_Annual_Range</t>
         </is>
       </c>
-      <c r="D19" s="20" t="inlineStr">
+      <c r="D19" s="15" t="inlineStr">
         <is>
           <t>01_Temperature (درجة الحرارة)</t>
         </is>
       </c>
-      <c r="E19" s="21" t="inlineStr">
+      <c r="E19" s="7" t="inlineStr">
         <is>
           <t>المدى الحراري السنوي (الفارق بين متوسط أدفأ شهور السنة ومتوسط أبرد شهور السنة).</t>
         </is>
       </c>
-      <c r="F19" s="22" t="inlineStr">
+      <c r="F19" s="16" t="inlineStr">
         <is>
           <t>°C</t>
         </is>
       </c>
-      <c r="G19" s="23" t="inlineStr">
+      <c r="G19" s="32" t="inlineStr">
         <is>
           <t>خريطة المدى الحراري السنوي لدرجات الحرارة (°C)</t>
         </is>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="10" t="n">
+      <c r="A20" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>T_MaxSumMo</t>
         </is>
       </c>
-      <c r="C20" s="12" t="inlineStr">
+      <c r="C20" s="29" t="inlineStr">
         <is>
           <t>T_Max_Summer_Month_Mean</t>
         </is>
       </c>
-      <c r="D20" s="13" t="inlineStr">
+      <c r="D20" s="18" t="inlineStr">
         <is>
           <t>01_Temperature (درجة الحرارة)</t>
         </is>
       </c>
-      <c r="E20" s="14" t="inlineStr">
+      <c r="E20" s="12" t="inlineStr">
         <is>
           <t>متوسط درجة الحرارة لأدفأ شهور فصل الصيف (أعلى متوسط شهري مسجل في الصيف).</t>
         </is>
       </c>
-      <c r="F20" s="15" t="inlineStr">
+      <c r="F20" s="19" t="inlineStr">
         <is>
           <t>°C</t>
         </is>
       </c>
-      <c r="G20" s="16" t="inlineStr">
+      <c r="G20" s="30" t="inlineStr">
         <is>
           <t>خريطة متوسط أدفأ شهور فصل الصيف (°C)</t>
         </is>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="17" t="n">
+      <c r="A21" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="18" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>T_MinWinMo</t>
         </is>
       </c>
-      <c r="C21" s="19" t="inlineStr">
+      <c r="C21" s="31" t="inlineStr">
         <is>
           <t>T_Min_Winter_Month_Mean</t>
         </is>
       </c>
-      <c r="D21" s="20" t="inlineStr">
+      <c r="D21" s="15" t="inlineStr">
         <is>
           <t>01_Temperature (درجة الحرارة)</t>
         </is>
       </c>
-      <c r="E21" s="21" t="inlineStr">
+      <c r="E21" s="7" t="inlineStr">
         <is>
           <t>متوسط درجة الحرارة لأبرد شهور فصل الشتاء (أدنى متوسط شهري مسجل في الشتاء).</t>
         </is>
       </c>
-      <c r="F21" s="22" t="inlineStr">
+      <c r="F21" s="16" t="inlineStr">
         <is>
           <t>°C</t>
         </is>
       </c>
-      <c r="G21" s="23" t="inlineStr">
+      <c r="G21" s="32" t="inlineStr">
         <is>
           <t>خريطة متوسط أبرد شهور فصل الشتاء (°C)</t>
         </is>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="10" t="n">
+      <c r="A22" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B22" s="10" t="inlineStr">
         <is>
           <t>T_MaxMean</t>
         </is>
       </c>
-      <c r="C22" s="12" t="inlineStr">
+      <c r="C22" s="29" t="inlineStr">
         <is>
           <t>T_Annual_Max_Mean</t>
         </is>
       </c>
-      <c r="D22" s="13" t="inlineStr">
+      <c r="D22" s="18" t="inlineStr">
         <is>
           <t>01_Temperature (درجة الحرارة)</t>
         </is>
       </c>
-      <c r="E22" s="14" t="inlineStr">
+      <c r="E22" s="12" t="inlineStr">
         <is>
           <t>المتوسط السنوي للنهايات العظمى اليومية لدرجة حرارة الهواء (T2M_MAX).</t>
         </is>
       </c>
-      <c r="F22" s="15" t="inlineStr">
+      <c r="F22" s="19" t="inlineStr">
         <is>
           <t>°C</t>
         </is>
       </c>
-      <c r="G22" s="16" t="inlineStr">
+      <c r="G22" s="30" t="inlineStr">
         <is>
           <t>خريطة المتوسط السنوي للنهايات العظمى لدرجة الحرارة (°C)</t>
         </is>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1">
-      <c r="A23" s="17" t="n">
+      <c r="A23" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="18" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>T_MinMean</t>
         </is>
       </c>
-      <c r="C23" s="19" t="inlineStr">
+      <c r="C23" s="31" t="inlineStr">
         <is>
           <t>T_Annual_Min_Mean</t>
         </is>
       </c>
-      <c r="D23" s="20" t="inlineStr">
+      <c r="D23" s="15" t="inlineStr">
         <is>
           <t>01_Temperature (درجة الحرارة)</t>
         </is>
       </c>
-      <c r="E23" s="21" t="inlineStr">
+      <c r="E23" s="7" t="inlineStr">
         <is>
           <t>المتوسط السنوي للنهايات الصغرى اليومية لدرجة حرارة الهواء (T2M_MIN).</t>
         </is>
       </c>
-      <c r="F23" s="22" t="inlineStr">
+      <c r="F23" s="16" t="inlineStr">
         <is>
           <t>°C</t>
         </is>
       </c>
-      <c r="G23" s="23" t="inlineStr">
+      <c r="G23" s="32" t="inlineStr">
         <is>
           <t>خريطة المتوسط السنوي للنهايات الصغرى لدرجة الحرارة (°C)</t>
         </is>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="10" t="n">
+      <c r="A24" s="8" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B24" s="10" t="inlineStr">
         <is>
           <t>HI_AnnMean</t>
         </is>
       </c>
-      <c r="C24" s="12" t="inlineStr">
+      <c r="C24" s="29" t="inlineStr">
         <is>
           <t>HI_Annual_Mean</t>
         </is>
       </c>
-      <c r="D24" s="13" t="inlineStr">
+      <c r="D24" s="18" t="inlineStr">
         <is>
           <t>11_Heat_Index (مؤشر الحرارة)</t>
         </is>
       </c>
-      <c r="E24" s="14" t="inlineStr">
+      <c r="E24" s="12" t="inlineStr">
         <is>
           <t>المتوسط السنوي لمؤشر الحرارة المحسوسة المحسوب بمعادلة روتفوش وستيدمان للحرارة والرطوبة.</t>
         </is>
       </c>
-      <c r="F24" s="15" t="inlineStr">
+      <c r="F24" s="19" t="inlineStr">
         <is>
           <t>°C</t>
         </is>
       </c>
-      <c r="G24" s="16" t="inlineStr">
+      <c r="G24" s="30" t="inlineStr">
         <is>
           <t>خريطة المتوسط السنوي لمؤشر الحرارة المحسوسة (°C)</t>
         </is>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="17" t="n">
+      <c r="A25" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="18" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>HI_SumMean</t>
         </is>
       </c>
-      <c r="C25" s="19" t="inlineStr">
+      <c r="C25" s="31" t="inlineStr">
         <is>
           <t>HI_Summer_Mean</t>
         </is>
       </c>
-      <c r="D25" s="20" t="inlineStr">
+      <c r="D25" s="15" t="inlineStr">
         <is>
           <t>11_Heat_Index (مؤشر الحرارة)</t>
         </is>
       </c>
-      <c r="E25" s="21" t="inlineStr">
+      <c r="E25" s="7" t="inlineStr">
         <is>
           <t>متوسط مؤشر الحرارة المحسوسة خلال فصل الصيف (مقياس الإجهاد الحراري الفعلي).</t>
         </is>
       </c>
-      <c r="F25" s="22" t="inlineStr">
+      <c r="F25" s="16" t="inlineStr">
         <is>
           <t>°C</t>
         </is>
       </c>
-      <c r="G25" s="23" t="inlineStr">
+      <c r="G25" s="32" t="inlineStr">
         <is>
           <t>خريطة متوسط مؤشر الحرارة المحسوسة خلال فصل الصيف (°C)</t>
         </is>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="10" t="n">
+      <c r="A26" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="11" t="inlineStr">
+      <c r="B26" s="10" t="inlineStr">
         <is>
           <t>HI_WinMean</t>
         </is>
       </c>
-      <c r="C26" s="12" t="inlineStr">
+      <c r="C26" s="29" t="inlineStr">
         <is>
           <t>HI_Winter_Mean</t>
         </is>
       </c>
-      <c r="D26" s="13" t="inlineStr">
+      <c r="D26" s="18" t="inlineStr">
         <is>
           <t>11_Heat_Index (مؤشر الحرارة)</t>
         </is>
       </c>
-      <c r="E26" s="14" t="inlineStr">
+      <c r="E26" s="12" t="inlineStr">
         <is>
           <t>متوسط مؤشر الحرارة الظاهرية/الهيوميدكس خلال فصل الشتاء في الأجواء الباردة والرطبة.</t>
         </is>
       </c>
-      <c r="F26" s="15" t="inlineStr">
+      <c r="F26" s="19" t="inlineStr">
         <is>
           <t>°C</t>
         </is>
       </c>
-      <c r="G26" s="16" t="inlineStr">
+      <c r="G26" s="30" t="inlineStr">
         <is>
           <t>خريطة متوسط درجة الحرارة المحسوسة خلال فصل الشتاء (°C)</t>
         </is>
       </c>
     </row>
     <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="17" t="n">
+      <c r="A27" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="18" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>HI_AnRng</t>
         </is>
       </c>
-      <c r="C27" s="19" t="inlineStr">
+      <c r="C27" s="31" t="inlineStr">
         <is>
           <t>HI_Annual_Range</t>
         </is>
       </c>
-      <c r="D27" s="20" t="inlineStr">
+      <c r="D27" s="15" t="inlineStr">
         <is>
           <t>11_Heat_Index (مؤشر الحرارة)</t>
         </is>
       </c>
-      <c r="E27" s="21" t="inlineStr">
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>المدى السنوي لمؤشر الحرارة المحسوسة (الفارق بين أعلى شهر إجهاد حراري وأدنى شهر).</t>
         </is>
       </c>
-      <c r="F27" s="22" t="inlineStr">
+      <c r="F27" s="16" t="inlineStr">
         <is>
           <t>°C</t>
         </is>
       </c>
-      <c r="G27" s="23" t="inlineStr">
+      <c r="G27" s="32" t="inlineStr">
         <is>
           <t>خريطة المدى السنوي لمؤشر الحرارة المحسوسة (°C)</t>
         </is>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="10" t="n">
+      <c r="A28" s="8" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B28" s="10" t="inlineStr">
         <is>
           <t>WBGT_SuMn</t>
         </is>
       </c>
-      <c r="C28" s="12" t="inlineStr">
+      <c r="C28" s="29" t="inlineStr">
         <is>
           <t>WBGT_Summer_Mean</t>
         </is>
       </c>
-      <c r="D28" s="13" t="inlineStr">
+      <c r="D28" s="18" t="inlineStr">
         <is>
           <t>11_Heat_Index (مؤشر الحرارة)</t>
         </is>
       </c>
-      <c r="E28" s="14" t="inlineStr">
+      <c r="E28" s="12" t="inlineStr">
         <is>
           <t>متوسط درجة حرارة البصيلة الرطبة الكروية الصيفي في الظل (معيار ISO 7243 للإجهاد المهني والرياضي).</t>
         </is>
       </c>
-      <c r="F28" s="15" t="inlineStr">
+      <c r="F28" s="19" t="inlineStr">
         <is>
           <t>°C</t>
         </is>
       </c>
-      <c r="G28" s="16" t="inlineStr">
+      <c r="G28" s="30" t="inlineStr">
         <is>
           <t>خريطة متوسط مؤشر الإجهاد الحراري الصيفي (WBGT) (°C)</t>
         </is>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="17" t="n">
+      <c r="A29" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="18" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>Td_AnnMean</t>
         </is>
       </c>
-      <c r="C29" s="19" t="inlineStr">
+      <c r="C29" s="31" t="inlineStr">
         <is>
           <t>Td_Annual_Mean</t>
         </is>
       </c>
-      <c r="D29" s="20" t="inlineStr">
+      <c r="D29" s="15" t="inlineStr">
         <is>
           <t>07_Dew_Point (نقطة الندى)</t>
         </is>
       </c>
-      <c r="E29" s="21" t="inlineStr">
+      <c r="E29" s="7" t="inlineStr">
         <is>
           <t>المتوسط الحسابي السنوي لدرجة حرارة نقطة الندى عند ارتفاع 2 متر.</t>
         </is>
       </c>
-      <c r="F29" s="22" t="inlineStr">
+      <c r="F29" s="16" t="inlineStr">
         <is>
           <t>°C</t>
         </is>
       </c>
-      <c r="G29" s="23" t="inlineStr">
+      <c r="G29" s="32" t="inlineStr">
         <is>
           <t>خريطة المتوسط السنوي لدرجة حرارة نقطة الندى (°C)</t>
         </is>
       </c>
     </row>
     <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="10" t="n">
+      <c r="A30" s="8" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B30" s="10" t="inlineStr">
         <is>
           <t>Td_WinMean</t>
         </is>
       </c>
-      <c r="C30" s="12" t="inlineStr">
+      <c r="C30" s="29" t="inlineStr">
         <is>
           <t>Td_Winter_Mean</t>
         </is>
       </c>
-      <c r="D30" s="13" t="inlineStr">
+      <c r="D30" s="18" t="inlineStr">
         <is>
           <t>07_Dew_Point (نقطة الندى)</t>
         </is>
       </c>
-      <c r="E30" s="14" t="inlineStr">
+      <c r="E30" s="12" t="inlineStr">
         <is>
           <t>متوسط درجة حرارة نقطة الندى خلال فصل الشتاء الأرصادي (DJF).</t>
         </is>
       </c>
-      <c r="F30" s="15" t="inlineStr">
+      <c r="F30" s="19" t="inlineStr">
         <is>
           <t>°C</t>
         </is>
       </c>
-      <c r="G30" s="16" t="inlineStr">
+      <c r="G30" s="30" t="inlineStr">
         <is>
           <t>خريطة متوسط درجة حرارة نقطة الندى خلال فصل الشتاء (°C)</t>
         </is>
       </c>
     </row>
     <row r="31" ht="24" customHeight="1">
-      <c r="A31" s="17" t="n">
+      <c r="A31" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="18" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>Td_SprMean</t>
         </is>
       </c>
-      <c r="C31" s="19" t="inlineStr">
+      <c r="C31" s="31" t="inlineStr">
         <is>
           <t>Td_Spring_Mean</t>
         </is>
       </c>
-      <c r="D31" s="20" t="inlineStr">
+      <c r="D31" s="15" t="inlineStr">
         <is>
           <t>07_Dew_Point (نقطة الندى)</t>
         </is>
       </c>
-      <c r="E31" s="21" t="inlineStr">
+      <c r="E31" s="7" t="inlineStr">
         <is>
           <t>متوسط درجة حرارة نقطة الندى خلال فصل الربيع الأرصادي (MAM).</t>
         </is>
       </c>
-      <c r="F31" s="22" t="inlineStr">
+      <c r="F31" s="16" t="inlineStr">
         <is>
           <t>°C</t>
         </is>
       </c>
-      <c r="G31" s="23" t="inlineStr">
+      <c r="G31" s="32" t="inlineStr">
         <is>
           <t>خريطة متوسط درجة حرارة نقطة الندى خلال فصل الربيع (°C)</t>
         </is>
       </c>
     </row>
     <row r="32" ht="24" customHeight="1">
-      <c r="A32" s="10" t="n">
+      <c r="A32" s="8" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="11" t="inlineStr">
+      <c r="B32" s="10" t="inlineStr">
         <is>
           <t>Td_SumMean</t>
         </is>
       </c>
-      <c r="C32" s="12" t="inlineStr">
+      <c r="C32" s="29" t="inlineStr">
         <is>
           <t>Td_Summer_Mean</t>
         </is>
       </c>
-      <c r="D32" s="13" t="inlineStr">
+      <c r="D32" s="18" t="inlineStr">
         <is>
           <t>07_Dew_Point (نقطة الندى)</t>
         </is>
       </c>
-      <c r="E32" s="14" t="inlineStr">
+      <c r="E32" s="12" t="inlineStr">
         <is>
           <t>متوسط درجة حرارة نقطة الندى خلال فصل الصيف الأرصادي (JJA - مؤشر مباشر للرطوبة الخانقة والكتمة).</t>
         </is>
       </c>
-      <c r="F32" s="15" t="inlineStr">
+      <c r="F32" s="19" t="inlineStr">
         <is>
           <t>°C</t>
         </is>
       </c>
-      <c r="G32" s="16" t="inlineStr">
+      <c r="G32" s="30" t="inlineStr">
         <is>
           <t>خريطة متوسط درجة حرارة نقطة الندى خلال فصل الصيف (°C)</t>
         </is>
       </c>
     </row>
     <row r="33" ht="24" customHeight="1">
-      <c r="A33" s="17" t="n">
+      <c r="A33" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="18" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>Td_AutMean</t>
         </is>
       </c>
-      <c r="C33" s="19" t="inlineStr">
+      <c r="C33" s="31" t="inlineStr">
         <is>
           <t>Td_Autumn_Mean</t>
         </is>
       </c>
-      <c r="D33" s="20" t="inlineStr">
+      <c r="D33" s="15" t="inlineStr">
         <is>
           <t>07_Dew_Point (نقطة الندى)</t>
         </is>
       </c>
-      <c r="E33" s="21" t="inlineStr">
+      <c r="E33" s="7" t="inlineStr">
         <is>
           <t>متوسط درجة حرارة نقطة الندى خلال فصل الخريف الأرصادي (SON).</t>
         </is>
       </c>
-      <c r="F33" s="22" t="inlineStr">
+      <c r="F33" s="16" t="inlineStr">
         <is>
           <t>°C</t>
         </is>
       </c>
-      <c r="G33" s="23" t="inlineStr">
+      <c r="G33" s="32" t="inlineStr">
         <is>
           <t>خريطة متوسط درجة حرارة نقطة الندى خلال فصل الخريف (°C)</t>
         </is>
       </c>
     </row>
     <row r="34" ht="24" customHeight="1">
-      <c r="A34" s="10" t="n">
+      <c r="A34" s="8" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="11" t="inlineStr">
+      <c r="B34" s="10" t="inlineStr">
         <is>
           <t>Td_AnnRng</t>
         </is>
       </c>
-      <c r="C34" s="12" t="inlineStr">
+      <c r="C34" s="29" t="inlineStr">
         <is>
           <t>Td_Annual_Range</t>
         </is>
       </c>
-      <c r="D34" s="13" t="inlineStr">
+      <c r="D34" s="18" t="inlineStr">
         <is>
           <t>07_Dew_Point (نقطة الندى)</t>
         </is>
       </c>
-      <c r="E34" s="14" t="inlineStr">
+      <c r="E34" s="12" t="inlineStr">
         <is>
           <t>المدى السنوي لدرجة حرارة نقطة الندى (الفارق بين أعلى وأدنى متوسط شهري لنقطة الندى).</t>
         </is>
       </c>
-      <c r="F34" s="15" t="inlineStr">
+      <c r="F34" s="19" t="inlineStr">
         <is>
           <t>°C</t>
         </is>
       </c>
-      <c r="G34" s="16" t="inlineStr">
+      <c r="G34" s="30" t="inlineStr">
         <is>
           <t>خريطة المدى السنوي لدرجة حرارة نقطة الندى (°C)</t>
         </is>
       </c>
     </row>
     <row r="35" ht="24" customHeight="1">
-      <c r="A35" s="17" t="n">
+      <c r="A35" s="3" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="18" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>R_AnnMean</t>
         </is>
       </c>
-      <c r="C35" s="19" t="inlineStr">
+      <c r="C35" s="31" t="inlineStr">
         <is>
           <t>R_Annual_Mean</t>
         </is>
       </c>
-      <c r="D35" s="20" t="inlineStr">
+      <c r="D35" s="15" t="inlineStr">
         <is>
           <t>02_Precipitation (الأمطار)</t>
         </is>
       </c>
-      <c r="E35" s="21" t="inlineStr">
+      <c r="E35" s="7" t="inlineStr">
         <is>
           <t>المتوسط السنوي لتساقط الأمطار (متوسط مجاميع السنين على مدار فترة الرصد 1996–2025).</t>
         </is>
       </c>
-      <c r="F35" s="22" t="inlineStr">
+      <c r="F35" s="16" t="inlineStr">
         <is>
           <t>ملم (mm)</t>
         </is>
       </c>
-      <c r="G35" s="23" t="inlineStr">
+      <c r="G35" s="32" t="inlineStr">
         <is>
           <t>خريطة المتوسط السنوي لتساقط الأمطار (ملم)</t>
         </is>
       </c>
     </row>
     <row r="36" ht="24" customHeight="1">
-      <c r="A36" s="10" t="n">
+      <c r="A36" s="8" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="11" t="inlineStr">
+      <c r="B36" s="10" t="inlineStr">
         <is>
           <t>R_MonMean</t>
         </is>
       </c>
-      <c r="C36" s="12" t="inlineStr">
+      <c r="C36" s="29" t="inlineStr">
         <is>
           <t>R_Month_Mean</t>
         </is>
       </c>
-      <c r="D36" s="13" t="inlineStr">
+      <c r="D36" s="18" t="inlineStr">
         <is>
           <t>02_Precipitation (الأمطار)</t>
         </is>
       </c>
-      <c r="E36" s="14" t="inlineStr">
+      <c r="E36" s="12" t="inlineStr">
         <is>
           <t>المتوسط الشهري لتساقط الأمطار (المتوسط السنوي مقسوماً على 12 شهراً).</t>
         </is>
       </c>
-      <c r="F36" s="15" t="inlineStr">
+      <c r="F36" s="19" t="inlineStr">
         <is>
           <t>ملم (mm)</t>
         </is>
       </c>
-      <c r="G36" s="16" t="inlineStr">
+      <c r="G36" s="30" t="inlineStr">
         <is>
           <t>خريطة المتوسط الشهري لتساقط الأمطار (ملم)</t>
         </is>
       </c>
     </row>
     <row r="37" ht="24" customHeight="1">
-      <c r="A37" s="17" t="n">
+      <c r="A37" s="3" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="18" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>R_AnnRng</t>
         </is>
       </c>
-      <c r="C37" s="19" t="inlineStr">
+      <c r="C37" s="31" t="inlineStr">
         <is>
           <t>R_Annual_Range</t>
         </is>
       </c>
-      <c r="D37" s="20" t="inlineStr">
+      <c r="D37" s="15" t="inlineStr">
         <is>
           <t>02_Precipitation (الأمطار)</t>
         </is>
       </c>
-      <c r="E37" s="21" t="inlineStr">
+      <c r="E37" s="7" t="inlineStr">
         <is>
           <t>المدى السنوي لتساقط الأمطار (الفارق بين أعلى شهر مطراً وأقل شهر مطراً في السنة).</t>
         </is>
       </c>
-      <c r="F37" s="22" t="inlineStr">
+      <c r="F37" s="16" t="inlineStr">
         <is>
           <t>ملم (mm)</t>
         </is>
       </c>
-      <c r="G37" s="23" t="inlineStr">
+      <c r="G37" s="32" t="inlineStr">
         <is>
           <t>خريطة المدى السنوي لتساقط الأمطار (ملم)</t>
         </is>
       </c>
     </row>
     <row r="38" ht="24" customHeight="1">
-      <c r="A38" s="10" t="n">
+      <c r="A38" s="8" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="11" t="inlineStr">
+      <c r="B38" s="10" t="inlineStr">
         <is>
           <t>R_SeaRng</t>
         </is>
       </c>
-      <c r="C38" s="12" t="inlineStr">
+      <c r="C38" s="29" t="inlineStr">
         <is>
           <t>R_Seasonal_Range</t>
         </is>
       </c>
-      <c r="D38" s="13" t="inlineStr">
+      <c r="D38" s="18" t="inlineStr">
         <is>
           <t>02_Precipitation (الأمطار)</t>
         </is>
       </c>
-      <c r="E38" s="14" t="inlineStr">
+      <c r="E38" s="12" t="inlineStr">
         <is>
           <t>المدى الفصلي لتساقط الأمطار (الفارق بين مجموع أعلى فصول السنة مطراً ومجموع أقلها مطراً).</t>
         </is>
       </c>
-      <c r="F38" s="15" t="inlineStr">
+      <c r="F38" s="19" t="inlineStr">
         <is>
           <t>ملم (mm)</t>
         </is>
       </c>
-      <c r="G38" s="16" t="inlineStr">
+      <c r="G38" s="30" t="inlineStr">
         <is>
           <t>خريطة المدى الفصلي لتساقط الأمطار (ملم)</t>
         </is>
       </c>
     </row>
     <row r="39" ht="24" customHeight="1">
-      <c r="A39" s="17" t="n">
+      <c r="A39" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="18" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>R_WinTot</t>
         </is>
       </c>
-      <c r="C39" s="19" t="inlineStr">
+      <c r="C39" s="31" t="inlineStr">
         <is>
           <t>R_Winter_Total</t>
         </is>
       </c>
-      <c r="D39" s="20" t="inlineStr">
+      <c r="D39" s="15" t="inlineStr">
         <is>
           <t>02_Precipitation (الأمطار)</t>
         </is>
       </c>
-      <c r="E39" s="21" t="inlineStr">
+      <c r="E39" s="7" t="inlineStr">
         <is>
           <t>المجموع التراكمي لأمطار فصل الشتاء الأرصادي (شهور ديسمبر، يناير، فبراير - DJF).</t>
         </is>
       </c>
-      <c r="F39" s="22" t="inlineStr">
+      <c r="F39" s="16" t="inlineStr">
         <is>
           <t>ملم (mm)</t>
         </is>
       </c>
-      <c r="G39" s="23" t="inlineStr">
+      <c r="G39" s="32" t="inlineStr">
         <is>
           <t>خريطة مجموع تساقط الأمطار خلال فصل الشتاء (ملم)</t>
         </is>
       </c>
     </row>
     <row r="40" ht="24" customHeight="1">
-      <c r="A40" s="10" t="n">
+      <c r="A40" s="8" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="11" t="inlineStr">
+      <c r="B40" s="10" t="inlineStr">
         <is>
           <t>R_SprTot</t>
         </is>
       </c>
-      <c r="C40" s="12" t="inlineStr">
+      <c r="C40" s="29" t="inlineStr">
         <is>
           <t>R_Spring_Total</t>
         </is>
       </c>
-      <c r="D40" s="13" t="inlineStr">
+      <c r="D40" s="18" t="inlineStr">
         <is>
           <t>02_Precipitation (الأمطار)</t>
         </is>
       </c>
-      <c r="E40" s="14" t="inlineStr">
+      <c r="E40" s="12" t="inlineStr">
         <is>
           <t>المجموع التراكمي لأمطار فصل الربيع الأرصادي (شهور مارس، أبريل، مايو - MAM).</t>
         </is>
       </c>
-      <c r="F40" s="15" t="inlineStr">
+      <c r="F40" s="19" t="inlineStr">
         <is>
           <t>ملم (mm)</t>
         </is>
       </c>
-      <c r="G40" s="16" t="inlineStr">
+      <c r="G40" s="30" t="inlineStr">
         <is>
           <t>خريطة مجموع تساقط الأمطار خلال فصل الربيع (ملم)</t>
         </is>
       </c>
     </row>
     <row r="41" ht="24" customHeight="1">
-      <c r="A41" s="17" t="n">
+      <c r="A41" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="18" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>R_SumTot</t>
         </is>
       </c>
-      <c r="C41" s="19" t="inlineStr">
+      <c r="C41" s="31" t="inlineStr">
         <is>
           <t>R_Summer_Total</t>
         </is>
       </c>
-      <c r="D41" s="20" t="inlineStr">
+      <c r="D41" s="15" t="inlineStr">
         <is>
           <t>02_Precipitation (الأمطار)</t>
         </is>
       </c>
-      <c r="E41" s="21" t="inlineStr">
+      <c r="E41" s="7" t="inlineStr">
         <is>
           <t>المجموع التراكمي لأمطار فصل الصيف الأرصادي (شهور يونيو، يوليو، أغسطس - JJA).</t>
         </is>
       </c>
-      <c r="F41" s="22" t="inlineStr">
+      <c r="F41" s="16" t="inlineStr">
         <is>
           <t>ملم (mm)</t>
         </is>
       </c>
-      <c r="G41" s="23" t="inlineStr">
+      <c r="G41" s="32" t="inlineStr">
         <is>
           <t>خريطة مجموع تساقط الأمطار خلال فصل الصيف (ملم)</t>
         </is>
       </c>
     </row>
     <row r="42" ht="24" customHeight="1">
-      <c r="A42" s="10" t="n">
+      <c r="A42" s="8" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="11" t="inlineStr">
+      <c r="B42" s="10" t="inlineStr">
         <is>
           <t>R_AutTot</t>
         </is>
       </c>
-      <c r="C42" s="12" t="inlineStr">
+      <c r="C42" s="29" t="inlineStr">
         <is>
           <t>R_Autumn_Total</t>
         </is>
       </c>
-      <c r="D42" s="13" t="inlineStr">
+      <c r="D42" s="18" t="inlineStr">
         <is>
           <t>02_Precipitation (الأمطار)</t>
         </is>
       </c>
-      <c r="E42" s="14" t="inlineStr">
+      <c r="E42" s="12" t="inlineStr">
         <is>
           <t>المجموع التراكمي لأمطار فصل الخريف الأرصادي (شهور سبتمبر، أكتوبر، نوفمبر - SON).</t>
         </is>
       </c>
-      <c r="F42" s="15" t="inlineStr">
+      <c r="F42" s="19" t="inlineStr">
         <is>
           <t>ملم (mm)</t>
         </is>
       </c>
-      <c r="G42" s="16" t="inlineStr">
+      <c r="G42" s="30" t="inlineStr">
         <is>
           <t>خريطة مجموع تساقط الأمطار خلال فصل الخريف (ملم)</t>
         </is>
       </c>
     </row>
     <row r="43" ht="24" customHeight="1">
-      <c r="A43" s="17" t="n">
+      <c r="A43" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="18" t="inlineStr">
+      <c r="B43" s="5" t="inlineStr">
         <is>
           <t>PSL_AnMean</t>
         </is>
       </c>
-      <c r="C43" s="19" t="inlineStr">
+      <c r="C43" s="31" t="inlineStr">
         <is>
           <t>PSL_Annual_Mean</t>
         </is>
       </c>
-      <c r="D43" s="20" t="inlineStr">
+      <c r="D43" s="15" t="inlineStr">
         <is>
           <t>03_Sea_Level_Pressure (ضغط مستوى البحر)</t>
         </is>
       </c>
-      <c r="E43" s="21" t="inlineStr">
+      <c r="E43" s="7" t="inlineStr">
         <is>
           <t>متوسط الضغط الجوي السنوي المصحح عند مستوى سطح البحر القياسي (Sea Level Pressure).</t>
         </is>
       </c>
-      <c r="F43" s="22" t="inlineStr">
+      <c r="F43" s="16" t="inlineStr">
         <is>
           <t>hPa / mbar</t>
         </is>
       </c>
-      <c r="G43" s="23" t="inlineStr">
+      <c r="G43" s="32" t="inlineStr">
         <is>
           <t>خريطة متوسط الضغط الجوي عند مستوى سطح البحر (hPa)</t>
         </is>
       </c>
     </row>
     <row r="44" ht="24" customHeight="1">
-      <c r="A44" s="10" t="n">
+      <c r="A44" s="8" t="n">
         <v>43</v>
       </c>
-      <c r="B44" s="11" t="inlineStr">
+      <c r="B44" s="10" t="inlineStr">
         <is>
           <t>PSL_WnMean</t>
         </is>
       </c>
-      <c r="C44" s="12" t="inlineStr">
+      <c r="C44" s="29" t="inlineStr">
         <is>
           <t>PSL_Winter_Mean</t>
         </is>
       </c>
-      <c r="D44" s="13" t="inlineStr">
+      <c r="D44" s="18" t="inlineStr">
         <is>
           <t>03_Sea_Level_Pressure (ضغط مستوى البحر)</t>
         </is>
       </c>
-      <c r="E44" s="14" t="inlineStr">
+      <c r="E44" s="12" t="inlineStr">
         <is>
           <t>متوسط الضغط الجوي عند مستوى سطح البحر لفصل الشتاء الأرصادي (DJF).</t>
         </is>
       </c>
-      <c r="F44" s="15" t="inlineStr">
+      <c r="F44" s="19" t="inlineStr">
         <is>
           <t>hPa / mbar</t>
         </is>
       </c>
-      <c r="G44" s="16" t="inlineStr">
+      <c r="G44" s="30" t="inlineStr">
         <is>
           <t>خريطة متوسط ضغط مستوى سطح البحر خلال فصل الشتاء (hPa)</t>
         </is>
       </c>
     </row>
     <row r="45" ht="24" customHeight="1">
-      <c r="A45" s="17" t="n">
+      <c r="A45" s="3" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="18" t="inlineStr">
+      <c r="B45" s="5" t="inlineStr">
         <is>
           <t>PSL_SpMean</t>
         </is>
       </c>
-      <c r="C45" s="19" t="inlineStr">
+      <c r="C45" s="31" t="inlineStr">
         <is>
           <t>PSL_Spring_Mean</t>
         </is>
       </c>
-      <c r="D45" s="20" t="inlineStr">
+      <c r="D45" s="15" t="inlineStr">
         <is>
           <t>03_Sea_Level_Pressure (ضغط مستوى البحر)</t>
         </is>
       </c>
-      <c r="E45" s="21" t="inlineStr">
+      <c r="E45" s="7" t="inlineStr">
         <is>
           <t>متوسط الضغط الجوي عند مستوى سطح البحر لفصل الربيع الأرصادي (MAM).</t>
         </is>
       </c>
-      <c r="F45" s="22" t="inlineStr">
+      <c r="F45" s="16" t="inlineStr">
         <is>
           <t>hPa / mbar</t>
         </is>
       </c>
-      <c r="G45" s="23" t="inlineStr">
+      <c r="G45" s="32" t="inlineStr">
         <is>
           <t>خريطة متوسط ضغط مستوى سطح البحر خلال فصل الربيع (hPa)</t>
         </is>
       </c>
     </row>
     <row r="46" ht="24" customHeight="1">
-      <c r="A46" s="10" t="n">
+      <c r="A46" s="8" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="11" t="inlineStr">
+      <c r="B46" s="10" t="inlineStr">
         <is>
           <t>PSL_SuMean</t>
         </is>
       </c>
-      <c r="C46" s="12" t="inlineStr">
+      <c r="C46" s="29" t="inlineStr">
         <is>
           <t>PSL_Summer_Mean</t>
         </is>
       </c>
-      <c r="D46" s="13" t="inlineStr">
+      <c r="D46" s="18" t="inlineStr">
         <is>
           <t>03_Sea_Level_Pressure (ضغط مستوى البحر)</t>
         </is>
       </c>
-      <c r="E46" s="14" t="inlineStr">
+      <c r="E46" s="12" t="inlineStr">
         <is>
           <t>متوسط الضغط الجوي عند مستوى سطح البحر لفصل الصيف الأرصادي (JJA).</t>
         </is>
       </c>
-      <c r="F46" s="15" t="inlineStr">
+      <c r="F46" s="19" t="inlineStr">
         <is>
           <t>hPa / mbar</t>
         </is>
       </c>
-      <c r="G46" s="16" t="inlineStr">
+      <c r="G46" s="30" t="inlineStr">
         <is>
           <t>خريطة متوسط ضغط مستوى سطح البحر خلال فصل الصيف (hPa)</t>
         </is>
       </c>
     </row>
     <row r="47" ht="24" customHeight="1">
-      <c r="A47" s="17" t="n">
+      <c r="A47" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="18" t="inlineStr">
+      <c r="B47" s="5" t="inlineStr">
         <is>
           <t>PSL_AuMean</t>
         </is>
       </c>
-      <c r="C47" s="19" t="inlineStr">
+      <c r="C47" s="31" t="inlineStr">
         <is>
           <t>PSL_Autumn_Mean</t>
         </is>
       </c>
-      <c r="D47" s="20" t="inlineStr">
+      <c r="D47" s="15" t="inlineStr">
         <is>
           <t>03_Sea_Level_Pressure (ضغط مستوى البحر)</t>
         </is>
       </c>
-      <c r="E47" s="21" t="inlineStr">
+      <c r="E47" s="7" t="inlineStr">
         <is>
           <t>متوسط الضغط الجوي عند مستوى سطح البحر لفصل الخريف الأرصادي (SON).</t>
         </is>
       </c>
-      <c r="F47" s="22" t="inlineStr">
+      <c r="F47" s="16" t="inlineStr">
         <is>
           <t>hPa / mbar</t>
         </is>
       </c>
-      <c r="G47" s="23" t="inlineStr">
+      <c r="G47" s="32" t="inlineStr">
         <is>
           <t>خريطة متوسط ضغط مستوى سطح البحر خلال فصل الخريف (hPa)</t>
         </is>
       </c>
     </row>
     <row r="48" ht="24" customHeight="1">
-      <c r="A48" s="10" t="n">
+      <c r="A48" s="8" t="n">
         <v>47</v>
       </c>
-      <c r="B48" s="11" t="inlineStr">
+      <c r="B48" s="10" t="inlineStr">
         <is>
           <t>PSL_AnRng</t>
         </is>
       </c>
-      <c r="C48" s="12" t="inlineStr">
+      <c r="C48" s="29" t="inlineStr">
         <is>
           <t>PSL_Annual_Range</t>
         </is>
       </c>
-      <c r="D48" s="13" t="inlineStr">
+      <c r="D48" s="18" t="inlineStr">
         <is>
           <t>03_Sea_Level_Pressure (ضغط مستوى البحر)</t>
         </is>
       </c>
-      <c r="E48" s="14" t="inlineStr">
+      <c r="E48" s="12" t="inlineStr">
         <is>
           <t>المدى البارومتري السنوي لضغط مستوى البحر (الفارق بين أعلى وأدنى متوسط شهري للضغط).</t>
         </is>
       </c>
-      <c r="F48" s="15" t="inlineStr">
+      <c r="F48" s="19" t="inlineStr">
         <is>
           <t>hPa / mbar</t>
         </is>
       </c>
-      <c r="G48" s="16" t="inlineStr">
+      <c r="G48" s="30" t="inlineStr">
         <is>
           <t>خريطة المدى السنوي لضغط مستوى سطح البحر (hPa)</t>
         </is>
       </c>
     </row>
     <row r="49" ht="24" customHeight="1">
-      <c r="A49" s="17" t="n">
+      <c r="A49" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="18" t="inlineStr">
+      <c r="B49" s="5" t="inlineStr">
         <is>
           <t>PS_AnnMean</t>
         </is>
       </c>
-      <c r="C49" s="19" t="inlineStr">
+      <c r="C49" s="31" t="inlineStr">
         <is>
           <t>PS_Annual_Mean</t>
         </is>
       </c>
-      <c r="D49" s="20" t="inlineStr">
+      <c r="D49" s="15" t="inlineStr">
         <is>
           <t>04_Surface_Pressure (الضغط السطحي)</t>
         </is>
       </c>
-      <c r="E49" s="21" t="inlineStr">
+      <c r="E49" s="7" t="inlineStr">
         <is>
           <t>المتوسط السنوي للضغط الجوي السطحي الفعلي الحقيقي عند منسوب تضاريس المحطة.</t>
         </is>
       </c>
-      <c r="F49" s="22" t="inlineStr">
+      <c r="F49" s="16" t="inlineStr">
         <is>
           <t>hPa / mbar</t>
         </is>
       </c>
-      <c r="G49" s="23" t="inlineStr">
+      <c r="G49" s="32" t="inlineStr">
         <is>
           <t>خريطة المتوسط السنوي للضغط الجوي السطحي (hPa)</t>
         </is>
       </c>
     </row>
     <row r="50" ht="24" customHeight="1">
-      <c r="A50" s="10" t="n">
+      <c r="A50" s="8" t="n">
         <v>49</v>
       </c>
-      <c r="B50" s="11" t="inlineStr">
+      <c r="B50" s="10" t="inlineStr">
         <is>
           <t>PS_WinMean</t>
         </is>
       </c>
-      <c r="C50" s="12" t="inlineStr">
+      <c r="C50" s="29" t="inlineStr">
         <is>
           <t>PS_Winter_Mean</t>
         </is>
       </c>
-      <c r="D50" s="13" t="inlineStr">
+      <c r="D50" s="18" t="inlineStr">
         <is>
           <t>04_Surface_Pressure (الضغط السطحي)</t>
         </is>
       </c>
-      <c r="E50" s="14" t="inlineStr">
+      <c r="E50" s="12" t="inlineStr">
         <is>
           <t>متوسط الضغط الجوي السطحي الفعلي لفصل الشتاء الأرصادي (DJF).</t>
         </is>
       </c>
-      <c r="F50" s="15" t="inlineStr">
+      <c r="F50" s="19" t="inlineStr">
         <is>
           <t>hPa / mbar</t>
         </is>
       </c>
-      <c r="G50" s="16" t="inlineStr">
+      <c r="G50" s="30" t="inlineStr">
         <is>
           <t>خريطة متوسط الضغط السطحي خلال فصل الشتاء (hPa)</t>
         </is>
       </c>
     </row>
     <row r="51" ht="24" customHeight="1">
-      <c r="A51" s="17" t="n">
+      <c r="A51" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="B51" s="18" t="inlineStr">
+      <c r="B51" s="5" t="inlineStr">
         <is>
           <t>PS_SprMean</t>
         </is>
       </c>
-      <c r="C51" s="19" t="inlineStr">
+      <c r="C51" s="31" t="inlineStr">
         <is>
           <t>PS_Spring_Mean</t>
         </is>
       </c>
-      <c r="D51" s="20" t="inlineStr">
+      <c r="D51" s="15" t="inlineStr">
         <is>
           <t>04_Surface_Pressure (الضغط السطحي)</t>
         </is>
       </c>
-      <c r="E51" s="21" t="inlineStr">
+      <c r="E51" s="7" t="inlineStr">
         <is>
           <t>متوسط الضغط الجوي السطحي الفعلي لفصل الربيع الأرصادي (MAM).</t>
         </is>
       </c>
-      <c r="F51" s="22" t="inlineStr">
+      <c r="F51" s="16" t="inlineStr">
         <is>
           <t>hPa / mbar</t>
         </is>
       </c>
-      <c r="G51" s="23" t="inlineStr">
+      <c r="G51" s="32" t="inlineStr">
         <is>
           <t>خريطة متوسط الضغط السطحي خلال فصل الربيع (hPa)</t>
         </is>
       </c>
     </row>
     <row r="52" ht="24" customHeight="1">
-      <c r="A52" s="10" t="n">
+      <c r="A52" s="8" t="n">
         <v>51</v>
       </c>
-      <c r="B52" s="11" t="inlineStr">
+      <c r="B52" s="10" t="inlineStr">
         <is>
           <t>PS_SumMean</t>
         </is>
       </c>
-      <c r="C52" s="12" t="inlineStr">
+      <c r="C52" s="29" t="inlineStr">
         <is>
           <t>PS_Summer_Mean</t>
         </is>
       </c>
-      <c r="D52" s="13" t="inlineStr">
+      <c r="D52" s="18" t="inlineStr">
         <is>
           <t>04_Surface_Pressure (الضغط السطحي)</t>
         </is>
       </c>
-      <c r="E52" s="14" t="inlineStr">
+      <c r="E52" s="12" t="inlineStr">
         <is>
           <t>متوسط الضغط الجوي السطحي الفعلي لفصل الصيف الأرصادي (JJA).</t>
         </is>
       </c>
-      <c r="F52" s="15" t="inlineStr">
+      <c r="F52" s="19" t="inlineStr">
         <is>
           <t>hPa / mbar</t>
         </is>
       </c>
-      <c r="G52" s="16" t="inlineStr">
+      <c r="G52" s="30" t="inlineStr">
         <is>
           <t>خريطة متوسط الضغط السطحي خلال فصل الصيف (hPa)</t>
         </is>
       </c>
     </row>
     <row r="53" ht="24" customHeight="1">
-      <c r="A53" s="17" t="n">
+      <c r="A53" s="3" t="n">
         <v>52</v>
       </c>
-      <c r="B53" s="18" t="inlineStr">
+      <c r="B53" s="5" t="inlineStr">
         <is>
           <t>PS_AutMean</t>
         </is>
       </c>
-      <c r="C53" s="19" t="inlineStr">
+      <c r="C53" s="31" t="inlineStr">
         <is>
           <t>PS_Autumn_Mean</t>
         </is>
       </c>
-      <c r="D53" s="20" t="inlineStr">
+      <c r="D53" s="15" t="inlineStr">
         <is>
           <t>04_Surface_Pressure (الضغط السطحي)</t>
         </is>
       </c>
-      <c r="E53" s="21" t="inlineStr">
+      <c r="E53" s="7" t="inlineStr">
         <is>
           <t>متوسط الضغط الجوي السطحي الفعلي لفصل الخريف الأرصادي (SON).</t>
         </is>
       </c>
-      <c r="F53" s="22" t="inlineStr">
+      <c r="F53" s="16" t="inlineStr">
         <is>
           <t>hPa / mbar</t>
         </is>
       </c>
-      <c r="G53" s="23" t="inlineStr">
+      <c r="G53" s="32" t="inlineStr">
         <is>
           <t>خريطة متوسط الضغط السطحي خلال فصل الخريف (hPa)</t>
         </is>
       </c>
     </row>
     <row r="54" ht="24" customHeight="1">
-      <c r="A54" s="10" t="n">
+      <c r="A54" s="8" t="n">
         <v>53</v>
       </c>
-      <c r="B54" s="11" t="inlineStr">
+      <c r="B54" s="10" t="inlineStr">
         <is>
           <t>PS_AnnRng</t>
         </is>
       </c>
-      <c r="C54" s="12" t="inlineStr">
+      <c r="C54" s="29" t="inlineStr">
         <is>
           <t>PS_Annual_Range</t>
         </is>
       </c>
-      <c r="D54" s="13" t="inlineStr">
+      <c r="D54" s="18" t="inlineStr">
         <is>
           <t>04_Surface_Pressure (الضغط السطحي)</t>
         </is>
       </c>
-      <c r="E54" s="14" t="inlineStr">
+      <c r="E54" s="12" t="inlineStr">
         <is>
           <t>المدى البارومتري السنوي للضغط السطحي (الفارق بين أعلى وأدنى متوسط شهري للضغط السطحي).</t>
         </is>
       </c>
-      <c r="F54" s="15" t="inlineStr">
+      <c r="F54" s="19" t="inlineStr">
         <is>
           <t>hPa / mbar</t>
         </is>
       </c>
-      <c r="G54" s="16" t="inlineStr">
+      <c r="G54" s="30" t="inlineStr">
         <is>
           <t>خريطة المدى السنوي للضغط الجوي السطحي (hPa)</t>
         </is>
       </c>
     </row>
     <row r="55" ht="24" customHeight="1">
-      <c r="A55" s="17" t="n">
+      <c r="A55" s="3" t="n">
         <v>54</v>
       </c>
-      <c r="B55" s="18" t="inlineStr">
+      <c r="B55" s="5" t="inlineStr">
         <is>
           <t>WSp_AnMean</t>
         </is>
       </c>
-      <c r="C55" s="19" t="inlineStr">
+      <c r="C55" s="31" t="inlineStr">
         <is>
           <t>W_Spd_Annual_Mean</t>
         </is>
       </c>
-      <c r="D55" s="20" t="inlineStr">
+      <c r="D55" s="15" t="inlineStr">
         <is>
           <t>05_Wind (الرياح)</t>
         </is>
       </c>
-      <c r="E55" s="21" t="inlineStr">
+      <c r="E55" s="7" t="inlineStr">
         <is>
           <t>المتوسط السنوي لسرعة الرياح عند ارتفاع 10 أمتار فوق سطح الأرض.</t>
         </is>
       </c>
-      <c r="F55" s="22" t="inlineStr">
+      <c r="F55" s="16" t="inlineStr">
         <is>
           <t>م/ث (m/s)</t>
         </is>
       </c>
-      <c r="G55" s="23" t="inlineStr">
+      <c r="G55" s="32" t="inlineStr">
         <is>
           <t>خريطة المتوسط السنوي لسرعة الرياح (م/ث)</t>
         </is>
       </c>
     </row>
     <row r="56" ht="24" customHeight="1">
-      <c r="A56" s="10" t="n">
+      <c r="A56" s="8" t="n">
         <v>55</v>
       </c>
-      <c r="B56" s="11" t="inlineStr">
+      <c r="B56" s="10" t="inlineStr">
         <is>
           <t>WSp_WnMean</t>
         </is>
       </c>
-      <c r="C56" s="12" t="inlineStr">
+      <c r="C56" s="29" t="inlineStr">
         <is>
           <t>W_Spd_Winter_Mean</t>
         </is>
       </c>
-      <c r="D56" s="13" t="inlineStr">
+      <c r="D56" s="18" t="inlineStr">
         <is>
           <t>05_Wind (الرياح)</t>
         </is>
       </c>
-      <c r="E56" s="14" t="inlineStr">
+      <c r="E56" s="12" t="inlineStr">
         <is>
           <t>متوسط سرعة الرياح لفصل الشتاء الأرصادي عند ارتفاع 10 أمتار (DJF).</t>
         </is>
       </c>
-      <c r="F56" s="15" t="inlineStr">
+      <c r="F56" s="19" t="inlineStr">
         <is>
           <t>م/ث (m/s)</t>
         </is>
       </c>
-      <c r="G56" s="16" t="inlineStr">
+      <c r="G56" s="30" t="inlineStr">
         <is>
           <t>خريطة متوسط سرعة الرياح خلال فصل الشتاء (م/ث)</t>
         </is>
       </c>
     </row>
     <row r="57" ht="24" customHeight="1">
-      <c r="A57" s="17" t="n">
+      <c r="A57" s="3" t="n">
         <v>56</v>
       </c>
-      <c r="B57" s="18" t="inlineStr">
+      <c r="B57" s="5" t="inlineStr">
         <is>
           <t>WSp_SpMean</t>
         </is>
       </c>
-      <c r="C57" s="19" t="inlineStr">
+      <c r="C57" s="31" t="inlineStr">
         <is>
           <t>W_Spd_Spring_Mean</t>
         </is>
       </c>
-      <c r="D57" s="20" t="inlineStr">
+      <c r="D57" s="15" t="inlineStr">
         <is>
           <t>05_Wind (الرياح)</t>
         </is>
       </c>
-      <c r="E57" s="21" t="inlineStr">
+      <c r="E57" s="7" t="inlineStr">
         <is>
           <t>متوسط سرعة الرياح لفصل الربيع الأرصادي عند ارتفاع 10 أمتار (MAM).</t>
         </is>
       </c>
-      <c r="F57" s="22" t="inlineStr">
+      <c r="F57" s="16" t="inlineStr">
         <is>
           <t>م/ث (m/s)</t>
         </is>
       </c>
-      <c r="G57" s="23" t="inlineStr">
+      <c r="G57" s="32" t="inlineStr">
         <is>
           <t>خريطة متوسط سرعة الرياح خلال فصل الربيع (م/ث)</t>
         </is>
       </c>
     </row>
     <row r="58" ht="24" customHeight="1">
-      <c r="A58" s="10" t="n">
+      <c r="A58" s="8" t="n">
         <v>57</v>
       </c>
-      <c r="B58" s="11" t="inlineStr">
+      <c r="B58" s="10" t="inlineStr">
         <is>
           <t>WSp_SuMean</t>
         </is>
       </c>
-      <c r="C58" s="12" t="inlineStr">
+      <c r="C58" s="29" t="inlineStr">
         <is>
           <t>W_Spd_Summer_Mean</t>
         </is>
       </c>
-      <c r="D58" s="13" t="inlineStr">
+      <c r="D58" s="18" t="inlineStr">
         <is>
           <t>05_Wind (الرياح)</t>
         </is>
       </c>
-      <c r="E58" s="14" t="inlineStr">
+      <c r="E58" s="12" t="inlineStr">
         <is>
           <t>متوسط سرعة الرياح لفصل الصيف الأرصادي عند ارتفاع 10 أمتار (JJA).</t>
         </is>
       </c>
-      <c r="F58" s="15" t="inlineStr">
+      <c r="F58" s="19" t="inlineStr">
         <is>
           <t>م/ث (m/s)</t>
         </is>
       </c>
-      <c r="G58" s="16" t="inlineStr">
+      <c r="G58" s="30" t="inlineStr">
         <is>
           <t>خريطة متوسط سرعة الرياح خلال فصل الصيف (م/ث)</t>
         </is>
       </c>
     </row>
     <row r="59" ht="24" customHeight="1">
-      <c r="A59" s="17" t="n">
+      <c r="A59" s="3" t="n">
         <v>58</v>
       </c>
-      <c r="B59" s="18" t="inlineStr">
+      <c r="B59" s="5" t="inlineStr">
         <is>
           <t>WSp_AuMean</t>
         </is>
       </c>
-      <c r="C59" s="19" t="inlineStr">
+      <c r="C59" s="31" t="inlineStr">
         <is>
           <t>W_Spd_Autumn_Mean</t>
         </is>
       </c>
-      <c r="D59" s="20" t="inlineStr">
+      <c r="D59" s="15" t="inlineStr">
         <is>
           <t>05_Wind (الرياح)</t>
         </is>
       </c>
-      <c r="E59" s="21" t="inlineStr">
+      <c r="E59" s="7" t="inlineStr">
         <is>
           <t>متوسط سرعة الرياح لفصل الخريف الأرصادي عند ارتفاع 10 أمتار (SON).</t>
         </is>
       </c>
-      <c r="F59" s="22" t="inlineStr">
+      <c r="F59" s="16" t="inlineStr">
         <is>
           <t>م/ث (m/s)</t>
         </is>
       </c>
-      <c r="G59" s="23" t="inlineStr">
+      <c r="G59" s="32" t="inlineStr">
         <is>
           <t>خريطة متوسط سرعة الرياح خلال فصل الخريف (م/ث)</t>
         </is>
       </c>
     </row>
     <row r="60" ht="24" customHeight="1">
-      <c r="A60" s="10" t="n">
+      <c r="A60" s="8" t="n">
         <v>59</v>
       </c>
-      <c r="B60" s="11" t="inlineStr">
+      <c r="B60" s="10" t="inlineStr">
         <is>
           <t>WSp_MaxMo</t>
         </is>
       </c>
-      <c r="C60" s="12" t="inlineStr">
+      <c r="C60" s="29" t="inlineStr">
         <is>
           <t>W_Spd_Annual_Max_Month</t>
         </is>
       </c>
-      <c r="D60" s="13" t="inlineStr">
+      <c r="D60" s="18" t="inlineStr">
         <is>
           <t>05_Wind (الرياح)</t>
         </is>
       </c>
-      <c r="E60" s="14" t="inlineStr">
+      <c r="E60" s="12" t="inlineStr">
         <is>
           <t>أقصى متوسط شهري مسجل لسرعة الرياح في السنة (ذروة النشاط الريحي).</t>
         </is>
       </c>
-      <c r="F60" s="15" t="inlineStr">
+      <c r="F60" s="19" t="inlineStr">
         <is>
           <t>م/ث (m/s)</t>
         </is>
       </c>
-      <c r="G60" s="16" t="inlineStr">
+      <c r="G60" s="30" t="inlineStr">
         <is>
           <t>خريطة أقصى متوسط شهري لسرعة الرياح (م/ث)</t>
         </is>
       </c>
     </row>
     <row r="61" ht="24" customHeight="1">
-      <c r="A61" s="17" t="n">
+      <c r="A61" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="B61" s="18" t="inlineStr">
+      <c r="B61" s="5" t="inlineStr">
         <is>
           <t>WSp_MinMo</t>
         </is>
       </c>
-      <c r="C61" s="19" t="inlineStr">
+      <c r="C61" s="31" t="inlineStr">
         <is>
           <t>W_Spd_Annual_Min_Month</t>
         </is>
       </c>
-      <c r="D61" s="20" t="inlineStr">
+      <c r="D61" s="15" t="inlineStr">
         <is>
           <t>05_Wind (الرياح)</t>
         </is>
       </c>
-      <c r="E61" s="21" t="inlineStr">
+      <c r="E61" s="7" t="inlineStr">
         <is>
           <t>أدنى متوسط شهري مسجل لسرعة الرياح في السنة (فترة الهدوء الريحي).</t>
         </is>
       </c>
-      <c r="F61" s="22" t="inlineStr">
+      <c r="F61" s="16" t="inlineStr">
         <is>
           <t>م/ث (m/s)</t>
         </is>
       </c>
-      <c r="G61" s="23" t="inlineStr">
+      <c r="G61" s="32" t="inlineStr">
         <is>
           <t>خريطة أدنى متوسط شهري لسرعة الرياح (م/ث)</t>
         </is>
       </c>
     </row>
     <row r="62" ht="24" customHeight="1">
-      <c r="A62" s="10" t="n">
+      <c r="A62" s="8" t="n">
         <v>61</v>
       </c>
-      <c r="B62" s="11" t="inlineStr">
+      <c r="B62" s="10" t="inlineStr">
         <is>
           <t>WSp_AnRng</t>
         </is>
       </c>
-      <c r="C62" s="12" t="inlineStr">
+      <c r="C62" s="29" t="inlineStr">
         <is>
           <t>W_Spd_Annual_Range</t>
         </is>
       </c>
-      <c r="D62" s="13" t="inlineStr">
+      <c r="D62" s="18" t="inlineStr">
         <is>
           <t>05_Wind (الرياح)</t>
         </is>
       </c>
-      <c r="E62" s="14" t="inlineStr">
+      <c r="E62" s="12" t="inlineStr">
         <is>
           <t>المدى السنوي لسرعة الرياح (الفارق بين أشد شهور السنة رياحاً وأهدأها سرعة).</t>
         </is>
       </c>
-      <c r="F62" s="15" t="inlineStr">
+      <c r="F62" s="19" t="inlineStr">
         <is>
           <t>م/ث (m/s)</t>
         </is>
       </c>
-      <c r="G62" s="16" t="inlineStr">
+      <c r="G62" s="30" t="inlineStr">
         <is>
           <t>خريطة المدى السنوي لسرعة الرياح (م/ث)</t>
         </is>
       </c>
     </row>
     <row r="63" ht="24" customHeight="1">
-      <c r="A63" s="17" t="n">
+      <c r="A63" s="3" t="n">
         <v>62</v>
       </c>
-      <c r="B63" s="18" t="inlineStr">
+      <c r="B63" s="5" t="inlineStr">
         <is>
           <t>WDr_AnMean</t>
         </is>
       </c>
-      <c r="C63" s="19" t="inlineStr">
+      <c r="C63" s="31" t="inlineStr">
         <is>
           <t>W_Dir_Annual_Mean</t>
         </is>
       </c>
-      <c r="D63" s="20" t="inlineStr">
+      <c r="D63" s="15" t="inlineStr">
         <is>
           <t>05_Wind (الرياح)</t>
         </is>
       </c>
-      <c r="E63" s="21" t="inlineStr">
+      <c r="E63" s="7" t="inlineStr">
         <is>
           <t>الاتجاه السائد السنوي للرياح بالدرجات الزاوية (محسوب بالمتوسط الدائري للمتجهات الدائرية atan2).</t>
         </is>
       </c>
-      <c r="F63" s="22" t="inlineStr">
+      <c r="F63" s="16" t="inlineStr">
         <is>
           <t>درجة (°)</t>
         </is>
       </c>
-      <c r="G63" s="23" t="inlineStr">
+      <c r="G63" s="32" t="inlineStr">
         <is>
           <t>خريطة الاتجاه السائد السنوي للرياح (درجات)</t>
         </is>
       </c>
     </row>
     <row r="64" ht="24" customHeight="1">
-      <c r="A64" s="10" t="n">
+      <c r="A64" s="8" t="n">
         <v>63</v>
       </c>
-      <c r="B64" s="11" t="inlineStr">
+      <c r="B64" s="10" t="inlineStr">
         <is>
           <t>WDr_WnMean</t>
         </is>
       </c>
-      <c r="C64" s="12" t="inlineStr">
+      <c r="C64" s="29" t="inlineStr">
         <is>
           <t>W_Dir_Winter_Mean</t>
         </is>
       </c>
-      <c r="D64" s="13" t="inlineStr">
+      <c r="D64" s="18" t="inlineStr">
         <is>
           <t>05_Wind (الرياح)</t>
         </is>
       </c>
-      <c r="E64" s="14" t="inlineStr">
+      <c r="E64" s="12" t="inlineStr">
         <is>
           <t>اتجاه الرياح السائد خلال فصل الشتاء الأرصادي بالدرجات الزاوية (DJF).</t>
         </is>
       </c>
-      <c r="F64" s="15" t="inlineStr">
+      <c r="F64" s="19" t="inlineStr">
         <is>
           <t>درجة (°)</t>
         </is>
       </c>
-      <c r="G64" s="16" t="inlineStr">
+      <c r="G64" s="30" t="inlineStr">
         <is>
           <t>خريطة اتجاه الرياح السائد خلال فصل الشتاء (درجات)</t>
         </is>
       </c>
     </row>
     <row r="65" ht="24" customHeight="1">
-      <c r="A65" s="17" t="n">
+      <c r="A65" s="3" t="n">
         <v>64</v>
       </c>
-      <c r="B65" s="18" t="inlineStr">
+      <c r="B65" s="5" t="inlineStr">
         <is>
           <t>WDr_SpMean</t>
         </is>
       </c>
-      <c r="C65" s="19" t="inlineStr">
+      <c r="C65" s="31" t="inlineStr">
         <is>
           <t>W_Dir_Spring_Mean</t>
         </is>
       </c>
-      <c r="D65" s="20" t="inlineStr">
+      <c r="D65" s="15" t="inlineStr">
         <is>
           <t>05_Wind (الرياح)</t>
         </is>
       </c>
-      <c r="E65" s="21" t="inlineStr">
+      <c r="E65" s="7" t="inlineStr">
         <is>
           <t>اتجاه الرياح السائد خلال فصل الربيع الأرصادي بالدرجات الزاوية (MAM).</t>
         </is>
       </c>
-      <c r="F65" s="22" t="inlineStr">
+      <c r="F65" s="16" t="inlineStr">
         <is>
           <t>درجة (°)</t>
         </is>
       </c>
-      <c r="G65" s="23" t="inlineStr">
+      <c r="G65" s="32" t="inlineStr">
         <is>
           <t>خريطة اتجاه الرياح السائد خلال فصل الربيع (درجات)</t>
         </is>
       </c>
     </row>
     <row r="66" ht="24" customHeight="1">
-      <c r="A66" s="10" t="n">
+      <c r="A66" s="8" t="n">
         <v>65</v>
       </c>
-      <c r="B66" s="11" t="inlineStr">
+      <c r="B66" s="10" t="inlineStr">
         <is>
           <t>WDr_SuMean</t>
         </is>
       </c>
-      <c r="C66" s="12" t="inlineStr">
+      <c r="C66" s="29" t="inlineStr">
         <is>
           <t>W_Dir_Summer_Mean</t>
         </is>
       </c>
-      <c r="D66" s="13" t="inlineStr">
+      <c r="D66" s="18" t="inlineStr">
         <is>
           <t>05_Wind (الرياح)</t>
         </is>
       </c>
-      <c r="E66" s="14" t="inlineStr">
+      <c r="E66" s="12" t="inlineStr">
         <is>
           <t>اتجاه الرياح السائد خلال فصل الصيف الأرصادي بالدرجات الزاوية (JJA).</t>
         </is>
       </c>
-      <c r="F66" s="15" t="inlineStr">
+      <c r="F66" s="19" t="inlineStr">
         <is>
           <t>درجة (°)</t>
         </is>
       </c>
-      <c r="G66" s="16" t="inlineStr">
+      <c r="G66" s="30" t="inlineStr">
         <is>
           <t>خريطة اتجاه الرياح السائد خلال فصل الصيف (درجات)</t>
         </is>
       </c>
     </row>
     <row r="67" ht="24" customHeight="1">
-      <c r="A67" s="17" t="n">
+      <c r="A67" s="3" t="n">
         <v>66</v>
       </c>
-      <c r="B67" s="18" t="inlineStr">
+      <c r="B67" s="5" t="inlineStr">
         <is>
           <t>WDr_AuMean</t>
         </is>
       </c>
-      <c r="C67" s="19" t="inlineStr">
+      <c r="C67" s="31" t="inlineStr">
         <is>
           <t>W_Dir_Autumn_Mean</t>
         </is>
       </c>
-      <c r="D67" s="20" t="inlineStr">
+      <c r="D67" s="15" t="inlineStr">
         <is>
           <t>05_Wind (الرياح)</t>
         </is>
       </c>
-      <c r="E67" s="21" t="inlineStr">
+      <c r="E67" s="7" t="inlineStr">
         <is>
           <t>اتجاه الرياح السائد خلال فصل الخريف الأرصادي بالدرجات الزاوية (SON).</t>
         </is>
       </c>
-      <c r="F67" s="22" t="inlineStr">
+      <c r="F67" s="16" t="inlineStr">
         <is>
           <t>درجة (°)</t>
         </is>
       </c>
-      <c r="G67" s="23" t="inlineStr">
+      <c r="G67" s="32" t="inlineStr">
         <is>
           <t>خريطة اتجاه الرياح السائد خلال فصل الخريف (درجات)</t>
         </is>
       </c>
     </row>
     <row r="68" ht="24" customHeight="1">
-      <c r="A68" s="10" t="n">
+      <c r="A68" s="8" t="n">
         <v>67</v>
       </c>
-      <c r="B68" s="11" t="inlineStr">
+      <c r="B68" s="10" t="inlineStr">
         <is>
           <t>RH_AnMean</t>
         </is>
       </c>
-      <c r="C68" s="12" t="inlineStr">
+      <c r="C68" s="29" t="inlineStr">
         <is>
           <t>RH_Annual_Mean</t>
         </is>
       </c>
-      <c r="D68" s="13" t="inlineStr">
+      <c r="D68" s="18" t="inlineStr">
         <is>
           <t>06_Relative_Humidity (الرطوبة النسبية)</t>
         </is>
       </c>
-      <c r="E68" s="14" t="inlineStr">
+      <c r="E68" s="12" t="inlineStr">
         <is>
           <t>المتوسط الحسابي السنوي للرطوبة النسبية للهواء عند ارتفاع 2 متر كنسبة مئوية.</t>
         </is>
       </c>
-      <c r="F68" s="15" t="inlineStr">
+      <c r="F68" s="19" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="G68" s="16" t="inlineStr">
+      <c r="G68" s="30" t="inlineStr">
         <is>
           <t>خريطة المتوسط السنوي للرطوبة النسبية (%)</t>
         </is>
       </c>
     </row>
     <row r="69" ht="24" customHeight="1">
-      <c r="A69" s="17" t="n">
+      <c r="A69" s="3" t="n">
         <v>68</v>
       </c>
-      <c r="B69" s="18" t="inlineStr">
+      <c r="B69" s="5" t="inlineStr">
         <is>
           <t>RH_WnMean</t>
         </is>
       </c>
-      <c r="C69" s="19" t="inlineStr">
+      <c r="C69" s="31" t="inlineStr">
         <is>
           <t>RH_Winter_Mean</t>
         </is>
       </c>
-      <c r="D69" s="20" t="inlineStr">
+      <c r="D69" s="15" t="inlineStr">
         <is>
           <t>06_Relative_Humidity (الرطوبة النسبية)</t>
         </is>
       </c>
-      <c r="E69" s="21" t="inlineStr">
+      <c r="E69" s="7" t="inlineStr">
         <is>
           <t>متوسط الرطوبة النسبية لفصل الشتاء الأرصادي (DJF).</t>
         </is>
       </c>
-      <c r="F69" s="22" t="inlineStr">
+      <c r="F69" s="16" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="G69" s="23" t="inlineStr">
+      <c r="G69" s="32" t="inlineStr">
         <is>
           <t>خريطة متوسط الرطوبة النسبية خلال فصل الشتاء (%)</t>
         </is>
       </c>
     </row>
     <row r="70" ht="24" customHeight="1">
-      <c r="A70" s="10" t="n">
+      <c r="A70" s="8" t="n">
         <v>69</v>
       </c>
-      <c r="B70" s="11" t="inlineStr">
+      <c r="B70" s="10" t="inlineStr">
         <is>
           <t>RH_SpMean</t>
         </is>
       </c>
-      <c r="C70" s="12" t="inlineStr">
+      <c r="C70" s="29" t="inlineStr">
         <is>
           <t>RH_Spring_Mean</t>
         </is>
       </c>
-      <c r="D70" s="13" t="inlineStr">
+      <c r="D70" s="18" t="inlineStr">
         <is>
           <t>06_Relative_Humidity (الرطوبة النسبية)</t>
         </is>
       </c>
-      <c r="E70" s="14" t="inlineStr">
+      <c r="E70" s="12" t="inlineStr">
         <is>
           <t>متوسط الرطوبة النسبية لفصل الربيع الأرصادي (MAM).</t>
         </is>
       </c>
-      <c r="F70" s="15" t="inlineStr">
+      <c r="F70" s="19" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="G70" s="16" t="inlineStr">
+      <c r="G70" s="30" t="inlineStr">
         <is>
           <t>خريطة متوسط الرطوبة النسبية خلال فصل الربيع (%)</t>
         </is>
       </c>
     </row>
     <row r="71" ht="24" customHeight="1">
-      <c r="A71" s="17" t="n">
+      <c r="A71" s="3" t="n">
         <v>70</v>
       </c>
-      <c r="B71" s="18" t="inlineStr">
+      <c r="B71" s="5" t="inlineStr">
         <is>
           <t>RH_SuMean</t>
         </is>
       </c>
-      <c r="C71" s="19" t="inlineStr">
+      <c r="C71" s="31" t="inlineStr">
         <is>
           <t>RH_Summer_Mean</t>
         </is>
       </c>
-      <c r="D71" s="20" t="inlineStr">
+      <c r="D71" s="15" t="inlineStr">
         <is>
           <t>06_Relative_Humidity (الرطوبة النسبية)</t>
         </is>
       </c>
-      <c r="E71" s="21" t="inlineStr">
+      <c r="E71" s="7" t="inlineStr">
         <is>
           <t>متوسط الرطوبة النسبية لفصل الصيف الأرصادي (JJA).</t>
         </is>
       </c>
-      <c r="F71" s="22" t="inlineStr">
+      <c r="F71" s="16" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="G71" s="23" t="inlineStr">
+      <c r="G71" s="32" t="inlineStr">
         <is>
           <t>خريطة متوسط الرطوبة النسبية خلال فصل الصيف (%)</t>
         </is>
       </c>
     </row>
     <row r="72" ht="24" customHeight="1">
-      <c r="A72" s="10" t="n">
+      <c r="A72" s="8" t="n">
         <v>71</v>
       </c>
-      <c r="B72" s="11" t="inlineStr">
+      <c r="B72" s="10" t="inlineStr">
         <is>
           <t>RH_AuMean</t>
         </is>
       </c>
-      <c r="C72" s="12" t="inlineStr">
+      <c r="C72" s="29" t="inlineStr">
         <is>
           <t>RH_Autumn_Mean</t>
         </is>
       </c>
-      <c r="D72" s="13" t="inlineStr">
+      <c r="D72" s="18" t="inlineStr">
         <is>
           <t>06_Relative_Humidity (الرطوبة النسبية)</t>
         </is>
       </c>
-      <c r="E72" s="14" t="inlineStr">
+      <c r="E72" s="12" t="inlineStr">
         <is>
           <t>متوسط الرطوبة النسبية لفصل الخريف الأرصادي (SON).</t>
         </is>
       </c>
-      <c r="F72" s="15" t="inlineStr">
+      <c r="F72" s="19" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="G72" s="16" t="inlineStr">
+      <c r="G72" s="30" t="inlineStr">
         <is>
           <t>خريطة متوسط الرطوبة النسبية خلال فصل الخريف (%)</t>
         </is>
       </c>
     </row>
     <row r="73" ht="24" customHeight="1">
-      <c r="A73" s="17" t="n">
+      <c r="A73" s="3" t="n">
         <v>72</v>
       </c>
-      <c r="B73" s="18" t="inlineStr">
+      <c r="B73" s="5" t="inlineStr">
         <is>
           <t>RH_AnRng</t>
         </is>
       </c>
-      <c r="C73" s="19" t="inlineStr">
+      <c r="C73" s="31" t="inlineStr">
         <is>
           <t>RH_Annual_Range</t>
         </is>
       </c>
-      <c r="D73" s="20" t="inlineStr">
+      <c r="D73" s="15" t="inlineStr">
         <is>
           <t>06_Relative_Humidity (الرطوبة النسبية)</t>
         </is>
       </c>
-      <c r="E73" s="21" t="inlineStr">
+      <c r="E73" s="7" t="inlineStr">
         <is>
           <t>المدى السنوي للرطوبة النسبية (الفارق بين أعلى شهر رطوبة وأدنى شهر رطوبة).</t>
         </is>
       </c>
-      <c r="F73" s="22" t="inlineStr">
+      <c r="F73" s="16" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="G73" s="23" t="inlineStr">
+      <c r="G73" s="32" t="inlineStr">
         <is>
           <t>خريطة المدى السنوي للرطوبة النسبية (%)</t>
         </is>
       </c>
     </row>
     <row r="74" ht="24" customHeight="1">
-      <c r="A74" s="10" t="n">
+      <c r="A74" s="8" t="n">
         <v>73</v>
       </c>
-      <c r="B74" s="11" t="inlineStr">
+      <c r="B74" s="10" t="inlineStr">
         <is>
           <t>Sol_AnMean</t>
         </is>
       </c>
-      <c r="C74" s="12" t="inlineStr">
+      <c r="C74" s="29" t="inlineStr">
         <is>
           <t>Sol_Annual_Mean</t>
         </is>
       </c>
-      <c r="D74" s="13" t="inlineStr">
+      <c r="D74" s="18" t="inlineStr">
         <is>
           <t>08_Solar_Radiation (الإشعاع الشمسي)</t>
         </is>
       </c>
-      <c r="E74" s="14" t="inlineStr">
+      <c r="E74" s="12" t="inlineStr">
         <is>
           <t>المتوسط اليومي السنوي للإشعاع الشمسي الكلي السطحي الواصل لسطح الأرض في كافة ظروف السماء.</t>
         </is>
       </c>
-      <c r="F74" s="15" t="inlineStr">
+      <c r="F74" s="19" t="inlineStr">
         <is>
           <t>kWh/m²/day</t>
         </is>
       </c>
-      <c r="G74" s="16" t="inlineStr">
+      <c r="G74" s="30" t="inlineStr">
         <is>
           <t>خريطة المتوسط اليومي السنوي للإشعاع الشمسي (kWh/m²/day)</t>
         </is>
       </c>
     </row>
     <row r="75" ht="24" customHeight="1">
-      <c r="A75" s="17" t="n">
+      <c r="A75" s="3" t="n">
         <v>74</v>
       </c>
-      <c r="B75" s="18" t="inlineStr">
+      <c r="B75" s="5" t="inlineStr">
         <is>
           <t>Sol_AnTot</t>
         </is>
       </c>
-      <c r="C75" s="19" t="inlineStr">
+      <c r="C75" s="31" t="inlineStr">
         <is>
           <t>Sol_Annual_Total</t>
         </is>
       </c>
-      <c r="D75" s="20" t="inlineStr">
+      <c r="D75" s="15" t="inlineStr">
         <is>
           <t>08_Solar_Radiation (الإشعاع الشمسي)</t>
         </is>
       </c>
-      <c r="E75" s="21" t="inlineStr">
+      <c r="E75" s="7" t="inlineStr">
         <is>
           <t>إجمالي الطاقة الشمسية السنوية التراكمية الساقطة على المتر المربع في السنة كاملة.</t>
         </is>
       </c>
-      <c r="F75" s="22" t="inlineStr">
+      <c r="F75" s="16" t="inlineStr">
         <is>
           <t>kWh/m²/year</t>
         </is>
       </c>
-      <c r="G75" s="23" t="inlineStr">
+      <c r="G75" s="32" t="inlineStr">
         <is>
           <t>خريطة إجمالي الطاقة الشمسية السنوية التراكمية (kWh/m²/year)</t>
         </is>
       </c>
     </row>
     <row r="76" ht="24" customHeight="1">
-      <c r="A76" s="10" t="n">
+      <c r="A76" s="8" t="n">
         <v>75</v>
       </c>
-      <c r="B76" s="11" t="inlineStr">
+      <c r="B76" s="10" t="inlineStr">
         <is>
           <t>Sol_WnMean</t>
         </is>
       </c>
-      <c r="C76" s="12" t="inlineStr">
+      <c r="C76" s="29" t="inlineStr">
         <is>
           <t>Sol_Winter_Mean</t>
         </is>
       </c>
-      <c r="D76" s="13" t="inlineStr">
+      <c r="D76" s="18" t="inlineStr">
         <is>
           <t>08_Solar_Radiation (الإشعاع الشمسي)</t>
         </is>
       </c>
-      <c r="E76" s="14" t="inlineStr">
+      <c r="E76" s="12" t="inlineStr">
         <is>
           <t>متوسط الإشعاع الشمسي اليومي لفصل الشتاء الأرصادي (DJF).</t>
         </is>
       </c>
-      <c r="F76" s="15" t="inlineStr">
+      <c r="F76" s="19" t="inlineStr">
         <is>
           <t>kWh/m²/day</t>
         </is>
       </c>
-      <c r="G76" s="16" t="inlineStr">
+      <c r="G76" s="30" t="inlineStr">
         <is>
           <t>خريطة متوسط الإشعاع الشمسي خلال فصل الشتاء (kWh/m²/day)</t>
         </is>
       </c>
     </row>
     <row r="77" ht="24" customHeight="1">
-      <c r="A77" s="17" t="n">
+      <c r="A77" s="3" t="n">
         <v>76</v>
       </c>
-      <c r="B77" s="18" t="inlineStr">
+      <c r="B77" s="5" t="inlineStr">
         <is>
           <t>Sol_SpMean</t>
         </is>
       </c>
-      <c r="C77" s="19" t="inlineStr">
+      <c r="C77" s="31" t="inlineStr">
         <is>
           <t>Sol_Spring_Mean</t>
         </is>
       </c>
-      <c r="D77" s="20" t="inlineStr">
+      <c r="D77" s="15" t="inlineStr">
         <is>
           <t>08_Solar_Radiation (الإشعاع الشمسي)</t>
         </is>
       </c>
-      <c r="E77" s="21" t="inlineStr">
+      <c r="E77" s="7" t="inlineStr">
         <is>
           <t>متوسط الإشعاع الشمسي اليومي لفصل الربيع الأرصادي (MAM).</t>
         </is>
       </c>
-      <c r="F77" s="22" t="inlineStr">
+      <c r="F77" s="16" t="inlineStr">
         <is>
           <t>kWh/m²/day</t>
         </is>
       </c>
-      <c r="G77" s="23" t="inlineStr">
+      <c r="G77" s="32" t="inlineStr">
         <is>
           <t>خريطة متوسط الإشعاع الشمسي خلال فصل الربيع (kWh/m²/day)</t>
         </is>
       </c>
     </row>
     <row r="78" ht="24" customHeight="1">
-      <c r="A78" s="10" t="n">
+      <c r="A78" s="8" t="n">
         <v>77</v>
       </c>
-      <c r="B78" s="11" t="inlineStr">
+      <c r="B78" s="10" t="inlineStr">
         <is>
           <t>Sol_SuMean</t>
         </is>
       </c>
-      <c r="C78" s="12" t="inlineStr">
+      <c r="C78" s="29" t="inlineStr">
         <is>
           <t>Sol_Summer_Mean</t>
         </is>
       </c>
-      <c r="D78" s="13" t="inlineStr">
+      <c r="D78" s="18" t="inlineStr">
         <is>
           <t>08_Solar_Radiation (الإشعاع الشمسي)</t>
         </is>
       </c>
-      <c r="E78" s="14" t="inlineStr">
+      <c r="E78" s="12" t="inlineStr">
         <is>
           <t>متوسط الإشعاع الشمسي اليومي لفصل الصيف الأرصادي (JJA).</t>
         </is>
       </c>
-      <c r="F78" s="15" t="inlineStr">
+      <c r="F78" s="19" t="inlineStr">
         <is>
           <t>kWh/m²/day</t>
         </is>
       </c>
-      <c r="G78" s="16" t="inlineStr">
+      <c r="G78" s="30" t="inlineStr">
         <is>
           <t>خريطة متوسط الإشعاع الشمسي خلال فصل الصيف (kWh/m²/day)</t>
         </is>
       </c>
     </row>
     <row r="79" ht="24" customHeight="1">
-      <c r="A79" s="17" t="n">
+      <c r="A79" s="3" t="n">
         <v>78</v>
       </c>
-      <c r="B79" s="18" t="inlineStr">
+      <c r="B79" s="5" t="inlineStr">
         <is>
           <t>Sol_AuMean</t>
         </is>
       </c>
-      <c r="C79" s="19" t="inlineStr">
+      <c r="C79" s="31" t="inlineStr">
         <is>
           <t>Sol_Autumn_Mean</t>
         </is>
       </c>
-      <c r="D79" s="20" t="inlineStr">
+      <c r="D79" s="15" t="inlineStr">
         <is>
           <t>08_Solar_Radiation (الإشعاع الشمسي)</t>
         </is>
       </c>
-      <c r="E79" s="21" t="inlineStr">
+      <c r="E79" s="7" t="inlineStr">
         <is>
           <t>متوسط الإشعاع الشمسي اليومي لفصل الخريف الأرصادي (SON).</t>
         </is>
       </c>
-      <c r="F79" s="22" t="inlineStr">
+      <c r="F79" s="16" t="inlineStr">
         <is>
           <t>kWh/m²/day</t>
         </is>
       </c>
-      <c r="G79" s="23" t="inlineStr">
+      <c r="G79" s="32" t="inlineStr">
         <is>
           <t>خريطة متوسط الإشعاع الشمسي خلال فصل الخريف (kWh/m²/day)</t>
         </is>
       </c>
     </row>
     <row r="80" ht="24" customHeight="1">
-      <c r="A80" s="10" t="n">
+      <c r="A80" s="8" t="n">
         <v>79</v>
       </c>
-      <c r="B80" s="11" t="inlineStr">
+      <c r="B80" s="10" t="inlineStr">
         <is>
           <t>Sol_AnRng</t>
         </is>
       </c>
-      <c r="C80" s="12" t="inlineStr">
+      <c r="C80" s="29" t="inlineStr">
         <is>
           <t>Sol_Annual_Range</t>
         </is>
       </c>
-      <c r="D80" s="13" t="inlineStr">
+      <c r="D80" s="18" t="inlineStr">
         <is>
           <t>08_Solar_Radiation (الإشعاع الشمسي)</t>
         </is>
       </c>
-      <c r="E80" s="14" t="inlineStr">
+      <c r="E80" s="12" t="inlineStr">
         <is>
           <t>المدى السنوي للإشعاع الشمسي (الفارق بين ذروة الإشعاع في الصيف وأدناه في الشتاء).</t>
         </is>
       </c>
-      <c r="F80" s="15" t="inlineStr">
+      <c r="F80" s="19" t="inlineStr">
         <is>
           <t>kWh/m²/day</t>
         </is>
       </c>
-      <c r="G80" s="16" t="inlineStr">
+      <c r="G80" s="30" t="inlineStr">
         <is>
           <t>خريطة المدى السنوي للإشعاع الشمسي (kWh/m²/day)</t>
         </is>
       </c>
     </row>
     <row r="81" ht="24" customHeight="1">
-      <c r="A81" s="17" t="n">
+      <c r="A81" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="B81" s="18" t="inlineStr">
+      <c r="B81" s="5" t="inlineStr">
         <is>
           <t>UV_AnMean</t>
         </is>
       </c>
-      <c r="C81" s="19" t="inlineStr">
+      <c r="C81" s="31" t="inlineStr">
         <is>
           <t>UV_Annual_Mean</t>
         </is>
       </c>
-      <c r="D81" s="20" t="inlineStr">
+      <c r="D81" s="15" t="inlineStr">
         <is>
           <t>09_UV_Index (الأشعة فوق البنفسجية)</t>
         </is>
       </c>
-      <c r="E81" s="21" t="inlineStr">
+      <c r="E81" s="7" t="inlineStr">
         <is>
           <t>المتوسط السنوي لمؤشر الأشعة فوق البنفسجية عند الظهيرة وفق منظومة منظمة الصحة العالمية.</t>
         </is>
       </c>
-      <c r="F81" s="22" t="inlineStr">
+      <c r="F81" s="16" t="inlineStr">
         <is>
           <t>مؤشر (0-16+)</t>
         </is>
       </c>
-      <c r="G81" s="23" t="inlineStr">
+      <c r="G81" s="32" t="inlineStr">
         <is>
           <t>خريطة المتوسط السنوي لمؤشر الأشعة فوق البنفسجية (UV)</t>
         </is>
       </c>
     </row>
     <row r="82" ht="24" customHeight="1">
-      <c r="A82" s="10" t="n">
+      <c r="A82" s="8" t="n">
         <v>81</v>
       </c>
-      <c r="B82" s="11" t="inlineStr">
+      <c r="B82" s="10" t="inlineStr">
         <is>
           <t>UV_WnMean</t>
         </is>
       </c>
-      <c r="C82" s="12" t="inlineStr">
+      <c r="C82" s="29" t="inlineStr">
         <is>
           <t>UV_Winter_Mean</t>
         </is>
       </c>
-      <c r="D82" s="13" t="inlineStr">
+      <c r="D82" s="18" t="inlineStr">
         <is>
           <t>09_UV_Index (الأشعة فوق البنفسجية)</t>
         </is>
       </c>
-      <c r="E82" s="14" t="inlineStr">
+      <c r="E82" s="12" t="inlineStr">
         <is>
           <t>متوسط مؤشر الأشعة فوق البنفسجية لفصل الشتاء الأرصادي (DJF).</t>
         </is>
       </c>
-      <c r="F82" s="15" t="inlineStr">
+      <c r="F82" s="19" t="inlineStr">
         <is>
           <t>مؤشر (0-16+)</t>
         </is>
       </c>
-      <c r="G82" s="16" t="inlineStr">
+      <c r="G82" s="30" t="inlineStr">
         <is>
           <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية خلال فصل الشتاء</t>
         </is>
       </c>
     </row>
     <row r="83" ht="24" customHeight="1">
-      <c r="A83" s="17" t="n">
+      <c r="A83" s="3" t="n">
         <v>82</v>
       </c>
-      <c r="B83" s="18" t="inlineStr">
+      <c r="B83" s="5" t="inlineStr">
         <is>
           <t>UV_SpMean</t>
         </is>
       </c>
-      <c r="C83" s="19" t="inlineStr">
+      <c r="C83" s="31" t="inlineStr">
         <is>
           <t>UV_Spring_Mean</t>
         </is>
       </c>
-      <c r="D83" s="20" t="inlineStr">
+      <c r="D83" s="15" t="inlineStr">
         <is>
           <t>09_UV_Index (الأشعة فوق البنفسجية)</t>
         </is>
       </c>
-      <c r="E83" s="21" t="inlineStr">
+      <c r="E83" s="7" t="inlineStr">
         <is>
           <t>متوسط مؤشر الأشعة فوق البنفسجية لفصل الربيع الأرصادي (MAM).</t>
         </is>
       </c>
-      <c r="F83" s="22" t="inlineStr">
+      <c r="F83" s="16" t="inlineStr">
         <is>
           <t>مؤشر (0-16+)</t>
         </is>
       </c>
-      <c r="G83" s="23" t="inlineStr">
+      <c r="G83" s="32" t="inlineStr">
         <is>
           <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية خلال فصل الربيع</t>
         </is>
       </c>
     </row>
     <row r="84" ht="24" customHeight="1">
-      <c r="A84" s="10" t="n">
+      <c r="A84" s="8" t="n">
         <v>83</v>
       </c>
-      <c r="B84" s="11" t="inlineStr">
+      <c r="B84" s="10" t="inlineStr">
         <is>
           <t>UV_SuMean</t>
         </is>
       </c>
-      <c r="C84" s="12" t="inlineStr">
+      <c r="C84" s="29" t="inlineStr">
         <is>
           <t>UV_Summer_Mean</t>
         </is>
       </c>
-      <c r="D84" s="13" t="inlineStr">
+      <c r="D84" s="18" t="inlineStr">
         <is>
           <t>09_UV_Index (الأشعة فوق البنفسجية)</t>
         </is>
       </c>
-      <c r="E84" s="14" t="inlineStr">
+      <c r="E84" s="12" t="inlineStr">
         <is>
           <t>متوسط مؤشر الأشعة فوق البنفسجية لفصل الصيف الأرصادي (JJA - ذروة مخاطر الحروق الشمسية).</t>
         </is>
       </c>
-      <c r="F84" s="15" t="inlineStr">
+      <c r="F84" s="19" t="inlineStr">
         <is>
           <t>مؤشر (0-16+)</t>
         </is>
       </c>
-      <c r="G84" s="16" t="inlineStr">
+      <c r="G84" s="30" t="inlineStr">
         <is>
           <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية خلال فصل الصيف</t>
         </is>
       </c>
     </row>
     <row r="85" ht="24" customHeight="1">
-      <c r="A85" s="17" t="n">
+      <c r="A85" s="3" t="n">
         <v>84</v>
       </c>
-      <c r="B85" s="18" t="inlineStr">
+      <c r="B85" s="5" t="inlineStr">
         <is>
           <t>UV_AuMean</t>
         </is>
       </c>
-      <c r="C85" s="19" t="inlineStr">
+      <c r="C85" s="31" t="inlineStr">
         <is>
           <t>UV_Autumn_Mean</t>
         </is>
       </c>
-      <c r="D85" s="20" t="inlineStr">
+      <c r="D85" s="15" t="inlineStr">
         <is>
           <t>09_UV_Index (الأشعة فوق البنفسجية)</t>
         </is>
       </c>
-      <c r="E85" s="21" t="inlineStr">
+      <c r="E85" s="7" t="inlineStr">
         <is>
           <t>متوسط مؤشر الأشعة فوق البنفسجية لفصل الخريف الأرصادي (SON).</t>
         </is>
       </c>
-      <c r="F85" s="22" t="inlineStr">
+      <c r="F85" s="16" t="inlineStr">
         <is>
           <t>مؤشر (0-16+)</t>
         </is>
       </c>
-      <c r="G85" s="23" t="inlineStr">
+      <c r="G85" s="32" t="inlineStr">
         <is>
           <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية خلال فصل الخريف</t>
         </is>
       </c>
     </row>
     <row r="86" ht="24" customHeight="1">
-      <c r="A86" s="10" t="n">
+      <c r="A86" s="8" t="n">
         <v>85</v>
       </c>
-      <c r="B86" s="11" t="inlineStr">
+      <c r="B86" s="10" t="inlineStr">
         <is>
           <t>UV_AnRng</t>
         </is>
       </c>
-      <c r="C86" s="12" t="inlineStr">
+      <c r="C86" s="29" t="inlineStr">
         <is>
           <t>UV_Annual_Range</t>
         </is>
       </c>
-      <c r="D86" s="13" t="inlineStr">
+      <c r="D86" s="18" t="inlineStr">
         <is>
           <t>09_UV_Index (الأشعة فوق البنفسجية)</t>
         </is>
       </c>
-      <c r="E86" s="14" t="inlineStr">
+      <c r="E86" s="12" t="inlineStr">
         <is>
           <t>المدى السنوي لمؤشر الأشعة فوق البنفسجية (الفارق بين ذروة الصيف وأدنى مستويات الشتاء).</t>
         </is>
       </c>
-      <c r="F86" s="15" t="inlineStr">
+      <c r="F86" s="19" t="inlineStr">
         <is>
           <t>مؤشر (0-16+)</t>
         </is>
       </c>
-      <c r="G86" s="16" t="inlineStr">
+      <c r="G86" s="30" t="inlineStr">
         <is>
           <t>خريطة المدى السنوي لمؤشر الأشعة فوق البنفسجية</t>
         </is>
       </c>
     </row>
     <row r="87" ht="24" customHeight="1">
-      <c r="A87" s="17" t="n">
+      <c r="A87" s="3" t="n">
         <v>86</v>
       </c>
-      <c r="B87" s="18" t="inlineStr">
+      <c r="B87" s="5" t="inlineStr">
         <is>
           <t>Cld_AnMean</t>
         </is>
       </c>
-      <c r="C87" s="19" t="inlineStr">
+      <c r="C87" s="31" t="inlineStr">
         <is>
           <t>Cld_Annual_Mean</t>
         </is>
       </c>
-      <c r="D87" s="20" t="inlineStr">
+      <c r="D87" s="15" t="inlineStr">
         <is>
           <t>10_Cloud_Cover (الغطاء السحابي)</t>
         </is>
       </c>
-      <c r="E87" s="21" t="inlineStr">
+      <c r="E87" s="7" t="inlineStr">
         <is>
           <t>المتوسط السنوي لنسبة تغطية السماء بالغيوم والسحب كنسبة مئوية.</t>
         </is>
       </c>
-      <c r="F87" s="22" t="inlineStr">
+      <c r="F87" s="16" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="G87" s="23" t="inlineStr">
+      <c r="G87" s="32" t="inlineStr">
         <is>
           <t>خريطة المتوسط السنوي لنسبة الغطاء السحابي (%)</t>
         </is>
       </c>
     </row>
     <row r="88" ht="24" customHeight="1">
-      <c r="A88" s="10" t="n">
+      <c r="A88" s="8" t="n">
         <v>87</v>
       </c>
-      <c r="B88" s="11" t="inlineStr">
+      <c r="B88" s="10" t="inlineStr">
         <is>
           <t>Cld_WnMean</t>
         </is>
       </c>
-      <c r="C88" s="12" t="inlineStr">
+      <c r="C88" s="29" t="inlineStr">
         <is>
           <t>Cld_Winter_Mean</t>
         </is>
       </c>
-      <c r="D88" s="13" t="inlineStr">
+      <c r="D88" s="18" t="inlineStr">
         <is>
           <t>10_Cloud_Cover (الغطاء السحابي)</t>
         </is>
       </c>
-      <c r="E88" s="14" t="inlineStr">
+      <c r="E88" s="12" t="inlineStr">
         <is>
           <t>متوسط نسبة تغطية السحب لفصل الشتاء الأرصادي (DJF).</t>
         </is>
       </c>
-      <c r="F88" s="15" t="inlineStr">
+      <c r="F88" s="19" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="G88" s="16" t="inlineStr">
+      <c r="G88" s="30" t="inlineStr">
         <is>
           <t>خريطة متوسط الغطاء السحابي خلال فصل الشتاء (%)</t>
         </is>
       </c>
     </row>
     <row r="89" ht="24" customHeight="1">
-      <c r="A89" s="17" t="n">
+      <c r="A89" s="3" t="n">
         <v>88</v>
       </c>
-      <c r="B89" s="18" t="inlineStr">
+      <c r="B89" s="5" t="inlineStr">
         <is>
           <t>Cld_SpMean</t>
         </is>
       </c>
-      <c r="C89" s="19" t="inlineStr">
+      <c r="C89" s="31" t="inlineStr">
         <is>
           <t>Cld_Spring_Mean</t>
         </is>
       </c>
-      <c r="D89" s="20" t="inlineStr">
+      <c r="D89" s="15" t="inlineStr">
         <is>
           <t>10_Cloud_Cover (الغطاء السحابي)</t>
         </is>
       </c>
-      <c r="E89" s="21" t="inlineStr">
+      <c r="E89" s="7" t="inlineStr">
         <is>
           <t>متوسط نسبة تغطية السحب لفصل الربيع الأرصادي (MAM).</t>
         </is>
       </c>
-      <c r="F89" s="22" t="inlineStr">
+      <c r="F89" s="16" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="G89" s="23" t="inlineStr">
+      <c r="G89" s="32" t="inlineStr">
         <is>
           <t>خريطة متوسط الغطاء السحابي خلال فصل الربيع (%)</t>
         </is>
       </c>
     </row>
     <row r="90" ht="24" customHeight="1">
-      <c r="A90" s="10" t="n">
+      <c r="A90" s="8" t="n">
         <v>89</v>
       </c>
-      <c r="B90" s="11" t="inlineStr">
+      <c r="B90" s="10" t="inlineStr">
         <is>
           <t>Cld_SuMean</t>
         </is>
       </c>
-      <c r="C90" s="12" t="inlineStr">
+      <c r="C90" s="29" t="inlineStr">
         <is>
           <t>Cld_Summer_Mean</t>
         </is>
       </c>
-      <c r="D90" s="13" t="inlineStr">
+      <c r="D90" s="18" t="inlineStr">
         <is>
           <t>10_Cloud_Cover (الغطاء السحابي)</t>
         </is>
       </c>
-      <c r="E90" s="14" t="inlineStr">
+      <c r="E90" s="12" t="inlineStr">
         <is>
           <t>متوسط نسبة تغطية السحب لفصل الصيف الأرصادي (JJA).</t>
         </is>
       </c>
-      <c r="F90" s="15" t="inlineStr">
+      <c r="F90" s="19" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="G90" s="16" t="inlineStr">
+      <c r="G90" s="30" t="inlineStr">
         <is>
           <t>خريطة متوسط الغطاء السحابي خلال فصل الصيف (%)</t>
         </is>
       </c>
     </row>
     <row r="91" ht="24" customHeight="1">
-      <c r="A91" s="17" t="n">
+      <c r="A91" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="B91" s="18" t="inlineStr">
+      <c r="B91" s="5" t="inlineStr">
         <is>
           <t>Cld_AuMean</t>
         </is>
       </c>
-      <c r="C91" s="19" t="inlineStr">
+      <c r="C91" s="31" t="inlineStr">
         <is>
           <t>Cld_Autumn_Mean</t>
         </is>
       </c>
-      <c r="D91" s="20" t="inlineStr">
+      <c r="D91" s="15" t="inlineStr">
         <is>
           <t>10_Cloud_Cover (الغطاء السحابي)</t>
         </is>
       </c>
-      <c r="E91" s="21" t="inlineStr">
+      <c r="E91" s="7" t="inlineStr">
         <is>
           <t>متوسط نسبة تغطية السحب لفصل الخريف الأرصادي (SON).</t>
         </is>
       </c>
-      <c r="F91" s="22" t="inlineStr">
+      <c r="F91" s="16" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="G91" s="23" t="inlineStr">
+      <c r="G91" s="32" t="inlineStr">
         <is>
           <t>خريطة متوسط الغطاء السحابي خلال فصل الخريف (%)</t>
         </is>
       </c>
     </row>
     <row r="92" ht="24" customHeight="1">
-      <c r="A92" s="10" t="n">
+      <c r="A92" s="8" t="n">
         <v>91</v>
       </c>
-      <c r="B92" s="11" t="inlineStr">
+      <c r="B92" s="10" t="inlineStr">
         <is>
           <t>Cld_AnRng</t>
         </is>
       </c>
-      <c r="C92" s="12" t="inlineStr">
+      <c r="C92" s="29" t="inlineStr">
         <is>
           <t>Cld_Annual_Range</t>
         </is>
       </c>
-      <c r="D92" s="13" t="inlineStr">
+      <c r="D92" s="18" t="inlineStr">
         <is>
           <t>10_Cloud_Cover (الغطاء السحابي)</t>
         </is>
       </c>
-      <c r="E92" s="14" t="inlineStr">
+      <c r="E92" s="12" t="inlineStr">
         <is>
           <t>المدى السنوي لتغطية السحب (الفارق بين أكثر شهور السنة غيوماً وأكثرها صفاءً).</t>
         </is>
       </c>
-      <c r="F92" s="15" t="inlineStr">
+      <c r="F92" s="19" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="G92" s="16" t="inlineStr">
+      <c r="G92" s="30" t="inlineStr">
         <is>
           <t>خريطة المدى السنوي لنسبة الغطاء السحابي (%)</t>
         </is>
       </c>
     </row>
     <row r="93" ht="24" customHeight="1">
-      <c r="A93" s="17" t="n">
+      <c r="A93" s="3" t="n">
         <v>92</v>
       </c>
-      <c r="B93" s="18" t="inlineStr">
+      <c r="B93" s="5" t="inlineStr">
         <is>
           <t>WC_WinMean</t>
         </is>
       </c>
-      <c r="C93" s="19" t="inlineStr">
+      <c r="C93" s="31" t="inlineStr">
         <is>
           <t>WC_Winter_Mean</t>
         </is>
       </c>
-      <c r="D93" s="20" t="inlineStr">
+      <c r="D93" s="15" t="inlineStr">
         <is>
           <t>12_Wind_Chill (مبرد الرياح)</t>
         </is>
       </c>
-      <c r="E93" s="21" t="inlineStr">
+      <c r="E93" s="7" t="inlineStr">
         <is>
           <t>متوسط درجة البرودة الريحية لفصل الشتاء المحسوبة بمعادلة NWS لخفض الحرارة بفعل سرعة الرياح.</t>
         </is>
       </c>
-      <c r="F93" s="22" t="inlineStr">
+      <c r="F93" s="16" t="inlineStr">
         <is>
           <t>°C</t>
         </is>
       </c>
-      <c r="G93" s="23" t="inlineStr">
+      <c r="G93" s="32" t="inlineStr">
         <is>
           <t>خريطة متوسط مبرد الرياح خلال فصل الشتاء (°C)</t>
         </is>
       </c>
     </row>
     <row r="94" ht="24" customHeight="1">
-      <c r="A94" s="10" t="n">
+      <c r="A94" s="8" t="n">
         <v>93</v>
       </c>
-      <c r="B94" s="11" t="inlineStr">
+      <c r="B94" s="10" t="inlineStr">
         <is>
           <t>WC_AnnMean</t>
         </is>
       </c>
-      <c r="C94" s="12" t="inlineStr">
+      <c r="C94" s="29" t="inlineStr">
         <is>
           <t>WC_Annual_Mean</t>
         </is>
       </c>
-      <c r="D94" s="13" t="inlineStr">
+      <c r="D94" s="18" t="inlineStr">
         <is>
           <t>12_Wind_Chill (مبرد الرياح)</t>
         </is>
       </c>
-      <c r="E94" s="14" t="inlineStr">
+      <c r="E94" s="12" t="inlineStr">
         <is>
           <t>المتوسط الحسابي السنوي لتأثير البرودة الريحية على حرارة الهواء المحسوسة.</t>
         </is>
       </c>
-      <c r="F94" s="15" t="inlineStr">
+      <c r="F94" s="19" t="inlineStr">
         <is>
           <t>°C</t>
         </is>
       </c>
-      <c r="G94" s="16" t="inlineStr">
+      <c r="G94" s="30" t="inlineStr">
         <is>
           <t>خريطة المتوسط السنوي لمبرد الرياح (°C)</t>
         </is>
       </c>
     </row>
     <row r="95" ht="24" customHeight="1">
-      <c r="A95" s="17" t="n">
+      <c r="A95" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="B95" s="18" t="inlineStr">
+      <c r="B95" s="5" t="inlineStr">
         <is>
           <t>DM_AridAnn</t>
         </is>
       </c>
-      <c r="C95" s="19" t="inlineStr">
+      <c r="C95" s="31" t="inlineStr">
         <is>
           <t>DM_Aridity_Annual</t>
         </is>
       </c>
-      <c r="D95" s="20" t="inlineStr">
+      <c r="D95" s="15" t="inlineStr">
         <is>
           <t>13_De_Martonne_Aridity (دليل دي مارتون)</t>
         </is>
       </c>
-      <c r="E95" s="21" t="inlineStr">
+      <c r="E95" s="7" t="inlineStr">
         <is>
           <t>دليل القحولة والجفاف السنوي لدي مارتون I = P / (T + 10) لتصنيف الأقاليم من القاحل فائق الجفاف إلى الرطب.</t>
         </is>
       </c>
-      <c r="F95" s="22" t="inlineStr">
+      <c r="F95" s="16" t="inlineStr">
         <is>
           <t>مؤشر (Index)</t>
         </is>
       </c>
-      <c r="G95" s="23" t="inlineStr">
+      <c r="G95" s="32" t="inlineStr">
         <is>
           <t>خريطة دليل دي مارتون السنوي للقحولة والجفاف</t>
         </is>
       </c>
     </row>
     <row r="96" ht="24" customHeight="1">
-      <c r="A96" s="10" t="n">
+      <c r="A96" s="8" t="n">
         <v>95</v>
       </c>
-      <c r="B96" s="11" t="inlineStr">
+      <c r="B96" s="10" t="inlineStr">
         <is>
           <t>ET_AnnTot</t>
         </is>
       </c>
-      <c r="C96" s="12" t="inlineStr">
+      <c r="C96" s="29" t="inlineStr">
         <is>
           <t>ET_Annual_Total</t>
         </is>
       </c>
-      <c r="D96" s="13" t="inlineStr">
+      <c r="D96" s="18" t="inlineStr">
         <is>
           <t>14_Evapotranspiration (البخر والنتح)</t>
         </is>
       </c>
-      <c r="E96" s="14" t="inlineStr">
+      <c r="E96" s="12" t="inlineStr">
         <is>
           <t>المجموع التراكمي السنوي للبخر والنتح المرجعي الكامن المحسوب بمعادلة Hargreaves-Samani (FAO-56).</t>
         </is>
       </c>
-      <c r="F96" s="15" t="inlineStr">
+      <c r="F96" s="19" t="inlineStr">
         <is>
           <t>ملم (mm)</t>
         </is>
       </c>
-      <c r="G96" s="16" t="inlineStr">
+      <c r="G96" s="30" t="inlineStr">
         <is>
           <t>خريطة المجموع السنوي للبخر والنتح (ملم)</t>
         </is>
       </c>
     </row>
     <row r="97" ht="24" customHeight="1">
-      <c r="A97" s="17" t="n">
+      <c r="A97" s="3" t="n">
         <v>96</v>
       </c>
-      <c r="B97" s="18" t="inlineStr">
+      <c r="B97" s="5" t="inlineStr">
         <is>
           <t>ET_AnnMean</t>
         </is>
       </c>
-      <c r="C97" s="19" t="inlineStr">
+      <c r="C97" s="31" t="inlineStr">
         <is>
           <t>ET_Annual_Mean</t>
         </is>
       </c>
-      <c r="D97" s="20" t="inlineStr">
+      <c r="D97" s="15" t="inlineStr">
         <is>
           <t>14_Evapotranspiration (البخر والنتح)</t>
         </is>
       </c>
-      <c r="E97" s="21" t="inlineStr">
+      <c r="E97" s="7" t="inlineStr">
         <is>
           <t>المعدل الشهري للبخر والنتح المرجعي (المجموع التراكمي السنوي مقسوماً على 12 شهراً).</t>
         </is>
       </c>
-      <c r="F97" s="22" t="inlineStr">
+      <c r="F97" s="16" t="inlineStr">
         <is>
           <t>ملم (mm)</t>
         </is>
       </c>
-      <c r="G97" s="23" t="inlineStr">
+      <c r="G97" s="32" t="inlineStr">
         <is>
           <t>خريطة المعدل الشهري للبخر والنتح (ملم)</t>
         </is>
       </c>
     </row>
     <row r="98" ht="24" customHeight="1">
-      <c r="A98" s="10" t="n">
+      <c r="A98" s="8" t="n">
         <v>97</v>
       </c>
-      <c r="B98" s="11" t="inlineStr">
+      <c r="B98" s="10" t="inlineStr">
         <is>
           <t>ET_AnnRng</t>
         </is>
       </c>
-      <c r="C98" s="12" t="inlineStr">
+      <c r="C98" s="29" t="inlineStr">
         <is>
           <t>ET_Annual_Range</t>
         </is>
       </c>
-      <c r="D98" s="13" t="inlineStr">
+      <c r="D98" s="18" t="inlineStr">
         <is>
           <t>14_Evapotranspiration (البخر والنتح)</t>
         </is>
       </c>
-      <c r="E98" s="14" t="inlineStr">
+      <c r="E98" s="12" t="inlineStr">
         <is>
           <t>المدى السنوي للبخر والنتح (الفارق بين أعلى شهور السنة فقداً للماء بالبخر والنتح وأدناها).</t>
         </is>
       </c>
-      <c r="F98" s="15" t="inlineStr">
+      <c r="F98" s="19" t="inlineStr">
         <is>
           <t>ملم (mm)</t>
         </is>
       </c>
-      <c r="G98" s="16" t="inlineStr">
+      <c r="G98" s="30" t="inlineStr">
         <is>
           <t>خريطة المدى السنوي للبخر والنتح (ملم)</t>
         </is>
       </c>
     </row>
     <row r="99" ht="24" customHeight="1">
-      <c r="A99" s="17" t="n">
+      <c r="A99" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="B99" s="18" t="inlineStr">
+      <c r="B99" s="5" t="inlineStr">
         <is>
           <t>ET_SeaRng</t>
         </is>
       </c>
-      <c r="C99" s="19" t="inlineStr">
+      <c r="C99" s="31" t="inlineStr">
         <is>
           <t>ET_Seasonal_Range</t>
         </is>
       </c>
-      <c r="D99" s="20" t="inlineStr">
+      <c r="D99" s="15" t="inlineStr">
         <is>
           <t>14_Evapotranspiration (البخر والنتح)</t>
         </is>
       </c>
-      <c r="E99" s="21" t="inlineStr">
+      <c r="E99" s="7" t="inlineStr">
         <is>
           <t>المدى الفصلي للبخر والنتح (الفارق بين مجموع أعلى فصول السنة في البخر والنتح ومجموع أقلها).</t>
         </is>
       </c>
-      <c r="F99" s="22" t="inlineStr">
+      <c r="F99" s="16" t="inlineStr">
         <is>
           <t>ملم (mm)</t>
         </is>
       </c>
-      <c r="G99" s="23" t="inlineStr">
+      <c r="G99" s="32" t="inlineStr">
         <is>
           <t>خريطة المدى الفصلي للبخر والنتح (ملم)</t>
         </is>
       </c>
     </row>
     <row r="100" ht="24" customHeight="1">
-      <c r="A100" s="10" t="n">
+      <c r="A100" s="8" t="n">
         <v>99</v>
       </c>
-      <c r="B100" s="11" t="inlineStr">
+      <c r="B100" s="10" t="inlineStr">
         <is>
           <t>ET_WinTot</t>
         </is>
       </c>
-      <c r="C100" s="12" t="inlineStr">
+      <c r="C100" s="29" t="inlineStr">
         <is>
           <t>ET_Winter_Total</t>
         </is>
       </c>
-      <c r="D100" s="13" t="inlineStr">
+      <c r="D100" s="18" t="inlineStr">
         <is>
           <t>14_Evapotranspiration (البخر والنتح)</t>
         </is>
       </c>
-      <c r="E100" s="14" t="inlineStr">
+      <c r="E100" s="12" t="inlineStr">
         <is>
           <t>مجموع البخر والنتح لفصل الشتاء الأرصادي (شهور ديسمبر، يناير، فبراير - DJF).</t>
         </is>
       </c>
-      <c r="F100" s="15" t="inlineStr">
+      <c r="F100" s="19" t="inlineStr">
         <is>
           <t>ملم (mm)</t>
         </is>
       </c>
-      <c r="G100" s="16" t="inlineStr">
+      <c r="G100" s="30" t="inlineStr">
         <is>
           <t>خريطة مجموع البخر والنتح خلال فصل الشتاء (ملم)</t>
         </is>
       </c>
     </row>
     <row r="101" ht="24" customHeight="1">
-      <c r="A101" s="17" t="n">
+      <c r="A101" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="B101" s="18" t="inlineStr">
+      <c r="B101" s="5" t="inlineStr">
         <is>
           <t>ET_SprTot</t>
         </is>
       </c>
-      <c r="C101" s="19" t="inlineStr">
+      <c r="C101" s="31" t="inlineStr">
         <is>
           <t>ET_Spring_Total</t>
         </is>
       </c>
-      <c r="D101" s="20" t="inlineStr">
+      <c r="D101" s="15" t="inlineStr">
         <is>
           <t>14_Evapotranspiration (البخر والنتح)</t>
         </is>
       </c>
-      <c r="E101" s="21" t="inlineStr">
+      <c r="E101" s="7" t="inlineStr">
         <is>
           <t>مجموع البخر والنتح لفصل الربيع الأرصادي (شهور مارس، أبريل، مايو - MAM).</t>
         </is>
       </c>
-      <c r="F101" s="22" t="inlineStr">
+      <c r="F101" s="16" t="inlineStr">
         <is>
           <t>ملم (mm)</t>
         </is>
       </c>
-      <c r="G101" s="23" t="inlineStr">
+      <c r="G101" s="32" t="inlineStr">
         <is>
           <t>خريطة مجموع البخر والنتح خلال فصل الربيع (ملم)</t>
         </is>
       </c>
     </row>
     <row r="102" ht="24" customHeight="1">
-      <c r="A102" s="10" t="n">
+      <c r="A102" s="8" t="n">
         <v>101</v>
       </c>
-      <c r="B102" s="11" t="inlineStr">
+      <c r="B102" s="10" t="inlineStr">
         <is>
           <t>ET_SumTot</t>
         </is>
       </c>
-      <c r="C102" s="12" t="inlineStr">
+      <c r="C102" s="29" t="inlineStr">
         <is>
           <t>ET_Summer_Total</t>
         </is>
       </c>
-      <c r="D102" s="13" t="inlineStr">
+      <c r="D102" s="18" t="inlineStr">
         <is>
           <t>14_Evapotranspiration (البخر والنتح)</t>
         </is>
       </c>
-      <c r="E102" s="14" t="inlineStr">
+      <c r="E102" s="12" t="inlineStr">
         <is>
           <t>مجموع البخر والنتح لفصل الصيف الأرصادي (شهور يونيو، يوليو، أغسطس - JJA).</t>
         </is>
       </c>
-      <c r="F102" s="15" t="inlineStr">
+      <c r="F102" s="19" t="inlineStr">
         <is>
           <t>ملم (mm)</t>
         </is>
       </c>
-      <c r="G102" s="16" t="inlineStr">
+      <c r="G102" s="30" t="inlineStr">
         <is>
           <t>خريطة مجموع البخر والنتح خلال فصل الصيف (ملم)</t>
         </is>
       </c>
     </row>
     <row r="103" ht="24" customHeight="1">
-      <c r="A103" s="17" t="n">
+      <c r="A103" s="3" t="n">
         <v>102</v>
       </c>
-      <c r="B103" s="18" t="inlineStr">
+      <c r="B103" s="5" t="inlineStr">
         <is>
           <t>ET_AutTot</t>
         </is>
       </c>
-      <c r="C103" s="19" t="inlineStr">
+      <c r="C103" s="31" t="inlineStr">
         <is>
           <t>ET_Autumn_Total</t>
         </is>
       </c>
-      <c r="D103" s="20" t="inlineStr">
+      <c r="D103" s="15" t="inlineStr">
         <is>
           <t>14_Evapotranspiration (البخر والنتح)</t>
         </is>
       </c>
-      <c r="E103" s="21" t="inlineStr">
+      <c r="E103" s="7" t="inlineStr">
         <is>
           <t>مجموع البخر والنتح لفصل الخريف الأرصادي (شهور سبتمبر، أكتوبر، نوفمبر - SON).</t>
         </is>
       </c>
-      <c r="F103" s="22" t="inlineStr">
+      <c r="F103" s="16" t="inlineStr">
         <is>
           <t>ملم (mm)</t>
         </is>
       </c>
-      <c r="G103" s="23" t="inlineStr">
+      <c r="G103" s="32" t="inlineStr">
         <is>
           <t>خريطة مجموع البخر والنتح خلال فصل الخريف (ملم)</t>
         </is>
       </c>
     </row>
     <row r="104" ht="24" customHeight="1">
-      <c r="A104" s="10" t="n">
+      <c r="A104" s="8" t="n">
         <v>103</v>
       </c>
-      <c r="B104" s="11" t="inlineStr">
+      <c r="B104" s="10" t="inlineStr">
         <is>
           <t>PET_HarAnn</t>
         </is>
       </c>
-      <c r="C104" s="12" t="inlineStr">
+      <c r="C104" s="29" t="inlineStr">
         <is>
           <t>PET_Hargreaves_Annual</t>
         </is>
       </c>
-      <c r="D104" s="13" t="inlineStr">
+      <c r="D104" s="18" t="inlineStr">
         <is>
           <t>14_Evapotranspiration (البخر والنتح)</t>
         </is>
       </c>
-      <c r="E104" s="14" t="inlineStr">
+      <c r="E104" s="12" t="inlineStr">
         <is>
           <t>التبخر-نتح الكامن السنوي بهارجريفز (حقل رديف مطابق تماماً لـ ET_Annual_Total للتوافقية العكسية).</t>
         </is>
       </c>
-      <c r="F104" s="15" t="inlineStr">
+      <c r="F104" s="19" t="inlineStr">
         <is>
           <t>ملم (mm)</t>
         </is>
       </c>
-      <c r="G104" s="16" t="inlineStr">
+      <c r="G104" s="30" t="inlineStr">
         <is>
           <t>خريطة التبخر والنتح الكامن السنوي بهارجريفز (ملم)</t>
         </is>
       </c>
     </row>
     <row r="105" ht="24" customHeight="1">
-      <c r="A105" s="17" t="n">
+      <c r="A105" s="3" t="n">
         <v>104</v>
       </c>
-      <c r="B105" s="18" t="inlineStr">
+      <c r="B105" s="5" t="inlineStr">
         <is>
           <t>UNEP_Arid</t>
         </is>
       </c>
-      <c r="C105" s="19" t="inlineStr">
+      <c r="C105" s="31" t="inlineStr">
         <is>
           <t>UNEP_Aridity_Annual</t>
         </is>
       </c>
-      <c r="D105" s="20" t="inlineStr">
+      <c r="D105" s="15" t="inlineStr">
         <is>
           <t>15_UNEP_Aridity (مؤشر UNEP)</t>
         </is>
       </c>
-      <c r="E105" s="21" t="inlineStr">
+      <c r="E105" s="7" t="inlineStr">
         <is>
           <t>مؤشر القحولة العالمي لبرنامج الأمم المتحدة للبيئة AI = P / ET_ann لتحديد المناطق القاحلة وشبه القاحلة.</t>
         </is>
       </c>
-      <c r="F105" s="22" t="inlineStr">
+      <c r="F105" s="16" t="inlineStr">
         <is>
           <t>نسبة (Ratio)</t>
         </is>
       </c>
-      <c r="G105" s="23" t="inlineStr">
+      <c r="G105" s="32" t="inlineStr">
         <is>
           <t>خريطة مؤشر القحولة العالمي لبرنامج الأمم المتحدة للبيئة</t>
         </is>
       </c>
     </row>
     <row r="106" ht="24" customHeight="1">
-      <c r="A106" s="10" t="n">
+      <c r="A106" s="8" t="n">
         <v>105</v>
       </c>
-      <c r="B106" s="11" t="inlineStr">
+      <c r="B106" s="10" t="inlineStr">
         <is>
           <t>WatDefAnn</t>
         </is>
       </c>
-      <c r="C106" s="12" t="inlineStr">
+      <c r="C106" s="29" t="inlineStr">
         <is>
           <t>Water_Deficit_Annual</t>
         </is>
       </c>
-      <c r="D106" s="13" t="inlineStr">
+      <c r="D106" s="18" t="inlineStr">
         <is>
           <t>16_Water_Deficit (العجز المائي)</t>
         </is>
       </c>
-      <c r="E106" s="14" t="inlineStr">
+      <c r="E106" s="12" t="inlineStr">
         <is>
           <t>الموازنة المائية المناخية السنوية الصافية WD = P - ET_ann (القيم السالبة تعبر عن عجز مائي والموجبة فائض مائي).</t>
         </is>
       </c>
-      <c r="F106" s="15" t="inlineStr">
+      <c r="F106" s="19" t="inlineStr">
         <is>
           <t>ملم (mm)</t>
         </is>
       </c>
-      <c r="G106" s="16" t="inlineStr">
+      <c r="G106" s="30" t="inlineStr">
         <is>
           <t>خريطة الموازنة والعجز المائي المناخي السنوي (ملم)</t>
         </is>
       </c>
     </row>
     <row r="107" ht="24" customHeight="1">
-      <c r="A107" s="17" t="n">
+      <c r="A107" s="3" t="n">
         <v>106</v>
       </c>
-      <c r="B107" s="18" t="inlineStr">
+      <c r="B107" s="5" t="inlineStr">
         <is>
           <t>Dry_Months</t>
         </is>
       </c>
-      <c r="C107" s="19" t="inlineStr">
+      <c r="C107" s="31" t="inlineStr">
         <is>
           <t>Dry_Months_Count</t>
         </is>
       </c>
-      <c r="D107" s="20" t="inlineStr">
+      <c r="D107" s="15" t="inlineStr">
         <is>
           <t>17_Dry_Months (الأشهر الجافة)</t>
         </is>
       </c>
-      <c r="E107" s="21" t="inlineStr">
+      <c r="E107" s="7" t="inlineStr">
         <is>
           <t>عدد أشهر السنة الجافة بيولوجياً ومناخياً وفق معيار والتر-ليث البيومناخي الشهير (P &lt; 2T).</t>
         </is>
       </c>
-      <c r="F107" s="22" t="inlineStr">
+      <c r="F107" s="16" t="inlineStr">
         <is>
           <t>شهر (0-12)</t>
         </is>
       </c>
-      <c r="G107" s="23" t="inlineStr">
+      <c r="G107" s="32" t="inlineStr">
         <is>
           <t>خريطة عدد الأشهر الجافة بيولوجياً في السنة</t>
         </is>
       </c>
     </row>
     <row r="108" ht="24" customHeight="1">
-      <c r="A108" s="10" t="n">
+      <c r="A108" s="8" t="n">
         <v>107</v>
       </c>
-      <c r="B108" s="11" t="inlineStr">
+      <c r="B108" s="10" t="inlineStr">
         <is>
           <t>T_TrendDec</t>
         </is>
       </c>
-      <c r="C108" s="12" t="inlineStr">
+      <c r="C108" s="29" t="inlineStr">
         <is>
           <t>T_Trend_Decade</t>
         </is>
       </c>
-      <c r="D108" s="13" t="inlineStr">
+      <c r="D108" s="18" t="inlineStr">
         <is>
           <t>18_Trends_And_Anomalies (الاتجاهات والشذوذ)</t>
         </is>
       </c>
-      <c r="E108" s="14" t="inlineStr">
+      <c r="E108" s="12" t="inlineStr">
         <is>
           <t>معدل تغير واتجاه درجة الحرارة لكل عقد زمني (10 سنوات) باستخدام انحدار المربعات الصغرى الخطي.</t>
         </is>
       </c>
-      <c r="F108" s="15" t="inlineStr">
+      <c r="F108" s="19" t="inlineStr">
         <is>
           <t>°C/decade</t>
         </is>
       </c>
-      <c r="G108" s="16" t="inlineStr">
+      <c r="G108" s="30" t="inlineStr">
         <is>
           <t>خريطة اتجاه تغير درجة الحرارة في العقد الزمني (°C/decade)</t>
         </is>
       </c>
     </row>
     <row r="109" ht="24" customHeight="1">
-      <c r="A109" s="17" t="n">
+      <c r="A109" s="3" t="n">
         <v>108</v>
       </c>
-      <c r="B109" s="18" t="inlineStr">
+      <c r="B109" s="5" t="inlineStr">
         <is>
           <t>R_TrendDec</t>
         </is>
       </c>
-      <c r="C109" s="19" t="inlineStr">
+      <c r="C109" s="31" t="inlineStr">
         <is>
           <t>R_Trend_Decade</t>
         </is>
       </c>
-      <c r="D109" s="20" t="inlineStr">
+      <c r="D109" s="15" t="inlineStr">
         <is>
           <t>18_Trends_And_Anomalies (الاتجاهات والشذوذ)</t>
         </is>
       </c>
-      <c r="E109" s="21" t="inlineStr">
+      <c r="E109" s="7" t="inlineStr">
         <is>
           <t>معدل تغير واتجاه تساقط الأمطار لكل عقد زمني (10 سنوات) باستخدام انحدار المربعات الصغرى الخطي.</t>
         </is>
       </c>
-      <c r="F109" s="22" t="inlineStr">
+      <c r="F109" s="16" t="inlineStr">
         <is>
           <t>mm/decade</t>
         </is>
       </c>
-      <c r="G109" s="23" t="inlineStr">
+      <c r="G109" s="32" t="inlineStr">
         <is>
           <t>خريطة اتجاه تغير تساقط الأمطار في العقد الزمني (mm/decade)</t>
         </is>
       </c>
     </row>
     <row r="110" ht="24" customHeight="1">
-      <c r="A110" s="10" t="n">
+      <c r="A110" s="8" t="n">
         <v>109</v>
       </c>
-      <c r="B110" s="11" t="inlineStr">
+      <c r="B110" s="10" t="inlineStr">
         <is>
           <t>T_AnomAnn</t>
         </is>
       </c>
-      <c r="C110" s="12" t="inlineStr">
+      <c r="C110" s="29" t="inlineStr">
         <is>
           <t>T_Anom_Annual</t>
         </is>
       </c>
-      <c r="D110" s="13" t="inlineStr">
+      <c r="D110" s="18" t="inlineStr">
         <is>
           <t>18_Trends_And_Anomalies (الاتجاهات والشذوذ)</t>
         </is>
       </c>
-      <c r="E110" s="14" t="inlineStr">
+      <c r="E110" s="12" t="inlineStr">
         <is>
           <t>الشذوذ الحراري السنوي لدرجة الحرارة مقارنة بخط الأساس المناخي العالمي 1991–2020.</t>
         </is>
       </c>
-      <c r="F110" s="15" t="inlineStr">
+      <c r="F110" s="19" t="inlineStr">
         <is>
           <t>°C</t>
         </is>
       </c>
-      <c r="G110" s="16" t="inlineStr">
+      <c r="G110" s="30" t="inlineStr">
         <is>
           <t>خريطة الشذوذ الحراري السنوي مقارنة بخط أساس 1991–2020 (°C)</t>
         </is>
       </c>
     </row>
     <row r="111" ht="24" customHeight="1">
-      <c r="A111" s="17" t="n">
+      <c r="A111" s="3" t="n">
         <v>110</v>
       </c>
-      <c r="B111" s="18" t="inlineStr">
+      <c r="B111" s="5" t="inlineStr">
         <is>
           <t>T_AnomWin</t>
         </is>
       </c>
-      <c r="C111" s="19" t="inlineStr">
+      <c r="C111" s="31" t="inlineStr">
         <is>
           <t>T_Anom_Winter</t>
         </is>
       </c>
-      <c r="D111" s="20" t="inlineStr">
+      <c r="D111" s="15" t="inlineStr">
         <is>
           <t>18_Trends_And_Anomalies (الاتجاهات والشذوذ)</t>
         </is>
       </c>
-      <c r="E111" s="21" t="inlineStr">
+      <c r="E111" s="7" t="inlineStr">
         <is>
           <t>الشذوذ الحراري لفصل الشتاء مقارنة بمتوسط شهور الشتاء لخط الأساس المناخي 1991–2020.</t>
         </is>
       </c>
-      <c r="F111" s="22" t="inlineStr">
+      <c r="F111" s="16" t="inlineStr">
         <is>
           <t>°C</t>
         </is>
       </c>
-      <c r="G111" s="23" t="inlineStr">
+      <c r="G111" s="32" t="inlineStr">
         <is>
           <t>خريطة الشذوذ الحراري لفصل الشتاء مقارنة بخط أساس 1991–2020 (°C)</t>
         </is>
       </c>
     </row>
     <row r="112" ht="24" customHeight="1">
-      <c r="A112" s="10" t="n">
+      <c r="A112" s="8" t="n">
         <v>111</v>
       </c>
-      <c r="B112" s="11" t="inlineStr">
+      <c r="B112" s="10" t="inlineStr">
         <is>
           <t>T_AnomSum</t>
         </is>
       </c>
-      <c r="C112" s="12" t="inlineStr">
+      <c r="C112" s="29" t="inlineStr">
         <is>
           <t>T_Anom_Summer</t>
         </is>
       </c>
-      <c r="D112" s="13" t="inlineStr">
+      <c r="D112" s="18" t="inlineStr">
         <is>
           <t>18_Trends_And_Anomalies (الاتجاهات والشذوذ)</t>
         </is>
       </c>
-      <c r="E112" s="14" t="inlineStr">
+      <c r="E112" s="12" t="inlineStr">
         <is>
           <t>الشذوذ الحراري لفصل الصيف مقارنة بمتوسط شهور الصيف لخط الأساس المناخي 1991–2020.</t>
         </is>
       </c>
-      <c r="F112" s="15" t="inlineStr">
+      <c r="F112" s="19" t="inlineStr">
         <is>
           <t>°C</t>
         </is>
       </c>
-      <c r="G112" s="16" t="inlineStr">
+      <c r="G112" s="30" t="inlineStr">
         <is>
           <t>خريطة الشذوذ الحراري لفصل الصيف مقارنة بخط أساس 1991–2020 (°C)</t>
         </is>
       </c>
     </row>
     <row r="113" ht="24" customHeight="1">
-      <c r="A113" s="17" t="n">
+      <c r="A113" s="3" t="n">
         <v>112</v>
       </c>
-      <c r="B113" s="18" t="inlineStr">
+      <c r="B113" s="5" t="inlineStr">
         <is>
           <t>R_AnomAnn</t>
         </is>
       </c>
-      <c r="C113" s="19" t="inlineStr">
+      <c r="C113" s="31" t="inlineStr">
         <is>
           <t>R_Anom_Annual</t>
         </is>
       </c>
-      <c r="D113" s="20" t="inlineStr">
+      <c r="D113" s="15" t="inlineStr">
         <is>
           <t>18_Trends_And_Anomalies (الاتجاهات والشذوذ)</t>
         </is>
       </c>
-      <c r="E113" s="21" t="inlineStr">
+      <c r="E113" s="7" t="inlineStr">
         <is>
           <t>شذوذ الأمطار السنوي المطلق مقارنة بمتوسط الأمطار لخط الأساس المناخي 1991–2020.</t>
         </is>
       </c>
-      <c r="F113" s="22" t="inlineStr">
+      <c r="F113" s="16" t="inlineStr">
         <is>
           <t>ملم (mm)</t>
         </is>
       </c>
-      <c r="G113" s="23" t="inlineStr">
+      <c r="G113" s="32" t="inlineStr">
         <is>
           <t>خريطة شذوذ تساقط الأمطار السنوي مقارنة بخط أساس 1991–2020 (ملم)</t>
         </is>
       </c>
     </row>
     <row r="114" ht="24" customHeight="1">
-      <c r="A114" s="10" t="n">
+      <c r="A114" s="8" t="n">
         <v>113</v>
       </c>
-      <c r="B114" s="11" t="inlineStr">
+      <c r="B114" s="10" t="inlineStr">
         <is>
           <t>R_AnomPct</t>
         </is>
       </c>
-      <c r="C114" s="12" t="inlineStr">
+      <c r="C114" s="29" t="inlineStr">
         <is>
           <t>R_Anom_Annual_Pct</t>
         </is>
       </c>
-      <c r="D114" s="13" t="inlineStr">
+      <c r="D114" s="18" t="inlineStr">
         <is>
           <t>18_Trends_And_Anomalies (الاتجاهات والشذوذ)</t>
         </is>
       </c>
-      <c r="E114" s="14" t="inlineStr">
+      <c r="E114" s="12" t="inlineStr">
         <is>
           <t>شذوذ الأمطار السنوي كنسبة مئوية من خط الأساس المناخي 1991–2020 (فرق نسبي مئوي).</t>
         </is>
       </c>
-      <c r="F114" s="15" t="inlineStr">
+      <c r="F114" s="19" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="G114" s="16" t="inlineStr">
+      <c r="G114" s="30" t="inlineStr">
         <is>
           <t>خريطة الشذوذ النسبي المئوي للأمطار مقارنة بخط أساس 1991–2020 (%)</t>
         </is>
       </c>
     </row>
     <row r="115" ht="24" customHeight="1">
-      <c r="A115" s="17" t="n">
+      <c r="A115" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="B115" s="18" t="inlineStr">
+      <c r="B115" s="5" t="inlineStr">
         <is>
           <t>R_AnomWin</t>
         </is>
       </c>
-      <c r="C115" s="19" t="inlineStr">
+      <c r="C115" s="31" t="inlineStr">
         <is>
           <t>R_Anom_Winter</t>
         </is>
       </c>
-      <c r="D115" s="20" t="inlineStr">
+      <c r="D115" s="15" t="inlineStr">
         <is>
           <t>18_Trends_And_Anomalies (الاتجاهات والشذوذ)</t>
         </is>
       </c>
-      <c r="E115" s="21" t="inlineStr">
+      <c r="E115" s="7" t="inlineStr">
         <is>
           <t>شذوذ أمطار فصل الشتاء المطلق مقارنة بأمطار شتاء خط الأساس المناخي 1991–2020.</t>
         </is>
       </c>
-      <c r="F115" s="22" t="inlineStr">
+      <c r="F115" s="16" t="inlineStr">
         <is>
           <t>ملم (mm)</t>
         </is>
       </c>
-      <c r="G115" s="23" t="inlineStr">
+      <c r="G115" s="32" t="inlineStr">
         <is>
           <t>خريطة شذوذ أمطار الشتاء مقارنة بخط أساس 1991–2020 (ملم)</t>
         </is>
       </c>
     </row>
     <row r="116" ht="24" customHeight="1">
-      <c r="A116" s="10" t="n">
+      <c r="A116" s="8" t="n">
         <v>115</v>
       </c>
-      <c r="B116" s="11" t="inlineStr">
+      <c r="B116" s="10" t="inlineStr">
         <is>
           <t>R_AnomWPct</t>
         </is>
       </c>
-      <c r="C116" s="12" t="inlineStr">
+      <c r="C116" s="29" t="inlineStr">
         <is>
           <t>R_Anom_Winter_Pct</t>
         </is>
       </c>
-      <c r="D116" s="13" t="inlineStr">
+      <c r="D116" s="18" t="inlineStr">
         <is>
           <t>18_Trends_And_Anomalies (الاتجاهات والشذوذ)</t>
         </is>
       </c>
-      <c r="E116" s="14" t="inlineStr">
+      <c r="E116" s="12" t="inlineStr">
         <is>
           <t>شذوذ أمطار فصل الشتاء كنسبة مئوية مقارنة بأمطار شتاء خط الأساس المناخي 1991–2020.</t>
         </is>
       </c>
-      <c r="F116" s="15" t="inlineStr">
+      <c r="F116" s="19" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="G116" s="16" t="inlineStr">
+      <c r="G116" s="30" t="inlineStr">
         <is>
           <t>خريطة الشذوذ النسبي المئوي لأمطار الشتاء مقارنة بخط أساس 1991–2020 (%)</t>
         </is>
@@ -4678,7 +5755,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4698,49 +5775,49 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
-      <c r="A1" s="24" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>الرقم
 No.</t>
         </is>
       </c>
-      <c r="B1" s="24" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>اسم العنصر في الأداة
 Tool Parameter &amp; Layer</t>
         </is>
       </c>
-      <c r="C1" s="24" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>الاسم باللغة العربية
 Module Arabic Name</t>
         </is>
       </c>
-      <c r="D1" s="24" t="inlineStr">
+      <c r="D1" s="13" t="inlineStr">
         <is>
           <t>مجلد الراستر (1:1)
 Output Raster Folder</t>
         </is>
       </c>
-      <c r="E1" s="24" t="inlineStr">
+      <c r="E1" s="13" t="inlineStr">
         <is>
           <t>طبقة المعالم (1:1)
 Feature Class Name</t>
         </is>
       </c>
-      <c r="F1" s="24" t="inlineStr">
+      <c r="F1" s="13" t="inlineStr">
         <is>
           <t>عدد المؤشرات
 Indicators</t>
         </is>
       </c>
-      <c r="G1" s="24" t="inlineStr">
+      <c r="G1" s="13" t="inlineStr">
         <is>
           <t>الوحدة الرئيسية
 Main Unit</t>
         </is>
       </c>
-      <c r="H1" s="24" t="inlineStr">
+      <c r="H1" s="13" t="inlineStr">
         <is>
           <t>المنهجية والمعادلة العلمية
 Scientific Method &amp; Standards</t>
@@ -4748,732 +5825,732 @@
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B2" s="25" t="inlineStr">
+      <c r="B2" s="17" t="inlineStr">
         <is>
           <t>01_Temperature</t>
         </is>
       </c>
-      <c r="C2" s="26" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>درجة الحرارة</t>
         </is>
       </c>
-      <c r="D2" s="25" t="inlineStr">
+      <c r="D2" s="17" t="inlineStr">
         <is>
           <t>01_Temperature</t>
         </is>
       </c>
-      <c r="E2" s="25" t="inlineStr">
+      <c r="E2" s="17" t="inlineStr">
         <is>
           <t>01_Temperature</t>
         </is>
       </c>
-      <c r="F2" s="10" t="n">
+      <c r="F2" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="G2" s="15" t="inlineStr">
+      <c r="G2" s="19" t="inlineStr">
         <is>
           <t>°C</t>
         </is>
       </c>
-      <c r="H2" s="13" t="inlineStr">
+      <c r="H2" s="18" t="inlineStr">
         <is>
           <t>NASA POWER T2M, T2M_MAX, T2M_MIN / WMO Climatological Normals</t>
         </is>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="17" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>02</t>
         </is>
       </c>
-      <c r="B3" s="27" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>02_Precipitation</t>
         </is>
       </c>
-      <c r="C3" s="28" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>الأمطار والتساقط</t>
         </is>
       </c>
-      <c r="D3" s="27" t="inlineStr">
+      <c r="D3" s="14" t="inlineStr">
         <is>
           <t>02_Precipitation</t>
         </is>
       </c>
-      <c r="E3" s="27" t="inlineStr">
+      <c r="E3" s="14" t="inlineStr">
         <is>
           <t>02_Precipitation</t>
         </is>
       </c>
-      <c r="F3" s="17" t="n">
+      <c r="F3" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="G3" s="22" t="inlineStr">
+      <c r="G3" s="16" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="H3" s="20" t="inlineStr">
+      <c r="H3" s="15" t="inlineStr">
         <is>
           <t>NASA POWER PRECTOTCORR / Annual, Seasonal Totals &amp; Ranges</t>
         </is>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>03</t>
         </is>
       </c>
-      <c r="B4" s="25" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>03_Sea_Level_Pressure</t>
         </is>
       </c>
-      <c r="C4" s="26" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>ضغط مستوى سطح البحر</t>
         </is>
       </c>
-      <c r="D4" s="25" t="inlineStr">
+      <c r="D4" s="17" t="inlineStr">
         <is>
           <t>03_Sea_Level_Pressure</t>
         </is>
       </c>
-      <c r="E4" s="25" t="inlineStr">
+      <c r="E4" s="17" t="inlineStr">
         <is>
           <t>03_Sea_Level_Pressure</t>
         </is>
       </c>
-      <c r="F4" s="10" t="n">
+      <c r="F4" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="G4" s="15" t="inlineStr">
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>hPa / mbar</t>
         </is>
       </c>
-      <c r="H4" s="13" t="inlineStr">
+      <c r="H4" s="18" t="inlineStr">
         <is>
           <t>NASA POWER SLP / Reduced to Standard Mean Sea Level</t>
         </is>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>04</t>
         </is>
       </c>
-      <c r="B5" s="27" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>04_Surface_Pressure</t>
         </is>
       </c>
-      <c r="C5" s="28" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>الضغط السطحي الفعلي</t>
         </is>
       </c>
-      <c r="D5" s="27" t="inlineStr">
+      <c r="D5" s="14" t="inlineStr">
         <is>
           <t>04_Surface_Pressure</t>
         </is>
       </c>
-      <c r="E5" s="27" t="inlineStr">
+      <c r="E5" s="14" t="inlineStr">
         <is>
           <t>04_Surface_Pressure</t>
         </is>
       </c>
-      <c r="F5" s="17" t="n">
+      <c r="F5" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="G5" s="22" t="inlineStr">
+      <c r="G5" s="16" t="inlineStr">
         <is>
           <t>hPa / mbar</t>
         </is>
       </c>
-      <c r="H5" s="20" t="inlineStr">
+      <c r="H5" s="15" t="inlineStr">
         <is>
           <t>NASA POWER PS / Actual Local Topographic Station Pressure</t>
         </is>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>05</t>
         </is>
       </c>
-      <c r="B6" s="25" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>05_Wind</t>
         </is>
       </c>
-      <c r="C6" s="26" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>الرياح السطحية (سرعة واتجاه)</t>
         </is>
       </c>
-      <c r="D6" s="25" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>05_Wind</t>
         </is>
       </c>
-      <c r="E6" s="25" t="inlineStr">
+      <c r="E6" s="17" t="inlineStr">
         <is>
           <t>05_Wind</t>
         </is>
       </c>
-      <c r="F6" s="10" t="n">
+      <c r="F6" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="G6" s="15" t="inlineStr">
+      <c r="G6" s="19" t="inlineStr">
         <is>
           <t>m/s, °</t>
         </is>
       </c>
-      <c r="H6" s="13" t="inlineStr">
+      <c r="H6" s="18" t="inlineStr">
         <is>
           <t>NASA POWER WS10M, WD10M / Circular Mean Vector atan2</t>
         </is>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>06</t>
         </is>
       </c>
-      <c r="B7" s="27" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>06_Relative_Humidity</t>
         </is>
       </c>
-      <c r="C7" s="28" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>الرطوبة النسبية</t>
         </is>
       </c>
-      <c r="D7" s="27" t="inlineStr">
+      <c r="D7" s="14" t="inlineStr">
         <is>
           <t>06_Relative_Humidity</t>
         </is>
       </c>
-      <c r="E7" s="27" t="inlineStr">
+      <c r="E7" s="14" t="inlineStr">
         <is>
           <t>06_Relative_Humidity</t>
         </is>
       </c>
-      <c r="F7" s="17" t="n">
+      <c r="F7" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="G7" s="22" t="inlineStr">
+      <c r="G7" s="16" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="H7" s="20" t="inlineStr">
+      <c r="H7" s="15" t="inlineStr">
         <is>
           <t>NASA POWER RH2M / Climatological Relative Humidity at 2m</t>
         </is>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>07</t>
         </is>
       </c>
-      <c r="B8" s="25" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>07_Dew_Point</t>
         </is>
       </c>
-      <c r="C8" s="26" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>نقطة الندى</t>
         </is>
       </c>
-      <c r="D8" s="25" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>07_Dew_Point</t>
         </is>
       </c>
-      <c r="E8" s="25" t="inlineStr">
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>07_Dew_Point</t>
         </is>
       </c>
-      <c r="F8" s="10" t="n">
+      <c r="F8" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="G8" s="15" t="inlineStr">
+      <c r="G8" s="19" t="inlineStr">
         <is>
           <t>°C</t>
         </is>
       </c>
-      <c r="H8" s="13" t="inlineStr">
+      <c r="H8" s="18" t="inlineStr">
         <is>
           <t>NASA POWER T2MDEW / Dew Point Temperature at 2m</t>
         </is>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>08</t>
         </is>
       </c>
-      <c r="B9" s="27" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>08_Solar_Radiation</t>
         </is>
       </c>
-      <c r="C9" s="28" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>الإشعاع الشمسي والطاقة</t>
         </is>
       </c>
-      <c r="D9" s="27" t="inlineStr">
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t>08_Solar_Radiation</t>
         </is>
       </c>
-      <c r="E9" s="27" t="inlineStr">
+      <c r="E9" s="14" t="inlineStr">
         <is>
           <t>08_Solar_Radiation</t>
         </is>
       </c>
-      <c r="F9" s="17" t="n">
+      <c r="F9" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="G9" s="22" t="inlineStr">
+      <c r="G9" s="16" t="inlineStr">
         <is>
           <t>kWh/m²/day</t>
         </is>
       </c>
-      <c r="H9" s="20" t="inlineStr">
+      <c r="H9" s="15" t="inlineStr">
         <is>
           <t>NASA POWER ALLSKY_SFC_SW_DWN / Daily Mean &amp; Cumulative Annual</t>
         </is>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>09</t>
         </is>
       </c>
-      <c r="B10" s="25" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>09_UV_Index</t>
         </is>
       </c>
-      <c r="C10" s="26" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>مؤشر الأشعة فوق البنفسجية</t>
         </is>
       </c>
-      <c r="D10" s="25" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>09_UV_Index</t>
         </is>
       </c>
-      <c r="E10" s="25" t="inlineStr">
+      <c r="E10" s="17" t="inlineStr">
         <is>
           <t>09_UV_Index</t>
         </is>
       </c>
-      <c r="F10" s="10" t="n">
+      <c r="F10" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="G10" s="15" t="inlineStr">
+      <c r="G10" s="19" t="inlineStr">
         <is>
           <t>Index (0–16+)</t>
         </is>
       </c>
-      <c r="H10" s="13" t="inlineStr">
+      <c r="H10" s="18" t="inlineStr">
         <is>
           <t>WHO / WMO Global Solar UV Index Standard</t>
         </is>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B11" s="27" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>10_Cloud_Cover</t>
         </is>
       </c>
-      <c r="C11" s="28" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>الغطاء السحابي</t>
         </is>
       </c>
-      <c r="D11" s="27" t="inlineStr">
+      <c r="D11" s="14" t="inlineStr">
         <is>
           <t>10_Cloud_Cover</t>
         </is>
       </c>
-      <c r="E11" s="27" t="inlineStr">
+      <c r="E11" s="14" t="inlineStr">
         <is>
           <t>10_Cloud_Cover</t>
         </is>
       </c>
-      <c r="F11" s="17" t="n">
+      <c r="F11" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="G11" s="22" t="inlineStr">
+      <c r="G11" s="16" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="H11" s="20" t="inlineStr">
+      <c r="H11" s="15" t="inlineStr">
         <is>
           <t>NASA POWER CLOUD_AMT / Total Sky Cloud Fraction</t>
         </is>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B12" s="25" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>11_Heat_Index</t>
         </is>
       </c>
-      <c r="C12" s="26" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>مؤشر الحرارة والإجهاد الحراري</t>
         </is>
       </c>
-      <c r="D12" s="25" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>11_Heat_Index</t>
         </is>
       </c>
-      <c r="E12" s="25" t="inlineStr">
+      <c r="E12" s="17" t="inlineStr">
         <is>
           <t>11_Heat_Index</t>
         </is>
       </c>
-      <c r="F12" s="10" t="n">
+      <c r="F12" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="G12" s="15" t="inlineStr">
+      <c r="G12" s="19" t="inlineStr">
         <is>
           <t>°C</t>
         </is>
       </c>
-      <c r="H12" s="13" t="inlineStr">
+      <c r="H12" s="18" t="inlineStr">
         <is>
           <t>Steadman-Rothfusz NWS Formula + Humidex + ISO 7243 WBGT</t>
         </is>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B13" s="27" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>12_Wind_Chill</t>
         </is>
       </c>
-      <c r="C13" s="28" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>مبرد الرياح</t>
         </is>
       </c>
-      <c r="D13" s="27" t="inlineStr">
+      <c r="D13" s="14" t="inlineStr">
         <is>
           <t>12_Wind_Chill</t>
         </is>
       </c>
-      <c r="E13" s="27" t="inlineStr">
+      <c r="E13" s="14" t="inlineStr">
         <is>
           <t>12_Wind_Chill</t>
         </is>
       </c>
-      <c r="F13" s="17" t="n">
+      <c r="F13" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G13" s="22" t="inlineStr">
+      <c r="G13" s="16" t="inlineStr">
         <is>
           <t>°C</t>
         </is>
       </c>
-      <c r="H13" s="20" t="inlineStr">
+      <c r="H13" s="15" t="inlineStr">
         <is>
           <t>US National Weather Service (NWS) Wind Chill Equivalent</t>
         </is>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="B14" s="25" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>13_De_Martonne_Aridity</t>
         </is>
       </c>
-      <c r="C14" s="26" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>دليل الجفاف لدي مارتون</t>
         </is>
       </c>
-      <c r="D14" s="25" t="inlineStr">
+      <c r="D14" s="17" t="inlineStr">
         <is>
           <t>13_De_Martonne_Aridity</t>
         </is>
       </c>
-      <c r="E14" s="25" t="inlineStr">
+      <c r="E14" s="17" t="inlineStr">
         <is>
           <t>13_De_Martonne_Aridity</t>
         </is>
       </c>
-      <c r="F14" s="10" t="n">
+      <c r="F14" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="G14" s="15" t="inlineStr">
+      <c r="G14" s="19" t="inlineStr">
         <is>
           <t>Index</t>
         </is>
       </c>
-      <c r="H14" s="13" t="inlineStr">
+      <c r="H14" s="18" t="inlineStr">
         <is>
           <t>De Martonne (1926) Aridity Index: I = P / (T + 10)</t>
         </is>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="B15" s="27" t="inlineStr">
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>14_Evapotranspiration</t>
         </is>
       </c>
-      <c r="C15" s="28" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>البخر والنتح المرجعي (ET)</t>
         </is>
       </c>
-      <c r="D15" s="27" t="inlineStr">
+      <c r="D15" s="14" t="inlineStr">
         <is>
           <t>14_Evapotranspiration</t>
         </is>
       </c>
-      <c r="E15" s="27" t="inlineStr">
+      <c r="E15" s="14" t="inlineStr">
         <is>
           <t>14_Evapotranspiration</t>
         </is>
       </c>
-      <c r="F15" s="17" t="n">
+      <c r="F15" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="G15" s="22" t="inlineStr">
+      <c r="G15" s="16" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="H15" s="20" t="inlineStr">
+      <c r="H15" s="15" t="inlineStr">
         <is>
           <t>FAO-56 Hargreaves-Samani (1985) Extraterrestrial Radiation Ra</t>
         </is>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="B16" s="25" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>15_UNEP_Aridity</t>
         </is>
       </c>
-      <c r="C16" s="26" t="inlineStr">
+      <c r="C16" s="9" t="inlineStr">
         <is>
           <t>مؤشر القحولة UNEP</t>
         </is>
       </c>
-      <c r="D16" s="25" t="inlineStr">
+      <c r="D16" s="17" t="inlineStr">
         <is>
           <t>15_UNEP_Aridity</t>
         </is>
       </c>
-      <c r="E16" s="25" t="inlineStr">
+      <c r="E16" s="17" t="inlineStr">
         <is>
           <t>15_UNEP_Aridity</t>
         </is>
       </c>
-      <c r="F16" s="10" t="n">
+      <c r="F16" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="G16" s="15" t="inlineStr">
+      <c r="G16" s="19" t="inlineStr">
         <is>
           <t>Ratio</t>
         </is>
       </c>
-      <c r="H16" s="13" t="inlineStr">
+      <c r="H16" s="18" t="inlineStr">
         <is>
           <t>UNEP Global Aridity Index: AI = P / ETo</t>
         </is>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="17" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="B17" s="27" t="inlineStr">
+      <c r="B17" s="14" t="inlineStr">
         <is>
           <t>16_Water_Deficit</t>
         </is>
       </c>
-      <c r="C17" s="28" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>الموازنة والعجز المائي</t>
         </is>
       </c>
-      <c r="D17" s="27" t="inlineStr">
+      <c r="D17" s="14" t="inlineStr">
         <is>
           <t>16_Water_Deficit</t>
         </is>
       </c>
-      <c r="E17" s="27" t="inlineStr">
+      <c r="E17" s="14" t="inlineStr">
         <is>
           <t>16_Water_Deficit</t>
         </is>
       </c>
-      <c r="F17" s="17" t="n">
+      <c r="F17" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G17" s="22" t="inlineStr">
+      <c r="G17" s="16" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="H17" s="20" t="inlineStr">
+      <c r="H17" s="15" t="inlineStr">
         <is>
           <t>Climatic Water Balance: WD = P - ETo (Negative = Deficit)</t>
         </is>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="B18" s="25" t="inlineStr">
+      <c r="B18" s="17" t="inlineStr">
         <is>
           <t>17_Dry_Months</t>
         </is>
       </c>
-      <c r="C18" s="26" t="inlineStr">
+      <c r="C18" s="9" t="inlineStr">
         <is>
           <t>عدد الأشهر الجافة بيولوجياً</t>
         </is>
       </c>
-      <c r="D18" s="25" t="inlineStr">
+      <c r="D18" s="17" t="inlineStr">
         <is>
           <t>17_Dry_Months</t>
         </is>
       </c>
-      <c r="E18" s="25" t="inlineStr">
+      <c r="E18" s="17" t="inlineStr">
         <is>
           <t>17_Dry_Months</t>
         </is>
       </c>
-      <c r="F18" s="10" t="n">
+      <c r="F18" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="G18" s="15" t="inlineStr">
+      <c r="G18" s="19" t="inlineStr">
         <is>
           <t>Months (0–12)</t>
         </is>
       </c>
-      <c r="H18" s="13" t="inlineStr">
+      <c r="H18" s="18" t="inlineStr">
         <is>
           <t>Walter-Lieth Bioclimatic Standard: P &lt; 2 * T</t>
         </is>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="B19" s="27" t="inlineStr">
+      <c r="B19" s="14" t="inlineStr">
         <is>
           <t>18_Trends_And_Anomalies</t>
         </is>
       </c>
-      <c r="C19" s="28" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>الاتجاهات والشذوذ المناخي</t>
         </is>
       </c>
-      <c r="D19" s="27" t="inlineStr">
+      <c r="D19" s="14" t="inlineStr">
         <is>
           <t>18_Trends_And_Anomalies</t>
         </is>
       </c>
-      <c r="E19" s="27" t="inlineStr">
+      <c r="E19" s="14" t="inlineStr">
         <is>
           <t>18_Trends_And_Anomalies</t>
         </is>
       </c>
-      <c r="F19" s="17" t="n">
+      <c r="F19" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="G19" s="22" t="inlineStr">
+      <c r="G19" s="16" t="inlineStr">
         <is>
           <t>°C, mm, %</t>
         </is>
       </c>
-      <c r="H19" s="20" t="inlineStr">
+      <c r="H19" s="15" t="inlineStr">
         <is>
           <t>OLS Linear Regression Trends &amp; WMO 1991–2020 Baseline Anomalies</t>
         </is>
       </c>
     </row>
     <row r="20" ht="26" customHeight="1">
-      <c r="C20" s="29" t="inlineStr">
+      <c r="C20" s="33" t="inlineStr">
         <is>
           <t>الإجمالي العام للمؤشرات المناخية:</t>
         </is>
       </c>
-      <c r="F20" s="30" t="n">
+      <c r="F20" s="34" t="n">
         <v>103</v>
       </c>
     </row>

--- a/docs/Climate_Atlas_Fields_Dictionary_AR_EN_Units.xlsx
+++ b/docs/Climate_Atlas_Fields_Dictionary_AR_EN_Units.xlsx
@@ -3025,12 +3025,12 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>R_WinTot</t>
+          <t>R_WinMean</t>
         </is>
       </c>
       <c r="C39" s="31" t="inlineStr">
         <is>
-          <t>R_Winter_Total</t>
+          <t>R_Winter_Mean</t>
         </is>
       </c>
       <c r="D39" s="15" t="inlineStr">
@@ -3040,17 +3040,17 @@
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>المجموع التراكمي لأمطار فصل الشتاء الأرصادي (شهور ديسمبر، يناير، فبراير - DJF).</t>
+          <t>متوسط هطول الأمطار خلال فصل الشتاء (شهور ديسمبر، يناير، فبراير - DJF).</t>
         </is>
       </c>
       <c r="F39" s="16" t="inlineStr">
         <is>
-          <t>ملم (mm)</t>
+          <t>مم/فصل (mm/season)</t>
         </is>
       </c>
       <c r="G39" s="32" t="inlineStr">
         <is>
-          <t>خريطة مجموع تساقط الأمطار خلال فصل الشتاء (ملم)</t>
+          <t>خريطة متوسط هطول الأمطار خلال فصل الشتاء (مم/فصل)</t>
         </is>
       </c>
     </row>
@@ -3060,12 +3060,12 @@
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>R_SprTot</t>
+          <t>R_SprMean</t>
         </is>
       </c>
       <c r="C40" s="29" t="inlineStr">
         <is>
-          <t>R_Spring_Total</t>
+          <t>R_Spring_Mean</t>
         </is>
       </c>
       <c r="D40" s="18" t="inlineStr">
@@ -3075,17 +3075,17 @@
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
-          <t>المجموع التراكمي لأمطار فصل الربيع الأرصادي (شهور مارس، أبريل، مايو - MAM).</t>
+          <t>متوسط هطول الأمطار خلال فصل الربيع (شهور مارس، أبريل، مايو - MAM).</t>
         </is>
       </c>
       <c r="F40" s="19" t="inlineStr">
         <is>
-          <t>ملم (mm)</t>
+          <t>مم/فصل (mm/season)</t>
         </is>
       </c>
       <c r="G40" s="30" t="inlineStr">
         <is>
-          <t>خريطة مجموع تساقط الأمطار خلال فصل الربيع (ملم)</t>
+          <t>خريطة متوسط هطول الأمطار خلال فصل الربيع (مم/فصل)</t>
         </is>
       </c>
     </row>
@@ -3095,12 +3095,12 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>R_SumTot</t>
+          <t>R_SumMean</t>
         </is>
       </c>
       <c r="C41" s="31" t="inlineStr">
         <is>
-          <t>R_Summer_Total</t>
+          <t>R_Summer_Mean</t>
         </is>
       </c>
       <c r="D41" s="15" t="inlineStr">
@@ -3110,17 +3110,17 @@
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>المجموع التراكمي لأمطار فصل الصيف الأرصادي (شهور يونيو، يوليو، أغسطس - JJA).</t>
+          <t>متوسط هطول الأمطار خلال فصل الصيف (شهور يونيو، يوليو، أغسطس - JJA).</t>
         </is>
       </c>
       <c r="F41" s="16" t="inlineStr">
         <is>
-          <t>ملم (mm)</t>
+          <t>مم/فصل (mm/season)</t>
         </is>
       </c>
       <c r="G41" s="32" t="inlineStr">
         <is>
-          <t>خريطة مجموع تساقط الأمطار خلال فصل الصيف (ملم)</t>
+          <t>خريطة متوسط هطول الأمطار خلال فصل الصيف (مم/فصل)</t>
         </is>
       </c>
     </row>
@@ -3130,12 +3130,12 @@
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>R_AutTot</t>
+          <t>R_AutMean</t>
         </is>
       </c>
       <c r="C42" s="29" t="inlineStr">
         <is>
-          <t>R_Autumn_Total</t>
+          <t>R_Autumn_Mean</t>
         </is>
       </c>
       <c r="D42" s="18" t="inlineStr">
@@ -3145,17 +3145,17 @@
       </c>
       <c r="E42" s="12" t="inlineStr">
         <is>
-          <t>المجموع التراكمي لأمطار فصل الخريف الأرصادي (شهور سبتمبر، أكتوبر، نوفمبر - SON).</t>
+          <t>متوسط هطول الأمطار خلال فصل الخريف (شهور سبتمبر، أكتوبر، نوفمبر - SON).</t>
         </is>
       </c>
       <c r="F42" s="19" t="inlineStr">
         <is>
-          <t>ملم (mm)</t>
+          <t>مم/فصل (mm/season)</t>
         </is>
       </c>
       <c r="G42" s="30" t="inlineStr">
         <is>
-          <t>خريطة مجموع تساقط الأمطار خلال فصل الخريف (ملم)</t>
+          <t>خريطة متوسط هطول الأمطار خلال فصل الخريف (مم/فصل)</t>
         </is>
       </c>
     </row>

--- a/docs/Climate_Atlas_Fields_Dictionary_AR_EN_Units.xlsx
+++ b/docs/Climate_Atlas_Fields_Dictionary_AR_EN_Units.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Modules_18_Summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Climate_Fields'!$A$1:$G$116</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Climate_Fields'!$A$1:$G$260</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Modules_18_Summary'!$A$1:$H$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -697,7 +697,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>1996 – 2025 (سلسلة مناخية قياسية مكتملة 30 عاماً)</t>
+          <t>1996 – 2025 (سلسلة 30 عاماً تشمل المتوسطات الشهرية والفصلية والسنوية)</t>
         </is>
       </c>
       <c r="D6" s="6" t="n"/>
@@ -766,7 +766,7 @@
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>116 حقلاً معيارياً (Standard Fields)</t>
+          <t>259 حقلاً معيارياً (247 مؤشراً مناخياً + 12 حقلاً إدارياً)</t>
         </is>
       </c>
       <c r="D9" s="11" t="n"/>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="E15" s="8" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F15" s="19" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         </is>
       </c>
       <c r="E17" s="8" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="F17" s="19" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="F18" s="16" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="E19" s="8" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="F19" s="19" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="F20" s="16" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="E21" s="8" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="F21" s="19" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="F22" s="16" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         </is>
       </c>
       <c r="E23" s="8" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="F23" s="19" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         </is>
       </c>
       <c r="E27" s="8" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="F27" s="19" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G116"/>
+  <dimension ref="A1:G260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2500,22 +2500,22 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>HI_AnnMean</t>
+          <t>T_JanMean</t>
         </is>
       </c>
       <c r="C24" s="29" t="inlineStr">
         <is>
-          <t>HI_Annual_Mean</t>
+          <t>T_January_Mean</t>
         </is>
       </c>
       <c r="D24" s="18" t="inlineStr">
         <is>
-          <t>11_Heat_Index (مؤشر الحرارة)</t>
+          <t>01_Temperature (درجة الحرارة)</t>
         </is>
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>المتوسط السنوي لمؤشر الحرارة المحسوسة المحسوب بمعادلة روتفوش وستيدمان للحرارة والرطوبة.</t>
+          <t>المتوسط الحسابي لدرجة حرارة الهواء عند ارتفاع 2 متر لشهر يناير عبر فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F24" s="19" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="G24" s="30" t="inlineStr">
         <is>
-          <t>خريطة المتوسط السنوي لمؤشر الحرارة المحسوسة (°C)</t>
+          <t>خريطة متوسط درجة الحرارة لشهر يناير (°C)</t>
         </is>
       </c>
     </row>
@@ -2535,22 +2535,22 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>HI_SumMean</t>
+          <t>T_FebMean</t>
         </is>
       </c>
       <c r="C25" s="31" t="inlineStr">
         <is>
-          <t>HI_Summer_Mean</t>
+          <t>T_February_Mean</t>
         </is>
       </c>
       <c r="D25" s="15" t="inlineStr">
         <is>
-          <t>11_Heat_Index (مؤشر الحرارة)</t>
+          <t>01_Temperature (درجة الحرارة)</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>متوسط مؤشر الحرارة المحسوسة خلال فصل الصيف (مقياس الإجهاد الحراري الفعلي).</t>
+          <t>المتوسط الحسابي لدرجة حرارة الهواء عند ارتفاع 2 متر لشهر فبراير عبر فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F25" s="16" t="inlineStr">
@@ -2560,7 +2560,7 @@
       </c>
       <c r="G25" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط مؤشر الحرارة المحسوسة خلال فصل الصيف (°C)</t>
+          <t>خريطة متوسط درجة الحرارة لشهر فبراير (°C)</t>
         </is>
       </c>
     </row>
@@ -2570,22 +2570,22 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>HI_WinMean</t>
+          <t>T_MarMean</t>
         </is>
       </c>
       <c r="C26" s="29" t="inlineStr">
         <is>
-          <t>HI_Winter_Mean</t>
+          <t>T_March_Mean</t>
         </is>
       </c>
       <c r="D26" s="18" t="inlineStr">
         <is>
-          <t>11_Heat_Index (مؤشر الحرارة)</t>
+          <t>01_Temperature (درجة الحرارة)</t>
         </is>
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
-          <t>متوسط مؤشر الحرارة الظاهرية/الهيوميدكس خلال فصل الشتاء في الأجواء الباردة والرطبة.</t>
+          <t>المتوسط الحسابي لدرجة حرارة الهواء عند ارتفاع 2 متر لشهر مارس عبر فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F26" s="19" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="G26" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط درجة الحرارة المحسوسة خلال فصل الشتاء (°C)</t>
+          <t>خريطة متوسط درجة الحرارة لشهر مارس (°C)</t>
         </is>
       </c>
     </row>
@@ -2605,22 +2605,22 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>HI_AnRng</t>
+          <t>T_AprMean</t>
         </is>
       </c>
       <c r="C27" s="31" t="inlineStr">
         <is>
-          <t>HI_Annual_Range</t>
+          <t>T_April_Mean</t>
         </is>
       </c>
       <c r="D27" s="15" t="inlineStr">
         <is>
-          <t>11_Heat_Index (مؤشر الحرارة)</t>
+          <t>01_Temperature (درجة الحرارة)</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>المدى السنوي لمؤشر الحرارة المحسوسة (الفارق بين أعلى شهر إجهاد حراري وأدنى شهر).</t>
+          <t>المتوسط الحسابي لدرجة حرارة الهواء عند ارتفاع 2 متر لشهر أبريل عبر فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F27" s="16" t="inlineStr">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="G27" s="32" t="inlineStr">
         <is>
-          <t>خريطة المدى السنوي لمؤشر الحرارة المحسوسة (°C)</t>
+          <t>خريطة متوسط درجة الحرارة لشهر أبريل (°C)</t>
         </is>
       </c>
     </row>
@@ -2640,22 +2640,22 @@
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>WBGT_SuMn</t>
+          <t>T_MayMean</t>
         </is>
       </c>
       <c r="C28" s="29" t="inlineStr">
         <is>
-          <t>WBGT_Summer_Mean</t>
+          <t>T_May_Mean</t>
         </is>
       </c>
       <c r="D28" s="18" t="inlineStr">
         <is>
-          <t>11_Heat_Index (مؤشر الحرارة)</t>
+          <t>01_Temperature (درجة الحرارة)</t>
         </is>
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>متوسط درجة حرارة البصيلة الرطبة الكروية الصيفي في الظل (معيار ISO 7243 للإجهاد المهني والرياضي).</t>
+          <t>المتوسط الحسابي لدرجة حرارة الهواء عند ارتفاع 2 متر لشهر مايو عبر فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F28" s="19" t="inlineStr">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="G28" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط مؤشر الإجهاد الحراري الصيفي (WBGT) (°C)</t>
+          <t>خريطة متوسط درجة الحرارة لشهر مايو (°C)</t>
         </is>
       </c>
     </row>
@@ -2675,22 +2675,22 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Td_AnnMean</t>
+          <t>T_JunMean</t>
         </is>
       </c>
       <c r="C29" s="31" t="inlineStr">
         <is>
-          <t>Td_Annual_Mean</t>
+          <t>T_June_Mean</t>
         </is>
       </c>
       <c r="D29" s="15" t="inlineStr">
         <is>
-          <t>07_Dew_Point (نقطة الندى)</t>
+          <t>01_Temperature (درجة الحرارة)</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>المتوسط الحسابي السنوي لدرجة حرارة نقطة الندى عند ارتفاع 2 متر.</t>
+          <t>المتوسط الحسابي لدرجة حرارة الهواء عند ارتفاع 2 متر لشهر يونيو عبر فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F29" s="16" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="G29" s="32" t="inlineStr">
         <is>
-          <t>خريطة المتوسط السنوي لدرجة حرارة نقطة الندى (°C)</t>
+          <t>خريطة متوسط درجة الحرارة لشهر يونيو (°C)</t>
         </is>
       </c>
     </row>
@@ -2710,22 +2710,22 @@
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>Td_WinMean</t>
+          <t>T_JulMean</t>
         </is>
       </c>
       <c r="C30" s="29" t="inlineStr">
         <is>
-          <t>Td_Winter_Mean</t>
+          <t>T_July_Mean</t>
         </is>
       </c>
       <c r="D30" s="18" t="inlineStr">
         <is>
-          <t>07_Dew_Point (نقطة الندى)</t>
+          <t>01_Temperature (درجة الحرارة)</t>
         </is>
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
-          <t>متوسط درجة حرارة نقطة الندى خلال فصل الشتاء الأرصادي (DJF).</t>
+          <t>المتوسط الحسابي لدرجة حرارة الهواء عند ارتفاع 2 متر لشهر يوليو عبر فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F30" s="19" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="G30" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط درجة حرارة نقطة الندى خلال فصل الشتاء (°C)</t>
+          <t>خريطة متوسط درجة الحرارة لشهر يوليو (°C)</t>
         </is>
       </c>
     </row>
@@ -2745,22 +2745,22 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Td_SprMean</t>
+          <t>T_AugMean</t>
         </is>
       </c>
       <c r="C31" s="31" t="inlineStr">
         <is>
-          <t>Td_Spring_Mean</t>
+          <t>T_August_Mean</t>
         </is>
       </c>
       <c r="D31" s="15" t="inlineStr">
         <is>
-          <t>07_Dew_Point (نقطة الندى)</t>
+          <t>01_Temperature (درجة الحرارة)</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>متوسط درجة حرارة نقطة الندى خلال فصل الربيع الأرصادي (MAM).</t>
+          <t>المتوسط الحسابي لدرجة حرارة الهواء عند ارتفاع 2 متر لشهر أغسطس عبر فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F31" s="16" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="G31" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط درجة حرارة نقطة الندى خلال فصل الربيع (°C)</t>
+          <t>خريطة متوسط درجة الحرارة لشهر أغسطس (°C)</t>
         </is>
       </c>
     </row>
@@ -2780,22 +2780,22 @@
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>Td_SumMean</t>
+          <t>T_SepMean</t>
         </is>
       </c>
       <c r="C32" s="29" t="inlineStr">
         <is>
-          <t>Td_Summer_Mean</t>
+          <t>T_September_Mean</t>
         </is>
       </c>
       <c r="D32" s="18" t="inlineStr">
         <is>
-          <t>07_Dew_Point (نقطة الندى)</t>
+          <t>01_Temperature (درجة الحرارة)</t>
         </is>
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>متوسط درجة حرارة نقطة الندى خلال فصل الصيف الأرصادي (JJA - مؤشر مباشر للرطوبة الخانقة والكتمة).</t>
+          <t>المتوسط الحسابي لدرجة حرارة الهواء عند ارتفاع 2 متر لشهر سبتمبر عبر فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F32" s="19" t="inlineStr">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="G32" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط درجة حرارة نقطة الندى خلال فصل الصيف (°C)</t>
+          <t>خريطة متوسط درجة الحرارة لشهر سبتمبر (°C)</t>
         </is>
       </c>
     </row>
@@ -2815,22 +2815,22 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Td_AutMean</t>
+          <t>T_OctMean</t>
         </is>
       </c>
       <c r="C33" s="31" t="inlineStr">
         <is>
-          <t>Td_Autumn_Mean</t>
+          <t>T_October_Mean</t>
         </is>
       </c>
       <c r="D33" s="15" t="inlineStr">
         <is>
-          <t>07_Dew_Point (نقطة الندى)</t>
+          <t>01_Temperature (درجة الحرارة)</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>متوسط درجة حرارة نقطة الندى خلال فصل الخريف الأرصادي (SON).</t>
+          <t>المتوسط الحسابي لدرجة حرارة الهواء عند ارتفاع 2 متر لشهر أكتوبر عبر فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F33" s="16" t="inlineStr">
@@ -2840,7 +2840,7 @@
       </c>
       <c r="G33" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط درجة حرارة نقطة الندى خلال فصل الخريف (°C)</t>
+          <t>خريطة متوسط درجة الحرارة لشهر أكتوبر (°C)</t>
         </is>
       </c>
     </row>
@@ -2850,22 +2850,22 @@
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>Td_AnnRng</t>
+          <t>T_NovMean</t>
         </is>
       </c>
       <c r="C34" s="29" t="inlineStr">
         <is>
-          <t>Td_Annual_Range</t>
+          <t>T_November_Mean</t>
         </is>
       </c>
       <c r="D34" s="18" t="inlineStr">
         <is>
-          <t>07_Dew_Point (نقطة الندى)</t>
+          <t>01_Temperature (درجة الحرارة)</t>
         </is>
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>المدى السنوي لدرجة حرارة نقطة الندى (الفارق بين أعلى وأدنى متوسط شهري لنقطة الندى).</t>
+          <t>المتوسط الحسابي لدرجة حرارة الهواء عند ارتفاع 2 متر لشهر نوفمبر عبر فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F34" s="19" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="G34" s="30" t="inlineStr">
         <is>
-          <t>خريطة المدى السنوي لدرجة حرارة نقطة الندى (°C)</t>
+          <t>خريطة متوسط درجة الحرارة لشهر نوفمبر (°C)</t>
         </is>
       </c>
     </row>
@@ -2885,32 +2885,32 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>R_AnnMean</t>
+          <t>T_DecMean</t>
         </is>
       </c>
       <c r="C35" s="31" t="inlineStr">
         <is>
-          <t>R_Annual_Mean</t>
+          <t>T_December_Mean</t>
         </is>
       </c>
       <c r="D35" s="15" t="inlineStr">
         <is>
-          <t>02_Precipitation (الأمطار)</t>
+          <t>01_Temperature (درجة الحرارة)</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>المتوسط السنوي لتساقط الأمطار (متوسط مجاميع السنين على مدار فترة الرصد 1996–2025).</t>
+          <t>المتوسط الحسابي لدرجة حرارة الهواء عند ارتفاع 2 متر لشهر ديسمبر عبر فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F35" s="16" t="inlineStr">
         <is>
-          <t>ملم (mm)</t>
+          <t>°C</t>
         </is>
       </c>
       <c r="G35" s="32" t="inlineStr">
         <is>
-          <t>خريطة المتوسط السنوي لتساقط الأمطار (ملم)</t>
+          <t>خريطة متوسط درجة الحرارة لشهر ديسمبر (°C)</t>
         </is>
       </c>
     </row>
@@ -2920,32 +2920,32 @@
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>R_MonMean</t>
+          <t>HI_AnnMean</t>
         </is>
       </c>
       <c r="C36" s="29" t="inlineStr">
         <is>
-          <t>R_Month_Mean</t>
+          <t>HI_Annual_Mean</t>
         </is>
       </c>
       <c r="D36" s="18" t="inlineStr">
         <is>
-          <t>02_Precipitation (الأمطار)</t>
+          <t>11_Heat_Index (مؤشر الحرارة)</t>
         </is>
       </c>
       <c r="E36" s="12" t="inlineStr">
         <is>
-          <t>المتوسط الشهري لتساقط الأمطار (المتوسط السنوي مقسوماً على 12 شهراً).</t>
+          <t>المتوسط السنوي لمؤشر الحرارة المحسوسة المحسوب بمعادلة روتفوش وستيدمان للحرارة والرطوبة.</t>
         </is>
       </c>
       <c r="F36" s="19" t="inlineStr">
         <is>
-          <t>ملم (mm)</t>
+          <t>°C</t>
         </is>
       </c>
       <c r="G36" s="30" t="inlineStr">
         <is>
-          <t>خريطة المتوسط الشهري لتساقط الأمطار (ملم)</t>
+          <t>خريطة المتوسط السنوي لمؤشر الحرارة المحسوسة (°C)</t>
         </is>
       </c>
     </row>
@@ -2955,32 +2955,32 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>R_AnnRng</t>
+          <t>HI_SumMean</t>
         </is>
       </c>
       <c r="C37" s="31" t="inlineStr">
         <is>
-          <t>R_Annual_Range</t>
+          <t>HI_Summer_Mean</t>
         </is>
       </c>
       <c r="D37" s="15" t="inlineStr">
         <is>
-          <t>02_Precipitation (الأمطار)</t>
+          <t>11_Heat_Index (مؤشر الحرارة)</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>المدى السنوي لتساقط الأمطار (الفارق بين أعلى شهر مطراً وأقل شهر مطراً في السنة).</t>
+          <t>متوسط مؤشر الحرارة المحسوسة خلال فصل الصيف (مقياس الإجهاد الحراري الفعلي).</t>
         </is>
       </c>
       <c r="F37" s="16" t="inlineStr">
         <is>
-          <t>ملم (mm)</t>
+          <t>°C</t>
         </is>
       </c>
       <c r="G37" s="32" t="inlineStr">
         <is>
-          <t>خريطة المدى السنوي لتساقط الأمطار (ملم)</t>
+          <t>خريطة متوسط مؤشر الحرارة المحسوسة خلال فصل الصيف (°C)</t>
         </is>
       </c>
     </row>
@@ -2990,32 +2990,32 @@
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>R_SeaRng</t>
+          <t>HI_WinMean</t>
         </is>
       </c>
       <c r="C38" s="29" t="inlineStr">
         <is>
-          <t>R_Seasonal_Range</t>
+          <t>HI_Winter_Mean</t>
         </is>
       </c>
       <c r="D38" s="18" t="inlineStr">
         <is>
-          <t>02_Precipitation (الأمطار)</t>
+          <t>11_Heat_Index (مؤشر الحرارة)</t>
         </is>
       </c>
       <c r="E38" s="12" t="inlineStr">
         <is>
-          <t>المدى الفصلي لتساقط الأمطار (الفارق بين مجموع أعلى فصول السنة مطراً ومجموع أقلها مطراً).</t>
+          <t>متوسط مؤشر الحرارة الظاهرية/الهيوميدكس خلال فصل الشتاء في الأجواء الباردة والرطبة.</t>
         </is>
       </c>
       <c r="F38" s="19" t="inlineStr">
         <is>
-          <t>ملم (mm)</t>
+          <t>°C</t>
         </is>
       </c>
       <c r="G38" s="30" t="inlineStr">
         <is>
-          <t>خريطة المدى الفصلي لتساقط الأمطار (ملم)</t>
+          <t>خريطة متوسط درجة الحرارة المحسوسة خلال فصل الشتاء (°C)</t>
         </is>
       </c>
     </row>
@@ -3025,32 +3025,32 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>R_WinMean</t>
+          <t>HI_AnRng</t>
         </is>
       </c>
       <c r="C39" s="31" t="inlineStr">
         <is>
-          <t>R_Winter_Mean</t>
+          <t>HI_Annual_Range</t>
         </is>
       </c>
       <c r="D39" s="15" t="inlineStr">
         <is>
-          <t>02_Precipitation (الأمطار)</t>
+          <t>11_Heat_Index (مؤشر الحرارة)</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>متوسط هطول الأمطار خلال فصل الشتاء (شهور ديسمبر، يناير، فبراير - DJF).</t>
+          <t>المدى السنوي لمؤشر الحرارة المحسوسة (الفارق بين أعلى شهر إجهاد حراري وأدنى شهر).</t>
         </is>
       </c>
       <c r="F39" s="16" t="inlineStr">
         <is>
-          <t>مم/فصل (mm/season)</t>
+          <t>°C</t>
         </is>
       </c>
       <c r="G39" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط هطول الأمطار خلال فصل الشتاء (مم/فصل)</t>
+          <t>خريطة المدى السنوي لمؤشر الحرارة المحسوسة (°C)</t>
         </is>
       </c>
     </row>
@@ -3060,32 +3060,32 @@
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>R_SprMean</t>
+          <t>WBGT_SuMn</t>
         </is>
       </c>
       <c r="C40" s="29" t="inlineStr">
         <is>
-          <t>R_Spring_Mean</t>
+          <t>WBGT_Summer_Mean</t>
         </is>
       </c>
       <c r="D40" s="18" t="inlineStr">
         <is>
-          <t>02_Precipitation (الأمطار)</t>
+          <t>11_Heat_Index (مؤشر الحرارة)</t>
         </is>
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
-          <t>متوسط هطول الأمطار خلال فصل الربيع (شهور مارس، أبريل، مايو - MAM).</t>
+          <t>متوسط درجة حرارة البصيلة الرطبة الكروية الصيفي في الظل (معيار ISO 7243 للإجهاد المهني والرياضي).</t>
         </is>
       </c>
       <c r="F40" s="19" t="inlineStr">
         <is>
-          <t>مم/فصل (mm/season)</t>
+          <t>°C</t>
         </is>
       </c>
       <c r="G40" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط هطول الأمطار خلال فصل الربيع (مم/فصل)</t>
+          <t>خريطة متوسط مؤشر الإجهاد الحراري الصيفي (WBGT) (°C)</t>
         </is>
       </c>
     </row>
@@ -3095,32 +3095,32 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>R_SumMean</t>
+          <t>Td_AnnMean</t>
         </is>
       </c>
       <c r="C41" s="31" t="inlineStr">
         <is>
-          <t>R_Summer_Mean</t>
+          <t>Td_Annual_Mean</t>
         </is>
       </c>
       <c r="D41" s="15" t="inlineStr">
         <is>
-          <t>02_Precipitation (الأمطار)</t>
+          <t>07_Dew_Point (نقطة الندى)</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>متوسط هطول الأمطار خلال فصل الصيف (شهور يونيو، يوليو، أغسطس - JJA).</t>
+          <t>المتوسط الحسابي السنوي لدرجة حرارة نقطة الندى عند ارتفاع 2 متر.</t>
         </is>
       </c>
       <c r="F41" s="16" t="inlineStr">
         <is>
-          <t>مم/فصل (mm/season)</t>
+          <t>°C</t>
         </is>
       </c>
       <c r="G41" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط هطول الأمطار خلال فصل الصيف (مم/فصل)</t>
+          <t>خريطة المتوسط السنوي لدرجة حرارة نقطة الندى (°C)</t>
         </is>
       </c>
     </row>
@@ -3130,32 +3130,32 @@
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>R_AutMean</t>
+          <t>Td_WinMean</t>
         </is>
       </c>
       <c r="C42" s="29" t="inlineStr">
         <is>
-          <t>R_Autumn_Mean</t>
+          <t>Td_Winter_Mean</t>
         </is>
       </c>
       <c r="D42" s="18" t="inlineStr">
         <is>
-          <t>02_Precipitation (الأمطار)</t>
+          <t>07_Dew_Point (نقطة الندى)</t>
         </is>
       </c>
       <c r="E42" s="12" t="inlineStr">
         <is>
-          <t>متوسط هطول الأمطار خلال فصل الخريف (شهور سبتمبر، أكتوبر، نوفمبر - SON).</t>
+          <t>متوسط درجة حرارة نقطة الندى خلال فصل الشتاء الأرصادي (DJF).</t>
         </is>
       </c>
       <c r="F42" s="19" t="inlineStr">
         <is>
-          <t>مم/فصل (mm/season)</t>
+          <t>°C</t>
         </is>
       </c>
       <c r="G42" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط هطول الأمطار خلال فصل الخريف (مم/فصل)</t>
+          <t>خريطة متوسط درجة حرارة نقطة الندى خلال فصل الشتاء (°C)</t>
         </is>
       </c>
     </row>
@@ -3165,32 +3165,32 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>PSL_AnMean</t>
+          <t>Td_SprMean</t>
         </is>
       </c>
       <c r="C43" s="31" t="inlineStr">
         <is>
-          <t>PSL_Annual_Mean</t>
+          <t>Td_Spring_Mean</t>
         </is>
       </c>
       <c r="D43" s="15" t="inlineStr">
         <is>
-          <t>03_Sea_Level_Pressure (ضغط مستوى البحر)</t>
+          <t>07_Dew_Point (نقطة الندى)</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي السنوي المصحح عند مستوى سطح البحر القياسي (Sea Level Pressure).</t>
+          <t>متوسط درجة حرارة نقطة الندى خلال فصل الربيع الأرصادي (MAM).</t>
         </is>
       </c>
       <c r="F43" s="16" t="inlineStr">
         <is>
-          <t>hPa / mbar</t>
+          <t>°C</t>
         </is>
       </c>
       <c r="G43" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط الضغط الجوي عند مستوى سطح البحر (hPa)</t>
+          <t>خريطة متوسط درجة حرارة نقطة الندى خلال فصل الربيع (°C)</t>
         </is>
       </c>
     </row>
@@ -3200,32 +3200,32 @@
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>PSL_WnMean</t>
+          <t>Td_SumMean</t>
         </is>
       </c>
       <c r="C44" s="29" t="inlineStr">
         <is>
-          <t>PSL_Winter_Mean</t>
+          <t>Td_Summer_Mean</t>
         </is>
       </c>
       <c r="D44" s="18" t="inlineStr">
         <is>
-          <t>03_Sea_Level_Pressure (ضغط مستوى البحر)</t>
+          <t>07_Dew_Point (نقطة الندى)</t>
         </is>
       </c>
       <c r="E44" s="12" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي عند مستوى سطح البحر لفصل الشتاء الأرصادي (DJF).</t>
+          <t>متوسط درجة حرارة نقطة الندى خلال فصل الصيف الأرصادي (JJA - مؤشر مباشر للرطوبة الخانقة والكتمة).</t>
         </is>
       </c>
       <c r="F44" s="19" t="inlineStr">
         <is>
-          <t>hPa / mbar</t>
+          <t>°C</t>
         </is>
       </c>
       <c r="G44" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط ضغط مستوى سطح البحر خلال فصل الشتاء (hPa)</t>
+          <t>خريطة متوسط درجة حرارة نقطة الندى خلال فصل الصيف (°C)</t>
         </is>
       </c>
     </row>
@@ -3235,32 +3235,32 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>PSL_SpMean</t>
+          <t>Td_AutMean</t>
         </is>
       </c>
       <c r="C45" s="31" t="inlineStr">
         <is>
-          <t>PSL_Spring_Mean</t>
+          <t>Td_Autumn_Mean</t>
         </is>
       </c>
       <c r="D45" s="15" t="inlineStr">
         <is>
-          <t>03_Sea_Level_Pressure (ضغط مستوى البحر)</t>
+          <t>07_Dew_Point (نقطة الندى)</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي عند مستوى سطح البحر لفصل الربيع الأرصادي (MAM).</t>
+          <t>متوسط درجة حرارة نقطة الندى خلال فصل الخريف الأرصادي (SON).</t>
         </is>
       </c>
       <c r="F45" s="16" t="inlineStr">
         <is>
-          <t>hPa / mbar</t>
+          <t>°C</t>
         </is>
       </c>
       <c r="G45" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط ضغط مستوى سطح البحر خلال فصل الربيع (hPa)</t>
+          <t>خريطة متوسط درجة حرارة نقطة الندى خلال فصل الخريف (°C)</t>
         </is>
       </c>
     </row>
@@ -3270,32 +3270,32 @@
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>PSL_SuMean</t>
+          <t>Td_AnnRng</t>
         </is>
       </c>
       <c r="C46" s="29" t="inlineStr">
         <is>
-          <t>PSL_Summer_Mean</t>
+          <t>Td_Annual_Range</t>
         </is>
       </c>
       <c r="D46" s="18" t="inlineStr">
         <is>
-          <t>03_Sea_Level_Pressure (ضغط مستوى البحر)</t>
+          <t>07_Dew_Point (نقطة الندى)</t>
         </is>
       </c>
       <c r="E46" s="12" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي عند مستوى سطح البحر لفصل الصيف الأرصادي (JJA).</t>
+          <t>المدى السنوي لدرجة حرارة نقطة الندى (الفارق بين أعلى وأدنى متوسط شهري لنقطة الندى).</t>
         </is>
       </c>
       <c r="F46" s="19" t="inlineStr">
         <is>
-          <t>hPa / mbar</t>
+          <t>°C</t>
         </is>
       </c>
       <c r="G46" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط ضغط مستوى سطح البحر خلال فصل الصيف (hPa)</t>
+          <t>خريطة المدى السنوي لدرجة حرارة نقطة الندى (°C)</t>
         </is>
       </c>
     </row>
@@ -3305,32 +3305,32 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>PSL_AuMean</t>
+          <t>Td_JanMean</t>
         </is>
       </c>
       <c r="C47" s="31" t="inlineStr">
         <is>
-          <t>PSL_Autumn_Mean</t>
+          <t>Td_January_Mean</t>
         </is>
       </c>
       <c r="D47" s="15" t="inlineStr">
         <is>
-          <t>03_Sea_Level_Pressure (ضغط مستوى البحر)</t>
+          <t>07_Dew_Point (نقطة الندى)</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي عند مستوى سطح البحر لفصل الخريف الأرصادي (SON).</t>
+          <t>متوسط درجة حرارة نقطة الندى عند ارتفاع 2 متر لشهر يناير.</t>
         </is>
       </c>
       <c r="F47" s="16" t="inlineStr">
         <is>
-          <t>hPa / mbar</t>
+          <t>°C</t>
         </is>
       </c>
       <c r="G47" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط ضغط مستوى سطح البحر خلال فصل الخريف (hPa)</t>
+          <t>خريطة متوسط درجة حرارة نقطة الندى لشهر يناير (°C)</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>PSL_AnRng</t>
+          <t>Td_FebMean</t>
         </is>
       </c>
       <c r="C48" s="29" t="inlineStr">
         <is>
-          <t>PSL_Annual_Range</t>
+          <t>Td_February_Mean</t>
         </is>
       </c>
       <c r="D48" s="18" t="inlineStr">
         <is>
-          <t>03_Sea_Level_Pressure (ضغط مستوى البحر)</t>
+          <t>07_Dew_Point (نقطة الندى)</t>
         </is>
       </c>
       <c r="E48" s="12" t="inlineStr">
         <is>
-          <t>المدى البارومتري السنوي لضغط مستوى البحر (الفارق بين أعلى وأدنى متوسط شهري للضغط).</t>
+          <t>متوسط درجة حرارة نقطة الندى عند ارتفاع 2 متر لشهر فبراير.</t>
         </is>
       </c>
       <c r="F48" s="19" t="inlineStr">
         <is>
-          <t>hPa / mbar</t>
+          <t>°C</t>
         </is>
       </c>
       <c r="G48" s="30" t="inlineStr">
         <is>
-          <t>خريطة المدى السنوي لضغط مستوى سطح البحر (hPa)</t>
+          <t>خريطة متوسط درجة حرارة نقطة الندى لشهر فبراير (°C)</t>
         </is>
       </c>
     </row>
@@ -3375,32 +3375,32 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>PS_AnnMean</t>
+          <t>Td_MarMean</t>
         </is>
       </c>
       <c r="C49" s="31" t="inlineStr">
         <is>
-          <t>PS_Annual_Mean</t>
+          <t>Td_March_Mean</t>
         </is>
       </c>
       <c r="D49" s="15" t="inlineStr">
         <is>
-          <t>04_Surface_Pressure (الضغط السطحي)</t>
+          <t>07_Dew_Point (نقطة الندى)</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>المتوسط السنوي للضغط الجوي السطحي الفعلي الحقيقي عند منسوب تضاريس المحطة.</t>
+          <t>متوسط درجة حرارة نقطة الندى عند ارتفاع 2 متر لشهر مارس.</t>
         </is>
       </c>
       <c r="F49" s="16" t="inlineStr">
         <is>
-          <t>hPa / mbar</t>
+          <t>°C</t>
         </is>
       </c>
       <c r="G49" s="32" t="inlineStr">
         <is>
-          <t>خريطة المتوسط السنوي للضغط الجوي السطحي (hPa)</t>
+          <t>خريطة متوسط درجة حرارة نقطة الندى لشهر مارس (°C)</t>
         </is>
       </c>
     </row>
@@ -3410,32 +3410,32 @@
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>PS_WinMean</t>
+          <t>Td_AprMean</t>
         </is>
       </c>
       <c r="C50" s="29" t="inlineStr">
         <is>
-          <t>PS_Winter_Mean</t>
+          <t>Td_April_Mean</t>
         </is>
       </c>
       <c r="D50" s="18" t="inlineStr">
         <is>
-          <t>04_Surface_Pressure (الضغط السطحي)</t>
+          <t>07_Dew_Point (نقطة الندى)</t>
         </is>
       </c>
       <c r="E50" s="12" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي السطحي الفعلي لفصل الشتاء الأرصادي (DJF).</t>
+          <t>متوسط درجة حرارة نقطة الندى عند ارتفاع 2 متر لشهر أبريل.</t>
         </is>
       </c>
       <c r="F50" s="19" t="inlineStr">
         <is>
-          <t>hPa / mbar</t>
+          <t>°C</t>
         </is>
       </c>
       <c r="G50" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط الضغط السطحي خلال فصل الشتاء (hPa)</t>
+          <t>خريطة متوسط درجة حرارة نقطة الندى لشهر أبريل (°C)</t>
         </is>
       </c>
     </row>
@@ -3445,32 +3445,32 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>PS_SprMean</t>
+          <t>Td_MayMean</t>
         </is>
       </c>
       <c r="C51" s="31" t="inlineStr">
         <is>
-          <t>PS_Spring_Mean</t>
+          <t>Td_May_Mean</t>
         </is>
       </c>
       <c r="D51" s="15" t="inlineStr">
         <is>
-          <t>04_Surface_Pressure (الضغط السطحي)</t>
+          <t>07_Dew_Point (نقطة الندى)</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي السطحي الفعلي لفصل الربيع الأرصادي (MAM).</t>
+          <t>متوسط درجة حرارة نقطة الندى عند ارتفاع 2 متر لشهر مايو.</t>
         </is>
       </c>
       <c r="F51" s="16" t="inlineStr">
         <is>
-          <t>hPa / mbar</t>
+          <t>°C</t>
         </is>
       </c>
       <c r="G51" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط الضغط السطحي خلال فصل الربيع (hPa)</t>
+          <t>خريطة متوسط درجة حرارة نقطة الندى لشهر مايو (°C)</t>
         </is>
       </c>
     </row>
@@ -3480,32 +3480,32 @@
       </c>
       <c r="B52" s="10" t="inlineStr">
         <is>
-          <t>PS_SumMean</t>
+          <t>Td_JunMean</t>
         </is>
       </c>
       <c r="C52" s="29" t="inlineStr">
         <is>
-          <t>PS_Summer_Mean</t>
+          <t>Td_June_Mean</t>
         </is>
       </c>
       <c r="D52" s="18" t="inlineStr">
         <is>
-          <t>04_Surface_Pressure (الضغط السطحي)</t>
+          <t>07_Dew_Point (نقطة الندى)</t>
         </is>
       </c>
       <c r="E52" s="12" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي السطحي الفعلي لفصل الصيف الأرصادي (JJA).</t>
+          <t>متوسط درجة حرارة نقطة الندى عند ارتفاع 2 متر لشهر يونيو.</t>
         </is>
       </c>
       <c r="F52" s="19" t="inlineStr">
         <is>
-          <t>hPa / mbar</t>
+          <t>°C</t>
         </is>
       </c>
       <c r="G52" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط الضغط السطحي خلال فصل الصيف (hPa)</t>
+          <t>خريطة متوسط درجة حرارة نقطة الندى لشهر يونيو (°C)</t>
         </is>
       </c>
     </row>
@@ -3515,32 +3515,32 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>PS_AutMean</t>
+          <t>Td_JulMean</t>
         </is>
       </c>
       <c r="C53" s="31" t="inlineStr">
         <is>
-          <t>PS_Autumn_Mean</t>
+          <t>Td_July_Mean</t>
         </is>
       </c>
       <c r="D53" s="15" t="inlineStr">
         <is>
-          <t>04_Surface_Pressure (الضغط السطحي)</t>
+          <t>07_Dew_Point (نقطة الندى)</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي السطحي الفعلي لفصل الخريف الأرصادي (SON).</t>
+          <t>متوسط درجة حرارة نقطة الندى عند ارتفاع 2 متر لشهر يوليو.</t>
         </is>
       </c>
       <c r="F53" s="16" t="inlineStr">
         <is>
-          <t>hPa / mbar</t>
+          <t>°C</t>
         </is>
       </c>
       <c r="G53" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط الضغط السطحي خلال فصل الخريف (hPa)</t>
+          <t>خريطة متوسط درجة حرارة نقطة الندى لشهر يوليو (°C)</t>
         </is>
       </c>
     </row>
@@ -3550,32 +3550,32 @@
       </c>
       <c r="B54" s="10" t="inlineStr">
         <is>
-          <t>PS_AnnRng</t>
+          <t>Td_AugMean</t>
         </is>
       </c>
       <c r="C54" s="29" t="inlineStr">
         <is>
-          <t>PS_Annual_Range</t>
+          <t>Td_August_Mean</t>
         </is>
       </c>
       <c r="D54" s="18" t="inlineStr">
         <is>
-          <t>04_Surface_Pressure (الضغط السطحي)</t>
+          <t>07_Dew_Point (نقطة الندى)</t>
         </is>
       </c>
       <c r="E54" s="12" t="inlineStr">
         <is>
-          <t>المدى البارومتري السنوي للضغط السطحي (الفارق بين أعلى وأدنى متوسط شهري للضغط السطحي).</t>
+          <t>متوسط درجة حرارة نقطة الندى عند ارتفاع 2 متر لشهر أغسطس.</t>
         </is>
       </c>
       <c r="F54" s="19" t="inlineStr">
         <is>
-          <t>hPa / mbar</t>
+          <t>°C</t>
         </is>
       </c>
       <c r="G54" s="30" t="inlineStr">
         <is>
-          <t>خريطة المدى السنوي للضغط الجوي السطحي (hPa)</t>
+          <t>خريطة متوسط درجة حرارة نقطة الندى لشهر أغسطس (°C)</t>
         </is>
       </c>
     </row>
@@ -3585,32 +3585,32 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>WSp_AnMean</t>
+          <t>Td_SepMean</t>
         </is>
       </c>
       <c r="C55" s="31" t="inlineStr">
         <is>
-          <t>W_Spd_Annual_Mean</t>
+          <t>Td_September_Mean</t>
         </is>
       </c>
       <c r="D55" s="15" t="inlineStr">
         <is>
-          <t>05_Wind (الرياح)</t>
+          <t>07_Dew_Point (نقطة الندى)</t>
         </is>
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>المتوسط السنوي لسرعة الرياح عند ارتفاع 10 أمتار فوق سطح الأرض.</t>
+          <t>متوسط درجة حرارة نقطة الندى عند ارتفاع 2 متر لشهر سبتمبر.</t>
         </is>
       </c>
       <c r="F55" s="16" t="inlineStr">
         <is>
-          <t>م/ث (m/s)</t>
+          <t>°C</t>
         </is>
       </c>
       <c r="G55" s="32" t="inlineStr">
         <is>
-          <t>خريطة المتوسط السنوي لسرعة الرياح (م/ث)</t>
+          <t>خريطة متوسط درجة حرارة نقطة الندى لشهر سبتمبر (°C)</t>
         </is>
       </c>
     </row>
@@ -3620,32 +3620,32 @@
       </c>
       <c r="B56" s="10" t="inlineStr">
         <is>
-          <t>WSp_WnMean</t>
+          <t>Td_OctMean</t>
         </is>
       </c>
       <c r="C56" s="29" t="inlineStr">
         <is>
-          <t>W_Spd_Winter_Mean</t>
+          <t>Td_October_Mean</t>
         </is>
       </c>
       <c r="D56" s="18" t="inlineStr">
         <is>
-          <t>05_Wind (الرياح)</t>
+          <t>07_Dew_Point (نقطة الندى)</t>
         </is>
       </c>
       <c r="E56" s="12" t="inlineStr">
         <is>
-          <t>متوسط سرعة الرياح لفصل الشتاء الأرصادي عند ارتفاع 10 أمتار (DJF).</t>
+          <t>متوسط درجة حرارة نقطة الندى عند ارتفاع 2 متر لشهر أكتوبر.</t>
         </is>
       </c>
       <c r="F56" s="19" t="inlineStr">
         <is>
-          <t>م/ث (m/s)</t>
+          <t>°C</t>
         </is>
       </c>
       <c r="G56" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط سرعة الرياح خلال فصل الشتاء (م/ث)</t>
+          <t>خريطة متوسط درجة حرارة نقطة الندى لشهر أكتوبر (°C)</t>
         </is>
       </c>
     </row>
@@ -3655,32 +3655,32 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>WSp_SpMean</t>
+          <t>Td_NovMean</t>
         </is>
       </c>
       <c r="C57" s="31" t="inlineStr">
         <is>
-          <t>W_Spd_Spring_Mean</t>
+          <t>Td_November_Mean</t>
         </is>
       </c>
       <c r="D57" s="15" t="inlineStr">
         <is>
-          <t>05_Wind (الرياح)</t>
+          <t>07_Dew_Point (نقطة الندى)</t>
         </is>
       </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
-          <t>متوسط سرعة الرياح لفصل الربيع الأرصادي عند ارتفاع 10 أمتار (MAM).</t>
+          <t>متوسط درجة حرارة نقطة الندى عند ارتفاع 2 متر لشهر نوفمبر.</t>
         </is>
       </c>
       <c r="F57" s="16" t="inlineStr">
         <is>
-          <t>م/ث (m/s)</t>
+          <t>°C</t>
         </is>
       </c>
       <c r="G57" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط سرعة الرياح خلال فصل الربيع (م/ث)</t>
+          <t>خريطة متوسط درجة حرارة نقطة الندى لشهر نوفمبر (°C)</t>
         </is>
       </c>
     </row>
@@ -3690,32 +3690,32 @@
       </c>
       <c r="B58" s="10" t="inlineStr">
         <is>
-          <t>WSp_SuMean</t>
+          <t>Td_DecMean</t>
         </is>
       </c>
       <c r="C58" s="29" t="inlineStr">
         <is>
-          <t>W_Spd_Summer_Mean</t>
+          <t>Td_December_Mean</t>
         </is>
       </c>
       <c r="D58" s="18" t="inlineStr">
         <is>
-          <t>05_Wind (الرياح)</t>
+          <t>07_Dew_Point (نقطة الندى)</t>
         </is>
       </c>
       <c r="E58" s="12" t="inlineStr">
         <is>
-          <t>متوسط سرعة الرياح لفصل الصيف الأرصادي عند ارتفاع 10 أمتار (JJA).</t>
+          <t>متوسط درجة حرارة نقطة الندى عند ارتفاع 2 متر لشهر ديسمبر.</t>
         </is>
       </c>
       <c r="F58" s="19" t="inlineStr">
         <is>
-          <t>م/ث (m/s)</t>
+          <t>°C</t>
         </is>
       </c>
       <c r="G58" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط سرعة الرياح خلال فصل الصيف (م/ث)</t>
+          <t>خريطة متوسط درجة حرارة نقطة الندى لشهر ديسمبر (°C)</t>
         </is>
       </c>
     </row>
@@ -3725,32 +3725,32 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>WSp_AuMean</t>
+          <t>R_AnnMean</t>
         </is>
       </c>
       <c r="C59" s="31" t="inlineStr">
         <is>
-          <t>W_Spd_Autumn_Mean</t>
+          <t>R_Annual_Mean</t>
         </is>
       </c>
       <c r="D59" s="15" t="inlineStr">
         <is>
-          <t>05_Wind (الرياح)</t>
+          <t>02_Precipitation (الأمطار)</t>
         </is>
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>متوسط سرعة الرياح لفصل الخريف الأرصادي عند ارتفاع 10 أمتار (SON).</t>
+          <t>المتوسط السنوي لتساقط الأمطار (متوسط مجاميع السنين على مدار فترة الرصد 1996–2025).</t>
         </is>
       </c>
       <c r="F59" s="16" t="inlineStr">
         <is>
-          <t>م/ث (m/s)</t>
+          <t>ملم (mm)</t>
         </is>
       </c>
       <c r="G59" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط سرعة الرياح خلال فصل الخريف (م/ث)</t>
+          <t>خريطة المتوسط السنوي لتساقط الأمطار (ملم)</t>
         </is>
       </c>
     </row>
@@ -3760,32 +3760,32 @@
       </c>
       <c r="B60" s="10" t="inlineStr">
         <is>
-          <t>WSp_MaxMo</t>
+          <t>R_MonMean</t>
         </is>
       </c>
       <c r="C60" s="29" t="inlineStr">
         <is>
-          <t>W_Spd_Annual_Max_Month</t>
+          <t>R_Month_Mean</t>
         </is>
       </c>
       <c r="D60" s="18" t="inlineStr">
         <is>
-          <t>05_Wind (الرياح)</t>
+          <t>02_Precipitation (الأمطار)</t>
         </is>
       </c>
       <c r="E60" s="12" t="inlineStr">
         <is>
-          <t>أقصى متوسط شهري مسجل لسرعة الرياح في السنة (ذروة النشاط الريحي).</t>
+          <t>المتوسط الشهري لتساقط الأمطار (المتوسط السنوي مقسوماً على 12 شهراً).</t>
         </is>
       </c>
       <c r="F60" s="19" t="inlineStr">
         <is>
-          <t>م/ث (m/s)</t>
+          <t>ملم (mm)</t>
         </is>
       </c>
       <c r="G60" s="30" t="inlineStr">
         <is>
-          <t>خريطة أقصى متوسط شهري لسرعة الرياح (م/ث)</t>
+          <t>خريطة المتوسط الشهري لتساقط الأمطار (ملم)</t>
         </is>
       </c>
     </row>
@@ -3795,32 +3795,32 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>WSp_MinMo</t>
+          <t>R_AnnRng</t>
         </is>
       </c>
       <c r="C61" s="31" t="inlineStr">
         <is>
-          <t>W_Spd_Annual_Min_Month</t>
+          <t>R_Annual_Range</t>
         </is>
       </c>
       <c r="D61" s="15" t="inlineStr">
         <is>
-          <t>05_Wind (الرياح)</t>
+          <t>02_Precipitation (الأمطار)</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>أدنى متوسط شهري مسجل لسرعة الرياح في السنة (فترة الهدوء الريحي).</t>
+          <t>المدى السنوي لتساقط الأمطار (الفارق بين أعلى شهر مطراً وأقل شهر مطراً في السنة).</t>
         </is>
       </c>
       <c r="F61" s="16" t="inlineStr">
         <is>
-          <t>م/ث (m/s)</t>
+          <t>ملم (mm)</t>
         </is>
       </c>
       <c r="G61" s="32" t="inlineStr">
         <is>
-          <t>خريطة أدنى متوسط شهري لسرعة الرياح (م/ث)</t>
+          <t>خريطة المدى السنوي لتساقط الأمطار (ملم)</t>
         </is>
       </c>
     </row>
@@ -3830,32 +3830,32 @@
       </c>
       <c r="B62" s="10" t="inlineStr">
         <is>
-          <t>WSp_AnRng</t>
+          <t>R_SeaRng</t>
         </is>
       </c>
       <c r="C62" s="29" t="inlineStr">
         <is>
-          <t>W_Spd_Annual_Range</t>
+          <t>R_Seasonal_Range</t>
         </is>
       </c>
       <c r="D62" s="18" t="inlineStr">
         <is>
-          <t>05_Wind (الرياح)</t>
+          <t>02_Precipitation (الأمطار)</t>
         </is>
       </c>
       <c r="E62" s="12" t="inlineStr">
         <is>
-          <t>المدى السنوي لسرعة الرياح (الفارق بين أشد شهور السنة رياحاً وأهدأها سرعة).</t>
+          <t>المدى الفصلي لتساقط الأمطار (الفارق بين مجموع أعلى فصول السنة مطراً ومجموع أقلها مطراً).</t>
         </is>
       </c>
       <c r="F62" s="19" t="inlineStr">
         <is>
-          <t>م/ث (m/s)</t>
+          <t>ملم (mm)</t>
         </is>
       </c>
       <c r="G62" s="30" t="inlineStr">
         <is>
-          <t>خريطة المدى السنوي لسرعة الرياح (م/ث)</t>
+          <t>خريطة المدى الفصلي لتساقط الأمطار (ملم)</t>
         </is>
       </c>
     </row>
@@ -3865,32 +3865,32 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>WDr_AnMean</t>
+          <t>R_WinMean</t>
         </is>
       </c>
       <c r="C63" s="31" t="inlineStr">
         <is>
-          <t>W_Dir_Annual_Mean</t>
+          <t>R_Winter_Mean</t>
         </is>
       </c>
       <c r="D63" s="15" t="inlineStr">
         <is>
-          <t>05_Wind (الرياح)</t>
+          <t>02_Precipitation (الأمطار)</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>الاتجاه السائد السنوي للرياح بالدرجات الزاوية (محسوب بالمتوسط الدائري للمتجهات الدائرية atan2).</t>
+          <t>متوسط هطول الأمطار خلال فصل الشتاء (شهور ديسمبر، يناير، فبراير - DJF).</t>
         </is>
       </c>
       <c r="F63" s="16" t="inlineStr">
         <is>
-          <t>درجة (°)</t>
+          <t>مم/فصل (mm/season)</t>
         </is>
       </c>
       <c r="G63" s="32" t="inlineStr">
         <is>
-          <t>خريطة الاتجاه السائد السنوي للرياح (درجات)</t>
+          <t>خريطة متوسط هطول الأمطار خلال فصل الشتاء (مم/فصل)</t>
         </is>
       </c>
     </row>
@@ -3900,32 +3900,32 @@
       </c>
       <c r="B64" s="10" t="inlineStr">
         <is>
-          <t>WDr_WnMean</t>
+          <t>R_SprMean</t>
         </is>
       </c>
       <c r="C64" s="29" t="inlineStr">
         <is>
-          <t>W_Dir_Winter_Mean</t>
+          <t>R_Spring_Mean</t>
         </is>
       </c>
       <c r="D64" s="18" t="inlineStr">
         <is>
-          <t>05_Wind (الرياح)</t>
+          <t>02_Precipitation (الأمطار)</t>
         </is>
       </c>
       <c r="E64" s="12" t="inlineStr">
         <is>
-          <t>اتجاه الرياح السائد خلال فصل الشتاء الأرصادي بالدرجات الزاوية (DJF).</t>
+          <t>متوسط هطول الأمطار خلال فصل الربيع (شهور مارس، أبريل، مايو - MAM).</t>
         </is>
       </c>
       <c r="F64" s="19" t="inlineStr">
         <is>
-          <t>درجة (°)</t>
+          <t>مم/فصل (mm/season)</t>
         </is>
       </c>
       <c r="G64" s="30" t="inlineStr">
         <is>
-          <t>خريطة اتجاه الرياح السائد خلال فصل الشتاء (درجات)</t>
+          <t>خريطة متوسط هطول الأمطار خلال فصل الربيع (مم/فصل)</t>
         </is>
       </c>
     </row>
@@ -3935,32 +3935,32 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>WDr_SpMean</t>
+          <t>R_SumMean</t>
         </is>
       </c>
       <c r="C65" s="31" t="inlineStr">
         <is>
-          <t>W_Dir_Spring_Mean</t>
+          <t>R_Summer_Mean</t>
         </is>
       </c>
       <c r="D65" s="15" t="inlineStr">
         <is>
-          <t>05_Wind (الرياح)</t>
+          <t>02_Precipitation (الأمطار)</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>اتجاه الرياح السائد خلال فصل الربيع الأرصادي بالدرجات الزاوية (MAM).</t>
+          <t>متوسط هطول الأمطار خلال فصل الصيف (شهور يونيو، يوليو، أغسطس - JJA).</t>
         </is>
       </c>
       <c r="F65" s="16" t="inlineStr">
         <is>
-          <t>درجة (°)</t>
+          <t>مم/فصل (mm/season)</t>
         </is>
       </c>
       <c r="G65" s="32" t="inlineStr">
         <is>
-          <t>خريطة اتجاه الرياح السائد خلال فصل الربيع (درجات)</t>
+          <t>خريطة متوسط هطول الأمطار خلال فصل الصيف (مم/فصل)</t>
         </is>
       </c>
     </row>
@@ -3970,32 +3970,32 @@
       </c>
       <c r="B66" s="10" t="inlineStr">
         <is>
-          <t>WDr_SuMean</t>
+          <t>R_AutMean</t>
         </is>
       </c>
       <c r="C66" s="29" t="inlineStr">
         <is>
-          <t>W_Dir_Summer_Mean</t>
+          <t>R_Autumn_Mean</t>
         </is>
       </c>
       <c r="D66" s="18" t="inlineStr">
         <is>
-          <t>05_Wind (الرياح)</t>
+          <t>02_Precipitation (الأمطار)</t>
         </is>
       </c>
       <c r="E66" s="12" t="inlineStr">
         <is>
-          <t>اتجاه الرياح السائد خلال فصل الصيف الأرصادي بالدرجات الزاوية (JJA).</t>
+          <t>متوسط هطول الأمطار خلال فصل الخريف (شهور سبتمبر، أكتوبر، نوفمبر - SON).</t>
         </is>
       </c>
       <c r="F66" s="19" t="inlineStr">
         <is>
-          <t>درجة (°)</t>
+          <t>مم/فصل (mm/season)</t>
         </is>
       </c>
       <c r="G66" s="30" t="inlineStr">
         <is>
-          <t>خريطة اتجاه الرياح السائد خلال فصل الصيف (درجات)</t>
+          <t>خريطة متوسط هطول الأمطار خلال فصل الخريف (مم/فصل)</t>
         </is>
       </c>
     </row>
@@ -4005,32 +4005,32 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>WDr_AuMean</t>
+          <t>R_JanMean</t>
         </is>
       </c>
       <c r="C67" s="31" t="inlineStr">
         <is>
-          <t>W_Dir_Autumn_Mean</t>
+          <t>R_January_Mean</t>
         </is>
       </c>
       <c r="D67" s="15" t="inlineStr">
         <is>
-          <t>05_Wind (الرياح)</t>
+          <t>02_Precipitation (الأمطار)</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>اتجاه الرياح السائد خلال فصل الخريف الأرصادي بالدرجات الزاوية (SON).</t>
+          <t>متوسط مجموع كميات الأمطار التراكمية لشهر يناير عبر سنوات فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F67" s="16" t="inlineStr">
         <is>
-          <t>درجة (°)</t>
+          <t>ملم/شهر (mm/month)</t>
         </is>
       </c>
       <c r="G67" s="32" t="inlineStr">
         <is>
-          <t>خريطة اتجاه الرياح السائد خلال فصل الخريف (درجات)</t>
+          <t>خريطة متوسط مجموع أمطار شهر يناير (ملم/شهر)</t>
         </is>
       </c>
     </row>
@@ -4040,32 +4040,32 @@
       </c>
       <c r="B68" s="10" t="inlineStr">
         <is>
-          <t>RH_AnMean</t>
+          <t>R_FebMean</t>
         </is>
       </c>
       <c r="C68" s="29" t="inlineStr">
         <is>
-          <t>RH_Annual_Mean</t>
+          <t>R_February_Mean</t>
         </is>
       </c>
       <c r="D68" s="18" t="inlineStr">
         <is>
-          <t>06_Relative_Humidity (الرطوبة النسبية)</t>
+          <t>02_Precipitation (الأمطار)</t>
         </is>
       </c>
       <c r="E68" s="12" t="inlineStr">
         <is>
-          <t>المتوسط الحسابي السنوي للرطوبة النسبية للهواء عند ارتفاع 2 متر كنسبة مئوية.</t>
+          <t>متوسط مجموع كميات الأمطار التراكمية لشهر فبراير عبر سنوات فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F68" s="19" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>ملم/شهر (mm/month)</t>
         </is>
       </c>
       <c r="G68" s="30" t="inlineStr">
         <is>
-          <t>خريطة المتوسط السنوي للرطوبة النسبية (%)</t>
+          <t>خريطة متوسط مجموع أمطار شهر فبراير (ملم/شهر)</t>
         </is>
       </c>
     </row>
@@ -4075,32 +4075,32 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>RH_WnMean</t>
+          <t>R_MarMean</t>
         </is>
       </c>
       <c r="C69" s="31" t="inlineStr">
         <is>
-          <t>RH_Winter_Mean</t>
+          <t>R_March_Mean</t>
         </is>
       </c>
       <c r="D69" s="15" t="inlineStr">
         <is>
-          <t>06_Relative_Humidity (الرطوبة النسبية)</t>
+          <t>02_Precipitation (الأمطار)</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>متوسط الرطوبة النسبية لفصل الشتاء الأرصادي (DJF).</t>
+          <t>متوسط مجموع كميات الأمطار التراكمية لشهر مارس عبر سنوات فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F69" s="16" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>ملم/شهر (mm/month)</t>
         </is>
       </c>
       <c r="G69" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط الرطوبة النسبية خلال فصل الشتاء (%)</t>
+          <t>خريطة متوسط مجموع أمطار شهر مارس (ملم/شهر)</t>
         </is>
       </c>
     </row>
@@ -4110,32 +4110,32 @@
       </c>
       <c r="B70" s="10" t="inlineStr">
         <is>
-          <t>RH_SpMean</t>
+          <t>R_AprMean</t>
         </is>
       </c>
       <c r="C70" s="29" t="inlineStr">
         <is>
-          <t>RH_Spring_Mean</t>
+          <t>R_April_Mean</t>
         </is>
       </c>
       <c r="D70" s="18" t="inlineStr">
         <is>
-          <t>06_Relative_Humidity (الرطوبة النسبية)</t>
+          <t>02_Precipitation (الأمطار)</t>
         </is>
       </c>
       <c r="E70" s="12" t="inlineStr">
         <is>
-          <t>متوسط الرطوبة النسبية لفصل الربيع الأرصادي (MAM).</t>
+          <t>متوسط مجموع كميات الأمطار التراكمية لشهر أبريل عبر سنوات فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F70" s="19" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>ملم/شهر (mm/month)</t>
         </is>
       </c>
       <c r="G70" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط الرطوبة النسبية خلال فصل الربيع (%)</t>
+          <t>خريطة متوسط مجموع أمطار شهر أبريل (ملم/شهر)</t>
         </is>
       </c>
     </row>
@@ -4145,32 +4145,32 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>RH_SuMean</t>
+          <t>R_MayMean</t>
         </is>
       </c>
       <c r="C71" s="31" t="inlineStr">
         <is>
-          <t>RH_Summer_Mean</t>
+          <t>R_May_Mean</t>
         </is>
       </c>
       <c r="D71" s="15" t="inlineStr">
         <is>
-          <t>06_Relative_Humidity (الرطوبة النسبية)</t>
+          <t>02_Precipitation (الأمطار)</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>متوسط الرطوبة النسبية لفصل الصيف الأرصادي (JJA).</t>
+          <t>متوسط مجموع كميات الأمطار التراكمية لشهر مايو عبر سنوات فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F71" s="16" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>ملم/شهر (mm/month)</t>
         </is>
       </c>
       <c r="G71" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط الرطوبة النسبية خلال فصل الصيف (%)</t>
+          <t>خريطة متوسط مجموع أمطار شهر مايو (ملم/شهر)</t>
         </is>
       </c>
     </row>
@@ -4180,32 +4180,32 @@
       </c>
       <c r="B72" s="10" t="inlineStr">
         <is>
-          <t>RH_AuMean</t>
+          <t>R_JunMean</t>
         </is>
       </c>
       <c r="C72" s="29" t="inlineStr">
         <is>
-          <t>RH_Autumn_Mean</t>
+          <t>R_June_Mean</t>
         </is>
       </c>
       <c r="D72" s="18" t="inlineStr">
         <is>
-          <t>06_Relative_Humidity (الرطوبة النسبية)</t>
+          <t>02_Precipitation (الأمطار)</t>
         </is>
       </c>
       <c r="E72" s="12" t="inlineStr">
         <is>
-          <t>متوسط الرطوبة النسبية لفصل الخريف الأرصادي (SON).</t>
+          <t>متوسط مجموع كميات الأمطار التراكمية لشهر يونيو عبر سنوات فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F72" s="19" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>ملم/شهر (mm/month)</t>
         </is>
       </c>
       <c r="G72" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط الرطوبة النسبية خلال فصل الخريف (%)</t>
+          <t>خريطة متوسط مجموع أمطار شهر يونيو (ملم/شهر)</t>
         </is>
       </c>
     </row>
@@ -4215,32 +4215,32 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>RH_AnRng</t>
+          <t>R_JulMean</t>
         </is>
       </c>
       <c r="C73" s="31" t="inlineStr">
         <is>
-          <t>RH_Annual_Range</t>
+          <t>R_July_Mean</t>
         </is>
       </c>
       <c r="D73" s="15" t="inlineStr">
         <is>
-          <t>06_Relative_Humidity (الرطوبة النسبية)</t>
+          <t>02_Precipitation (الأمطار)</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>المدى السنوي للرطوبة النسبية (الفارق بين أعلى شهر رطوبة وأدنى شهر رطوبة).</t>
+          <t>متوسط مجموع كميات الأمطار التراكمية لشهر يوليو عبر سنوات فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F73" s="16" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>ملم/شهر (mm/month)</t>
         </is>
       </c>
       <c r="G73" s="32" t="inlineStr">
         <is>
-          <t>خريطة المدى السنوي للرطوبة النسبية (%)</t>
+          <t>خريطة متوسط مجموع أمطار شهر يوليو (ملم/شهر)</t>
         </is>
       </c>
     </row>
@@ -4250,32 +4250,32 @@
       </c>
       <c r="B74" s="10" t="inlineStr">
         <is>
-          <t>Sol_AnMean</t>
+          <t>R_AugMean</t>
         </is>
       </c>
       <c r="C74" s="29" t="inlineStr">
         <is>
-          <t>Sol_Annual_Mean</t>
+          <t>R_August_Mean</t>
         </is>
       </c>
       <c r="D74" s="18" t="inlineStr">
         <is>
-          <t>08_Solar_Radiation (الإشعاع الشمسي)</t>
+          <t>02_Precipitation (الأمطار)</t>
         </is>
       </c>
       <c r="E74" s="12" t="inlineStr">
         <is>
-          <t>المتوسط اليومي السنوي للإشعاع الشمسي الكلي السطحي الواصل لسطح الأرض في كافة ظروف السماء.</t>
+          <t>متوسط مجموع كميات الأمطار التراكمية لشهر أغسطس عبر سنوات فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F74" s="19" t="inlineStr">
         <is>
-          <t>kWh/m²/day</t>
+          <t>ملم/شهر (mm/month)</t>
         </is>
       </c>
       <c r="G74" s="30" t="inlineStr">
         <is>
-          <t>خريطة المتوسط اليومي السنوي للإشعاع الشمسي (kWh/m²/day)</t>
+          <t>خريطة متوسط مجموع أمطار شهر أغسطس (ملم/شهر)</t>
         </is>
       </c>
     </row>
@@ -4285,32 +4285,32 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>Sol_AnTot</t>
+          <t>R_SepMean</t>
         </is>
       </c>
       <c r="C75" s="31" t="inlineStr">
         <is>
-          <t>Sol_Annual_Total</t>
+          <t>R_September_Mean</t>
         </is>
       </c>
       <c r="D75" s="15" t="inlineStr">
         <is>
-          <t>08_Solar_Radiation (الإشعاع الشمسي)</t>
+          <t>02_Precipitation (الأمطار)</t>
         </is>
       </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
-          <t>إجمالي الطاقة الشمسية السنوية التراكمية الساقطة على المتر المربع في السنة كاملة.</t>
+          <t>متوسط مجموع كميات الأمطار التراكمية لشهر سبتمبر عبر سنوات فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F75" s="16" t="inlineStr">
         <is>
-          <t>kWh/m²/year</t>
+          <t>ملم/شهر (mm/month)</t>
         </is>
       </c>
       <c r="G75" s="32" t="inlineStr">
         <is>
-          <t>خريطة إجمالي الطاقة الشمسية السنوية التراكمية (kWh/m²/year)</t>
+          <t>خريطة متوسط مجموع أمطار شهر سبتمبر (ملم/شهر)</t>
         </is>
       </c>
     </row>
@@ -4320,32 +4320,32 @@
       </c>
       <c r="B76" s="10" t="inlineStr">
         <is>
-          <t>Sol_WnMean</t>
+          <t>R_OctMean</t>
         </is>
       </c>
       <c r="C76" s="29" t="inlineStr">
         <is>
-          <t>Sol_Winter_Mean</t>
+          <t>R_October_Mean</t>
         </is>
       </c>
       <c r="D76" s="18" t="inlineStr">
         <is>
-          <t>08_Solar_Radiation (الإشعاع الشمسي)</t>
+          <t>02_Precipitation (الأمطار)</t>
         </is>
       </c>
       <c r="E76" s="12" t="inlineStr">
         <is>
-          <t>متوسط الإشعاع الشمسي اليومي لفصل الشتاء الأرصادي (DJF).</t>
+          <t>متوسط مجموع كميات الأمطار التراكمية لشهر أكتوبر عبر سنوات فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F76" s="19" t="inlineStr">
         <is>
-          <t>kWh/m²/day</t>
+          <t>ملم/شهر (mm/month)</t>
         </is>
       </c>
       <c r="G76" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط الإشعاع الشمسي خلال فصل الشتاء (kWh/m²/day)</t>
+          <t>خريطة متوسط مجموع أمطار شهر أكتوبر (ملم/شهر)</t>
         </is>
       </c>
     </row>
@@ -4355,32 +4355,32 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>Sol_SpMean</t>
+          <t>R_NovMean</t>
         </is>
       </c>
       <c r="C77" s="31" t="inlineStr">
         <is>
-          <t>Sol_Spring_Mean</t>
+          <t>R_November_Mean</t>
         </is>
       </c>
       <c r="D77" s="15" t="inlineStr">
         <is>
-          <t>08_Solar_Radiation (الإشعاع الشمسي)</t>
+          <t>02_Precipitation (الأمطار)</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
-          <t>متوسط الإشعاع الشمسي اليومي لفصل الربيع الأرصادي (MAM).</t>
+          <t>متوسط مجموع كميات الأمطار التراكمية لشهر نوفمبر عبر سنوات فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F77" s="16" t="inlineStr">
         <is>
-          <t>kWh/m²/day</t>
+          <t>ملم/شهر (mm/month)</t>
         </is>
       </c>
       <c r="G77" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط الإشعاع الشمسي خلال فصل الربيع (kWh/m²/day)</t>
+          <t>خريطة متوسط مجموع أمطار شهر نوفمبر (ملم/شهر)</t>
         </is>
       </c>
     </row>
@@ -4390,32 +4390,32 @@
       </c>
       <c r="B78" s="10" t="inlineStr">
         <is>
-          <t>Sol_SuMean</t>
+          <t>R_DecMean</t>
         </is>
       </c>
       <c r="C78" s="29" t="inlineStr">
         <is>
-          <t>Sol_Summer_Mean</t>
+          <t>R_December_Mean</t>
         </is>
       </c>
       <c r="D78" s="18" t="inlineStr">
         <is>
-          <t>08_Solar_Radiation (الإشعاع الشمسي)</t>
+          <t>02_Precipitation (الأمطار)</t>
         </is>
       </c>
       <c r="E78" s="12" t="inlineStr">
         <is>
-          <t>متوسط الإشعاع الشمسي اليومي لفصل الصيف الأرصادي (JJA).</t>
+          <t>متوسط مجموع كميات الأمطار التراكمية لشهر ديسمبر عبر سنوات فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F78" s="19" t="inlineStr">
         <is>
-          <t>kWh/m²/day</t>
+          <t>ملم/شهر (mm/month)</t>
         </is>
       </c>
       <c r="G78" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط الإشعاع الشمسي خلال فصل الصيف (kWh/m²/day)</t>
+          <t>خريطة متوسط مجموع أمطار شهر ديسمبر (ملم/شهر)</t>
         </is>
       </c>
     </row>
@@ -4425,32 +4425,32 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>Sol_AuMean</t>
+          <t>PSL_AnMean</t>
         </is>
       </c>
       <c r="C79" s="31" t="inlineStr">
         <is>
-          <t>Sol_Autumn_Mean</t>
+          <t>PSL_Annual_Mean</t>
         </is>
       </c>
       <c r="D79" s="15" t="inlineStr">
         <is>
-          <t>08_Solar_Radiation (الإشعاع الشمسي)</t>
+          <t>03_Sea_Level_Pressure (ضغط مستوى البحر)</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>متوسط الإشعاع الشمسي اليومي لفصل الخريف الأرصادي (SON).</t>
+          <t>متوسط الضغط الجوي السنوي المصحح عند مستوى سطح البحر القياسي (Sea Level Pressure).</t>
         </is>
       </c>
       <c r="F79" s="16" t="inlineStr">
         <is>
-          <t>kWh/m²/day</t>
+          <t>hPa / mbar</t>
         </is>
       </c>
       <c r="G79" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط الإشعاع الشمسي خلال فصل الخريف (kWh/m²/day)</t>
+          <t>خريطة متوسط الضغط الجوي عند مستوى سطح البحر (hPa)</t>
         </is>
       </c>
     </row>
@@ -4460,32 +4460,32 @@
       </c>
       <c r="B80" s="10" t="inlineStr">
         <is>
-          <t>Sol_AnRng</t>
+          <t>PSL_WnMean</t>
         </is>
       </c>
       <c r="C80" s="29" t="inlineStr">
         <is>
-          <t>Sol_Annual_Range</t>
+          <t>PSL_Winter_Mean</t>
         </is>
       </c>
       <c r="D80" s="18" t="inlineStr">
         <is>
-          <t>08_Solar_Radiation (الإشعاع الشمسي)</t>
+          <t>03_Sea_Level_Pressure (ضغط مستوى البحر)</t>
         </is>
       </c>
       <c r="E80" s="12" t="inlineStr">
         <is>
-          <t>المدى السنوي للإشعاع الشمسي (الفارق بين ذروة الإشعاع في الصيف وأدناه في الشتاء).</t>
+          <t>متوسط الضغط الجوي عند مستوى سطح البحر لفصل الشتاء الأرصادي (DJF).</t>
         </is>
       </c>
       <c r="F80" s="19" t="inlineStr">
         <is>
-          <t>kWh/m²/day</t>
+          <t>hPa / mbar</t>
         </is>
       </c>
       <c r="G80" s="30" t="inlineStr">
         <is>
-          <t>خريطة المدى السنوي للإشعاع الشمسي (kWh/m²/day)</t>
+          <t>خريطة متوسط ضغط مستوى سطح البحر خلال فصل الشتاء (hPa)</t>
         </is>
       </c>
     </row>
@@ -4495,32 +4495,32 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>UV_AnMean</t>
+          <t>PSL_SpMean</t>
         </is>
       </c>
       <c r="C81" s="31" t="inlineStr">
         <is>
-          <t>UV_Annual_Mean</t>
+          <t>PSL_Spring_Mean</t>
         </is>
       </c>
       <c r="D81" s="15" t="inlineStr">
         <is>
-          <t>09_UV_Index (الأشعة فوق البنفسجية)</t>
+          <t>03_Sea_Level_Pressure (ضغط مستوى البحر)</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
-          <t>المتوسط السنوي لمؤشر الأشعة فوق البنفسجية عند الظهيرة وفق منظومة منظمة الصحة العالمية.</t>
+          <t>متوسط الضغط الجوي عند مستوى سطح البحر لفصل الربيع الأرصادي (MAM).</t>
         </is>
       </c>
       <c r="F81" s="16" t="inlineStr">
         <is>
-          <t>مؤشر (0-16+)</t>
+          <t>hPa / mbar</t>
         </is>
       </c>
       <c r="G81" s="32" t="inlineStr">
         <is>
-          <t>خريطة المتوسط السنوي لمؤشر الأشعة فوق البنفسجية (UV)</t>
+          <t>خريطة متوسط ضغط مستوى سطح البحر خلال فصل الربيع (hPa)</t>
         </is>
       </c>
     </row>
@@ -4530,32 +4530,32 @@
       </c>
       <c r="B82" s="10" t="inlineStr">
         <is>
-          <t>UV_WnMean</t>
+          <t>PSL_SuMean</t>
         </is>
       </c>
       <c r="C82" s="29" t="inlineStr">
         <is>
-          <t>UV_Winter_Mean</t>
+          <t>PSL_Summer_Mean</t>
         </is>
       </c>
       <c r="D82" s="18" t="inlineStr">
         <is>
-          <t>09_UV_Index (الأشعة فوق البنفسجية)</t>
+          <t>03_Sea_Level_Pressure (ضغط مستوى البحر)</t>
         </is>
       </c>
       <c r="E82" s="12" t="inlineStr">
         <is>
-          <t>متوسط مؤشر الأشعة فوق البنفسجية لفصل الشتاء الأرصادي (DJF).</t>
+          <t>متوسط الضغط الجوي عند مستوى سطح البحر لفصل الصيف الأرصادي (JJA).</t>
         </is>
       </c>
       <c r="F82" s="19" t="inlineStr">
         <is>
-          <t>مؤشر (0-16+)</t>
+          <t>hPa / mbar</t>
         </is>
       </c>
       <c r="G82" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية خلال فصل الشتاء</t>
+          <t>خريطة متوسط ضغط مستوى سطح البحر خلال فصل الصيف (hPa)</t>
         </is>
       </c>
     </row>
@@ -4565,32 +4565,32 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>UV_SpMean</t>
+          <t>PSL_AuMean</t>
         </is>
       </c>
       <c r="C83" s="31" t="inlineStr">
         <is>
-          <t>UV_Spring_Mean</t>
+          <t>PSL_Autumn_Mean</t>
         </is>
       </c>
       <c r="D83" s="15" t="inlineStr">
         <is>
-          <t>09_UV_Index (الأشعة فوق البنفسجية)</t>
+          <t>03_Sea_Level_Pressure (ضغط مستوى البحر)</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t>متوسط مؤشر الأشعة فوق البنفسجية لفصل الربيع الأرصادي (MAM).</t>
+          <t>متوسط الضغط الجوي عند مستوى سطح البحر لفصل الخريف الأرصادي (SON).</t>
         </is>
       </c>
       <c r="F83" s="16" t="inlineStr">
         <is>
-          <t>مؤشر (0-16+)</t>
+          <t>hPa / mbar</t>
         </is>
       </c>
       <c r="G83" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية خلال فصل الربيع</t>
+          <t>خريطة متوسط ضغط مستوى سطح البحر خلال فصل الخريف (hPa)</t>
         </is>
       </c>
     </row>
@@ -4600,32 +4600,32 @@
       </c>
       <c r="B84" s="10" t="inlineStr">
         <is>
-          <t>UV_SuMean</t>
+          <t>PSL_AnRng</t>
         </is>
       </c>
       <c r="C84" s="29" t="inlineStr">
         <is>
-          <t>UV_Summer_Mean</t>
+          <t>PSL_Annual_Range</t>
         </is>
       </c>
       <c r="D84" s="18" t="inlineStr">
         <is>
-          <t>09_UV_Index (الأشعة فوق البنفسجية)</t>
+          <t>03_Sea_Level_Pressure (ضغط مستوى البحر)</t>
         </is>
       </c>
       <c r="E84" s="12" t="inlineStr">
         <is>
-          <t>متوسط مؤشر الأشعة فوق البنفسجية لفصل الصيف الأرصادي (JJA - ذروة مخاطر الحروق الشمسية).</t>
+          <t>المدى البارومتري السنوي لضغط مستوى البحر (الفارق بين أعلى وأدنى متوسط شهري للضغط).</t>
         </is>
       </c>
       <c r="F84" s="19" t="inlineStr">
         <is>
-          <t>مؤشر (0-16+)</t>
+          <t>hPa / mbar</t>
         </is>
       </c>
       <c r="G84" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية خلال فصل الصيف</t>
+          <t>خريطة المدى السنوي لضغط مستوى سطح البحر (hPa)</t>
         </is>
       </c>
     </row>
@@ -4635,32 +4635,32 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>UV_AuMean</t>
+          <t>PSL_JanMn</t>
         </is>
       </c>
       <c r="C85" s="31" t="inlineStr">
         <is>
-          <t>UV_Autumn_Mean</t>
+          <t>PSL_January_Mean</t>
         </is>
       </c>
       <c r="D85" s="15" t="inlineStr">
         <is>
-          <t>09_UV_Index (الأشعة فوق البنفسجية)</t>
+          <t>03_Sea_Level_Pressure (ضغط مستوى البحر)</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
-          <t>متوسط مؤشر الأشعة فوق البنفسجية لفصل الخريف الأرصادي (SON).</t>
+          <t>متوسط الضغط الجوي المصحح لمستوى سطح البحر القياسي لشهر يناير (SLP).</t>
         </is>
       </c>
       <c r="F85" s="16" t="inlineStr">
         <is>
-          <t>مؤشر (0-16+)</t>
+          <t>hPa / mbar</t>
         </is>
       </c>
       <c r="G85" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية خلال فصل الخريف</t>
+          <t>خريطة متوسط ضغط مستوى سطح البحر لشهر يناير (hPa)</t>
         </is>
       </c>
     </row>
@@ -4670,32 +4670,32 @@
       </c>
       <c r="B86" s="10" t="inlineStr">
         <is>
-          <t>UV_AnRng</t>
+          <t>PSL_FebMn</t>
         </is>
       </c>
       <c r="C86" s="29" t="inlineStr">
         <is>
-          <t>UV_Annual_Range</t>
+          <t>PSL_February_Mean</t>
         </is>
       </c>
       <c r="D86" s="18" t="inlineStr">
         <is>
-          <t>09_UV_Index (الأشعة فوق البنفسجية)</t>
+          <t>03_Sea_Level_Pressure (ضغط مستوى البحر)</t>
         </is>
       </c>
       <c r="E86" s="12" t="inlineStr">
         <is>
-          <t>المدى السنوي لمؤشر الأشعة فوق البنفسجية (الفارق بين ذروة الصيف وأدنى مستويات الشتاء).</t>
+          <t>متوسط الضغط الجوي المصحح لمستوى سطح البحر القياسي لشهر فبراير (SLP).</t>
         </is>
       </c>
       <c r="F86" s="19" t="inlineStr">
         <is>
-          <t>مؤشر (0-16+)</t>
+          <t>hPa / mbar</t>
         </is>
       </c>
       <c r="G86" s="30" t="inlineStr">
         <is>
-          <t>خريطة المدى السنوي لمؤشر الأشعة فوق البنفسجية</t>
+          <t>خريطة متوسط ضغط مستوى سطح البحر لشهر فبراير (hPa)</t>
         </is>
       </c>
     </row>
@@ -4705,32 +4705,32 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>Cld_AnMean</t>
+          <t>PSL_MarMn</t>
         </is>
       </c>
       <c r="C87" s="31" t="inlineStr">
         <is>
-          <t>Cld_Annual_Mean</t>
+          <t>PSL_March_Mean</t>
         </is>
       </c>
       <c r="D87" s="15" t="inlineStr">
         <is>
-          <t>10_Cloud_Cover (الغطاء السحابي)</t>
+          <t>03_Sea_Level_Pressure (ضغط مستوى البحر)</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr">
         <is>
-          <t>المتوسط السنوي لنسبة تغطية السماء بالغيوم والسحب كنسبة مئوية.</t>
+          <t>متوسط الضغط الجوي المصحح لمستوى سطح البحر القياسي لشهر مارس (SLP).</t>
         </is>
       </c>
       <c r="F87" s="16" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>hPa / mbar</t>
         </is>
       </c>
       <c r="G87" s="32" t="inlineStr">
         <is>
-          <t>خريطة المتوسط السنوي لنسبة الغطاء السحابي (%)</t>
+          <t>خريطة متوسط ضغط مستوى سطح البحر لشهر مارس (hPa)</t>
         </is>
       </c>
     </row>
@@ -4740,32 +4740,32 @@
       </c>
       <c r="B88" s="10" t="inlineStr">
         <is>
-          <t>Cld_WnMean</t>
+          <t>PSL_AprMn</t>
         </is>
       </c>
       <c r="C88" s="29" t="inlineStr">
         <is>
-          <t>Cld_Winter_Mean</t>
+          <t>PSL_April_Mean</t>
         </is>
       </c>
       <c r="D88" s="18" t="inlineStr">
         <is>
-          <t>10_Cloud_Cover (الغطاء السحابي)</t>
+          <t>03_Sea_Level_Pressure (ضغط مستوى البحر)</t>
         </is>
       </c>
       <c r="E88" s="12" t="inlineStr">
         <is>
-          <t>متوسط نسبة تغطية السحب لفصل الشتاء الأرصادي (DJF).</t>
+          <t>متوسط الضغط الجوي المصحح لمستوى سطح البحر القياسي لشهر أبريل (SLP).</t>
         </is>
       </c>
       <c r="F88" s="19" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>hPa / mbar</t>
         </is>
       </c>
       <c r="G88" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط الغطاء السحابي خلال فصل الشتاء (%)</t>
+          <t>خريطة متوسط ضغط مستوى سطح البحر لشهر أبريل (hPa)</t>
         </is>
       </c>
     </row>
@@ -4775,32 +4775,32 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>Cld_SpMean</t>
+          <t>PSL_MayMn</t>
         </is>
       </c>
       <c r="C89" s="31" t="inlineStr">
         <is>
-          <t>Cld_Spring_Mean</t>
+          <t>PSL_May_Mean</t>
         </is>
       </c>
       <c r="D89" s="15" t="inlineStr">
         <is>
-          <t>10_Cloud_Cover (الغطاء السحابي)</t>
+          <t>03_Sea_Level_Pressure (ضغط مستوى البحر)</t>
         </is>
       </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
-          <t>متوسط نسبة تغطية السحب لفصل الربيع الأرصادي (MAM).</t>
+          <t>متوسط الضغط الجوي المصحح لمستوى سطح البحر القياسي لشهر مايو (SLP).</t>
         </is>
       </c>
       <c r="F89" s="16" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>hPa / mbar</t>
         </is>
       </c>
       <c r="G89" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط الغطاء السحابي خلال فصل الربيع (%)</t>
+          <t>خريطة متوسط ضغط مستوى سطح البحر لشهر مايو (hPa)</t>
         </is>
       </c>
     </row>
@@ -4810,32 +4810,32 @@
       </c>
       <c r="B90" s="10" t="inlineStr">
         <is>
-          <t>Cld_SuMean</t>
+          <t>PSL_JunMn</t>
         </is>
       </c>
       <c r="C90" s="29" t="inlineStr">
         <is>
-          <t>Cld_Summer_Mean</t>
+          <t>PSL_June_Mean</t>
         </is>
       </c>
       <c r="D90" s="18" t="inlineStr">
         <is>
-          <t>10_Cloud_Cover (الغطاء السحابي)</t>
+          <t>03_Sea_Level_Pressure (ضغط مستوى البحر)</t>
         </is>
       </c>
       <c r="E90" s="12" t="inlineStr">
         <is>
-          <t>متوسط نسبة تغطية السحب لفصل الصيف الأرصادي (JJA).</t>
+          <t>متوسط الضغط الجوي المصحح لمستوى سطح البحر القياسي لشهر يونيو (SLP).</t>
         </is>
       </c>
       <c r="F90" s="19" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>hPa / mbar</t>
         </is>
       </c>
       <c r="G90" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط الغطاء السحابي خلال فصل الصيف (%)</t>
+          <t>خريطة متوسط ضغط مستوى سطح البحر لشهر يونيو (hPa)</t>
         </is>
       </c>
     </row>
@@ -4845,32 +4845,32 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>Cld_AuMean</t>
+          <t>PSL_JulMn</t>
         </is>
       </c>
       <c r="C91" s="31" t="inlineStr">
         <is>
-          <t>Cld_Autumn_Mean</t>
+          <t>PSL_July_Mean</t>
         </is>
       </c>
       <c r="D91" s="15" t="inlineStr">
         <is>
-          <t>10_Cloud_Cover (الغطاء السحابي)</t>
+          <t>03_Sea_Level_Pressure (ضغط مستوى البحر)</t>
         </is>
       </c>
       <c r="E91" s="7" t="inlineStr">
         <is>
-          <t>متوسط نسبة تغطية السحب لفصل الخريف الأرصادي (SON).</t>
+          <t>متوسط الضغط الجوي المصحح لمستوى سطح البحر القياسي لشهر يوليو (SLP).</t>
         </is>
       </c>
       <c r="F91" s="16" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>hPa / mbar</t>
         </is>
       </c>
       <c r="G91" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط الغطاء السحابي خلال فصل الخريف (%)</t>
+          <t>خريطة متوسط ضغط مستوى سطح البحر لشهر يوليو (hPa)</t>
         </is>
       </c>
     </row>
@@ -4880,32 +4880,32 @@
       </c>
       <c r="B92" s="10" t="inlineStr">
         <is>
-          <t>Cld_AnRng</t>
+          <t>PSL_AugMn</t>
         </is>
       </c>
       <c r="C92" s="29" t="inlineStr">
         <is>
-          <t>Cld_Annual_Range</t>
+          <t>PSL_August_Mean</t>
         </is>
       </c>
       <c r="D92" s="18" t="inlineStr">
         <is>
-          <t>10_Cloud_Cover (الغطاء السحابي)</t>
+          <t>03_Sea_Level_Pressure (ضغط مستوى البحر)</t>
         </is>
       </c>
       <c r="E92" s="12" t="inlineStr">
         <is>
-          <t>المدى السنوي لتغطية السحب (الفارق بين أكثر شهور السنة غيوماً وأكثرها صفاءً).</t>
+          <t>متوسط الضغط الجوي المصحح لمستوى سطح البحر القياسي لشهر أغسطس (SLP).</t>
         </is>
       </c>
       <c r="F92" s="19" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>hPa / mbar</t>
         </is>
       </c>
       <c r="G92" s="30" t="inlineStr">
         <is>
-          <t>خريطة المدى السنوي لنسبة الغطاء السحابي (%)</t>
+          <t>خريطة متوسط ضغط مستوى سطح البحر لشهر أغسطس (hPa)</t>
         </is>
       </c>
     </row>
@@ -4915,32 +4915,32 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>WC_WinMean</t>
+          <t>PSL_SepMn</t>
         </is>
       </c>
       <c r="C93" s="31" t="inlineStr">
         <is>
-          <t>WC_Winter_Mean</t>
+          <t>PSL_September_Mean</t>
         </is>
       </c>
       <c r="D93" s="15" t="inlineStr">
         <is>
-          <t>12_Wind_Chill (مبرد الرياح)</t>
+          <t>03_Sea_Level_Pressure (ضغط مستوى البحر)</t>
         </is>
       </c>
       <c r="E93" s="7" t="inlineStr">
         <is>
-          <t>متوسط درجة البرودة الريحية لفصل الشتاء المحسوبة بمعادلة NWS لخفض الحرارة بفعل سرعة الرياح.</t>
+          <t>متوسط الضغط الجوي المصحح لمستوى سطح البحر القياسي لشهر سبتمبر (SLP).</t>
         </is>
       </c>
       <c r="F93" s="16" t="inlineStr">
         <is>
-          <t>°C</t>
+          <t>hPa / mbar</t>
         </is>
       </c>
       <c r="G93" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط مبرد الرياح خلال فصل الشتاء (°C)</t>
+          <t>خريطة متوسط ضغط مستوى سطح البحر لشهر سبتمبر (hPa)</t>
         </is>
       </c>
     </row>
@@ -4950,32 +4950,32 @@
       </c>
       <c r="B94" s="10" t="inlineStr">
         <is>
-          <t>WC_AnnMean</t>
+          <t>PSL_OctMn</t>
         </is>
       </c>
       <c r="C94" s="29" t="inlineStr">
         <is>
-          <t>WC_Annual_Mean</t>
+          <t>PSL_October_Mean</t>
         </is>
       </c>
       <c r="D94" s="18" t="inlineStr">
         <is>
-          <t>12_Wind_Chill (مبرد الرياح)</t>
+          <t>03_Sea_Level_Pressure (ضغط مستوى البحر)</t>
         </is>
       </c>
       <c r="E94" s="12" t="inlineStr">
         <is>
-          <t>المتوسط الحسابي السنوي لتأثير البرودة الريحية على حرارة الهواء المحسوسة.</t>
+          <t>متوسط الضغط الجوي المصحح لمستوى سطح البحر القياسي لشهر أكتوبر (SLP).</t>
         </is>
       </c>
       <c r="F94" s="19" t="inlineStr">
         <is>
-          <t>°C</t>
+          <t>hPa / mbar</t>
         </is>
       </c>
       <c r="G94" s="30" t="inlineStr">
         <is>
-          <t>خريطة المتوسط السنوي لمبرد الرياح (°C)</t>
+          <t>خريطة متوسط ضغط مستوى سطح البحر لشهر أكتوبر (hPa)</t>
         </is>
       </c>
     </row>
@@ -4985,32 +4985,32 @@
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>DM_AridAnn</t>
+          <t>PSL_NovMn</t>
         </is>
       </c>
       <c r="C95" s="31" t="inlineStr">
         <is>
-          <t>DM_Aridity_Annual</t>
+          <t>PSL_November_Mean</t>
         </is>
       </c>
       <c r="D95" s="15" t="inlineStr">
         <is>
-          <t>13_De_Martonne_Aridity (دليل دي مارتون)</t>
+          <t>03_Sea_Level_Pressure (ضغط مستوى البحر)</t>
         </is>
       </c>
       <c r="E95" s="7" t="inlineStr">
         <is>
-          <t>دليل القحولة والجفاف السنوي لدي مارتون I = P / (T + 10) لتصنيف الأقاليم من القاحل فائق الجفاف إلى الرطب.</t>
+          <t>متوسط الضغط الجوي المصحح لمستوى سطح البحر القياسي لشهر نوفمبر (SLP).</t>
         </is>
       </c>
       <c r="F95" s="16" t="inlineStr">
         <is>
-          <t>مؤشر (Index)</t>
+          <t>hPa / mbar</t>
         </is>
       </c>
       <c r="G95" s="32" t="inlineStr">
         <is>
-          <t>خريطة دليل دي مارتون السنوي للقحولة والجفاف</t>
+          <t>خريطة متوسط ضغط مستوى سطح البحر لشهر نوفمبر (hPa)</t>
         </is>
       </c>
     </row>
@@ -5020,32 +5020,32 @@
       </c>
       <c r="B96" s="10" t="inlineStr">
         <is>
-          <t>ET_AnnTot</t>
+          <t>PSL_DecMn</t>
         </is>
       </c>
       <c r="C96" s="29" t="inlineStr">
         <is>
-          <t>ET_Annual_Total</t>
+          <t>PSL_December_Mean</t>
         </is>
       </c>
       <c r="D96" s="18" t="inlineStr">
         <is>
-          <t>14_Evapotranspiration (البخر والنتح)</t>
+          <t>03_Sea_Level_Pressure (ضغط مستوى البحر)</t>
         </is>
       </c>
       <c r="E96" s="12" t="inlineStr">
         <is>
-          <t>المجموع التراكمي السنوي للبخر والنتح المرجعي الكامن المحسوب بمعادلة Hargreaves-Samani (FAO-56).</t>
+          <t>متوسط الضغط الجوي المصحح لمستوى سطح البحر القياسي لشهر ديسمبر (SLP).</t>
         </is>
       </c>
       <c r="F96" s="19" t="inlineStr">
         <is>
-          <t>ملم (mm)</t>
+          <t>hPa / mbar</t>
         </is>
       </c>
       <c r="G96" s="30" t="inlineStr">
         <is>
-          <t>خريطة المجموع السنوي للبخر والنتح (ملم)</t>
+          <t>خريطة متوسط ضغط مستوى سطح البحر لشهر ديسمبر (hPa)</t>
         </is>
       </c>
     </row>
@@ -5055,32 +5055,32 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>ET_AnnMean</t>
+          <t>PS_AnnMean</t>
         </is>
       </c>
       <c r="C97" s="31" t="inlineStr">
         <is>
-          <t>ET_Annual_Mean</t>
+          <t>PS_Annual_Mean</t>
         </is>
       </c>
       <c r="D97" s="15" t="inlineStr">
         <is>
-          <t>14_Evapotranspiration (البخر والنتح)</t>
+          <t>04_Surface_Pressure (الضغط السطحي)</t>
         </is>
       </c>
       <c r="E97" s="7" t="inlineStr">
         <is>
-          <t>المعدل الشهري للبخر والنتح المرجعي (المجموع التراكمي السنوي مقسوماً على 12 شهراً).</t>
+          <t>المتوسط السنوي للضغط الجوي السطحي الفعلي الحقيقي عند منسوب تضاريس المحطة.</t>
         </is>
       </c>
       <c r="F97" s="16" t="inlineStr">
         <is>
-          <t>ملم (mm)</t>
+          <t>hPa / mbar</t>
         </is>
       </c>
       <c r="G97" s="32" t="inlineStr">
         <is>
-          <t>خريطة المعدل الشهري للبخر والنتح (ملم)</t>
+          <t>خريطة المتوسط السنوي للضغط الجوي السطحي (hPa)</t>
         </is>
       </c>
     </row>
@@ -5090,32 +5090,32 @@
       </c>
       <c r="B98" s="10" t="inlineStr">
         <is>
-          <t>ET_AnnRng</t>
+          <t>PS_WinMean</t>
         </is>
       </c>
       <c r="C98" s="29" t="inlineStr">
         <is>
-          <t>ET_Annual_Range</t>
+          <t>PS_Winter_Mean</t>
         </is>
       </c>
       <c r="D98" s="18" t="inlineStr">
         <is>
-          <t>14_Evapotranspiration (البخر والنتح)</t>
+          <t>04_Surface_Pressure (الضغط السطحي)</t>
         </is>
       </c>
       <c r="E98" s="12" t="inlineStr">
         <is>
-          <t>المدى السنوي للبخر والنتح (الفارق بين أعلى شهور السنة فقداً للماء بالبخر والنتح وأدناها).</t>
+          <t>متوسط الضغط الجوي السطحي الفعلي لفصل الشتاء الأرصادي (DJF).</t>
         </is>
       </c>
       <c r="F98" s="19" t="inlineStr">
         <is>
-          <t>ملم (mm)</t>
+          <t>hPa / mbar</t>
         </is>
       </c>
       <c r="G98" s="30" t="inlineStr">
         <is>
-          <t>خريطة المدى السنوي للبخر والنتح (ملم)</t>
+          <t>خريطة متوسط الضغط السطحي خلال فصل الشتاء (hPa)</t>
         </is>
       </c>
     </row>
@@ -5125,32 +5125,32 @@
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>ET_SeaRng</t>
+          <t>PS_SprMean</t>
         </is>
       </c>
       <c r="C99" s="31" t="inlineStr">
         <is>
-          <t>ET_Seasonal_Range</t>
+          <t>PS_Spring_Mean</t>
         </is>
       </c>
       <c r="D99" s="15" t="inlineStr">
         <is>
-          <t>14_Evapotranspiration (البخر والنتح)</t>
+          <t>04_Surface_Pressure (الضغط السطحي)</t>
         </is>
       </c>
       <c r="E99" s="7" t="inlineStr">
         <is>
-          <t>المدى الفصلي للبخر والنتح (الفارق بين مجموع أعلى فصول السنة في البخر والنتح ومجموع أقلها).</t>
+          <t>متوسط الضغط الجوي السطحي الفعلي لفصل الربيع الأرصادي (MAM).</t>
         </is>
       </c>
       <c r="F99" s="16" t="inlineStr">
         <is>
-          <t>ملم (mm)</t>
+          <t>hPa / mbar</t>
         </is>
       </c>
       <c r="G99" s="32" t="inlineStr">
         <is>
-          <t>خريطة المدى الفصلي للبخر والنتح (ملم)</t>
+          <t>خريطة متوسط الضغط السطحي خلال فصل الربيع (hPa)</t>
         </is>
       </c>
     </row>
@@ -5160,32 +5160,32 @@
       </c>
       <c r="B100" s="10" t="inlineStr">
         <is>
-          <t>ET_WinTot</t>
+          <t>PS_SumMean</t>
         </is>
       </c>
       <c r="C100" s="29" t="inlineStr">
         <is>
-          <t>ET_Winter_Total</t>
+          <t>PS_Summer_Mean</t>
         </is>
       </c>
       <c r="D100" s="18" t="inlineStr">
         <is>
-          <t>14_Evapotranspiration (البخر والنتح)</t>
+          <t>04_Surface_Pressure (الضغط السطحي)</t>
         </is>
       </c>
       <c r="E100" s="12" t="inlineStr">
         <is>
-          <t>مجموع البخر والنتح لفصل الشتاء الأرصادي (شهور ديسمبر، يناير، فبراير - DJF).</t>
+          <t>متوسط الضغط الجوي السطحي الفعلي لفصل الصيف الأرصادي (JJA).</t>
         </is>
       </c>
       <c r="F100" s="19" t="inlineStr">
         <is>
-          <t>ملم (mm)</t>
+          <t>hPa / mbar</t>
         </is>
       </c>
       <c r="G100" s="30" t="inlineStr">
         <is>
-          <t>خريطة مجموع البخر والنتح خلال فصل الشتاء (ملم)</t>
+          <t>خريطة متوسط الضغط السطحي خلال فصل الصيف (hPa)</t>
         </is>
       </c>
     </row>
@@ -5195,32 +5195,32 @@
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>ET_SprTot</t>
+          <t>PS_AutMean</t>
         </is>
       </c>
       <c r="C101" s="31" t="inlineStr">
         <is>
-          <t>ET_Spring_Total</t>
+          <t>PS_Autumn_Mean</t>
         </is>
       </c>
       <c r="D101" s="15" t="inlineStr">
         <is>
-          <t>14_Evapotranspiration (البخر والنتح)</t>
+          <t>04_Surface_Pressure (الضغط السطحي)</t>
         </is>
       </c>
       <c r="E101" s="7" t="inlineStr">
         <is>
-          <t>مجموع البخر والنتح لفصل الربيع الأرصادي (شهور مارس، أبريل، مايو - MAM).</t>
+          <t>متوسط الضغط الجوي السطحي الفعلي لفصل الخريف الأرصادي (SON).</t>
         </is>
       </c>
       <c r="F101" s="16" t="inlineStr">
         <is>
-          <t>ملم (mm)</t>
+          <t>hPa / mbar</t>
         </is>
       </c>
       <c r="G101" s="32" t="inlineStr">
         <is>
-          <t>خريطة مجموع البخر والنتح خلال فصل الربيع (ملم)</t>
+          <t>خريطة متوسط الضغط السطحي خلال فصل الخريف (hPa)</t>
         </is>
       </c>
     </row>
@@ -5230,32 +5230,32 @@
       </c>
       <c r="B102" s="10" t="inlineStr">
         <is>
-          <t>ET_SumTot</t>
+          <t>PS_AnnRng</t>
         </is>
       </c>
       <c r="C102" s="29" t="inlineStr">
         <is>
-          <t>ET_Summer_Total</t>
+          <t>PS_Annual_Range</t>
         </is>
       </c>
       <c r="D102" s="18" t="inlineStr">
         <is>
-          <t>14_Evapotranspiration (البخر والنتح)</t>
+          <t>04_Surface_Pressure (الضغط السطحي)</t>
         </is>
       </c>
       <c r="E102" s="12" t="inlineStr">
         <is>
-          <t>مجموع البخر والنتح لفصل الصيف الأرصادي (شهور يونيو، يوليو، أغسطس - JJA).</t>
+          <t>المدى البارومتري السنوي للضغط السطحي (الفارق بين أعلى وأدنى متوسط شهري للضغط السطحي).</t>
         </is>
       </c>
       <c r="F102" s="19" t="inlineStr">
         <is>
-          <t>ملم (mm)</t>
+          <t>hPa / mbar</t>
         </is>
       </c>
       <c r="G102" s="30" t="inlineStr">
         <is>
-          <t>خريطة مجموع البخر والنتح خلال فصل الصيف (ملم)</t>
+          <t>خريطة المدى السنوي للضغط الجوي السطحي (hPa)</t>
         </is>
       </c>
     </row>
@@ -5265,32 +5265,32 @@
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>ET_AutTot</t>
+          <t>PS_JanMean</t>
         </is>
       </c>
       <c r="C103" s="31" t="inlineStr">
         <is>
-          <t>ET_Autumn_Total</t>
+          <t>PS_January_Mean</t>
         </is>
       </c>
       <c r="D103" s="15" t="inlineStr">
         <is>
-          <t>14_Evapotranspiration (البخر والنتح)</t>
+          <t>04_Surface_Pressure (الضغط السطحي)</t>
         </is>
       </c>
       <c r="E103" s="7" t="inlineStr">
         <is>
-          <t>مجموع البخر والنتح لفصل الخريف الأرصادي (شهور سبتمبر، أكتوبر، نوفمبر - SON).</t>
+          <t>متوسط الضغط الجوي السطحي الفعلي الحقيقي عند منسوب المحطة لشهر يناير.</t>
         </is>
       </c>
       <c r="F103" s="16" t="inlineStr">
         <is>
-          <t>ملم (mm)</t>
+          <t>hPa / mbar</t>
         </is>
       </c>
       <c r="G103" s="32" t="inlineStr">
         <is>
-          <t>خريطة مجموع البخر والنتح خلال فصل الخريف (ملم)</t>
+          <t>خريطة متوسط الضغط السطحي الفعلي لشهر يناير (hPa)</t>
         </is>
       </c>
     </row>
@@ -5300,32 +5300,32 @@
       </c>
       <c r="B104" s="10" t="inlineStr">
         <is>
-          <t>PET_HarAnn</t>
+          <t>PS_FebMean</t>
         </is>
       </c>
       <c r="C104" s="29" t="inlineStr">
         <is>
-          <t>PET_Hargreaves_Annual</t>
+          <t>PS_February_Mean</t>
         </is>
       </c>
       <c r="D104" s="18" t="inlineStr">
         <is>
-          <t>14_Evapotranspiration (البخر والنتح)</t>
+          <t>04_Surface_Pressure (الضغط السطحي)</t>
         </is>
       </c>
       <c r="E104" s="12" t="inlineStr">
         <is>
-          <t>التبخر-نتح الكامن السنوي بهارجريفز (حقل رديف مطابق تماماً لـ ET_Annual_Total للتوافقية العكسية).</t>
+          <t>متوسط الضغط الجوي السطحي الفعلي الحقيقي عند منسوب المحطة لشهر فبراير.</t>
         </is>
       </c>
       <c r="F104" s="19" t="inlineStr">
         <is>
-          <t>ملم (mm)</t>
+          <t>hPa / mbar</t>
         </is>
       </c>
       <c r="G104" s="30" t="inlineStr">
         <is>
-          <t>خريطة التبخر والنتح الكامن السنوي بهارجريفز (ملم)</t>
+          <t>خريطة متوسط الضغط السطحي الفعلي لشهر فبراير (hPa)</t>
         </is>
       </c>
     </row>
@@ -5335,32 +5335,32 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>UNEP_Arid</t>
+          <t>PS_MarMean</t>
         </is>
       </c>
       <c r="C105" s="31" t="inlineStr">
         <is>
-          <t>UNEP_Aridity_Annual</t>
+          <t>PS_March_Mean</t>
         </is>
       </c>
       <c r="D105" s="15" t="inlineStr">
         <is>
-          <t>15_UNEP_Aridity (مؤشر UNEP)</t>
+          <t>04_Surface_Pressure (الضغط السطحي)</t>
         </is>
       </c>
       <c r="E105" s="7" t="inlineStr">
         <is>
-          <t>مؤشر القحولة العالمي لبرنامج الأمم المتحدة للبيئة AI = P / ET_ann لتحديد المناطق القاحلة وشبه القاحلة.</t>
+          <t>متوسط الضغط الجوي السطحي الفعلي الحقيقي عند منسوب المحطة لشهر مارس.</t>
         </is>
       </c>
       <c r="F105" s="16" t="inlineStr">
         <is>
-          <t>نسبة (Ratio)</t>
+          <t>hPa / mbar</t>
         </is>
       </c>
       <c r="G105" s="32" t="inlineStr">
         <is>
-          <t>خريطة مؤشر القحولة العالمي لبرنامج الأمم المتحدة للبيئة</t>
+          <t>خريطة متوسط الضغط السطحي الفعلي لشهر مارس (hPa)</t>
         </is>
       </c>
     </row>
@@ -5370,32 +5370,32 @@
       </c>
       <c r="B106" s="10" t="inlineStr">
         <is>
-          <t>WatDefAnn</t>
+          <t>PS_AprMean</t>
         </is>
       </c>
       <c r="C106" s="29" t="inlineStr">
         <is>
-          <t>Water_Deficit_Annual</t>
+          <t>PS_April_Mean</t>
         </is>
       </c>
       <c r="D106" s="18" t="inlineStr">
         <is>
-          <t>16_Water_Deficit (العجز المائي)</t>
+          <t>04_Surface_Pressure (الضغط السطحي)</t>
         </is>
       </c>
       <c r="E106" s="12" t="inlineStr">
         <is>
-          <t>الموازنة المائية المناخية السنوية الصافية WD = P - ET_ann (القيم السالبة تعبر عن عجز مائي والموجبة فائض مائي).</t>
+          <t>متوسط الضغط الجوي السطحي الفعلي الحقيقي عند منسوب المحطة لشهر أبريل.</t>
         </is>
       </c>
       <c r="F106" s="19" t="inlineStr">
         <is>
-          <t>ملم (mm)</t>
+          <t>hPa / mbar</t>
         </is>
       </c>
       <c r="G106" s="30" t="inlineStr">
         <is>
-          <t>خريطة الموازنة والعجز المائي المناخي السنوي (ملم)</t>
+          <t>خريطة متوسط الضغط السطحي الفعلي لشهر أبريل (hPa)</t>
         </is>
       </c>
     </row>
@@ -5405,32 +5405,32 @@
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>Dry_Months</t>
+          <t>PS_MayMean</t>
         </is>
       </c>
       <c r="C107" s="31" t="inlineStr">
         <is>
-          <t>Dry_Months_Count</t>
+          <t>PS_May_Mean</t>
         </is>
       </c>
       <c r="D107" s="15" t="inlineStr">
         <is>
-          <t>17_Dry_Months (الأشهر الجافة)</t>
+          <t>04_Surface_Pressure (الضغط السطحي)</t>
         </is>
       </c>
       <c r="E107" s="7" t="inlineStr">
         <is>
-          <t>عدد أشهر السنة الجافة بيولوجياً ومناخياً وفق معيار والتر-ليث البيومناخي الشهير (P &lt; 2T).</t>
+          <t>متوسط الضغط الجوي السطحي الفعلي الحقيقي عند منسوب المحطة لشهر مايو.</t>
         </is>
       </c>
       <c r="F107" s="16" t="inlineStr">
         <is>
-          <t>شهر (0-12)</t>
+          <t>hPa / mbar</t>
         </is>
       </c>
       <c r="G107" s="32" t="inlineStr">
         <is>
-          <t>خريطة عدد الأشهر الجافة بيولوجياً في السنة</t>
+          <t>خريطة متوسط الضغط السطحي الفعلي لشهر مايو (hPa)</t>
         </is>
       </c>
     </row>
@@ -5440,32 +5440,32 @@
       </c>
       <c r="B108" s="10" t="inlineStr">
         <is>
-          <t>T_TrendDec</t>
+          <t>PS_JunMean</t>
         </is>
       </c>
       <c r="C108" s="29" t="inlineStr">
         <is>
-          <t>T_Trend_Decade</t>
+          <t>PS_June_Mean</t>
         </is>
       </c>
       <c r="D108" s="18" t="inlineStr">
         <is>
-          <t>18_Trends_And_Anomalies (الاتجاهات والشذوذ)</t>
+          <t>04_Surface_Pressure (الضغط السطحي)</t>
         </is>
       </c>
       <c r="E108" s="12" t="inlineStr">
         <is>
-          <t>معدل تغير واتجاه درجة الحرارة لكل عقد زمني (10 سنوات) باستخدام انحدار المربعات الصغرى الخطي.</t>
+          <t>متوسط الضغط الجوي السطحي الفعلي الحقيقي عند منسوب المحطة لشهر يونيو.</t>
         </is>
       </c>
       <c r="F108" s="19" t="inlineStr">
         <is>
-          <t>°C/decade</t>
+          <t>hPa / mbar</t>
         </is>
       </c>
       <c r="G108" s="30" t="inlineStr">
         <is>
-          <t>خريطة اتجاه تغير درجة الحرارة في العقد الزمني (°C/decade)</t>
+          <t>خريطة متوسط الضغط السطحي الفعلي لشهر يونيو (hPa)</t>
         </is>
       </c>
     </row>
@@ -5475,32 +5475,32 @@
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>R_TrendDec</t>
+          <t>PS_JulMean</t>
         </is>
       </c>
       <c r="C109" s="31" t="inlineStr">
         <is>
-          <t>R_Trend_Decade</t>
+          <t>PS_July_Mean</t>
         </is>
       </c>
       <c r="D109" s="15" t="inlineStr">
         <is>
-          <t>18_Trends_And_Anomalies (الاتجاهات والشذوذ)</t>
+          <t>04_Surface_Pressure (الضغط السطحي)</t>
         </is>
       </c>
       <c r="E109" s="7" t="inlineStr">
         <is>
-          <t>معدل تغير واتجاه تساقط الأمطار لكل عقد زمني (10 سنوات) باستخدام انحدار المربعات الصغرى الخطي.</t>
+          <t>متوسط الضغط الجوي السطحي الفعلي الحقيقي عند منسوب المحطة لشهر يوليو.</t>
         </is>
       </c>
       <c r="F109" s="16" t="inlineStr">
         <is>
-          <t>mm/decade</t>
+          <t>hPa / mbar</t>
         </is>
       </c>
       <c r="G109" s="32" t="inlineStr">
         <is>
-          <t>خريطة اتجاه تغير تساقط الأمطار في العقد الزمني (mm/decade)</t>
+          <t>خريطة متوسط الضغط السطحي الفعلي لشهر يوليو (hPa)</t>
         </is>
       </c>
     </row>
@@ -5510,32 +5510,32 @@
       </c>
       <c r="B110" s="10" t="inlineStr">
         <is>
-          <t>T_AnomAnn</t>
+          <t>PS_AugMean</t>
         </is>
       </c>
       <c r="C110" s="29" t="inlineStr">
         <is>
-          <t>T_Anom_Annual</t>
+          <t>PS_August_Mean</t>
         </is>
       </c>
       <c r="D110" s="18" t="inlineStr">
         <is>
-          <t>18_Trends_And_Anomalies (الاتجاهات والشذوذ)</t>
+          <t>04_Surface_Pressure (الضغط السطحي)</t>
         </is>
       </c>
       <c r="E110" s="12" t="inlineStr">
         <is>
-          <t>الشذوذ الحراري السنوي لدرجة الحرارة مقارنة بخط الأساس المناخي العالمي 1991–2020.</t>
+          <t>متوسط الضغط الجوي السطحي الفعلي الحقيقي عند منسوب المحطة لشهر أغسطس.</t>
         </is>
       </c>
       <c r="F110" s="19" t="inlineStr">
         <is>
-          <t>°C</t>
+          <t>hPa / mbar</t>
         </is>
       </c>
       <c r="G110" s="30" t="inlineStr">
         <is>
-          <t>خريطة الشذوذ الحراري السنوي مقارنة بخط أساس 1991–2020 (°C)</t>
+          <t>خريطة متوسط الضغط السطحي الفعلي لشهر أغسطس (hPa)</t>
         </is>
       </c>
     </row>
@@ -5545,32 +5545,32 @@
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>T_AnomWin</t>
+          <t>PS_SepMean</t>
         </is>
       </c>
       <c r="C111" s="31" t="inlineStr">
         <is>
-          <t>T_Anom_Winter</t>
+          <t>PS_September_Mean</t>
         </is>
       </c>
       <c r="D111" s="15" t="inlineStr">
         <is>
-          <t>18_Trends_And_Anomalies (الاتجاهات والشذوذ)</t>
+          <t>04_Surface_Pressure (الضغط السطحي)</t>
         </is>
       </c>
       <c r="E111" s="7" t="inlineStr">
         <is>
-          <t>الشذوذ الحراري لفصل الشتاء مقارنة بمتوسط شهور الشتاء لخط الأساس المناخي 1991–2020.</t>
+          <t>متوسط الضغط الجوي السطحي الفعلي الحقيقي عند منسوب المحطة لشهر سبتمبر.</t>
         </is>
       </c>
       <c r="F111" s="16" t="inlineStr">
         <is>
-          <t>°C</t>
+          <t>hPa / mbar</t>
         </is>
       </c>
       <c r="G111" s="32" t="inlineStr">
         <is>
-          <t>خريطة الشذوذ الحراري لفصل الشتاء مقارنة بخط أساس 1991–2020 (°C)</t>
+          <t>خريطة متوسط الضغط السطحي الفعلي لشهر سبتمبر (hPa)</t>
         </is>
       </c>
     </row>
@@ -5580,32 +5580,32 @@
       </c>
       <c r="B112" s="10" t="inlineStr">
         <is>
-          <t>T_AnomSum</t>
+          <t>PS_OctMean</t>
         </is>
       </c>
       <c r="C112" s="29" t="inlineStr">
         <is>
-          <t>T_Anom_Summer</t>
+          <t>PS_October_Mean</t>
         </is>
       </c>
       <c r="D112" s="18" t="inlineStr">
         <is>
-          <t>18_Trends_And_Anomalies (الاتجاهات والشذوذ)</t>
+          <t>04_Surface_Pressure (الضغط السطحي)</t>
         </is>
       </c>
       <c r="E112" s="12" t="inlineStr">
         <is>
-          <t>الشذوذ الحراري لفصل الصيف مقارنة بمتوسط شهور الصيف لخط الأساس المناخي 1991–2020.</t>
+          <t>متوسط الضغط الجوي السطحي الفعلي الحقيقي عند منسوب المحطة لشهر أكتوبر.</t>
         </is>
       </c>
       <c r="F112" s="19" t="inlineStr">
         <is>
-          <t>°C</t>
+          <t>hPa / mbar</t>
         </is>
       </c>
       <c r="G112" s="30" t="inlineStr">
         <is>
-          <t>خريطة الشذوذ الحراري لفصل الصيف مقارنة بخط أساس 1991–2020 (°C)</t>
+          <t>خريطة متوسط الضغط السطحي الفعلي لشهر أكتوبر (hPa)</t>
         </is>
       </c>
     </row>
@@ -5615,32 +5615,32 @@
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>R_AnomAnn</t>
+          <t>PS_NovMean</t>
         </is>
       </c>
       <c r="C113" s="31" t="inlineStr">
         <is>
-          <t>R_Anom_Annual</t>
+          <t>PS_November_Mean</t>
         </is>
       </c>
       <c r="D113" s="15" t="inlineStr">
         <is>
-          <t>18_Trends_And_Anomalies (الاتجاهات والشذوذ)</t>
+          <t>04_Surface_Pressure (الضغط السطحي)</t>
         </is>
       </c>
       <c r="E113" s="7" t="inlineStr">
         <is>
-          <t>شذوذ الأمطار السنوي المطلق مقارنة بمتوسط الأمطار لخط الأساس المناخي 1991–2020.</t>
+          <t>متوسط الضغط الجوي السطحي الفعلي الحقيقي عند منسوب المحطة لشهر نوفمبر.</t>
         </is>
       </c>
       <c r="F113" s="16" t="inlineStr">
         <is>
-          <t>ملم (mm)</t>
+          <t>hPa / mbar</t>
         </is>
       </c>
       <c r="G113" s="32" t="inlineStr">
         <is>
-          <t>خريطة شذوذ تساقط الأمطار السنوي مقارنة بخط أساس 1991–2020 (ملم)</t>
+          <t>خريطة متوسط الضغط السطحي الفعلي لشهر نوفمبر (hPa)</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="B114" s="10" t="inlineStr">
         <is>
-          <t>R_AnomPct</t>
+          <t>PS_DecMean</t>
         </is>
       </c>
       <c r="C114" s="29" t="inlineStr">
         <is>
-          <t>R_Anom_Annual_Pct</t>
+          <t>PS_December_Mean</t>
         </is>
       </c>
       <c r="D114" s="18" t="inlineStr">
         <is>
-          <t>18_Trends_And_Anomalies (الاتجاهات والشذوذ)</t>
+          <t>04_Surface_Pressure (الضغط السطحي)</t>
         </is>
       </c>
       <c r="E114" s="12" t="inlineStr">
         <is>
-          <t>شذوذ الأمطار السنوي كنسبة مئوية من خط الأساس المناخي 1991–2020 (فرق نسبي مئوي).</t>
+          <t>متوسط الضغط الجوي السطحي الفعلي الحقيقي عند منسوب المحطة لشهر ديسمبر.</t>
         </is>
       </c>
       <c r="F114" s="19" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>hPa / mbar</t>
         </is>
       </c>
       <c r="G114" s="30" t="inlineStr">
         <is>
-          <t>خريطة الشذوذ النسبي المئوي للأمطار مقارنة بخط أساس 1991–2020 (%)</t>
+          <t>خريطة متوسط الضغط السطحي الفعلي لشهر ديسمبر (hPa)</t>
         </is>
       </c>
     </row>
@@ -5685,32 +5685,32 @@
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>R_AnomWin</t>
+          <t>WSp_AnMean</t>
         </is>
       </c>
       <c r="C115" s="31" t="inlineStr">
         <is>
-          <t>R_Anom_Winter</t>
+          <t>W_Spd_Annual_Mean</t>
         </is>
       </c>
       <c r="D115" s="15" t="inlineStr">
         <is>
-          <t>18_Trends_And_Anomalies (الاتجاهات والشذوذ)</t>
+          <t>05_Wind (الرياح)</t>
         </is>
       </c>
       <c r="E115" s="7" t="inlineStr">
         <is>
-          <t>شذوذ أمطار فصل الشتاء المطلق مقارنة بأمطار شتاء خط الأساس المناخي 1991–2020.</t>
+          <t>المتوسط السنوي لسرعة الرياح عند ارتفاع 10 أمتار فوق سطح الأرض.</t>
         </is>
       </c>
       <c r="F115" s="16" t="inlineStr">
         <is>
-          <t>ملم (mm)</t>
+          <t>م/ث (m/s)</t>
         </is>
       </c>
       <c r="G115" s="32" t="inlineStr">
         <is>
-          <t>خريطة شذوذ أمطار الشتاء مقارنة بخط أساس 1991–2020 (ملم)</t>
+          <t>خريطة المتوسط السنوي لسرعة الرياح (م/ث)</t>
         </is>
       </c>
     </row>
@@ -5720,37 +5720,5077 @@
       </c>
       <c r="B116" s="10" t="inlineStr">
         <is>
+          <t>WSp_WnMean</t>
+        </is>
+      </c>
+      <c r="C116" s="29" t="inlineStr">
+        <is>
+          <t>W_Spd_Winter_Mean</t>
+        </is>
+      </c>
+      <c r="D116" s="18" t="inlineStr">
+        <is>
+          <t>05_Wind (الرياح)</t>
+        </is>
+      </c>
+      <c r="E116" s="12" t="inlineStr">
+        <is>
+          <t>متوسط سرعة الرياح لفصل الشتاء الأرصادي عند ارتفاع 10 أمتار (DJF).</t>
+        </is>
+      </c>
+      <c r="F116" s="19" t="inlineStr">
+        <is>
+          <t>م/ث (m/s)</t>
+        </is>
+      </c>
+      <c r="G116" s="30" t="inlineStr">
+        <is>
+          <t>خريطة متوسط سرعة الرياح خلال فصل الشتاء (م/ث)</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="24" customHeight="1">
+      <c r="A117" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" s="5" t="inlineStr">
+        <is>
+          <t>WSp_SpMean</t>
+        </is>
+      </c>
+      <c r="C117" s="31" t="inlineStr">
+        <is>
+          <t>W_Spd_Spring_Mean</t>
+        </is>
+      </c>
+      <c r="D117" s="15" t="inlineStr">
+        <is>
+          <t>05_Wind (الرياح)</t>
+        </is>
+      </c>
+      <c r="E117" s="7" t="inlineStr">
+        <is>
+          <t>متوسط سرعة الرياح لفصل الربيع الأرصادي عند ارتفاع 10 أمتار (MAM).</t>
+        </is>
+      </c>
+      <c r="F117" s="16" t="inlineStr">
+        <is>
+          <t>م/ث (m/s)</t>
+        </is>
+      </c>
+      <c r="G117" s="32" t="inlineStr">
+        <is>
+          <t>خريطة متوسط سرعة الرياح خلال فصل الربيع (م/ث)</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="24" customHeight="1">
+      <c r="A118" s="8" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" s="10" t="inlineStr">
+        <is>
+          <t>WSp_SuMean</t>
+        </is>
+      </c>
+      <c r="C118" s="29" t="inlineStr">
+        <is>
+          <t>W_Spd_Summer_Mean</t>
+        </is>
+      </c>
+      <c r="D118" s="18" t="inlineStr">
+        <is>
+          <t>05_Wind (الرياح)</t>
+        </is>
+      </c>
+      <c r="E118" s="12" t="inlineStr">
+        <is>
+          <t>متوسط سرعة الرياح لفصل الصيف الأرصادي عند ارتفاع 10 أمتار (JJA).</t>
+        </is>
+      </c>
+      <c r="F118" s="19" t="inlineStr">
+        <is>
+          <t>م/ث (m/s)</t>
+        </is>
+      </c>
+      <c r="G118" s="30" t="inlineStr">
+        <is>
+          <t>خريطة متوسط سرعة الرياح خلال فصل الصيف (م/ث)</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="24" customHeight="1">
+      <c r="A119" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" s="5" t="inlineStr">
+        <is>
+          <t>WSp_AuMean</t>
+        </is>
+      </c>
+      <c r="C119" s="31" t="inlineStr">
+        <is>
+          <t>W_Spd_Autumn_Mean</t>
+        </is>
+      </c>
+      <c r="D119" s="15" t="inlineStr">
+        <is>
+          <t>05_Wind (الرياح)</t>
+        </is>
+      </c>
+      <c r="E119" s="7" t="inlineStr">
+        <is>
+          <t>متوسط سرعة الرياح لفصل الخريف الأرصادي عند ارتفاع 10 أمتار (SON).</t>
+        </is>
+      </c>
+      <c r="F119" s="16" t="inlineStr">
+        <is>
+          <t>م/ث (m/s)</t>
+        </is>
+      </c>
+      <c r="G119" s="32" t="inlineStr">
+        <is>
+          <t>خريطة متوسط سرعة الرياح خلال فصل الخريف (م/ث)</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="24" customHeight="1">
+      <c r="A120" s="8" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" s="10" t="inlineStr">
+        <is>
+          <t>WSp_MaxMo</t>
+        </is>
+      </c>
+      <c r="C120" s="29" t="inlineStr">
+        <is>
+          <t>W_Spd_Annual_Max_Month</t>
+        </is>
+      </c>
+      <c r="D120" s="18" t="inlineStr">
+        <is>
+          <t>05_Wind (الرياح)</t>
+        </is>
+      </c>
+      <c r="E120" s="12" t="inlineStr">
+        <is>
+          <t>أقصى متوسط شهري مسجل لسرعة الرياح في السنة (ذروة النشاط الريحي).</t>
+        </is>
+      </c>
+      <c r="F120" s="19" t="inlineStr">
+        <is>
+          <t>م/ث (m/s)</t>
+        </is>
+      </c>
+      <c r="G120" s="30" t="inlineStr">
+        <is>
+          <t>خريطة أقصى متوسط شهري لسرعة الرياح (م/ث)</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="24" customHeight="1">
+      <c r="A121" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" s="5" t="inlineStr">
+        <is>
+          <t>WSp_MinMo</t>
+        </is>
+      </c>
+      <c r="C121" s="31" t="inlineStr">
+        <is>
+          <t>W_Spd_Annual_Min_Month</t>
+        </is>
+      </c>
+      <c r="D121" s="15" t="inlineStr">
+        <is>
+          <t>05_Wind (الرياح)</t>
+        </is>
+      </c>
+      <c r="E121" s="7" t="inlineStr">
+        <is>
+          <t>أدنى متوسط شهري مسجل لسرعة الرياح في السنة (فترة الهدوء الريحي).</t>
+        </is>
+      </c>
+      <c r="F121" s="16" t="inlineStr">
+        <is>
+          <t>م/ث (m/s)</t>
+        </is>
+      </c>
+      <c r="G121" s="32" t="inlineStr">
+        <is>
+          <t>خريطة أدنى متوسط شهري لسرعة الرياح (م/ث)</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="24" customHeight="1">
+      <c r="A122" s="8" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" s="10" t="inlineStr">
+        <is>
+          <t>WSp_AnRng</t>
+        </is>
+      </c>
+      <c r="C122" s="29" t="inlineStr">
+        <is>
+          <t>W_Spd_Annual_Range</t>
+        </is>
+      </c>
+      <c r="D122" s="18" t="inlineStr">
+        <is>
+          <t>05_Wind (الرياح)</t>
+        </is>
+      </c>
+      <c r="E122" s="12" t="inlineStr">
+        <is>
+          <t>المدى السنوي لسرعة الرياح (الفارق بين أشد شهور السنة رياحاً وأهدأها سرعة).</t>
+        </is>
+      </c>
+      <c r="F122" s="19" t="inlineStr">
+        <is>
+          <t>م/ث (m/s)</t>
+        </is>
+      </c>
+      <c r="G122" s="30" t="inlineStr">
+        <is>
+          <t>خريطة المدى السنوي لسرعة الرياح (م/ث)</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="24" customHeight="1">
+      <c r="A123" s="3" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" s="5" t="inlineStr">
+        <is>
+          <t>WDr_AnMean</t>
+        </is>
+      </c>
+      <c r="C123" s="31" t="inlineStr">
+        <is>
+          <t>W_Dir_Annual_Mean</t>
+        </is>
+      </c>
+      <c r="D123" s="15" t="inlineStr">
+        <is>
+          <t>05_Wind (الرياح)</t>
+        </is>
+      </c>
+      <c r="E123" s="7" t="inlineStr">
+        <is>
+          <t>الاتجاه السائد السنوي للرياح بالدرجات الزاوية (محسوب بالمتوسط الدائري للمتجهات الدائرية atan2).</t>
+        </is>
+      </c>
+      <c r="F123" s="16" t="inlineStr">
+        <is>
+          <t>درجة (°)</t>
+        </is>
+      </c>
+      <c r="G123" s="32" t="inlineStr">
+        <is>
+          <t>خريطة الاتجاه السائد السنوي للرياح (درجات)</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="24" customHeight="1">
+      <c r="A124" s="8" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" s="10" t="inlineStr">
+        <is>
+          <t>WDr_WnMean</t>
+        </is>
+      </c>
+      <c r="C124" s="29" t="inlineStr">
+        <is>
+          <t>W_Dir_Winter_Mean</t>
+        </is>
+      </c>
+      <c r="D124" s="18" t="inlineStr">
+        <is>
+          <t>05_Wind (الرياح)</t>
+        </is>
+      </c>
+      <c r="E124" s="12" t="inlineStr">
+        <is>
+          <t>اتجاه الرياح السائد خلال فصل الشتاء الأرصادي بالدرجات الزاوية (DJF).</t>
+        </is>
+      </c>
+      <c r="F124" s="19" t="inlineStr">
+        <is>
+          <t>درجة (°)</t>
+        </is>
+      </c>
+      <c r="G124" s="30" t="inlineStr">
+        <is>
+          <t>خريطة اتجاه الرياح السائد خلال فصل الشتاء (درجات)</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="24" customHeight="1">
+      <c r="A125" s="3" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" s="5" t="inlineStr">
+        <is>
+          <t>WDr_SpMean</t>
+        </is>
+      </c>
+      <c r="C125" s="31" t="inlineStr">
+        <is>
+          <t>W_Dir_Spring_Mean</t>
+        </is>
+      </c>
+      <c r="D125" s="15" t="inlineStr">
+        <is>
+          <t>05_Wind (الرياح)</t>
+        </is>
+      </c>
+      <c r="E125" s="7" t="inlineStr">
+        <is>
+          <t>اتجاه الرياح السائد خلال فصل الربيع الأرصادي بالدرجات الزاوية (MAM).</t>
+        </is>
+      </c>
+      <c r="F125" s="16" t="inlineStr">
+        <is>
+          <t>درجة (°)</t>
+        </is>
+      </c>
+      <c r="G125" s="32" t="inlineStr">
+        <is>
+          <t>خريطة اتجاه الرياح السائد خلال فصل الربيع (درجات)</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="24" customHeight="1">
+      <c r="A126" s="8" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" s="10" t="inlineStr">
+        <is>
+          <t>WDr_SuMean</t>
+        </is>
+      </c>
+      <c r="C126" s="29" t="inlineStr">
+        <is>
+          <t>W_Dir_Summer_Mean</t>
+        </is>
+      </c>
+      <c r="D126" s="18" t="inlineStr">
+        <is>
+          <t>05_Wind (الرياح)</t>
+        </is>
+      </c>
+      <c r="E126" s="12" t="inlineStr">
+        <is>
+          <t>اتجاه الرياح السائد خلال فصل الصيف الأرصادي بالدرجات الزاوية (JJA).</t>
+        </is>
+      </c>
+      <c r="F126" s="19" t="inlineStr">
+        <is>
+          <t>درجة (°)</t>
+        </is>
+      </c>
+      <c r="G126" s="30" t="inlineStr">
+        <is>
+          <t>خريطة اتجاه الرياح السائد خلال فصل الصيف (درجات)</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="24" customHeight="1">
+      <c r="A127" s="3" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" s="5" t="inlineStr">
+        <is>
+          <t>WDr_AuMean</t>
+        </is>
+      </c>
+      <c r="C127" s="31" t="inlineStr">
+        <is>
+          <t>W_Dir_Autumn_Mean</t>
+        </is>
+      </c>
+      <c r="D127" s="15" t="inlineStr">
+        <is>
+          <t>05_Wind (الرياح)</t>
+        </is>
+      </c>
+      <c r="E127" s="7" t="inlineStr">
+        <is>
+          <t>اتجاه الرياح السائد خلال فصل الخريف الأرصادي بالدرجات الزاوية (SON).</t>
+        </is>
+      </c>
+      <c r="F127" s="16" t="inlineStr">
+        <is>
+          <t>درجة (°)</t>
+        </is>
+      </c>
+      <c r="G127" s="32" t="inlineStr">
+        <is>
+          <t>خريطة اتجاه الرياح السائد خلال فصل الخريف (درجات)</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="24" customHeight="1">
+      <c r="A128" s="8" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" s="10" t="inlineStr">
+        <is>
+          <t>WSp_JanMn</t>
+        </is>
+      </c>
+      <c r="C128" s="29" t="inlineStr">
+        <is>
+          <t>W_Spd_January_Mean</t>
+        </is>
+      </c>
+      <c r="D128" s="18" t="inlineStr">
+        <is>
+          <t>05_Wind (الرياح)</t>
+        </is>
+      </c>
+      <c r="E128" s="12" t="inlineStr">
+        <is>
+          <t>متوسط سرعة الرياح على ارتفاع 10 أمتار لشهر يناير عبر فترة الرصد.</t>
+        </is>
+      </c>
+      <c r="F128" s="19" t="inlineStr">
+        <is>
+          <t>م/ث (m/s)</t>
+        </is>
+      </c>
+      <c r="G128" s="30" t="inlineStr">
+        <is>
+          <t>خريطة متوسط سرعة الرياح لشهر يناير (م/ث)</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="24" customHeight="1">
+      <c r="A129" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" s="5" t="inlineStr">
+        <is>
+          <t>WSp_FebMn</t>
+        </is>
+      </c>
+      <c r="C129" s="31" t="inlineStr">
+        <is>
+          <t>W_Spd_February_Mean</t>
+        </is>
+      </c>
+      <c r="D129" s="15" t="inlineStr">
+        <is>
+          <t>05_Wind (الرياح)</t>
+        </is>
+      </c>
+      <c r="E129" s="7" t="inlineStr">
+        <is>
+          <t>متوسط سرعة الرياح على ارتفاع 10 أمتار لشهر فبراير عبر فترة الرصد.</t>
+        </is>
+      </c>
+      <c r="F129" s="16" t="inlineStr">
+        <is>
+          <t>م/ث (m/s)</t>
+        </is>
+      </c>
+      <c r="G129" s="32" t="inlineStr">
+        <is>
+          <t>خريطة متوسط سرعة الرياح لشهر فبراير (م/ث)</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="24" customHeight="1">
+      <c r="A130" s="8" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" s="10" t="inlineStr">
+        <is>
+          <t>WSp_MarMn</t>
+        </is>
+      </c>
+      <c r="C130" s="29" t="inlineStr">
+        <is>
+          <t>W_Spd_March_Mean</t>
+        </is>
+      </c>
+      <c r="D130" s="18" t="inlineStr">
+        <is>
+          <t>05_Wind (الرياح)</t>
+        </is>
+      </c>
+      <c r="E130" s="12" t="inlineStr">
+        <is>
+          <t>متوسط سرعة الرياح على ارتفاع 10 أمتار لشهر مارس عبر فترة الرصد.</t>
+        </is>
+      </c>
+      <c r="F130" s="19" t="inlineStr">
+        <is>
+          <t>م/ث (m/s)</t>
+        </is>
+      </c>
+      <c r="G130" s="30" t="inlineStr">
+        <is>
+          <t>خريطة متوسط سرعة الرياح لشهر مارس (م/ث)</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="24" customHeight="1">
+      <c r="A131" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" s="5" t="inlineStr">
+        <is>
+          <t>WSp_AprMn</t>
+        </is>
+      </c>
+      <c r="C131" s="31" t="inlineStr">
+        <is>
+          <t>W_Spd_April_Mean</t>
+        </is>
+      </c>
+      <c r="D131" s="15" t="inlineStr">
+        <is>
+          <t>05_Wind (الرياح)</t>
+        </is>
+      </c>
+      <c r="E131" s="7" t="inlineStr">
+        <is>
+          <t>متوسط سرعة الرياح على ارتفاع 10 أمتار لشهر أبريل عبر فترة الرصد.</t>
+        </is>
+      </c>
+      <c r="F131" s="16" t="inlineStr">
+        <is>
+          <t>م/ث (m/s)</t>
+        </is>
+      </c>
+      <c r="G131" s="32" t="inlineStr">
+        <is>
+          <t>خريطة متوسط سرعة الرياح لشهر أبريل (م/ث)</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="24" customHeight="1">
+      <c r="A132" s="8" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" s="10" t="inlineStr">
+        <is>
+          <t>WSp_MayMn</t>
+        </is>
+      </c>
+      <c r="C132" s="29" t="inlineStr">
+        <is>
+          <t>W_Spd_May_Mean</t>
+        </is>
+      </c>
+      <c r="D132" s="18" t="inlineStr">
+        <is>
+          <t>05_Wind (الرياح)</t>
+        </is>
+      </c>
+      <c r="E132" s="12" t="inlineStr">
+        <is>
+          <t>متوسط سرعة الرياح على ارتفاع 10 أمتار لشهر مايو عبر فترة الرصد.</t>
+        </is>
+      </c>
+      <c r="F132" s="19" t="inlineStr">
+        <is>
+          <t>م/ث (m/s)</t>
+        </is>
+      </c>
+      <c r="G132" s="30" t="inlineStr">
+        <is>
+          <t>خريطة متوسط سرعة الرياح لشهر مايو (م/ث)</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="24" customHeight="1">
+      <c r="A133" s="3" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" s="5" t="inlineStr">
+        <is>
+          <t>WSp_JunMn</t>
+        </is>
+      </c>
+      <c r="C133" s="31" t="inlineStr">
+        <is>
+          <t>W_Spd_June_Mean</t>
+        </is>
+      </c>
+      <c r="D133" s="15" t="inlineStr">
+        <is>
+          <t>05_Wind (الرياح)</t>
+        </is>
+      </c>
+      <c r="E133" s="7" t="inlineStr">
+        <is>
+          <t>متوسط سرعة الرياح على ارتفاع 10 أمتار لشهر يونيو عبر فترة الرصد.</t>
+        </is>
+      </c>
+      <c r="F133" s="16" t="inlineStr">
+        <is>
+          <t>م/ث (m/s)</t>
+        </is>
+      </c>
+      <c r="G133" s="32" t="inlineStr">
+        <is>
+          <t>خريطة متوسط سرعة الرياح لشهر يونيو (م/ث)</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="24" customHeight="1">
+      <c r="A134" s="8" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" s="10" t="inlineStr">
+        <is>
+          <t>WSp_JulMn</t>
+        </is>
+      </c>
+      <c r="C134" s="29" t="inlineStr">
+        <is>
+          <t>W_Spd_July_Mean</t>
+        </is>
+      </c>
+      <c r="D134" s="18" t="inlineStr">
+        <is>
+          <t>05_Wind (الرياح)</t>
+        </is>
+      </c>
+      <c r="E134" s="12" t="inlineStr">
+        <is>
+          <t>متوسط سرعة الرياح على ارتفاع 10 أمتار لشهر يوليو عبر فترة الرصد.</t>
+        </is>
+      </c>
+      <c r="F134" s="19" t="inlineStr">
+        <is>
+          <t>م/ث (m/s)</t>
+        </is>
+      </c>
+      <c r="G134" s="30" t="inlineStr">
+        <is>
+          <t>خريطة متوسط سرعة الرياح لشهر يوليو (م/ث)</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="24" customHeight="1">
+      <c r="A135" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" s="5" t="inlineStr">
+        <is>
+          <t>WSp_AugMn</t>
+        </is>
+      </c>
+      <c r="C135" s="31" t="inlineStr">
+        <is>
+          <t>W_Spd_August_Mean</t>
+        </is>
+      </c>
+      <c r="D135" s="15" t="inlineStr">
+        <is>
+          <t>05_Wind (الرياح)</t>
+        </is>
+      </c>
+      <c r="E135" s="7" t="inlineStr">
+        <is>
+          <t>متوسط سرعة الرياح على ارتفاع 10 أمتار لشهر أغسطس عبر فترة الرصد.</t>
+        </is>
+      </c>
+      <c r="F135" s="16" t="inlineStr">
+        <is>
+          <t>م/ث (m/s)</t>
+        </is>
+      </c>
+      <c r="G135" s="32" t="inlineStr">
+        <is>
+          <t>خريطة متوسط سرعة الرياح لشهر أغسطس (م/ث)</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="24" customHeight="1">
+      <c r="A136" s="8" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" s="10" t="inlineStr">
+        <is>
+          <t>WSp_SepMn</t>
+        </is>
+      </c>
+      <c r="C136" s="29" t="inlineStr">
+        <is>
+          <t>W_Spd_September_Mean</t>
+        </is>
+      </c>
+      <c r="D136" s="18" t="inlineStr">
+        <is>
+          <t>05_Wind (الرياح)</t>
+        </is>
+      </c>
+      <c r="E136" s="12" t="inlineStr">
+        <is>
+          <t>متوسط سرعة الرياح على ارتفاع 10 أمتار لشهر سبتمبر عبر فترة الرصد.</t>
+        </is>
+      </c>
+      <c r="F136" s="19" t="inlineStr">
+        <is>
+          <t>م/ث (m/s)</t>
+        </is>
+      </c>
+      <c r="G136" s="30" t="inlineStr">
+        <is>
+          <t>خريطة متوسط سرعة الرياح لشهر سبتمبر (م/ث)</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="24" customHeight="1">
+      <c r="A137" s="3" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" s="5" t="inlineStr">
+        <is>
+          <t>WSp_OctMn</t>
+        </is>
+      </c>
+      <c r="C137" s="31" t="inlineStr">
+        <is>
+          <t>W_Spd_October_Mean</t>
+        </is>
+      </c>
+      <c r="D137" s="15" t="inlineStr">
+        <is>
+          <t>05_Wind (الرياح)</t>
+        </is>
+      </c>
+      <c r="E137" s="7" t="inlineStr">
+        <is>
+          <t>متوسط سرعة الرياح على ارتفاع 10 أمتار لشهر أكتوبر عبر فترة الرصد.</t>
+        </is>
+      </c>
+      <c r="F137" s="16" t="inlineStr">
+        <is>
+          <t>م/ث (m/s)</t>
+        </is>
+      </c>
+      <c r="G137" s="32" t="inlineStr">
+        <is>
+          <t>خريطة متوسط سرعة الرياح لشهر أكتوبر (م/ث)</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="24" customHeight="1">
+      <c r="A138" s="8" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" s="10" t="inlineStr">
+        <is>
+          <t>WSp_NovMn</t>
+        </is>
+      </c>
+      <c r="C138" s="29" t="inlineStr">
+        <is>
+          <t>W_Spd_November_Mean</t>
+        </is>
+      </c>
+      <c r="D138" s="18" t="inlineStr">
+        <is>
+          <t>05_Wind (الرياح)</t>
+        </is>
+      </c>
+      <c r="E138" s="12" t="inlineStr">
+        <is>
+          <t>متوسط سرعة الرياح على ارتفاع 10 أمتار لشهر نوفمبر عبر فترة الرصد.</t>
+        </is>
+      </c>
+      <c r="F138" s="19" t="inlineStr">
+        <is>
+          <t>م/ث (m/s)</t>
+        </is>
+      </c>
+      <c r="G138" s="30" t="inlineStr">
+        <is>
+          <t>خريطة متوسط سرعة الرياح لشهر نوفمبر (م/ث)</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="24" customHeight="1">
+      <c r="A139" s="3" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" s="5" t="inlineStr">
+        <is>
+          <t>WSp_DecMn</t>
+        </is>
+      </c>
+      <c r="C139" s="31" t="inlineStr">
+        <is>
+          <t>W_Spd_December_Mean</t>
+        </is>
+      </c>
+      <c r="D139" s="15" t="inlineStr">
+        <is>
+          <t>05_Wind (الرياح)</t>
+        </is>
+      </c>
+      <c r="E139" s="7" t="inlineStr">
+        <is>
+          <t>متوسط سرعة الرياح على ارتفاع 10 أمتار لشهر ديسمبر عبر فترة الرصد.</t>
+        </is>
+      </c>
+      <c r="F139" s="16" t="inlineStr">
+        <is>
+          <t>م/ث (m/s)</t>
+        </is>
+      </c>
+      <c r="G139" s="32" t="inlineStr">
+        <is>
+          <t>خريطة متوسط سرعة الرياح لشهر ديسمبر (م/ث)</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="24" customHeight="1">
+      <c r="A140" s="8" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" s="10" t="inlineStr">
+        <is>
+          <t>WDr_JanMn</t>
+        </is>
+      </c>
+      <c r="C140" s="29" t="inlineStr">
+        <is>
+          <t>W_Dir_January_Mean</t>
+        </is>
+      </c>
+      <c r="D140" s="18" t="inlineStr">
+        <is>
+          <t>05_Wind (الرياح)</t>
+        </is>
+      </c>
+      <c r="E140" s="12" t="inlineStr">
+        <is>
+          <t>متوسط اتجاه الرياح السائد لشهر يناير محسوب بالمتوسط الدائري المتجهي (atan2).</t>
+        </is>
+      </c>
+      <c r="F140" s="19" t="inlineStr">
+        <is>
+          <t>درجة (°) / Degree</t>
+        </is>
+      </c>
+      <c r="G140" s="30" t="inlineStr">
+        <is>
+          <t>خريطة اتجاه الرياح السائد لشهر يناير (°)</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="24" customHeight="1">
+      <c r="A141" s="3" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" s="5" t="inlineStr">
+        <is>
+          <t>WDr_FebMn</t>
+        </is>
+      </c>
+      <c r="C141" s="31" t="inlineStr">
+        <is>
+          <t>W_Dir_February_Mean</t>
+        </is>
+      </c>
+      <c r="D141" s="15" t="inlineStr">
+        <is>
+          <t>05_Wind (الرياح)</t>
+        </is>
+      </c>
+      <c r="E141" s="7" t="inlineStr">
+        <is>
+          <t>متوسط اتجاه الرياح السائد لشهر فبراير محسوب بالمتوسط الدائري المتجهي (atan2).</t>
+        </is>
+      </c>
+      <c r="F141" s="16" t="inlineStr">
+        <is>
+          <t>درجة (°) / Degree</t>
+        </is>
+      </c>
+      <c r="G141" s="32" t="inlineStr">
+        <is>
+          <t>خريطة اتجاه الرياح السائد لشهر فبراير (°)</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="24" customHeight="1">
+      <c r="A142" s="8" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" s="10" t="inlineStr">
+        <is>
+          <t>WDr_MarMn</t>
+        </is>
+      </c>
+      <c r="C142" s="29" t="inlineStr">
+        <is>
+          <t>W_Dir_March_Mean</t>
+        </is>
+      </c>
+      <c r="D142" s="18" t="inlineStr">
+        <is>
+          <t>05_Wind (الرياح)</t>
+        </is>
+      </c>
+      <c r="E142" s="12" t="inlineStr">
+        <is>
+          <t>متوسط اتجاه الرياح السائد لشهر مارس محسوب بالمتوسط الدائري المتجهي (atan2).</t>
+        </is>
+      </c>
+      <c r="F142" s="19" t="inlineStr">
+        <is>
+          <t>درجة (°) / Degree</t>
+        </is>
+      </c>
+      <c r="G142" s="30" t="inlineStr">
+        <is>
+          <t>خريطة اتجاه الرياح السائد لشهر مارس (°)</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="24" customHeight="1">
+      <c r="A143" s="3" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" s="5" t="inlineStr">
+        <is>
+          <t>WDr_AprMn</t>
+        </is>
+      </c>
+      <c r="C143" s="31" t="inlineStr">
+        <is>
+          <t>W_Dir_April_Mean</t>
+        </is>
+      </c>
+      <c r="D143" s="15" t="inlineStr">
+        <is>
+          <t>05_Wind (الرياح)</t>
+        </is>
+      </c>
+      <c r="E143" s="7" t="inlineStr">
+        <is>
+          <t>متوسط اتجاه الرياح السائد لشهر أبريل محسوب بالمتوسط الدائري المتجهي (atan2).</t>
+        </is>
+      </c>
+      <c r="F143" s="16" t="inlineStr">
+        <is>
+          <t>درجة (°) / Degree</t>
+        </is>
+      </c>
+      <c r="G143" s="32" t="inlineStr">
+        <is>
+          <t>خريطة اتجاه الرياح السائد لشهر أبريل (°)</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="24" customHeight="1">
+      <c r="A144" s="8" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" s="10" t="inlineStr">
+        <is>
+          <t>WDr_MayMn</t>
+        </is>
+      </c>
+      <c r="C144" s="29" t="inlineStr">
+        <is>
+          <t>W_Dir_May_Mean</t>
+        </is>
+      </c>
+      <c r="D144" s="18" t="inlineStr">
+        <is>
+          <t>05_Wind (الرياح)</t>
+        </is>
+      </c>
+      <c r="E144" s="12" t="inlineStr">
+        <is>
+          <t>متوسط اتجاه الرياح السائد لشهر مايو محسوب بالمتوسط الدائري المتجهي (atan2).</t>
+        </is>
+      </c>
+      <c r="F144" s="19" t="inlineStr">
+        <is>
+          <t>درجة (°) / Degree</t>
+        </is>
+      </c>
+      <c r="G144" s="30" t="inlineStr">
+        <is>
+          <t>خريطة اتجاه الرياح السائد لشهر مايو (°)</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="24" customHeight="1">
+      <c r="A145" s="3" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" s="5" t="inlineStr">
+        <is>
+          <t>WDr_JunMn</t>
+        </is>
+      </c>
+      <c r="C145" s="31" t="inlineStr">
+        <is>
+          <t>W_Dir_June_Mean</t>
+        </is>
+      </c>
+      <c r="D145" s="15" t="inlineStr">
+        <is>
+          <t>05_Wind (الرياح)</t>
+        </is>
+      </c>
+      <c r="E145" s="7" t="inlineStr">
+        <is>
+          <t>متوسط اتجاه الرياح السائد لشهر يونيو محسوب بالمتوسط الدائري المتجهي (atan2).</t>
+        </is>
+      </c>
+      <c r="F145" s="16" t="inlineStr">
+        <is>
+          <t>درجة (°) / Degree</t>
+        </is>
+      </c>
+      <c r="G145" s="32" t="inlineStr">
+        <is>
+          <t>خريطة اتجاه الرياح السائد لشهر يونيو (°)</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="24" customHeight="1">
+      <c r="A146" s="8" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" s="10" t="inlineStr">
+        <is>
+          <t>WDr_JulMn</t>
+        </is>
+      </c>
+      <c r="C146" s="29" t="inlineStr">
+        <is>
+          <t>W_Dir_July_Mean</t>
+        </is>
+      </c>
+      <c r="D146" s="18" t="inlineStr">
+        <is>
+          <t>05_Wind (الرياح)</t>
+        </is>
+      </c>
+      <c r="E146" s="12" t="inlineStr">
+        <is>
+          <t>متوسط اتجاه الرياح السائد لشهر يوليو محسوب بالمتوسط الدائري المتجهي (atan2).</t>
+        </is>
+      </c>
+      <c r="F146" s="19" t="inlineStr">
+        <is>
+          <t>درجة (°) / Degree</t>
+        </is>
+      </c>
+      <c r="G146" s="30" t="inlineStr">
+        <is>
+          <t>خريطة اتجاه الرياح السائد لشهر يوليو (°)</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="24" customHeight="1">
+      <c r="A147" s="3" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" s="5" t="inlineStr">
+        <is>
+          <t>WDr_AugMn</t>
+        </is>
+      </c>
+      <c r="C147" s="31" t="inlineStr">
+        <is>
+          <t>W_Dir_August_Mean</t>
+        </is>
+      </c>
+      <c r="D147" s="15" t="inlineStr">
+        <is>
+          <t>05_Wind (الرياح)</t>
+        </is>
+      </c>
+      <c r="E147" s="7" t="inlineStr">
+        <is>
+          <t>متوسط اتجاه الرياح السائد لشهر أغسطس محسوب بالمتوسط الدائري المتجهي (atan2).</t>
+        </is>
+      </c>
+      <c r="F147" s="16" t="inlineStr">
+        <is>
+          <t>درجة (°) / Degree</t>
+        </is>
+      </c>
+      <c r="G147" s="32" t="inlineStr">
+        <is>
+          <t>خريطة اتجاه الرياح السائد لشهر أغسطس (°)</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="24" customHeight="1">
+      <c r="A148" s="8" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" s="10" t="inlineStr">
+        <is>
+          <t>WDr_SepMn</t>
+        </is>
+      </c>
+      <c r="C148" s="29" t="inlineStr">
+        <is>
+          <t>W_Dir_September_Mean</t>
+        </is>
+      </c>
+      <c r="D148" s="18" t="inlineStr">
+        <is>
+          <t>05_Wind (الرياح)</t>
+        </is>
+      </c>
+      <c r="E148" s="12" t="inlineStr">
+        <is>
+          <t>متوسط اتجاه الرياح السائد لشهر سبتمبر محسوب بالمتوسط الدائري المتجهي (atan2).</t>
+        </is>
+      </c>
+      <c r="F148" s="19" t="inlineStr">
+        <is>
+          <t>درجة (°) / Degree</t>
+        </is>
+      </c>
+      <c r="G148" s="30" t="inlineStr">
+        <is>
+          <t>خريطة اتجاه الرياح السائد لشهر سبتمبر (°)</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="24" customHeight="1">
+      <c r="A149" s="3" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" s="5" t="inlineStr">
+        <is>
+          <t>WDr_OctMn</t>
+        </is>
+      </c>
+      <c r="C149" s="31" t="inlineStr">
+        <is>
+          <t>W_Dir_October_Mean</t>
+        </is>
+      </c>
+      <c r="D149" s="15" t="inlineStr">
+        <is>
+          <t>05_Wind (الرياح)</t>
+        </is>
+      </c>
+      <c r="E149" s="7" t="inlineStr">
+        <is>
+          <t>متوسط اتجاه الرياح السائد لشهر أكتوبر محسوب بالمتوسط الدائري المتجهي (atan2).</t>
+        </is>
+      </c>
+      <c r="F149" s="16" t="inlineStr">
+        <is>
+          <t>درجة (°) / Degree</t>
+        </is>
+      </c>
+      <c r="G149" s="32" t="inlineStr">
+        <is>
+          <t>خريطة اتجاه الرياح السائد لشهر أكتوبر (°)</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="24" customHeight="1">
+      <c r="A150" s="8" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" s="10" t="inlineStr">
+        <is>
+          <t>WDr_NovMn</t>
+        </is>
+      </c>
+      <c r="C150" s="29" t="inlineStr">
+        <is>
+          <t>W_Dir_November_Mean</t>
+        </is>
+      </c>
+      <c r="D150" s="18" t="inlineStr">
+        <is>
+          <t>05_Wind (الرياح)</t>
+        </is>
+      </c>
+      <c r="E150" s="12" t="inlineStr">
+        <is>
+          <t>متوسط اتجاه الرياح السائد لشهر نوفمبر محسوب بالمتوسط الدائري المتجهي (atan2).</t>
+        </is>
+      </c>
+      <c r="F150" s="19" t="inlineStr">
+        <is>
+          <t>درجة (°) / Degree</t>
+        </is>
+      </c>
+      <c r="G150" s="30" t="inlineStr">
+        <is>
+          <t>خريطة اتجاه الرياح السائد لشهر نوفمبر (°)</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="24" customHeight="1">
+      <c r="A151" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" s="5" t="inlineStr">
+        <is>
+          <t>WDr_DecMn</t>
+        </is>
+      </c>
+      <c r="C151" s="31" t="inlineStr">
+        <is>
+          <t>W_Dir_December_Mean</t>
+        </is>
+      </c>
+      <c r="D151" s="15" t="inlineStr">
+        <is>
+          <t>05_Wind (الرياح)</t>
+        </is>
+      </c>
+      <c r="E151" s="7" t="inlineStr">
+        <is>
+          <t>متوسط اتجاه الرياح السائد لشهر ديسمبر محسوب بالمتوسط الدائري المتجهي (atan2).</t>
+        </is>
+      </c>
+      <c r="F151" s="16" t="inlineStr">
+        <is>
+          <t>درجة (°) / Degree</t>
+        </is>
+      </c>
+      <c r="G151" s="32" t="inlineStr">
+        <is>
+          <t>خريطة اتجاه الرياح السائد لشهر ديسمبر (°)</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="24" customHeight="1">
+      <c r="A152" s="8" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" s="10" t="inlineStr">
+        <is>
+          <t>RH_AnMean</t>
+        </is>
+      </c>
+      <c r="C152" s="29" t="inlineStr">
+        <is>
+          <t>RH_Annual_Mean</t>
+        </is>
+      </c>
+      <c r="D152" s="18" t="inlineStr">
+        <is>
+          <t>06_Relative_Humidity (الرطوبة النسبية)</t>
+        </is>
+      </c>
+      <c r="E152" s="12" t="inlineStr">
+        <is>
+          <t>المتوسط الحسابي السنوي للرطوبة النسبية للهواء عند ارتفاع 2 متر كنسبة مئوية.</t>
+        </is>
+      </c>
+      <c r="F152" s="19" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="G152" s="30" t="inlineStr">
+        <is>
+          <t>خريطة المتوسط السنوي للرطوبة النسبية (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="24" customHeight="1">
+      <c r="A153" s="3" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" s="5" t="inlineStr">
+        <is>
+          <t>RH_WnMean</t>
+        </is>
+      </c>
+      <c r="C153" s="31" t="inlineStr">
+        <is>
+          <t>RH_Winter_Mean</t>
+        </is>
+      </c>
+      <c r="D153" s="15" t="inlineStr">
+        <is>
+          <t>06_Relative_Humidity (الرطوبة النسبية)</t>
+        </is>
+      </c>
+      <c r="E153" s="7" t="inlineStr">
+        <is>
+          <t>متوسط الرطوبة النسبية لفصل الشتاء الأرصادي (DJF).</t>
+        </is>
+      </c>
+      <c r="F153" s="16" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="G153" s="32" t="inlineStr">
+        <is>
+          <t>خريطة متوسط الرطوبة النسبية خلال فصل الشتاء (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="24" customHeight="1">
+      <c r="A154" s="8" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" s="10" t="inlineStr">
+        <is>
+          <t>RH_SpMean</t>
+        </is>
+      </c>
+      <c r="C154" s="29" t="inlineStr">
+        <is>
+          <t>RH_Spring_Mean</t>
+        </is>
+      </c>
+      <c r="D154" s="18" t="inlineStr">
+        <is>
+          <t>06_Relative_Humidity (الرطوبة النسبية)</t>
+        </is>
+      </c>
+      <c r="E154" s="12" t="inlineStr">
+        <is>
+          <t>متوسط الرطوبة النسبية لفصل الربيع الأرصادي (MAM).</t>
+        </is>
+      </c>
+      <c r="F154" s="19" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="G154" s="30" t="inlineStr">
+        <is>
+          <t>خريطة متوسط الرطوبة النسبية خلال فصل الربيع (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="24" customHeight="1">
+      <c r="A155" s="3" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" s="5" t="inlineStr">
+        <is>
+          <t>RH_SuMean</t>
+        </is>
+      </c>
+      <c r="C155" s="31" t="inlineStr">
+        <is>
+          <t>RH_Summer_Mean</t>
+        </is>
+      </c>
+      <c r="D155" s="15" t="inlineStr">
+        <is>
+          <t>06_Relative_Humidity (الرطوبة النسبية)</t>
+        </is>
+      </c>
+      <c r="E155" s="7" t="inlineStr">
+        <is>
+          <t>متوسط الرطوبة النسبية لفصل الصيف الأرصادي (JJA).</t>
+        </is>
+      </c>
+      <c r="F155" s="16" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="G155" s="32" t="inlineStr">
+        <is>
+          <t>خريطة متوسط الرطوبة النسبية خلال فصل الصيف (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="24" customHeight="1">
+      <c r="A156" s="8" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" s="10" t="inlineStr">
+        <is>
+          <t>RH_AuMean</t>
+        </is>
+      </c>
+      <c r="C156" s="29" t="inlineStr">
+        <is>
+          <t>RH_Autumn_Mean</t>
+        </is>
+      </c>
+      <c r="D156" s="18" t="inlineStr">
+        <is>
+          <t>06_Relative_Humidity (الرطوبة النسبية)</t>
+        </is>
+      </c>
+      <c r="E156" s="12" t="inlineStr">
+        <is>
+          <t>متوسط الرطوبة النسبية لفصل الخريف الأرصادي (SON).</t>
+        </is>
+      </c>
+      <c r="F156" s="19" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="G156" s="30" t="inlineStr">
+        <is>
+          <t>خريطة متوسط الرطوبة النسبية خلال فصل الخريف (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="24" customHeight="1">
+      <c r="A157" s="3" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" s="5" t="inlineStr">
+        <is>
+          <t>RH_AnRng</t>
+        </is>
+      </c>
+      <c r="C157" s="31" t="inlineStr">
+        <is>
+          <t>RH_Annual_Range</t>
+        </is>
+      </c>
+      <c r="D157" s="15" t="inlineStr">
+        <is>
+          <t>06_Relative_Humidity (الرطوبة النسبية)</t>
+        </is>
+      </c>
+      <c r="E157" s="7" t="inlineStr">
+        <is>
+          <t>المدى السنوي للرطوبة النسبية (الفارق بين أعلى شهر رطوبة وأدنى شهر رطوبة).</t>
+        </is>
+      </c>
+      <c r="F157" s="16" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="G157" s="32" t="inlineStr">
+        <is>
+          <t>خريطة المدى السنوي للرطوبة النسبية (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="24" customHeight="1">
+      <c r="A158" s="8" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" s="10" t="inlineStr">
+        <is>
+          <t>RH_JanMean</t>
+        </is>
+      </c>
+      <c r="C158" s="29" t="inlineStr">
+        <is>
+          <t>RH_January_Mean</t>
+        </is>
+      </c>
+      <c r="D158" s="18" t="inlineStr">
+        <is>
+          <t>06_Relative_Humidity (الرطوبة النسبية)</t>
+        </is>
+      </c>
+      <c r="E158" s="12" t="inlineStr">
+        <is>
+          <t>متوسط الرطوبة النسبية عند ارتفاع 2 متر لشهر يناير عبر فترة الرصد.</t>
+        </is>
+      </c>
+      <c r="F158" s="19" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="G158" s="30" t="inlineStr">
+        <is>
+          <t>خريطة متوسط الرطوبة النسبية لشهر يناير (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="24" customHeight="1">
+      <c r="A159" s="3" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" s="5" t="inlineStr">
+        <is>
+          <t>RH_FebMean</t>
+        </is>
+      </c>
+      <c r="C159" s="31" t="inlineStr">
+        <is>
+          <t>RH_February_Mean</t>
+        </is>
+      </c>
+      <c r="D159" s="15" t="inlineStr">
+        <is>
+          <t>06_Relative_Humidity (الرطوبة النسبية)</t>
+        </is>
+      </c>
+      <c r="E159" s="7" t="inlineStr">
+        <is>
+          <t>متوسط الرطوبة النسبية عند ارتفاع 2 متر لشهر فبراير عبر فترة الرصد.</t>
+        </is>
+      </c>
+      <c r="F159" s="16" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="G159" s="32" t="inlineStr">
+        <is>
+          <t>خريطة متوسط الرطوبة النسبية لشهر فبراير (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="24" customHeight="1">
+      <c r="A160" s="8" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" s="10" t="inlineStr">
+        <is>
+          <t>RH_MarMean</t>
+        </is>
+      </c>
+      <c r="C160" s="29" t="inlineStr">
+        <is>
+          <t>RH_March_Mean</t>
+        </is>
+      </c>
+      <c r="D160" s="18" t="inlineStr">
+        <is>
+          <t>06_Relative_Humidity (الرطوبة النسبية)</t>
+        </is>
+      </c>
+      <c r="E160" s="12" t="inlineStr">
+        <is>
+          <t>متوسط الرطوبة النسبية عند ارتفاع 2 متر لشهر مارس عبر فترة الرصد.</t>
+        </is>
+      </c>
+      <c r="F160" s="19" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="G160" s="30" t="inlineStr">
+        <is>
+          <t>خريطة متوسط الرطوبة النسبية لشهر مارس (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="24" customHeight="1">
+      <c r="A161" s="3" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" s="5" t="inlineStr">
+        <is>
+          <t>RH_AprMean</t>
+        </is>
+      </c>
+      <c r="C161" s="31" t="inlineStr">
+        <is>
+          <t>RH_April_Mean</t>
+        </is>
+      </c>
+      <c r="D161" s="15" t="inlineStr">
+        <is>
+          <t>06_Relative_Humidity (الرطوبة النسبية)</t>
+        </is>
+      </c>
+      <c r="E161" s="7" t="inlineStr">
+        <is>
+          <t>متوسط الرطوبة النسبية عند ارتفاع 2 متر لشهر أبريل عبر فترة الرصد.</t>
+        </is>
+      </c>
+      <c r="F161" s="16" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="G161" s="32" t="inlineStr">
+        <is>
+          <t>خريطة متوسط الرطوبة النسبية لشهر أبريل (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="24" customHeight="1">
+      <c r="A162" s="8" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" s="10" t="inlineStr">
+        <is>
+          <t>RH_MayMean</t>
+        </is>
+      </c>
+      <c r="C162" s="29" t="inlineStr">
+        <is>
+          <t>RH_May_Mean</t>
+        </is>
+      </c>
+      <c r="D162" s="18" t="inlineStr">
+        <is>
+          <t>06_Relative_Humidity (الرطوبة النسبية)</t>
+        </is>
+      </c>
+      <c r="E162" s="12" t="inlineStr">
+        <is>
+          <t>متوسط الرطوبة النسبية عند ارتفاع 2 متر لشهر مايو عبر فترة الرصد.</t>
+        </is>
+      </c>
+      <c r="F162" s="19" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="G162" s="30" t="inlineStr">
+        <is>
+          <t>خريطة متوسط الرطوبة النسبية لشهر مايو (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="24" customHeight="1">
+      <c r="A163" s="3" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" s="5" t="inlineStr">
+        <is>
+          <t>RH_JunMean</t>
+        </is>
+      </c>
+      <c r="C163" s="31" t="inlineStr">
+        <is>
+          <t>RH_June_Mean</t>
+        </is>
+      </c>
+      <c r="D163" s="15" t="inlineStr">
+        <is>
+          <t>06_Relative_Humidity (الرطوبة النسبية)</t>
+        </is>
+      </c>
+      <c r="E163" s="7" t="inlineStr">
+        <is>
+          <t>متوسط الرطوبة النسبية عند ارتفاع 2 متر لشهر يونيو عبر فترة الرصد.</t>
+        </is>
+      </c>
+      <c r="F163" s="16" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="G163" s="32" t="inlineStr">
+        <is>
+          <t>خريطة متوسط الرطوبة النسبية لشهر يونيو (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="24" customHeight="1">
+      <c r="A164" s="8" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" s="10" t="inlineStr">
+        <is>
+          <t>RH_JulMean</t>
+        </is>
+      </c>
+      <c r="C164" s="29" t="inlineStr">
+        <is>
+          <t>RH_July_Mean</t>
+        </is>
+      </c>
+      <c r="D164" s="18" t="inlineStr">
+        <is>
+          <t>06_Relative_Humidity (الرطوبة النسبية)</t>
+        </is>
+      </c>
+      <c r="E164" s="12" t="inlineStr">
+        <is>
+          <t>متوسط الرطوبة النسبية عند ارتفاع 2 متر لشهر يوليو عبر فترة الرصد.</t>
+        </is>
+      </c>
+      <c r="F164" s="19" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="G164" s="30" t="inlineStr">
+        <is>
+          <t>خريطة متوسط الرطوبة النسبية لشهر يوليو (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="24" customHeight="1">
+      <c r="A165" s="3" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" s="5" t="inlineStr">
+        <is>
+          <t>RH_AugMean</t>
+        </is>
+      </c>
+      <c r="C165" s="31" t="inlineStr">
+        <is>
+          <t>RH_August_Mean</t>
+        </is>
+      </c>
+      <c r="D165" s="15" t="inlineStr">
+        <is>
+          <t>06_Relative_Humidity (الرطوبة النسبية)</t>
+        </is>
+      </c>
+      <c r="E165" s="7" t="inlineStr">
+        <is>
+          <t>متوسط الرطوبة النسبية عند ارتفاع 2 متر لشهر أغسطس عبر فترة الرصد.</t>
+        </is>
+      </c>
+      <c r="F165" s="16" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="G165" s="32" t="inlineStr">
+        <is>
+          <t>خريطة متوسط الرطوبة النسبية لشهر أغسطس (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="24" customHeight="1">
+      <c r="A166" s="8" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" s="10" t="inlineStr">
+        <is>
+          <t>RH_SepMean</t>
+        </is>
+      </c>
+      <c r="C166" s="29" t="inlineStr">
+        <is>
+          <t>RH_September_Mean</t>
+        </is>
+      </c>
+      <c r="D166" s="18" t="inlineStr">
+        <is>
+          <t>06_Relative_Humidity (الرطوبة النسبية)</t>
+        </is>
+      </c>
+      <c r="E166" s="12" t="inlineStr">
+        <is>
+          <t>متوسط الرطوبة النسبية عند ارتفاع 2 متر لشهر سبتمبر عبر فترة الرصد.</t>
+        </is>
+      </c>
+      <c r="F166" s="19" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="G166" s="30" t="inlineStr">
+        <is>
+          <t>خريطة متوسط الرطوبة النسبية لشهر سبتمبر (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="24" customHeight="1">
+      <c r="A167" s="3" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" s="5" t="inlineStr">
+        <is>
+          <t>RH_OctMean</t>
+        </is>
+      </c>
+      <c r="C167" s="31" t="inlineStr">
+        <is>
+          <t>RH_October_Mean</t>
+        </is>
+      </c>
+      <c r="D167" s="15" t="inlineStr">
+        <is>
+          <t>06_Relative_Humidity (الرطوبة النسبية)</t>
+        </is>
+      </c>
+      <c r="E167" s="7" t="inlineStr">
+        <is>
+          <t>متوسط الرطوبة النسبية عند ارتفاع 2 متر لشهر أكتوبر عبر فترة الرصد.</t>
+        </is>
+      </c>
+      <c r="F167" s="16" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="G167" s="32" t="inlineStr">
+        <is>
+          <t>خريطة متوسط الرطوبة النسبية لشهر أكتوبر (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="24" customHeight="1">
+      <c r="A168" s="8" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" s="10" t="inlineStr">
+        <is>
+          <t>RH_NovMean</t>
+        </is>
+      </c>
+      <c r="C168" s="29" t="inlineStr">
+        <is>
+          <t>RH_November_Mean</t>
+        </is>
+      </c>
+      <c r="D168" s="18" t="inlineStr">
+        <is>
+          <t>06_Relative_Humidity (الرطوبة النسبية)</t>
+        </is>
+      </c>
+      <c r="E168" s="12" t="inlineStr">
+        <is>
+          <t>متوسط الرطوبة النسبية عند ارتفاع 2 متر لشهر نوفمبر عبر فترة الرصد.</t>
+        </is>
+      </c>
+      <c r="F168" s="19" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="G168" s="30" t="inlineStr">
+        <is>
+          <t>خريطة متوسط الرطوبة النسبية لشهر نوفمبر (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="24" customHeight="1">
+      <c r="A169" s="3" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" s="5" t="inlineStr">
+        <is>
+          <t>RH_DecMean</t>
+        </is>
+      </c>
+      <c r="C169" s="31" t="inlineStr">
+        <is>
+          <t>RH_December_Mean</t>
+        </is>
+      </c>
+      <c r="D169" s="15" t="inlineStr">
+        <is>
+          <t>06_Relative_Humidity (الرطوبة النسبية)</t>
+        </is>
+      </c>
+      <c r="E169" s="7" t="inlineStr">
+        <is>
+          <t>متوسط الرطوبة النسبية عند ارتفاع 2 متر لشهر ديسمبر عبر فترة الرصد.</t>
+        </is>
+      </c>
+      <c r="F169" s="16" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="G169" s="32" t="inlineStr">
+        <is>
+          <t>خريطة متوسط الرطوبة النسبية لشهر ديسمبر (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="24" customHeight="1">
+      <c r="A170" s="8" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" s="10" t="inlineStr">
+        <is>
+          <t>Sol_AnMean</t>
+        </is>
+      </c>
+      <c r="C170" s="29" t="inlineStr">
+        <is>
+          <t>Sol_Annual_Mean</t>
+        </is>
+      </c>
+      <c r="D170" s="18" t="inlineStr">
+        <is>
+          <t>08_Solar_Radiation (الإشعاع الشمسي)</t>
+        </is>
+      </c>
+      <c r="E170" s="12" t="inlineStr">
+        <is>
+          <t>المتوسط اليومي السنوي للإشعاع الشمسي الكلي السطحي الواصل لسطح الأرض في كافة ظروف السماء.</t>
+        </is>
+      </c>
+      <c r="F170" s="19" t="inlineStr">
+        <is>
+          <t>kWh/m²/day</t>
+        </is>
+      </c>
+      <c r="G170" s="30" t="inlineStr">
+        <is>
+          <t>خريطة المتوسط اليومي السنوي للإشعاع الشمسي (kWh/m²/day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="24" customHeight="1">
+      <c r="A171" s="3" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" s="5" t="inlineStr">
+        <is>
+          <t>Sol_AnTot</t>
+        </is>
+      </c>
+      <c r="C171" s="31" t="inlineStr">
+        <is>
+          <t>Sol_Annual_Total</t>
+        </is>
+      </c>
+      <c r="D171" s="15" t="inlineStr">
+        <is>
+          <t>08_Solar_Radiation (الإشعاع الشمسي)</t>
+        </is>
+      </c>
+      <c r="E171" s="7" t="inlineStr">
+        <is>
+          <t>إجمالي الطاقة الشمسية السنوية التراكمية الساقطة على المتر المربع في السنة كاملة.</t>
+        </is>
+      </c>
+      <c r="F171" s="16" t="inlineStr">
+        <is>
+          <t>kWh/m²/year</t>
+        </is>
+      </c>
+      <c r="G171" s="32" t="inlineStr">
+        <is>
+          <t>خريطة إجمالي الطاقة الشمسية السنوية التراكمية (kWh/m²/year)</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="24" customHeight="1">
+      <c r="A172" s="8" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" s="10" t="inlineStr">
+        <is>
+          <t>Sol_WnMean</t>
+        </is>
+      </c>
+      <c r="C172" s="29" t="inlineStr">
+        <is>
+          <t>Sol_Winter_Mean</t>
+        </is>
+      </c>
+      <c r="D172" s="18" t="inlineStr">
+        <is>
+          <t>08_Solar_Radiation (الإشعاع الشمسي)</t>
+        </is>
+      </c>
+      <c r="E172" s="12" t="inlineStr">
+        <is>
+          <t>متوسط الإشعاع الشمسي اليومي لفصل الشتاء الأرصادي (DJF).</t>
+        </is>
+      </c>
+      <c r="F172" s="19" t="inlineStr">
+        <is>
+          <t>kWh/m²/day</t>
+        </is>
+      </c>
+      <c r="G172" s="30" t="inlineStr">
+        <is>
+          <t>خريطة متوسط الإشعاع الشمسي خلال فصل الشتاء (kWh/m²/day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="24" customHeight="1">
+      <c r="A173" s="3" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" s="5" t="inlineStr">
+        <is>
+          <t>Sol_SpMean</t>
+        </is>
+      </c>
+      <c r="C173" s="31" t="inlineStr">
+        <is>
+          <t>Sol_Spring_Mean</t>
+        </is>
+      </c>
+      <c r="D173" s="15" t="inlineStr">
+        <is>
+          <t>08_Solar_Radiation (الإشعاع الشمسي)</t>
+        </is>
+      </c>
+      <c r="E173" s="7" t="inlineStr">
+        <is>
+          <t>متوسط الإشعاع الشمسي اليومي لفصل الربيع الأرصادي (MAM).</t>
+        </is>
+      </c>
+      <c r="F173" s="16" t="inlineStr">
+        <is>
+          <t>kWh/m²/day</t>
+        </is>
+      </c>
+      <c r="G173" s="32" t="inlineStr">
+        <is>
+          <t>خريطة متوسط الإشعاع الشمسي خلال فصل الربيع (kWh/m²/day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="24" customHeight="1">
+      <c r="A174" s="8" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" s="10" t="inlineStr">
+        <is>
+          <t>Sol_SuMean</t>
+        </is>
+      </c>
+      <c r="C174" s="29" t="inlineStr">
+        <is>
+          <t>Sol_Summer_Mean</t>
+        </is>
+      </c>
+      <c r="D174" s="18" t="inlineStr">
+        <is>
+          <t>08_Solar_Radiation (الإشعاع الشمسي)</t>
+        </is>
+      </c>
+      <c r="E174" s="12" t="inlineStr">
+        <is>
+          <t>متوسط الإشعاع الشمسي اليومي لفصل الصيف الأرصادي (JJA).</t>
+        </is>
+      </c>
+      <c r="F174" s="19" t="inlineStr">
+        <is>
+          <t>kWh/m²/day</t>
+        </is>
+      </c>
+      <c r="G174" s="30" t="inlineStr">
+        <is>
+          <t>خريطة متوسط الإشعاع الشمسي خلال فصل الصيف (kWh/m²/day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="24" customHeight="1">
+      <c r="A175" s="3" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" s="5" t="inlineStr">
+        <is>
+          <t>Sol_AuMean</t>
+        </is>
+      </c>
+      <c r="C175" s="31" t="inlineStr">
+        <is>
+          <t>Sol_Autumn_Mean</t>
+        </is>
+      </c>
+      <c r="D175" s="15" t="inlineStr">
+        <is>
+          <t>08_Solar_Radiation (الإشعاع الشمسي)</t>
+        </is>
+      </c>
+      <c r="E175" s="7" t="inlineStr">
+        <is>
+          <t>متوسط الإشعاع الشمسي اليومي لفصل الخريف الأرصادي (SON).</t>
+        </is>
+      </c>
+      <c r="F175" s="16" t="inlineStr">
+        <is>
+          <t>kWh/m²/day</t>
+        </is>
+      </c>
+      <c r="G175" s="32" t="inlineStr">
+        <is>
+          <t>خريطة متوسط الإشعاع الشمسي خلال فصل الخريف (kWh/m²/day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="24" customHeight="1">
+      <c r="A176" s="8" t="n">
+        <v>175</v>
+      </c>
+      <c r="B176" s="10" t="inlineStr">
+        <is>
+          <t>Sol_AnRng</t>
+        </is>
+      </c>
+      <c r="C176" s="29" t="inlineStr">
+        <is>
+          <t>Sol_Annual_Range</t>
+        </is>
+      </c>
+      <c r="D176" s="18" t="inlineStr">
+        <is>
+          <t>08_Solar_Radiation (الإشعاع الشمسي)</t>
+        </is>
+      </c>
+      <c r="E176" s="12" t="inlineStr">
+        <is>
+          <t>المدى السنوي للإشعاع الشمسي (الفارق بين ذروة الإشعاع في الصيف وأدناه في الشتاء).</t>
+        </is>
+      </c>
+      <c r="F176" s="19" t="inlineStr">
+        <is>
+          <t>kWh/m²/day</t>
+        </is>
+      </c>
+      <c r="G176" s="30" t="inlineStr">
+        <is>
+          <t>خريطة المدى السنوي للإشعاع الشمسي (kWh/m²/day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="24" customHeight="1">
+      <c r="A177" s="3" t="n">
+        <v>176</v>
+      </c>
+      <c r="B177" s="5" t="inlineStr">
+        <is>
+          <t>Sol_JanMn</t>
+        </is>
+      </c>
+      <c r="C177" s="31" t="inlineStr">
+        <is>
+          <t>Sol_January_Mean</t>
+        </is>
+      </c>
+      <c r="D177" s="15" t="inlineStr">
+        <is>
+          <t>08_Solar_Radiation (الإشعاع الشمسي)</t>
+        </is>
+      </c>
+      <c r="E177" s="7" t="inlineStr">
+        <is>
+          <t>المعدل اليومي للإشعاع الشمسي الكلي الساقط على السطح الأفقي لشهر يناير.</t>
+        </is>
+      </c>
+      <c r="F177" s="16" t="inlineStr">
+        <is>
+          <t>kWh/m²/day</t>
+        </is>
+      </c>
+      <c r="G177" s="32" t="inlineStr">
+        <is>
+          <t>خريطة المعدل اليومي للإشعاع الشمسي لشهر يناير (kWh/m²/day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="24" customHeight="1">
+      <c r="A178" s="8" t="n">
+        <v>177</v>
+      </c>
+      <c r="B178" s="10" t="inlineStr">
+        <is>
+          <t>Sol_FebMn</t>
+        </is>
+      </c>
+      <c r="C178" s="29" t="inlineStr">
+        <is>
+          <t>Sol_February_Mean</t>
+        </is>
+      </c>
+      <c r="D178" s="18" t="inlineStr">
+        <is>
+          <t>08_Solar_Radiation (الإشعاع الشمسي)</t>
+        </is>
+      </c>
+      <c r="E178" s="12" t="inlineStr">
+        <is>
+          <t>المعدل اليومي للإشعاع الشمسي الكلي الساقط على السطح الأفقي لشهر فبراير.</t>
+        </is>
+      </c>
+      <c r="F178" s="19" t="inlineStr">
+        <is>
+          <t>kWh/m²/day</t>
+        </is>
+      </c>
+      <c r="G178" s="30" t="inlineStr">
+        <is>
+          <t>خريطة المعدل اليومي للإشعاع الشمسي لشهر فبراير (kWh/m²/day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="24" customHeight="1">
+      <c r="A179" s="3" t="n">
+        <v>178</v>
+      </c>
+      <c r="B179" s="5" t="inlineStr">
+        <is>
+          <t>Sol_MarMn</t>
+        </is>
+      </c>
+      <c r="C179" s="31" t="inlineStr">
+        <is>
+          <t>Sol_March_Mean</t>
+        </is>
+      </c>
+      <c r="D179" s="15" t="inlineStr">
+        <is>
+          <t>08_Solar_Radiation (الإشعاع الشمسي)</t>
+        </is>
+      </c>
+      <c r="E179" s="7" t="inlineStr">
+        <is>
+          <t>المعدل اليومي للإشعاع الشمسي الكلي الساقط على السطح الأفقي لشهر مارس.</t>
+        </is>
+      </c>
+      <c r="F179" s="16" t="inlineStr">
+        <is>
+          <t>kWh/m²/day</t>
+        </is>
+      </c>
+      <c r="G179" s="32" t="inlineStr">
+        <is>
+          <t>خريطة المعدل اليومي للإشعاع الشمسي لشهر مارس (kWh/m²/day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="24" customHeight="1">
+      <c r="A180" s="8" t="n">
+        <v>179</v>
+      </c>
+      <c r="B180" s="10" t="inlineStr">
+        <is>
+          <t>Sol_AprMn</t>
+        </is>
+      </c>
+      <c r="C180" s="29" t="inlineStr">
+        <is>
+          <t>Sol_April_Mean</t>
+        </is>
+      </c>
+      <c r="D180" s="18" t="inlineStr">
+        <is>
+          <t>08_Solar_Radiation (الإشعاع الشمسي)</t>
+        </is>
+      </c>
+      <c r="E180" s="12" t="inlineStr">
+        <is>
+          <t>المعدل اليومي للإشعاع الشمسي الكلي الساقط على السطح الأفقي لشهر أبريل.</t>
+        </is>
+      </c>
+      <c r="F180" s="19" t="inlineStr">
+        <is>
+          <t>kWh/m²/day</t>
+        </is>
+      </c>
+      <c r="G180" s="30" t="inlineStr">
+        <is>
+          <t>خريطة المعدل اليومي للإشعاع الشمسي لشهر أبريل (kWh/m²/day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="24" customHeight="1">
+      <c r="A181" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="B181" s="5" t="inlineStr">
+        <is>
+          <t>Sol_MayMn</t>
+        </is>
+      </c>
+      <c r="C181" s="31" t="inlineStr">
+        <is>
+          <t>Sol_May_Mean</t>
+        </is>
+      </c>
+      <c r="D181" s="15" t="inlineStr">
+        <is>
+          <t>08_Solar_Radiation (الإشعاع الشمسي)</t>
+        </is>
+      </c>
+      <c r="E181" s="7" t="inlineStr">
+        <is>
+          <t>المعدل اليومي للإشعاع الشمسي الكلي الساقط على السطح الأفقي لشهر مايو.</t>
+        </is>
+      </c>
+      <c r="F181" s="16" t="inlineStr">
+        <is>
+          <t>kWh/m²/day</t>
+        </is>
+      </c>
+      <c r="G181" s="32" t="inlineStr">
+        <is>
+          <t>خريطة المعدل اليومي للإشعاع الشمسي لشهر مايو (kWh/m²/day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="24" customHeight="1">
+      <c r="A182" s="8" t="n">
+        <v>181</v>
+      </c>
+      <c r="B182" s="10" t="inlineStr">
+        <is>
+          <t>Sol_JunMn</t>
+        </is>
+      </c>
+      <c r="C182" s="29" t="inlineStr">
+        <is>
+          <t>Sol_June_Mean</t>
+        </is>
+      </c>
+      <c r="D182" s="18" t="inlineStr">
+        <is>
+          <t>08_Solar_Radiation (الإشعاع الشمسي)</t>
+        </is>
+      </c>
+      <c r="E182" s="12" t="inlineStr">
+        <is>
+          <t>المعدل اليومي للإشعاع الشمسي الكلي الساقط على السطح الأفقي لشهر يونيو.</t>
+        </is>
+      </c>
+      <c r="F182" s="19" t="inlineStr">
+        <is>
+          <t>kWh/m²/day</t>
+        </is>
+      </c>
+      <c r="G182" s="30" t="inlineStr">
+        <is>
+          <t>خريطة المعدل اليومي للإشعاع الشمسي لشهر يونيو (kWh/m²/day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="24" customHeight="1">
+      <c r="A183" s="3" t="n">
+        <v>182</v>
+      </c>
+      <c r="B183" s="5" t="inlineStr">
+        <is>
+          <t>Sol_JulMn</t>
+        </is>
+      </c>
+      <c r="C183" s="31" t="inlineStr">
+        <is>
+          <t>Sol_July_Mean</t>
+        </is>
+      </c>
+      <c r="D183" s="15" t="inlineStr">
+        <is>
+          <t>08_Solar_Radiation (الإشعاع الشمسي)</t>
+        </is>
+      </c>
+      <c r="E183" s="7" t="inlineStr">
+        <is>
+          <t>المعدل اليومي للإشعاع الشمسي الكلي الساقط على السطح الأفقي لشهر يوليو.</t>
+        </is>
+      </c>
+      <c r="F183" s="16" t="inlineStr">
+        <is>
+          <t>kWh/m²/day</t>
+        </is>
+      </c>
+      <c r="G183" s="32" t="inlineStr">
+        <is>
+          <t>خريطة المعدل اليومي للإشعاع الشمسي لشهر يوليو (kWh/m²/day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="24" customHeight="1">
+      <c r="A184" s="8" t="n">
+        <v>183</v>
+      </c>
+      <c r="B184" s="10" t="inlineStr">
+        <is>
+          <t>Sol_AugMn</t>
+        </is>
+      </c>
+      <c r="C184" s="29" t="inlineStr">
+        <is>
+          <t>Sol_August_Mean</t>
+        </is>
+      </c>
+      <c r="D184" s="18" t="inlineStr">
+        <is>
+          <t>08_Solar_Radiation (الإشعاع الشمسي)</t>
+        </is>
+      </c>
+      <c r="E184" s="12" t="inlineStr">
+        <is>
+          <t>المعدل اليومي للإشعاع الشمسي الكلي الساقط على السطح الأفقي لشهر أغسطس.</t>
+        </is>
+      </c>
+      <c r="F184" s="19" t="inlineStr">
+        <is>
+          <t>kWh/m²/day</t>
+        </is>
+      </c>
+      <c r="G184" s="30" t="inlineStr">
+        <is>
+          <t>خريطة المعدل اليومي للإشعاع الشمسي لشهر أغسطس (kWh/m²/day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="24" customHeight="1">
+      <c r="A185" s="3" t="n">
+        <v>184</v>
+      </c>
+      <c r="B185" s="5" t="inlineStr">
+        <is>
+          <t>Sol_SepMn</t>
+        </is>
+      </c>
+      <c r="C185" s="31" t="inlineStr">
+        <is>
+          <t>Sol_September_Mean</t>
+        </is>
+      </c>
+      <c r="D185" s="15" t="inlineStr">
+        <is>
+          <t>08_Solar_Radiation (الإشعاع الشمسي)</t>
+        </is>
+      </c>
+      <c r="E185" s="7" t="inlineStr">
+        <is>
+          <t>المعدل اليومي للإشعاع الشمسي الكلي الساقط على السطح الأفقي لشهر سبتمبر.</t>
+        </is>
+      </c>
+      <c r="F185" s="16" t="inlineStr">
+        <is>
+          <t>kWh/m²/day</t>
+        </is>
+      </c>
+      <c r="G185" s="32" t="inlineStr">
+        <is>
+          <t>خريطة المعدل اليومي للإشعاع الشمسي لشهر سبتمبر (kWh/m²/day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="24" customHeight="1">
+      <c r="A186" s="8" t="n">
+        <v>185</v>
+      </c>
+      <c r="B186" s="10" t="inlineStr">
+        <is>
+          <t>Sol_OctMn</t>
+        </is>
+      </c>
+      <c r="C186" s="29" t="inlineStr">
+        <is>
+          <t>Sol_October_Mean</t>
+        </is>
+      </c>
+      <c r="D186" s="18" t="inlineStr">
+        <is>
+          <t>08_Solar_Radiation (الإشعاع الشمسي)</t>
+        </is>
+      </c>
+      <c r="E186" s="12" t="inlineStr">
+        <is>
+          <t>المعدل اليومي للإشعاع الشمسي الكلي الساقط على السطح الأفقي لشهر أكتوبر.</t>
+        </is>
+      </c>
+      <c r="F186" s="19" t="inlineStr">
+        <is>
+          <t>kWh/m²/day</t>
+        </is>
+      </c>
+      <c r="G186" s="30" t="inlineStr">
+        <is>
+          <t>خريطة المعدل اليومي للإشعاع الشمسي لشهر أكتوبر (kWh/m²/day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="24" customHeight="1">
+      <c r="A187" s="3" t="n">
+        <v>186</v>
+      </c>
+      <c r="B187" s="5" t="inlineStr">
+        <is>
+          <t>Sol_NovMn</t>
+        </is>
+      </c>
+      <c r="C187" s="31" t="inlineStr">
+        <is>
+          <t>Sol_November_Mean</t>
+        </is>
+      </c>
+      <c r="D187" s="15" t="inlineStr">
+        <is>
+          <t>08_Solar_Radiation (الإشعاع الشمسي)</t>
+        </is>
+      </c>
+      <c r="E187" s="7" t="inlineStr">
+        <is>
+          <t>المعدل اليومي للإشعاع الشمسي الكلي الساقط على السطح الأفقي لشهر نوفمبر.</t>
+        </is>
+      </c>
+      <c r="F187" s="16" t="inlineStr">
+        <is>
+          <t>kWh/m²/day</t>
+        </is>
+      </c>
+      <c r="G187" s="32" t="inlineStr">
+        <is>
+          <t>خريطة المعدل اليومي للإشعاع الشمسي لشهر نوفمبر (kWh/m²/day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="24" customHeight="1">
+      <c r="A188" s="8" t="n">
+        <v>187</v>
+      </c>
+      <c r="B188" s="10" t="inlineStr">
+        <is>
+          <t>Sol_DecMn</t>
+        </is>
+      </c>
+      <c r="C188" s="29" t="inlineStr">
+        <is>
+          <t>Sol_December_Mean</t>
+        </is>
+      </c>
+      <c r="D188" s="18" t="inlineStr">
+        <is>
+          <t>08_Solar_Radiation (الإشعاع الشمسي)</t>
+        </is>
+      </c>
+      <c r="E188" s="12" t="inlineStr">
+        <is>
+          <t>المعدل اليومي للإشعاع الشمسي الكلي الساقط على السطح الأفقي لشهر ديسمبر.</t>
+        </is>
+      </c>
+      <c r="F188" s="19" t="inlineStr">
+        <is>
+          <t>kWh/m²/day</t>
+        </is>
+      </c>
+      <c r="G188" s="30" t="inlineStr">
+        <is>
+          <t>خريطة المعدل اليومي للإشعاع الشمسي لشهر ديسمبر (kWh/m²/day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="24" customHeight="1">
+      <c r="A189" s="3" t="n">
+        <v>188</v>
+      </c>
+      <c r="B189" s="5" t="inlineStr">
+        <is>
+          <t>UV_AnMean</t>
+        </is>
+      </c>
+      <c r="C189" s="31" t="inlineStr">
+        <is>
+          <t>UV_Annual_Mean</t>
+        </is>
+      </c>
+      <c r="D189" s="15" t="inlineStr">
+        <is>
+          <t>09_UV_Index (الأشعة فوق البنفسجية)</t>
+        </is>
+      </c>
+      <c r="E189" s="7" t="inlineStr">
+        <is>
+          <t>المتوسط السنوي لمؤشر الأشعة فوق البنفسجية عند الظهيرة وفق منظومة منظمة الصحة العالمية.</t>
+        </is>
+      </c>
+      <c r="F189" s="16" t="inlineStr">
+        <is>
+          <t>مؤشر (0-16+)</t>
+        </is>
+      </c>
+      <c r="G189" s="32" t="inlineStr">
+        <is>
+          <t>خريطة المتوسط السنوي لمؤشر الأشعة فوق البنفسجية (UV)</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="24" customHeight="1">
+      <c r="A190" s="8" t="n">
+        <v>189</v>
+      </c>
+      <c r="B190" s="10" t="inlineStr">
+        <is>
+          <t>UV_WnMean</t>
+        </is>
+      </c>
+      <c r="C190" s="29" t="inlineStr">
+        <is>
+          <t>UV_Winter_Mean</t>
+        </is>
+      </c>
+      <c r="D190" s="18" t="inlineStr">
+        <is>
+          <t>09_UV_Index (الأشعة فوق البنفسجية)</t>
+        </is>
+      </c>
+      <c r="E190" s="12" t="inlineStr">
+        <is>
+          <t>متوسط مؤشر الأشعة فوق البنفسجية لفصل الشتاء الأرصادي (DJF).</t>
+        </is>
+      </c>
+      <c r="F190" s="19" t="inlineStr">
+        <is>
+          <t>مؤشر (0-16+)</t>
+        </is>
+      </c>
+      <c r="G190" s="30" t="inlineStr">
+        <is>
+          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية خلال فصل الشتاء</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="24" customHeight="1">
+      <c r="A191" s="3" t="n">
+        <v>190</v>
+      </c>
+      <c r="B191" s="5" t="inlineStr">
+        <is>
+          <t>UV_SpMean</t>
+        </is>
+      </c>
+      <c r="C191" s="31" t="inlineStr">
+        <is>
+          <t>UV_Spring_Mean</t>
+        </is>
+      </c>
+      <c r="D191" s="15" t="inlineStr">
+        <is>
+          <t>09_UV_Index (الأشعة فوق البنفسجية)</t>
+        </is>
+      </c>
+      <c r="E191" s="7" t="inlineStr">
+        <is>
+          <t>متوسط مؤشر الأشعة فوق البنفسجية لفصل الربيع الأرصادي (MAM).</t>
+        </is>
+      </c>
+      <c r="F191" s="16" t="inlineStr">
+        <is>
+          <t>مؤشر (0-16+)</t>
+        </is>
+      </c>
+      <c r="G191" s="32" t="inlineStr">
+        <is>
+          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية خلال فصل الربيع</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="24" customHeight="1">
+      <c r="A192" s="8" t="n">
+        <v>191</v>
+      </c>
+      <c r="B192" s="10" t="inlineStr">
+        <is>
+          <t>UV_SuMean</t>
+        </is>
+      </c>
+      <c r="C192" s="29" t="inlineStr">
+        <is>
+          <t>UV_Summer_Mean</t>
+        </is>
+      </c>
+      <c r="D192" s="18" t="inlineStr">
+        <is>
+          <t>09_UV_Index (الأشعة فوق البنفسجية)</t>
+        </is>
+      </c>
+      <c r="E192" s="12" t="inlineStr">
+        <is>
+          <t>متوسط مؤشر الأشعة فوق البنفسجية لفصل الصيف الأرصادي (JJA - ذروة مخاطر الحروق الشمسية).</t>
+        </is>
+      </c>
+      <c r="F192" s="19" t="inlineStr">
+        <is>
+          <t>مؤشر (0-16+)</t>
+        </is>
+      </c>
+      <c r="G192" s="30" t="inlineStr">
+        <is>
+          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية خلال فصل الصيف</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="24" customHeight="1">
+      <c r="A193" s="3" t="n">
+        <v>192</v>
+      </c>
+      <c r="B193" s="5" t="inlineStr">
+        <is>
+          <t>UV_AuMean</t>
+        </is>
+      </c>
+      <c r="C193" s="31" t="inlineStr">
+        <is>
+          <t>UV_Autumn_Mean</t>
+        </is>
+      </c>
+      <c r="D193" s="15" t="inlineStr">
+        <is>
+          <t>09_UV_Index (الأشعة فوق البنفسجية)</t>
+        </is>
+      </c>
+      <c r="E193" s="7" t="inlineStr">
+        <is>
+          <t>متوسط مؤشر الأشعة فوق البنفسجية لفصل الخريف الأرصادي (SON).</t>
+        </is>
+      </c>
+      <c r="F193" s="16" t="inlineStr">
+        <is>
+          <t>مؤشر (0-16+)</t>
+        </is>
+      </c>
+      <c r="G193" s="32" t="inlineStr">
+        <is>
+          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية خلال فصل الخريف</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="24" customHeight="1">
+      <c r="A194" s="8" t="n">
+        <v>193</v>
+      </c>
+      <c r="B194" s="10" t="inlineStr">
+        <is>
+          <t>UV_AnRng</t>
+        </is>
+      </c>
+      <c r="C194" s="29" t="inlineStr">
+        <is>
+          <t>UV_Annual_Range</t>
+        </is>
+      </c>
+      <c r="D194" s="18" t="inlineStr">
+        <is>
+          <t>09_UV_Index (الأشعة فوق البنفسجية)</t>
+        </is>
+      </c>
+      <c r="E194" s="12" t="inlineStr">
+        <is>
+          <t>المدى السنوي لمؤشر الأشعة فوق البنفسجية (الفارق بين ذروة الصيف وأدنى مستويات الشتاء).</t>
+        </is>
+      </c>
+      <c r="F194" s="19" t="inlineStr">
+        <is>
+          <t>مؤشر (0-16+)</t>
+        </is>
+      </c>
+      <c r="G194" s="30" t="inlineStr">
+        <is>
+          <t>خريطة المدى السنوي لمؤشر الأشعة فوق البنفسجية</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="24" customHeight="1">
+      <c r="A195" s="3" t="n">
+        <v>194</v>
+      </c>
+      <c r="B195" s="5" t="inlineStr">
+        <is>
+          <t>UV_JanMean</t>
+        </is>
+      </c>
+      <c r="C195" s="31" t="inlineStr">
+        <is>
+          <t>UV_January_Mean</t>
+        </is>
+      </c>
+      <c r="D195" s="15" t="inlineStr">
+        <is>
+          <t>09_UV_Index (الأشعة فوق البنفسجية)</t>
+        </is>
+      </c>
+      <c r="E195" s="7" t="inlineStr">
+        <is>
+          <t>متوسط مؤشر الأشعة فوق البنفسجية القصوى لشهر يناير وفق معيار WHO.</t>
+        </is>
+      </c>
+      <c r="F195" s="16" t="inlineStr">
+        <is>
+          <t>مؤشر (0-16+)</t>
+        </is>
+      </c>
+      <c r="G195" s="32" t="inlineStr">
+        <is>
+          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية لشهر يناير</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="24" customHeight="1">
+      <c r="A196" s="8" t="n">
+        <v>195</v>
+      </c>
+      <c r="B196" s="10" t="inlineStr">
+        <is>
+          <t>UV_FebMean</t>
+        </is>
+      </c>
+      <c r="C196" s="29" t="inlineStr">
+        <is>
+          <t>UV_February_Mean</t>
+        </is>
+      </c>
+      <c r="D196" s="18" t="inlineStr">
+        <is>
+          <t>09_UV_Index (الأشعة فوق البنفسجية)</t>
+        </is>
+      </c>
+      <c r="E196" s="12" t="inlineStr">
+        <is>
+          <t>متوسط مؤشر الأشعة فوق البنفسجية القصوى لشهر فبراير وفق معيار WHO.</t>
+        </is>
+      </c>
+      <c r="F196" s="19" t="inlineStr">
+        <is>
+          <t>مؤشر (0-16+)</t>
+        </is>
+      </c>
+      <c r="G196" s="30" t="inlineStr">
+        <is>
+          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية لشهر فبراير</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" ht="24" customHeight="1">
+      <c r="A197" s="3" t="n">
+        <v>196</v>
+      </c>
+      <c r="B197" s="5" t="inlineStr">
+        <is>
+          <t>UV_MarMean</t>
+        </is>
+      </c>
+      <c r="C197" s="31" t="inlineStr">
+        <is>
+          <t>UV_March_Mean</t>
+        </is>
+      </c>
+      <c r="D197" s="15" t="inlineStr">
+        <is>
+          <t>09_UV_Index (الأشعة فوق البنفسجية)</t>
+        </is>
+      </c>
+      <c r="E197" s="7" t="inlineStr">
+        <is>
+          <t>متوسط مؤشر الأشعة فوق البنفسجية القصوى لشهر مارس وفق معيار WHO.</t>
+        </is>
+      </c>
+      <c r="F197" s="16" t="inlineStr">
+        <is>
+          <t>مؤشر (0-16+)</t>
+        </is>
+      </c>
+      <c r="G197" s="32" t="inlineStr">
+        <is>
+          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية لشهر مارس</t>
+        </is>
+      </c>
+    </row>
+    <row r="198" ht="24" customHeight="1">
+      <c r="A198" s="8" t="n">
+        <v>197</v>
+      </c>
+      <c r="B198" s="10" t="inlineStr">
+        <is>
+          <t>UV_AprMean</t>
+        </is>
+      </c>
+      <c r="C198" s="29" t="inlineStr">
+        <is>
+          <t>UV_April_Mean</t>
+        </is>
+      </c>
+      <c r="D198" s="18" t="inlineStr">
+        <is>
+          <t>09_UV_Index (الأشعة فوق البنفسجية)</t>
+        </is>
+      </c>
+      <c r="E198" s="12" t="inlineStr">
+        <is>
+          <t>متوسط مؤشر الأشعة فوق البنفسجية القصوى لشهر أبريل وفق معيار WHO.</t>
+        </is>
+      </c>
+      <c r="F198" s="19" t="inlineStr">
+        <is>
+          <t>مؤشر (0-16+)</t>
+        </is>
+      </c>
+      <c r="G198" s="30" t="inlineStr">
+        <is>
+          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية لشهر أبريل</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="24" customHeight="1">
+      <c r="A199" s="3" t="n">
+        <v>198</v>
+      </c>
+      <c r="B199" s="5" t="inlineStr">
+        <is>
+          <t>UV_MayMean</t>
+        </is>
+      </c>
+      <c r="C199" s="31" t="inlineStr">
+        <is>
+          <t>UV_May_Mean</t>
+        </is>
+      </c>
+      <c r="D199" s="15" t="inlineStr">
+        <is>
+          <t>09_UV_Index (الأشعة فوق البنفسجية)</t>
+        </is>
+      </c>
+      <c r="E199" s="7" t="inlineStr">
+        <is>
+          <t>متوسط مؤشر الأشعة فوق البنفسجية القصوى لشهر مايو وفق معيار WHO.</t>
+        </is>
+      </c>
+      <c r="F199" s="16" t="inlineStr">
+        <is>
+          <t>مؤشر (0-16+)</t>
+        </is>
+      </c>
+      <c r="G199" s="32" t="inlineStr">
+        <is>
+          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية لشهر مايو</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="24" customHeight="1">
+      <c r="A200" s="8" t="n">
+        <v>199</v>
+      </c>
+      <c r="B200" s="10" t="inlineStr">
+        <is>
+          <t>UV_JunMean</t>
+        </is>
+      </c>
+      <c r="C200" s="29" t="inlineStr">
+        <is>
+          <t>UV_June_Mean</t>
+        </is>
+      </c>
+      <c r="D200" s="18" t="inlineStr">
+        <is>
+          <t>09_UV_Index (الأشعة فوق البنفسجية)</t>
+        </is>
+      </c>
+      <c r="E200" s="12" t="inlineStr">
+        <is>
+          <t>متوسط مؤشر الأشعة فوق البنفسجية القصوى لشهر يونيو وفق معيار WHO.</t>
+        </is>
+      </c>
+      <c r="F200" s="19" t="inlineStr">
+        <is>
+          <t>مؤشر (0-16+)</t>
+        </is>
+      </c>
+      <c r="G200" s="30" t="inlineStr">
+        <is>
+          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية لشهر يونيو</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="24" customHeight="1">
+      <c r="A201" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="B201" s="5" t="inlineStr">
+        <is>
+          <t>UV_JulMean</t>
+        </is>
+      </c>
+      <c r="C201" s="31" t="inlineStr">
+        <is>
+          <t>UV_July_Mean</t>
+        </is>
+      </c>
+      <c r="D201" s="15" t="inlineStr">
+        <is>
+          <t>09_UV_Index (الأشعة فوق البنفسجية)</t>
+        </is>
+      </c>
+      <c r="E201" s="7" t="inlineStr">
+        <is>
+          <t>متوسط مؤشر الأشعة فوق البنفسجية القصوى لشهر يوليو وفق معيار WHO.</t>
+        </is>
+      </c>
+      <c r="F201" s="16" t="inlineStr">
+        <is>
+          <t>مؤشر (0-16+)</t>
+        </is>
+      </c>
+      <c r="G201" s="32" t="inlineStr">
+        <is>
+          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية لشهر يوليو</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" ht="24" customHeight="1">
+      <c r="A202" s="8" t="n">
+        <v>201</v>
+      </c>
+      <c r="B202" s="10" t="inlineStr">
+        <is>
+          <t>UV_AugMean</t>
+        </is>
+      </c>
+      <c r="C202" s="29" t="inlineStr">
+        <is>
+          <t>UV_August_Mean</t>
+        </is>
+      </c>
+      <c r="D202" s="18" t="inlineStr">
+        <is>
+          <t>09_UV_Index (الأشعة فوق البنفسجية)</t>
+        </is>
+      </c>
+      <c r="E202" s="12" t="inlineStr">
+        <is>
+          <t>متوسط مؤشر الأشعة فوق البنفسجية القصوى لشهر أغسطس وفق معيار WHO.</t>
+        </is>
+      </c>
+      <c r="F202" s="19" t="inlineStr">
+        <is>
+          <t>مؤشر (0-16+)</t>
+        </is>
+      </c>
+      <c r="G202" s="30" t="inlineStr">
+        <is>
+          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية لشهر أغسطس</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" ht="24" customHeight="1">
+      <c r="A203" s="3" t="n">
+        <v>202</v>
+      </c>
+      <c r="B203" s="5" t="inlineStr">
+        <is>
+          <t>UV_SepMean</t>
+        </is>
+      </c>
+      <c r="C203" s="31" t="inlineStr">
+        <is>
+          <t>UV_September_Mean</t>
+        </is>
+      </c>
+      <c r="D203" s="15" t="inlineStr">
+        <is>
+          <t>09_UV_Index (الأشعة فوق البنفسجية)</t>
+        </is>
+      </c>
+      <c r="E203" s="7" t="inlineStr">
+        <is>
+          <t>متوسط مؤشر الأشعة فوق البنفسجية القصوى لشهر سبتمبر وفق معيار WHO.</t>
+        </is>
+      </c>
+      <c r="F203" s="16" t="inlineStr">
+        <is>
+          <t>مؤشر (0-16+)</t>
+        </is>
+      </c>
+      <c r="G203" s="32" t="inlineStr">
+        <is>
+          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية لشهر سبتمبر</t>
+        </is>
+      </c>
+    </row>
+    <row r="204" ht="24" customHeight="1">
+      <c r="A204" s="8" t="n">
+        <v>203</v>
+      </c>
+      <c r="B204" s="10" t="inlineStr">
+        <is>
+          <t>UV_OctMean</t>
+        </is>
+      </c>
+      <c r="C204" s="29" t="inlineStr">
+        <is>
+          <t>UV_October_Mean</t>
+        </is>
+      </c>
+      <c r="D204" s="18" t="inlineStr">
+        <is>
+          <t>09_UV_Index (الأشعة فوق البنفسجية)</t>
+        </is>
+      </c>
+      <c r="E204" s="12" t="inlineStr">
+        <is>
+          <t>متوسط مؤشر الأشعة فوق البنفسجية القصوى لشهر أكتوبر وفق معيار WHO.</t>
+        </is>
+      </c>
+      <c r="F204" s="19" t="inlineStr">
+        <is>
+          <t>مؤشر (0-16+)</t>
+        </is>
+      </c>
+      <c r="G204" s="30" t="inlineStr">
+        <is>
+          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية لشهر أكتوبر</t>
+        </is>
+      </c>
+    </row>
+    <row r="205" ht="24" customHeight="1">
+      <c r="A205" s="3" t="n">
+        <v>204</v>
+      </c>
+      <c r="B205" s="5" t="inlineStr">
+        <is>
+          <t>UV_NovMean</t>
+        </is>
+      </c>
+      <c r="C205" s="31" t="inlineStr">
+        <is>
+          <t>UV_November_Mean</t>
+        </is>
+      </c>
+      <c r="D205" s="15" t="inlineStr">
+        <is>
+          <t>09_UV_Index (الأشعة فوق البنفسجية)</t>
+        </is>
+      </c>
+      <c r="E205" s="7" t="inlineStr">
+        <is>
+          <t>متوسط مؤشر الأشعة فوق البنفسجية القصوى لشهر نوفمبر وفق معيار WHO.</t>
+        </is>
+      </c>
+      <c r="F205" s="16" t="inlineStr">
+        <is>
+          <t>مؤشر (0-16+)</t>
+        </is>
+      </c>
+      <c r="G205" s="32" t="inlineStr">
+        <is>
+          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية لشهر نوفمبر</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="24" customHeight="1">
+      <c r="A206" s="8" t="n">
+        <v>205</v>
+      </c>
+      <c r="B206" s="10" t="inlineStr">
+        <is>
+          <t>UV_DecMean</t>
+        </is>
+      </c>
+      <c r="C206" s="29" t="inlineStr">
+        <is>
+          <t>UV_December_Mean</t>
+        </is>
+      </c>
+      <c r="D206" s="18" t="inlineStr">
+        <is>
+          <t>09_UV_Index (الأشعة فوق البنفسجية)</t>
+        </is>
+      </c>
+      <c r="E206" s="12" t="inlineStr">
+        <is>
+          <t>متوسط مؤشر الأشعة فوق البنفسجية القصوى لشهر ديسمبر وفق معيار WHO.</t>
+        </is>
+      </c>
+      <c r="F206" s="19" t="inlineStr">
+        <is>
+          <t>مؤشر (0-16+)</t>
+        </is>
+      </c>
+      <c r="G206" s="30" t="inlineStr">
+        <is>
+          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية لشهر ديسمبر</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="24" customHeight="1">
+      <c r="A207" s="3" t="n">
+        <v>206</v>
+      </c>
+      <c r="B207" s="5" t="inlineStr">
+        <is>
+          <t>Cld_AnMean</t>
+        </is>
+      </c>
+      <c r="C207" s="31" t="inlineStr">
+        <is>
+          <t>Cld_Annual_Mean</t>
+        </is>
+      </c>
+      <c r="D207" s="15" t="inlineStr">
+        <is>
+          <t>10_Cloud_Cover (الغطاء السحابي)</t>
+        </is>
+      </c>
+      <c r="E207" s="7" t="inlineStr">
+        <is>
+          <t>المتوسط السنوي لنسبة تغطية السماء بالغيوم والسحب كنسبة مئوية.</t>
+        </is>
+      </c>
+      <c r="F207" s="16" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="G207" s="32" t="inlineStr">
+        <is>
+          <t>خريطة المتوسط السنوي لنسبة الغطاء السحابي (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="208" ht="24" customHeight="1">
+      <c r="A208" s="8" t="n">
+        <v>207</v>
+      </c>
+      <c r="B208" s="10" t="inlineStr">
+        <is>
+          <t>Cld_WnMean</t>
+        </is>
+      </c>
+      <c r="C208" s="29" t="inlineStr">
+        <is>
+          <t>Cld_Winter_Mean</t>
+        </is>
+      </c>
+      <c r="D208" s="18" t="inlineStr">
+        <is>
+          <t>10_Cloud_Cover (الغطاء السحابي)</t>
+        </is>
+      </c>
+      <c r="E208" s="12" t="inlineStr">
+        <is>
+          <t>متوسط نسبة تغطية السحب لفصل الشتاء الأرصادي (DJF).</t>
+        </is>
+      </c>
+      <c r="F208" s="19" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="G208" s="30" t="inlineStr">
+        <is>
+          <t>خريطة متوسط الغطاء السحابي خلال فصل الشتاء (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="209" ht="24" customHeight="1">
+      <c r="A209" s="3" t="n">
+        <v>208</v>
+      </c>
+      <c r="B209" s="5" t="inlineStr">
+        <is>
+          <t>Cld_SpMean</t>
+        </is>
+      </c>
+      <c r="C209" s="31" t="inlineStr">
+        <is>
+          <t>Cld_Spring_Mean</t>
+        </is>
+      </c>
+      <c r="D209" s="15" t="inlineStr">
+        <is>
+          <t>10_Cloud_Cover (الغطاء السحابي)</t>
+        </is>
+      </c>
+      <c r="E209" s="7" t="inlineStr">
+        <is>
+          <t>متوسط نسبة تغطية السحب لفصل الربيع الأرصادي (MAM).</t>
+        </is>
+      </c>
+      <c r="F209" s="16" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="G209" s="32" t="inlineStr">
+        <is>
+          <t>خريطة متوسط الغطاء السحابي خلال فصل الربيع (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" ht="24" customHeight="1">
+      <c r="A210" s="8" t="n">
+        <v>209</v>
+      </c>
+      <c r="B210" s="10" t="inlineStr">
+        <is>
+          <t>Cld_SuMean</t>
+        </is>
+      </c>
+      <c r="C210" s="29" t="inlineStr">
+        <is>
+          <t>Cld_Summer_Mean</t>
+        </is>
+      </c>
+      <c r="D210" s="18" t="inlineStr">
+        <is>
+          <t>10_Cloud_Cover (الغطاء السحابي)</t>
+        </is>
+      </c>
+      <c r="E210" s="12" t="inlineStr">
+        <is>
+          <t>متوسط نسبة تغطية السحب لفصل الصيف الأرصادي (JJA).</t>
+        </is>
+      </c>
+      <c r="F210" s="19" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="G210" s="30" t="inlineStr">
+        <is>
+          <t>خريطة متوسط الغطاء السحابي خلال فصل الصيف (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" ht="24" customHeight="1">
+      <c r="A211" s="3" t="n">
+        <v>210</v>
+      </c>
+      <c r="B211" s="5" t="inlineStr">
+        <is>
+          <t>Cld_AuMean</t>
+        </is>
+      </c>
+      <c r="C211" s="31" t="inlineStr">
+        <is>
+          <t>Cld_Autumn_Mean</t>
+        </is>
+      </c>
+      <c r="D211" s="15" t="inlineStr">
+        <is>
+          <t>10_Cloud_Cover (الغطاء السحابي)</t>
+        </is>
+      </c>
+      <c r="E211" s="7" t="inlineStr">
+        <is>
+          <t>متوسط نسبة تغطية السحب لفصل الخريف الأرصادي (SON).</t>
+        </is>
+      </c>
+      <c r="F211" s="16" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="G211" s="32" t="inlineStr">
+        <is>
+          <t>خريطة متوسط الغطاء السحابي خلال فصل الخريف (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="212" ht="24" customHeight="1">
+      <c r="A212" s="8" t="n">
+        <v>211</v>
+      </c>
+      <c r="B212" s="10" t="inlineStr">
+        <is>
+          <t>Cld_AnRng</t>
+        </is>
+      </c>
+      <c r="C212" s="29" t="inlineStr">
+        <is>
+          <t>Cld_Annual_Range</t>
+        </is>
+      </c>
+      <c r="D212" s="18" t="inlineStr">
+        <is>
+          <t>10_Cloud_Cover (الغطاء السحابي)</t>
+        </is>
+      </c>
+      <c r="E212" s="12" t="inlineStr">
+        <is>
+          <t>المدى السنوي لتغطية السحب (الفارق بين أكثر شهور السنة غيوماً وأكثرها صفاءً).</t>
+        </is>
+      </c>
+      <c r="F212" s="19" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="G212" s="30" t="inlineStr">
+        <is>
+          <t>خريطة المدى السنوي لنسبة الغطاء السحابي (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" ht="24" customHeight="1">
+      <c r="A213" s="3" t="n">
+        <v>212</v>
+      </c>
+      <c r="B213" s="5" t="inlineStr">
+        <is>
+          <t>Cld_JanMn</t>
+        </is>
+      </c>
+      <c r="C213" s="31" t="inlineStr">
+        <is>
+          <t>Cld_January_Mean</t>
+        </is>
+      </c>
+      <c r="D213" s="15" t="inlineStr">
+        <is>
+          <t>10_Cloud_Cover (الغطاء السحابي)</t>
+        </is>
+      </c>
+      <c r="E213" s="7" t="inlineStr">
+        <is>
+          <t>متوسط نسبة الغطاء السحابي الكلي للسماء لشهر يناير.</t>
+        </is>
+      </c>
+      <c r="F213" s="16" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="G213" s="32" t="inlineStr">
+        <is>
+          <t>خريطة متوسط الغطاء السحابي لشهر يناير (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="214" ht="24" customHeight="1">
+      <c r="A214" s="8" t="n">
+        <v>213</v>
+      </c>
+      <c r="B214" s="10" t="inlineStr">
+        <is>
+          <t>Cld_FebMn</t>
+        </is>
+      </c>
+      <c r="C214" s="29" t="inlineStr">
+        <is>
+          <t>Cld_February_Mean</t>
+        </is>
+      </c>
+      <c r="D214" s="18" t="inlineStr">
+        <is>
+          <t>10_Cloud_Cover (الغطاء السحابي)</t>
+        </is>
+      </c>
+      <c r="E214" s="12" t="inlineStr">
+        <is>
+          <t>متوسط نسبة الغطاء السحابي الكلي للسماء لشهر فبراير.</t>
+        </is>
+      </c>
+      <c r="F214" s="19" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="G214" s="30" t="inlineStr">
+        <is>
+          <t>خريطة متوسط الغطاء السحابي لشهر فبراير (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="215" ht="24" customHeight="1">
+      <c r="A215" s="3" t="n">
+        <v>214</v>
+      </c>
+      <c r="B215" s="5" t="inlineStr">
+        <is>
+          <t>Cld_MarMn</t>
+        </is>
+      </c>
+      <c r="C215" s="31" t="inlineStr">
+        <is>
+          <t>Cld_March_Mean</t>
+        </is>
+      </c>
+      <c r="D215" s="15" t="inlineStr">
+        <is>
+          <t>10_Cloud_Cover (الغطاء السحابي)</t>
+        </is>
+      </c>
+      <c r="E215" s="7" t="inlineStr">
+        <is>
+          <t>متوسط نسبة الغطاء السحابي الكلي للسماء لشهر مارس.</t>
+        </is>
+      </c>
+      <c r="F215" s="16" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="G215" s="32" t="inlineStr">
+        <is>
+          <t>خريطة متوسط الغطاء السحابي لشهر مارس (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="216" ht="24" customHeight="1">
+      <c r="A216" s="8" t="n">
+        <v>215</v>
+      </c>
+      <c r="B216" s="10" t="inlineStr">
+        <is>
+          <t>Cld_AprMn</t>
+        </is>
+      </c>
+      <c r="C216" s="29" t="inlineStr">
+        <is>
+          <t>Cld_April_Mean</t>
+        </is>
+      </c>
+      <c r="D216" s="18" t="inlineStr">
+        <is>
+          <t>10_Cloud_Cover (الغطاء السحابي)</t>
+        </is>
+      </c>
+      <c r="E216" s="12" t="inlineStr">
+        <is>
+          <t>متوسط نسبة الغطاء السحابي الكلي للسماء لشهر أبريل.</t>
+        </is>
+      </c>
+      <c r="F216" s="19" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="G216" s="30" t="inlineStr">
+        <is>
+          <t>خريطة متوسط الغطاء السحابي لشهر أبريل (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="217" ht="24" customHeight="1">
+      <c r="A217" s="3" t="n">
+        <v>216</v>
+      </c>
+      <c r="B217" s="5" t="inlineStr">
+        <is>
+          <t>Cld_MayMn</t>
+        </is>
+      </c>
+      <c r="C217" s="31" t="inlineStr">
+        <is>
+          <t>Cld_May_Mean</t>
+        </is>
+      </c>
+      <c r="D217" s="15" t="inlineStr">
+        <is>
+          <t>10_Cloud_Cover (الغطاء السحابي)</t>
+        </is>
+      </c>
+      <c r="E217" s="7" t="inlineStr">
+        <is>
+          <t>متوسط نسبة الغطاء السحابي الكلي للسماء لشهر مايو.</t>
+        </is>
+      </c>
+      <c r="F217" s="16" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="G217" s="32" t="inlineStr">
+        <is>
+          <t>خريطة متوسط الغطاء السحابي لشهر مايو (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="218" ht="24" customHeight="1">
+      <c r="A218" s="8" t="n">
+        <v>217</v>
+      </c>
+      <c r="B218" s="10" t="inlineStr">
+        <is>
+          <t>Cld_JunMn</t>
+        </is>
+      </c>
+      <c r="C218" s="29" t="inlineStr">
+        <is>
+          <t>Cld_June_Mean</t>
+        </is>
+      </c>
+      <c r="D218" s="18" t="inlineStr">
+        <is>
+          <t>10_Cloud_Cover (الغطاء السحابي)</t>
+        </is>
+      </c>
+      <c r="E218" s="12" t="inlineStr">
+        <is>
+          <t>متوسط نسبة الغطاء السحابي الكلي للسماء لشهر يونيو.</t>
+        </is>
+      </c>
+      <c r="F218" s="19" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="G218" s="30" t="inlineStr">
+        <is>
+          <t>خريطة متوسط الغطاء السحابي لشهر يونيو (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="219" ht="24" customHeight="1">
+      <c r="A219" s="3" t="n">
+        <v>218</v>
+      </c>
+      <c r="B219" s="5" t="inlineStr">
+        <is>
+          <t>Cld_JulMn</t>
+        </is>
+      </c>
+      <c r="C219" s="31" t="inlineStr">
+        <is>
+          <t>Cld_July_Mean</t>
+        </is>
+      </c>
+      <c r="D219" s="15" t="inlineStr">
+        <is>
+          <t>10_Cloud_Cover (الغطاء السحابي)</t>
+        </is>
+      </c>
+      <c r="E219" s="7" t="inlineStr">
+        <is>
+          <t>متوسط نسبة الغطاء السحابي الكلي للسماء لشهر يوليو.</t>
+        </is>
+      </c>
+      <c r="F219" s="16" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="G219" s="32" t="inlineStr">
+        <is>
+          <t>خريطة متوسط الغطاء السحابي لشهر يوليو (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="220" ht="24" customHeight="1">
+      <c r="A220" s="8" t="n">
+        <v>219</v>
+      </c>
+      <c r="B220" s="10" t="inlineStr">
+        <is>
+          <t>Cld_AugMn</t>
+        </is>
+      </c>
+      <c r="C220" s="29" t="inlineStr">
+        <is>
+          <t>Cld_August_Mean</t>
+        </is>
+      </c>
+      <c r="D220" s="18" t="inlineStr">
+        <is>
+          <t>10_Cloud_Cover (الغطاء السحابي)</t>
+        </is>
+      </c>
+      <c r="E220" s="12" t="inlineStr">
+        <is>
+          <t>متوسط نسبة الغطاء السحابي الكلي للسماء لشهر أغسطس.</t>
+        </is>
+      </c>
+      <c r="F220" s="19" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="G220" s="30" t="inlineStr">
+        <is>
+          <t>خريطة متوسط الغطاء السحابي لشهر أغسطس (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="221" ht="24" customHeight="1">
+      <c r="A221" s="3" t="n">
+        <v>220</v>
+      </c>
+      <c r="B221" s="5" t="inlineStr">
+        <is>
+          <t>Cld_SepMn</t>
+        </is>
+      </c>
+      <c r="C221" s="31" t="inlineStr">
+        <is>
+          <t>Cld_September_Mean</t>
+        </is>
+      </c>
+      <c r="D221" s="15" t="inlineStr">
+        <is>
+          <t>10_Cloud_Cover (الغطاء السحابي)</t>
+        </is>
+      </c>
+      <c r="E221" s="7" t="inlineStr">
+        <is>
+          <t>متوسط نسبة الغطاء السحابي الكلي للسماء لشهر سبتمبر.</t>
+        </is>
+      </c>
+      <c r="F221" s="16" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="G221" s="32" t="inlineStr">
+        <is>
+          <t>خريطة متوسط الغطاء السحابي لشهر سبتمبر (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="222" ht="24" customHeight="1">
+      <c r="A222" s="8" t="n">
+        <v>221</v>
+      </c>
+      <c r="B222" s="10" t="inlineStr">
+        <is>
+          <t>Cld_OctMn</t>
+        </is>
+      </c>
+      <c r="C222" s="29" t="inlineStr">
+        <is>
+          <t>Cld_October_Mean</t>
+        </is>
+      </c>
+      <c r="D222" s="18" t="inlineStr">
+        <is>
+          <t>10_Cloud_Cover (الغطاء السحابي)</t>
+        </is>
+      </c>
+      <c r="E222" s="12" t="inlineStr">
+        <is>
+          <t>متوسط نسبة الغطاء السحابي الكلي للسماء لشهر أكتوبر.</t>
+        </is>
+      </c>
+      <c r="F222" s="19" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="G222" s="30" t="inlineStr">
+        <is>
+          <t>خريطة متوسط الغطاء السحابي لشهر أكتوبر (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="223" ht="24" customHeight="1">
+      <c r="A223" s="3" t="n">
+        <v>222</v>
+      </c>
+      <c r="B223" s="5" t="inlineStr">
+        <is>
+          <t>Cld_NovMn</t>
+        </is>
+      </c>
+      <c r="C223" s="31" t="inlineStr">
+        <is>
+          <t>Cld_November_Mean</t>
+        </is>
+      </c>
+      <c r="D223" s="15" t="inlineStr">
+        <is>
+          <t>10_Cloud_Cover (الغطاء السحابي)</t>
+        </is>
+      </c>
+      <c r="E223" s="7" t="inlineStr">
+        <is>
+          <t>متوسط نسبة الغطاء السحابي الكلي للسماء لشهر نوفمبر.</t>
+        </is>
+      </c>
+      <c r="F223" s="16" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="G223" s="32" t="inlineStr">
+        <is>
+          <t>خريطة متوسط الغطاء السحابي لشهر نوفمبر (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="224" ht="24" customHeight="1">
+      <c r="A224" s="8" t="n">
+        <v>223</v>
+      </c>
+      <c r="B224" s="10" t="inlineStr">
+        <is>
+          <t>Cld_DecMn</t>
+        </is>
+      </c>
+      <c r="C224" s="29" t="inlineStr">
+        <is>
+          <t>Cld_December_Mean</t>
+        </is>
+      </c>
+      <c r="D224" s="18" t="inlineStr">
+        <is>
+          <t>10_Cloud_Cover (الغطاء السحابي)</t>
+        </is>
+      </c>
+      <c r="E224" s="12" t="inlineStr">
+        <is>
+          <t>متوسط نسبة الغطاء السحابي الكلي للسماء لشهر ديسمبر.</t>
+        </is>
+      </c>
+      <c r="F224" s="19" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="G224" s="30" t="inlineStr">
+        <is>
+          <t>خريطة متوسط الغطاء السحابي لشهر ديسمبر (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="225" ht="24" customHeight="1">
+      <c r="A225" s="3" t="n">
+        <v>224</v>
+      </c>
+      <c r="B225" s="5" t="inlineStr">
+        <is>
+          <t>WC_WinMean</t>
+        </is>
+      </c>
+      <c r="C225" s="31" t="inlineStr">
+        <is>
+          <t>WC_Winter_Mean</t>
+        </is>
+      </c>
+      <c r="D225" s="15" t="inlineStr">
+        <is>
+          <t>12_Wind_Chill (مبرد الرياح)</t>
+        </is>
+      </c>
+      <c r="E225" s="7" t="inlineStr">
+        <is>
+          <t>متوسط درجة البرودة الريحية لفصل الشتاء المحسوبة بمعادلة NWS لخفض الحرارة بفعل سرعة الرياح.</t>
+        </is>
+      </c>
+      <c r="F225" s="16" t="inlineStr">
+        <is>
+          <t>°C</t>
+        </is>
+      </c>
+      <c r="G225" s="32" t="inlineStr">
+        <is>
+          <t>خريطة متوسط مبرد الرياح خلال فصل الشتاء (°C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="226" ht="24" customHeight="1">
+      <c r="A226" s="8" t="n">
+        <v>225</v>
+      </c>
+      <c r="B226" s="10" t="inlineStr">
+        <is>
+          <t>WC_AnnMean</t>
+        </is>
+      </c>
+      <c r="C226" s="29" t="inlineStr">
+        <is>
+          <t>WC_Annual_Mean</t>
+        </is>
+      </c>
+      <c r="D226" s="18" t="inlineStr">
+        <is>
+          <t>12_Wind_Chill (مبرد الرياح)</t>
+        </is>
+      </c>
+      <c r="E226" s="12" t="inlineStr">
+        <is>
+          <t>المتوسط الحسابي السنوي لتأثير البرودة الريحية على حرارة الهواء المحسوسة.</t>
+        </is>
+      </c>
+      <c r="F226" s="19" t="inlineStr">
+        <is>
+          <t>°C</t>
+        </is>
+      </c>
+      <c r="G226" s="30" t="inlineStr">
+        <is>
+          <t>خريطة المتوسط السنوي لمبرد الرياح (°C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="227" ht="24" customHeight="1">
+      <c r="A227" s="3" t="n">
+        <v>226</v>
+      </c>
+      <c r="B227" s="5" t="inlineStr">
+        <is>
+          <t>DM_AridAnn</t>
+        </is>
+      </c>
+      <c r="C227" s="31" t="inlineStr">
+        <is>
+          <t>DM_Aridity_Annual</t>
+        </is>
+      </c>
+      <c r="D227" s="15" t="inlineStr">
+        <is>
+          <t>13_De_Martonne_Aridity (دليل دي مارتون)</t>
+        </is>
+      </c>
+      <c r="E227" s="7" t="inlineStr">
+        <is>
+          <t>دليل القحولة والجفاف السنوي لدي مارتون I = P / (T + 10) لتصنيف الأقاليم من القاحل فائق الجفاف إلى الرطب.</t>
+        </is>
+      </c>
+      <c r="F227" s="16" t="inlineStr">
+        <is>
+          <t>مؤشر (Index)</t>
+        </is>
+      </c>
+      <c r="G227" s="32" t="inlineStr">
+        <is>
+          <t>خريطة دليل دي مارتون السنوي للقحولة والجفاف</t>
+        </is>
+      </c>
+    </row>
+    <row r="228" ht="24" customHeight="1">
+      <c r="A228" s="8" t="n">
+        <v>227</v>
+      </c>
+      <c r="B228" s="10" t="inlineStr">
+        <is>
+          <t>ET_AnnTot</t>
+        </is>
+      </c>
+      <c r="C228" s="29" t="inlineStr">
+        <is>
+          <t>ET_Annual_Total</t>
+        </is>
+      </c>
+      <c r="D228" s="18" t="inlineStr">
+        <is>
+          <t>14_Evapotranspiration (البخر والنتح)</t>
+        </is>
+      </c>
+      <c r="E228" s="12" t="inlineStr">
+        <is>
+          <t>المجموع التراكمي السنوي للبخر والنتح المرجعي الكامن المحسوب بمعادلة Hargreaves-Samani (FAO-56).</t>
+        </is>
+      </c>
+      <c r="F228" s="19" t="inlineStr">
+        <is>
+          <t>ملم (mm)</t>
+        </is>
+      </c>
+      <c r="G228" s="30" t="inlineStr">
+        <is>
+          <t>خريطة المجموع السنوي للبخر والنتح (ملم)</t>
+        </is>
+      </c>
+    </row>
+    <row r="229" ht="24" customHeight="1">
+      <c r="A229" s="3" t="n">
+        <v>228</v>
+      </c>
+      <c r="B229" s="5" t="inlineStr">
+        <is>
+          <t>ET_AnnMean</t>
+        </is>
+      </c>
+      <c r="C229" s="31" t="inlineStr">
+        <is>
+          <t>ET_Annual_Mean</t>
+        </is>
+      </c>
+      <c r="D229" s="15" t="inlineStr">
+        <is>
+          <t>14_Evapotranspiration (البخر والنتح)</t>
+        </is>
+      </c>
+      <c r="E229" s="7" t="inlineStr">
+        <is>
+          <t>المعدل الشهري للبخر والنتح المرجعي (المجموع التراكمي السنوي مقسوماً على 12 شهراً).</t>
+        </is>
+      </c>
+      <c r="F229" s="16" t="inlineStr">
+        <is>
+          <t>ملم (mm)</t>
+        </is>
+      </c>
+      <c r="G229" s="32" t="inlineStr">
+        <is>
+          <t>خريطة المعدل الشهري للبخر والنتح (ملم)</t>
+        </is>
+      </c>
+    </row>
+    <row r="230" ht="24" customHeight="1">
+      <c r="A230" s="8" t="n">
+        <v>229</v>
+      </c>
+      <c r="B230" s="10" t="inlineStr">
+        <is>
+          <t>ET_AnnRng</t>
+        </is>
+      </c>
+      <c r="C230" s="29" t="inlineStr">
+        <is>
+          <t>ET_Annual_Range</t>
+        </is>
+      </c>
+      <c r="D230" s="18" t="inlineStr">
+        <is>
+          <t>14_Evapotranspiration (البخر والنتح)</t>
+        </is>
+      </c>
+      <c r="E230" s="12" t="inlineStr">
+        <is>
+          <t>المدى السنوي للبخر والنتح (الفارق بين أعلى شهور السنة فقداً للماء بالبخر والنتح وأدناها).</t>
+        </is>
+      </c>
+      <c r="F230" s="19" t="inlineStr">
+        <is>
+          <t>ملم (mm)</t>
+        </is>
+      </c>
+      <c r="G230" s="30" t="inlineStr">
+        <is>
+          <t>خريطة المدى السنوي للبخر والنتح (ملم)</t>
+        </is>
+      </c>
+    </row>
+    <row r="231" ht="24" customHeight="1">
+      <c r="A231" s="3" t="n">
+        <v>230</v>
+      </c>
+      <c r="B231" s="5" t="inlineStr">
+        <is>
+          <t>ET_SeaRng</t>
+        </is>
+      </c>
+      <c r="C231" s="31" t="inlineStr">
+        <is>
+          <t>ET_Seasonal_Range</t>
+        </is>
+      </c>
+      <c r="D231" s="15" t="inlineStr">
+        <is>
+          <t>14_Evapotranspiration (البخر والنتح)</t>
+        </is>
+      </c>
+      <c r="E231" s="7" t="inlineStr">
+        <is>
+          <t>المدى الفصلي للبخر والنتح (الفارق بين مجموع أعلى فصول السنة في البخر والنتح ومجموع أقلها).</t>
+        </is>
+      </c>
+      <c r="F231" s="16" t="inlineStr">
+        <is>
+          <t>ملم (mm)</t>
+        </is>
+      </c>
+      <c r="G231" s="32" t="inlineStr">
+        <is>
+          <t>خريطة المدى الفصلي للبخر والنتح (ملم)</t>
+        </is>
+      </c>
+    </row>
+    <row r="232" ht="24" customHeight="1">
+      <c r="A232" s="8" t="n">
+        <v>231</v>
+      </c>
+      <c r="B232" s="10" t="inlineStr">
+        <is>
+          <t>ET_WinTot</t>
+        </is>
+      </c>
+      <c r="C232" s="29" t="inlineStr">
+        <is>
+          <t>ET_Winter_Total</t>
+        </is>
+      </c>
+      <c r="D232" s="18" t="inlineStr">
+        <is>
+          <t>14_Evapotranspiration (البخر والنتح)</t>
+        </is>
+      </c>
+      <c r="E232" s="12" t="inlineStr">
+        <is>
+          <t>مجموع البخر والنتح لفصل الشتاء الأرصادي (شهور ديسمبر، يناير، فبراير - DJF).</t>
+        </is>
+      </c>
+      <c r="F232" s="19" t="inlineStr">
+        <is>
+          <t>ملم (mm)</t>
+        </is>
+      </c>
+      <c r="G232" s="30" t="inlineStr">
+        <is>
+          <t>خريطة مجموع البخر والنتح خلال فصل الشتاء (ملم)</t>
+        </is>
+      </c>
+    </row>
+    <row r="233" ht="24" customHeight="1">
+      <c r="A233" s="3" t="n">
+        <v>232</v>
+      </c>
+      <c r="B233" s="5" t="inlineStr">
+        <is>
+          <t>ET_SprTot</t>
+        </is>
+      </c>
+      <c r="C233" s="31" t="inlineStr">
+        <is>
+          <t>ET_Spring_Total</t>
+        </is>
+      </c>
+      <c r="D233" s="15" t="inlineStr">
+        <is>
+          <t>14_Evapotranspiration (البخر والنتح)</t>
+        </is>
+      </c>
+      <c r="E233" s="7" t="inlineStr">
+        <is>
+          <t>مجموع البخر والنتح لفصل الربيع الأرصادي (شهور مارس، أبريل، مايو - MAM).</t>
+        </is>
+      </c>
+      <c r="F233" s="16" t="inlineStr">
+        <is>
+          <t>ملم (mm)</t>
+        </is>
+      </c>
+      <c r="G233" s="32" t="inlineStr">
+        <is>
+          <t>خريطة مجموع البخر والنتح خلال فصل الربيع (ملم)</t>
+        </is>
+      </c>
+    </row>
+    <row r="234" ht="24" customHeight="1">
+      <c r="A234" s="8" t="n">
+        <v>233</v>
+      </c>
+      <c r="B234" s="10" t="inlineStr">
+        <is>
+          <t>ET_SumTot</t>
+        </is>
+      </c>
+      <c r="C234" s="29" t="inlineStr">
+        <is>
+          <t>ET_Summer_Total</t>
+        </is>
+      </c>
+      <c r="D234" s="18" t="inlineStr">
+        <is>
+          <t>14_Evapotranspiration (البخر والنتح)</t>
+        </is>
+      </c>
+      <c r="E234" s="12" t="inlineStr">
+        <is>
+          <t>مجموع البخر والنتح لفصل الصيف الأرصادي (شهور يونيو، يوليو، أغسطس - JJA).</t>
+        </is>
+      </c>
+      <c r="F234" s="19" t="inlineStr">
+        <is>
+          <t>ملم (mm)</t>
+        </is>
+      </c>
+      <c r="G234" s="30" t="inlineStr">
+        <is>
+          <t>خريطة مجموع البخر والنتح خلال فصل الصيف (ملم)</t>
+        </is>
+      </c>
+    </row>
+    <row r="235" ht="24" customHeight="1">
+      <c r="A235" s="3" t="n">
+        <v>234</v>
+      </c>
+      <c r="B235" s="5" t="inlineStr">
+        <is>
+          <t>ET_AutTot</t>
+        </is>
+      </c>
+      <c r="C235" s="31" t="inlineStr">
+        <is>
+          <t>ET_Autumn_Total</t>
+        </is>
+      </c>
+      <c r="D235" s="15" t="inlineStr">
+        <is>
+          <t>14_Evapotranspiration (البخر والنتح)</t>
+        </is>
+      </c>
+      <c r="E235" s="7" t="inlineStr">
+        <is>
+          <t>مجموع البخر والنتح لفصل الخريف الأرصادي (شهور سبتمبر، أكتوبر، نوفمبر - SON).</t>
+        </is>
+      </c>
+      <c r="F235" s="16" t="inlineStr">
+        <is>
+          <t>ملم (mm)</t>
+        </is>
+      </c>
+      <c r="G235" s="32" t="inlineStr">
+        <is>
+          <t>خريطة مجموع البخر والنتح خلال فصل الخريف (ملم)</t>
+        </is>
+      </c>
+    </row>
+    <row r="236" ht="24" customHeight="1">
+      <c r="A236" s="8" t="n">
+        <v>235</v>
+      </c>
+      <c r="B236" s="10" t="inlineStr">
+        <is>
+          <t>PET_HarAnn</t>
+        </is>
+      </c>
+      <c r="C236" s="29" t="inlineStr">
+        <is>
+          <t>PET_Hargreaves_Annual</t>
+        </is>
+      </c>
+      <c r="D236" s="18" t="inlineStr">
+        <is>
+          <t>14_Evapotranspiration (البخر والنتح)</t>
+        </is>
+      </c>
+      <c r="E236" s="12" t="inlineStr">
+        <is>
+          <t>التبخر-نتح الكامن السنوي بهارجريفز (حقل رديف مطابق تماماً لـ ET_Annual_Total للتوافقية العكسية).</t>
+        </is>
+      </c>
+      <c r="F236" s="19" t="inlineStr">
+        <is>
+          <t>ملم (mm)</t>
+        </is>
+      </c>
+      <c r="G236" s="30" t="inlineStr">
+        <is>
+          <t>خريطة التبخر والنتح الكامن السنوي بهارجريفز (ملم)</t>
+        </is>
+      </c>
+    </row>
+    <row r="237" ht="24" customHeight="1">
+      <c r="A237" s="3" t="n">
+        <v>236</v>
+      </c>
+      <c r="B237" s="5" t="inlineStr">
+        <is>
+          <t>ET_JanTot</t>
+        </is>
+      </c>
+      <c r="C237" s="31" t="inlineStr">
+        <is>
+          <t>ET_January_Total</t>
+        </is>
+      </c>
+      <c r="D237" s="15" t="inlineStr">
+        <is>
+          <t>14_Evapotranspiration (البخر والنتح)</t>
+        </is>
+      </c>
+      <c r="E237" s="7" t="inlineStr">
+        <is>
+          <t>متوسط مجموع البخر والنتح المرجعي الكامن لشهر يناير بطريقة هارجريفز-ساماني FAO-56.</t>
+        </is>
+      </c>
+      <c r="F237" s="16" t="inlineStr">
+        <is>
+          <t>ملم/شهر (mm/month)</t>
+        </is>
+      </c>
+      <c r="G237" s="32" t="inlineStr">
+        <is>
+          <t>خريطة مجموع البخر والنتح لشهر يناير (ملم/شهر)</t>
+        </is>
+      </c>
+    </row>
+    <row r="238" ht="24" customHeight="1">
+      <c r="A238" s="8" t="n">
+        <v>237</v>
+      </c>
+      <c r="B238" s="10" t="inlineStr">
+        <is>
+          <t>ET_FebTot</t>
+        </is>
+      </c>
+      <c r="C238" s="29" t="inlineStr">
+        <is>
+          <t>ET_February_Total</t>
+        </is>
+      </c>
+      <c r="D238" s="18" t="inlineStr">
+        <is>
+          <t>14_Evapotranspiration (البخر والنتح)</t>
+        </is>
+      </c>
+      <c r="E238" s="12" t="inlineStr">
+        <is>
+          <t>متوسط مجموع البخر والنتح المرجعي الكامن لشهر فبراير بطريقة هارجريفز-ساماني FAO-56.</t>
+        </is>
+      </c>
+      <c r="F238" s="19" t="inlineStr">
+        <is>
+          <t>ملم/شهر (mm/month)</t>
+        </is>
+      </c>
+      <c r="G238" s="30" t="inlineStr">
+        <is>
+          <t>خريطة مجموع البخر والنتح لشهر فبراير (ملم/شهر)</t>
+        </is>
+      </c>
+    </row>
+    <row r="239" ht="24" customHeight="1">
+      <c r="A239" s="3" t="n">
+        <v>238</v>
+      </c>
+      <c r="B239" s="5" t="inlineStr">
+        <is>
+          <t>ET_MarTot</t>
+        </is>
+      </c>
+      <c r="C239" s="31" t="inlineStr">
+        <is>
+          <t>ET_March_Total</t>
+        </is>
+      </c>
+      <c r="D239" s="15" t="inlineStr">
+        <is>
+          <t>14_Evapotranspiration (البخر والنتح)</t>
+        </is>
+      </c>
+      <c r="E239" s="7" t="inlineStr">
+        <is>
+          <t>متوسط مجموع البخر والنتح المرجعي الكامن لشهر مارس بطريقة هارجريفز-ساماني FAO-56.</t>
+        </is>
+      </c>
+      <c r="F239" s="16" t="inlineStr">
+        <is>
+          <t>ملم/شهر (mm/month)</t>
+        </is>
+      </c>
+      <c r="G239" s="32" t="inlineStr">
+        <is>
+          <t>خريطة مجموع البخر والنتح لشهر مارس (ملم/شهر)</t>
+        </is>
+      </c>
+    </row>
+    <row r="240" ht="24" customHeight="1">
+      <c r="A240" s="8" t="n">
+        <v>239</v>
+      </c>
+      <c r="B240" s="10" t="inlineStr">
+        <is>
+          <t>ET_AprTot</t>
+        </is>
+      </c>
+      <c r="C240" s="29" t="inlineStr">
+        <is>
+          <t>ET_April_Total</t>
+        </is>
+      </c>
+      <c r="D240" s="18" t="inlineStr">
+        <is>
+          <t>14_Evapotranspiration (البخر والنتح)</t>
+        </is>
+      </c>
+      <c r="E240" s="12" t="inlineStr">
+        <is>
+          <t>متوسط مجموع البخر والنتح المرجعي الكامن لشهر أبريل بطريقة هارجريفز-ساماني FAO-56.</t>
+        </is>
+      </c>
+      <c r="F240" s="19" t="inlineStr">
+        <is>
+          <t>ملم/شهر (mm/month)</t>
+        </is>
+      </c>
+      <c r="G240" s="30" t="inlineStr">
+        <is>
+          <t>خريطة مجموع البخر والنتح لشهر أبريل (ملم/شهر)</t>
+        </is>
+      </c>
+    </row>
+    <row r="241" ht="24" customHeight="1">
+      <c r="A241" s="3" t="n">
+        <v>240</v>
+      </c>
+      <c r="B241" s="5" t="inlineStr">
+        <is>
+          <t>ET_MayTot</t>
+        </is>
+      </c>
+      <c r="C241" s="31" t="inlineStr">
+        <is>
+          <t>ET_May_Total</t>
+        </is>
+      </c>
+      <c r="D241" s="15" t="inlineStr">
+        <is>
+          <t>14_Evapotranspiration (البخر والنتح)</t>
+        </is>
+      </c>
+      <c r="E241" s="7" t="inlineStr">
+        <is>
+          <t>متوسط مجموع البخر والنتح المرجعي الكامن لشهر مايو بطريقة هارجريفز-ساماني FAO-56.</t>
+        </is>
+      </c>
+      <c r="F241" s="16" t="inlineStr">
+        <is>
+          <t>ملم/شهر (mm/month)</t>
+        </is>
+      </c>
+      <c r="G241" s="32" t="inlineStr">
+        <is>
+          <t>خريطة مجموع البخر والنتح لشهر مايو (ملم/شهر)</t>
+        </is>
+      </c>
+    </row>
+    <row r="242" ht="24" customHeight="1">
+      <c r="A242" s="8" t="n">
+        <v>241</v>
+      </c>
+      <c r="B242" s="10" t="inlineStr">
+        <is>
+          <t>ET_JunTot</t>
+        </is>
+      </c>
+      <c r="C242" s="29" t="inlineStr">
+        <is>
+          <t>ET_June_Total</t>
+        </is>
+      </c>
+      <c r="D242" s="18" t="inlineStr">
+        <is>
+          <t>14_Evapotranspiration (البخر والنتح)</t>
+        </is>
+      </c>
+      <c r="E242" s="12" t="inlineStr">
+        <is>
+          <t>متوسط مجموع البخر والنتح المرجعي الكامن لشهر يونيو بطريقة هارجريفز-ساماني FAO-56.</t>
+        </is>
+      </c>
+      <c r="F242" s="19" t="inlineStr">
+        <is>
+          <t>ملم/شهر (mm/month)</t>
+        </is>
+      </c>
+      <c r="G242" s="30" t="inlineStr">
+        <is>
+          <t>خريطة مجموع البخر والنتح لشهر يونيو (ملم/شهر)</t>
+        </is>
+      </c>
+    </row>
+    <row r="243" ht="24" customHeight="1">
+      <c r="A243" s="3" t="n">
+        <v>242</v>
+      </c>
+      <c r="B243" s="5" t="inlineStr">
+        <is>
+          <t>ET_JulTot</t>
+        </is>
+      </c>
+      <c r="C243" s="31" t="inlineStr">
+        <is>
+          <t>ET_July_Total</t>
+        </is>
+      </c>
+      <c r="D243" s="15" t="inlineStr">
+        <is>
+          <t>14_Evapotranspiration (البخر والنتح)</t>
+        </is>
+      </c>
+      <c r="E243" s="7" t="inlineStr">
+        <is>
+          <t>متوسط مجموع البخر والنتح المرجعي الكامن لشهر يوليو بطريقة هارجريفز-ساماني FAO-56.</t>
+        </is>
+      </c>
+      <c r="F243" s="16" t="inlineStr">
+        <is>
+          <t>ملم/شهر (mm/month)</t>
+        </is>
+      </c>
+      <c r="G243" s="32" t="inlineStr">
+        <is>
+          <t>خريطة مجموع البخر والنتح لشهر يوليو (ملم/شهر)</t>
+        </is>
+      </c>
+    </row>
+    <row r="244" ht="24" customHeight="1">
+      <c r="A244" s="8" t="n">
+        <v>243</v>
+      </c>
+      <c r="B244" s="10" t="inlineStr">
+        <is>
+          <t>ET_AugTot</t>
+        </is>
+      </c>
+      <c r="C244" s="29" t="inlineStr">
+        <is>
+          <t>ET_August_Total</t>
+        </is>
+      </c>
+      <c r="D244" s="18" t="inlineStr">
+        <is>
+          <t>14_Evapotranspiration (البخر والنتح)</t>
+        </is>
+      </c>
+      <c r="E244" s="12" t="inlineStr">
+        <is>
+          <t>متوسط مجموع البخر والنتح المرجعي الكامن لشهر أغسطس بطريقة هارجريفز-ساماني FAO-56.</t>
+        </is>
+      </c>
+      <c r="F244" s="19" t="inlineStr">
+        <is>
+          <t>ملم/شهر (mm/month)</t>
+        </is>
+      </c>
+      <c r="G244" s="30" t="inlineStr">
+        <is>
+          <t>خريطة مجموع البخر والنتح لشهر أغسطس (ملم/شهر)</t>
+        </is>
+      </c>
+    </row>
+    <row r="245" ht="24" customHeight="1">
+      <c r="A245" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="B245" s="5" t="inlineStr">
+        <is>
+          <t>ET_SepTot</t>
+        </is>
+      </c>
+      <c r="C245" s="31" t="inlineStr">
+        <is>
+          <t>ET_September_Total</t>
+        </is>
+      </c>
+      <c r="D245" s="15" t="inlineStr">
+        <is>
+          <t>14_Evapotranspiration (البخر والنتح)</t>
+        </is>
+      </c>
+      <c r="E245" s="7" t="inlineStr">
+        <is>
+          <t>متوسط مجموع البخر والنتح المرجعي الكامن لشهر سبتمبر بطريقة هارجريفز-ساماني FAO-56.</t>
+        </is>
+      </c>
+      <c r="F245" s="16" t="inlineStr">
+        <is>
+          <t>ملم/شهر (mm/month)</t>
+        </is>
+      </c>
+      <c r="G245" s="32" t="inlineStr">
+        <is>
+          <t>خريطة مجموع البخر والنتح لشهر سبتمبر (ملم/شهر)</t>
+        </is>
+      </c>
+    </row>
+    <row r="246" ht="24" customHeight="1">
+      <c r="A246" s="8" t="n">
+        <v>245</v>
+      </c>
+      <c r="B246" s="10" t="inlineStr">
+        <is>
+          <t>ET_OctTot</t>
+        </is>
+      </c>
+      <c r="C246" s="29" t="inlineStr">
+        <is>
+          <t>ET_October_Total</t>
+        </is>
+      </c>
+      <c r="D246" s="18" t="inlineStr">
+        <is>
+          <t>14_Evapotranspiration (البخر والنتح)</t>
+        </is>
+      </c>
+      <c r="E246" s="12" t="inlineStr">
+        <is>
+          <t>متوسط مجموع البخر والنتح المرجعي الكامن لشهر أكتوبر بطريقة هارجريفز-ساماني FAO-56.</t>
+        </is>
+      </c>
+      <c r="F246" s="19" t="inlineStr">
+        <is>
+          <t>ملم/شهر (mm/month)</t>
+        </is>
+      </c>
+      <c r="G246" s="30" t="inlineStr">
+        <is>
+          <t>خريطة مجموع البخر والنتح لشهر أكتوبر (ملم/شهر)</t>
+        </is>
+      </c>
+    </row>
+    <row r="247" ht="24" customHeight="1">
+      <c r="A247" s="3" t="n">
+        <v>246</v>
+      </c>
+      <c r="B247" s="5" t="inlineStr">
+        <is>
+          <t>ET_NovTot</t>
+        </is>
+      </c>
+      <c r="C247" s="31" t="inlineStr">
+        <is>
+          <t>ET_November_Total</t>
+        </is>
+      </c>
+      <c r="D247" s="15" t="inlineStr">
+        <is>
+          <t>14_Evapotranspiration (البخر والنتح)</t>
+        </is>
+      </c>
+      <c r="E247" s="7" t="inlineStr">
+        <is>
+          <t>متوسط مجموع البخر والنتح المرجعي الكامن لشهر نوفمبر بطريقة هارجريفز-ساماني FAO-56.</t>
+        </is>
+      </c>
+      <c r="F247" s="16" t="inlineStr">
+        <is>
+          <t>ملم/شهر (mm/month)</t>
+        </is>
+      </c>
+      <c r="G247" s="32" t="inlineStr">
+        <is>
+          <t>خريطة مجموع البخر والنتح لشهر نوفمبر (ملم/شهر)</t>
+        </is>
+      </c>
+    </row>
+    <row r="248" ht="24" customHeight="1">
+      <c r="A248" s="8" t="n">
+        <v>247</v>
+      </c>
+      <c r="B248" s="10" t="inlineStr">
+        <is>
+          <t>ET_DecTot</t>
+        </is>
+      </c>
+      <c r="C248" s="29" t="inlineStr">
+        <is>
+          <t>ET_December_Total</t>
+        </is>
+      </c>
+      <c r="D248" s="18" t="inlineStr">
+        <is>
+          <t>14_Evapotranspiration (البخر والنتح)</t>
+        </is>
+      </c>
+      <c r="E248" s="12" t="inlineStr">
+        <is>
+          <t>متوسط مجموع البخر والنتح المرجعي الكامن لشهر ديسمبر بطريقة هارجريفز-ساماني FAO-56.</t>
+        </is>
+      </c>
+      <c r="F248" s="19" t="inlineStr">
+        <is>
+          <t>ملم/شهر (mm/month)</t>
+        </is>
+      </c>
+      <c r="G248" s="30" t="inlineStr">
+        <is>
+          <t>خريطة مجموع البخر والنتح لشهر ديسمبر (ملم/شهر)</t>
+        </is>
+      </c>
+    </row>
+    <row r="249" ht="24" customHeight="1">
+      <c r="A249" s="3" t="n">
+        <v>248</v>
+      </c>
+      <c r="B249" s="5" t="inlineStr">
+        <is>
+          <t>UNEP_Arid</t>
+        </is>
+      </c>
+      <c r="C249" s="31" t="inlineStr">
+        <is>
+          <t>UNEP_Aridity_Annual</t>
+        </is>
+      </c>
+      <c r="D249" s="15" t="inlineStr">
+        <is>
+          <t>15_UNEP_Aridity (مؤشر UNEP)</t>
+        </is>
+      </c>
+      <c r="E249" s="7" t="inlineStr">
+        <is>
+          <t>مؤشر القحولة العالمي لبرنامج الأمم المتحدة للبيئة AI = P / ET_ann لتحديد المناطق القاحلة وشبه القاحلة.</t>
+        </is>
+      </c>
+      <c r="F249" s="16" t="inlineStr">
+        <is>
+          <t>نسبة (Ratio)</t>
+        </is>
+      </c>
+      <c r="G249" s="32" t="inlineStr">
+        <is>
+          <t>خريطة مؤشر القحولة العالمي لبرنامج الأمم المتحدة للبيئة</t>
+        </is>
+      </c>
+    </row>
+    <row r="250" ht="24" customHeight="1">
+      <c r="A250" s="8" t="n">
+        <v>249</v>
+      </c>
+      <c r="B250" s="10" t="inlineStr">
+        <is>
+          <t>WatDefAnn</t>
+        </is>
+      </c>
+      <c r="C250" s="29" t="inlineStr">
+        <is>
+          <t>Water_Deficit_Annual</t>
+        </is>
+      </c>
+      <c r="D250" s="18" t="inlineStr">
+        <is>
+          <t>16_Water_Deficit (العجز المائي)</t>
+        </is>
+      </c>
+      <c r="E250" s="12" t="inlineStr">
+        <is>
+          <t>الموازنة المائية المناخية السنوية الصافية WD = P - ET_ann (القيم السالبة تعبر عن عجز مائي والموجبة فائض مائي).</t>
+        </is>
+      </c>
+      <c r="F250" s="19" t="inlineStr">
+        <is>
+          <t>ملم (mm)</t>
+        </is>
+      </c>
+      <c r="G250" s="30" t="inlineStr">
+        <is>
+          <t>خريطة الموازنة والعجز المائي المناخي السنوي (ملم)</t>
+        </is>
+      </c>
+    </row>
+    <row r="251" ht="24" customHeight="1">
+      <c r="A251" s="3" t="n">
+        <v>250</v>
+      </c>
+      <c r="B251" s="5" t="inlineStr">
+        <is>
+          <t>Dry_Months</t>
+        </is>
+      </c>
+      <c r="C251" s="31" t="inlineStr">
+        <is>
+          <t>Dry_Months_Count</t>
+        </is>
+      </c>
+      <c r="D251" s="15" t="inlineStr">
+        <is>
+          <t>17_Dry_Months (الأشهر الجافة)</t>
+        </is>
+      </c>
+      <c r="E251" s="7" t="inlineStr">
+        <is>
+          <t>عدد أشهر السنة الجافة بيولوجياً ومناخياً وفق معيار والتر-ليث البيومناخي الشهير (P &lt; 2T).</t>
+        </is>
+      </c>
+      <c r="F251" s="16" t="inlineStr">
+        <is>
+          <t>شهر (0-12)</t>
+        </is>
+      </c>
+      <c r="G251" s="32" t="inlineStr">
+        <is>
+          <t>خريطة عدد الأشهر الجافة بيولوجياً في السنة</t>
+        </is>
+      </c>
+    </row>
+    <row r="252" ht="24" customHeight="1">
+      <c r="A252" s="8" t="n">
+        <v>251</v>
+      </c>
+      <c r="B252" s="10" t="inlineStr">
+        <is>
+          <t>T_TrendDec</t>
+        </is>
+      </c>
+      <c r="C252" s="29" t="inlineStr">
+        <is>
+          <t>T_Trend_Decade</t>
+        </is>
+      </c>
+      <c r="D252" s="18" t="inlineStr">
+        <is>
+          <t>18_Trends_And_Anomalies (الاتجاهات والشذوذ)</t>
+        </is>
+      </c>
+      <c r="E252" s="12" t="inlineStr">
+        <is>
+          <t>معدل تغير واتجاه درجة الحرارة لكل عقد زمني (10 سنوات) باستخدام انحدار المربعات الصغرى الخطي.</t>
+        </is>
+      </c>
+      <c r="F252" s="19" t="inlineStr">
+        <is>
+          <t>°C/decade</t>
+        </is>
+      </c>
+      <c r="G252" s="30" t="inlineStr">
+        <is>
+          <t>خريطة اتجاه تغير درجة الحرارة في العقد الزمني (°C/decade)</t>
+        </is>
+      </c>
+    </row>
+    <row r="253" ht="24" customHeight="1">
+      <c r="A253" s="3" t="n">
+        <v>252</v>
+      </c>
+      <c r="B253" s="5" t="inlineStr">
+        <is>
+          <t>R_TrendDec</t>
+        </is>
+      </c>
+      <c r="C253" s="31" t="inlineStr">
+        <is>
+          <t>R_Trend_Decade</t>
+        </is>
+      </c>
+      <c r="D253" s="15" t="inlineStr">
+        <is>
+          <t>18_Trends_And_Anomalies (الاتجاهات والشذوذ)</t>
+        </is>
+      </c>
+      <c r="E253" s="7" t="inlineStr">
+        <is>
+          <t>معدل تغير واتجاه تساقط الأمطار لكل عقد زمني (10 سنوات) باستخدام انحدار المربعات الصغرى الخطي.</t>
+        </is>
+      </c>
+      <c r="F253" s="16" t="inlineStr">
+        <is>
+          <t>mm/decade</t>
+        </is>
+      </c>
+      <c r="G253" s="32" t="inlineStr">
+        <is>
+          <t>خريطة اتجاه تغير تساقط الأمطار في العقد الزمني (mm/decade)</t>
+        </is>
+      </c>
+    </row>
+    <row r="254" ht="24" customHeight="1">
+      <c r="A254" s="8" t="n">
+        <v>253</v>
+      </c>
+      <c r="B254" s="10" t="inlineStr">
+        <is>
+          <t>T_AnomAnn</t>
+        </is>
+      </c>
+      <c r="C254" s="29" t="inlineStr">
+        <is>
+          <t>T_Anom_Annual</t>
+        </is>
+      </c>
+      <c r="D254" s="18" t="inlineStr">
+        <is>
+          <t>18_Trends_And_Anomalies (الاتجاهات والشذوذ)</t>
+        </is>
+      </c>
+      <c r="E254" s="12" t="inlineStr">
+        <is>
+          <t>الشذوذ الحراري السنوي لدرجة الحرارة مقارنة بخط الأساس المناخي العالمي 1991–2020.</t>
+        </is>
+      </c>
+      <c r="F254" s="19" t="inlineStr">
+        <is>
+          <t>°C</t>
+        </is>
+      </c>
+      <c r="G254" s="30" t="inlineStr">
+        <is>
+          <t>خريطة الشذوذ الحراري السنوي مقارنة بخط أساس 1991–2020 (°C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="255" ht="24" customHeight="1">
+      <c r="A255" s="3" t="n">
+        <v>254</v>
+      </c>
+      <c r="B255" s="5" t="inlineStr">
+        <is>
+          <t>T_AnomWin</t>
+        </is>
+      </c>
+      <c r="C255" s="31" t="inlineStr">
+        <is>
+          <t>T_Anom_Winter</t>
+        </is>
+      </c>
+      <c r="D255" s="15" t="inlineStr">
+        <is>
+          <t>18_Trends_And_Anomalies (الاتجاهات والشذوذ)</t>
+        </is>
+      </c>
+      <c r="E255" s="7" t="inlineStr">
+        <is>
+          <t>الشذوذ الحراري لفصل الشتاء مقارنة بمتوسط شهور الشتاء لخط الأساس المناخي 1991–2020.</t>
+        </is>
+      </c>
+      <c r="F255" s="16" t="inlineStr">
+        <is>
+          <t>°C</t>
+        </is>
+      </c>
+      <c r="G255" s="32" t="inlineStr">
+        <is>
+          <t>خريطة الشذوذ الحراري لفصل الشتاء مقارنة بخط أساس 1991–2020 (°C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="256" ht="24" customHeight="1">
+      <c r="A256" s="8" t="n">
+        <v>255</v>
+      </c>
+      <c r="B256" s="10" t="inlineStr">
+        <is>
+          <t>T_AnomSum</t>
+        </is>
+      </c>
+      <c r="C256" s="29" t="inlineStr">
+        <is>
+          <t>T_Anom_Summer</t>
+        </is>
+      </c>
+      <c r="D256" s="18" t="inlineStr">
+        <is>
+          <t>18_Trends_And_Anomalies (الاتجاهات والشذوذ)</t>
+        </is>
+      </c>
+      <c r="E256" s="12" t="inlineStr">
+        <is>
+          <t>الشذوذ الحراري لفصل الصيف مقارنة بمتوسط شهور الصيف لخط الأساس المناخي 1991–2020.</t>
+        </is>
+      </c>
+      <c r="F256" s="19" t="inlineStr">
+        <is>
+          <t>°C</t>
+        </is>
+      </c>
+      <c r="G256" s="30" t="inlineStr">
+        <is>
+          <t>خريطة الشذوذ الحراري لفصل الصيف مقارنة بخط أساس 1991–2020 (°C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="257" ht="24" customHeight="1">
+      <c r="A257" s="3" t="n">
+        <v>256</v>
+      </c>
+      <c r="B257" s="5" t="inlineStr">
+        <is>
+          <t>R_AnomAnn</t>
+        </is>
+      </c>
+      <c r="C257" s="31" t="inlineStr">
+        <is>
+          <t>R_Anom_Annual</t>
+        </is>
+      </c>
+      <c r="D257" s="15" t="inlineStr">
+        <is>
+          <t>18_Trends_And_Anomalies (الاتجاهات والشذوذ)</t>
+        </is>
+      </c>
+      <c r="E257" s="7" t="inlineStr">
+        <is>
+          <t>شذوذ الأمطار السنوي المطلق مقارنة بمتوسط الأمطار لخط الأساس المناخي 1991–2020.</t>
+        </is>
+      </c>
+      <c r="F257" s="16" t="inlineStr">
+        <is>
+          <t>ملم (mm)</t>
+        </is>
+      </c>
+      <c r="G257" s="32" t="inlineStr">
+        <is>
+          <t>خريطة شذوذ تساقط الأمطار السنوي مقارنة بخط أساس 1991–2020 (ملم)</t>
+        </is>
+      </c>
+    </row>
+    <row r="258" ht="24" customHeight="1">
+      <c r="A258" s="8" t="n">
+        <v>257</v>
+      </c>
+      <c r="B258" s="10" t="inlineStr">
+        <is>
+          <t>R_AnomPct</t>
+        </is>
+      </c>
+      <c r="C258" s="29" t="inlineStr">
+        <is>
+          <t>R_Anom_Annual_Pct</t>
+        </is>
+      </c>
+      <c r="D258" s="18" t="inlineStr">
+        <is>
+          <t>18_Trends_And_Anomalies (الاتجاهات والشذوذ)</t>
+        </is>
+      </c>
+      <c r="E258" s="12" t="inlineStr">
+        <is>
+          <t>شذوذ الأمطار السنوي كنسبة مئوية من خط الأساس المناخي 1991–2020 (فرق نسبي مئوي).</t>
+        </is>
+      </c>
+      <c r="F258" s="19" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="G258" s="30" t="inlineStr">
+        <is>
+          <t>خريطة الشذوذ النسبي المئوي للأمطار مقارنة بخط أساس 1991–2020 (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="259" ht="24" customHeight="1">
+      <c r="A259" s="3" t="n">
+        <v>258</v>
+      </c>
+      <c r="B259" s="5" t="inlineStr">
+        <is>
+          <t>R_AnomWin</t>
+        </is>
+      </c>
+      <c r="C259" s="31" t="inlineStr">
+        <is>
+          <t>R_Anom_Winter</t>
+        </is>
+      </c>
+      <c r="D259" s="15" t="inlineStr">
+        <is>
+          <t>18_Trends_And_Anomalies (الاتجاهات والشذوذ)</t>
+        </is>
+      </c>
+      <c r="E259" s="7" t="inlineStr">
+        <is>
+          <t>شذوذ أمطار فصل الشتاء المطلق مقارنة بأمطار شتاء خط الأساس المناخي 1991–2020.</t>
+        </is>
+      </c>
+      <c r="F259" s="16" t="inlineStr">
+        <is>
+          <t>ملم (mm)</t>
+        </is>
+      </c>
+      <c r="G259" s="32" t="inlineStr">
+        <is>
+          <t>خريطة شذوذ أمطار الشتاء مقارنة بخط أساس 1991–2020 (ملم)</t>
+        </is>
+      </c>
+    </row>
+    <row r="260" ht="24" customHeight="1">
+      <c r="A260" s="8" t="n">
+        <v>259</v>
+      </c>
+      <c r="B260" s="10" t="inlineStr">
+        <is>
           <t>R_AnomWPct</t>
         </is>
       </c>
-      <c r="C116" s="29" t="inlineStr">
+      <c r="C260" s="29" t="inlineStr">
         <is>
           <t>R_Anom_Winter_Pct</t>
         </is>
       </c>
-      <c r="D116" s="18" t="inlineStr">
+      <c r="D260" s="18" t="inlineStr">
         <is>
           <t>18_Trends_And_Anomalies (الاتجاهات والشذوذ)</t>
         </is>
       </c>
-      <c r="E116" s="12" t="inlineStr">
+      <c r="E260" s="12" t="inlineStr">
         <is>
           <t>شذوذ أمطار فصل الشتاء كنسبة مئوية مقارنة بأمطار شتاء خط الأساس المناخي 1991–2020.</t>
         </is>
       </c>
-      <c r="F116" s="19" t="inlineStr">
+      <c r="F260" s="19" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="G116" s="30" t="inlineStr">
+      <c r="G260" s="30" t="inlineStr">
         <is>
           <t>خريطة الشذوذ النسبي المئوي لأمطار الشتاء مقارنة بخط أساس 1991–2020 (%)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G116"/>
+  <autoFilter ref="A1:G260"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5851,7 +10891,7 @@
         </is>
       </c>
       <c r="F2" s="8" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G2" s="19" t="inlineStr">
         <is>
@@ -5891,7 +10931,7 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="G3" s="16" t="inlineStr">
         <is>
@@ -5931,7 +10971,7 @@
         </is>
       </c>
       <c r="F4" s="8" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="G4" s="19" t="inlineStr">
         <is>
@@ -5971,7 +11011,7 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="G5" s="16" t="inlineStr">
         <is>
@@ -6011,7 +11051,7 @@
         </is>
       </c>
       <c r="F6" s="8" t="n">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="G6" s="19" t="inlineStr">
         <is>
@@ -6051,7 +11091,7 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="G7" s="16" t="inlineStr">
         <is>
@@ -6091,7 +11131,7 @@
         </is>
       </c>
       <c r="F8" s="8" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="G8" s="19" t="inlineStr">
         <is>
@@ -6131,7 +11171,7 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G9" s="16" t="inlineStr">
         <is>
@@ -6171,7 +11211,7 @@
         </is>
       </c>
       <c r="F10" s="8" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="G10" s="19" t="inlineStr">
         <is>
@@ -6211,7 +11251,7 @@
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="G11" s="16" t="inlineStr">
         <is>
@@ -6371,7 +11411,7 @@
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="G15" s="16" t="inlineStr">
         <is>
@@ -6551,7 +11591,7 @@
         </is>
       </c>
       <c r="F20" s="34" t="n">
-        <v>103</v>
+        <v>247</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Climate_Atlas_Fields_Dictionary_AR_EN_Units.xlsx
+++ b/docs/Climate_Atlas_Fields_Dictionary_AR_EN_Units.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Modules_18_Summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Climate_Fields'!$A$1:$G$260</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Climate_Fields'!$A$1:$G$271</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Modules_18_Summary'!$A$1:$H$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         </is>
       </c>
       <c r="E17" s="8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F17" s="19" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F18" s="16" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="E19" s="8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F19" s="19" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F20" s="16" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G260"/>
+  <dimension ref="A1:G271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2185,12 +2185,12 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>T_WinMean</t>
+          <t>T_MonMean</t>
         </is>
       </c>
       <c r="C15" s="31" t="inlineStr">
         <is>
-          <t>T_Winter_Mean</t>
+          <t>T_Month_Mean</t>
         </is>
       </c>
       <c r="D15" s="15" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>متوسط درجة حرارة الهواء لفصل الشتاء الأرصادي (شهور ديسمبر، يناير، فبراير - DJF).</t>
+          <t>المتوسط الشهري لدرجة حرارة الهواء عند ارتفاع 2 متر (متوسط الـ 12 شهراً المناخي).</t>
         </is>
       </c>
       <c r="F15" s="16" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="G15" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط درجة الحرارة خلال فصل الشتاء (°C)</t>
+          <t>خريطة المتوسط الشهري لدرجة الحرارة (°C)</t>
         </is>
       </c>
     </row>
@@ -2220,12 +2220,12 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>T_SprMean</t>
+          <t>T_WinMean</t>
         </is>
       </c>
       <c r="C16" s="29" t="inlineStr">
         <is>
-          <t>T_Spring_Mean</t>
+          <t>T_Winter_Mean</t>
         </is>
       </c>
       <c r="D16" s="18" t="inlineStr">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>متوسط درجة حرارة الهواء لفصل الربيع الأرصادي (شهور مارس، أبريل، مايو - MAM).</t>
+          <t>متوسط درجة حرارة الهواء لفصل الشتاء الأرصادي (شهور ديسمبر، يناير، فبراير - DJF).</t>
         </is>
       </c>
       <c r="F16" s="19" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="G16" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط درجة الحرارة خلال فصل الربيع (°C)</t>
+          <t>خريطة متوسط درجة الحرارة خلال فصل الشتاء (°C)</t>
         </is>
       </c>
     </row>
@@ -2255,12 +2255,12 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>T_SumMean</t>
+          <t>T_SprMean</t>
         </is>
       </c>
       <c r="C17" s="31" t="inlineStr">
         <is>
-          <t>T_Summer_Mean</t>
+          <t>T_Spring_Mean</t>
         </is>
       </c>
       <c r="D17" s="15" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>متوسط درجة حرارة الهواء لفصل الصيف الأرصادي (شهور يونيو، يوليو، أغسطس - JJA).</t>
+          <t>متوسط درجة حرارة الهواء لفصل الربيع الأرصادي (شهور مارس، أبريل، مايو - MAM).</t>
         </is>
       </c>
       <c r="F17" s="16" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="G17" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط درجة الحرارة خلال فصل الصيف (°C)</t>
+          <t>خريطة متوسط درجة الحرارة خلال فصل الربيع (°C)</t>
         </is>
       </c>
     </row>
@@ -2290,12 +2290,12 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>T_AutMean</t>
+          <t>T_SumMean</t>
         </is>
       </c>
       <c r="C18" s="29" t="inlineStr">
         <is>
-          <t>T_Autumn_Mean</t>
+          <t>T_Summer_Mean</t>
         </is>
       </c>
       <c r="D18" s="18" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>متوسط درجة حرارة الهواء لفصل الخريف الأرصادي (شهور سبتمبر، أكتوبر، نوفمبر - SON).</t>
+          <t>متوسط درجة حرارة الهواء لفصل الصيف الأرصادي (شهور يونيو، يوليو، أغسطس - JJA).</t>
         </is>
       </c>
       <c r="F18" s="19" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="G18" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط درجة الحرارة خلال فصل الخريف (°C)</t>
+          <t>خريطة متوسط درجة الحرارة خلال فصل الصيف (°C)</t>
         </is>
       </c>
     </row>
@@ -2325,12 +2325,12 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>T_AnnRng</t>
+          <t>T_AutMean</t>
         </is>
       </c>
       <c r="C19" s="31" t="inlineStr">
         <is>
-          <t>T_Annual_Range</t>
+          <t>T_Autumn_Mean</t>
         </is>
       </c>
       <c r="D19" s="15" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>المدى الحراري السنوي (الفارق بين متوسط أدفأ شهور السنة ومتوسط أبرد شهور السنة).</t>
+          <t>متوسط درجة حرارة الهواء لفصل الخريف الأرصادي (شهور سبتمبر، أكتوبر، نوفمبر - SON).</t>
         </is>
       </c>
       <c r="F19" s="16" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="G19" s="32" t="inlineStr">
         <is>
-          <t>خريطة المدى الحراري السنوي لدرجات الحرارة (°C)</t>
+          <t>خريطة متوسط درجة الحرارة خلال فصل الخريف (°C)</t>
         </is>
       </c>
     </row>
@@ -2360,12 +2360,12 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>T_MaxSumMo</t>
+          <t>T_AnnRng</t>
         </is>
       </c>
       <c r="C20" s="29" t="inlineStr">
         <is>
-          <t>T_Max_Summer_Month_Mean</t>
+          <t>T_Annual_Range</t>
         </is>
       </c>
       <c r="D20" s="18" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>متوسط درجة الحرارة لأدفأ شهور فصل الصيف (أعلى متوسط شهري مسجل في الصيف).</t>
+          <t>المدى الحراري السنوي (الفارق بين متوسط أدفأ شهور السنة ومتوسط أبرد شهور السنة).</t>
         </is>
       </c>
       <c r="F20" s="19" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="G20" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط أدفأ شهور فصل الصيف (°C)</t>
+          <t>خريطة المدى الحراري السنوي لدرجات الحرارة (°C)</t>
         </is>
       </c>
     </row>
@@ -2395,12 +2395,12 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>T_MinWinMo</t>
+          <t>T_MaxSumMo</t>
         </is>
       </c>
       <c r="C21" s="31" t="inlineStr">
         <is>
-          <t>T_Min_Winter_Month_Mean</t>
+          <t>T_Max_Summer_Month_Mean</t>
         </is>
       </c>
       <c r="D21" s="15" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>متوسط درجة الحرارة لأبرد شهور فصل الشتاء (أدنى متوسط شهري مسجل في الشتاء).</t>
+          <t>متوسط درجة الحرارة لأدفأ شهور فصل الصيف (أعلى متوسط شهري مسجل في الصيف).</t>
         </is>
       </c>
       <c r="F21" s="16" t="inlineStr">
@@ -2420,7 +2420,7 @@
       </c>
       <c r="G21" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط أبرد شهور فصل الشتاء (°C)</t>
+          <t>خريطة متوسط أدفأ شهور فصل الصيف (°C)</t>
         </is>
       </c>
     </row>
@@ -2430,12 +2430,12 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>T_MaxMean</t>
+          <t>T_MinWinMo</t>
         </is>
       </c>
       <c r="C22" s="29" t="inlineStr">
         <is>
-          <t>T_Annual_Max_Mean</t>
+          <t>T_Min_Winter_Month_Mean</t>
         </is>
       </c>
       <c r="D22" s="18" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
-          <t>المتوسط السنوي للنهايات العظمى اليومية لدرجة حرارة الهواء (T2M_MAX).</t>
+          <t>متوسط درجة الحرارة لأبرد شهور فصل الشتاء (أدنى متوسط شهري مسجل في الشتاء).</t>
         </is>
       </c>
       <c r="F22" s="19" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="G22" s="30" t="inlineStr">
         <is>
-          <t>خريطة المتوسط السنوي للنهايات العظمى لدرجة الحرارة (°C)</t>
+          <t>خريطة متوسط أبرد شهور فصل الشتاء (°C)</t>
         </is>
       </c>
     </row>
@@ -2465,12 +2465,12 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>T_MinMean</t>
+          <t>T_MaxMean</t>
         </is>
       </c>
       <c r="C23" s="31" t="inlineStr">
         <is>
-          <t>T_Annual_Min_Mean</t>
+          <t>T_Annual_Max_Mean</t>
         </is>
       </c>
       <c r="D23" s="15" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>المتوسط السنوي للنهايات الصغرى اليومية لدرجة حرارة الهواء (T2M_MIN).</t>
+          <t>المتوسط السنوي للنهايات العظمى اليومية لدرجة حرارة الهواء (T2M_MAX).</t>
         </is>
       </c>
       <c r="F23" s="16" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="G23" s="32" t="inlineStr">
         <is>
-          <t>خريطة المتوسط السنوي للنهايات الصغرى لدرجة الحرارة (°C)</t>
+          <t>خريطة المتوسط السنوي للنهايات العظمى لدرجة الحرارة (°C)</t>
         </is>
       </c>
     </row>
@@ -2500,12 +2500,12 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>T_JanMean</t>
+          <t>T_MinMean</t>
         </is>
       </c>
       <c r="C24" s="29" t="inlineStr">
         <is>
-          <t>T_January_Mean</t>
+          <t>T_Annual_Min_Mean</t>
         </is>
       </c>
       <c r="D24" s="18" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>المتوسط الحسابي لدرجة حرارة الهواء عند ارتفاع 2 متر لشهر يناير عبر فترة الرصد 1996–2025.</t>
+          <t>المتوسط السنوي للنهايات الصغرى اليومية لدرجة حرارة الهواء (T2M_MIN).</t>
         </is>
       </c>
       <c r="F24" s="19" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="G24" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط درجة الحرارة لشهر يناير (°C)</t>
+          <t>خريطة المتوسط السنوي للنهايات الصغرى لدرجة الحرارة (°C)</t>
         </is>
       </c>
     </row>
@@ -2535,12 +2535,12 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>T_FebMean</t>
+          <t>T_JanMean</t>
         </is>
       </c>
       <c r="C25" s="31" t="inlineStr">
         <is>
-          <t>T_February_Mean</t>
+          <t>T_January_Mean</t>
         </is>
       </c>
       <c r="D25" s="15" t="inlineStr">
@@ -2550,7 +2550,7 @@
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>المتوسط الحسابي لدرجة حرارة الهواء عند ارتفاع 2 متر لشهر فبراير عبر فترة الرصد 1996–2025.</t>
+          <t>المتوسط الحسابي لدرجة حرارة الهواء عند ارتفاع 2 متر لشهر يناير عبر فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F25" s="16" t="inlineStr">
@@ -2560,7 +2560,7 @@
       </c>
       <c r="G25" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط درجة الحرارة لشهر فبراير (°C)</t>
+          <t>خريطة متوسط درجة الحرارة لشهر يناير (°C)</t>
         </is>
       </c>
     </row>
@@ -2570,12 +2570,12 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>T_MarMean</t>
+          <t>T_FebMean</t>
         </is>
       </c>
       <c r="C26" s="29" t="inlineStr">
         <is>
-          <t>T_March_Mean</t>
+          <t>T_February_Mean</t>
         </is>
       </c>
       <c r="D26" s="18" t="inlineStr">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
-          <t>المتوسط الحسابي لدرجة حرارة الهواء عند ارتفاع 2 متر لشهر مارس عبر فترة الرصد 1996–2025.</t>
+          <t>المتوسط الحسابي لدرجة حرارة الهواء عند ارتفاع 2 متر لشهر فبراير عبر فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F26" s="19" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="G26" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط درجة الحرارة لشهر مارس (°C)</t>
+          <t>خريطة متوسط درجة الحرارة لشهر فبراير (°C)</t>
         </is>
       </c>
     </row>
@@ -2605,12 +2605,12 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>T_AprMean</t>
+          <t>T_MarMean</t>
         </is>
       </c>
       <c r="C27" s="31" t="inlineStr">
         <is>
-          <t>T_April_Mean</t>
+          <t>T_March_Mean</t>
         </is>
       </c>
       <c r="D27" s="15" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>المتوسط الحسابي لدرجة حرارة الهواء عند ارتفاع 2 متر لشهر أبريل عبر فترة الرصد 1996–2025.</t>
+          <t>المتوسط الحسابي لدرجة حرارة الهواء عند ارتفاع 2 متر لشهر مارس عبر فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F27" s="16" t="inlineStr">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="G27" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط درجة الحرارة لشهر أبريل (°C)</t>
+          <t>خريطة متوسط درجة الحرارة لشهر مارس (°C)</t>
         </is>
       </c>
     </row>
@@ -2640,12 +2640,12 @@
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>T_MayMean</t>
+          <t>T_AprMean</t>
         </is>
       </c>
       <c r="C28" s="29" t="inlineStr">
         <is>
-          <t>T_May_Mean</t>
+          <t>T_April_Mean</t>
         </is>
       </c>
       <c r="D28" s="18" t="inlineStr">
@@ -2655,7 +2655,7 @@
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>المتوسط الحسابي لدرجة حرارة الهواء عند ارتفاع 2 متر لشهر مايو عبر فترة الرصد 1996–2025.</t>
+          <t>المتوسط الحسابي لدرجة حرارة الهواء عند ارتفاع 2 متر لشهر أبريل عبر فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F28" s="19" t="inlineStr">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="G28" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط درجة الحرارة لشهر مايو (°C)</t>
+          <t>خريطة متوسط درجة الحرارة لشهر أبريل (°C)</t>
         </is>
       </c>
     </row>
@@ -2675,12 +2675,12 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>T_JunMean</t>
+          <t>T_MayMean</t>
         </is>
       </c>
       <c r="C29" s="31" t="inlineStr">
         <is>
-          <t>T_June_Mean</t>
+          <t>T_May_Mean</t>
         </is>
       </c>
       <c r="D29" s="15" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>المتوسط الحسابي لدرجة حرارة الهواء عند ارتفاع 2 متر لشهر يونيو عبر فترة الرصد 1996–2025.</t>
+          <t>المتوسط الحسابي لدرجة حرارة الهواء عند ارتفاع 2 متر لشهر مايو عبر فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F29" s="16" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="G29" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط درجة الحرارة لشهر يونيو (°C)</t>
+          <t>خريطة متوسط درجة الحرارة لشهر مايو (°C)</t>
         </is>
       </c>
     </row>
@@ -2710,12 +2710,12 @@
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>T_JulMean</t>
+          <t>T_JunMean</t>
         </is>
       </c>
       <c r="C30" s="29" t="inlineStr">
         <is>
-          <t>T_July_Mean</t>
+          <t>T_June_Mean</t>
         </is>
       </c>
       <c r="D30" s="18" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
-          <t>المتوسط الحسابي لدرجة حرارة الهواء عند ارتفاع 2 متر لشهر يوليو عبر فترة الرصد 1996–2025.</t>
+          <t>المتوسط الحسابي لدرجة حرارة الهواء عند ارتفاع 2 متر لشهر يونيو عبر فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F30" s="19" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="G30" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط درجة الحرارة لشهر يوليو (°C)</t>
+          <t>خريطة متوسط درجة الحرارة لشهر يونيو (°C)</t>
         </is>
       </c>
     </row>
@@ -2745,12 +2745,12 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>T_AugMean</t>
+          <t>T_JulMean</t>
         </is>
       </c>
       <c r="C31" s="31" t="inlineStr">
         <is>
-          <t>T_August_Mean</t>
+          <t>T_July_Mean</t>
         </is>
       </c>
       <c r="D31" s="15" t="inlineStr">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>المتوسط الحسابي لدرجة حرارة الهواء عند ارتفاع 2 متر لشهر أغسطس عبر فترة الرصد 1996–2025.</t>
+          <t>المتوسط الحسابي لدرجة حرارة الهواء عند ارتفاع 2 متر لشهر يوليو عبر فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F31" s="16" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="G31" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط درجة الحرارة لشهر أغسطس (°C)</t>
+          <t>خريطة متوسط درجة الحرارة لشهر يوليو (°C)</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>T_SepMean</t>
+          <t>T_AugMean</t>
         </is>
       </c>
       <c r="C32" s="29" t="inlineStr">
         <is>
-          <t>T_September_Mean</t>
+          <t>T_August_Mean</t>
         </is>
       </c>
       <c r="D32" s="18" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>المتوسط الحسابي لدرجة حرارة الهواء عند ارتفاع 2 متر لشهر سبتمبر عبر فترة الرصد 1996–2025.</t>
+          <t>المتوسط الحسابي لدرجة حرارة الهواء عند ارتفاع 2 متر لشهر أغسطس عبر فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F32" s="19" t="inlineStr">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="G32" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط درجة الحرارة لشهر سبتمبر (°C)</t>
+          <t>خريطة متوسط درجة الحرارة لشهر أغسطس (°C)</t>
         </is>
       </c>
     </row>
@@ -2815,12 +2815,12 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>T_OctMean</t>
+          <t>T_SepMean</t>
         </is>
       </c>
       <c r="C33" s="31" t="inlineStr">
         <is>
-          <t>T_October_Mean</t>
+          <t>T_September_Mean</t>
         </is>
       </c>
       <c r="D33" s="15" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>المتوسط الحسابي لدرجة حرارة الهواء عند ارتفاع 2 متر لشهر أكتوبر عبر فترة الرصد 1996–2025.</t>
+          <t>المتوسط الحسابي لدرجة حرارة الهواء عند ارتفاع 2 متر لشهر سبتمبر عبر فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F33" s="16" t="inlineStr">
@@ -2840,7 +2840,7 @@
       </c>
       <c r="G33" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط درجة الحرارة لشهر أكتوبر (°C)</t>
+          <t>خريطة متوسط درجة الحرارة لشهر سبتمبر (°C)</t>
         </is>
       </c>
     </row>
@@ -2850,12 +2850,12 @@
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>T_NovMean</t>
+          <t>T_OctMean</t>
         </is>
       </c>
       <c r="C34" s="29" t="inlineStr">
         <is>
-          <t>T_November_Mean</t>
+          <t>T_October_Mean</t>
         </is>
       </c>
       <c r="D34" s="18" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>المتوسط الحسابي لدرجة حرارة الهواء عند ارتفاع 2 متر لشهر نوفمبر عبر فترة الرصد 1996–2025.</t>
+          <t>المتوسط الحسابي لدرجة حرارة الهواء عند ارتفاع 2 متر لشهر أكتوبر عبر فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F34" s="19" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="G34" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط درجة الحرارة لشهر نوفمبر (°C)</t>
+          <t>خريطة متوسط درجة الحرارة لشهر أكتوبر (°C)</t>
         </is>
       </c>
     </row>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>T_DecMean</t>
+          <t>T_NovMean</t>
         </is>
       </c>
       <c r="C35" s="31" t="inlineStr">
         <is>
-          <t>T_December_Mean</t>
+          <t>T_November_Mean</t>
         </is>
       </c>
       <c r="D35" s="15" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>المتوسط الحسابي لدرجة حرارة الهواء عند ارتفاع 2 متر لشهر ديسمبر عبر فترة الرصد 1996–2025.</t>
+          <t>المتوسط الحسابي لدرجة حرارة الهواء عند ارتفاع 2 متر لشهر نوفمبر عبر فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F35" s="16" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="G35" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط درجة الحرارة لشهر ديسمبر (°C)</t>
+          <t>خريطة متوسط درجة الحرارة لشهر نوفمبر (°C)</t>
         </is>
       </c>
     </row>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>HI_AnnMean</t>
+          <t>T_DecMean</t>
         </is>
       </c>
       <c r="C36" s="29" t="inlineStr">
         <is>
-          <t>HI_Annual_Mean</t>
+          <t>T_December_Mean</t>
         </is>
       </c>
       <c r="D36" s="18" t="inlineStr">
         <is>
-          <t>11_Heat_Index (مؤشر الحرارة)</t>
+          <t>01_Temperature (درجة الحرارة)</t>
         </is>
       </c>
       <c r="E36" s="12" t="inlineStr">
         <is>
-          <t>المتوسط السنوي لمؤشر الحرارة المحسوسة المحسوب بمعادلة روتفوش وستيدمان للحرارة والرطوبة.</t>
+          <t>المتوسط الحسابي لدرجة حرارة الهواء عند ارتفاع 2 متر لشهر ديسمبر عبر فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F36" s="19" t="inlineStr">
@@ -2945,7 +2945,7 @@
       </c>
       <c r="G36" s="30" t="inlineStr">
         <is>
-          <t>خريطة المتوسط السنوي لمؤشر الحرارة المحسوسة (°C)</t>
+          <t>خريطة متوسط درجة الحرارة لشهر ديسمبر (°C)</t>
         </is>
       </c>
     </row>
@@ -2955,12 +2955,12 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>HI_SumMean</t>
+          <t>HI_AnnMean</t>
         </is>
       </c>
       <c r="C37" s="31" t="inlineStr">
         <is>
-          <t>HI_Summer_Mean</t>
+          <t>HI_Annual_Mean</t>
         </is>
       </c>
       <c r="D37" s="15" t="inlineStr">
@@ -2970,7 +2970,7 @@
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>متوسط مؤشر الحرارة المحسوسة خلال فصل الصيف (مقياس الإجهاد الحراري الفعلي).</t>
+          <t>المتوسط السنوي لمؤشر الحرارة المحسوسة المحسوب بمعادلة روتفوش وستيدمان للحرارة والرطوبة.</t>
         </is>
       </c>
       <c r="F37" s="16" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="G37" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط مؤشر الحرارة المحسوسة خلال فصل الصيف (°C)</t>
+          <t>خريطة المتوسط السنوي لمؤشر الحرارة المحسوسة (°C)</t>
         </is>
       </c>
     </row>
@@ -2990,12 +2990,12 @@
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>HI_WinMean</t>
+          <t>HI_SumMean</t>
         </is>
       </c>
       <c r="C38" s="29" t="inlineStr">
         <is>
-          <t>HI_Winter_Mean</t>
+          <t>HI_Summer_Mean</t>
         </is>
       </c>
       <c r="D38" s="18" t="inlineStr">
@@ -3005,7 +3005,7 @@
       </c>
       <c r="E38" s="12" t="inlineStr">
         <is>
-          <t>متوسط مؤشر الحرارة الظاهرية/الهيوميدكس خلال فصل الشتاء في الأجواء الباردة والرطبة.</t>
+          <t>متوسط مؤشر الحرارة المحسوسة خلال فصل الصيف (مقياس الإجهاد الحراري الفعلي).</t>
         </is>
       </c>
       <c r="F38" s="19" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="G38" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط درجة الحرارة المحسوسة خلال فصل الشتاء (°C)</t>
+          <t>خريطة متوسط مؤشر الحرارة المحسوسة خلال فصل الصيف (°C)</t>
         </is>
       </c>
     </row>
@@ -3025,12 +3025,12 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>HI_AnRng</t>
+          <t>HI_WinMean</t>
         </is>
       </c>
       <c r="C39" s="31" t="inlineStr">
         <is>
-          <t>HI_Annual_Range</t>
+          <t>HI_Winter_Mean</t>
         </is>
       </c>
       <c r="D39" s="15" t="inlineStr">
@@ -3040,7 +3040,7 @@
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>المدى السنوي لمؤشر الحرارة المحسوسة (الفارق بين أعلى شهر إجهاد حراري وأدنى شهر).</t>
+          <t>متوسط مؤشر الحرارة الظاهرية/الهيوميدكس خلال فصل الشتاء في الأجواء الباردة والرطبة.</t>
         </is>
       </c>
       <c r="F39" s="16" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="G39" s="32" t="inlineStr">
         <is>
-          <t>خريطة المدى السنوي لمؤشر الحرارة المحسوسة (°C)</t>
+          <t>خريطة متوسط درجة الحرارة المحسوسة خلال فصل الشتاء (°C)</t>
         </is>
       </c>
     </row>
@@ -3060,12 +3060,12 @@
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>WBGT_SuMn</t>
+          <t>HI_AnRng</t>
         </is>
       </c>
       <c r="C40" s="29" t="inlineStr">
         <is>
-          <t>WBGT_Summer_Mean</t>
+          <t>HI_Annual_Range</t>
         </is>
       </c>
       <c r="D40" s="18" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
-          <t>متوسط درجة حرارة البصيلة الرطبة الكروية الصيفي في الظل (معيار ISO 7243 للإجهاد المهني والرياضي).</t>
+          <t>المدى السنوي لمؤشر الحرارة المحسوسة (الفارق بين أعلى شهر إجهاد حراري وأدنى شهر).</t>
         </is>
       </c>
       <c r="F40" s="19" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="G40" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط مؤشر الإجهاد الحراري الصيفي (WBGT) (°C)</t>
+          <t>خريطة المدى السنوي لمؤشر الحرارة المحسوسة (°C)</t>
         </is>
       </c>
     </row>
@@ -3095,22 +3095,22 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Td_AnnMean</t>
+          <t>WBGT_SuMn</t>
         </is>
       </c>
       <c r="C41" s="31" t="inlineStr">
         <is>
-          <t>Td_Annual_Mean</t>
+          <t>WBGT_Summer_Mean</t>
         </is>
       </c>
       <c r="D41" s="15" t="inlineStr">
         <is>
-          <t>07_Dew_Point (نقطة الندى)</t>
+          <t>11_Heat_Index (مؤشر الحرارة)</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>المتوسط الحسابي السنوي لدرجة حرارة نقطة الندى عند ارتفاع 2 متر.</t>
+          <t>متوسط درجة حرارة البصيلة الرطبة الكروية الصيفي في الظل (معيار ISO 7243 للإجهاد المهني والرياضي).</t>
         </is>
       </c>
       <c r="F41" s="16" t="inlineStr">
@@ -3120,7 +3120,7 @@
       </c>
       <c r="G41" s="32" t="inlineStr">
         <is>
-          <t>خريطة المتوسط السنوي لدرجة حرارة نقطة الندى (°C)</t>
+          <t>خريطة متوسط مؤشر الإجهاد الحراري الصيفي (WBGT) (°C)</t>
         </is>
       </c>
     </row>
@@ -3130,12 +3130,12 @@
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>Td_WinMean</t>
+          <t>Td_AnnMean</t>
         </is>
       </c>
       <c r="C42" s="29" t="inlineStr">
         <is>
-          <t>Td_Winter_Mean</t>
+          <t>Td_Annual_Mean</t>
         </is>
       </c>
       <c r="D42" s="18" t="inlineStr">
@@ -3145,7 +3145,7 @@
       </c>
       <c r="E42" s="12" t="inlineStr">
         <is>
-          <t>متوسط درجة حرارة نقطة الندى خلال فصل الشتاء الأرصادي (DJF).</t>
+          <t>المتوسط الحسابي السنوي لدرجة حرارة نقطة الندى عند ارتفاع 2 متر.</t>
         </is>
       </c>
       <c r="F42" s="19" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="G42" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط درجة حرارة نقطة الندى خلال فصل الشتاء (°C)</t>
+          <t>خريطة المتوسط السنوي لدرجة حرارة نقطة الندى (°C)</t>
         </is>
       </c>
     </row>
@@ -3165,22 +3165,22 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Td_SprMean</t>
+          <t>Td_MonMean</t>
         </is>
       </c>
       <c r="C43" s="31" t="inlineStr">
         <is>
-          <t>Td_Spring_Mean</t>
+          <t>Td_Month_Mean</t>
         </is>
       </c>
       <c r="D43" s="15" t="inlineStr">
         <is>
-          <t>07_Dew_Point (نقطة الندى)</t>
+          <t>07_Dew_Point (درجة حرارة نقطة الندى)</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>متوسط درجة حرارة نقطة الندى خلال فصل الربيع الأرصادي (MAM).</t>
+          <t>المتوسط الشهري لدرجة حرارة نقطة الندى عند ارتفاع 2 متر (متوسط الـ 12 شهراً).</t>
         </is>
       </c>
       <c r="F43" s="16" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="G43" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط درجة حرارة نقطة الندى خلال فصل الربيع (°C)</t>
+          <t>خريطة المتوسط الشهري لنقطة الندى (°C)</t>
         </is>
       </c>
     </row>
@@ -3200,12 +3200,12 @@
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>Td_SumMean</t>
+          <t>Td_WinMean</t>
         </is>
       </c>
       <c r="C44" s="29" t="inlineStr">
         <is>
-          <t>Td_Summer_Mean</t>
+          <t>Td_Winter_Mean</t>
         </is>
       </c>
       <c r="D44" s="18" t="inlineStr">
@@ -3215,7 +3215,7 @@
       </c>
       <c r="E44" s="12" t="inlineStr">
         <is>
-          <t>متوسط درجة حرارة نقطة الندى خلال فصل الصيف الأرصادي (JJA - مؤشر مباشر للرطوبة الخانقة والكتمة).</t>
+          <t>متوسط درجة حرارة نقطة الندى خلال فصل الشتاء الأرصادي (DJF).</t>
         </is>
       </c>
       <c r="F44" s="19" t="inlineStr">
@@ -3225,7 +3225,7 @@
       </c>
       <c r="G44" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط درجة حرارة نقطة الندى خلال فصل الصيف (°C)</t>
+          <t>خريطة متوسط درجة حرارة نقطة الندى خلال فصل الشتاء (°C)</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Td_AutMean</t>
+          <t>Td_SprMean</t>
         </is>
       </c>
       <c r="C45" s="31" t="inlineStr">
         <is>
-          <t>Td_Autumn_Mean</t>
+          <t>Td_Spring_Mean</t>
         </is>
       </c>
       <c r="D45" s="15" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>متوسط درجة حرارة نقطة الندى خلال فصل الخريف الأرصادي (SON).</t>
+          <t>متوسط درجة حرارة نقطة الندى خلال فصل الربيع الأرصادي (MAM).</t>
         </is>
       </c>
       <c r="F45" s="16" t="inlineStr">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="G45" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط درجة حرارة نقطة الندى خلال فصل الخريف (°C)</t>
+          <t>خريطة متوسط درجة حرارة نقطة الندى خلال فصل الربيع (°C)</t>
         </is>
       </c>
     </row>
@@ -3270,12 +3270,12 @@
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>Td_AnnRng</t>
+          <t>Td_SumMean</t>
         </is>
       </c>
       <c r="C46" s="29" t="inlineStr">
         <is>
-          <t>Td_Annual_Range</t>
+          <t>Td_Summer_Mean</t>
         </is>
       </c>
       <c r="D46" s="18" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="E46" s="12" t="inlineStr">
         <is>
-          <t>المدى السنوي لدرجة حرارة نقطة الندى (الفارق بين أعلى وأدنى متوسط شهري لنقطة الندى).</t>
+          <t>متوسط درجة حرارة نقطة الندى خلال فصل الصيف الأرصادي (JJA - مؤشر مباشر للرطوبة الخانقة والكتمة).</t>
         </is>
       </c>
       <c r="F46" s="19" t="inlineStr">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="G46" s="30" t="inlineStr">
         <is>
-          <t>خريطة المدى السنوي لدرجة حرارة نقطة الندى (°C)</t>
+          <t>خريطة متوسط درجة حرارة نقطة الندى خلال فصل الصيف (°C)</t>
         </is>
       </c>
     </row>
@@ -3305,12 +3305,12 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Td_JanMean</t>
+          <t>Td_AutMean</t>
         </is>
       </c>
       <c r="C47" s="31" t="inlineStr">
         <is>
-          <t>Td_January_Mean</t>
+          <t>Td_Autumn_Mean</t>
         </is>
       </c>
       <c r="D47" s="15" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>متوسط درجة حرارة نقطة الندى عند ارتفاع 2 متر لشهر يناير.</t>
+          <t>متوسط درجة حرارة نقطة الندى خلال فصل الخريف الأرصادي (SON).</t>
         </is>
       </c>
       <c r="F47" s="16" t="inlineStr">
@@ -3330,7 +3330,7 @@
       </c>
       <c r="G47" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط درجة حرارة نقطة الندى لشهر يناير (°C)</t>
+          <t>خريطة متوسط درجة حرارة نقطة الندى خلال فصل الخريف (°C)</t>
         </is>
       </c>
     </row>
@@ -3340,12 +3340,12 @@
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>Td_FebMean</t>
+          <t>Td_AnnRng</t>
         </is>
       </c>
       <c r="C48" s="29" t="inlineStr">
         <is>
-          <t>Td_February_Mean</t>
+          <t>Td_Annual_Range</t>
         </is>
       </c>
       <c r="D48" s="18" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="E48" s="12" t="inlineStr">
         <is>
-          <t>متوسط درجة حرارة نقطة الندى عند ارتفاع 2 متر لشهر فبراير.</t>
+          <t>المدى السنوي لدرجة حرارة نقطة الندى (الفارق بين أعلى وأدنى متوسط شهري لنقطة الندى).</t>
         </is>
       </c>
       <c r="F48" s="19" t="inlineStr">
@@ -3365,7 +3365,7 @@
       </c>
       <c r="G48" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط درجة حرارة نقطة الندى لشهر فبراير (°C)</t>
+          <t>خريطة المدى السنوي لدرجة حرارة نقطة الندى (°C)</t>
         </is>
       </c>
     </row>
@@ -3375,12 +3375,12 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Td_MarMean</t>
+          <t>Td_JanMean</t>
         </is>
       </c>
       <c r="C49" s="31" t="inlineStr">
         <is>
-          <t>Td_March_Mean</t>
+          <t>Td_January_Mean</t>
         </is>
       </c>
       <c r="D49" s="15" t="inlineStr">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>متوسط درجة حرارة نقطة الندى عند ارتفاع 2 متر لشهر مارس.</t>
+          <t>متوسط درجة حرارة نقطة الندى عند ارتفاع 2 متر لشهر يناير.</t>
         </is>
       </c>
       <c r="F49" s="16" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="G49" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط درجة حرارة نقطة الندى لشهر مارس (°C)</t>
+          <t>خريطة متوسط درجة حرارة نقطة الندى لشهر يناير (°C)</t>
         </is>
       </c>
     </row>
@@ -3410,12 +3410,12 @@
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>Td_AprMean</t>
+          <t>Td_FebMean</t>
         </is>
       </c>
       <c r="C50" s="29" t="inlineStr">
         <is>
-          <t>Td_April_Mean</t>
+          <t>Td_February_Mean</t>
         </is>
       </c>
       <c r="D50" s="18" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="E50" s="12" t="inlineStr">
         <is>
-          <t>متوسط درجة حرارة نقطة الندى عند ارتفاع 2 متر لشهر أبريل.</t>
+          <t>متوسط درجة حرارة نقطة الندى عند ارتفاع 2 متر لشهر فبراير.</t>
         </is>
       </c>
       <c r="F50" s="19" t="inlineStr">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="G50" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط درجة حرارة نقطة الندى لشهر أبريل (°C)</t>
+          <t>خريطة متوسط درجة حرارة نقطة الندى لشهر فبراير (°C)</t>
         </is>
       </c>
     </row>
@@ -3445,12 +3445,12 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Td_MayMean</t>
+          <t>Td_MarMean</t>
         </is>
       </c>
       <c r="C51" s="31" t="inlineStr">
         <is>
-          <t>Td_May_Mean</t>
+          <t>Td_March_Mean</t>
         </is>
       </c>
       <c r="D51" s="15" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>متوسط درجة حرارة نقطة الندى عند ارتفاع 2 متر لشهر مايو.</t>
+          <t>متوسط درجة حرارة نقطة الندى عند ارتفاع 2 متر لشهر مارس.</t>
         </is>
       </c>
       <c r="F51" s="16" t="inlineStr">
@@ -3470,7 +3470,7 @@
       </c>
       <c r="G51" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط درجة حرارة نقطة الندى لشهر مايو (°C)</t>
+          <t>خريطة متوسط درجة حرارة نقطة الندى لشهر مارس (°C)</t>
         </is>
       </c>
     </row>
@@ -3480,12 +3480,12 @@
       </c>
       <c r="B52" s="10" t="inlineStr">
         <is>
-          <t>Td_JunMean</t>
+          <t>Td_AprMean</t>
         </is>
       </c>
       <c r="C52" s="29" t="inlineStr">
         <is>
-          <t>Td_June_Mean</t>
+          <t>Td_April_Mean</t>
         </is>
       </c>
       <c r="D52" s="18" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="E52" s="12" t="inlineStr">
         <is>
-          <t>متوسط درجة حرارة نقطة الندى عند ارتفاع 2 متر لشهر يونيو.</t>
+          <t>متوسط درجة حرارة نقطة الندى عند ارتفاع 2 متر لشهر أبريل.</t>
         </is>
       </c>
       <c r="F52" s="19" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="G52" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط درجة حرارة نقطة الندى لشهر يونيو (°C)</t>
+          <t>خريطة متوسط درجة حرارة نقطة الندى لشهر أبريل (°C)</t>
         </is>
       </c>
     </row>
@@ -3515,12 +3515,12 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Td_JulMean</t>
+          <t>Td_MayMean</t>
         </is>
       </c>
       <c r="C53" s="31" t="inlineStr">
         <is>
-          <t>Td_July_Mean</t>
+          <t>Td_May_Mean</t>
         </is>
       </c>
       <c r="D53" s="15" t="inlineStr">
@@ -3530,7 +3530,7 @@
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>متوسط درجة حرارة نقطة الندى عند ارتفاع 2 متر لشهر يوليو.</t>
+          <t>متوسط درجة حرارة نقطة الندى عند ارتفاع 2 متر لشهر مايو.</t>
         </is>
       </c>
       <c r="F53" s="16" t="inlineStr">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="G53" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط درجة حرارة نقطة الندى لشهر يوليو (°C)</t>
+          <t>خريطة متوسط درجة حرارة نقطة الندى لشهر مايو (°C)</t>
         </is>
       </c>
     </row>
@@ -3550,12 +3550,12 @@
       </c>
       <c r="B54" s="10" t="inlineStr">
         <is>
-          <t>Td_AugMean</t>
+          <t>Td_JunMean</t>
         </is>
       </c>
       <c r="C54" s="29" t="inlineStr">
         <is>
-          <t>Td_August_Mean</t>
+          <t>Td_June_Mean</t>
         </is>
       </c>
       <c r="D54" s="18" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="E54" s="12" t="inlineStr">
         <is>
-          <t>متوسط درجة حرارة نقطة الندى عند ارتفاع 2 متر لشهر أغسطس.</t>
+          <t>متوسط درجة حرارة نقطة الندى عند ارتفاع 2 متر لشهر يونيو.</t>
         </is>
       </c>
       <c r="F54" s="19" t="inlineStr">
@@ -3575,7 +3575,7 @@
       </c>
       <c r="G54" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط درجة حرارة نقطة الندى لشهر أغسطس (°C)</t>
+          <t>خريطة متوسط درجة حرارة نقطة الندى لشهر يونيو (°C)</t>
         </is>
       </c>
     </row>
@@ -3585,12 +3585,12 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Td_SepMean</t>
+          <t>Td_JulMean</t>
         </is>
       </c>
       <c r="C55" s="31" t="inlineStr">
         <is>
-          <t>Td_September_Mean</t>
+          <t>Td_July_Mean</t>
         </is>
       </c>
       <c r="D55" s="15" t="inlineStr">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>متوسط درجة حرارة نقطة الندى عند ارتفاع 2 متر لشهر سبتمبر.</t>
+          <t>متوسط درجة حرارة نقطة الندى عند ارتفاع 2 متر لشهر يوليو.</t>
         </is>
       </c>
       <c r="F55" s="16" t="inlineStr">
@@ -3610,7 +3610,7 @@
       </c>
       <c r="G55" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط درجة حرارة نقطة الندى لشهر سبتمبر (°C)</t>
+          <t>خريطة متوسط درجة حرارة نقطة الندى لشهر يوليو (°C)</t>
         </is>
       </c>
     </row>
@@ -3620,12 +3620,12 @@
       </c>
       <c r="B56" s="10" t="inlineStr">
         <is>
-          <t>Td_OctMean</t>
+          <t>Td_AugMean</t>
         </is>
       </c>
       <c r="C56" s="29" t="inlineStr">
         <is>
-          <t>Td_October_Mean</t>
+          <t>Td_August_Mean</t>
         </is>
       </c>
       <c r="D56" s="18" t="inlineStr">
@@ -3635,7 +3635,7 @@
       </c>
       <c r="E56" s="12" t="inlineStr">
         <is>
-          <t>متوسط درجة حرارة نقطة الندى عند ارتفاع 2 متر لشهر أكتوبر.</t>
+          <t>متوسط درجة حرارة نقطة الندى عند ارتفاع 2 متر لشهر أغسطس.</t>
         </is>
       </c>
       <c r="F56" s="19" t="inlineStr">
@@ -3645,7 +3645,7 @@
       </c>
       <c r="G56" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط درجة حرارة نقطة الندى لشهر أكتوبر (°C)</t>
+          <t>خريطة متوسط درجة حرارة نقطة الندى لشهر أغسطس (°C)</t>
         </is>
       </c>
     </row>
@@ -3655,12 +3655,12 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Td_NovMean</t>
+          <t>Td_SepMean</t>
         </is>
       </c>
       <c r="C57" s="31" t="inlineStr">
         <is>
-          <t>Td_November_Mean</t>
+          <t>Td_September_Mean</t>
         </is>
       </c>
       <c r="D57" s="15" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
-          <t>متوسط درجة حرارة نقطة الندى عند ارتفاع 2 متر لشهر نوفمبر.</t>
+          <t>متوسط درجة حرارة نقطة الندى عند ارتفاع 2 متر لشهر سبتمبر.</t>
         </is>
       </c>
       <c r="F57" s="16" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="G57" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط درجة حرارة نقطة الندى لشهر نوفمبر (°C)</t>
+          <t>خريطة متوسط درجة حرارة نقطة الندى لشهر سبتمبر (°C)</t>
         </is>
       </c>
     </row>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="B58" s="10" t="inlineStr">
         <is>
-          <t>Td_DecMean</t>
+          <t>Td_OctMean</t>
         </is>
       </c>
       <c r="C58" s="29" t="inlineStr">
         <is>
-          <t>Td_December_Mean</t>
+          <t>Td_October_Mean</t>
         </is>
       </c>
       <c r="D58" s="18" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="E58" s="12" t="inlineStr">
         <is>
-          <t>متوسط درجة حرارة نقطة الندى عند ارتفاع 2 متر لشهر ديسمبر.</t>
+          <t>متوسط درجة حرارة نقطة الندى عند ارتفاع 2 متر لشهر أكتوبر.</t>
         </is>
       </c>
       <c r="F58" s="19" t="inlineStr">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="G58" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط درجة حرارة نقطة الندى لشهر ديسمبر (°C)</t>
+          <t>خريطة متوسط درجة حرارة نقطة الندى لشهر أكتوبر (°C)</t>
         </is>
       </c>
     </row>
@@ -3725,32 +3725,32 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>R_AnnMean</t>
+          <t>Td_NovMean</t>
         </is>
       </c>
       <c r="C59" s="31" t="inlineStr">
         <is>
-          <t>R_Annual_Mean</t>
+          <t>Td_November_Mean</t>
         </is>
       </c>
       <c r="D59" s="15" t="inlineStr">
         <is>
-          <t>02_Precipitation (الأمطار)</t>
+          <t>07_Dew_Point (نقطة الندى)</t>
         </is>
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>المتوسط السنوي لتساقط الأمطار (متوسط مجاميع السنين على مدار فترة الرصد 1996–2025).</t>
+          <t>متوسط درجة حرارة نقطة الندى عند ارتفاع 2 متر لشهر نوفمبر.</t>
         </is>
       </c>
       <c r="F59" s="16" t="inlineStr">
         <is>
-          <t>ملم (mm)</t>
+          <t>°C</t>
         </is>
       </c>
       <c r="G59" s="32" t="inlineStr">
         <is>
-          <t>خريطة المتوسط السنوي لتساقط الأمطار (ملم)</t>
+          <t>خريطة متوسط درجة حرارة نقطة الندى لشهر نوفمبر (°C)</t>
         </is>
       </c>
     </row>
@@ -3760,32 +3760,32 @@
       </c>
       <c r="B60" s="10" t="inlineStr">
         <is>
-          <t>R_MonMean</t>
+          <t>Td_DecMean</t>
         </is>
       </c>
       <c r="C60" s="29" t="inlineStr">
         <is>
-          <t>R_Month_Mean</t>
+          <t>Td_December_Mean</t>
         </is>
       </c>
       <c r="D60" s="18" t="inlineStr">
         <is>
-          <t>02_Precipitation (الأمطار)</t>
+          <t>07_Dew_Point (نقطة الندى)</t>
         </is>
       </c>
       <c r="E60" s="12" t="inlineStr">
         <is>
-          <t>المتوسط الشهري لتساقط الأمطار (المتوسط السنوي مقسوماً على 12 شهراً).</t>
+          <t>متوسط درجة حرارة نقطة الندى عند ارتفاع 2 متر لشهر ديسمبر.</t>
         </is>
       </c>
       <c r="F60" s="19" t="inlineStr">
         <is>
-          <t>ملم (mm)</t>
+          <t>°C</t>
         </is>
       </c>
       <c r="G60" s="30" t="inlineStr">
         <is>
-          <t>خريطة المتوسط الشهري لتساقط الأمطار (ملم)</t>
+          <t>خريطة متوسط درجة حرارة نقطة الندى لشهر ديسمبر (°C)</t>
         </is>
       </c>
     </row>
@@ -3795,12 +3795,12 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>R_AnnRng</t>
+          <t>R_AnnMean</t>
         </is>
       </c>
       <c r="C61" s="31" t="inlineStr">
         <is>
-          <t>R_Annual_Range</t>
+          <t>R_Annual_Mean</t>
         </is>
       </c>
       <c r="D61" s="15" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>المدى السنوي لتساقط الأمطار (الفارق بين أعلى شهر مطراً وأقل شهر مطراً في السنة).</t>
+          <t>المتوسط السنوي لتساقط الأمطار (متوسط مجاميع السنين على مدار فترة الرصد 1996–2025).</t>
         </is>
       </c>
       <c r="F61" s="16" t="inlineStr">
@@ -3820,7 +3820,7 @@
       </c>
       <c r="G61" s="32" t="inlineStr">
         <is>
-          <t>خريطة المدى السنوي لتساقط الأمطار (ملم)</t>
+          <t>خريطة المتوسط السنوي لتساقط الأمطار (ملم)</t>
         </is>
       </c>
     </row>
@@ -3830,12 +3830,12 @@
       </c>
       <c r="B62" s="10" t="inlineStr">
         <is>
-          <t>R_SeaRng</t>
+          <t>R_MonMean</t>
         </is>
       </c>
       <c r="C62" s="29" t="inlineStr">
         <is>
-          <t>R_Seasonal_Range</t>
+          <t>R_Month_Mean</t>
         </is>
       </c>
       <c r="D62" s="18" t="inlineStr">
@@ -3845,7 +3845,7 @@
       </c>
       <c r="E62" s="12" t="inlineStr">
         <is>
-          <t>المدى الفصلي لتساقط الأمطار (الفارق بين مجموع أعلى فصول السنة مطراً ومجموع أقلها مطراً).</t>
+          <t>المتوسط الشهري لتساقط الأمطار (المتوسط السنوي مقسوماً على 12 شهراً).</t>
         </is>
       </c>
       <c r="F62" s="19" t="inlineStr">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="G62" s="30" t="inlineStr">
         <is>
-          <t>خريطة المدى الفصلي لتساقط الأمطار (ملم)</t>
+          <t>خريطة المتوسط الشهري لتساقط الأمطار (ملم)</t>
         </is>
       </c>
     </row>
@@ -3865,12 +3865,12 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>R_WinMean</t>
+          <t>R_AnnRng</t>
         </is>
       </c>
       <c r="C63" s="31" t="inlineStr">
         <is>
-          <t>R_Winter_Mean</t>
+          <t>R_Annual_Range</t>
         </is>
       </c>
       <c r="D63" s="15" t="inlineStr">
@@ -3880,17 +3880,17 @@
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>متوسط هطول الأمطار خلال فصل الشتاء (شهور ديسمبر، يناير، فبراير - DJF).</t>
+          <t>المدى السنوي لتساقط الأمطار (الفارق بين أعلى شهر مطراً وأقل شهر مطراً في السنة).</t>
         </is>
       </c>
       <c r="F63" s="16" t="inlineStr">
         <is>
-          <t>مم/فصل (mm/season)</t>
+          <t>ملم (mm)</t>
         </is>
       </c>
       <c r="G63" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط هطول الأمطار خلال فصل الشتاء (مم/فصل)</t>
+          <t>خريطة المدى السنوي لتساقط الأمطار (ملم)</t>
         </is>
       </c>
     </row>
@@ -3900,12 +3900,12 @@
       </c>
       <c r="B64" s="10" t="inlineStr">
         <is>
-          <t>R_SprMean</t>
+          <t>R_SeaRng</t>
         </is>
       </c>
       <c r="C64" s="29" t="inlineStr">
         <is>
-          <t>R_Spring_Mean</t>
+          <t>R_Seasonal_Range</t>
         </is>
       </c>
       <c r="D64" s="18" t="inlineStr">
@@ -3915,17 +3915,17 @@
       </c>
       <c r="E64" s="12" t="inlineStr">
         <is>
-          <t>متوسط هطول الأمطار خلال فصل الربيع (شهور مارس، أبريل، مايو - MAM).</t>
+          <t>المدى الفصلي لتساقط الأمطار (الفارق بين مجموع أعلى فصول السنة مطراً ومجموع أقلها مطراً).</t>
         </is>
       </c>
       <c r="F64" s="19" t="inlineStr">
         <is>
-          <t>مم/فصل (mm/season)</t>
+          <t>ملم (mm)</t>
         </is>
       </c>
       <c r="G64" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط هطول الأمطار خلال فصل الربيع (مم/فصل)</t>
+          <t>خريطة المدى الفصلي لتساقط الأمطار (ملم)</t>
         </is>
       </c>
     </row>
@@ -3935,12 +3935,12 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>R_SumMean</t>
+          <t>R_WinMean</t>
         </is>
       </c>
       <c r="C65" s="31" t="inlineStr">
         <is>
-          <t>R_Summer_Mean</t>
+          <t>R_Winter_Mean</t>
         </is>
       </c>
       <c r="D65" s="15" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>متوسط هطول الأمطار خلال فصل الصيف (شهور يونيو، يوليو، أغسطس - JJA).</t>
+          <t>متوسط هطول الأمطار خلال فصل الشتاء (شهور ديسمبر، يناير، فبراير - DJF).</t>
         </is>
       </c>
       <c r="F65" s="16" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="G65" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط هطول الأمطار خلال فصل الصيف (مم/فصل)</t>
+          <t>خريطة متوسط هطول الأمطار خلال فصل الشتاء (مم/فصل)</t>
         </is>
       </c>
     </row>
@@ -3970,12 +3970,12 @@
       </c>
       <c r="B66" s="10" t="inlineStr">
         <is>
-          <t>R_AutMean</t>
+          <t>R_SprMean</t>
         </is>
       </c>
       <c r="C66" s="29" t="inlineStr">
         <is>
-          <t>R_Autumn_Mean</t>
+          <t>R_Spring_Mean</t>
         </is>
       </c>
       <c r="D66" s="18" t="inlineStr">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="E66" s="12" t="inlineStr">
         <is>
-          <t>متوسط هطول الأمطار خلال فصل الخريف (شهور سبتمبر، أكتوبر، نوفمبر - SON).</t>
+          <t>متوسط هطول الأمطار خلال فصل الربيع (شهور مارس، أبريل، مايو - MAM).</t>
         </is>
       </c>
       <c r="F66" s="19" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="G66" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط هطول الأمطار خلال فصل الخريف (مم/فصل)</t>
+          <t>خريطة متوسط هطول الأمطار خلال فصل الربيع (مم/فصل)</t>
         </is>
       </c>
     </row>
@@ -4005,12 +4005,12 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>R_JanMean</t>
+          <t>R_SumMean</t>
         </is>
       </c>
       <c r="C67" s="31" t="inlineStr">
         <is>
-          <t>R_January_Mean</t>
+          <t>R_Summer_Mean</t>
         </is>
       </c>
       <c r="D67" s="15" t="inlineStr">
@@ -4020,17 +4020,17 @@
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>متوسط مجموع كميات الأمطار التراكمية لشهر يناير عبر سنوات فترة الرصد 1996–2025.</t>
+          <t>متوسط هطول الأمطار خلال فصل الصيف (شهور يونيو، يوليو، أغسطس - JJA).</t>
         </is>
       </c>
       <c r="F67" s="16" t="inlineStr">
         <is>
-          <t>ملم/شهر (mm/month)</t>
+          <t>مم/فصل (mm/season)</t>
         </is>
       </c>
       <c r="G67" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط مجموع أمطار شهر يناير (ملم/شهر)</t>
+          <t>خريطة متوسط هطول الأمطار خلال فصل الصيف (مم/فصل)</t>
         </is>
       </c>
     </row>
@@ -4040,12 +4040,12 @@
       </c>
       <c r="B68" s="10" t="inlineStr">
         <is>
-          <t>R_FebMean</t>
+          <t>R_AutMean</t>
         </is>
       </c>
       <c r="C68" s="29" t="inlineStr">
         <is>
-          <t>R_February_Mean</t>
+          <t>R_Autumn_Mean</t>
         </is>
       </c>
       <c r="D68" s="18" t="inlineStr">
@@ -4055,17 +4055,17 @@
       </c>
       <c r="E68" s="12" t="inlineStr">
         <is>
-          <t>متوسط مجموع كميات الأمطار التراكمية لشهر فبراير عبر سنوات فترة الرصد 1996–2025.</t>
+          <t>متوسط هطول الأمطار خلال فصل الخريف (شهور سبتمبر، أكتوبر، نوفمبر - SON).</t>
         </is>
       </c>
       <c r="F68" s="19" t="inlineStr">
         <is>
-          <t>ملم/شهر (mm/month)</t>
+          <t>مم/فصل (mm/season)</t>
         </is>
       </c>
       <c r="G68" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط مجموع أمطار شهر فبراير (ملم/شهر)</t>
+          <t>خريطة متوسط هطول الأمطار خلال فصل الخريف (مم/فصل)</t>
         </is>
       </c>
     </row>
@@ -4075,12 +4075,12 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>R_MarMean</t>
+          <t>R_JanMean</t>
         </is>
       </c>
       <c r="C69" s="31" t="inlineStr">
         <is>
-          <t>R_March_Mean</t>
+          <t>R_January_Mean</t>
         </is>
       </c>
       <c r="D69" s="15" t="inlineStr">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>متوسط مجموع كميات الأمطار التراكمية لشهر مارس عبر سنوات فترة الرصد 1996–2025.</t>
+          <t>متوسط مجموع كميات الأمطار التراكمية لشهر يناير عبر سنوات فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F69" s="16" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="G69" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط مجموع أمطار شهر مارس (ملم/شهر)</t>
+          <t>خريطة متوسط مجموع أمطار شهر يناير (ملم/شهر)</t>
         </is>
       </c>
     </row>
@@ -4110,12 +4110,12 @@
       </c>
       <c r="B70" s="10" t="inlineStr">
         <is>
-          <t>R_AprMean</t>
+          <t>R_FebMean</t>
         </is>
       </c>
       <c r="C70" s="29" t="inlineStr">
         <is>
-          <t>R_April_Mean</t>
+          <t>R_February_Mean</t>
         </is>
       </c>
       <c r="D70" s="18" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="E70" s="12" t="inlineStr">
         <is>
-          <t>متوسط مجموع كميات الأمطار التراكمية لشهر أبريل عبر سنوات فترة الرصد 1996–2025.</t>
+          <t>متوسط مجموع كميات الأمطار التراكمية لشهر فبراير عبر سنوات فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F70" s="19" t="inlineStr">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="G70" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط مجموع أمطار شهر أبريل (ملم/شهر)</t>
+          <t>خريطة متوسط مجموع أمطار شهر فبراير (ملم/شهر)</t>
         </is>
       </c>
     </row>
@@ -4145,12 +4145,12 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>R_MayMean</t>
+          <t>R_MarMean</t>
         </is>
       </c>
       <c r="C71" s="31" t="inlineStr">
         <is>
-          <t>R_May_Mean</t>
+          <t>R_March_Mean</t>
         </is>
       </c>
       <c r="D71" s="15" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>متوسط مجموع كميات الأمطار التراكمية لشهر مايو عبر سنوات فترة الرصد 1996–2025.</t>
+          <t>متوسط مجموع كميات الأمطار التراكمية لشهر مارس عبر سنوات فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F71" s="16" t="inlineStr">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="G71" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط مجموع أمطار شهر مايو (ملم/شهر)</t>
+          <t>خريطة متوسط مجموع أمطار شهر مارس (ملم/شهر)</t>
         </is>
       </c>
     </row>
@@ -4180,12 +4180,12 @@
       </c>
       <c r="B72" s="10" t="inlineStr">
         <is>
-          <t>R_JunMean</t>
+          <t>R_AprMean</t>
         </is>
       </c>
       <c r="C72" s="29" t="inlineStr">
         <is>
-          <t>R_June_Mean</t>
+          <t>R_April_Mean</t>
         </is>
       </c>
       <c r="D72" s="18" t="inlineStr">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="E72" s="12" t="inlineStr">
         <is>
-          <t>متوسط مجموع كميات الأمطار التراكمية لشهر يونيو عبر سنوات فترة الرصد 1996–2025.</t>
+          <t>متوسط مجموع كميات الأمطار التراكمية لشهر أبريل عبر سنوات فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F72" s="19" t="inlineStr">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="G72" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط مجموع أمطار شهر يونيو (ملم/شهر)</t>
+          <t>خريطة متوسط مجموع أمطار شهر أبريل (ملم/شهر)</t>
         </is>
       </c>
     </row>
@@ -4215,12 +4215,12 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>R_JulMean</t>
+          <t>R_MayMean</t>
         </is>
       </c>
       <c r="C73" s="31" t="inlineStr">
         <is>
-          <t>R_July_Mean</t>
+          <t>R_May_Mean</t>
         </is>
       </c>
       <c r="D73" s="15" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>متوسط مجموع كميات الأمطار التراكمية لشهر يوليو عبر سنوات فترة الرصد 1996–2025.</t>
+          <t>متوسط مجموع كميات الأمطار التراكمية لشهر مايو عبر سنوات فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F73" s="16" t="inlineStr">
@@ -4240,7 +4240,7 @@
       </c>
       <c r="G73" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط مجموع أمطار شهر يوليو (ملم/شهر)</t>
+          <t>خريطة متوسط مجموع أمطار شهر مايو (ملم/شهر)</t>
         </is>
       </c>
     </row>
@@ -4250,12 +4250,12 @@
       </c>
       <c r="B74" s="10" t="inlineStr">
         <is>
-          <t>R_AugMean</t>
+          <t>R_JunMean</t>
         </is>
       </c>
       <c r="C74" s="29" t="inlineStr">
         <is>
-          <t>R_August_Mean</t>
+          <t>R_June_Mean</t>
         </is>
       </c>
       <c r="D74" s="18" t="inlineStr">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="E74" s="12" t="inlineStr">
         <is>
-          <t>متوسط مجموع كميات الأمطار التراكمية لشهر أغسطس عبر سنوات فترة الرصد 1996–2025.</t>
+          <t>متوسط مجموع كميات الأمطار التراكمية لشهر يونيو عبر سنوات فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F74" s="19" t="inlineStr">
@@ -4275,7 +4275,7 @@
       </c>
       <c r="G74" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط مجموع أمطار شهر أغسطس (ملم/شهر)</t>
+          <t>خريطة متوسط مجموع أمطار شهر يونيو (ملم/شهر)</t>
         </is>
       </c>
     </row>
@@ -4285,12 +4285,12 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>R_SepMean</t>
+          <t>R_JulMean</t>
         </is>
       </c>
       <c r="C75" s="31" t="inlineStr">
         <is>
-          <t>R_September_Mean</t>
+          <t>R_July_Mean</t>
         </is>
       </c>
       <c r="D75" s="15" t="inlineStr">
@@ -4300,7 +4300,7 @@
       </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
-          <t>متوسط مجموع كميات الأمطار التراكمية لشهر سبتمبر عبر سنوات فترة الرصد 1996–2025.</t>
+          <t>متوسط مجموع كميات الأمطار التراكمية لشهر يوليو عبر سنوات فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F75" s="16" t="inlineStr">
@@ -4310,7 +4310,7 @@
       </c>
       <c r="G75" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط مجموع أمطار شهر سبتمبر (ملم/شهر)</t>
+          <t>خريطة متوسط مجموع أمطار شهر يوليو (ملم/شهر)</t>
         </is>
       </c>
     </row>
@@ -4320,12 +4320,12 @@
       </c>
       <c r="B76" s="10" t="inlineStr">
         <is>
-          <t>R_OctMean</t>
+          <t>R_AugMean</t>
         </is>
       </c>
       <c r="C76" s="29" t="inlineStr">
         <is>
-          <t>R_October_Mean</t>
+          <t>R_August_Mean</t>
         </is>
       </c>
       <c r="D76" s="18" t="inlineStr">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="E76" s="12" t="inlineStr">
         <is>
-          <t>متوسط مجموع كميات الأمطار التراكمية لشهر أكتوبر عبر سنوات فترة الرصد 1996–2025.</t>
+          <t>متوسط مجموع كميات الأمطار التراكمية لشهر أغسطس عبر سنوات فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F76" s="19" t="inlineStr">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="G76" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط مجموع أمطار شهر أكتوبر (ملم/شهر)</t>
+          <t>خريطة متوسط مجموع أمطار شهر أغسطس (ملم/شهر)</t>
         </is>
       </c>
     </row>
@@ -4355,12 +4355,12 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>R_NovMean</t>
+          <t>R_SepMean</t>
         </is>
       </c>
       <c r="C77" s="31" t="inlineStr">
         <is>
-          <t>R_November_Mean</t>
+          <t>R_September_Mean</t>
         </is>
       </c>
       <c r="D77" s="15" t="inlineStr">
@@ -4370,7 +4370,7 @@
       </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
-          <t>متوسط مجموع كميات الأمطار التراكمية لشهر نوفمبر عبر سنوات فترة الرصد 1996–2025.</t>
+          <t>متوسط مجموع كميات الأمطار التراكمية لشهر سبتمبر عبر سنوات فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F77" s="16" t="inlineStr">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="G77" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط مجموع أمطار شهر نوفمبر (ملم/شهر)</t>
+          <t>خريطة متوسط مجموع أمطار شهر سبتمبر (ملم/شهر)</t>
         </is>
       </c>
     </row>
@@ -4390,12 +4390,12 @@
       </c>
       <c r="B78" s="10" t="inlineStr">
         <is>
-          <t>R_DecMean</t>
+          <t>R_OctMean</t>
         </is>
       </c>
       <c r="C78" s="29" t="inlineStr">
         <is>
-          <t>R_December_Mean</t>
+          <t>R_October_Mean</t>
         </is>
       </c>
       <c r="D78" s="18" t="inlineStr">
@@ -4405,7 +4405,7 @@
       </c>
       <c r="E78" s="12" t="inlineStr">
         <is>
-          <t>متوسط مجموع كميات الأمطار التراكمية لشهر ديسمبر عبر سنوات فترة الرصد 1996–2025.</t>
+          <t>متوسط مجموع كميات الأمطار التراكمية لشهر أكتوبر عبر سنوات فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F78" s="19" t="inlineStr">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="G78" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط مجموع أمطار شهر ديسمبر (ملم/شهر)</t>
+          <t>خريطة متوسط مجموع أمطار شهر أكتوبر (ملم/شهر)</t>
         </is>
       </c>
     </row>
@@ -4425,32 +4425,32 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>PSL_AnMean</t>
+          <t>R_NovMean</t>
         </is>
       </c>
       <c r="C79" s="31" t="inlineStr">
         <is>
-          <t>PSL_Annual_Mean</t>
+          <t>R_November_Mean</t>
         </is>
       </c>
       <c r="D79" s="15" t="inlineStr">
         <is>
-          <t>03_Sea_Level_Pressure (ضغط مستوى البحر)</t>
+          <t>02_Precipitation (الأمطار)</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي السنوي المصحح عند مستوى سطح البحر القياسي (Sea Level Pressure).</t>
+          <t>متوسط مجموع كميات الأمطار التراكمية لشهر نوفمبر عبر سنوات فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F79" s="16" t="inlineStr">
         <is>
-          <t>hPa / mbar</t>
+          <t>ملم/شهر (mm/month)</t>
         </is>
       </c>
       <c r="G79" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط الضغط الجوي عند مستوى سطح البحر (hPa)</t>
+          <t>خريطة متوسط مجموع أمطار شهر نوفمبر (ملم/شهر)</t>
         </is>
       </c>
     </row>
@@ -4460,32 +4460,32 @@
       </c>
       <c r="B80" s="10" t="inlineStr">
         <is>
-          <t>PSL_WnMean</t>
+          <t>R_DecMean</t>
         </is>
       </c>
       <c r="C80" s="29" t="inlineStr">
         <is>
-          <t>PSL_Winter_Mean</t>
+          <t>R_December_Mean</t>
         </is>
       </c>
       <c r="D80" s="18" t="inlineStr">
         <is>
-          <t>03_Sea_Level_Pressure (ضغط مستوى البحر)</t>
+          <t>02_Precipitation (الأمطار)</t>
         </is>
       </c>
       <c r="E80" s="12" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي عند مستوى سطح البحر لفصل الشتاء الأرصادي (DJF).</t>
+          <t>متوسط مجموع كميات الأمطار التراكمية لشهر ديسمبر عبر سنوات فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F80" s="19" t="inlineStr">
         <is>
-          <t>hPa / mbar</t>
+          <t>ملم/شهر (mm/month)</t>
         </is>
       </c>
       <c r="G80" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط ضغط مستوى سطح البحر خلال فصل الشتاء (hPa)</t>
+          <t>خريطة متوسط مجموع أمطار شهر ديسمبر (ملم/شهر)</t>
         </is>
       </c>
     </row>
@@ -4495,12 +4495,12 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>PSL_SpMean</t>
+          <t>PSL_AnMean</t>
         </is>
       </c>
       <c r="C81" s="31" t="inlineStr">
         <is>
-          <t>PSL_Spring_Mean</t>
+          <t>PSL_Annual_Mean</t>
         </is>
       </c>
       <c r="D81" s="15" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي عند مستوى سطح البحر لفصل الربيع الأرصادي (MAM).</t>
+          <t>متوسط الضغط الجوي السنوي المصحح عند مستوى سطح البحر القياسي (Sea Level Pressure).</t>
         </is>
       </c>
       <c r="F81" s="16" t="inlineStr">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="G81" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط ضغط مستوى سطح البحر خلال فصل الربيع (hPa)</t>
+          <t>خريطة متوسط الضغط الجوي عند مستوى سطح البحر (hPa)</t>
         </is>
       </c>
     </row>
@@ -4530,12 +4530,12 @@
       </c>
       <c r="B82" s="10" t="inlineStr">
         <is>
-          <t>PSL_SuMean</t>
+          <t>PSL_MonMea</t>
         </is>
       </c>
       <c r="C82" s="29" t="inlineStr">
         <is>
-          <t>PSL_Summer_Mean</t>
+          <t>PSL_Month_Mean</t>
         </is>
       </c>
       <c r="D82" s="18" t="inlineStr">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="E82" s="12" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي عند مستوى سطح البحر لفصل الصيف الأرصادي (JJA).</t>
+          <t>المتوسط الشهري للضغط الجوي المصحح عند مستوى سطح البحر القياسي (متوسط الـ 12 شهراً).</t>
         </is>
       </c>
       <c r="F82" s="19" t="inlineStr">
@@ -4555,7 +4555,7 @@
       </c>
       <c r="G82" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط ضغط مستوى سطح البحر خلال فصل الصيف (hPa)</t>
+          <t>خريطة المتوسط الشهري لضغط مستوى سطح البحر (hPa)</t>
         </is>
       </c>
     </row>
@@ -4565,12 +4565,12 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>PSL_AuMean</t>
+          <t>PSL_WnMean</t>
         </is>
       </c>
       <c r="C83" s="31" t="inlineStr">
         <is>
-          <t>PSL_Autumn_Mean</t>
+          <t>PSL_Winter_Mean</t>
         </is>
       </c>
       <c r="D83" s="15" t="inlineStr">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي عند مستوى سطح البحر لفصل الخريف الأرصادي (SON).</t>
+          <t>متوسط الضغط الجوي عند مستوى سطح البحر لفصل الشتاء الأرصادي (DJF).</t>
         </is>
       </c>
       <c r="F83" s="16" t="inlineStr">
@@ -4590,7 +4590,7 @@
       </c>
       <c r="G83" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط ضغط مستوى سطح البحر خلال فصل الخريف (hPa)</t>
+          <t>خريطة متوسط ضغط مستوى سطح البحر خلال فصل الشتاء (hPa)</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="B84" s="10" t="inlineStr">
         <is>
-          <t>PSL_AnRng</t>
+          <t>PSL_SpMean</t>
         </is>
       </c>
       <c r="C84" s="29" t="inlineStr">
         <is>
-          <t>PSL_Annual_Range</t>
+          <t>PSL_Spring_Mean</t>
         </is>
       </c>
       <c r="D84" s="18" t="inlineStr">
@@ -4615,7 +4615,7 @@
       </c>
       <c r="E84" s="12" t="inlineStr">
         <is>
-          <t>المدى البارومتري السنوي لضغط مستوى البحر (الفارق بين أعلى وأدنى متوسط شهري للضغط).</t>
+          <t>متوسط الضغط الجوي عند مستوى سطح البحر لفصل الربيع الأرصادي (MAM).</t>
         </is>
       </c>
       <c r="F84" s="19" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="G84" s="30" t="inlineStr">
         <is>
-          <t>خريطة المدى السنوي لضغط مستوى سطح البحر (hPa)</t>
+          <t>خريطة متوسط ضغط مستوى سطح البحر خلال فصل الربيع (hPa)</t>
         </is>
       </c>
     </row>
@@ -4635,12 +4635,12 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>PSL_JanMn</t>
+          <t>PSL_SuMean</t>
         </is>
       </c>
       <c r="C85" s="31" t="inlineStr">
         <is>
-          <t>PSL_January_Mean</t>
+          <t>PSL_Summer_Mean</t>
         </is>
       </c>
       <c r="D85" s="15" t="inlineStr">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي المصحح لمستوى سطح البحر القياسي لشهر يناير (SLP).</t>
+          <t>متوسط الضغط الجوي عند مستوى سطح البحر لفصل الصيف الأرصادي (JJA).</t>
         </is>
       </c>
       <c r="F85" s="16" t="inlineStr">
@@ -4660,7 +4660,7 @@
       </c>
       <c r="G85" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط ضغط مستوى سطح البحر لشهر يناير (hPa)</t>
+          <t>خريطة متوسط ضغط مستوى سطح البحر خلال فصل الصيف (hPa)</t>
         </is>
       </c>
     </row>
@@ -4670,12 +4670,12 @@
       </c>
       <c r="B86" s="10" t="inlineStr">
         <is>
-          <t>PSL_FebMn</t>
+          <t>PSL_AuMean</t>
         </is>
       </c>
       <c r="C86" s="29" t="inlineStr">
         <is>
-          <t>PSL_February_Mean</t>
+          <t>PSL_Autumn_Mean</t>
         </is>
       </c>
       <c r="D86" s="18" t="inlineStr">
@@ -4685,7 +4685,7 @@
       </c>
       <c r="E86" s="12" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي المصحح لمستوى سطح البحر القياسي لشهر فبراير (SLP).</t>
+          <t>متوسط الضغط الجوي عند مستوى سطح البحر لفصل الخريف الأرصادي (SON).</t>
         </is>
       </c>
       <c r="F86" s="19" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="G86" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط ضغط مستوى سطح البحر لشهر فبراير (hPa)</t>
+          <t>خريطة متوسط ضغط مستوى سطح البحر خلال فصل الخريف (hPa)</t>
         </is>
       </c>
     </row>
@@ -4705,12 +4705,12 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>PSL_MarMn</t>
+          <t>PSL_AnRng</t>
         </is>
       </c>
       <c r="C87" s="31" t="inlineStr">
         <is>
-          <t>PSL_March_Mean</t>
+          <t>PSL_Annual_Range</t>
         </is>
       </c>
       <c r="D87" s="15" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="E87" s="7" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي المصحح لمستوى سطح البحر القياسي لشهر مارس (SLP).</t>
+          <t>المدى البارومتري السنوي لضغط مستوى البحر (الفارق بين أعلى وأدنى متوسط شهري للضغط).</t>
         </is>
       </c>
       <c r="F87" s="16" t="inlineStr">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="G87" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط ضغط مستوى سطح البحر لشهر مارس (hPa)</t>
+          <t>خريطة المدى السنوي لضغط مستوى سطح البحر (hPa)</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="B88" s="10" t="inlineStr">
         <is>
-          <t>PSL_AprMn</t>
+          <t>PSL_JanMn</t>
         </is>
       </c>
       <c r="C88" s="29" t="inlineStr">
         <is>
-          <t>PSL_April_Mean</t>
+          <t>PSL_January_Mean</t>
         </is>
       </c>
       <c r="D88" s="18" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="E88" s="12" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي المصحح لمستوى سطح البحر القياسي لشهر أبريل (SLP).</t>
+          <t>متوسط الضغط الجوي المصحح لمستوى سطح البحر القياسي لشهر يناير (SLP).</t>
         </is>
       </c>
       <c r="F88" s="19" t="inlineStr">
@@ -4765,7 +4765,7 @@
       </c>
       <c r="G88" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط ضغط مستوى سطح البحر لشهر أبريل (hPa)</t>
+          <t>خريطة متوسط ضغط مستوى سطح البحر لشهر يناير (hPa)</t>
         </is>
       </c>
     </row>
@@ -4775,12 +4775,12 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>PSL_MayMn</t>
+          <t>PSL_FebMn</t>
         </is>
       </c>
       <c r="C89" s="31" t="inlineStr">
         <is>
-          <t>PSL_May_Mean</t>
+          <t>PSL_February_Mean</t>
         </is>
       </c>
       <c r="D89" s="15" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي المصحح لمستوى سطح البحر القياسي لشهر مايو (SLP).</t>
+          <t>متوسط الضغط الجوي المصحح لمستوى سطح البحر القياسي لشهر فبراير (SLP).</t>
         </is>
       </c>
       <c r="F89" s="16" t="inlineStr">
@@ -4800,7 +4800,7 @@
       </c>
       <c r="G89" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط ضغط مستوى سطح البحر لشهر مايو (hPa)</t>
+          <t>خريطة متوسط ضغط مستوى سطح البحر لشهر فبراير (hPa)</t>
         </is>
       </c>
     </row>
@@ -4810,12 +4810,12 @@
       </c>
       <c r="B90" s="10" t="inlineStr">
         <is>
-          <t>PSL_JunMn</t>
+          <t>PSL_MarMn</t>
         </is>
       </c>
       <c r="C90" s="29" t="inlineStr">
         <is>
-          <t>PSL_June_Mean</t>
+          <t>PSL_March_Mean</t>
         </is>
       </c>
       <c r="D90" s="18" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="E90" s="12" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي المصحح لمستوى سطح البحر القياسي لشهر يونيو (SLP).</t>
+          <t>متوسط الضغط الجوي المصحح لمستوى سطح البحر القياسي لشهر مارس (SLP).</t>
         </is>
       </c>
       <c r="F90" s="19" t="inlineStr">
@@ -4835,7 +4835,7 @@
       </c>
       <c r="G90" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط ضغط مستوى سطح البحر لشهر يونيو (hPa)</t>
+          <t>خريطة متوسط ضغط مستوى سطح البحر لشهر مارس (hPa)</t>
         </is>
       </c>
     </row>
@@ -4845,12 +4845,12 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>PSL_JulMn</t>
+          <t>PSL_AprMn</t>
         </is>
       </c>
       <c r="C91" s="31" t="inlineStr">
         <is>
-          <t>PSL_July_Mean</t>
+          <t>PSL_April_Mean</t>
         </is>
       </c>
       <c r="D91" s="15" t="inlineStr">
@@ -4860,7 +4860,7 @@
       </c>
       <c r="E91" s="7" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي المصحح لمستوى سطح البحر القياسي لشهر يوليو (SLP).</t>
+          <t>متوسط الضغط الجوي المصحح لمستوى سطح البحر القياسي لشهر أبريل (SLP).</t>
         </is>
       </c>
       <c r="F91" s="16" t="inlineStr">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="G91" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط ضغط مستوى سطح البحر لشهر يوليو (hPa)</t>
+          <t>خريطة متوسط ضغط مستوى سطح البحر لشهر أبريل (hPa)</t>
         </is>
       </c>
     </row>
@@ -4880,12 +4880,12 @@
       </c>
       <c r="B92" s="10" t="inlineStr">
         <is>
-          <t>PSL_AugMn</t>
+          <t>PSL_MayMn</t>
         </is>
       </c>
       <c r="C92" s="29" t="inlineStr">
         <is>
-          <t>PSL_August_Mean</t>
+          <t>PSL_May_Mean</t>
         </is>
       </c>
       <c r="D92" s="18" t="inlineStr">
@@ -4895,7 +4895,7 @@
       </c>
       <c r="E92" s="12" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي المصحح لمستوى سطح البحر القياسي لشهر أغسطس (SLP).</t>
+          <t>متوسط الضغط الجوي المصحح لمستوى سطح البحر القياسي لشهر مايو (SLP).</t>
         </is>
       </c>
       <c r="F92" s="19" t="inlineStr">
@@ -4905,7 +4905,7 @@
       </c>
       <c r="G92" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط ضغط مستوى سطح البحر لشهر أغسطس (hPa)</t>
+          <t>خريطة متوسط ضغط مستوى سطح البحر لشهر مايو (hPa)</t>
         </is>
       </c>
     </row>
@@ -4915,12 +4915,12 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>PSL_SepMn</t>
+          <t>PSL_JunMn</t>
         </is>
       </c>
       <c r="C93" s="31" t="inlineStr">
         <is>
-          <t>PSL_September_Mean</t>
+          <t>PSL_June_Mean</t>
         </is>
       </c>
       <c r="D93" s="15" t="inlineStr">
@@ -4930,7 +4930,7 @@
       </c>
       <c r="E93" s="7" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي المصحح لمستوى سطح البحر القياسي لشهر سبتمبر (SLP).</t>
+          <t>متوسط الضغط الجوي المصحح لمستوى سطح البحر القياسي لشهر يونيو (SLP).</t>
         </is>
       </c>
       <c r="F93" s="16" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="G93" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط ضغط مستوى سطح البحر لشهر سبتمبر (hPa)</t>
+          <t>خريطة متوسط ضغط مستوى سطح البحر لشهر يونيو (hPa)</t>
         </is>
       </c>
     </row>
@@ -4950,12 +4950,12 @@
       </c>
       <c r="B94" s="10" t="inlineStr">
         <is>
-          <t>PSL_OctMn</t>
+          <t>PSL_JulMn</t>
         </is>
       </c>
       <c r="C94" s="29" t="inlineStr">
         <is>
-          <t>PSL_October_Mean</t>
+          <t>PSL_July_Mean</t>
         </is>
       </c>
       <c r="D94" s="18" t="inlineStr">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="E94" s="12" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي المصحح لمستوى سطح البحر القياسي لشهر أكتوبر (SLP).</t>
+          <t>متوسط الضغط الجوي المصحح لمستوى سطح البحر القياسي لشهر يوليو (SLP).</t>
         </is>
       </c>
       <c r="F94" s="19" t="inlineStr">
@@ -4975,7 +4975,7 @@
       </c>
       <c r="G94" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط ضغط مستوى سطح البحر لشهر أكتوبر (hPa)</t>
+          <t>خريطة متوسط ضغط مستوى سطح البحر لشهر يوليو (hPa)</t>
         </is>
       </c>
     </row>
@@ -4985,12 +4985,12 @@
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>PSL_NovMn</t>
+          <t>PSL_AugMn</t>
         </is>
       </c>
       <c r="C95" s="31" t="inlineStr">
         <is>
-          <t>PSL_November_Mean</t>
+          <t>PSL_August_Mean</t>
         </is>
       </c>
       <c r="D95" s="15" t="inlineStr">
@@ -5000,7 +5000,7 @@
       </c>
       <c r="E95" s="7" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي المصحح لمستوى سطح البحر القياسي لشهر نوفمبر (SLP).</t>
+          <t>متوسط الضغط الجوي المصحح لمستوى سطح البحر القياسي لشهر أغسطس (SLP).</t>
         </is>
       </c>
       <c r="F95" s="16" t="inlineStr">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="G95" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط ضغط مستوى سطح البحر لشهر نوفمبر (hPa)</t>
+          <t>خريطة متوسط ضغط مستوى سطح البحر لشهر أغسطس (hPa)</t>
         </is>
       </c>
     </row>
@@ -5020,12 +5020,12 @@
       </c>
       <c r="B96" s="10" t="inlineStr">
         <is>
-          <t>PSL_DecMn</t>
+          <t>PSL_SepMn</t>
         </is>
       </c>
       <c r="C96" s="29" t="inlineStr">
         <is>
-          <t>PSL_December_Mean</t>
+          <t>PSL_September_Mean</t>
         </is>
       </c>
       <c r="D96" s="18" t="inlineStr">
@@ -5035,7 +5035,7 @@
       </c>
       <c r="E96" s="12" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي المصحح لمستوى سطح البحر القياسي لشهر ديسمبر (SLP).</t>
+          <t>متوسط الضغط الجوي المصحح لمستوى سطح البحر القياسي لشهر سبتمبر (SLP).</t>
         </is>
       </c>
       <c r="F96" s="19" t="inlineStr">
@@ -5045,7 +5045,7 @@
       </c>
       <c r="G96" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط ضغط مستوى سطح البحر لشهر ديسمبر (hPa)</t>
+          <t>خريطة متوسط ضغط مستوى سطح البحر لشهر سبتمبر (hPa)</t>
         </is>
       </c>
     </row>
@@ -5055,22 +5055,22 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>PS_AnnMean</t>
+          <t>PSL_OctMn</t>
         </is>
       </c>
       <c r="C97" s="31" t="inlineStr">
         <is>
-          <t>PS_Annual_Mean</t>
+          <t>PSL_October_Mean</t>
         </is>
       </c>
       <c r="D97" s="15" t="inlineStr">
         <is>
-          <t>04_Surface_Pressure (الضغط السطحي)</t>
+          <t>03_Sea_Level_Pressure (ضغط مستوى البحر)</t>
         </is>
       </c>
       <c r="E97" s="7" t="inlineStr">
         <is>
-          <t>المتوسط السنوي للضغط الجوي السطحي الفعلي الحقيقي عند منسوب تضاريس المحطة.</t>
+          <t>متوسط الضغط الجوي المصحح لمستوى سطح البحر القياسي لشهر أكتوبر (SLP).</t>
         </is>
       </c>
       <c r="F97" s="16" t="inlineStr">
@@ -5080,7 +5080,7 @@
       </c>
       <c r="G97" s="32" t="inlineStr">
         <is>
-          <t>خريطة المتوسط السنوي للضغط الجوي السطحي (hPa)</t>
+          <t>خريطة متوسط ضغط مستوى سطح البحر لشهر أكتوبر (hPa)</t>
         </is>
       </c>
     </row>
@@ -5090,22 +5090,22 @@
       </c>
       <c r="B98" s="10" t="inlineStr">
         <is>
-          <t>PS_WinMean</t>
+          <t>PSL_NovMn</t>
         </is>
       </c>
       <c r="C98" s="29" t="inlineStr">
         <is>
-          <t>PS_Winter_Mean</t>
+          <t>PSL_November_Mean</t>
         </is>
       </c>
       <c r="D98" s="18" t="inlineStr">
         <is>
-          <t>04_Surface_Pressure (الضغط السطحي)</t>
+          <t>03_Sea_Level_Pressure (ضغط مستوى البحر)</t>
         </is>
       </c>
       <c r="E98" s="12" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي السطحي الفعلي لفصل الشتاء الأرصادي (DJF).</t>
+          <t>متوسط الضغط الجوي المصحح لمستوى سطح البحر القياسي لشهر نوفمبر (SLP).</t>
         </is>
       </c>
       <c r="F98" s="19" t="inlineStr">
@@ -5115,7 +5115,7 @@
       </c>
       <c r="G98" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط الضغط السطحي خلال فصل الشتاء (hPa)</t>
+          <t>خريطة متوسط ضغط مستوى سطح البحر لشهر نوفمبر (hPa)</t>
         </is>
       </c>
     </row>
@@ -5125,22 +5125,22 @@
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>PS_SprMean</t>
+          <t>PSL_DecMn</t>
         </is>
       </c>
       <c r="C99" s="31" t="inlineStr">
         <is>
-          <t>PS_Spring_Mean</t>
+          <t>PSL_December_Mean</t>
         </is>
       </c>
       <c r="D99" s="15" t="inlineStr">
         <is>
-          <t>04_Surface_Pressure (الضغط السطحي)</t>
+          <t>03_Sea_Level_Pressure (ضغط مستوى البحر)</t>
         </is>
       </c>
       <c r="E99" s="7" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي السطحي الفعلي لفصل الربيع الأرصادي (MAM).</t>
+          <t>متوسط الضغط الجوي المصحح لمستوى سطح البحر القياسي لشهر ديسمبر (SLP).</t>
         </is>
       </c>
       <c r="F99" s="16" t="inlineStr">
@@ -5150,7 +5150,7 @@
       </c>
       <c r="G99" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط الضغط السطحي خلال فصل الربيع (hPa)</t>
+          <t>خريطة متوسط ضغط مستوى سطح البحر لشهر ديسمبر (hPa)</t>
         </is>
       </c>
     </row>
@@ -5160,12 +5160,12 @@
       </c>
       <c r="B100" s="10" t="inlineStr">
         <is>
-          <t>PS_SumMean</t>
+          <t>PS_AnnMean</t>
         </is>
       </c>
       <c r="C100" s="29" t="inlineStr">
         <is>
-          <t>PS_Summer_Mean</t>
+          <t>PS_Annual_Mean</t>
         </is>
       </c>
       <c r="D100" s="18" t="inlineStr">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="E100" s="12" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي السطحي الفعلي لفصل الصيف الأرصادي (JJA).</t>
+          <t>المتوسط السنوي للضغط الجوي السطحي الفعلي الحقيقي عند منسوب تضاريس المحطة.</t>
         </is>
       </c>
       <c r="F100" s="19" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="G100" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط الضغط السطحي خلال فصل الصيف (hPa)</t>
+          <t>خريطة المتوسط السنوي للضغط الجوي السطحي (hPa)</t>
         </is>
       </c>
     </row>
@@ -5195,12 +5195,12 @@
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>PS_AutMean</t>
+          <t>PS_MonMean</t>
         </is>
       </c>
       <c r="C101" s="31" t="inlineStr">
         <is>
-          <t>PS_Autumn_Mean</t>
+          <t>PS_Month_Mean</t>
         </is>
       </c>
       <c r="D101" s="15" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="E101" s="7" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي السطحي الفعلي لفصل الخريف الأرصادي (SON).</t>
+          <t>المتوسط الشهري للضغط الجوي السطحي الفعلي للمحطة (متوسط الـ 12 شهراً).</t>
         </is>
       </c>
       <c r="F101" s="16" t="inlineStr">
@@ -5220,7 +5220,7 @@
       </c>
       <c r="G101" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط الضغط السطحي خلال فصل الخريف (hPa)</t>
+          <t>خريطة المتوسط الشهري للضغط الجوي السطحي (hPa)</t>
         </is>
       </c>
     </row>
@@ -5230,12 +5230,12 @@
       </c>
       <c r="B102" s="10" t="inlineStr">
         <is>
-          <t>PS_AnnRng</t>
+          <t>PS_WinMean</t>
         </is>
       </c>
       <c r="C102" s="29" t="inlineStr">
         <is>
-          <t>PS_Annual_Range</t>
+          <t>PS_Winter_Mean</t>
         </is>
       </c>
       <c r="D102" s="18" t="inlineStr">
@@ -5245,7 +5245,7 @@
       </c>
       <c r="E102" s="12" t="inlineStr">
         <is>
-          <t>المدى البارومتري السنوي للضغط السطحي (الفارق بين أعلى وأدنى متوسط شهري للضغط السطحي).</t>
+          <t>متوسط الضغط الجوي السطحي الفعلي لفصل الشتاء الأرصادي (DJF).</t>
         </is>
       </c>
       <c r="F102" s="19" t="inlineStr">
@@ -5255,7 +5255,7 @@
       </c>
       <c r="G102" s="30" t="inlineStr">
         <is>
-          <t>خريطة المدى السنوي للضغط الجوي السطحي (hPa)</t>
+          <t>خريطة متوسط الضغط السطحي خلال فصل الشتاء (hPa)</t>
         </is>
       </c>
     </row>
@@ -5265,12 +5265,12 @@
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>PS_JanMean</t>
+          <t>PS_SprMean</t>
         </is>
       </c>
       <c r="C103" s="31" t="inlineStr">
         <is>
-          <t>PS_January_Mean</t>
+          <t>PS_Spring_Mean</t>
         </is>
       </c>
       <c r="D103" s="15" t="inlineStr">
@@ -5280,7 +5280,7 @@
       </c>
       <c r="E103" s="7" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي السطحي الفعلي الحقيقي عند منسوب المحطة لشهر يناير.</t>
+          <t>متوسط الضغط الجوي السطحي الفعلي لفصل الربيع الأرصادي (MAM).</t>
         </is>
       </c>
       <c r="F103" s="16" t="inlineStr">
@@ -5290,7 +5290,7 @@
       </c>
       <c r="G103" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط الضغط السطحي الفعلي لشهر يناير (hPa)</t>
+          <t>خريطة متوسط الضغط السطحي خلال فصل الربيع (hPa)</t>
         </is>
       </c>
     </row>
@@ -5300,12 +5300,12 @@
       </c>
       <c r="B104" s="10" t="inlineStr">
         <is>
-          <t>PS_FebMean</t>
+          <t>PS_SumMean</t>
         </is>
       </c>
       <c r="C104" s="29" t="inlineStr">
         <is>
-          <t>PS_February_Mean</t>
+          <t>PS_Summer_Mean</t>
         </is>
       </c>
       <c r="D104" s="18" t="inlineStr">
@@ -5315,7 +5315,7 @@
       </c>
       <c r="E104" s="12" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي السطحي الفعلي الحقيقي عند منسوب المحطة لشهر فبراير.</t>
+          <t>متوسط الضغط الجوي السطحي الفعلي لفصل الصيف الأرصادي (JJA).</t>
         </is>
       </c>
       <c r="F104" s="19" t="inlineStr">
@@ -5325,7 +5325,7 @@
       </c>
       <c r="G104" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط الضغط السطحي الفعلي لشهر فبراير (hPa)</t>
+          <t>خريطة متوسط الضغط السطحي خلال فصل الصيف (hPa)</t>
         </is>
       </c>
     </row>
@@ -5335,12 +5335,12 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>PS_MarMean</t>
+          <t>PS_AutMean</t>
         </is>
       </c>
       <c r="C105" s="31" t="inlineStr">
         <is>
-          <t>PS_March_Mean</t>
+          <t>PS_Autumn_Mean</t>
         </is>
       </c>
       <c r="D105" s="15" t="inlineStr">
@@ -5350,7 +5350,7 @@
       </c>
       <c r="E105" s="7" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي السطحي الفعلي الحقيقي عند منسوب المحطة لشهر مارس.</t>
+          <t>متوسط الضغط الجوي السطحي الفعلي لفصل الخريف الأرصادي (SON).</t>
         </is>
       </c>
       <c r="F105" s="16" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="G105" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط الضغط السطحي الفعلي لشهر مارس (hPa)</t>
+          <t>خريطة متوسط الضغط السطحي خلال فصل الخريف (hPa)</t>
         </is>
       </c>
     </row>
@@ -5370,12 +5370,12 @@
       </c>
       <c r="B106" s="10" t="inlineStr">
         <is>
-          <t>PS_AprMean</t>
+          <t>PS_AnnRng</t>
         </is>
       </c>
       <c r="C106" s="29" t="inlineStr">
         <is>
-          <t>PS_April_Mean</t>
+          <t>PS_Annual_Range</t>
         </is>
       </c>
       <c r="D106" s="18" t="inlineStr">
@@ -5385,7 +5385,7 @@
       </c>
       <c r="E106" s="12" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي السطحي الفعلي الحقيقي عند منسوب المحطة لشهر أبريل.</t>
+          <t>المدى البارومتري السنوي للضغط السطحي (الفارق بين أعلى وأدنى متوسط شهري للضغط السطحي).</t>
         </is>
       </c>
       <c r="F106" s="19" t="inlineStr">
@@ -5395,7 +5395,7 @@
       </c>
       <c r="G106" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط الضغط السطحي الفعلي لشهر أبريل (hPa)</t>
+          <t>خريطة المدى السنوي للضغط الجوي السطحي (hPa)</t>
         </is>
       </c>
     </row>
@@ -5405,12 +5405,12 @@
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>PS_MayMean</t>
+          <t>PS_JanMean</t>
         </is>
       </c>
       <c r="C107" s="31" t="inlineStr">
         <is>
-          <t>PS_May_Mean</t>
+          <t>PS_January_Mean</t>
         </is>
       </c>
       <c r="D107" s="15" t="inlineStr">
@@ -5420,7 +5420,7 @@
       </c>
       <c r="E107" s="7" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي السطحي الفعلي الحقيقي عند منسوب المحطة لشهر مايو.</t>
+          <t>متوسط الضغط الجوي السطحي الفعلي الحقيقي عند منسوب المحطة لشهر يناير.</t>
         </is>
       </c>
       <c r="F107" s="16" t="inlineStr">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="G107" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط الضغط السطحي الفعلي لشهر مايو (hPa)</t>
+          <t>خريطة متوسط الضغط السطحي الفعلي لشهر يناير (hPa)</t>
         </is>
       </c>
     </row>
@@ -5440,12 +5440,12 @@
       </c>
       <c r="B108" s="10" t="inlineStr">
         <is>
-          <t>PS_JunMean</t>
+          <t>PS_FebMean</t>
         </is>
       </c>
       <c r="C108" s="29" t="inlineStr">
         <is>
-          <t>PS_June_Mean</t>
+          <t>PS_February_Mean</t>
         </is>
       </c>
       <c r="D108" s="18" t="inlineStr">
@@ -5455,7 +5455,7 @@
       </c>
       <c r="E108" s="12" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي السطحي الفعلي الحقيقي عند منسوب المحطة لشهر يونيو.</t>
+          <t>متوسط الضغط الجوي السطحي الفعلي الحقيقي عند منسوب المحطة لشهر فبراير.</t>
         </is>
       </c>
       <c r="F108" s="19" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="G108" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط الضغط السطحي الفعلي لشهر يونيو (hPa)</t>
+          <t>خريطة متوسط الضغط السطحي الفعلي لشهر فبراير (hPa)</t>
         </is>
       </c>
     </row>
@@ -5475,12 +5475,12 @@
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>PS_JulMean</t>
+          <t>PS_MarMean</t>
         </is>
       </c>
       <c r="C109" s="31" t="inlineStr">
         <is>
-          <t>PS_July_Mean</t>
+          <t>PS_March_Mean</t>
         </is>
       </c>
       <c r="D109" s="15" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="E109" s="7" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي السطحي الفعلي الحقيقي عند منسوب المحطة لشهر يوليو.</t>
+          <t>متوسط الضغط الجوي السطحي الفعلي الحقيقي عند منسوب المحطة لشهر مارس.</t>
         </is>
       </c>
       <c r="F109" s="16" t="inlineStr">
@@ -5500,7 +5500,7 @@
       </c>
       <c r="G109" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط الضغط السطحي الفعلي لشهر يوليو (hPa)</t>
+          <t>خريطة متوسط الضغط السطحي الفعلي لشهر مارس (hPa)</t>
         </is>
       </c>
     </row>
@@ -5510,12 +5510,12 @@
       </c>
       <c r="B110" s="10" t="inlineStr">
         <is>
-          <t>PS_AugMean</t>
+          <t>PS_AprMean</t>
         </is>
       </c>
       <c r="C110" s="29" t="inlineStr">
         <is>
-          <t>PS_August_Mean</t>
+          <t>PS_April_Mean</t>
         </is>
       </c>
       <c r="D110" s="18" t="inlineStr">
@@ -5525,7 +5525,7 @@
       </c>
       <c r="E110" s="12" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي السطحي الفعلي الحقيقي عند منسوب المحطة لشهر أغسطس.</t>
+          <t>متوسط الضغط الجوي السطحي الفعلي الحقيقي عند منسوب المحطة لشهر أبريل.</t>
         </is>
       </c>
       <c r="F110" s="19" t="inlineStr">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="G110" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط الضغط السطحي الفعلي لشهر أغسطس (hPa)</t>
+          <t>خريطة متوسط الضغط السطحي الفعلي لشهر أبريل (hPa)</t>
         </is>
       </c>
     </row>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>PS_SepMean</t>
+          <t>PS_MayMean</t>
         </is>
       </c>
       <c r="C111" s="31" t="inlineStr">
         <is>
-          <t>PS_September_Mean</t>
+          <t>PS_May_Mean</t>
         </is>
       </c>
       <c r="D111" s="15" t="inlineStr">
@@ -5560,7 +5560,7 @@
       </c>
       <c r="E111" s="7" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي السطحي الفعلي الحقيقي عند منسوب المحطة لشهر سبتمبر.</t>
+          <t>متوسط الضغط الجوي السطحي الفعلي الحقيقي عند منسوب المحطة لشهر مايو.</t>
         </is>
       </c>
       <c r="F111" s="16" t="inlineStr">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="G111" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط الضغط السطحي الفعلي لشهر سبتمبر (hPa)</t>
+          <t>خريطة متوسط الضغط السطحي الفعلي لشهر مايو (hPa)</t>
         </is>
       </c>
     </row>
@@ -5580,12 +5580,12 @@
       </c>
       <c r="B112" s="10" t="inlineStr">
         <is>
-          <t>PS_OctMean</t>
+          <t>PS_JunMean</t>
         </is>
       </c>
       <c r="C112" s="29" t="inlineStr">
         <is>
-          <t>PS_October_Mean</t>
+          <t>PS_June_Mean</t>
         </is>
       </c>
       <c r="D112" s="18" t="inlineStr">
@@ -5595,7 +5595,7 @@
       </c>
       <c r="E112" s="12" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي السطحي الفعلي الحقيقي عند منسوب المحطة لشهر أكتوبر.</t>
+          <t>متوسط الضغط الجوي السطحي الفعلي الحقيقي عند منسوب المحطة لشهر يونيو.</t>
         </is>
       </c>
       <c r="F112" s="19" t="inlineStr">
@@ -5605,7 +5605,7 @@
       </c>
       <c r="G112" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط الضغط السطحي الفعلي لشهر أكتوبر (hPa)</t>
+          <t>خريطة متوسط الضغط السطحي الفعلي لشهر يونيو (hPa)</t>
         </is>
       </c>
     </row>
@@ -5615,12 +5615,12 @@
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>PS_NovMean</t>
+          <t>PS_JulMean</t>
         </is>
       </c>
       <c r="C113" s="31" t="inlineStr">
         <is>
-          <t>PS_November_Mean</t>
+          <t>PS_July_Mean</t>
         </is>
       </c>
       <c r="D113" s="15" t="inlineStr">
@@ -5630,7 +5630,7 @@
       </c>
       <c r="E113" s="7" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي السطحي الفعلي الحقيقي عند منسوب المحطة لشهر نوفمبر.</t>
+          <t>متوسط الضغط الجوي السطحي الفعلي الحقيقي عند منسوب المحطة لشهر يوليو.</t>
         </is>
       </c>
       <c r="F113" s="16" t="inlineStr">
@@ -5640,7 +5640,7 @@
       </c>
       <c r="G113" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط الضغط السطحي الفعلي لشهر نوفمبر (hPa)</t>
+          <t>خريطة متوسط الضغط السطحي الفعلي لشهر يوليو (hPa)</t>
         </is>
       </c>
     </row>
@@ -5650,12 +5650,12 @@
       </c>
       <c r="B114" s="10" t="inlineStr">
         <is>
-          <t>PS_DecMean</t>
+          <t>PS_AugMean</t>
         </is>
       </c>
       <c r="C114" s="29" t="inlineStr">
         <is>
-          <t>PS_December_Mean</t>
+          <t>PS_August_Mean</t>
         </is>
       </c>
       <c r="D114" s="18" t="inlineStr">
@@ -5665,7 +5665,7 @@
       </c>
       <c r="E114" s="12" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي السطحي الفعلي الحقيقي عند منسوب المحطة لشهر ديسمبر.</t>
+          <t>متوسط الضغط الجوي السطحي الفعلي الحقيقي عند منسوب المحطة لشهر أغسطس.</t>
         </is>
       </c>
       <c r="F114" s="19" t="inlineStr">
@@ -5675,7 +5675,7 @@
       </c>
       <c r="G114" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط الضغط السطحي الفعلي لشهر ديسمبر (hPa)</t>
+          <t>خريطة متوسط الضغط السطحي الفعلي لشهر أغسطس (hPa)</t>
         </is>
       </c>
     </row>
@@ -5685,32 +5685,32 @@
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>WSp_AnMean</t>
+          <t>PS_SepMean</t>
         </is>
       </c>
       <c r="C115" s="31" t="inlineStr">
         <is>
-          <t>W_Spd_Annual_Mean</t>
+          <t>PS_September_Mean</t>
         </is>
       </c>
       <c r="D115" s="15" t="inlineStr">
         <is>
-          <t>05_Wind (الرياح)</t>
+          <t>04_Surface_Pressure (الضغط السطحي)</t>
         </is>
       </c>
       <c r="E115" s="7" t="inlineStr">
         <is>
-          <t>المتوسط السنوي لسرعة الرياح عند ارتفاع 10 أمتار فوق سطح الأرض.</t>
+          <t>متوسط الضغط الجوي السطحي الفعلي الحقيقي عند منسوب المحطة لشهر سبتمبر.</t>
         </is>
       </c>
       <c r="F115" s="16" t="inlineStr">
         <is>
-          <t>م/ث (m/s)</t>
+          <t>hPa / mbar</t>
         </is>
       </c>
       <c r="G115" s="32" t="inlineStr">
         <is>
-          <t>خريطة المتوسط السنوي لسرعة الرياح (م/ث)</t>
+          <t>خريطة متوسط الضغط السطحي الفعلي لشهر سبتمبر (hPa)</t>
         </is>
       </c>
     </row>
@@ -5720,32 +5720,32 @@
       </c>
       <c r="B116" s="10" t="inlineStr">
         <is>
-          <t>WSp_WnMean</t>
+          <t>PS_OctMean</t>
         </is>
       </c>
       <c r="C116" s="29" t="inlineStr">
         <is>
-          <t>W_Spd_Winter_Mean</t>
+          <t>PS_October_Mean</t>
         </is>
       </c>
       <c r="D116" s="18" t="inlineStr">
         <is>
-          <t>05_Wind (الرياح)</t>
+          <t>04_Surface_Pressure (الضغط السطحي)</t>
         </is>
       </c>
       <c r="E116" s="12" t="inlineStr">
         <is>
-          <t>متوسط سرعة الرياح لفصل الشتاء الأرصادي عند ارتفاع 10 أمتار (DJF).</t>
+          <t>متوسط الضغط الجوي السطحي الفعلي الحقيقي عند منسوب المحطة لشهر أكتوبر.</t>
         </is>
       </c>
       <c r="F116" s="19" t="inlineStr">
         <is>
-          <t>م/ث (m/s)</t>
+          <t>hPa / mbar</t>
         </is>
       </c>
       <c r="G116" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط سرعة الرياح خلال فصل الشتاء (م/ث)</t>
+          <t>خريطة متوسط الضغط السطحي الفعلي لشهر أكتوبر (hPa)</t>
         </is>
       </c>
     </row>
@@ -5755,32 +5755,32 @@
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>WSp_SpMean</t>
+          <t>PS_NovMean</t>
         </is>
       </c>
       <c r="C117" s="31" t="inlineStr">
         <is>
-          <t>W_Spd_Spring_Mean</t>
+          <t>PS_November_Mean</t>
         </is>
       </c>
       <c r="D117" s="15" t="inlineStr">
         <is>
-          <t>05_Wind (الرياح)</t>
+          <t>04_Surface_Pressure (الضغط السطحي)</t>
         </is>
       </c>
       <c r="E117" s="7" t="inlineStr">
         <is>
-          <t>متوسط سرعة الرياح لفصل الربيع الأرصادي عند ارتفاع 10 أمتار (MAM).</t>
+          <t>متوسط الضغط الجوي السطحي الفعلي الحقيقي عند منسوب المحطة لشهر نوفمبر.</t>
         </is>
       </c>
       <c r="F117" s="16" t="inlineStr">
         <is>
-          <t>م/ث (m/s)</t>
+          <t>hPa / mbar</t>
         </is>
       </c>
       <c r="G117" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط سرعة الرياح خلال فصل الربيع (م/ث)</t>
+          <t>خريطة متوسط الضغط السطحي الفعلي لشهر نوفمبر (hPa)</t>
         </is>
       </c>
     </row>
@@ -5790,32 +5790,32 @@
       </c>
       <c r="B118" s="10" t="inlineStr">
         <is>
-          <t>WSp_SuMean</t>
+          <t>PS_DecMean</t>
         </is>
       </c>
       <c r="C118" s="29" t="inlineStr">
         <is>
-          <t>W_Spd_Summer_Mean</t>
+          <t>PS_December_Mean</t>
         </is>
       </c>
       <c r="D118" s="18" t="inlineStr">
         <is>
-          <t>05_Wind (الرياح)</t>
+          <t>04_Surface_Pressure (الضغط السطحي)</t>
         </is>
       </c>
       <c r="E118" s="12" t="inlineStr">
         <is>
-          <t>متوسط سرعة الرياح لفصل الصيف الأرصادي عند ارتفاع 10 أمتار (JJA).</t>
+          <t>متوسط الضغط الجوي السطحي الفعلي الحقيقي عند منسوب المحطة لشهر ديسمبر.</t>
         </is>
       </c>
       <c r="F118" s="19" t="inlineStr">
         <is>
-          <t>م/ث (m/s)</t>
+          <t>hPa / mbar</t>
         </is>
       </c>
       <c r="G118" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط سرعة الرياح خلال فصل الصيف (م/ث)</t>
+          <t>خريطة متوسط الضغط السطحي الفعلي لشهر ديسمبر (hPa)</t>
         </is>
       </c>
     </row>
@@ -5825,12 +5825,12 @@
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>WSp_AuMean</t>
+          <t>WSp_AnMean</t>
         </is>
       </c>
       <c r="C119" s="31" t="inlineStr">
         <is>
-          <t>W_Spd_Autumn_Mean</t>
+          <t>W_Spd_Annual_Mean</t>
         </is>
       </c>
       <c r="D119" s="15" t="inlineStr">
@@ -5840,7 +5840,7 @@
       </c>
       <c r="E119" s="7" t="inlineStr">
         <is>
-          <t>متوسط سرعة الرياح لفصل الخريف الأرصادي عند ارتفاع 10 أمتار (SON).</t>
+          <t>المتوسط السنوي لسرعة الرياح عند ارتفاع 10 أمتار فوق سطح الأرض.</t>
         </is>
       </c>
       <c r="F119" s="16" t="inlineStr">
@@ -5850,7 +5850,7 @@
       </c>
       <c r="G119" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط سرعة الرياح خلال فصل الخريف (م/ث)</t>
+          <t>خريطة المتوسط السنوي لسرعة الرياح (م/ث)</t>
         </is>
       </c>
     </row>
@@ -5860,32 +5860,32 @@
       </c>
       <c r="B120" s="10" t="inlineStr">
         <is>
-          <t>WSp_MaxMo</t>
+          <t>WSp_MonMea</t>
         </is>
       </c>
       <c r="C120" s="29" t="inlineStr">
         <is>
-          <t>W_Spd_Annual_Max_Month</t>
+          <t>W_Spd_Month_Mean</t>
         </is>
       </c>
       <c r="D120" s="18" t="inlineStr">
         <is>
-          <t>05_Wind (الرياح)</t>
+          <t>05_Wind (الرياح السطحية)</t>
         </is>
       </c>
       <c r="E120" s="12" t="inlineStr">
         <is>
-          <t>أقصى متوسط شهري مسجل لسرعة الرياح في السنة (ذروة النشاط الريحي).</t>
+          <t>المتوسط الشهري لسرعة الرياح على ارتفاع 10 أمتار (متوسط الـ 12 شهراً).</t>
         </is>
       </c>
       <c r="F120" s="19" t="inlineStr">
         <is>
-          <t>م/ث (m/s)</t>
+          <t>m/s</t>
         </is>
       </c>
       <c r="G120" s="30" t="inlineStr">
         <is>
-          <t>خريطة أقصى متوسط شهري لسرعة الرياح (م/ث)</t>
+          <t>خريطة المتوسط الشهري لسرعة الرياح (m/s)</t>
         </is>
       </c>
     </row>
@@ -5895,12 +5895,12 @@
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>WSp_MinMo</t>
+          <t>WSp_WnMean</t>
         </is>
       </c>
       <c r="C121" s="31" t="inlineStr">
         <is>
-          <t>W_Spd_Annual_Min_Month</t>
+          <t>W_Spd_Winter_Mean</t>
         </is>
       </c>
       <c r="D121" s="15" t="inlineStr">
@@ -5910,7 +5910,7 @@
       </c>
       <c r="E121" s="7" t="inlineStr">
         <is>
-          <t>أدنى متوسط شهري مسجل لسرعة الرياح في السنة (فترة الهدوء الريحي).</t>
+          <t>متوسط سرعة الرياح لفصل الشتاء الأرصادي عند ارتفاع 10 أمتار (DJF).</t>
         </is>
       </c>
       <c r="F121" s="16" t="inlineStr">
@@ -5920,7 +5920,7 @@
       </c>
       <c r="G121" s="32" t="inlineStr">
         <is>
-          <t>خريطة أدنى متوسط شهري لسرعة الرياح (م/ث)</t>
+          <t>خريطة متوسط سرعة الرياح خلال فصل الشتاء (م/ث)</t>
         </is>
       </c>
     </row>
@@ -5930,12 +5930,12 @@
       </c>
       <c r="B122" s="10" t="inlineStr">
         <is>
-          <t>WSp_AnRng</t>
+          <t>WSp_SpMean</t>
         </is>
       </c>
       <c r="C122" s="29" t="inlineStr">
         <is>
-          <t>W_Spd_Annual_Range</t>
+          <t>W_Spd_Spring_Mean</t>
         </is>
       </c>
       <c r="D122" s="18" t="inlineStr">
@@ -5945,7 +5945,7 @@
       </c>
       <c r="E122" s="12" t="inlineStr">
         <is>
-          <t>المدى السنوي لسرعة الرياح (الفارق بين أشد شهور السنة رياحاً وأهدأها سرعة).</t>
+          <t>متوسط سرعة الرياح لفصل الربيع الأرصادي عند ارتفاع 10 أمتار (MAM).</t>
         </is>
       </c>
       <c r="F122" s="19" t="inlineStr">
@@ -5955,7 +5955,7 @@
       </c>
       <c r="G122" s="30" t="inlineStr">
         <is>
-          <t>خريطة المدى السنوي لسرعة الرياح (م/ث)</t>
+          <t>خريطة متوسط سرعة الرياح خلال فصل الربيع (م/ث)</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>WDr_AnMean</t>
+          <t>WSp_SuMean</t>
         </is>
       </c>
       <c r="C123" s="31" t="inlineStr">
         <is>
-          <t>W_Dir_Annual_Mean</t>
+          <t>W_Spd_Summer_Mean</t>
         </is>
       </c>
       <c r="D123" s="15" t="inlineStr">
@@ -5980,17 +5980,17 @@
       </c>
       <c r="E123" s="7" t="inlineStr">
         <is>
-          <t>الاتجاه السائد السنوي للرياح بالدرجات الزاوية (محسوب بالمتوسط الدائري للمتجهات الدائرية atan2).</t>
+          <t>متوسط سرعة الرياح لفصل الصيف الأرصادي عند ارتفاع 10 أمتار (JJA).</t>
         </is>
       </c>
       <c r="F123" s="16" t="inlineStr">
         <is>
-          <t>درجة (°)</t>
+          <t>م/ث (m/s)</t>
         </is>
       </c>
       <c r="G123" s="32" t="inlineStr">
         <is>
-          <t>خريطة الاتجاه السائد السنوي للرياح (درجات)</t>
+          <t>خريطة متوسط سرعة الرياح خلال فصل الصيف (م/ث)</t>
         </is>
       </c>
     </row>
@@ -6000,12 +6000,12 @@
       </c>
       <c r="B124" s="10" t="inlineStr">
         <is>
-          <t>WDr_WnMean</t>
+          <t>WSp_AuMean</t>
         </is>
       </c>
       <c r="C124" s="29" t="inlineStr">
         <is>
-          <t>W_Dir_Winter_Mean</t>
+          <t>W_Spd_Autumn_Mean</t>
         </is>
       </c>
       <c r="D124" s="18" t="inlineStr">
@@ -6015,17 +6015,17 @@
       </c>
       <c r="E124" s="12" t="inlineStr">
         <is>
-          <t>اتجاه الرياح السائد خلال فصل الشتاء الأرصادي بالدرجات الزاوية (DJF).</t>
+          <t>متوسط سرعة الرياح لفصل الخريف الأرصادي عند ارتفاع 10 أمتار (SON).</t>
         </is>
       </c>
       <c r="F124" s="19" t="inlineStr">
         <is>
-          <t>درجة (°)</t>
+          <t>م/ث (m/s)</t>
         </is>
       </c>
       <c r="G124" s="30" t="inlineStr">
         <is>
-          <t>خريطة اتجاه الرياح السائد خلال فصل الشتاء (درجات)</t>
+          <t>خريطة متوسط سرعة الرياح خلال فصل الخريف (م/ث)</t>
         </is>
       </c>
     </row>
@@ -6035,12 +6035,12 @@
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>WDr_SpMean</t>
+          <t>WSp_MaxMo</t>
         </is>
       </c>
       <c r="C125" s="31" t="inlineStr">
         <is>
-          <t>W_Dir_Spring_Mean</t>
+          <t>W_Spd_Annual_Max_Month</t>
         </is>
       </c>
       <c r="D125" s="15" t="inlineStr">
@@ -6050,17 +6050,17 @@
       </c>
       <c r="E125" s="7" t="inlineStr">
         <is>
-          <t>اتجاه الرياح السائد خلال فصل الربيع الأرصادي بالدرجات الزاوية (MAM).</t>
+          <t>أقصى متوسط شهري مسجل لسرعة الرياح في السنة (ذروة النشاط الريحي).</t>
         </is>
       </c>
       <c r="F125" s="16" t="inlineStr">
         <is>
-          <t>درجة (°)</t>
+          <t>م/ث (m/s)</t>
         </is>
       </c>
       <c r="G125" s="32" t="inlineStr">
         <is>
-          <t>خريطة اتجاه الرياح السائد خلال فصل الربيع (درجات)</t>
+          <t>خريطة أقصى متوسط شهري لسرعة الرياح (م/ث)</t>
         </is>
       </c>
     </row>
@@ -6070,12 +6070,12 @@
       </c>
       <c r="B126" s="10" t="inlineStr">
         <is>
-          <t>WDr_SuMean</t>
+          <t>WSp_MinMo</t>
         </is>
       </c>
       <c r="C126" s="29" t="inlineStr">
         <is>
-          <t>W_Dir_Summer_Mean</t>
+          <t>W_Spd_Annual_Min_Month</t>
         </is>
       </c>
       <c r="D126" s="18" t="inlineStr">
@@ -6085,17 +6085,17 @@
       </c>
       <c r="E126" s="12" t="inlineStr">
         <is>
-          <t>اتجاه الرياح السائد خلال فصل الصيف الأرصادي بالدرجات الزاوية (JJA).</t>
+          <t>أدنى متوسط شهري مسجل لسرعة الرياح في السنة (فترة الهدوء الريحي).</t>
         </is>
       </c>
       <c r="F126" s="19" t="inlineStr">
         <is>
-          <t>درجة (°)</t>
+          <t>م/ث (m/s)</t>
         </is>
       </c>
       <c r="G126" s="30" t="inlineStr">
         <is>
-          <t>خريطة اتجاه الرياح السائد خلال فصل الصيف (درجات)</t>
+          <t>خريطة أدنى متوسط شهري لسرعة الرياح (م/ث)</t>
         </is>
       </c>
     </row>
@@ -6105,12 +6105,12 @@
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>WDr_AuMean</t>
+          <t>WSp_AnRng</t>
         </is>
       </c>
       <c r="C127" s="31" t="inlineStr">
         <is>
-          <t>W_Dir_Autumn_Mean</t>
+          <t>W_Spd_Annual_Range</t>
         </is>
       </c>
       <c r="D127" s="15" t="inlineStr">
@@ -6120,17 +6120,17 @@
       </c>
       <c r="E127" s="7" t="inlineStr">
         <is>
-          <t>اتجاه الرياح السائد خلال فصل الخريف الأرصادي بالدرجات الزاوية (SON).</t>
+          <t>المدى السنوي لسرعة الرياح (الفارق بين أشد شهور السنة رياحاً وأهدأها سرعة).</t>
         </is>
       </c>
       <c r="F127" s="16" t="inlineStr">
         <is>
-          <t>درجة (°)</t>
+          <t>م/ث (m/s)</t>
         </is>
       </c>
       <c r="G127" s="32" t="inlineStr">
         <is>
-          <t>خريطة اتجاه الرياح السائد خلال فصل الخريف (درجات)</t>
+          <t>خريطة المدى السنوي لسرعة الرياح (م/ث)</t>
         </is>
       </c>
     </row>
@@ -6140,12 +6140,12 @@
       </c>
       <c r="B128" s="10" t="inlineStr">
         <is>
-          <t>WSp_JanMn</t>
+          <t>WDr_AnMean</t>
         </is>
       </c>
       <c r="C128" s="29" t="inlineStr">
         <is>
-          <t>W_Spd_January_Mean</t>
+          <t>W_Dir_Annual_Mean</t>
         </is>
       </c>
       <c r="D128" s="18" t="inlineStr">
@@ -6155,17 +6155,17 @@
       </c>
       <c r="E128" s="12" t="inlineStr">
         <is>
-          <t>متوسط سرعة الرياح على ارتفاع 10 أمتار لشهر يناير عبر فترة الرصد.</t>
+          <t>الاتجاه السائد السنوي للرياح بالدرجات الزاوية (محسوب بالمتوسط الدائري للمتجهات الدائرية atan2).</t>
         </is>
       </c>
       <c r="F128" s="19" t="inlineStr">
         <is>
-          <t>م/ث (m/s)</t>
+          <t>درجة (°)</t>
         </is>
       </c>
       <c r="G128" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط سرعة الرياح لشهر يناير (م/ث)</t>
+          <t>خريطة الاتجاه السائد السنوي للرياح (درجات)</t>
         </is>
       </c>
     </row>
@@ -6175,32 +6175,32 @@
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>WSp_FebMn</t>
+          <t>WDr_MonMea</t>
         </is>
       </c>
       <c r="C129" s="31" t="inlineStr">
         <is>
-          <t>W_Spd_February_Mean</t>
+          <t>W_Dir_Month_Mean</t>
         </is>
       </c>
       <c r="D129" s="15" t="inlineStr">
         <is>
-          <t>05_Wind (الرياح)</t>
+          <t>05_Wind (الرياح السطحية)</t>
         </is>
       </c>
       <c r="E129" s="7" t="inlineStr">
         <is>
-          <t>متوسط سرعة الرياح على ارتفاع 10 أمتار لشهر فبراير عبر فترة الرصد.</t>
+          <t>المتوسط الشهري لاتجاه الرياح السائدة (المتوسط الدائري للشهور الـ 12).</t>
         </is>
       </c>
       <c r="F129" s="16" t="inlineStr">
         <is>
-          <t>م/ث (m/s)</t>
+          <t>°</t>
         </is>
       </c>
       <c r="G129" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط سرعة الرياح لشهر فبراير (م/ث)</t>
+          <t>خريطة المتوسط الشهري لاتجاه الرياح السائدة (°)</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="B130" s="10" t="inlineStr">
         <is>
-          <t>WSp_MarMn</t>
+          <t>WDr_WnMean</t>
         </is>
       </c>
       <c r="C130" s="29" t="inlineStr">
         <is>
-          <t>W_Spd_March_Mean</t>
+          <t>W_Dir_Winter_Mean</t>
         </is>
       </c>
       <c r="D130" s="18" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="E130" s="12" t="inlineStr">
         <is>
-          <t>متوسط سرعة الرياح على ارتفاع 10 أمتار لشهر مارس عبر فترة الرصد.</t>
+          <t>اتجاه الرياح السائد خلال فصل الشتاء الأرصادي بالدرجات الزاوية (DJF).</t>
         </is>
       </c>
       <c r="F130" s="19" t="inlineStr">
         <is>
-          <t>م/ث (m/s)</t>
+          <t>درجة (°)</t>
         </is>
       </c>
       <c r="G130" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط سرعة الرياح لشهر مارس (م/ث)</t>
+          <t>خريطة اتجاه الرياح السائد خلال فصل الشتاء (درجات)</t>
         </is>
       </c>
     </row>
@@ -6245,12 +6245,12 @@
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>WSp_AprMn</t>
+          <t>WDr_SpMean</t>
         </is>
       </c>
       <c r="C131" s="31" t="inlineStr">
         <is>
-          <t>W_Spd_April_Mean</t>
+          <t>W_Dir_Spring_Mean</t>
         </is>
       </c>
       <c r="D131" s="15" t="inlineStr">
@@ -6260,17 +6260,17 @@
       </c>
       <c r="E131" s="7" t="inlineStr">
         <is>
-          <t>متوسط سرعة الرياح على ارتفاع 10 أمتار لشهر أبريل عبر فترة الرصد.</t>
+          <t>اتجاه الرياح السائد خلال فصل الربيع الأرصادي بالدرجات الزاوية (MAM).</t>
         </is>
       </c>
       <c r="F131" s="16" t="inlineStr">
         <is>
-          <t>م/ث (m/s)</t>
+          <t>درجة (°)</t>
         </is>
       </c>
       <c r="G131" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط سرعة الرياح لشهر أبريل (م/ث)</t>
+          <t>خريطة اتجاه الرياح السائد خلال فصل الربيع (درجات)</t>
         </is>
       </c>
     </row>
@@ -6280,12 +6280,12 @@
       </c>
       <c r="B132" s="10" t="inlineStr">
         <is>
-          <t>WSp_MayMn</t>
+          <t>WDr_SuMean</t>
         </is>
       </c>
       <c r="C132" s="29" t="inlineStr">
         <is>
-          <t>W_Spd_May_Mean</t>
+          <t>W_Dir_Summer_Mean</t>
         </is>
       </c>
       <c r="D132" s="18" t="inlineStr">
@@ -6295,17 +6295,17 @@
       </c>
       <c r="E132" s="12" t="inlineStr">
         <is>
-          <t>متوسط سرعة الرياح على ارتفاع 10 أمتار لشهر مايو عبر فترة الرصد.</t>
+          <t>اتجاه الرياح السائد خلال فصل الصيف الأرصادي بالدرجات الزاوية (JJA).</t>
         </is>
       </c>
       <c r="F132" s="19" t="inlineStr">
         <is>
-          <t>م/ث (m/s)</t>
+          <t>درجة (°)</t>
         </is>
       </c>
       <c r="G132" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط سرعة الرياح لشهر مايو (م/ث)</t>
+          <t>خريطة اتجاه الرياح السائد خلال فصل الصيف (درجات)</t>
         </is>
       </c>
     </row>
@@ -6315,12 +6315,12 @@
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>WSp_JunMn</t>
+          <t>WDr_AuMean</t>
         </is>
       </c>
       <c r="C133" s="31" t="inlineStr">
         <is>
-          <t>W_Spd_June_Mean</t>
+          <t>W_Dir_Autumn_Mean</t>
         </is>
       </c>
       <c r="D133" s="15" t="inlineStr">
@@ -6330,17 +6330,17 @@
       </c>
       <c r="E133" s="7" t="inlineStr">
         <is>
-          <t>متوسط سرعة الرياح على ارتفاع 10 أمتار لشهر يونيو عبر فترة الرصد.</t>
+          <t>اتجاه الرياح السائد خلال فصل الخريف الأرصادي بالدرجات الزاوية (SON).</t>
         </is>
       </c>
       <c r="F133" s="16" t="inlineStr">
         <is>
-          <t>م/ث (m/s)</t>
+          <t>درجة (°)</t>
         </is>
       </c>
       <c r="G133" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط سرعة الرياح لشهر يونيو (م/ث)</t>
+          <t>خريطة اتجاه الرياح السائد خلال فصل الخريف (درجات)</t>
         </is>
       </c>
     </row>
@@ -6350,12 +6350,12 @@
       </c>
       <c r="B134" s="10" t="inlineStr">
         <is>
-          <t>WSp_JulMn</t>
+          <t>WSp_JanMn</t>
         </is>
       </c>
       <c r="C134" s="29" t="inlineStr">
         <is>
-          <t>W_Spd_July_Mean</t>
+          <t>W_Spd_January_Mean</t>
         </is>
       </c>
       <c r="D134" s="18" t="inlineStr">
@@ -6365,7 +6365,7 @@
       </c>
       <c r="E134" s="12" t="inlineStr">
         <is>
-          <t>متوسط سرعة الرياح على ارتفاع 10 أمتار لشهر يوليو عبر فترة الرصد.</t>
+          <t>متوسط سرعة الرياح على ارتفاع 10 أمتار لشهر يناير عبر فترة الرصد.</t>
         </is>
       </c>
       <c r="F134" s="19" t="inlineStr">
@@ -6375,7 +6375,7 @@
       </c>
       <c r="G134" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط سرعة الرياح لشهر يوليو (م/ث)</t>
+          <t>خريطة متوسط سرعة الرياح لشهر يناير (م/ث)</t>
         </is>
       </c>
     </row>
@@ -6385,12 +6385,12 @@
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>WSp_AugMn</t>
+          <t>WSp_FebMn</t>
         </is>
       </c>
       <c r="C135" s="31" t="inlineStr">
         <is>
-          <t>W_Spd_August_Mean</t>
+          <t>W_Spd_February_Mean</t>
         </is>
       </c>
       <c r="D135" s="15" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="E135" s="7" t="inlineStr">
         <is>
-          <t>متوسط سرعة الرياح على ارتفاع 10 أمتار لشهر أغسطس عبر فترة الرصد.</t>
+          <t>متوسط سرعة الرياح على ارتفاع 10 أمتار لشهر فبراير عبر فترة الرصد.</t>
         </is>
       </c>
       <c r="F135" s="16" t="inlineStr">
@@ -6410,7 +6410,7 @@
       </c>
       <c r="G135" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط سرعة الرياح لشهر أغسطس (م/ث)</t>
+          <t>خريطة متوسط سرعة الرياح لشهر فبراير (م/ث)</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="B136" s="10" t="inlineStr">
         <is>
-          <t>WSp_SepMn</t>
+          <t>WSp_MarMn</t>
         </is>
       </c>
       <c r="C136" s="29" t="inlineStr">
         <is>
-          <t>W_Spd_September_Mean</t>
+          <t>W_Spd_March_Mean</t>
         </is>
       </c>
       <c r="D136" s="18" t="inlineStr">
@@ -6435,7 +6435,7 @@
       </c>
       <c r="E136" s="12" t="inlineStr">
         <is>
-          <t>متوسط سرعة الرياح على ارتفاع 10 أمتار لشهر سبتمبر عبر فترة الرصد.</t>
+          <t>متوسط سرعة الرياح على ارتفاع 10 أمتار لشهر مارس عبر فترة الرصد.</t>
         </is>
       </c>
       <c r="F136" s="19" t="inlineStr">
@@ -6445,7 +6445,7 @@
       </c>
       <c r="G136" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط سرعة الرياح لشهر سبتمبر (م/ث)</t>
+          <t>خريطة متوسط سرعة الرياح لشهر مارس (م/ث)</t>
         </is>
       </c>
     </row>
@@ -6455,12 +6455,12 @@
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>WSp_OctMn</t>
+          <t>WSp_AprMn</t>
         </is>
       </c>
       <c r="C137" s="31" t="inlineStr">
         <is>
-          <t>W_Spd_October_Mean</t>
+          <t>W_Spd_April_Mean</t>
         </is>
       </c>
       <c r="D137" s="15" t="inlineStr">
@@ -6470,7 +6470,7 @@
       </c>
       <c r="E137" s="7" t="inlineStr">
         <is>
-          <t>متوسط سرعة الرياح على ارتفاع 10 أمتار لشهر أكتوبر عبر فترة الرصد.</t>
+          <t>متوسط سرعة الرياح على ارتفاع 10 أمتار لشهر أبريل عبر فترة الرصد.</t>
         </is>
       </c>
       <c r="F137" s="16" t="inlineStr">
@@ -6480,7 +6480,7 @@
       </c>
       <c r="G137" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط سرعة الرياح لشهر أكتوبر (م/ث)</t>
+          <t>خريطة متوسط سرعة الرياح لشهر أبريل (م/ث)</t>
         </is>
       </c>
     </row>
@@ -6490,12 +6490,12 @@
       </c>
       <c r="B138" s="10" t="inlineStr">
         <is>
-          <t>WSp_NovMn</t>
+          <t>WSp_MayMn</t>
         </is>
       </c>
       <c r="C138" s="29" t="inlineStr">
         <is>
-          <t>W_Spd_November_Mean</t>
+          <t>W_Spd_May_Mean</t>
         </is>
       </c>
       <c r="D138" s="18" t="inlineStr">
@@ -6505,7 +6505,7 @@
       </c>
       <c r="E138" s="12" t="inlineStr">
         <is>
-          <t>متوسط سرعة الرياح على ارتفاع 10 أمتار لشهر نوفمبر عبر فترة الرصد.</t>
+          <t>متوسط سرعة الرياح على ارتفاع 10 أمتار لشهر مايو عبر فترة الرصد.</t>
         </is>
       </c>
       <c r="F138" s="19" t="inlineStr">
@@ -6515,7 +6515,7 @@
       </c>
       <c r="G138" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط سرعة الرياح لشهر نوفمبر (م/ث)</t>
+          <t>خريطة متوسط سرعة الرياح لشهر مايو (م/ث)</t>
         </is>
       </c>
     </row>
@@ -6525,12 +6525,12 @@
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>WSp_DecMn</t>
+          <t>WSp_JunMn</t>
         </is>
       </c>
       <c r="C139" s="31" t="inlineStr">
         <is>
-          <t>W_Spd_December_Mean</t>
+          <t>W_Spd_June_Mean</t>
         </is>
       </c>
       <c r="D139" s="15" t="inlineStr">
@@ -6540,7 +6540,7 @@
       </c>
       <c r="E139" s="7" t="inlineStr">
         <is>
-          <t>متوسط سرعة الرياح على ارتفاع 10 أمتار لشهر ديسمبر عبر فترة الرصد.</t>
+          <t>متوسط سرعة الرياح على ارتفاع 10 أمتار لشهر يونيو عبر فترة الرصد.</t>
         </is>
       </c>
       <c r="F139" s="16" t="inlineStr">
@@ -6550,7 +6550,7 @@
       </c>
       <c r="G139" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط سرعة الرياح لشهر ديسمبر (م/ث)</t>
+          <t>خريطة متوسط سرعة الرياح لشهر يونيو (م/ث)</t>
         </is>
       </c>
     </row>
@@ -6560,12 +6560,12 @@
       </c>
       <c r="B140" s="10" t="inlineStr">
         <is>
-          <t>WDr_JanMn</t>
+          <t>WSp_JulMn</t>
         </is>
       </c>
       <c r="C140" s="29" t="inlineStr">
         <is>
-          <t>W_Dir_January_Mean</t>
+          <t>W_Spd_July_Mean</t>
         </is>
       </c>
       <c r="D140" s="18" t="inlineStr">
@@ -6575,17 +6575,17 @@
       </c>
       <c r="E140" s="12" t="inlineStr">
         <is>
-          <t>متوسط اتجاه الرياح السائد لشهر يناير محسوب بالمتوسط الدائري المتجهي (atan2).</t>
+          <t>متوسط سرعة الرياح على ارتفاع 10 أمتار لشهر يوليو عبر فترة الرصد.</t>
         </is>
       </c>
       <c r="F140" s="19" t="inlineStr">
         <is>
-          <t>درجة (°) / Degree</t>
+          <t>م/ث (m/s)</t>
         </is>
       </c>
       <c r="G140" s="30" t="inlineStr">
         <is>
-          <t>خريطة اتجاه الرياح السائد لشهر يناير (°)</t>
+          <t>خريطة متوسط سرعة الرياح لشهر يوليو (م/ث)</t>
         </is>
       </c>
     </row>
@@ -6595,12 +6595,12 @@
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>WDr_FebMn</t>
+          <t>WSp_AugMn</t>
         </is>
       </c>
       <c r="C141" s="31" t="inlineStr">
         <is>
-          <t>W_Dir_February_Mean</t>
+          <t>W_Spd_August_Mean</t>
         </is>
       </c>
       <c r="D141" s="15" t="inlineStr">
@@ -6610,17 +6610,17 @@
       </c>
       <c r="E141" s="7" t="inlineStr">
         <is>
-          <t>متوسط اتجاه الرياح السائد لشهر فبراير محسوب بالمتوسط الدائري المتجهي (atan2).</t>
+          <t>متوسط سرعة الرياح على ارتفاع 10 أمتار لشهر أغسطس عبر فترة الرصد.</t>
         </is>
       </c>
       <c r="F141" s="16" t="inlineStr">
         <is>
-          <t>درجة (°) / Degree</t>
+          <t>م/ث (m/s)</t>
         </is>
       </c>
       <c r="G141" s="32" t="inlineStr">
         <is>
-          <t>خريطة اتجاه الرياح السائد لشهر فبراير (°)</t>
+          <t>خريطة متوسط سرعة الرياح لشهر أغسطس (م/ث)</t>
         </is>
       </c>
     </row>
@@ -6630,12 +6630,12 @@
       </c>
       <c r="B142" s="10" t="inlineStr">
         <is>
-          <t>WDr_MarMn</t>
+          <t>WSp_SepMn</t>
         </is>
       </c>
       <c r="C142" s="29" t="inlineStr">
         <is>
-          <t>W_Dir_March_Mean</t>
+          <t>W_Spd_September_Mean</t>
         </is>
       </c>
       <c r="D142" s="18" t="inlineStr">
@@ -6645,17 +6645,17 @@
       </c>
       <c r="E142" s="12" t="inlineStr">
         <is>
-          <t>متوسط اتجاه الرياح السائد لشهر مارس محسوب بالمتوسط الدائري المتجهي (atan2).</t>
+          <t>متوسط سرعة الرياح على ارتفاع 10 أمتار لشهر سبتمبر عبر فترة الرصد.</t>
         </is>
       </c>
       <c r="F142" s="19" t="inlineStr">
         <is>
-          <t>درجة (°) / Degree</t>
+          <t>م/ث (m/s)</t>
         </is>
       </c>
       <c r="G142" s="30" t="inlineStr">
         <is>
-          <t>خريطة اتجاه الرياح السائد لشهر مارس (°)</t>
+          <t>خريطة متوسط سرعة الرياح لشهر سبتمبر (م/ث)</t>
         </is>
       </c>
     </row>
@@ -6665,12 +6665,12 @@
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>WDr_AprMn</t>
+          <t>WSp_OctMn</t>
         </is>
       </c>
       <c r="C143" s="31" t="inlineStr">
         <is>
-          <t>W_Dir_April_Mean</t>
+          <t>W_Spd_October_Mean</t>
         </is>
       </c>
       <c r="D143" s="15" t="inlineStr">
@@ -6680,17 +6680,17 @@
       </c>
       <c r="E143" s="7" t="inlineStr">
         <is>
-          <t>متوسط اتجاه الرياح السائد لشهر أبريل محسوب بالمتوسط الدائري المتجهي (atan2).</t>
+          <t>متوسط سرعة الرياح على ارتفاع 10 أمتار لشهر أكتوبر عبر فترة الرصد.</t>
         </is>
       </c>
       <c r="F143" s="16" t="inlineStr">
         <is>
-          <t>درجة (°) / Degree</t>
+          <t>م/ث (m/s)</t>
         </is>
       </c>
       <c r="G143" s="32" t="inlineStr">
         <is>
-          <t>خريطة اتجاه الرياح السائد لشهر أبريل (°)</t>
+          <t>خريطة متوسط سرعة الرياح لشهر أكتوبر (م/ث)</t>
         </is>
       </c>
     </row>
@@ -6700,12 +6700,12 @@
       </c>
       <c r="B144" s="10" t="inlineStr">
         <is>
-          <t>WDr_MayMn</t>
+          <t>WSp_NovMn</t>
         </is>
       </c>
       <c r="C144" s="29" t="inlineStr">
         <is>
-          <t>W_Dir_May_Mean</t>
+          <t>W_Spd_November_Mean</t>
         </is>
       </c>
       <c r="D144" s="18" t="inlineStr">
@@ -6715,17 +6715,17 @@
       </c>
       <c r="E144" s="12" t="inlineStr">
         <is>
-          <t>متوسط اتجاه الرياح السائد لشهر مايو محسوب بالمتوسط الدائري المتجهي (atan2).</t>
+          <t>متوسط سرعة الرياح على ارتفاع 10 أمتار لشهر نوفمبر عبر فترة الرصد.</t>
         </is>
       </c>
       <c r="F144" s="19" t="inlineStr">
         <is>
-          <t>درجة (°) / Degree</t>
+          <t>م/ث (m/s)</t>
         </is>
       </c>
       <c r="G144" s="30" t="inlineStr">
         <is>
-          <t>خريطة اتجاه الرياح السائد لشهر مايو (°)</t>
+          <t>خريطة متوسط سرعة الرياح لشهر نوفمبر (م/ث)</t>
         </is>
       </c>
     </row>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>WDr_JunMn</t>
+          <t>WSp_DecMn</t>
         </is>
       </c>
       <c r="C145" s="31" t="inlineStr">
         <is>
-          <t>W_Dir_June_Mean</t>
+          <t>W_Spd_December_Mean</t>
         </is>
       </c>
       <c r="D145" s="15" t="inlineStr">
@@ -6750,17 +6750,17 @@
       </c>
       <c r="E145" s="7" t="inlineStr">
         <is>
-          <t>متوسط اتجاه الرياح السائد لشهر يونيو محسوب بالمتوسط الدائري المتجهي (atan2).</t>
+          <t>متوسط سرعة الرياح على ارتفاع 10 أمتار لشهر ديسمبر عبر فترة الرصد.</t>
         </is>
       </c>
       <c r="F145" s="16" t="inlineStr">
         <is>
-          <t>درجة (°) / Degree</t>
+          <t>م/ث (m/s)</t>
         </is>
       </c>
       <c r="G145" s="32" t="inlineStr">
         <is>
-          <t>خريطة اتجاه الرياح السائد لشهر يونيو (°)</t>
+          <t>خريطة متوسط سرعة الرياح لشهر ديسمبر (م/ث)</t>
         </is>
       </c>
     </row>
@@ -6770,12 +6770,12 @@
       </c>
       <c r="B146" s="10" t="inlineStr">
         <is>
-          <t>WDr_JulMn</t>
+          <t>WDr_JanMn</t>
         </is>
       </c>
       <c r="C146" s="29" t="inlineStr">
         <is>
-          <t>W_Dir_July_Mean</t>
+          <t>W_Dir_January_Mean</t>
         </is>
       </c>
       <c r="D146" s="18" t="inlineStr">
@@ -6785,7 +6785,7 @@
       </c>
       <c r="E146" s="12" t="inlineStr">
         <is>
-          <t>متوسط اتجاه الرياح السائد لشهر يوليو محسوب بالمتوسط الدائري المتجهي (atan2).</t>
+          <t>متوسط اتجاه الرياح السائد لشهر يناير محسوب بالمتوسط الدائري المتجهي (atan2).</t>
         </is>
       </c>
       <c r="F146" s="19" t="inlineStr">
@@ -6795,7 +6795,7 @@
       </c>
       <c r="G146" s="30" t="inlineStr">
         <is>
-          <t>خريطة اتجاه الرياح السائد لشهر يوليو (°)</t>
+          <t>خريطة اتجاه الرياح السائد لشهر يناير (°)</t>
         </is>
       </c>
     </row>
@@ -6805,12 +6805,12 @@
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>WDr_AugMn</t>
+          <t>WDr_FebMn</t>
         </is>
       </c>
       <c r="C147" s="31" t="inlineStr">
         <is>
-          <t>W_Dir_August_Mean</t>
+          <t>W_Dir_February_Mean</t>
         </is>
       </c>
       <c r="D147" s="15" t="inlineStr">
@@ -6820,7 +6820,7 @@
       </c>
       <c r="E147" s="7" t="inlineStr">
         <is>
-          <t>متوسط اتجاه الرياح السائد لشهر أغسطس محسوب بالمتوسط الدائري المتجهي (atan2).</t>
+          <t>متوسط اتجاه الرياح السائد لشهر فبراير محسوب بالمتوسط الدائري المتجهي (atan2).</t>
         </is>
       </c>
       <c r="F147" s="16" t="inlineStr">
@@ -6830,7 +6830,7 @@
       </c>
       <c r="G147" s="32" t="inlineStr">
         <is>
-          <t>خريطة اتجاه الرياح السائد لشهر أغسطس (°)</t>
+          <t>خريطة اتجاه الرياح السائد لشهر فبراير (°)</t>
         </is>
       </c>
     </row>
@@ -6840,12 +6840,12 @@
       </c>
       <c r="B148" s="10" t="inlineStr">
         <is>
-          <t>WDr_SepMn</t>
+          <t>WDr_MarMn</t>
         </is>
       </c>
       <c r="C148" s="29" t="inlineStr">
         <is>
-          <t>W_Dir_September_Mean</t>
+          <t>W_Dir_March_Mean</t>
         </is>
       </c>
       <c r="D148" s="18" t="inlineStr">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="E148" s="12" t="inlineStr">
         <is>
-          <t>متوسط اتجاه الرياح السائد لشهر سبتمبر محسوب بالمتوسط الدائري المتجهي (atan2).</t>
+          <t>متوسط اتجاه الرياح السائد لشهر مارس محسوب بالمتوسط الدائري المتجهي (atan2).</t>
         </is>
       </c>
       <c r="F148" s="19" t="inlineStr">
@@ -6865,7 +6865,7 @@
       </c>
       <c r="G148" s="30" t="inlineStr">
         <is>
-          <t>خريطة اتجاه الرياح السائد لشهر سبتمبر (°)</t>
+          <t>خريطة اتجاه الرياح السائد لشهر مارس (°)</t>
         </is>
       </c>
     </row>
@@ -6875,12 +6875,12 @@
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>WDr_OctMn</t>
+          <t>WDr_AprMn</t>
         </is>
       </c>
       <c r="C149" s="31" t="inlineStr">
         <is>
-          <t>W_Dir_October_Mean</t>
+          <t>W_Dir_April_Mean</t>
         </is>
       </c>
       <c r="D149" s="15" t="inlineStr">
@@ -6890,7 +6890,7 @@
       </c>
       <c r="E149" s="7" t="inlineStr">
         <is>
-          <t>متوسط اتجاه الرياح السائد لشهر أكتوبر محسوب بالمتوسط الدائري المتجهي (atan2).</t>
+          <t>متوسط اتجاه الرياح السائد لشهر أبريل محسوب بالمتوسط الدائري المتجهي (atan2).</t>
         </is>
       </c>
       <c r="F149" s="16" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="G149" s="32" t="inlineStr">
         <is>
-          <t>خريطة اتجاه الرياح السائد لشهر أكتوبر (°)</t>
+          <t>خريطة اتجاه الرياح السائد لشهر أبريل (°)</t>
         </is>
       </c>
     </row>
@@ -6910,12 +6910,12 @@
       </c>
       <c r="B150" s="10" t="inlineStr">
         <is>
-          <t>WDr_NovMn</t>
+          <t>WDr_MayMn</t>
         </is>
       </c>
       <c r="C150" s="29" t="inlineStr">
         <is>
-          <t>W_Dir_November_Mean</t>
+          <t>W_Dir_May_Mean</t>
         </is>
       </c>
       <c r="D150" s="18" t="inlineStr">
@@ -6925,7 +6925,7 @@
       </c>
       <c r="E150" s="12" t="inlineStr">
         <is>
-          <t>متوسط اتجاه الرياح السائد لشهر نوفمبر محسوب بالمتوسط الدائري المتجهي (atan2).</t>
+          <t>متوسط اتجاه الرياح السائد لشهر مايو محسوب بالمتوسط الدائري المتجهي (atan2).</t>
         </is>
       </c>
       <c r="F150" s="19" t="inlineStr">
@@ -6935,7 +6935,7 @@
       </c>
       <c r="G150" s="30" t="inlineStr">
         <is>
-          <t>خريطة اتجاه الرياح السائد لشهر نوفمبر (°)</t>
+          <t>خريطة اتجاه الرياح السائد لشهر مايو (°)</t>
         </is>
       </c>
     </row>
@@ -6945,12 +6945,12 @@
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>WDr_DecMn</t>
+          <t>WDr_JunMn</t>
         </is>
       </c>
       <c r="C151" s="31" t="inlineStr">
         <is>
-          <t>W_Dir_December_Mean</t>
+          <t>W_Dir_June_Mean</t>
         </is>
       </c>
       <c r="D151" s="15" t="inlineStr">
@@ -6960,7 +6960,7 @@
       </c>
       <c r="E151" s="7" t="inlineStr">
         <is>
-          <t>متوسط اتجاه الرياح السائد لشهر ديسمبر محسوب بالمتوسط الدائري المتجهي (atan2).</t>
+          <t>متوسط اتجاه الرياح السائد لشهر يونيو محسوب بالمتوسط الدائري المتجهي (atan2).</t>
         </is>
       </c>
       <c r="F151" s="16" t="inlineStr">
@@ -6970,7 +6970,7 @@
       </c>
       <c r="G151" s="32" t="inlineStr">
         <is>
-          <t>خريطة اتجاه الرياح السائد لشهر ديسمبر (°)</t>
+          <t>خريطة اتجاه الرياح السائد لشهر يونيو (°)</t>
         </is>
       </c>
     </row>
@@ -6980,32 +6980,32 @@
       </c>
       <c r="B152" s="10" t="inlineStr">
         <is>
-          <t>RH_AnMean</t>
+          <t>WDr_JulMn</t>
         </is>
       </c>
       <c r="C152" s="29" t="inlineStr">
         <is>
-          <t>RH_Annual_Mean</t>
+          <t>W_Dir_July_Mean</t>
         </is>
       </c>
       <c r="D152" s="18" t="inlineStr">
         <is>
-          <t>06_Relative_Humidity (الرطوبة النسبية)</t>
+          <t>05_Wind (الرياح)</t>
         </is>
       </c>
       <c r="E152" s="12" t="inlineStr">
         <is>
-          <t>المتوسط الحسابي السنوي للرطوبة النسبية للهواء عند ارتفاع 2 متر كنسبة مئوية.</t>
+          <t>متوسط اتجاه الرياح السائد لشهر يوليو محسوب بالمتوسط الدائري المتجهي (atan2).</t>
         </is>
       </c>
       <c r="F152" s="19" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>درجة (°) / Degree</t>
         </is>
       </c>
       <c r="G152" s="30" t="inlineStr">
         <is>
-          <t>خريطة المتوسط السنوي للرطوبة النسبية (%)</t>
+          <t>خريطة اتجاه الرياح السائد لشهر يوليو (°)</t>
         </is>
       </c>
     </row>
@@ -7015,32 +7015,32 @@
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>RH_WnMean</t>
+          <t>WDr_AugMn</t>
         </is>
       </c>
       <c r="C153" s="31" t="inlineStr">
         <is>
-          <t>RH_Winter_Mean</t>
+          <t>W_Dir_August_Mean</t>
         </is>
       </c>
       <c r="D153" s="15" t="inlineStr">
         <is>
-          <t>06_Relative_Humidity (الرطوبة النسبية)</t>
+          <t>05_Wind (الرياح)</t>
         </is>
       </c>
       <c r="E153" s="7" t="inlineStr">
         <is>
-          <t>متوسط الرطوبة النسبية لفصل الشتاء الأرصادي (DJF).</t>
+          <t>متوسط اتجاه الرياح السائد لشهر أغسطس محسوب بالمتوسط الدائري المتجهي (atan2).</t>
         </is>
       </c>
       <c r="F153" s="16" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>درجة (°) / Degree</t>
         </is>
       </c>
       <c r="G153" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط الرطوبة النسبية خلال فصل الشتاء (%)</t>
+          <t>خريطة اتجاه الرياح السائد لشهر أغسطس (°)</t>
         </is>
       </c>
     </row>
@@ -7050,32 +7050,32 @@
       </c>
       <c r="B154" s="10" t="inlineStr">
         <is>
-          <t>RH_SpMean</t>
+          <t>WDr_SepMn</t>
         </is>
       </c>
       <c r="C154" s="29" t="inlineStr">
         <is>
-          <t>RH_Spring_Mean</t>
+          <t>W_Dir_September_Mean</t>
         </is>
       </c>
       <c r="D154" s="18" t="inlineStr">
         <is>
-          <t>06_Relative_Humidity (الرطوبة النسبية)</t>
+          <t>05_Wind (الرياح)</t>
         </is>
       </c>
       <c r="E154" s="12" t="inlineStr">
         <is>
-          <t>متوسط الرطوبة النسبية لفصل الربيع الأرصادي (MAM).</t>
+          <t>متوسط اتجاه الرياح السائد لشهر سبتمبر محسوب بالمتوسط الدائري المتجهي (atan2).</t>
         </is>
       </c>
       <c r="F154" s="19" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>درجة (°) / Degree</t>
         </is>
       </c>
       <c r="G154" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط الرطوبة النسبية خلال فصل الربيع (%)</t>
+          <t>خريطة اتجاه الرياح السائد لشهر سبتمبر (°)</t>
         </is>
       </c>
     </row>
@@ -7085,32 +7085,32 @@
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
-          <t>RH_SuMean</t>
+          <t>WDr_OctMn</t>
         </is>
       </c>
       <c r="C155" s="31" t="inlineStr">
         <is>
-          <t>RH_Summer_Mean</t>
+          <t>W_Dir_October_Mean</t>
         </is>
       </c>
       <c r="D155" s="15" t="inlineStr">
         <is>
-          <t>06_Relative_Humidity (الرطوبة النسبية)</t>
+          <t>05_Wind (الرياح)</t>
         </is>
       </c>
       <c r="E155" s="7" t="inlineStr">
         <is>
-          <t>متوسط الرطوبة النسبية لفصل الصيف الأرصادي (JJA).</t>
+          <t>متوسط اتجاه الرياح السائد لشهر أكتوبر محسوب بالمتوسط الدائري المتجهي (atan2).</t>
         </is>
       </c>
       <c r="F155" s="16" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>درجة (°) / Degree</t>
         </is>
       </c>
       <c r="G155" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط الرطوبة النسبية خلال فصل الصيف (%)</t>
+          <t>خريطة اتجاه الرياح السائد لشهر أكتوبر (°)</t>
         </is>
       </c>
     </row>
@@ -7120,32 +7120,32 @@
       </c>
       <c r="B156" s="10" t="inlineStr">
         <is>
-          <t>RH_AuMean</t>
+          <t>WDr_NovMn</t>
         </is>
       </c>
       <c r="C156" s="29" t="inlineStr">
         <is>
-          <t>RH_Autumn_Mean</t>
+          <t>W_Dir_November_Mean</t>
         </is>
       </c>
       <c r="D156" s="18" t="inlineStr">
         <is>
-          <t>06_Relative_Humidity (الرطوبة النسبية)</t>
+          <t>05_Wind (الرياح)</t>
         </is>
       </c>
       <c r="E156" s="12" t="inlineStr">
         <is>
-          <t>متوسط الرطوبة النسبية لفصل الخريف الأرصادي (SON).</t>
+          <t>متوسط اتجاه الرياح السائد لشهر نوفمبر محسوب بالمتوسط الدائري المتجهي (atan2).</t>
         </is>
       </c>
       <c r="F156" s="19" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>درجة (°) / Degree</t>
         </is>
       </c>
       <c r="G156" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط الرطوبة النسبية خلال فصل الخريف (%)</t>
+          <t>خريطة اتجاه الرياح السائد لشهر نوفمبر (°)</t>
         </is>
       </c>
     </row>
@@ -7155,32 +7155,32 @@
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>RH_AnRng</t>
+          <t>WDr_DecMn</t>
         </is>
       </c>
       <c r="C157" s="31" t="inlineStr">
         <is>
-          <t>RH_Annual_Range</t>
+          <t>W_Dir_December_Mean</t>
         </is>
       </c>
       <c r="D157" s="15" t="inlineStr">
         <is>
-          <t>06_Relative_Humidity (الرطوبة النسبية)</t>
+          <t>05_Wind (الرياح)</t>
         </is>
       </c>
       <c r="E157" s="7" t="inlineStr">
         <is>
-          <t>المدى السنوي للرطوبة النسبية (الفارق بين أعلى شهر رطوبة وأدنى شهر رطوبة).</t>
+          <t>متوسط اتجاه الرياح السائد لشهر ديسمبر محسوب بالمتوسط الدائري المتجهي (atan2).</t>
         </is>
       </c>
       <c r="F157" s="16" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>درجة (°) / Degree</t>
         </is>
       </c>
       <c r="G157" s="32" t="inlineStr">
         <is>
-          <t>خريطة المدى السنوي للرطوبة النسبية (%)</t>
+          <t>خريطة اتجاه الرياح السائد لشهر ديسمبر (°)</t>
         </is>
       </c>
     </row>
@@ -7190,12 +7190,12 @@
       </c>
       <c r="B158" s="10" t="inlineStr">
         <is>
-          <t>RH_JanMean</t>
+          <t>RH_AnMean</t>
         </is>
       </c>
       <c r="C158" s="29" t="inlineStr">
         <is>
-          <t>RH_January_Mean</t>
+          <t>RH_Annual_Mean</t>
         </is>
       </c>
       <c r="D158" s="18" t="inlineStr">
@@ -7205,7 +7205,7 @@
       </c>
       <c r="E158" s="12" t="inlineStr">
         <is>
-          <t>متوسط الرطوبة النسبية عند ارتفاع 2 متر لشهر يناير عبر فترة الرصد.</t>
+          <t>المتوسط الحسابي السنوي للرطوبة النسبية للهواء عند ارتفاع 2 متر كنسبة مئوية.</t>
         </is>
       </c>
       <c r="F158" s="19" t="inlineStr">
@@ -7215,7 +7215,7 @@
       </c>
       <c r="G158" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط الرطوبة النسبية لشهر يناير (%)</t>
+          <t>خريطة المتوسط السنوي للرطوبة النسبية (%)</t>
         </is>
       </c>
     </row>
@@ -7225,12 +7225,12 @@
       </c>
       <c r="B159" s="5" t="inlineStr">
         <is>
-          <t>RH_FebMean</t>
+          <t>RH_MonMean</t>
         </is>
       </c>
       <c r="C159" s="31" t="inlineStr">
         <is>
-          <t>RH_February_Mean</t>
+          <t>RH_Month_Mean</t>
         </is>
       </c>
       <c r="D159" s="15" t="inlineStr">
@@ -7240,7 +7240,7 @@
       </c>
       <c r="E159" s="7" t="inlineStr">
         <is>
-          <t>متوسط الرطوبة النسبية عند ارتفاع 2 متر لشهر فبراير عبر فترة الرصد.</t>
+          <t>المتوسط الشهري للرطوبة النسبية عند ارتفاع 2 متر (متوسط الـ 12 شهراً).</t>
         </is>
       </c>
       <c r="F159" s="16" t="inlineStr">
@@ -7250,7 +7250,7 @@
       </c>
       <c r="G159" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط الرطوبة النسبية لشهر فبراير (%)</t>
+          <t>خريطة المتوسط الشهري للرطوبة النسبية (%)</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="B160" s="10" t="inlineStr">
         <is>
-          <t>RH_MarMean</t>
+          <t>RH_WnMean</t>
         </is>
       </c>
       <c r="C160" s="29" t="inlineStr">
         <is>
-          <t>RH_March_Mean</t>
+          <t>RH_Winter_Mean</t>
         </is>
       </c>
       <c r="D160" s="18" t="inlineStr">
@@ -7275,7 +7275,7 @@
       </c>
       <c r="E160" s="12" t="inlineStr">
         <is>
-          <t>متوسط الرطوبة النسبية عند ارتفاع 2 متر لشهر مارس عبر فترة الرصد.</t>
+          <t>متوسط الرطوبة النسبية لفصل الشتاء الأرصادي (DJF).</t>
         </is>
       </c>
       <c r="F160" s="19" t="inlineStr">
@@ -7285,7 +7285,7 @@
       </c>
       <c r="G160" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط الرطوبة النسبية لشهر مارس (%)</t>
+          <t>خريطة متوسط الرطوبة النسبية خلال فصل الشتاء (%)</t>
         </is>
       </c>
     </row>
@@ -7295,12 +7295,12 @@
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
-          <t>RH_AprMean</t>
+          <t>RH_SpMean</t>
         </is>
       </c>
       <c r="C161" s="31" t="inlineStr">
         <is>
-          <t>RH_April_Mean</t>
+          <t>RH_Spring_Mean</t>
         </is>
       </c>
       <c r="D161" s="15" t="inlineStr">
@@ -7310,7 +7310,7 @@
       </c>
       <c r="E161" s="7" t="inlineStr">
         <is>
-          <t>متوسط الرطوبة النسبية عند ارتفاع 2 متر لشهر أبريل عبر فترة الرصد.</t>
+          <t>متوسط الرطوبة النسبية لفصل الربيع الأرصادي (MAM).</t>
         </is>
       </c>
       <c r="F161" s="16" t="inlineStr">
@@ -7320,7 +7320,7 @@
       </c>
       <c r="G161" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط الرطوبة النسبية لشهر أبريل (%)</t>
+          <t>خريطة متوسط الرطوبة النسبية خلال فصل الربيع (%)</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="B162" s="10" t="inlineStr">
         <is>
-          <t>RH_MayMean</t>
+          <t>RH_SuMean</t>
         </is>
       </c>
       <c r="C162" s="29" t="inlineStr">
         <is>
-          <t>RH_May_Mean</t>
+          <t>RH_Summer_Mean</t>
         </is>
       </c>
       <c r="D162" s="18" t="inlineStr">
@@ -7345,7 +7345,7 @@
       </c>
       <c r="E162" s="12" t="inlineStr">
         <is>
-          <t>متوسط الرطوبة النسبية عند ارتفاع 2 متر لشهر مايو عبر فترة الرصد.</t>
+          <t>متوسط الرطوبة النسبية لفصل الصيف الأرصادي (JJA).</t>
         </is>
       </c>
       <c r="F162" s="19" t="inlineStr">
@@ -7355,7 +7355,7 @@
       </c>
       <c r="G162" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط الرطوبة النسبية لشهر مايو (%)</t>
+          <t>خريطة متوسط الرطوبة النسبية خلال فصل الصيف (%)</t>
         </is>
       </c>
     </row>
@@ -7365,12 +7365,12 @@
       </c>
       <c r="B163" s="5" t="inlineStr">
         <is>
-          <t>RH_JunMean</t>
+          <t>RH_AuMean</t>
         </is>
       </c>
       <c r="C163" s="31" t="inlineStr">
         <is>
-          <t>RH_June_Mean</t>
+          <t>RH_Autumn_Mean</t>
         </is>
       </c>
       <c r="D163" s="15" t="inlineStr">
@@ -7380,7 +7380,7 @@
       </c>
       <c r="E163" s="7" t="inlineStr">
         <is>
-          <t>متوسط الرطوبة النسبية عند ارتفاع 2 متر لشهر يونيو عبر فترة الرصد.</t>
+          <t>متوسط الرطوبة النسبية لفصل الخريف الأرصادي (SON).</t>
         </is>
       </c>
       <c r="F163" s="16" t="inlineStr">
@@ -7390,7 +7390,7 @@
       </c>
       <c r="G163" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط الرطوبة النسبية لشهر يونيو (%)</t>
+          <t>خريطة متوسط الرطوبة النسبية خلال فصل الخريف (%)</t>
         </is>
       </c>
     </row>
@@ -7400,12 +7400,12 @@
       </c>
       <c r="B164" s="10" t="inlineStr">
         <is>
-          <t>RH_JulMean</t>
+          <t>RH_AnRng</t>
         </is>
       </c>
       <c r="C164" s="29" t="inlineStr">
         <is>
-          <t>RH_July_Mean</t>
+          <t>RH_Annual_Range</t>
         </is>
       </c>
       <c r="D164" s="18" t="inlineStr">
@@ -7415,7 +7415,7 @@
       </c>
       <c r="E164" s="12" t="inlineStr">
         <is>
-          <t>متوسط الرطوبة النسبية عند ارتفاع 2 متر لشهر يوليو عبر فترة الرصد.</t>
+          <t>المدى السنوي للرطوبة النسبية (الفارق بين أعلى شهر رطوبة وأدنى شهر رطوبة).</t>
         </is>
       </c>
       <c r="F164" s="19" t="inlineStr">
@@ -7425,7 +7425,7 @@
       </c>
       <c r="G164" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط الرطوبة النسبية لشهر يوليو (%)</t>
+          <t>خريطة المدى السنوي للرطوبة النسبية (%)</t>
         </is>
       </c>
     </row>
@@ -7435,12 +7435,12 @@
       </c>
       <c r="B165" s="5" t="inlineStr">
         <is>
-          <t>RH_AugMean</t>
+          <t>RH_JanMean</t>
         </is>
       </c>
       <c r="C165" s="31" t="inlineStr">
         <is>
-          <t>RH_August_Mean</t>
+          <t>RH_January_Mean</t>
         </is>
       </c>
       <c r="D165" s="15" t="inlineStr">
@@ -7450,7 +7450,7 @@
       </c>
       <c r="E165" s="7" t="inlineStr">
         <is>
-          <t>متوسط الرطوبة النسبية عند ارتفاع 2 متر لشهر أغسطس عبر فترة الرصد.</t>
+          <t>متوسط الرطوبة النسبية عند ارتفاع 2 متر لشهر يناير عبر فترة الرصد.</t>
         </is>
       </c>
       <c r="F165" s="16" t="inlineStr">
@@ -7460,7 +7460,7 @@
       </c>
       <c r="G165" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط الرطوبة النسبية لشهر أغسطس (%)</t>
+          <t>خريطة متوسط الرطوبة النسبية لشهر يناير (%)</t>
         </is>
       </c>
     </row>
@@ -7470,12 +7470,12 @@
       </c>
       <c r="B166" s="10" t="inlineStr">
         <is>
-          <t>RH_SepMean</t>
+          <t>RH_FebMean</t>
         </is>
       </c>
       <c r="C166" s="29" t="inlineStr">
         <is>
-          <t>RH_September_Mean</t>
+          <t>RH_February_Mean</t>
         </is>
       </c>
       <c r="D166" s="18" t="inlineStr">
@@ -7485,7 +7485,7 @@
       </c>
       <c r="E166" s="12" t="inlineStr">
         <is>
-          <t>متوسط الرطوبة النسبية عند ارتفاع 2 متر لشهر سبتمبر عبر فترة الرصد.</t>
+          <t>متوسط الرطوبة النسبية عند ارتفاع 2 متر لشهر فبراير عبر فترة الرصد.</t>
         </is>
       </c>
       <c r="F166" s="19" t="inlineStr">
@@ -7495,7 +7495,7 @@
       </c>
       <c r="G166" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط الرطوبة النسبية لشهر سبتمبر (%)</t>
+          <t>خريطة متوسط الرطوبة النسبية لشهر فبراير (%)</t>
         </is>
       </c>
     </row>
@@ -7505,12 +7505,12 @@
       </c>
       <c r="B167" s="5" t="inlineStr">
         <is>
-          <t>RH_OctMean</t>
+          <t>RH_MarMean</t>
         </is>
       </c>
       <c r="C167" s="31" t="inlineStr">
         <is>
-          <t>RH_October_Mean</t>
+          <t>RH_March_Mean</t>
         </is>
       </c>
       <c r="D167" s="15" t="inlineStr">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="E167" s="7" t="inlineStr">
         <is>
-          <t>متوسط الرطوبة النسبية عند ارتفاع 2 متر لشهر أكتوبر عبر فترة الرصد.</t>
+          <t>متوسط الرطوبة النسبية عند ارتفاع 2 متر لشهر مارس عبر فترة الرصد.</t>
         </is>
       </c>
       <c r="F167" s="16" t="inlineStr">
@@ -7530,7 +7530,7 @@
       </c>
       <c r="G167" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط الرطوبة النسبية لشهر أكتوبر (%)</t>
+          <t>خريطة متوسط الرطوبة النسبية لشهر مارس (%)</t>
         </is>
       </c>
     </row>
@@ -7540,12 +7540,12 @@
       </c>
       <c r="B168" s="10" t="inlineStr">
         <is>
-          <t>RH_NovMean</t>
+          <t>RH_AprMean</t>
         </is>
       </c>
       <c r="C168" s="29" t="inlineStr">
         <is>
-          <t>RH_November_Mean</t>
+          <t>RH_April_Mean</t>
         </is>
       </c>
       <c r="D168" s="18" t="inlineStr">
@@ -7555,7 +7555,7 @@
       </c>
       <c r="E168" s="12" t="inlineStr">
         <is>
-          <t>متوسط الرطوبة النسبية عند ارتفاع 2 متر لشهر نوفمبر عبر فترة الرصد.</t>
+          <t>متوسط الرطوبة النسبية عند ارتفاع 2 متر لشهر أبريل عبر فترة الرصد.</t>
         </is>
       </c>
       <c r="F168" s="19" t="inlineStr">
@@ -7565,7 +7565,7 @@
       </c>
       <c r="G168" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط الرطوبة النسبية لشهر نوفمبر (%)</t>
+          <t>خريطة متوسط الرطوبة النسبية لشهر أبريل (%)</t>
         </is>
       </c>
     </row>
@@ -7575,12 +7575,12 @@
       </c>
       <c r="B169" s="5" t="inlineStr">
         <is>
-          <t>RH_DecMean</t>
+          <t>RH_MayMean</t>
         </is>
       </c>
       <c r="C169" s="31" t="inlineStr">
         <is>
-          <t>RH_December_Mean</t>
+          <t>RH_May_Mean</t>
         </is>
       </c>
       <c r="D169" s="15" t="inlineStr">
@@ -7590,7 +7590,7 @@
       </c>
       <c r="E169" s="7" t="inlineStr">
         <is>
-          <t>متوسط الرطوبة النسبية عند ارتفاع 2 متر لشهر ديسمبر عبر فترة الرصد.</t>
+          <t>متوسط الرطوبة النسبية عند ارتفاع 2 متر لشهر مايو عبر فترة الرصد.</t>
         </is>
       </c>
       <c r="F169" s="16" t="inlineStr">
@@ -7600,7 +7600,7 @@
       </c>
       <c r="G169" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط الرطوبة النسبية لشهر ديسمبر (%)</t>
+          <t>خريطة متوسط الرطوبة النسبية لشهر مايو (%)</t>
         </is>
       </c>
     </row>
@@ -7610,32 +7610,32 @@
       </c>
       <c r="B170" s="10" t="inlineStr">
         <is>
-          <t>Sol_AnMean</t>
+          <t>RH_JunMean</t>
         </is>
       </c>
       <c r="C170" s="29" t="inlineStr">
         <is>
-          <t>Sol_Annual_Mean</t>
+          <t>RH_June_Mean</t>
         </is>
       </c>
       <c r="D170" s="18" t="inlineStr">
         <is>
-          <t>08_Solar_Radiation (الإشعاع الشمسي)</t>
+          <t>06_Relative_Humidity (الرطوبة النسبية)</t>
         </is>
       </c>
       <c r="E170" s="12" t="inlineStr">
         <is>
-          <t>المتوسط اليومي السنوي للإشعاع الشمسي الكلي السطحي الواصل لسطح الأرض في كافة ظروف السماء.</t>
+          <t>متوسط الرطوبة النسبية عند ارتفاع 2 متر لشهر يونيو عبر فترة الرصد.</t>
         </is>
       </c>
       <c r="F170" s="19" t="inlineStr">
         <is>
-          <t>kWh/m²/day</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G170" s="30" t="inlineStr">
         <is>
-          <t>خريطة المتوسط اليومي السنوي للإشعاع الشمسي (kWh/m²/day)</t>
+          <t>خريطة متوسط الرطوبة النسبية لشهر يونيو (%)</t>
         </is>
       </c>
     </row>
@@ -7645,32 +7645,32 @@
       </c>
       <c r="B171" s="5" t="inlineStr">
         <is>
-          <t>Sol_AnTot</t>
+          <t>RH_JulMean</t>
         </is>
       </c>
       <c r="C171" s="31" t="inlineStr">
         <is>
-          <t>Sol_Annual_Total</t>
+          <t>RH_July_Mean</t>
         </is>
       </c>
       <c r="D171" s="15" t="inlineStr">
         <is>
-          <t>08_Solar_Radiation (الإشعاع الشمسي)</t>
+          <t>06_Relative_Humidity (الرطوبة النسبية)</t>
         </is>
       </c>
       <c r="E171" s="7" t="inlineStr">
         <is>
-          <t>إجمالي الطاقة الشمسية السنوية التراكمية الساقطة على المتر المربع في السنة كاملة.</t>
+          <t>متوسط الرطوبة النسبية عند ارتفاع 2 متر لشهر يوليو عبر فترة الرصد.</t>
         </is>
       </c>
       <c r="F171" s="16" t="inlineStr">
         <is>
-          <t>kWh/m²/year</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G171" s="32" t="inlineStr">
         <is>
-          <t>خريطة إجمالي الطاقة الشمسية السنوية التراكمية (kWh/m²/year)</t>
+          <t>خريطة متوسط الرطوبة النسبية لشهر يوليو (%)</t>
         </is>
       </c>
     </row>
@@ -7680,32 +7680,32 @@
       </c>
       <c r="B172" s="10" t="inlineStr">
         <is>
-          <t>Sol_WnMean</t>
+          <t>RH_AugMean</t>
         </is>
       </c>
       <c r="C172" s="29" t="inlineStr">
         <is>
-          <t>Sol_Winter_Mean</t>
+          <t>RH_August_Mean</t>
         </is>
       </c>
       <c r="D172" s="18" t="inlineStr">
         <is>
-          <t>08_Solar_Radiation (الإشعاع الشمسي)</t>
+          <t>06_Relative_Humidity (الرطوبة النسبية)</t>
         </is>
       </c>
       <c r="E172" s="12" t="inlineStr">
         <is>
-          <t>متوسط الإشعاع الشمسي اليومي لفصل الشتاء الأرصادي (DJF).</t>
+          <t>متوسط الرطوبة النسبية عند ارتفاع 2 متر لشهر أغسطس عبر فترة الرصد.</t>
         </is>
       </c>
       <c r="F172" s="19" t="inlineStr">
         <is>
-          <t>kWh/m²/day</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G172" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط الإشعاع الشمسي خلال فصل الشتاء (kWh/m²/day)</t>
+          <t>خريطة متوسط الرطوبة النسبية لشهر أغسطس (%)</t>
         </is>
       </c>
     </row>
@@ -7715,32 +7715,32 @@
       </c>
       <c r="B173" s="5" t="inlineStr">
         <is>
-          <t>Sol_SpMean</t>
+          <t>RH_SepMean</t>
         </is>
       </c>
       <c r="C173" s="31" t="inlineStr">
         <is>
-          <t>Sol_Spring_Mean</t>
+          <t>RH_September_Mean</t>
         </is>
       </c>
       <c r="D173" s="15" t="inlineStr">
         <is>
-          <t>08_Solar_Radiation (الإشعاع الشمسي)</t>
+          <t>06_Relative_Humidity (الرطوبة النسبية)</t>
         </is>
       </c>
       <c r="E173" s="7" t="inlineStr">
         <is>
-          <t>متوسط الإشعاع الشمسي اليومي لفصل الربيع الأرصادي (MAM).</t>
+          <t>متوسط الرطوبة النسبية عند ارتفاع 2 متر لشهر سبتمبر عبر فترة الرصد.</t>
         </is>
       </c>
       <c r="F173" s="16" t="inlineStr">
         <is>
-          <t>kWh/m²/day</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G173" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط الإشعاع الشمسي خلال فصل الربيع (kWh/m²/day)</t>
+          <t>خريطة متوسط الرطوبة النسبية لشهر سبتمبر (%)</t>
         </is>
       </c>
     </row>
@@ -7750,32 +7750,32 @@
       </c>
       <c r="B174" s="10" t="inlineStr">
         <is>
-          <t>Sol_SuMean</t>
+          <t>RH_OctMean</t>
         </is>
       </c>
       <c r="C174" s="29" t="inlineStr">
         <is>
-          <t>Sol_Summer_Mean</t>
+          <t>RH_October_Mean</t>
         </is>
       </c>
       <c r="D174" s="18" t="inlineStr">
         <is>
-          <t>08_Solar_Radiation (الإشعاع الشمسي)</t>
+          <t>06_Relative_Humidity (الرطوبة النسبية)</t>
         </is>
       </c>
       <c r="E174" s="12" t="inlineStr">
         <is>
-          <t>متوسط الإشعاع الشمسي اليومي لفصل الصيف الأرصادي (JJA).</t>
+          <t>متوسط الرطوبة النسبية عند ارتفاع 2 متر لشهر أكتوبر عبر فترة الرصد.</t>
         </is>
       </c>
       <c r="F174" s="19" t="inlineStr">
         <is>
-          <t>kWh/m²/day</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G174" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط الإشعاع الشمسي خلال فصل الصيف (kWh/m²/day)</t>
+          <t>خريطة متوسط الرطوبة النسبية لشهر أكتوبر (%)</t>
         </is>
       </c>
     </row>
@@ -7785,32 +7785,32 @@
       </c>
       <c r="B175" s="5" t="inlineStr">
         <is>
-          <t>Sol_AuMean</t>
+          <t>RH_NovMean</t>
         </is>
       </c>
       <c r="C175" s="31" t="inlineStr">
         <is>
-          <t>Sol_Autumn_Mean</t>
+          <t>RH_November_Mean</t>
         </is>
       </c>
       <c r="D175" s="15" t="inlineStr">
         <is>
-          <t>08_Solar_Radiation (الإشعاع الشمسي)</t>
+          <t>06_Relative_Humidity (الرطوبة النسبية)</t>
         </is>
       </c>
       <c r="E175" s="7" t="inlineStr">
         <is>
-          <t>متوسط الإشعاع الشمسي اليومي لفصل الخريف الأرصادي (SON).</t>
+          <t>متوسط الرطوبة النسبية عند ارتفاع 2 متر لشهر نوفمبر عبر فترة الرصد.</t>
         </is>
       </c>
       <c r="F175" s="16" t="inlineStr">
         <is>
-          <t>kWh/m²/day</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G175" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط الإشعاع الشمسي خلال فصل الخريف (kWh/m²/day)</t>
+          <t>خريطة متوسط الرطوبة النسبية لشهر نوفمبر (%)</t>
         </is>
       </c>
     </row>
@@ -7820,32 +7820,32 @@
       </c>
       <c r="B176" s="10" t="inlineStr">
         <is>
-          <t>Sol_AnRng</t>
+          <t>RH_DecMean</t>
         </is>
       </c>
       <c r="C176" s="29" t="inlineStr">
         <is>
-          <t>Sol_Annual_Range</t>
+          <t>RH_December_Mean</t>
         </is>
       </c>
       <c r="D176" s="18" t="inlineStr">
         <is>
-          <t>08_Solar_Radiation (الإشعاع الشمسي)</t>
+          <t>06_Relative_Humidity (الرطوبة النسبية)</t>
         </is>
       </c>
       <c r="E176" s="12" t="inlineStr">
         <is>
-          <t>المدى السنوي للإشعاع الشمسي (الفارق بين ذروة الإشعاع في الصيف وأدناه في الشتاء).</t>
+          <t>متوسط الرطوبة النسبية عند ارتفاع 2 متر لشهر ديسمبر عبر فترة الرصد.</t>
         </is>
       </c>
       <c r="F176" s="19" t="inlineStr">
         <is>
-          <t>kWh/m²/day</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G176" s="30" t="inlineStr">
         <is>
-          <t>خريطة المدى السنوي للإشعاع الشمسي (kWh/m²/day)</t>
+          <t>خريطة متوسط الرطوبة النسبية لشهر ديسمبر (%)</t>
         </is>
       </c>
     </row>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="B177" s="5" t="inlineStr">
         <is>
-          <t>Sol_JanMn</t>
+          <t>Sol_AnMean</t>
         </is>
       </c>
       <c r="C177" s="31" t="inlineStr">
         <is>
-          <t>Sol_January_Mean</t>
+          <t>Sol_Annual_Mean</t>
         </is>
       </c>
       <c r="D177" s="15" t="inlineStr">
@@ -7870,7 +7870,7 @@
       </c>
       <c r="E177" s="7" t="inlineStr">
         <is>
-          <t>المعدل اليومي للإشعاع الشمسي الكلي الساقط على السطح الأفقي لشهر يناير.</t>
+          <t>المتوسط اليومي السنوي للإشعاع الشمسي الكلي السطحي الواصل لسطح الأرض في كافة ظروف السماء.</t>
         </is>
       </c>
       <c r="F177" s="16" t="inlineStr">
@@ -7880,7 +7880,7 @@
       </c>
       <c r="G177" s="32" t="inlineStr">
         <is>
-          <t>خريطة المعدل اليومي للإشعاع الشمسي لشهر يناير (kWh/m²/day)</t>
+          <t>خريطة المتوسط اليومي السنوي للإشعاع الشمسي (kWh/m²/day)</t>
         </is>
       </c>
     </row>
@@ -7890,12 +7890,12 @@
       </c>
       <c r="B178" s="10" t="inlineStr">
         <is>
-          <t>Sol_FebMn</t>
+          <t>Sol_MonMea</t>
         </is>
       </c>
       <c r="C178" s="29" t="inlineStr">
         <is>
-          <t>Sol_February_Mean</t>
+          <t>Sol_Month_Mean</t>
         </is>
       </c>
       <c r="D178" s="18" t="inlineStr">
@@ -7905,7 +7905,7 @@
       </c>
       <c r="E178" s="12" t="inlineStr">
         <is>
-          <t>المعدل اليومي للإشعاع الشمسي الكلي الساقط على السطح الأفقي لشهر فبراير.</t>
+          <t>المتوسط الشهري للإشعاع الشمسي اليومي الساقط على السطح الأفقي (متوسط الـ 12 شهراً).</t>
         </is>
       </c>
       <c r="F178" s="19" t="inlineStr">
@@ -7915,7 +7915,7 @@
       </c>
       <c r="G178" s="30" t="inlineStr">
         <is>
-          <t>خريطة المعدل اليومي للإشعاع الشمسي لشهر فبراير (kWh/m²/day)</t>
+          <t>خريطة المتوسط الشهري للإشعاع الشمسي اليومي (kWh/m²/day)</t>
         </is>
       </c>
     </row>
@@ -7925,12 +7925,12 @@
       </c>
       <c r="B179" s="5" t="inlineStr">
         <is>
-          <t>Sol_MarMn</t>
+          <t>Sol_AnTot</t>
         </is>
       </c>
       <c r="C179" s="31" t="inlineStr">
         <is>
-          <t>Sol_March_Mean</t>
+          <t>Sol_Annual_Total</t>
         </is>
       </c>
       <c r="D179" s="15" t="inlineStr">
@@ -7940,17 +7940,17 @@
       </c>
       <c r="E179" s="7" t="inlineStr">
         <is>
-          <t>المعدل اليومي للإشعاع الشمسي الكلي الساقط على السطح الأفقي لشهر مارس.</t>
+          <t>إجمالي الطاقة الشمسية السنوية التراكمية الساقطة على المتر المربع في السنة كاملة.</t>
         </is>
       </c>
       <c r="F179" s="16" t="inlineStr">
         <is>
-          <t>kWh/m²/day</t>
+          <t>kWh/m²/year</t>
         </is>
       </c>
       <c r="G179" s="32" t="inlineStr">
         <is>
-          <t>خريطة المعدل اليومي للإشعاع الشمسي لشهر مارس (kWh/m²/day)</t>
+          <t>خريطة إجمالي الطاقة الشمسية السنوية التراكمية (kWh/m²/year)</t>
         </is>
       </c>
     </row>
@@ -7960,12 +7960,12 @@
       </c>
       <c r="B180" s="10" t="inlineStr">
         <is>
-          <t>Sol_AprMn</t>
+          <t>Sol_WnMean</t>
         </is>
       </c>
       <c r="C180" s="29" t="inlineStr">
         <is>
-          <t>Sol_April_Mean</t>
+          <t>Sol_Winter_Mean</t>
         </is>
       </c>
       <c r="D180" s="18" t="inlineStr">
@@ -7975,7 +7975,7 @@
       </c>
       <c r="E180" s="12" t="inlineStr">
         <is>
-          <t>المعدل اليومي للإشعاع الشمسي الكلي الساقط على السطح الأفقي لشهر أبريل.</t>
+          <t>متوسط الإشعاع الشمسي اليومي لفصل الشتاء الأرصادي (DJF).</t>
         </is>
       </c>
       <c r="F180" s="19" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="G180" s="30" t="inlineStr">
         <is>
-          <t>خريطة المعدل اليومي للإشعاع الشمسي لشهر أبريل (kWh/m²/day)</t>
+          <t>خريطة متوسط الإشعاع الشمسي خلال فصل الشتاء (kWh/m²/day)</t>
         </is>
       </c>
     </row>
@@ -7995,12 +7995,12 @@
       </c>
       <c r="B181" s="5" t="inlineStr">
         <is>
-          <t>Sol_MayMn</t>
+          <t>Sol_SpMean</t>
         </is>
       </c>
       <c r="C181" s="31" t="inlineStr">
         <is>
-          <t>Sol_May_Mean</t>
+          <t>Sol_Spring_Mean</t>
         </is>
       </c>
       <c r="D181" s="15" t="inlineStr">
@@ -8010,7 +8010,7 @@
       </c>
       <c r="E181" s="7" t="inlineStr">
         <is>
-          <t>المعدل اليومي للإشعاع الشمسي الكلي الساقط على السطح الأفقي لشهر مايو.</t>
+          <t>متوسط الإشعاع الشمسي اليومي لفصل الربيع الأرصادي (MAM).</t>
         </is>
       </c>
       <c r="F181" s="16" t="inlineStr">
@@ -8020,7 +8020,7 @@
       </c>
       <c r="G181" s="32" t="inlineStr">
         <is>
-          <t>خريطة المعدل اليومي للإشعاع الشمسي لشهر مايو (kWh/m²/day)</t>
+          <t>خريطة متوسط الإشعاع الشمسي خلال فصل الربيع (kWh/m²/day)</t>
         </is>
       </c>
     </row>
@@ -8030,12 +8030,12 @@
       </c>
       <c r="B182" s="10" t="inlineStr">
         <is>
-          <t>Sol_JunMn</t>
+          <t>Sol_SuMean</t>
         </is>
       </c>
       <c r="C182" s="29" t="inlineStr">
         <is>
-          <t>Sol_June_Mean</t>
+          <t>Sol_Summer_Mean</t>
         </is>
       </c>
       <c r="D182" s="18" t="inlineStr">
@@ -8045,7 +8045,7 @@
       </c>
       <c r="E182" s="12" t="inlineStr">
         <is>
-          <t>المعدل اليومي للإشعاع الشمسي الكلي الساقط على السطح الأفقي لشهر يونيو.</t>
+          <t>متوسط الإشعاع الشمسي اليومي لفصل الصيف الأرصادي (JJA).</t>
         </is>
       </c>
       <c r="F182" s="19" t="inlineStr">
@@ -8055,7 +8055,7 @@
       </c>
       <c r="G182" s="30" t="inlineStr">
         <is>
-          <t>خريطة المعدل اليومي للإشعاع الشمسي لشهر يونيو (kWh/m²/day)</t>
+          <t>خريطة متوسط الإشعاع الشمسي خلال فصل الصيف (kWh/m²/day)</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="B183" s="5" t="inlineStr">
         <is>
-          <t>Sol_JulMn</t>
+          <t>Sol_AuMean</t>
         </is>
       </c>
       <c r="C183" s="31" t="inlineStr">
         <is>
-          <t>Sol_July_Mean</t>
+          <t>Sol_Autumn_Mean</t>
         </is>
       </c>
       <c r="D183" s="15" t="inlineStr">
@@ -8080,7 +8080,7 @@
       </c>
       <c r="E183" s="7" t="inlineStr">
         <is>
-          <t>المعدل اليومي للإشعاع الشمسي الكلي الساقط على السطح الأفقي لشهر يوليو.</t>
+          <t>متوسط الإشعاع الشمسي اليومي لفصل الخريف الأرصادي (SON).</t>
         </is>
       </c>
       <c r="F183" s="16" t="inlineStr">
@@ -8090,7 +8090,7 @@
       </c>
       <c r="G183" s="32" t="inlineStr">
         <is>
-          <t>خريطة المعدل اليومي للإشعاع الشمسي لشهر يوليو (kWh/m²/day)</t>
+          <t>خريطة متوسط الإشعاع الشمسي خلال فصل الخريف (kWh/m²/day)</t>
         </is>
       </c>
     </row>
@@ -8100,12 +8100,12 @@
       </c>
       <c r="B184" s="10" t="inlineStr">
         <is>
-          <t>Sol_AugMn</t>
+          <t>Sol_AnRng</t>
         </is>
       </c>
       <c r="C184" s="29" t="inlineStr">
         <is>
-          <t>Sol_August_Mean</t>
+          <t>Sol_Annual_Range</t>
         </is>
       </c>
       <c r="D184" s="18" t="inlineStr">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="E184" s="12" t="inlineStr">
         <is>
-          <t>المعدل اليومي للإشعاع الشمسي الكلي الساقط على السطح الأفقي لشهر أغسطس.</t>
+          <t>المدى السنوي للإشعاع الشمسي (الفارق بين ذروة الإشعاع في الصيف وأدناه في الشتاء).</t>
         </is>
       </c>
       <c r="F184" s="19" t="inlineStr">
@@ -8125,7 +8125,7 @@
       </c>
       <c r="G184" s="30" t="inlineStr">
         <is>
-          <t>خريطة المعدل اليومي للإشعاع الشمسي لشهر أغسطس (kWh/m²/day)</t>
+          <t>خريطة المدى السنوي للإشعاع الشمسي (kWh/m²/day)</t>
         </is>
       </c>
     </row>
@@ -8135,12 +8135,12 @@
       </c>
       <c r="B185" s="5" t="inlineStr">
         <is>
-          <t>Sol_SepMn</t>
+          <t>Sol_JanMn</t>
         </is>
       </c>
       <c r="C185" s="31" t="inlineStr">
         <is>
-          <t>Sol_September_Mean</t>
+          <t>Sol_January_Mean</t>
         </is>
       </c>
       <c r="D185" s="15" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="E185" s="7" t="inlineStr">
         <is>
-          <t>المعدل اليومي للإشعاع الشمسي الكلي الساقط على السطح الأفقي لشهر سبتمبر.</t>
+          <t>المعدل اليومي للإشعاع الشمسي الكلي الساقط على السطح الأفقي لشهر يناير.</t>
         </is>
       </c>
       <c r="F185" s="16" t="inlineStr">
@@ -8160,7 +8160,7 @@
       </c>
       <c r="G185" s="32" t="inlineStr">
         <is>
-          <t>خريطة المعدل اليومي للإشعاع الشمسي لشهر سبتمبر (kWh/m²/day)</t>
+          <t>خريطة المعدل اليومي للإشعاع الشمسي لشهر يناير (kWh/m²/day)</t>
         </is>
       </c>
     </row>
@@ -8170,12 +8170,12 @@
       </c>
       <c r="B186" s="10" t="inlineStr">
         <is>
-          <t>Sol_OctMn</t>
+          <t>Sol_FebMn</t>
         </is>
       </c>
       <c r="C186" s="29" t="inlineStr">
         <is>
-          <t>Sol_October_Mean</t>
+          <t>Sol_February_Mean</t>
         </is>
       </c>
       <c r="D186" s="18" t="inlineStr">
@@ -8185,7 +8185,7 @@
       </c>
       <c r="E186" s="12" t="inlineStr">
         <is>
-          <t>المعدل اليومي للإشعاع الشمسي الكلي الساقط على السطح الأفقي لشهر أكتوبر.</t>
+          <t>المعدل اليومي للإشعاع الشمسي الكلي الساقط على السطح الأفقي لشهر فبراير.</t>
         </is>
       </c>
       <c r="F186" s="19" t="inlineStr">
@@ -8195,7 +8195,7 @@
       </c>
       <c r="G186" s="30" t="inlineStr">
         <is>
-          <t>خريطة المعدل اليومي للإشعاع الشمسي لشهر أكتوبر (kWh/m²/day)</t>
+          <t>خريطة المعدل اليومي للإشعاع الشمسي لشهر فبراير (kWh/m²/day)</t>
         </is>
       </c>
     </row>
@@ -8205,12 +8205,12 @@
       </c>
       <c r="B187" s="5" t="inlineStr">
         <is>
-          <t>Sol_NovMn</t>
+          <t>Sol_MarMn</t>
         </is>
       </c>
       <c r="C187" s="31" t="inlineStr">
         <is>
-          <t>Sol_November_Mean</t>
+          <t>Sol_March_Mean</t>
         </is>
       </c>
       <c r="D187" s="15" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="E187" s="7" t="inlineStr">
         <is>
-          <t>المعدل اليومي للإشعاع الشمسي الكلي الساقط على السطح الأفقي لشهر نوفمبر.</t>
+          <t>المعدل اليومي للإشعاع الشمسي الكلي الساقط على السطح الأفقي لشهر مارس.</t>
         </is>
       </c>
       <c r="F187" s="16" t="inlineStr">
@@ -8230,7 +8230,7 @@
       </c>
       <c r="G187" s="32" t="inlineStr">
         <is>
-          <t>خريطة المعدل اليومي للإشعاع الشمسي لشهر نوفمبر (kWh/m²/day)</t>
+          <t>خريطة المعدل اليومي للإشعاع الشمسي لشهر مارس (kWh/m²/day)</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="B188" s="10" t="inlineStr">
         <is>
-          <t>Sol_DecMn</t>
+          <t>Sol_AprMn</t>
         </is>
       </c>
       <c r="C188" s="29" t="inlineStr">
         <is>
-          <t>Sol_December_Mean</t>
+          <t>Sol_April_Mean</t>
         </is>
       </c>
       <c r="D188" s="18" t="inlineStr">
@@ -8255,7 +8255,7 @@
       </c>
       <c r="E188" s="12" t="inlineStr">
         <is>
-          <t>المعدل اليومي للإشعاع الشمسي الكلي الساقط على السطح الأفقي لشهر ديسمبر.</t>
+          <t>المعدل اليومي للإشعاع الشمسي الكلي الساقط على السطح الأفقي لشهر أبريل.</t>
         </is>
       </c>
       <c r="F188" s="19" t="inlineStr">
@@ -8265,7 +8265,7 @@
       </c>
       <c r="G188" s="30" t="inlineStr">
         <is>
-          <t>خريطة المعدل اليومي للإشعاع الشمسي لشهر ديسمبر (kWh/m²/day)</t>
+          <t>خريطة المعدل اليومي للإشعاع الشمسي لشهر أبريل (kWh/m²/day)</t>
         </is>
       </c>
     </row>
@@ -8275,32 +8275,32 @@
       </c>
       <c r="B189" s="5" t="inlineStr">
         <is>
-          <t>UV_AnMean</t>
+          <t>Sol_MayMn</t>
         </is>
       </c>
       <c r="C189" s="31" t="inlineStr">
         <is>
-          <t>UV_Annual_Mean</t>
+          <t>Sol_May_Mean</t>
         </is>
       </c>
       <c r="D189" s="15" t="inlineStr">
         <is>
-          <t>09_UV_Index (الأشعة فوق البنفسجية)</t>
+          <t>08_Solar_Radiation (الإشعاع الشمسي)</t>
         </is>
       </c>
       <c r="E189" s="7" t="inlineStr">
         <is>
-          <t>المتوسط السنوي لمؤشر الأشعة فوق البنفسجية عند الظهيرة وفق منظومة منظمة الصحة العالمية.</t>
+          <t>المعدل اليومي للإشعاع الشمسي الكلي الساقط على السطح الأفقي لشهر مايو.</t>
         </is>
       </c>
       <c r="F189" s="16" t="inlineStr">
         <is>
-          <t>مؤشر (0-16+)</t>
+          <t>kWh/m²/day</t>
         </is>
       </c>
       <c r="G189" s="32" t="inlineStr">
         <is>
-          <t>خريطة المتوسط السنوي لمؤشر الأشعة فوق البنفسجية (UV)</t>
+          <t>خريطة المعدل اليومي للإشعاع الشمسي لشهر مايو (kWh/m²/day)</t>
         </is>
       </c>
     </row>
@@ -8310,32 +8310,32 @@
       </c>
       <c r="B190" s="10" t="inlineStr">
         <is>
-          <t>UV_WnMean</t>
+          <t>Sol_JunMn</t>
         </is>
       </c>
       <c r="C190" s="29" t="inlineStr">
         <is>
-          <t>UV_Winter_Mean</t>
+          <t>Sol_June_Mean</t>
         </is>
       </c>
       <c r="D190" s="18" t="inlineStr">
         <is>
-          <t>09_UV_Index (الأشعة فوق البنفسجية)</t>
+          <t>08_Solar_Radiation (الإشعاع الشمسي)</t>
         </is>
       </c>
       <c r="E190" s="12" t="inlineStr">
         <is>
-          <t>متوسط مؤشر الأشعة فوق البنفسجية لفصل الشتاء الأرصادي (DJF).</t>
+          <t>المعدل اليومي للإشعاع الشمسي الكلي الساقط على السطح الأفقي لشهر يونيو.</t>
         </is>
       </c>
       <c r="F190" s="19" t="inlineStr">
         <is>
-          <t>مؤشر (0-16+)</t>
+          <t>kWh/m²/day</t>
         </is>
       </c>
       <c r="G190" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية خلال فصل الشتاء</t>
+          <t>خريطة المعدل اليومي للإشعاع الشمسي لشهر يونيو (kWh/m²/day)</t>
         </is>
       </c>
     </row>
@@ -8345,32 +8345,32 @@
       </c>
       <c r="B191" s="5" t="inlineStr">
         <is>
-          <t>UV_SpMean</t>
+          <t>Sol_JulMn</t>
         </is>
       </c>
       <c r="C191" s="31" t="inlineStr">
         <is>
-          <t>UV_Spring_Mean</t>
+          <t>Sol_July_Mean</t>
         </is>
       </c>
       <c r="D191" s="15" t="inlineStr">
         <is>
-          <t>09_UV_Index (الأشعة فوق البنفسجية)</t>
+          <t>08_Solar_Radiation (الإشعاع الشمسي)</t>
         </is>
       </c>
       <c r="E191" s="7" t="inlineStr">
         <is>
-          <t>متوسط مؤشر الأشعة فوق البنفسجية لفصل الربيع الأرصادي (MAM).</t>
+          <t>المعدل اليومي للإشعاع الشمسي الكلي الساقط على السطح الأفقي لشهر يوليو.</t>
         </is>
       </c>
       <c r="F191" s="16" t="inlineStr">
         <is>
-          <t>مؤشر (0-16+)</t>
+          <t>kWh/m²/day</t>
         </is>
       </c>
       <c r="G191" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية خلال فصل الربيع</t>
+          <t>خريطة المعدل اليومي للإشعاع الشمسي لشهر يوليو (kWh/m²/day)</t>
         </is>
       </c>
     </row>
@@ -8380,32 +8380,32 @@
       </c>
       <c r="B192" s="10" t="inlineStr">
         <is>
-          <t>UV_SuMean</t>
+          <t>Sol_AugMn</t>
         </is>
       </c>
       <c r="C192" s="29" t="inlineStr">
         <is>
-          <t>UV_Summer_Mean</t>
+          <t>Sol_August_Mean</t>
         </is>
       </c>
       <c r="D192" s="18" t="inlineStr">
         <is>
-          <t>09_UV_Index (الأشعة فوق البنفسجية)</t>
+          <t>08_Solar_Radiation (الإشعاع الشمسي)</t>
         </is>
       </c>
       <c r="E192" s="12" t="inlineStr">
         <is>
-          <t>متوسط مؤشر الأشعة فوق البنفسجية لفصل الصيف الأرصادي (JJA - ذروة مخاطر الحروق الشمسية).</t>
+          <t>المعدل اليومي للإشعاع الشمسي الكلي الساقط على السطح الأفقي لشهر أغسطس.</t>
         </is>
       </c>
       <c r="F192" s="19" t="inlineStr">
         <is>
-          <t>مؤشر (0-16+)</t>
+          <t>kWh/m²/day</t>
         </is>
       </c>
       <c r="G192" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية خلال فصل الصيف</t>
+          <t>خريطة المعدل اليومي للإشعاع الشمسي لشهر أغسطس (kWh/m²/day)</t>
         </is>
       </c>
     </row>
@@ -8415,32 +8415,32 @@
       </c>
       <c r="B193" s="5" t="inlineStr">
         <is>
-          <t>UV_AuMean</t>
+          <t>Sol_SepMn</t>
         </is>
       </c>
       <c r="C193" s="31" t="inlineStr">
         <is>
-          <t>UV_Autumn_Mean</t>
+          <t>Sol_September_Mean</t>
         </is>
       </c>
       <c r="D193" s="15" t="inlineStr">
         <is>
-          <t>09_UV_Index (الأشعة فوق البنفسجية)</t>
+          <t>08_Solar_Radiation (الإشعاع الشمسي)</t>
         </is>
       </c>
       <c r="E193" s="7" t="inlineStr">
         <is>
-          <t>متوسط مؤشر الأشعة فوق البنفسجية لفصل الخريف الأرصادي (SON).</t>
+          <t>المعدل اليومي للإشعاع الشمسي الكلي الساقط على السطح الأفقي لشهر سبتمبر.</t>
         </is>
       </c>
       <c r="F193" s="16" t="inlineStr">
         <is>
-          <t>مؤشر (0-16+)</t>
+          <t>kWh/m²/day</t>
         </is>
       </c>
       <c r="G193" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية خلال فصل الخريف</t>
+          <t>خريطة المعدل اليومي للإشعاع الشمسي لشهر سبتمبر (kWh/m²/day)</t>
         </is>
       </c>
     </row>
@@ -8450,32 +8450,32 @@
       </c>
       <c r="B194" s="10" t="inlineStr">
         <is>
-          <t>UV_AnRng</t>
+          <t>Sol_OctMn</t>
         </is>
       </c>
       <c r="C194" s="29" t="inlineStr">
         <is>
-          <t>UV_Annual_Range</t>
+          <t>Sol_October_Mean</t>
         </is>
       </c>
       <c r="D194" s="18" t="inlineStr">
         <is>
-          <t>09_UV_Index (الأشعة فوق البنفسجية)</t>
+          <t>08_Solar_Radiation (الإشعاع الشمسي)</t>
         </is>
       </c>
       <c r="E194" s="12" t="inlineStr">
         <is>
-          <t>المدى السنوي لمؤشر الأشعة فوق البنفسجية (الفارق بين ذروة الصيف وأدنى مستويات الشتاء).</t>
+          <t>المعدل اليومي للإشعاع الشمسي الكلي الساقط على السطح الأفقي لشهر أكتوبر.</t>
         </is>
       </c>
       <c r="F194" s="19" t="inlineStr">
         <is>
-          <t>مؤشر (0-16+)</t>
+          <t>kWh/m²/day</t>
         </is>
       </c>
       <c r="G194" s="30" t="inlineStr">
         <is>
-          <t>خريطة المدى السنوي لمؤشر الأشعة فوق البنفسجية</t>
+          <t>خريطة المعدل اليومي للإشعاع الشمسي لشهر أكتوبر (kWh/m²/day)</t>
         </is>
       </c>
     </row>
@@ -8485,32 +8485,32 @@
       </c>
       <c r="B195" s="5" t="inlineStr">
         <is>
-          <t>UV_JanMean</t>
+          <t>Sol_NovMn</t>
         </is>
       </c>
       <c r="C195" s="31" t="inlineStr">
         <is>
-          <t>UV_January_Mean</t>
+          <t>Sol_November_Mean</t>
         </is>
       </c>
       <c r="D195" s="15" t="inlineStr">
         <is>
-          <t>09_UV_Index (الأشعة فوق البنفسجية)</t>
+          <t>08_Solar_Radiation (الإشعاع الشمسي)</t>
         </is>
       </c>
       <c r="E195" s="7" t="inlineStr">
         <is>
-          <t>متوسط مؤشر الأشعة فوق البنفسجية القصوى لشهر يناير وفق معيار WHO.</t>
+          <t>المعدل اليومي للإشعاع الشمسي الكلي الساقط على السطح الأفقي لشهر نوفمبر.</t>
         </is>
       </c>
       <c r="F195" s="16" t="inlineStr">
         <is>
-          <t>مؤشر (0-16+)</t>
+          <t>kWh/m²/day</t>
         </is>
       </c>
       <c r="G195" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية لشهر يناير</t>
+          <t>خريطة المعدل اليومي للإشعاع الشمسي لشهر نوفمبر (kWh/m²/day)</t>
         </is>
       </c>
     </row>
@@ -8520,32 +8520,32 @@
       </c>
       <c r="B196" s="10" t="inlineStr">
         <is>
-          <t>UV_FebMean</t>
+          <t>Sol_DecMn</t>
         </is>
       </c>
       <c r="C196" s="29" t="inlineStr">
         <is>
-          <t>UV_February_Mean</t>
+          <t>Sol_December_Mean</t>
         </is>
       </c>
       <c r="D196" s="18" t="inlineStr">
         <is>
-          <t>09_UV_Index (الأشعة فوق البنفسجية)</t>
+          <t>08_Solar_Radiation (الإشعاع الشمسي)</t>
         </is>
       </c>
       <c r="E196" s="12" t="inlineStr">
         <is>
-          <t>متوسط مؤشر الأشعة فوق البنفسجية القصوى لشهر فبراير وفق معيار WHO.</t>
+          <t>المعدل اليومي للإشعاع الشمسي الكلي الساقط على السطح الأفقي لشهر ديسمبر.</t>
         </is>
       </c>
       <c r="F196" s="19" t="inlineStr">
         <is>
-          <t>مؤشر (0-16+)</t>
+          <t>kWh/m²/day</t>
         </is>
       </c>
       <c r="G196" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية لشهر فبراير</t>
+          <t>خريطة المعدل اليومي للإشعاع الشمسي لشهر ديسمبر (kWh/m²/day)</t>
         </is>
       </c>
     </row>
@@ -8555,12 +8555,12 @@
       </c>
       <c r="B197" s="5" t="inlineStr">
         <is>
-          <t>UV_MarMean</t>
+          <t>UV_AnMean</t>
         </is>
       </c>
       <c r="C197" s="31" t="inlineStr">
         <is>
-          <t>UV_March_Mean</t>
+          <t>UV_Annual_Mean</t>
         </is>
       </c>
       <c r="D197" s="15" t="inlineStr">
@@ -8570,7 +8570,7 @@
       </c>
       <c r="E197" s="7" t="inlineStr">
         <is>
-          <t>متوسط مؤشر الأشعة فوق البنفسجية القصوى لشهر مارس وفق معيار WHO.</t>
+          <t>المتوسط السنوي لمؤشر الأشعة فوق البنفسجية عند الظهيرة وفق منظومة منظمة الصحة العالمية.</t>
         </is>
       </c>
       <c r="F197" s="16" t="inlineStr">
@@ -8580,7 +8580,7 @@
       </c>
       <c r="G197" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية لشهر مارس</t>
+          <t>خريطة المتوسط السنوي لمؤشر الأشعة فوق البنفسجية (UV)</t>
         </is>
       </c>
     </row>
@@ -8590,32 +8590,32 @@
       </c>
       <c r="B198" s="10" t="inlineStr">
         <is>
-          <t>UV_AprMean</t>
+          <t>UV_MonMean</t>
         </is>
       </c>
       <c r="C198" s="29" t="inlineStr">
         <is>
-          <t>UV_April_Mean</t>
+          <t>UV_Month_Mean</t>
         </is>
       </c>
       <c r="D198" s="18" t="inlineStr">
         <is>
-          <t>09_UV_Index (الأشعة فوق البنفسجية)</t>
+          <t>09_UV_Index (مؤشر الأشعة فوق البنفسجية)</t>
         </is>
       </c>
       <c r="E198" s="12" t="inlineStr">
         <is>
-          <t>متوسط مؤشر الأشعة فوق البنفسجية القصوى لشهر أبريل وفق معيار WHO.</t>
+          <t>المتوسط الشهري لمؤشر الأشعة فوق البنفسجية في سماء صافية (متوسط الـ 12 شهراً).</t>
         </is>
       </c>
       <c r="F198" s="19" t="inlineStr">
         <is>
-          <t>مؤشر (0-16+)</t>
+          <t>Index</t>
         </is>
       </c>
       <c r="G198" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية لشهر أبريل</t>
+          <t>خريطة المتوسط الشهري لمؤشر الأشعة فوق البنفسجية</t>
         </is>
       </c>
     </row>
@@ -8625,12 +8625,12 @@
       </c>
       <c r="B199" s="5" t="inlineStr">
         <is>
-          <t>UV_MayMean</t>
+          <t>UV_WnMean</t>
         </is>
       </c>
       <c r="C199" s="31" t="inlineStr">
         <is>
-          <t>UV_May_Mean</t>
+          <t>UV_Winter_Mean</t>
         </is>
       </c>
       <c r="D199" s="15" t="inlineStr">
@@ -8640,7 +8640,7 @@
       </c>
       <c r="E199" s="7" t="inlineStr">
         <is>
-          <t>متوسط مؤشر الأشعة فوق البنفسجية القصوى لشهر مايو وفق معيار WHO.</t>
+          <t>متوسط مؤشر الأشعة فوق البنفسجية لفصل الشتاء الأرصادي (DJF).</t>
         </is>
       </c>
       <c r="F199" s="16" t="inlineStr">
@@ -8650,7 +8650,7 @@
       </c>
       <c r="G199" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية لشهر مايو</t>
+          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية خلال فصل الشتاء</t>
         </is>
       </c>
     </row>
@@ -8660,12 +8660,12 @@
       </c>
       <c r="B200" s="10" t="inlineStr">
         <is>
-          <t>UV_JunMean</t>
+          <t>UV_SpMean</t>
         </is>
       </c>
       <c r="C200" s="29" t="inlineStr">
         <is>
-          <t>UV_June_Mean</t>
+          <t>UV_Spring_Mean</t>
         </is>
       </c>
       <c r="D200" s="18" t="inlineStr">
@@ -8675,7 +8675,7 @@
       </c>
       <c r="E200" s="12" t="inlineStr">
         <is>
-          <t>متوسط مؤشر الأشعة فوق البنفسجية القصوى لشهر يونيو وفق معيار WHO.</t>
+          <t>متوسط مؤشر الأشعة فوق البنفسجية لفصل الربيع الأرصادي (MAM).</t>
         </is>
       </c>
       <c r="F200" s="19" t="inlineStr">
@@ -8685,7 +8685,7 @@
       </c>
       <c r="G200" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية لشهر يونيو</t>
+          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية خلال فصل الربيع</t>
         </is>
       </c>
     </row>
@@ -8695,12 +8695,12 @@
       </c>
       <c r="B201" s="5" t="inlineStr">
         <is>
-          <t>UV_JulMean</t>
+          <t>UV_SuMean</t>
         </is>
       </c>
       <c r="C201" s="31" t="inlineStr">
         <is>
-          <t>UV_July_Mean</t>
+          <t>UV_Summer_Mean</t>
         </is>
       </c>
       <c r="D201" s="15" t="inlineStr">
@@ -8710,7 +8710,7 @@
       </c>
       <c r="E201" s="7" t="inlineStr">
         <is>
-          <t>متوسط مؤشر الأشعة فوق البنفسجية القصوى لشهر يوليو وفق معيار WHO.</t>
+          <t>متوسط مؤشر الأشعة فوق البنفسجية لفصل الصيف الأرصادي (JJA - ذروة مخاطر الحروق الشمسية).</t>
         </is>
       </c>
       <c r="F201" s="16" t="inlineStr">
@@ -8720,7 +8720,7 @@
       </c>
       <c r="G201" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية لشهر يوليو</t>
+          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية خلال فصل الصيف</t>
         </is>
       </c>
     </row>
@@ -8730,12 +8730,12 @@
       </c>
       <c r="B202" s="10" t="inlineStr">
         <is>
-          <t>UV_AugMean</t>
+          <t>UV_AuMean</t>
         </is>
       </c>
       <c r="C202" s="29" t="inlineStr">
         <is>
-          <t>UV_August_Mean</t>
+          <t>UV_Autumn_Mean</t>
         </is>
       </c>
       <c r="D202" s="18" t="inlineStr">
@@ -8745,7 +8745,7 @@
       </c>
       <c r="E202" s="12" t="inlineStr">
         <is>
-          <t>متوسط مؤشر الأشعة فوق البنفسجية القصوى لشهر أغسطس وفق معيار WHO.</t>
+          <t>متوسط مؤشر الأشعة فوق البنفسجية لفصل الخريف الأرصادي (SON).</t>
         </is>
       </c>
       <c r="F202" s="19" t="inlineStr">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="G202" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية لشهر أغسطس</t>
+          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية خلال فصل الخريف</t>
         </is>
       </c>
     </row>
@@ -8765,12 +8765,12 @@
       </c>
       <c r="B203" s="5" t="inlineStr">
         <is>
-          <t>UV_SepMean</t>
+          <t>UV_AnRng</t>
         </is>
       </c>
       <c r="C203" s="31" t="inlineStr">
         <is>
-          <t>UV_September_Mean</t>
+          <t>UV_Annual_Range</t>
         </is>
       </c>
       <c r="D203" s="15" t="inlineStr">
@@ -8780,7 +8780,7 @@
       </c>
       <c r="E203" s="7" t="inlineStr">
         <is>
-          <t>متوسط مؤشر الأشعة فوق البنفسجية القصوى لشهر سبتمبر وفق معيار WHO.</t>
+          <t>المدى السنوي لمؤشر الأشعة فوق البنفسجية (الفارق بين ذروة الصيف وأدنى مستويات الشتاء).</t>
         </is>
       </c>
       <c r="F203" s="16" t="inlineStr">
@@ -8790,7 +8790,7 @@
       </c>
       <c r="G203" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية لشهر سبتمبر</t>
+          <t>خريطة المدى السنوي لمؤشر الأشعة فوق البنفسجية</t>
         </is>
       </c>
     </row>
@@ -8800,12 +8800,12 @@
       </c>
       <c r="B204" s="10" t="inlineStr">
         <is>
-          <t>UV_OctMean</t>
+          <t>UV_JanMean</t>
         </is>
       </c>
       <c r="C204" s="29" t="inlineStr">
         <is>
-          <t>UV_October_Mean</t>
+          <t>UV_January_Mean</t>
         </is>
       </c>
       <c r="D204" s="18" t="inlineStr">
@@ -8815,7 +8815,7 @@
       </c>
       <c r="E204" s="12" t="inlineStr">
         <is>
-          <t>متوسط مؤشر الأشعة فوق البنفسجية القصوى لشهر أكتوبر وفق معيار WHO.</t>
+          <t>متوسط مؤشر الأشعة فوق البنفسجية القصوى لشهر يناير وفق معيار WHO.</t>
         </is>
       </c>
       <c r="F204" s="19" t="inlineStr">
@@ -8825,7 +8825,7 @@
       </c>
       <c r="G204" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية لشهر أكتوبر</t>
+          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية لشهر يناير</t>
         </is>
       </c>
     </row>
@@ -8835,12 +8835,12 @@
       </c>
       <c r="B205" s="5" t="inlineStr">
         <is>
-          <t>UV_NovMean</t>
+          <t>UV_FebMean</t>
         </is>
       </c>
       <c r="C205" s="31" t="inlineStr">
         <is>
-          <t>UV_November_Mean</t>
+          <t>UV_February_Mean</t>
         </is>
       </c>
       <c r="D205" s="15" t="inlineStr">
@@ -8850,7 +8850,7 @@
       </c>
       <c r="E205" s="7" t="inlineStr">
         <is>
-          <t>متوسط مؤشر الأشعة فوق البنفسجية القصوى لشهر نوفمبر وفق معيار WHO.</t>
+          <t>متوسط مؤشر الأشعة فوق البنفسجية القصوى لشهر فبراير وفق معيار WHO.</t>
         </is>
       </c>
       <c r="F205" s="16" t="inlineStr">
@@ -8860,7 +8860,7 @@
       </c>
       <c r="G205" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية لشهر نوفمبر</t>
+          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية لشهر فبراير</t>
         </is>
       </c>
     </row>
@@ -8870,12 +8870,12 @@
       </c>
       <c r="B206" s="10" t="inlineStr">
         <is>
-          <t>UV_DecMean</t>
+          <t>UV_MarMean</t>
         </is>
       </c>
       <c r="C206" s="29" t="inlineStr">
         <is>
-          <t>UV_December_Mean</t>
+          <t>UV_March_Mean</t>
         </is>
       </c>
       <c r="D206" s="18" t="inlineStr">
@@ -8885,7 +8885,7 @@
       </c>
       <c r="E206" s="12" t="inlineStr">
         <is>
-          <t>متوسط مؤشر الأشعة فوق البنفسجية القصوى لشهر ديسمبر وفق معيار WHO.</t>
+          <t>متوسط مؤشر الأشعة فوق البنفسجية القصوى لشهر مارس وفق معيار WHO.</t>
         </is>
       </c>
       <c r="F206" s="19" t="inlineStr">
@@ -8895,7 +8895,7 @@
       </c>
       <c r="G206" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية لشهر ديسمبر</t>
+          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية لشهر مارس</t>
         </is>
       </c>
     </row>
@@ -8905,32 +8905,32 @@
       </c>
       <c r="B207" s="5" t="inlineStr">
         <is>
-          <t>Cld_AnMean</t>
+          <t>UV_AprMean</t>
         </is>
       </c>
       <c r="C207" s="31" t="inlineStr">
         <is>
-          <t>Cld_Annual_Mean</t>
+          <t>UV_April_Mean</t>
         </is>
       </c>
       <c r="D207" s="15" t="inlineStr">
         <is>
-          <t>10_Cloud_Cover (الغطاء السحابي)</t>
+          <t>09_UV_Index (الأشعة فوق البنفسجية)</t>
         </is>
       </c>
       <c r="E207" s="7" t="inlineStr">
         <is>
-          <t>المتوسط السنوي لنسبة تغطية السماء بالغيوم والسحب كنسبة مئوية.</t>
+          <t>متوسط مؤشر الأشعة فوق البنفسجية القصوى لشهر أبريل وفق معيار WHO.</t>
         </is>
       </c>
       <c r="F207" s="16" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>مؤشر (0-16+)</t>
         </is>
       </c>
       <c r="G207" s="32" t="inlineStr">
         <is>
-          <t>خريطة المتوسط السنوي لنسبة الغطاء السحابي (%)</t>
+          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية لشهر أبريل</t>
         </is>
       </c>
     </row>
@@ -8940,32 +8940,32 @@
       </c>
       <c r="B208" s="10" t="inlineStr">
         <is>
-          <t>Cld_WnMean</t>
+          <t>UV_MayMean</t>
         </is>
       </c>
       <c r="C208" s="29" t="inlineStr">
         <is>
-          <t>Cld_Winter_Mean</t>
+          <t>UV_May_Mean</t>
         </is>
       </c>
       <c r="D208" s="18" t="inlineStr">
         <is>
-          <t>10_Cloud_Cover (الغطاء السحابي)</t>
+          <t>09_UV_Index (الأشعة فوق البنفسجية)</t>
         </is>
       </c>
       <c r="E208" s="12" t="inlineStr">
         <is>
-          <t>متوسط نسبة تغطية السحب لفصل الشتاء الأرصادي (DJF).</t>
+          <t>متوسط مؤشر الأشعة فوق البنفسجية القصوى لشهر مايو وفق معيار WHO.</t>
         </is>
       </c>
       <c r="F208" s="19" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>مؤشر (0-16+)</t>
         </is>
       </c>
       <c r="G208" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط الغطاء السحابي خلال فصل الشتاء (%)</t>
+          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية لشهر مايو</t>
         </is>
       </c>
     </row>
@@ -8975,32 +8975,32 @@
       </c>
       <c r="B209" s="5" t="inlineStr">
         <is>
-          <t>Cld_SpMean</t>
+          <t>UV_JunMean</t>
         </is>
       </c>
       <c r="C209" s="31" t="inlineStr">
         <is>
-          <t>Cld_Spring_Mean</t>
+          <t>UV_June_Mean</t>
         </is>
       </c>
       <c r="D209" s="15" t="inlineStr">
         <is>
-          <t>10_Cloud_Cover (الغطاء السحابي)</t>
+          <t>09_UV_Index (الأشعة فوق البنفسجية)</t>
         </is>
       </c>
       <c r="E209" s="7" t="inlineStr">
         <is>
-          <t>متوسط نسبة تغطية السحب لفصل الربيع الأرصادي (MAM).</t>
+          <t>متوسط مؤشر الأشعة فوق البنفسجية القصوى لشهر يونيو وفق معيار WHO.</t>
         </is>
       </c>
       <c r="F209" s="16" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>مؤشر (0-16+)</t>
         </is>
       </c>
       <c r="G209" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط الغطاء السحابي خلال فصل الربيع (%)</t>
+          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية لشهر يونيو</t>
         </is>
       </c>
     </row>
@@ -9010,32 +9010,32 @@
       </c>
       <c r="B210" s="10" t="inlineStr">
         <is>
-          <t>Cld_SuMean</t>
+          <t>UV_JulMean</t>
         </is>
       </c>
       <c r="C210" s="29" t="inlineStr">
         <is>
-          <t>Cld_Summer_Mean</t>
+          <t>UV_July_Mean</t>
         </is>
       </c>
       <c r="D210" s="18" t="inlineStr">
         <is>
-          <t>10_Cloud_Cover (الغطاء السحابي)</t>
+          <t>09_UV_Index (الأشعة فوق البنفسجية)</t>
         </is>
       </c>
       <c r="E210" s="12" t="inlineStr">
         <is>
-          <t>متوسط نسبة تغطية السحب لفصل الصيف الأرصادي (JJA).</t>
+          <t>متوسط مؤشر الأشعة فوق البنفسجية القصوى لشهر يوليو وفق معيار WHO.</t>
         </is>
       </c>
       <c r="F210" s="19" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>مؤشر (0-16+)</t>
         </is>
       </c>
       <c r="G210" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط الغطاء السحابي خلال فصل الصيف (%)</t>
+          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية لشهر يوليو</t>
         </is>
       </c>
     </row>
@@ -9045,32 +9045,32 @@
       </c>
       <c r="B211" s="5" t="inlineStr">
         <is>
-          <t>Cld_AuMean</t>
+          <t>UV_AugMean</t>
         </is>
       </c>
       <c r="C211" s="31" t="inlineStr">
         <is>
-          <t>Cld_Autumn_Mean</t>
+          <t>UV_August_Mean</t>
         </is>
       </c>
       <c r="D211" s="15" t="inlineStr">
         <is>
-          <t>10_Cloud_Cover (الغطاء السحابي)</t>
+          <t>09_UV_Index (الأشعة فوق البنفسجية)</t>
         </is>
       </c>
       <c r="E211" s="7" t="inlineStr">
         <is>
-          <t>متوسط نسبة تغطية السحب لفصل الخريف الأرصادي (SON).</t>
+          <t>متوسط مؤشر الأشعة فوق البنفسجية القصوى لشهر أغسطس وفق معيار WHO.</t>
         </is>
       </c>
       <c r="F211" s="16" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>مؤشر (0-16+)</t>
         </is>
       </c>
       <c r="G211" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط الغطاء السحابي خلال فصل الخريف (%)</t>
+          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية لشهر أغسطس</t>
         </is>
       </c>
     </row>
@@ -9080,32 +9080,32 @@
       </c>
       <c r="B212" s="10" t="inlineStr">
         <is>
-          <t>Cld_AnRng</t>
+          <t>UV_SepMean</t>
         </is>
       </c>
       <c r="C212" s="29" t="inlineStr">
         <is>
-          <t>Cld_Annual_Range</t>
+          <t>UV_September_Mean</t>
         </is>
       </c>
       <c r="D212" s="18" t="inlineStr">
         <is>
-          <t>10_Cloud_Cover (الغطاء السحابي)</t>
+          <t>09_UV_Index (الأشعة فوق البنفسجية)</t>
         </is>
       </c>
       <c r="E212" s="12" t="inlineStr">
         <is>
-          <t>المدى السنوي لتغطية السحب (الفارق بين أكثر شهور السنة غيوماً وأكثرها صفاءً).</t>
+          <t>متوسط مؤشر الأشعة فوق البنفسجية القصوى لشهر سبتمبر وفق معيار WHO.</t>
         </is>
       </c>
       <c r="F212" s="19" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>مؤشر (0-16+)</t>
         </is>
       </c>
       <c r="G212" s="30" t="inlineStr">
         <is>
-          <t>خريطة المدى السنوي لنسبة الغطاء السحابي (%)</t>
+          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية لشهر سبتمبر</t>
         </is>
       </c>
     </row>
@@ -9115,32 +9115,32 @@
       </c>
       <c r="B213" s="5" t="inlineStr">
         <is>
-          <t>Cld_JanMn</t>
+          <t>UV_OctMean</t>
         </is>
       </c>
       <c r="C213" s="31" t="inlineStr">
         <is>
-          <t>Cld_January_Mean</t>
+          <t>UV_October_Mean</t>
         </is>
       </c>
       <c r="D213" s="15" t="inlineStr">
         <is>
-          <t>10_Cloud_Cover (الغطاء السحابي)</t>
+          <t>09_UV_Index (الأشعة فوق البنفسجية)</t>
         </is>
       </c>
       <c r="E213" s="7" t="inlineStr">
         <is>
-          <t>متوسط نسبة الغطاء السحابي الكلي للسماء لشهر يناير.</t>
+          <t>متوسط مؤشر الأشعة فوق البنفسجية القصوى لشهر أكتوبر وفق معيار WHO.</t>
         </is>
       </c>
       <c r="F213" s="16" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>مؤشر (0-16+)</t>
         </is>
       </c>
       <c r="G213" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط الغطاء السحابي لشهر يناير (%)</t>
+          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية لشهر أكتوبر</t>
         </is>
       </c>
     </row>
@@ -9150,32 +9150,32 @@
       </c>
       <c r="B214" s="10" t="inlineStr">
         <is>
-          <t>Cld_FebMn</t>
+          <t>UV_NovMean</t>
         </is>
       </c>
       <c r="C214" s="29" t="inlineStr">
         <is>
-          <t>Cld_February_Mean</t>
+          <t>UV_November_Mean</t>
         </is>
       </c>
       <c r="D214" s="18" t="inlineStr">
         <is>
-          <t>10_Cloud_Cover (الغطاء السحابي)</t>
+          <t>09_UV_Index (الأشعة فوق البنفسجية)</t>
         </is>
       </c>
       <c r="E214" s="12" t="inlineStr">
         <is>
-          <t>متوسط نسبة الغطاء السحابي الكلي للسماء لشهر فبراير.</t>
+          <t>متوسط مؤشر الأشعة فوق البنفسجية القصوى لشهر نوفمبر وفق معيار WHO.</t>
         </is>
       </c>
       <c r="F214" s="19" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>مؤشر (0-16+)</t>
         </is>
       </c>
       <c r="G214" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط الغطاء السحابي لشهر فبراير (%)</t>
+          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية لشهر نوفمبر</t>
         </is>
       </c>
     </row>
@@ -9185,32 +9185,32 @@
       </c>
       <c r="B215" s="5" t="inlineStr">
         <is>
-          <t>Cld_MarMn</t>
+          <t>UV_DecMean</t>
         </is>
       </c>
       <c r="C215" s="31" t="inlineStr">
         <is>
-          <t>Cld_March_Mean</t>
+          <t>UV_December_Mean</t>
         </is>
       </c>
       <c r="D215" s="15" t="inlineStr">
         <is>
-          <t>10_Cloud_Cover (الغطاء السحابي)</t>
+          <t>09_UV_Index (الأشعة فوق البنفسجية)</t>
         </is>
       </c>
       <c r="E215" s="7" t="inlineStr">
         <is>
-          <t>متوسط نسبة الغطاء السحابي الكلي للسماء لشهر مارس.</t>
+          <t>متوسط مؤشر الأشعة فوق البنفسجية القصوى لشهر ديسمبر وفق معيار WHO.</t>
         </is>
       </c>
       <c r="F215" s="16" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>مؤشر (0-16+)</t>
         </is>
       </c>
       <c r="G215" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط الغطاء السحابي لشهر مارس (%)</t>
+          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية لشهر ديسمبر</t>
         </is>
       </c>
     </row>
@@ -9220,12 +9220,12 @@
       </c>
       <c r="B216" s="10" t="inlineStr">
         <is>
-          <t>Cld_AprMn</t>
+          <t>Cld_AnMean</t>
         </is>
       </c>
       <c r="C216" s="29" t="inlineStr">
         <is>
-          <t>Cld_April_Mean</t>
+          <t>Cld_Annual_Mean</t>
         </is>
       </c>
       <c r="D216" s="18" t="inlineStr">
@@ -9235,7 +9235,7 @@
       </c>
       <c r="E216" s="12" t="inlineStr">
         <is>
-          <t>متوسط نسبة الغطاء السحابي الكلي للسماء لشهر أبريل.</t>
+          <t>المتوسط السنوي لنسبة تغطية السماء بالغيوم والسحب كنسبة مئوية.</t>
         </is>
       </c>
       <c r="F216" s="19" t="inlineStr">
@@ -9245,7 +9245,7 @@
       </c>
       <c r="G216" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط الغطاء السحابي لشهر أبريل (%)</t>
+          <t>خريطة المتوسط السنوي لنسبة الغطاء السحابي (%)</t>
         </is>
       </c>
     </row>
@@ -9255,12 +9255,12 @@
       </c>
       <c r="B217" s="5" t="inlineStr">
         <is>
-          <t>Cld_MayMn</t>
+          <t>Cld_MonMea</t>
         </is>
       </c>
       <c r="C217" s="31" t="inlineStr">
         <is>
-          <t>Cld_May_Mean</t>
+          <t>Cld_Month_Mean</t>
         </is>
       </c>
       <c r="D217" s="15" t="inlineStr">
@@ -9270,7 +9270,7 @@
       </c>
       <c r="E217" s="7" t="inlineStr">
         <is>
-          <t>متوسط نسبة الغطاء السحابي الكلي للسماء لشهر مايو.</t>
+          <t>المتوسط الشهري لكمية الغطاء السحابي الكلي (متوسط الـ 12 شهراً).</t>
         </is>
       </c>
       <c r="F217" s="16" t="inlineStr">
@@ -9280,7 +9280,7 @@
       </c>
       <c r="G217" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط الغطاء السحابي لشهر مايو (%)</t>
+          <t>خريطة المتوسط الشهري للغطاء السحابي (%)</t>
         </is>
       </c>
     </row>
@@ -9290,12 +9290,12 @@
       </c>
       <c r="B218" s="10" t="inlineStr">
         <is>
-          <t>Cld_JunMn</t>
+          <t>Cld_WnMean</t>
         </is>
       </c>
       <c r="C218" s="29" t="inlineStr">
         <is>
-          <t>Cld_June_Mean</t>
+          <t>Cld_Winter_Mean</t>
         </is>
       </c>
       <c r="D218" s="18" t="inlineStr">
@@ -9305,7 +9305,7 @@
       </c>
       <c r="E218" s="12" t="inlineStr">
         <is>
-          <t>متوسط نسبة الغطاء السحابي الكلي للسماء لشهر يونيو.</t>
+          <t>متوسط نسبة تغطية السحب لفصل الشتاء الأرصادي (DJF).</t>
         </is>
       </c>
       <c r="F218" s="19" t="inlineStr">
@@ -9315,7 +9315,7 @@
       </c>
       <c r="G218" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط الغطاء السحابي لشهر يونيو (%)</t>
+          <t>خريطة متوسط الغطاء السحابي خلال فصل الشتاء (%)</t>
         </is>
       </c>
     </row>
@@ -9325,12 +9325,12 @@
       </c>
       <c r="B219" s="5" t="inlineStr">
         <is>
-          <t>Cld_JulMn</t>
+          <t>Cld_SpMean</t>
         </is>
       </c>
       <c r="C219" s="31" t="inlineStr">
         <is>
-          <t>Cld_July_Mean</t>
+          <t>Cld_Spring_Mean</t>
         </is>
       </c>
       <c r="D219" s="15" t="inlineStr">
@@ -9340,7 +9340,7 @@
       </c>
       <c r="E219" s="7" t="inlineStr">
         <is>
-          <t>متوسط نسبة الغطاء السحابي الكلي للسماء لشهر يوليو.</t>
+          <t>متوسط نسبة تغطية السحب لفصل الربيع الأرصادي (MAM).</t>
         </is>
       </c>
       <c r="F219" s="16" t="inlineStr">
@@ -9350,7 +9350,7 @@
       </c>
       <c r="G219" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط الغطاء السحابي لشهر يوليو (%)</t>
+          <t>خريطة متوسط الغطاء السحابي خلال فصل الربيع (%)</t>
         </is>
       </c>
     </row>
@@ -9360,12 +9360,12 @@
       </c>
       <c r="B220" s="10" t="inlineStr">
         <is>
-          <t>Cld_AugMn</t>
+          <t>Cld_SuMean</t>
         </is>
       </c>
       <c r="C220" s="29" t="inlineStr">
         <is>
-          <t>Cld_August_Mean</t>
+          <t>Cld_Summer_Mean</t>
         </is>
       </c>
       <c r="D220" s="18" t="inlineStr">
@@ -9375,7 +9375,7 @@
       </c>
       <c r="E220" s="12" t="inlineStr">
         <is>
-          <t>متوسط نسبة الغطاء السحابي الكلي للسماء لشهر أغسطس.</t>
+          <t>متوسط نسبة تغطية السحب لفصل الصيف الأرصادي (JJA).</t>
         </is>
       </c>
       <c r="F220" s="19" t="inlineStr">
@@ -9385,7 +9385,7 @@
       </c>
       <c r="G220" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط الغطاء السحابي لشهر أغسطس (%)</t>
+          <t>خريطة متوسط الغطاء السحابي خلال فصل الصيف (%)</t>
         </is>
       </c>
     </row>
@@ -9395,12 +9395,12 @@
       </c>
       <c r="B221" s="5" t="inlineStr">
         <is>
-          <t>Cld_SepMn</t>
+          <t>Cld_AuMean</t>
         </is>
       </c>
       <c r="C221" s="31" t="inlineStr">
         <is>
-          <t>Cld_September_Mean</t>
+          <t>Cld_Autumn_Mean</t>
         </is>
       </c>
       <c r="D221" s="15" t="inlineStr">
@@ -9410,7 +9410,7 @@
       </c>
       <c r="E221" s="7" t="inlineStr">
         <is>
-          <t>متوسط نسبة الغطاء السحابي الكلي للسماء لشهر سبتمبر.</t>
+          <t>متوسط نسبة تغطية السحب لفصل الخريف الأرصادي (SON).</t>
         </is>
       </c>
       <c r="F221" s="16" t="inlineStr">
@@ -9420,7 +9420,7 @@
       </c>
       <c r="G221" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط الغطاء السحابي لشهر سبتمبر (%)</t>
+          <t>خريطة متوسط الغطاء السحابي خلال فصل الخريف (%)</t>
         </is>
       </c>
     </row>
@@ -9430,12 +9430,12 @@
       </c>
       <c r="B222" s="10" t="inlineStr">
         <is>
-          <t>Cld_OctMn</t>
+          <t>Cld_AnRng</t>
         </is>
       </c>
       <c r="C222" s="29" t="inlineStr">
         <is>
-          <t>Cld_October_Mean</t>
+          <t>Cld_Annual_Range</t>
         </is>
       </c>
       <c r="D222" s="18" t="inlineStr">
@@ -9445,7 +9445,7 @@
       </c>
       <c r="E222" s="12" t="inlineStr">
         <is>
-          <t>متوسط نسبة الغطاء السحابي الكلي للسماء لشهر أكتوبر.</t>
+          <t>المدى السنوي لتغطية السحب (الفارق بين أكثر شهور السنة غيوماً وأكثرها صفاءً).</t>
         </is>
       </c>
       <c r="F222" s="19" t="inlineStr">
@@ -9455,7 +9455,7 @@
       </c>
       <c r="G222" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط الغطاء السحابي لشهر أكتوبر (%)</t>
+          <t>خريطة المدى السنوي لنسبة الغطاء السحابي (%)</t>
         </is>
       </c>
     </row>
@@ -9465,12 +9465,12 @@
       </c>
       <c r="B223" s="5" t="inlineStr">
         <is>
-          <t>Cld_NovMn</t>
+          <t>Cld_JanMn</t>
         </is>
       </c>
       <c r="C223" s="31" t="inlineStr">
         <is>
-          <t>Cld_November_Mean</t>
+          <t>Cld_January_Mean</t>
         </is>
       </c>
       <c r="D223" s="15" t="inlineStr">
@@ -9480,7 +9480,7 @@
       </c>
       <c r="E223" s="7" t="inlineStr">
         <is>
-          <t>متوسط نسبة الغطاء السحابي الكلي للسماء لشهر نوفمبر.</t>
+          <t>متوسط نسبة الغطاء السحابي الكلي للسماء لشهر يناير.</t>
         </is>
       </c>
       <c r="F223" s="16" t="inlineStr">
@@ -9490,7 +9490,7 @@
       </c>
       <c r="G223" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط الغطاء السحابي لشهر نوفمبر (%)</t>
+          <t>خريطة متوسط الغطاء السحابي لشهر يناير (%)</t>
         </is>
       </c>
     </row>
@@ -9500,12 +9500,12 @@
       </c>
       <c r="B224" s="10" t="inlineStr">
         <is>
-          <t>Cld_DecMn</t>
+          <t>Cld_FebMn</t>
         </is>
       </c>
       <c r="C224" s="29" t="inlineStr">
         <is>
-          <t>Cld_December_Mean</t>
+          <t>Cld_February_Mean</t>
         </is>
       </c>
       <c r="D224" s="18" t="inlineStr">
@@ -9515,7 +9515,7 @@
       </c>
       <c r="E224" s="12" t="inlineStr">
         <is>
-          <t>متوسط نسبة الغطاء السحابي الكلي للسماء لشهر ديسمبر.</t>
+          <t>متوسط نسبة الغطاء السحابي الكلي للسماء لشهر فبراير.</t>
         </is>
       </c>
       <c r="F224" s="19" t="inlineStr">
@@ -9525,7 +9525,7 @@
       </c>
       <c r="G224" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط الغطاء السحابي لشهر ديسمبر (%)</t>
+          <t>خريطة متوسط الغطاء السحابي لشهر فبراير (%)</t>
         </is>
       </c>
     </row>
@@ -9535,32 +9535,32 @@
       </c>
       <c r="B225" s="5" t="inlineStr">
         <is>
-          <t>WC_WinMean</t>
+          <t>Cld_MarMn</t>
         </is>
       </c>
       <c r="C225" s="31" t="inlineStr">
         <is>
-          <t>WC_Winter_Mean</t>
+          <t>Cld_March_Mean</t>
         </is>
       </c>
       <c r="D225" s="15" t="inlineStr">
         <is>
-          <t>12_Wind_Chill (مبرد الرياح)</t>
+          <t>10_Cloud_Cover (الغطاء السحابي)</t>
         </is>
       </c>
       <c r="E225" s="7" t="inlineStr">
         <is>
-          <t>متوسط درجة البرودة الريحية لفصل الشتاء المحسوبة بمعادلة NWS لخفض الحرارة بفعل سرعة الرياح.</t>
+          <t>متوسط نسبة الغطاء السحابي الكلي للسماء لشهر مارس.</t>
         </is>
       </c>
       <c r="F225" s="16" t="inlineStr">
         <is>
-          <t>°C</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G225" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط مبرد الرياح خلال فصل الشتاء (°C)</t>
+          <t>خريطة متوسط الغطاء السحابي لشهر مارس (%)</t>
         </is>
       </c>
     </row>
@@ -9570,32 +9570,32 @@
       </c>
       <c r="B226" s="10" t="inlineStr">
         <is>
-          <t>WC_AnnMean</t>
+          <t>Cld_AprMn</t>
         </is>
       </c>
       <c r="C226" s="29" t="inlineStr">
         <is>
-          <t>WC_Annual_Mean</t>
+          <t>Cld_April_Mean</t>
         </is>
       </c>
       <c r="D226" s="18" t="inlineStr">
         <is>
-          <t>12_Wind_Chill (مبرد الرياح)</t>
+          <t>10_Cloud_Cover (الغطاء السحابي)</t>
         </is>
       </c>
       <c r="E226" s="12" t="inlineStr">
         <is>
-          <t>المتوسط الحسابي السنوي لتأثير البرودة الريحية على حرارة الهواء المحسوسة.</t>
+          <t>متوسط نسبة الغطاء السحابي الكلي للسماء لشهر أبريل.</t>
         </is>
       </c>
       <c r="F226" s="19" t="inlineStr">
         <is>
-          <t>°C</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G226" s="30" t="inlineStr">
         <is>
-          <t>خريطة المتوسط السنوي لمبرد الرياح (°C)</t>
+          <t>خريطة متوسط الغطاء السحابي لشهر أبريل (%)</t>
         </is>
       </c>
     </row>
@@ -9605,32 +9605,32 @@
       </c>
       <c r="B227" s="5" t="inlineStr">
         <is>
-          <t>DM_AridAnn</t>
+          <t>Cld_MayMn</t>
         </is>
       </c>
       <c r="C227" s="31" t="inlineStr">
         <is>
-          <t>DM_Aridity_Annual</t>
+          <t>Cld_May_Mean</t>
         </is>
       </c>
       <c r="D227" s="15" t="inlineStr">
         <is>
-          <t>13_De_Martonne_Aridity (دليل دي مارتون)</t>
+          <t>10_Cloud_Cover (الغطاء السحابي)</t>
         </is>
       </c>
       <c r="E227" s="7" t="inlineStr">
         <is>
-          <t>دليل القحولة والجفاف السنوي لدي مارتون I = P / (T + 10) لتصنيف الأقاليم من القاحل فائق الجفاف إلى الرطب.</t>
+          <t>متوسط نسبة الغطاء السحابي الكلي للسماء لشهر مايو.</t>
         </is>
       </c>
       <c r="F227" s="16" t="inlineStr">
         <is>
-          <t>مؤشر (Index)</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G227" s="32" t="inlineStr">
         <is>
-          <t>خريطة دليل دي مارتون السنوي للقحولة والجفاف</t>
+          <t>خريطة متوسط الغطاء السحابي لشهر مايو (%)</t>
         </is>
       </c>
     </row>
@@ -9640,32 +9640,32 @@
       </c>
       <c r="B228" s="10" t="inlineStr">
         <is>
-          <t>ET_AnnTot</t>
+          <t>Cld_JunMn</t>
         </is>
       </c>
       <c r="C228" s="29" t="inlineStr">
         <is>
-          <t>ET_Annual_Total</t>
+          <t>Cld_June_Mean</t>
         </is>
       </c>
       <c r="D228" s="18" t="inlineStr">
         <is>
-          <t>14_Evapotranspiration (البخر والنتح)</t>
+          <t>10_Cloud_Cover (الغطاء السحابي)</t>
         </is>
       </c>
       <c r="E228" s="12" t="inlineStr">
         <is>
-          <t>المجموع التراكمي السنوي للبخر والنتح المرجعي الكامن المحسوب بمعادلة Hargreaves-Samani (FAO-56).</t>
+          <t>متوسط نسبة الغطاء السحابي الكلي للسماء لشهر يونيو.</t>
         </is>
       </c>
       <c r="F228" s="19" t="inlineStr">
         <is>
-          <t>ملم (mm)</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G228" s="30" t="inlineStr">
         <is>
-          <t>خريطة المجموع السنوي للبخر والنتح (ملم)</t>
+          <t>خريطة متوسط الغطاء السحابي لشهر يونيو (%)</t>
         </is>
       </c>
     </row>
@@ -9675,32 +9675,32 @@
       </c>
       <c r="B229" s="5" t="inlineStr">
         <is>
-          <t>ET_AnnMean</t>
+          <t>Cld_JulMn</t>
         </is>
       </c>
       <c r="C229" s="31" t="inlineStr">
         <is>
-          <t>ET_Annual_Mean</t>
+          <t>Cld_July_Mean</t>
         </is>
       </c>
       <c r="D229" s="15" t="inlineStr">
         <is>
-          <t>14_Evapotranspiration (البخر والنتح)</t>
+          <t>10_Cloud_Cover (الغطاء السحابي)</t>
         </is>
       </c>
       <c r="E229" s="7" t="inlineStr">
         <is>
-          <t>المعدل الشهري للبخر والنتح المرجعي (المجموع التراكمي السنوي مقسوماً على 12 شهراً).</t>
+          <t>متوسط نسبة الغطاء السحابي الكلي للسماء لشهر يوليو.</t>
         </is>
       </c>
       <c r="F229" s="16" t="inlineStr">
         <is>
-          <t>ملم (mm)</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G229" s="32" t="inlineStr">
         <is>
-          <t>خريطة المعدل الشهري للبخر والنتح (ملم)</t>
+          <t>خريطة متوسط الغطاء السحابي لشهر يوليو (%)</t>
         </is>
       </c>
     </row>
@@ -9710,32 +9710,32 @@
       </c>
       <c r="B230" s="10" t="inlineStr">
         <is>
-          <t>ET_AnnRng</t>
+          <t>Cld_AugMn</t>
         </is>
       </c>
       <c r="C230" s="29" t="inlineStr">
         <is>
-          <t>ET_Annual_Range</t>
+          <t>Cld_August_Mean</t>
         </is>
       </c>
       <c r="D230" s="18" t="inlineStr">
         <is>
-          <t>14_Evapotranspiration (البخر والنتح)</t>
+          <t>10_Cloud_Cover (الغطاء السحابي)</t>
         </is>
       </c>
       <c r="E230" s="12" t="inlineStr">
         <is>
-          <t>المدى السنوي للبخر والنتح (الفارق بين أعلى شهور السنة فقداً للماء بالبخر والنتح وأدناها).</t>
+          <t>متوسط نسبة الغطاء السحابي الكلي للسماء لشهر أغسطس.</t>
         </is>
       </c>
       <c r="F230" s="19" t="inlineStr">
         <is>
-          <t>ملم (mm)</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G230" s="30" t="inlineStr">
         <is>
-          <t>خريطة المدى السنوي للبخر والنتح (ملم)</t>
+          <t>خريطة متوسط الغطاء السحابي لشهر أغسطس (%)</t>
         </is>
       </c>
     </row>
@@ -9745,32 +9745,32 @@
       </c>
       <c r="B231" s="5" t="inlineStr">
         <is>
-          <t>ET_SeaRng</t>
+          <t>Cld_SepMn</t>
         </is>
       </c>
       <c r="C231" s="31" t="inlineStr">
         <is>
-          <t>ET_Seasonal_Range</t>
+          <t>Cld_September_Mean</t>
         </is>
       </c>
       <c r="D231" s="15" t="inlineStr">
         <is>
-          <t>14_Evapotranspiration (البخر والنتح)</t>
+          <t>10_Cloud_Cover (الغطاء السحابي)</t>
         </is>
       </c>
       <c r="E231" s="7" t="inlineStr">
         <is>
-          <t>المدى الفصلي للبخر والنتح (الفارق بين مجموع أعلى فصول السنة في البخر والنتح ومجموع أقلها).</t>
+          <t>متوسط نسبة الغطاء السحابي الكلي للسماء لشهر سبتمبر.</t>
         </is>
       </c>
       <c r="F231" s="16" t="inlineStr">
         <is>
-          <t>ملم (mm)</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G231" s="32" t="inlineStr">
         <is>
-          <t>خريطة المدى الفصلي للبخر والنتح (ملم)</t>
+          <t>خريطة متوسط الغطاء السحابي لشهر سبتمبر (%)</t>
         </is>
       </c>
     </row>
@@ -9780,32 +9780,32 @@
       </c>
       <c r="B232" s="10" t="inlineStr">
         <is>
-          <t>ET_WinTot</t>
+          <t>Cld_OctMn</t>
         </is>
       </c>
       <c r="C232" s="29" t="inlineStr">
         <is>
-          <t>ET_Winter_Total</t>
+          <t>Cld_October_Mean</t>
         </is>
       </c>
       <c r="D232" s="18" t="inlineStr">
         <is>
-          <t>14_Evapotranspiration (البخر والنتح)</t>
+          <t>10_Cloud_Cover (الغطاء السحابي)</t>
         </is>
       </c>
       <c r="E232" s="12" t="inlineStr">
         <is>
-          <t>مجموع البخر والنتح لفصل الشتاء الأرصادي (شهور ديسمبر، يناير، فبراير - DJF).</t>
+          <t>متوسط نسبة الغطاء السحابي الكلي للسماء لشهر أكتوبر.</t>
         </is>
       </c>
       <c r="F232" s="19" t="inlineStr">
         <is>
-          <t>ملم (mm)</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G232" s="30" t="inlineStr">
         <is>
-          <t>خريطة مجموع البخر والنتح خلال فصل الشتاء (ملم)</t>
+          <t>خريطة متوسط الغطاء السحابي لشهر أكتوبر (%)</t>
         </is>
       </c>
     </row>
@@ -9815,32 +9815,32 @@
       </c>
       <c r="B233" s="5" t="inlineStr">
         <is>
-          <t>ET_SprTot</t>
+          <t>Cld_NovMn</t>
         </is>
       </c>
       <c r="C233" s="31" t="inlineStr">
         <is>
-          <t>ET_Spring_Total</t>
+          <t>Cld_November_Mean</t>
         </is>
       </c>
       <c r="D233" s="15" t="inlineStr">
         <is>
-          <t>14_Evapotranspiration (البخر والنتح)</t>
+          <t>10_Cloud_Cover (الغطاء السحابي)</t>
         </is>
       </c>
       <c r="E233" s="7" t="inlineStr">
         <is>
-          <t>مجموع البخر والنتح لفصل الربيع الأرصادي (شهور مارس، أبريل، مايو - MAM).</t>
+          <t>متوسط نسبة الغطاء السحابي الكلي للسماء لشهر نوفمبر.</t>
         </is>
       </c>
       <c r="F233" s="16" t="inlineStr">
         <is>
-          <t>ملم (mm)</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G233" s="32" t="inlineStr">
         <is>
-          <t>خريطة مجموع البخر والنتح خلال فصل الربيع (ملم)</t>
+          <t>خريطة متوسط الغطاء السحابي لشهر نوفمبر (%)</t>
         </is>
       </c>
     </row>
@@ -9850,32 +9850,32 @@
       </c>
       <c r="B234" s="10" t="inlineStr">
         <is>
-          <t>ET_SumTot</t>
+          <t>Cld_DecMn</t>
         </is>
       </c>
       <c r="C234" s="29" t="inlineStr">
         <is>
-          <t>ET_Summer_Total</t>
+          <t>Cld_December_Mean</t>
         </is>
       </c>
       <c r="D234" s="18" t="inlineStr">
         <is>
-          <t>14_Evapotranspiration (البخر والنتح)</t>
+          <t>10_Cloud_Cover (الغطاء السحابي)</t>
         </is>
       </c>
       <c r="E234" s="12" t="inlineStr">
         <is>
-          <t>مجموع البخر والنتح لفصل الصيف الأرصادي (شهور يونيو، يوليو، أغسطس - JJA).</t>
+          <t>متوسط نسبة الغطاء السحابي الكلي للسماء لشهر ديسمبر.</t>
         </is>
       </c>
       <c r="F234" s="19" t="inlineStr">
         <is>
-          <t>ملم (mm)</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G234" s="30" t="inlineStr">
         <is>
-          <t>خريطة مجموع البخر والنتح خلال فصل الصيف (ملم)</t>
+          <t>خريطة متوسط الغطاء السحابي لشهر ديسمبر (%)</t>
         </is>
       </c>
     </row>
@@ -9885,32 +9885,32 @@
       </c>
       <c r="B235" s="5" t="inlineStr">
         <is>
-          <t>ET_AutTot</t>
+          <t>WC_WinMean</t>
         </is>
       </c>
       <c r="C235" s="31" t="inlineStr">
         <is>
-          <t>ET_Autumn_Total</t>
+          <t>WC_Winter_Mean</t>
         </is>
       </c>
       <c r="D235" s="15" t="inlineStr">
         <is>
-          <t>14_Evapotranspiration (البخر والنتح)</t>
+          <t>12_Wind_Chill (مبرد الرياح)</t>
         </is>
       </c>
       <c r="E235" s="7" t="inlineStr">
         <is>
-          <t>مجموع البخر والنتح لفصل الخريف الأرصادي (شهور سبتمبر، أكتوبر، نوفمبر - SON).</t>
+          <t>متوسط درجة البرودة الريحية لفصل الشتاء المحسوبة بمعادلة NWS لخفض الحرارة بفعل سرعة الرياح.</t>
         </is>
       </c>
       <c r="F235" s="16" t="inlineStr">
         <is>
-          <t>ملم (mm)</t>
+          <t>°C</t>
         </is>
       </c>
       <c r="G235" s="32" t="inlineStr">
         <is>
-          <t>خريطة مجموع البخر والنتح خلال فصل الخريف (ملم)</t>
+          <t>خريطة متوسط مبرد الرياح خلال فصل الشتاء (°C)</t>
         </is>
       </c>
     </row>
@@ -9920,32 +9920,32 @@
       </c>
       <c r="B236" s="10" t="inlineStr">
         <is>
-          <t>PET_HarAnn</t>
+          <t>WC_AnnMean</t>
         </is>
       </c>
       <c r="C236" s="29" t="inlineStr">
         <is>
-          <t>PET_Hargreaves_Annual</t>
+          <t>WC_Annual_Mean</t>
         </is>
       </c>
       <c r="D236" s="18" t="inlineStr">
         <is>
-          <t>14_Evapotranspiration (البخر والنتح)</t>
+          <t>12_Wind_Chill (مبرد الرياح)</t>
         </is>
       </c>
       <c r="E236" s="12" t="inlineStr">
         <is>
-          <t>التبخر-نتح الكامن السنوي بهارجريفز (حقل رديف مطابق تماماً لـ ET_Annual_Total للتوافقية العكسية).</t>
+          <t>المتوسط الحسابي السنوي لتأثير البرودة الريحية على حرارة الهواء المحسوسة.</t>
         </is>
       </c>
       <c r="F236" s="19" t="inlineStr">
         <is>
-          <t>ملم (mm)</t>
+          <t>°C</t>
         </is>
       </c>
       <c r="G236" s="30" t="inlineStr">
         <is>
-          <t>خريطة التبخر والنتح الكامن السنوي بهارجريفز (ملم)</t>
+          <t>خريطة المتوسط السنوي لمبرد الرياح (°C)</t>
         </is>
       </c>
     </row>
@@ -9955,32 +9955,32 @@
       </c>
       <c r="B237" s="5" t="inlineStr">
         <is>
-          <t>ET_JanTot</t>
+          <t>DM_AridAnn</t>
         </is>
       </c>
       <c r="C237" s="31" t="inlineStr">
         <is>
-          <t>ET_January_Total</t>
+          <t>DM_Aridity_Annual</t>
         </is>
       </c>
       <c r="D237" s="15" t="inlineStr">
         <is>
-          <t>14_Evapotranspiration (البخر والنتح)</t>
+          <t>13_De_Martonne_Aridity (دليل دي مارتون)</t>
         </is>
       </c>
       <c r="E237" s="7" t="inlineStr">
         <is>
-          <t>متوسط مجموع البخر والنتح المرجعي الكامن لشهر يناير بطريقة هارجريفز-ساماني FAO-56.</t>
+          <t>دليل القحولة والجفاف السنوي لدي مارتون I = P / (T + 10) لتصنيف الأقاليم من القاحل فائق الجفاف إلى الرطب.</t>
         </is>
       </c>
       <c r="F237" s="16" t="inlineStr">
         <is>
-          <t>ملم/شهر (mm/month)</t>
+          <t>مؤشر (Index)</t>
         </is>
       </c>
       <c r="G237" s="32" t="inlineStr">
         <is>
-          <t>خريطة مجموع البخر والنتح لشهر يناير (ملم/شهر)</t>
+          <t>خريطة دليل دي مارتون السنوي للقحولة والجفاف</t>
         </is>
       </c>
     </row>
@@ -9990,12 +9990,12 @@
       </c>
       <c r="B238" s="10" t="inlineStr">
         <is>
-          <t>ET_FebTot</t>
+          <t>ET_AnnTot</t>
         </is>
       </c>
       <c r="C238" s="29" t="inlineStr">
         <is>
-          <t>ET_February_Total</t>
+          <t>ET_Annual_Total</t>
         </is>
       </c>
       <c r="D238" s="18" t="inlineStr">
@@ -10005,17 +10005,17 @@
       </c>
       <c r="E238" s="12" t="inlineStr">
         <is>
-          <t>متوسط مجموع البخر والنتح المرجعي الكامن لشهر فبراير بطريقة هارجريفز-ساماني FAO-56.</t>
+          <t>المجموع التراكمي السنوي للبخر والنتح المرجعي الكامن المحسوب بمعادلة Hargreaves-Samani (FAO-56).</t>
         </is>
       </c>
       <c r="F238" s="19" t="inlineStr">
         <is>
-          <t>ملم/شهر (mm/month)</t>
+          <t>ملم (mm)</t>
         </is>
       </c>
       <c r="G238" s="30" t="inlineStr">
         <is>
-          <t>خريطة مجموع البخر والنتح لشهر فبراير (ملم/شهر)</t>
+          <t>خريطة المجموع السنوي للبخر والنتح (ملم)</t>
         </is>
       </c>
     </row>
@@ -10025,12 +10025,12 @@
       </c>
       <c r="B239" s="5" t="inlineStr">
         <is>
-          <t>ET_MarTot</t>
+          <t>ET_AnnMean</t>
         </is>
       </c>
       <c r="C239" s="31" t="inlineStr">
         <is>
-          <t>ET_March_Total</t>
+          <t>ET_Annual_Mean</t>
         </is>
       </c>
       <c r="D239" s="15" t="inlineStr">
@@ -10040,17 +10040,17 @@
       </c>
       <c r="E239" s="7" t="inlineStr">
         <is>
-          <t>متوسط مجموع البخر والنتح المرجعي الكامن لشهر مارس بطريقة هارجريفز-ساماني FAO-56.</t>
+          <t>المعدل الشهري للبخر والنتح المرجعي (المجموع التراكمي السنوي مقسوماً على 12 شهراً).</t>
         </is>
       </c>
       <c r="F239" s="16" t="inlineStr">
         <is>
-          <t>ملم/شهر (mm/month)</t>
+          <t>ملم (mm)</t>
         </is>
       </c>
       <c r="G239" s="32" t="inlineStr">
         <is>
-          <t>خريطة مجموع البخر والنتح لشهر مارس (ملم/شهر)</t>
+          <t>خريطة المعدل الشهري للبخر والنتح (ملم)</t>
         </is>
       </c>
     </row>
@@ -10060,32 +10060,32 @@
       </c>
       <c r="B240" s="10" t="inlineStr">
         <is>
-          <t>ET_AprTot</t>
+          <t>ET_MonMean</t>
         </is>
       </c>
       <c r="C240" s="29" t="inlineStr">
         <is>
-          <t>ET_April_Total</t>
+          <t>ET_Month_Mean</t>
         </is>
       </c>
       <c r="D240" s="18" t="inlineStr">
         <is>
-          <t>14_Evapotranspiration (البخر والنتح)</t>
+          <t>14_Evapotranspiration (البخر-نتح المرجعي)</t>
         </is>
       </c>
       <c r="E240" s="12" t="inlineStr">
         <is>
-          <t>متوسط مجموع البخر والنتح المرجعي الكامن لشهر أبريل بطريقة هارجريفز-ساماني FAO-56.</t>
+          <t>المعدل الشهري للبخر-نتح المرجعي المحسوب بطريقة هارجريفز (متوسط الشهور = المجموع السنوي / 12).</t>
         </is>
       </c>
       <c r="F240" s="19" t="inlineStr">
         <is>
-          <t>ملم/شهر (mm/month)</t>
+          <t>mm/month</t>
         </is>
       </c>
       <c r="G240" s="30" t="inlineStr">
         <is>
-          <t>خريطة مجموع البخر والنتح لشهر أبريل (ملم/شهر)</t>
+          <t>خريطة المتوسط الشهري للبخر والنتح المرجعي (mm/month)</t>
         </is>
       </c>
     </row>
@@ -10095,12 +10095,12 @@
       </c>
       <c r="B241" s="5" t="inlineStr">
         <is>
-          <t>ET_MayTot</t>
+          <t>ET_AnnRng</t>
         </is>
       </c>
       <c r="C241" s="31" t="inlineStr">
         <is>
-          <t>ET_May_Total</t>
+          <t>ET_Annual_Range</t>
         </is>
       </c>
       <c r="D241" s="15" t="inlineStr">
@@ -10110,17 +10110,17 @@
       </c>
       <c r="E241" s="7" t="inlineStr">
         <is>
-          <t>متوسط مجموع البخر والنتح المرجعي الكامن لشهر مايو بطريقة هارجريفز-ساماني FAO-56.</t>
+          <t>المدى السنوي للبخر والنتح (الفارق بين أعلى شهور السنة فقداً للماء بالبخر والنتح وأدناها).</t>
         </is>
       </c>
       <c r="F241" s="16" t="inlineStr">
         <is>
-          <t>ملم/شهر (mm/month)</t>
+          <t>ملم (mm)</t>
         </is>
       </c>
       <c r="G241" s="32" t="inlineStr">
         <is>
-          <t>خريطة مجموع البخر والنتح لشهر مايو (ملم/شهر)</t>
+          <t>خريطة المدى السنوي للبخر والنتح (ملم)</t>
         </is>
       </c>
     </row>
@@ -10130,12 +10130,12 @@
       </c>
       <c r="B242" s="10" t="inlineStr">
         <is>
-          <t>ET_JunTot</t>
+          <t>ET_SeaRng</t>
         </is>
       </c>
       <c r="C242" s="29" t="inlineStr">
         <is>
-          <t>ET_June_Total</t>
+          <t>ET_Seasonal_Range</t>
         </is>
       </c>
       <c r="D242" s="18" t="inlineStr">
@@ -10145,17 +10145,17 @@
       </c>
       <c r="E242" s="12" t="inlineStr">
         <is>
-          <t>متوسط مجموع البخر والنتح المرجعي الكامن لشهر يونيو بطريقة هارجريفز-ساماني FAO-56.</t>
+          <t>المدى الفصلي للبخر والنتح (الفارق بين مجموع أعلى فصول السنة في البخر والنتح ومجموع أقلها).</t>
         </is>
       </c>
       <c r="F242" s="19" t="inlineStr">
         <is>
-          <t>ملم/شهر (mm/month)</t>
+          <t>ملم (mm)</t>
         </is>
       </c>
       <c r="G242" s="30" t="inlineStr">
         <is>
-          <t>خريطة مجموع البخر والنتح لشهر يونيو (ملم/شهر)</t>
+          <t>خريطة المدى الفصلي للبخر والنتح (ملم)</t>
         </is>
       </c>
     </row>
@@ -10165,12 +10165,12 @@
       </c>
       <c r="B243" s="5" t="inlineStr">
         <is>
-          <t>ET_JulTot</t>
+          <t>ET_WinTot</t>
         </is>
       </c>
       <c r="C243" s="31" t="inlineStr">
         <is>
-          <t>ET_July_Total</t>
+          <t>ET_Winter_Total</t>
         </is>
       </c>
       <c r="D243" s="15" t="inlineStr">
@@ -10180,17 +10180,17 @@
       </c>
       <c r="E243" s="7" t="inlineStr">
         <is>
-          <t>متوسط مجموع البخر والنتح المرجعي الكامن لشهر يوليو بطريقة هارجريفز-ساماني FAO-56.</t>
+          <t>مجموع البخر والنتح لفصل الشتاء الأرصادي (شهور ديسمبر، يناير، فبراير - DJF).</t>
         </is>
       </c>
       <c r="F243" s="16" t="inlineStr">
         <is>
-          <t>ملم/شهر (mm/month)</t>
+          <t>ملم (mm)</t>
         </is>
       </c>
       <c r="G243" s="32" t="inlineStr">
         <is>
-          <t>خريطة مجموع البخر والنتح لشهر يوليو (ملم/شهر)</t>
+          <t>خريطة مجموع البخر والنتح خلال فصل الشتاء (ملم)</t>
         </is>
       </c>
     </row>
@@ -10200,12 +10200,12 @@
       </c>
       <c r="B244" s="10" t="inlineStr">
         <is>
-          <t>ET_AugTot</t>
+          <t>ET_SprTot</t>
         </is>
       </c>
       <c r="C244" s="29" t="inlineStr">
         <is>
-          <t>ET_August_Total</t>
+          <t>ET_Spring_Total</t>
         </is>
       </c>
       <c r="D244" s="18" t="inlineStr">
@@ -10215,17 +10215,17 @@
       </c>
       <c r="E244" s="12" t="inlineStr">
         <is>
-          <t>متوسط مجموع البخر والنتح المرجعي الكامن لشهر أغسطس بطريقة هارجريفز-ساماني FAO-56.</t>
+          <t>مجموع البخر والنتح لفصل الربيع الأرصادي (شهور مارس، أبريل، مايو - MAM).</t>
         </is>
       </c>
       <c r="F244" s="19" t="inlineStr">
         <is>
-          <t>ملم/شهر (mm/month)</t>
+          <t>ملم (mm)</t>
         </is>
       </c>
       <c r="G244" s="30" t="inlineStr">
         <is>
-          <t>خريطة مجموع البخر والنتح لشهر أغسطس (ملم/شهر)</t>
+          <t>خريطة مجموع البخر والنتح خلال فصل الربيع (ملم)</t>
         </is>
       </c>
     </row>
@@ -10235,12 +10235,12 @@
       </c>
       <c r="B245" s="5" t="inlineStr">
         <is>
-          <t>ET_SepTot</t>
+          <t>ET_SumTot</t>
         </is>
       </c>
       <c r="C245" s="31" t="inlineStr">
         <is>
-          <t>ET_September_Total</t>
+          <t>ET_Summer_Total</t>
         </is>
       </c>
       <c r="D245" s="15" t="inlineStr">
@@ -10250,17 +10250,17 @@
       </c>
       <c r="E245" s="7" t="inlineStr">
         <is>
-          <t>متوسط مجموع البخر والنتح المرجعي الكامن لشهر سبتمبر بطريقة هارجريفز-ساماني FAO-56.</t>
+          <t>مجموع البخر والنتح لفصل الصيف الأرصادي (شهور يونيو، يوليو، أغسطس - JJA).</t>
         </is>
       </c>
       <c r="F245" s="16" t="inlineStr">
         <is>
-          <t>ملم/شهر (mm/month)</t>
+          <t>ملم (mm)</t>
         </is>
       </c>
       <c r="G245" s="32" t="inlineStr">
         <is>
-          <t>خريطة مجموع البخر والنتح لشهر سبتمبر (ملم/شهر)</t>
+          <t>خريطة مجموع البخر والنتح خلال فصل الصيف (ملم)</t>
         </is>
       </c>
     </row>
@@ -10270,12 +10270,12 @@
       </c>
       <c r="B246" s="10" t="inlineStr">
         <is>
-          <t>ET_OctTot</t>
+          <t>ET_AutTot</t>
         </is>
       </c>
       <c r="C246" s="29" t="inlineStr">
         <is>
-          <t>ET_October_Total</t>
+          <t>ET_Autumn_Total</t>
         </is>
       </c>
       <c r="D246" s="18" t="inlineStr">
@@ -10285,17 +10285,17 @@
       </c>
       <c r="E246" s="12" t="inlineStr">
         <is>
-          <t>متوسط مجموع البخر والنتح المرجعي الكامن لشهر أكتوبر بطريقة هارجريفز-ساماني FAO-56.</t>
+          <t>مجموع البخر والنتح لفصل الخريف الأرصادي (شهور سبتمبر، أكتوبر، نوفمبر - SON).</t>
         </is>
       </c>
       <c r="F246" s="19" t="inlineStr">
         <is>
-          <t>ملم/شهر (mm/month)</t>
+          <t>ملم (mm)</t>
         </is>
       </c>
       <c r="G246" s="30" t="inlineStr">
         <is>
-          <t>خريطة مجموع البخر والنتح لشهر أكتوبر (ملم/شهر)</t>
+          <t>خريطة مجموع البخر والنتح خلال فصل الخريف (ملم)</t>
         </is>
       </c>
     </row>
@@ -10305,12 +10305,12 @@
       </c>
       <c r="B247" s="5" t="inlineStr">
         <is>
-          <t>ET_NovTot</t>
+          <t>PET_HarAnn</t>
         </is>
       </c>
       <c r="C247" s="31" t="inlineStr">
         <is>
-          <t>ET_November_Total</t>
+          <t>PET_Hargreaves_Annual</t>
         </is>
       </c>
       <c r="D247" s="15" t="inlineStr">
@@ -10320,17 +10320,17 @@
       </c>
       <c r="E247" s="7" t="inlineStr">
         <is>
-          <t>متوسط مجموع البخر والنتح المرجعي الكامن لشهر نوفمبر بطريقة هارجريفز-ساماني FAO-56.</t>
+          <t>التبخر-نتح الكامن السنوي بهارجريفز (حقل رديف مطابق تماماً لـ ET_Annual_Total للتوافقية العكسية).</t>
         </is>
       </c>
       <c r="F247" s="16" t="inlineStr">
         <is>
-          <t>ملم/شهر (mm/month)</t>
+          <t>ملم (mm)</t>
         </is>
       </c>
       <c r="G247" s="32" t="inlineStr">
         <is>
-          <t>خريطة مجموع البخر والنتح لشهر نوفمبر (ملم/شهر)</t>
+          <t>خريطة التبخر والنتح الكامن السنوي بهارجريفز (ملم)</t>
         </is>
       </c>
     </row>
@@ -10340,12 +10340,12 @@
       </c>
       <c r="B248" s="10" t="inlineStr">
         <is>
-          <t>ET_DecTot</t>
+          <t>ET_JanTot</t>
         </is>
       </c>
       <c r="C248" s="29" t="inlineStr">
         <is>
-          <t>ET_December_Total</t>
+          <t>ET_January_Total</t>
         </is>
       </c>
       <c r="D248" s="18" t="inlineStr">
@@ -10355,7 +10355,7 @@
       </c>
       <c r="E248" s="12" t="inlineStr">
         <is>
-          <t>متوسط مجموع البخر والنتح المرجعي الكامن لشهر ديسمبر بطريقة هارجريفز-ساماني FAO-56.</t>
+          <t>متوسط مجموع البخر والنتح المرجعي الكامن لشهر يناير بطريقة هارجريفز-ساماني FAO-56.</t>
         </is>
       </c>
       <c r="F248" s="19" t="inlineStr">
@@ -10365,7 +10365,7 @@
       </c>
       <c r="G248" s="30" t="inlineStr">
         <is>
-          <t>خريطة مجموع البخر والنتح لشهر ديسمبر (ملم/شهر)</t>
+          <t>خريطة مجموع البخر والنتح لشهر يناير (ملم/شهر)</t>
         </is>
       </c>
     </row>
@@ -10375,32 +10375,32 @@
       </c>
       <c r="B249" s="5" t="inlineStr">
         <is>
-          <t>UNEP_Arid</t>
+          <t>ET_FebTot</t>
         </is>
       </c>
       <c r="C249" s="31" t="inlineStr">
         <is>
-          <t>UNEP_Aridity_Annual</t>
+          <t>ET_February_Total</t>
         </is>
       </c>
       <c r="D249" s="15" t="inlineStr">
         <is>
-          <t>15_UNEP_Aridity (مؤشر UNEP)</t>
+          <t>14_Evapotranspiration (البخر والنتح)</t>
         </is>
       </c>
       <c r="E249" s="7" t="inlineStr">
         <is>
-          <t>مؤشر القحولة العالمي لبرنامج الأمم المتحدة للبيئة AI = P / ET_ann لتحديد المناطق القاحلة وشبه القاحلة.</t>
+          <t>متوسط مجموع البخر والنتح المرجعي الكامن لشهر فبراير بطريقة هارجريفز-ساماني FAO-56.</t>
         </is>
       </c>
       <c r="F249" s="16" t="inlineStr">
         <is>
-          <t>نسبة (Ratio)</t>
+          <t>ملم/شهر (mm/month)</t>
         </is>
       </c>
       <c r="G249" s="32" t="inlineStr">
         <is>
-          <t>خريطة مؤشر القحولة العالمي لبرنامج الأمم المتحدة للبيئة</t>
+          <t>خريطة مجموع البخر والنتح لشهر فبراير (ملم/شهر)</t>
         </is>
       </c>
     </row>
@@ -10410,32 +10410,32 @@
       </c>
       <c r="B250" s="10" t="inlineStr">
         <is>
-          <t>WatDefAnn</t>
+          <t>ET_MarTot</t>
         </is>
       </c>
       <c r="C250" s="29" t="inlineStr">
         <is>
-          <t>Water_Deficit_Annual</t>
+          <t>ET_March_Total</t>
         </is>
       </c>
       <c r="D250" s="18" t="inlineStr">
         <is>
-          <t>16_Water_Deficit (العجز المائي)</t>
+          <t>14_Evapotranspiration (البخر والنتح)</t>
         </is>
       </c>
       <c r="E250" s="12" t="inlineStr">
         <is>
-          <t>الموازنة المائية المناخية السنوية الصافية WD = P - ET_ann (القيم السالبة تعبر عن عجز مائي والموجبة فائض مائي).</t>
+          <t>متوسط مجموع البخر والنتح المرجعي الكامن لشهر مارس بطريقة هارجريفز-ساماني FAO-56.</t>
         </is>
       </c>
       <c r="F250" s="19" t="inlineStr">
         <is>
-          <t>ملم (mm)</t>
+          <t>ملم/شهر (mm/month)</t>
         </is>
       </c>
       <c r="G250" s="30" t="inlineStr">
         <is>
-          <t>خريطة الموازنة والعجز المائي المناخي السنوي (ملم)</t>
+          <t>خريطة مجموع البخر والنتح لشهر مارس (ملم/شهر)</t>
         </is>
       </c>
     </row>
@@ -10445,32 +10445,32 @@
       </c>
       <c r="B251" s="5" t="inlineStr">
         <is>
-          <t>Dry_Months</t>
+          <t>ET_AprTot</t>
         </is>
       </c>
       <c r="C251" s="31" t="inlineStr">
         <is>
-          <t>Dry_Months_Count</t>
+          <t>ET_April_Total</t>
         </is>
       </c>
       <c r="D251" s="15" t="inlineStr">
         <is>
-          <t>17_Dry_Months (الأشهر الجافة)</t>
+          <t>14_Evapotranspiration (البخر والنتح)</t>
         </is>
       </c>
       <c r="E251" s="7" t="inlineStr">
         <is>
-          <t>عدد أشهر السنة الجافة بيولوجياً ومناخياً وفق معيار والتر-ليث البيومناخي الشهير (P &lt; 2T).</t>
+          <t>متوسط مجموع البخر والنتح المرجعي الكامن لشهر أبريل بطريقة هارجريفز-ساماني FAO-56.</t>
         </is>
       </c>
       <c r="F251" s="16" t="inlineStr">
         <is>
-          <t>شهر (0-12)</t>
+          <t>ملم/شهر (mm/month)</t>
         </is>
       </c>
       <c r="G251" s="32" t="inlineStr">
         <is>
-          <t>خريطة عدد الأشهر الجافة بيولوجياً في السنة</t>
+          <t>خريطة مجموع البخر والنتح لشهر أبريل (ملم/شهر)</t>
         </is>
       </c>
     </row>
@@ -10480,32 +10480,32 @@
       </c>
       <c r="B252" s="10" t="inlineStr">
         <is>
-          <t>T_TrendDec</t>
+          <t>ET_MayTot</t>
         </is>
       </c>
       <c r="C252" s="29" t="inlineStr">
         <is>
-          <t>T_Trend_Decade</t>
+          <t>ET_May_Total</t>
         </is>
       </c>
       <c r="D252" s="18" t="inlineStr">
         <is>
-          <t>18_Trends_And_Anomalies (الاتجاهات والشذوذ)</t>
+          <t>14_Evapotranspiration (البخر والنتح)</t>
         </is>
       </c>
       <c r="E252" s="12" t="inlineStr">
         <is>
-          <t>معدل تغير واتجاه درجة الحرارة لكل عقد زمني (10 سنوات) باستخدام انحدار المربعات الصغرى الخطي.</t>
+          <t>متوسط مجموع البخر والنتح المرجعي الكامن لشهر مايو بطريقة هارجريفز-ساماني FAO-56.</t>
         </is>
       </c>
       <c r="F252" s="19" t="inlineStr">
         <is>
-          <t>°C/decade</t>
+          <t>ملم/شهر (mm/month)</t>
         </is>
       </c>
       <c r="G252" s="30" t="inlineStr">
         <is>
-          <t>خريطة اتجاه تغير درجة الحرارة في العقد الزمني (°C/decade)</t>
+          <t>خريطة مجموع البخر والنتح لشهر مايو (ملم/شهر)</t>
         </is>
       </c>
     </row>
@@ -10515,32 +10515,32 @@
       </c>
       <c r="B253" s="5" t="inlineStr">
         <is>
-          <t>R_TrendDec</t>
+          <t>ET_JunTot</t>
         </is>
       </c>
       <c r="C253" s="31" t="inlineStr">
         <is>
-          <t>R_Trend_Decade</t>
+          <t>ET_June_Total</t>
         </is>
       </c>
       <c r="D253" s="15" t="inlineStr">
         <is>
-          <t>18_Trends_And_Anomalies (الاتجاهات والشذوذ)</t>
+          <t>14_Evapotranspiration (البخر والنتح)</t>
         </is>
       </c>
       <c r="E253" s="7" t="inlineStr">
         <is>
-          <t>معدل تغير واتجاه تساقط الأمطار لكل عقد زمني (10 سنوات) باستخدام انحدار المربعات الصغرى الخطي.</t>
+          <t>متوسط مجموع البخر والنتح المرجعي الكامن لشهر يونيو بطريقة هارجريفز-ساماني FAO-56.</t>
         </is>
       </c>
       <c r="F253" s="16" t="inlineStr">
         <is>
-          <t>mm/decade</t>
+          <t>ملم/شهر (mm/month)</t>
         </is>
       </c>
       <c r="G253" s="32" t="inlineStr">
         <is>
-          <t>خريطة اتجاه تغير تساقط الأمطار في العقد الزمني (mm/decade)</t>
+          <t>خريطة مجموع البخر والنتح لشهر يونيو (ملم/شهر)</t>
         </is>
       </c>
     </row>
@@ -10550,32 +10550,32 @@
       </c>
       <c r="B254" s="10" t="inlineStr">
         <is>
-          <t>T_AnomAnn</t>
+          <t>ET_JulTot</t>
         </is>
       </c>
       <c r="C254" s="29" t="inlineStr">
         <is>
-          <t>T_Anom_Annual</t>
+          <t>ET_July_Total</t>
         </is>
       </c>
       <c r="D254" s="18" t="inlineStr">
         <is>
-          <t>18_Trends_And_Anomalies (الاتجاهات والشذوذ)</t>
+          <t>14_Evapotranspiration (البخر والنتح)</t>
         </is>
       </c>
       <c r="E254" s="12" t="inlineStr">
         <is>
-          <t>الشذوذ الحراري السنوي لدرجة الحرارة مقارنة بخط الأساس المناخي العالمي 1991–2020.</t>
+          <t>متوسط مجموع البخر والنتح المرجعي الكامن لشهر يوليو بطريقة هارجريفز-ساماني FAO-56.</t>
         </is>
       </c>
       <c r="F254" s="19" t="inlineStr">
         <is>
-          <t>°C</t>
+          <t>ملم/شهر (mm/month)</t>
         </is>
       </c>
       <c r="G254" s="30" t="inlineStr">
         <is>
-          <t>خريطة الشذوذ الحراري السنوي مقارنة بخط أساس 1991–2020 (°C)</t>
+          <t>خريطة مجموع البخر والنتح لشهر يوليو (ملم/شهر)</t>
         </is>
       </c>
     </row>
@@ -10585,32 +10585,32 @@
       </c>
       <c r="B255" s="5" t="inlineStr">
         <is>
-          <t>T_AnomWin</t>
+          <t>ET_AugTot</t>
         </is>
       </c>
       <c r="C255" s="31" t="inlineStr">
         <is>
-          <t>T_Anom_Winter</t>
+          <t>ET_August_Total</t>
         </is>
       </c>
       <c r="D255" s="15" t="inlineStr">
         <is>
-          <t>18_Trends_And_Anomalies (الاتجاهات والشذوذ)</t>
+          <t>14_Evapotranspiration (البخر والنتح)</t>
         </is>
       </c>
       <c r="E255" s="7" t="inlineStr">
         <is>
-          <t>الشذوذ الحراري لفصل الشتاء مقارنة بمتوسط شهور الشتاء لخط الأساس المناخي 1991–2020.</t>
+          <t>متوسط مجموع البخر والنتح المرجعي الكامن لشهر أغسطس بطريقة هارجريفز-ساماني FAO-56.</t>
         </is>
       </c>
       <c r="F255" s="16" t="inlineStr">
         <is>
-          <t>°C</t>
+          <t>ملم/شهر (mm/month)</t>
         </is>
       </c>
       <c r="G255" s="32" t="inlineStr">
         <is>
-          <t>خريطة الشذوذ الحراري لفصل الشتاء مقارنة بخط أساس 1991–2020 (°C)</t>
+          <t>خريطة مجموع البخر والنتح لشهر أغسطس (ملم/شهر)</t>
         </is>
       </c>
     </row>
@@ -10620,32 +10620,32 @@
       </c>
       <c r="B256" s="10" t="inlineStr">
         <is>
-          <t>T_AnomSum</t>
+          <t>ET_SepTot</t>
         </is>
       </c>
       <c r="C256" s="29" t="inlineStr">
         <is>
-          <t>T_Anom_Summer</t>
+          <t>ET_September_Total</t>
         </is>
       </c>
       <c r="D256" s="18" t="inlineStr">
         <is>
-          <t>18_Trends_And_Anomalies (الاتجاهات والشذوذ)</t>
+          <t>14_Evapotranspiration (البخر والنتح)</t>
         </is>
       </c>
       <c r="E256" s="12" t="inlineStr">
         <is>
-          <t>الشذوذ الحراري لفصل الصيف مقارنة بمتوسط شهور الصيف لخط الأساس المناخي 1991–2020.</t>
+          <t>متوسط مجموع البخر والنتح المرجعي الكامن لشهر سبتمبر بطريقة هارجريفز-ساماني FAO-56.</t>
         </is>
       </c>
       <c r="F256" s="19" t="inlineStr">
         <is>
-          <t>°C</t>
+          <t>ملم/شهر (mm/month)</t>
         </is>
       </c>
       <c r="G256" s="30" t="inlineStr">
         <is>
-          <t>خريطة الشذوذ الحراري لفصل الصيف مقارنة بخط أساس 1991–2020 (°C)</t>
+          <t>خريطة مجموع البخر والنتح لشهر سبتمبر (ملم/شهر)</t>
         </is>
       </c>
     </row>
@@ -10655,32 +10655,32 @@
       </c>
       <c r="B257" s="5" t="inlineStr">
         <is>
-          <t>R_AnomAnn</t>
+          <t>ET_OctTot</t>
         </is>
       </c>
       <c r="C257" s="31" t="inlineStr">
         <is>
-          <t>R_Anom_Annual</t>
+          <t>ET_October_Total</t>
         </is>
       </c>
       <c r="D257" s="15" t="inlineStr">
         <is>
-          <t>18_Trends_And_Anomalies (الاتجاهات والشذوذ)</t>
+          <t>14_Evapotranspiration (البخر والنتح)</t>
         </is>
       </c>
       <c r="E257" s="7" t="inlineStr">
         <is>
-          <t>شذوذ الأمطار السنوي المطلق مقارنة بمتوسط الأمطار لخط الأساس المناخي 1991–2020.</t>
+          <t>متوسط مجموع البخر والنتح المرجعي الكامن لشهر أكتوبر بطريقة هارجريفز-ساماني FAO-56.</t>
         </is>
       </c>
       <c r="F257" s="16" t="inlineStr">
         <is>
-          <t>ملم (mm)</t>
+          <t>ملم/شهر (mm/month)</t>
         </is>
       </c>
       <c r="G257" s="32" t="inlineStr">
         <is>
-          <t>خريطة شذوذ تساقط الأمطار السنوي مقارنة بخط أساس 1991–2020 (ملم)</t>
+          <t>خريطة مجموع البخر والنتح لشهر أكتوبر (ملم/شهر)</t>
         </is>
       </c>
     </row>
@@ -10690,32 +10690,32 @@
       </c>
       <c r="B258" s="10" t="inlineStr">
         <is>
-          <t>R_AnomPct</t>
+          <t>ET_NovTot</t>
         </is>
       </c>
       <c r="C258" s="29" t="inlineStr">
         <is>
-          <t>R_Anom_Annual_Pct</t>
+          <t>ET_November_Total</t>
         </is>
       </c>
       <c r="D258" s="18" t="inlineStr">
         <is>
-          <t>18_Trends_And_Anomalies (الاتجاهات والشذوذ)</t>
+          <t>14_Evapotranspiration (البخر والنتح)</t>
         </is>
       </c>
       <c r="E258" s="12" t="inlineStr">
         <is>
-          <t>شذوذ الأمطار السنوي كنسبة مئوية من خط الأساس المناخي 1991–2020 (فرق نسبي مئوي).</t>
+          <t>متوسط مجموع البخر والنتح المرجعي الكامن لشهر نوفمبر بطريقة هارجريفز-ساماني FAO-56.</t>
         </is>
       </c>
       <c r="F258" s="19" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>ملم/شهر (mm/month)</t>
         </is>
       </c>
       <c r="G258" s="30" t="inlineStr">
         <is>
-          <t>خريطة الشذوذ النسبي المئوي للأمطار مقارنة بخط أساس 1991–2020 (%)</t>
+          <t>خريطة مجموع البخر والنتح لشهر نوفمبر (ملم/شهر)</t>
         </is>
       </c>
     </row>
@@ -10725,32 +10725,32 @@
       </c>
       <c r="B259" s="5" t="inlineStr">
         <is>
-          <t>R_AnomWin</t>
+          <t>ET_DecTot</t>
         </is>
       </c>
       <c r="C259" s="31" t="inlineStr">
         <is>
-          <t>R_Anom_Winter</t>
+          <t>ET_December_Total</t>
         </is>
       </c>
       <c r="D259" s="15" t="inlineStr">
         <is>
-          <t>18_Trends_And_Anomalies (الاتجاهات والشذوذ)</t>
+          <t>14_Evapotranspiration (البخر والنتح)</t>
         </is>
       </c>
       <c r="E259" s="7" t="inlineStr">
         <is>
-          <t>شذوذ أمطار فصل الشتاء المطلق مقارنة بأمطار شتاء خط الأساس المناخي 1991–2020.</t>
+          <t>متوسط مجموع البخر والنتح المرجعي الكامن لشهر ديسمبر بطريقة هارجريفز-ساماني FAO-56.</t>
         </is>
       </c>
       <c r="F259" s="16" t="inlineStr">
         <is>
-          <t>ملم (mm)</t>
+          <t>ملم/شهر (mm/month)</t>
         </is>
       </c>
       <c r="G259" s="32" t="inlineStr">
         <is>
-          <t>خريطة شذوذ أمطار الشتاء مقارنة بخط أساس 1991–2020 (ملم)</t>
+          <t>خريطة مجموع البخر والنتح لشهر ديسمبر (ملم/شهر)</t>
         </is>
       </c>
     </row>
@@ -10760,37 +10760,422 @@
       </c>
       <c r="B260" s="10" t="inlineStr">
         <is>
+          <t>UNEP_Arid</t>
+        </is>
+      </c>
+      <c r="C260" s="29" t="inlineStr">
+        <is>
+          <t>UNEP_Aridity_Annual</t>
+        </is>
+      </c>
+      <c r="D260" s="18" t="inlineStr">
+        <is>
+          <t>15_UNEP_Aridity (مؤشر UNEP)</t>
+        </is>
+      </c>
+      <c r="E260" s="12" t="inlineStr">
+        <is>
+          <t>مؤشر القحولة العالمي لبرنامج الأمم المتحدة للبيئة AI = P / ET_ann لتحديد المناطق القاحلة وشبه القاحلة.</t>
+        </is>
+      </c>
+      <c r="F260" s="19" t="inlineStr">
+        <is>
+          <t>نسبة (Ratio)</t>
+        </is>
+      </c>
+      <c r="G260" s="30" t="inlineStr">
+        <is>
+          <t>خريطة مؤشر القحولة العالمي لبرنامج الأمم المتحدة للبيئة</t>
+        </is>
+      </c>
+    </row>
+    <row r="261" ht="24" customHeight="1">
+      <c r="A261" s="3" t="n">
+        <v>260</v>
+      </c>
+      <c r="B261" s="5" t="inlineStr">
+        <is>
+          <t>WatDefAnn</t>
+        </is>
+      </c>
+      <c r="C261" s="31" t="inlineStr">
+        <is>
+          <t>Water_Deficit_Annual</t>
+        </is>
+      </c>
+      <c r="D261" s="15" t="inlineStr">
+        <is>
+          <t>16_Water_Deficit (العجز المائي)</t>
+        </is>
+      </c>
+      <c r="E261" s="7" t="inlineStr">
+        <is>
+          <t>الموازنة المائية المناخية السنوية الصافية WD = P - ET_ann (القيم السالبة تعبر عن عجز مائي والموجبة فائض مائي).</t>
+        </is>
+      </c>
+      <c r="F261" s="16" t="inlineStr">
+        <is>
+          <t>ملم (mm)</t>
+        </is>
+      </c>
+      <c r="G261" s="32" t="inlineStr">
+        <is>
+          <t>خريطة الموازنة والعجز المائي المناخي السنوي (ملم)</t>
+        </is>
+      </c>
+    </row>
+    <row r="262" ht="24" customHeight="1">
+      <c r="A262" s="8" t="n">
+        <v>261</v>
+      </c>
+      <c r="B262" s="10" t="inlineStr">
+        <is>
+          <t>Dry_Months</t>
+        </is>
+      </c>
+      <c r="C262" s="29" t="inlineStr">
+        <is>
+          <t>Dry_Months_Count</t>
+        </is>
+      </c>
+      <c r="D262" s="18" t="inlineStr">
+        <is>
+          <t>17_Dry_Months (الأشهر الجافة)</t>
+        </is>
+      </c>
+      <c r="E262" s="12" t="inlineStr">
+        <is>
+          <t>عدد أشهر السنة الجافة بيولوجياً ومناخياً وفق معيار والتر-ليث البيومناخي الشهير (P &lt; 2T).</t>
+        </is>
+      </c>
+      <c r="F262" s="19" t="inlineStr">
+        <is>
+          <t>شهر (0-12)</t>
+        </is>
+      </c>
+      <c r="G262" s="30" t="inlineStr">
+        <is>
+          <t>خريطة عدد الأشهر الجافة بيولوجياً في السنة</t>
+        </is>
+      </c>
+    </row>
+    <row r="263" ht="24" customHeight="1">
+      <c r="A263" s="3" t="n">
+        <v>262</v>
+      </c>
+      <c r="B263" s="5" t="inlineStr">
+        <is>
+          <t>T_TrendDec</t>
+        </is>
+      </c>
+      <c r="C263" s="31" t="inlineStr">
+        <is>
+          <t>T_Trend_Decade</t>
+        </is>
+      </c>
+      <c r="D263" s="15" t="inlineStr">
+        <is>
+          <t>18_Trends_And_Anomalies (الاتجاهات والشذوذ)</t>
+        </is>
+      </c>
+      <c r="E263" s="7" t="inlineStr">
+        <is>
+          <t>معدل تغير واتجاه درجة الحرارة لكل عقد زمني (10 سنوات) باستخدام انحدار المربعات الصغرى الخطي.</t>
+        </is>
+      </c>
+      <c r="F263" s="16" t="inlineStr">
+        <is>
+          <t>°C/decade</t>
+        </is>
+      </c>
+      <c r="G263" s="32" t="inlineStr">
+        <is>
+          <t>خريطة اتجاه تغير درجة الحرارة في العقد الزمني (°C/decade)</t>
+        </is>
+      </c>
+    </row>
+    <row r="264" ht="24" customHeight="1">
+      <c r="A264" s="8" t="n">
+        <v>263</v>
+      </c>
+      <c r="B264" s="10" t="inlineStr">
+        <is>
+          <t>R_TrendDec</t>
+        </is>
+      </c>
+      <c r="C264" s="29" t="inlineStr">
+        <is>
+          <t>R_Trend_Decade</t>
+        </is>
+      </c>
+      <c r="D264" s="18" t="inlineStr">
+        <is>
+          <t>18_Trends_And_Anomalies (الاتجاهات والشذوذ)</t>
+        </is>
+      </c>
+      <c r="E264" s="12" t="inlineStr">
+        <is>
+          <t>معدل تغير واتجاه تساقط الأمطار لكل عقد زمني (10 سنوات) باستخدام انحدار المربعات الصغرى الخطي.</t>
+        </is>
+      </c>
+      <c r="F264" s="19" t="inlineStr">
+        <is>
+          <t>mm/decade</t>
+        </is>
+      </c>
+      <c r="G264" s="30" t="inlineStr">
+        <is>
+          <t>خريطة اتجاه تغير تساقط الأمطار في العقد الزمني (mm/decade)</t>
+        </is>
+      </c>
+    </row>
+    <row r="265" ht="24" customHeight="1">
+      <c r="A265" s="3" t="n">
+        <v>264</v>
+      </c>
+      <c r="B265" s="5" t="inlineStr">
+        <is>
+          <t>T_AnomAnn</t>
+        </is>
+      </c>
+      <c r="C265" s="31" t="inlineStr">
+        <is>
+          <t>T_Anom_Annual</t>
+        </is>
+      </c>
+      <c r="D265" s="15" t="inlineStr">
+        <is>
+          <t>18_Trends_And_Anomalies (الاتجاهات والشذوذ)</t>
+        </is>
+      </c>
+      <c r="E265" s="7" t="inlineStr">
+        <is>
+          <t>الشذوذ الحراري السنوي لدرجة الحرارة مقارنة بخط الأساس المناخي العالمي 1991–2020.</t>
+        </is>
+      </c>
+      <c r="F265" s="16" t="inlineStr">
+        <is>
+          <t>°C</t>
+        </is>
+      </c>
+      <c r="G265" s="32" t="inlineStr">
+        <is>
+          <t>خريطة الشذوذ الحراري السنوي مقارنة بخط أساس 1991–2020 (°C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="266" ht="24" customHeight="1">
+      <c r="A266" s="8" t="n">
+        <v>265</v>
+      </c>
+      <c r="B266" s="10" t="inlineStr">
+        <is>
+          <t>T_AnomWin</t>
+        </is>
+      </c>
+      <c r="C266" s="29" t="inlineStr">
+        <is>
+          <t>T_Anom_Winter</t>
+        </is>
+      </c>
+      <c r="D266" s="18" t="inlineStr">
+        <is>
+          <t>18_Trends_And_Anomalies (الاتجاهات والشذوذ)</t>
+        </is>
+      </c>
+      <c r="E266" s="12" t="inlineStr">
+        <is>
+          <t>الشذوذ الحراري لفصل الشتاء مقارنة بمتوسط شهور الشتاء لخط الأساس المناخي 1991–2020.</t>
+        </is>
+      </c>
+      <c r="F266" s="19" t="inlineStr">
+        <is>
+          <t>°C</t>
+        </is>
+      </c>
+      <c r="G266" s="30" t="inlineStr">
+        <is>
+          <t>خريطة الشذوذ الحراري لفصل الشتاء مقارنة بخط أساس 1991–2020 (°C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="267" ht="24" customHeight="1">
+      <c r="A267" s="3" t="n">
+        <v>266</v>
+      </c>
+      <c r="B267" s="5" t="inlineStr">
+        <is>
+          <t>T_AnomSum</t>
+        </is>
+      </c>
+      <c r="C267" s="31" t="inlineStr">
+        <is>
+          <t>T_Anom_Summer</t>
+        </is>
+      </c>
+      <c r="D267" s="15" t="inlineStr">
+        <is>
+          <t>18_Trends_And_Anomalies (الاتجاهات والشذوذ)</t>
+        </is>
+      </c>
+      <c r="E267" s="7" t="inlineStr">
+        <is>
+          <t>الشذوذ الحراري لفصل الصيف مقارنة بمتوسط شهور الصيف لخط الأساس المناخي 1991–2020.</t>
+        </is>
+      </c>
+      <c r="F267" s="16" t="inlineStr">
+        <is>
+          <t>°C</t>
+        </is>
+      </c>
+      <c r="G267" s="32" t="inlineStr">
+        <is>
+          <t>خريطة الشذوذ الحراري لفصل الصيف مقارنة بخط أساس 1991–2020 (°C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="268" ht="24" customHeight="1">
+      <c r="A268" s="8" t="n">
+        <v>267</v>
+      </c>
+      <c r="B268" s="10" t="inlineStr">
+        <is>
+          <t>R_AnomAnn</t>
+        </is>
+      </c>
+      <c r="C268" s="29" t="inlineStr">
+        <is>
+          <t>R_Anom_Annual</t>
+        </is>
+      </c>
+      <c r="D268" s="18" t="inlineStr">
+        <is>
+          <t>18_Trends_And_Anomalies (الاتجاهات والشذوذ)</t>
+        </is>
+      </c>
+      <c r="E268" s="12" t="inlineStr">
+        <is>
+          <t>شذوذ الأمطار السنوي المطلق مقارنة بمتوسط الأمطار لخط الأساس المناخي 1991–2020.</t>
+        </is>
+      </c>
+      <c r="F268" s="19" t="inlineStr">
+        <is>
+          <t>ملم (mm)</t>
+        </is>
+      </c>
+      <c r="G268" s="30" t="inlineStr">
+        <is>
+          <t>خريطة شذوذ تساقط الأمطار السنوي مقارنة بخط أساس 1991–2020 (ملم)</t>
+        </is>
+      </c>
+    </row>
+    <row r="269" ht="24" customHeight="1">
+      <c r="A269" s="3" t="n">
+        <v>268</v>
+      </c>
+      <c r="B269" s="5" t="inlineStr">
+        <is>
+          <t>R_AnomPct</t>
+        </is>
+      </c>
+      <c r="C269" s="31" t="inlineStr">
+        <is>
+          <t>R_Anom_Annual_Pct</t>
+        </is>
+      </c>
+      <c r="D269" s="15" t="inlineStr">
+        <is>
+          <t>18_Trends_And_Anomalies (الاتجاهات والشذوذ)</t>
+        </is>
+      </c>
+      <c r="E269" s="7" t="inlineStr">
+        <is>
+          <t>شذوذ الأمطار السنوي كنسبة مئوية من خط الأساس المناخي 1991–2020 (فرق نسبي مئوي).</t>
+        </is>
+      </c>
+      <c r="F269" s="16" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="G269" s="32" t="inlineStr">
+        <is>
+          <t>خريطة الشذوذ النسبي المئوي للأمطار مقارنة بخط أساس 1991–2020 (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="270" ht="24" customHeight="1">
+      <c r="A270" s="8" t="n">
+        <v>269</v>
+      </c>
+      <c r="B270" s="10" t="inlineStr">
+        <is>
+          <t>R_AnomWin</t>
+        </is>
+      </c>
+      <c r="C270" s="29" t="inlineStr">
+        <is>
+          <t>R_Anom_Winter</t>
+        </is>
+      </c>
+      <c r="D270" s="18" t="inlineStr">
+        <is>
+          <t>18_Trends_And_Anomalies (الاتجاهات والشذوذ)</t>
+        </is>
+      </c>
+      <c r="E270" s="12" t="inlineStr">
+        <is>
+          <t>شذوذ أمطار فصل الشتاء المطلق مقارنة بأمطار شتاء خط الأساس المناخي 1991–2020.</t>
+        </is>
+      </c>
+      <c r="F270" s="19" t="inlineStr">
+        <is>
+          <t>ملم (mm)</t>
+        </is>
+      </c>
+      <c r="G270" s="30" t="inlineStr">
+        <is>
+          <t>خريطة شذوذ أمطار الشتاء مقارنة بخط أساس 1991–2020 (ملم)</t>
+        </is>
+      </c>
+    </row>
+    <row r="271" ht="24" customHeight="1">
+      <c r="A271" s="3" t="n">
+        <v>270</v>
+      </c>
+      <c r="B271" s="5" t="inlineStr">
+        <is>
           <t>R_AnomWPct</t>
         </is>
       </c>
-      <c r="C260" s="29" t="inlineStr">
+      <c r="C271" s="31" t="inlineStr">
         <is>
           <t>R_Anom_Winter_Pct</t>
         </is>
       </c>
-      <c r="D260" s="18" t="inlineStr">
+      <c r="D271" s="15" t="inlineStr">
         <is>
           <t>18_Trends_And_Anomalies (الاتجاهات والشذوذ)</t>
         </is>
       </c>
-      <c r="E260" s="12" t="inlineStr">
+      <c r="E271" s="7" t="inlineStr">
         <is>
           <t>شذوذ أمطار فصل الشتاء كنسبة مئوية مقارنة بأمطار شتاء خط الأساس المناخي 1991–2020.</t>
         </is>
       </c>
-      <c r="F260" s="19" t="inlineStr">
+      <c r="F271" s="16" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="G260" s="30" t="inlineStr">
+      <c r="G271" s="32" t="inlineStr">
         <is>
           <t>خريطة الشذوذ النسبي المئوي لأمطار الشتاء مقارنة بخط أساس 1991–2020 (%)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G260"/>
+  <autoFilter ref="A1:G271"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10891,7 +11276,7 @@
         </is>
       </c>
       <c r="F2" s="8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G2" s="19" t="inlineStr">
         <is>
@@ -10971,7 +11356,7 @@
         </is>
       </c>
       <c r="F4" s="8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G4" s="19" t="inlineStr">
         <is>
@@ -11011,7 +11396,7 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G5" s="16" t="inlineStr">
         <is>
@@ -11051,7 +11436,7 @@
         </is>
       </c>
       <c r="F6" s="8" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G6" s="19" t="inlineStr">
         <is>
@@ -11091,7 +11476,7 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G7" s="16" t="inlineStr">
         <is>
@@ -11131,7 +11516,7 @@
         </is>
       </c>
       <c r="F8" s="8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G8" s="19" t="inlineStr">
         <is>
@@ -11591,7 +11976,7 @@
         </is>
       </c>
       <c r="F20" s="34" t="n">
-        <v>247</v>
+        <v>254</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Climate_Atlas_Fields_Dictionary_AR_EN_Units.xlsx
+++ b/docs/Climate_Atlas_Fields_Dictionary_AR_EN_Units.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Modules_18_Summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Climate_Fields'!$A$1:$G$271</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Climate_Fields'!$A$1:$G$280</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Modules_18_Summary'!$A$1:$H$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1669,7 +1669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G271"/>
+  <dimension ref="A1:G280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2395,22 +2395,22 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>T_MaxSumMo</t>
+          <t>T_SeaRng</t>
         </is>
       </c>
       <c r="C21" s="31" t="inlineStr">
         <is>
-          <t>T_Max_Summer_Month_Mean</t>
+          <t>T_Seasonal_Range</t>
         </is>
       </c>
       <c r="D21" s="15" t="inlineStr">
         <is>
-          <t>01_Temperature (درجة الحرارة)</t>
+          <t>01_Temperature (درجات الحرارة)</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>متوسط درجة الحرارة لأدفأ شهور فصل الصيف (أعلى متوسط شهري مسجل في الصيف).</t>
+          <t>المدى الفصلي لدرجة الحرارة (الفارق بين أدفأ فصول السنة وأبردها).</t>
         </is>
       </c>
       <c r="F21" s="16" t="inlineStr">
@@ -2420,7 +2420,7 @@
       </c>
       <c r="G21" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط أدفأ شهور فصل الصيف (°C)</t>
+          <t>خريطة المدى الفصلي لدرجة الحرارة (°C)</t>
         </is>
       </c>
     </row>
@@ -2430,12 +2430,12 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>T_MinWinMo</t>
+          <t>T_MaxSumMo</t>
         </is>
       </c>
       <c r="C22" s="29" t="inlineStr">
         <is>
-          <t>T_Min_Winter_Month_Mean</t>
+          <t>T_Max_Summer_Month_Mean</t>
         </is>
       </c>
       <c r="D22" s="18" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
-          <t>متوسط درجة الحرارة لأبرد شهور فصل الشتاء (أدنى متوسط شهري مسجل في الشتاء).</t>
+          <t>متوسط درجة الحرارة لأدفأ شهور فصل الصيف (أعلى متوسط شهري مسجل في الصيف).</t>
         </is>
       </c>
       <c r="F22" s="19" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="G22" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط أبرد شهور فصل الشتاء (°C)</t>
+          <t>خريطة متوسط أدفأ شهور فصل الصيف (°C)</t>
         </is>
       </c>
     </row>
@@ -2465,12 +2465,12 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>T_MaxMean</t>
+          <t>T_MinWinMo</t>
         </is>
       </c>
       <c r="C23" s="31" t="inlineStr">
         <is>
-          <t>T_Annual_Max_Mean</t>
+          <t>T_Min_Winter_Month_Mean</t>
         </is>
       </c>
       <c r="D23" s="15" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>المتوسط السنوي للنهايات العظمى اليومية لدرجة حرارة الهواء (T2M_MAX).</t>
+          <t>متوسط درجة الحرارة لأبرد شهور فصل الشتاء (أدنى متوسط شهري مسجل في الشتاء).</t>
         </is>
       </c>
       <c r="F23" s="16" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="G23" s="32" t="inlineStr">
         <is>
-          <t>خريطة المتوسط السنوي للنهايات العظمى لدرجة الحرارة (°C)</t>
+          <t>خريطة متوسط أبرد شهور فصل الشتاء (°C)</t>
         </is>
       </c>
     </row>
@@ -2500,12 +2500,12 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>T_MinMean</t>
+          <t>T_MaxMean</t>
         </is>
       </c>
       <c r="C24" s="29" t="inlineStr">
         <is>
-          <t>T_Annual_Min_Mean</t>
+          <t>T_Annual_Max_Mean</t>
         </is>
       </c>
       <c r="D24" s="18" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>المتوسط السنوي للنهايات الصغرى اليومية لدرجة حرارة الهواء (T2M_MIN).</t>
+          <t>المتوسط السنوي للنهايات العظمى اليومية لدرجة حرارة الهواء (T2M_MAX).</t>
         </is>
       </c>
       <c r="F24" s="19" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="G24" s="30" t="inlineStr">
         <is>
-          <t>خريطة المتوسط السنوي للنهايات الصغرى لدرجة الحرارة (°C)</t>
+          <t>خريطة المتوسط السنوي للنهايات العظمى لدرجة الحرارة (°C)</t>
         </is>
       </c>
     </row>
@@ -2535,12 +2535,12 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>T_JanMean</t>
+          <t>T_MinMean</t>
         </is>
       </c>
       <c r="C25" s="31" t="inlineStr">
         <is>
-          <t>T_January_Mean</t>
+          <t>T_Annual_Min_Mean</t>
         </is>
       </c>
       <c r="D25" s="15" t="inlineStr">
@@ -2550,7 +2550,7 @@
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>المتوسط الحسابي لدرجة حرارة الهواء عند ارتفاع 2 متر لشهر يناير عبر فترة الرصد 1996–2025.</t>
+          <t>المتوسط السنوي للنهايات الصغرى اليومية لدرجة حرارة الهواء (T2M_MIN).</t>
         </is>
       </c>
       <c r="F25" s="16" t="inlineStr">
@@ -2560,7 +2560,7 @@
       </c>
       <c r="G25" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط درجة الحرارة لشهر يناير (°C)</t>
+          <t>خريطة المتوسط السنوي للنهايات الصغرى لدرجة الحرارة (°C)</t>
         </is>
       </c>
     </row>
@@ -2570,12 +2570,12 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>T_FebMean</t>
+          <t>T_JanMean</t>
         </is>
       </c>
       <c r="C26" s="29" t="inlineStr">
         <is>
-          <t>T_February_Mean</t>
+          <t>T_January_Mean</t>
         </is>
       </c>
       <c r="D26" s="18" t="inlineStr">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
-          <t>المتوسط الحسابي لدرجة حرارة الهواء عند ارتفاع 2 متر لشهر فبراير عبر فترة الرصد 1996–2025.</t>
+          <t>المتوسط الحسابي لدرجة حرارة الهواء عند ارتفاع 2 متر لشهر يناير عبر فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F26" s="19" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="G26" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط درجة الحرارة لشهر فبراير (°C)</t>
+          <t>خريطة متوسط درجة الحرارة لشهر يناير (°C)</t>
         </is>
       </c>
     </row>
@@ -2605,12 +2605,12 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>T_MarMean</t>
+          <t>T_FebMean</t>
         </is>
       </c>
       <c r="C27" s="31" t="inlineStr">
         <is>
-          <t>T_March_Mean</t>
+          <t>T_February_Mean</t>
         </is>
       </c>
       <c r="D27" s="15" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>المتوسط الحسابي لدرجة حرارة الهواء عند ارتفاع 2 متر لشهر مارس عبر فترة الرصد 1996–2025.</t>
+          <t>المتوسط الحسابي لدرجة حرارة الهواء عند ارتفاع 2 متر لشهر فبراير عبر فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F27" s="16" t="inlineStr">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="G27" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط درجة الحرارة لشهر مارس (°C)</t>
+          <t>خريطة متوسط درجة الحرارة لشهر فبراير (°C)</t>
         </is>
       </c>
     </row>
@@ -2640,12 +2640,12 @@
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>T_AprMean</t>
+          <t>T_MarMean</t>
         </is>
       </c>
       <c r="C28" s="29" t="inlineStr">
         <is>
-          <t>T_April_Mean</t>
+          <t>T_March_Mean</t>
         </is>
       </c>
       <c r="D28" s="18" t="inlineStr">
@@ -2655,7 +2655,7 @@
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>المتوسط الحسابي لدرجة حرارة الهواء عند ارتفاع 2 متر لشهر أبريل عبر فترة الرصد 1996–2025.</t>
+          <t>المتوسط الحسابي لدرجة حرارة الهواء عند ارتفاع 2 متر لشهر مارس عبر فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F28" s="19" t="inlineStr">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="G28" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط درجة الحرارة لشهر أبريل (°C)</t>
+          <t>خريطة متوسط درجة الحرارة لشهر مارس (°C)</t>
         </is>
       </c>
     </row>
@@ -2675,12 +2675,12 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>T_MayMean</t>
+          <t>T_AprMean</t>
         </is>
       </c>
       <c r="C29" s="31" t="inlineStr">
         <is>
-          <t>T_May_Mean</t>
+          <t>T_April_Mean</t>
         </is>
       </c>
       <c r="D29" s="15" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>المتوسط الحسابي لدرجة حرارة الهواء عند ارتفاع 2 متر لشهر مايو عبر فترة الرصد 1996–2025.</t>
+          <t>المتوسط الحسابي لدرجة حرارة الهواء عند ارتفاع 2 متر لشهر أبريل عبر فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F29" s="16" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="G29" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط درجة الحرارة لشهر مايو (°C)</t>
+          <t>خريطة متوسط درجة الحرارة لشهر أبريل (°C)</t>
         </is>
       </c>
     </row>
@@ -2710,12 +2710,12 @@
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>T_JunMean</t>
+          <t>T_MayMean</t>
         </is>
       </c>
       <c r="C30" s="29" t="inlineStr">
         <is>
-          <t>T_June_Mean</t>
+          <t>T_May_Mean</t>
         </is>
       </c>
       <c r="D30" s="18" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
-          <t>المتوسط الحسابي لدرجة حرارة الهواء عند ارتفاع 2 متر لشهر يونيو عبر فترة الرصد 1996–2025.</t>
+          <t>المتوسط الحسابي لدرجة حرارة الهواء عند ارتفاع 2 متر لشهر مايو عبر فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F30" s="19" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="G30" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط درجة الحرارة لشهر يونيو (°C)</t>
+          <t>خريطة متوسط درجة الحرارة لشهر مايو (°C)</t>
         </is>
       </c>
     </row>
@@ -2745,12 +2745,12 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>T_JulMean</t>
+          <t>T_JunMean</t>
         </is>
       </c>
       <c r="C31" s="31" t="inlineStr">
         <is>
-          <t>T_July_Mean</t>
+          <t>T_June_Mean</t>
         </is>
       </c>
       <c r="D31" s="15" t="inlineStr">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>المتوسط الحسابي لدرجة حرارة الهواء عند ارتفاع 2 متر لشهر يوليو عبر فترة الرصد 1996–2025.</t>
+          <t>المتوسط الحسابي لدرجة حرارة الهواء عند ارتفاع 2 متر لشهر يونيو عبر فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F31" s="16" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="G31" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط درجة الحرارة لشهر يوليو (°C)</t>
+          <t>خريطة متوسط درجة الحرارة لشهر يونيو (°C)</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>T_AugMean</t>
+          <t>T_JulMean</t>
         </is>
       </c>
       <c r="C32" s="29" t="inlineStr">
         <is>
-          <t>T_August_Mean</t>
+          <t>T_July_Mean</t>
         </is>
       </c>
       <c r="D32" s="18" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>المتوسط الحسابي لدرجة حرارة الهواء عند ارتفاع 2 متر لشهر أغسطس عبر فترة الرصد 1996–2025.</t>
+          <t>المتوسط الحسابي لدرجة حرارة الهواء عند ارتفاع 2 متر لشهر يوليو عبر فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F32" s="19" t="inlineStr">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="G32" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط درجة الحرارة لشهر أغسطس (°C)</t>
+          <t>خريطة متوسط درجة الحرارة لشهر يوليو (°C)</t>
         </is>
       </c>
     </row>
@@ -2815,12 +2815,12 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>T_SepMean</t>
+          <t>T_AugMean</t>
         </is>
       </c>
       <c r="C33" s="31" t="inlineStr">
         <is>
-          <t>T_September_Mean</t>
+          <t>T_August_Mean</t>
         </is>
       </c>
       <c r="D33" s="15" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>المتوسط الحسابي لدرجة حرارة الهواء عند ارتفاع 2 متر لشهر سبتمبر عبر فترة الرصد 1996–2025.</t>
+          <t>المتوسط الحسابي لدرجة حرارة الهواء عند ارتفاع 2 متر لشهر أغسطس عبر فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F33" s="16" t="inlineStr">
@@ -2840,7 +2840,7 @@
       </c>
       <c r="G33" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط درجة الحرارة لشهر سبتمبر (°C)</t>
+          <t>خريطة متوسط درجة الحرارة لشهر أغسطس (°C)</t>
         </is>
       </c>
     </row>
@@ -2850,12 +2850,12 @@
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>T_OctMean</t>
+          <t>T_SepMean</t>
         </is>
       </c>
       <c r="C34" s="29" t="inlineStr">
         <is>
-          <t>T_October_Mean</t>
+          <t>T_September_Mean</t>
         </is>
       </c>
       <c r="D34" s="18" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>المتوسط الحسابي لدرجة حرارة الهواء عند ارتفاع 2 متر لشهر أكتوبر عبر فترة الرصد 1996–2025.</t>
+          <t>المتوسط الحسابي لدرجة حرارة الهواء عند ارتفاع 2 متر لشهر سبتمبر عبر فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F34" s="19" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="G34" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط درجة الحرارة لشهر أكتوبر (°C)</t>
+          <t>خريطة متوسط درجة الحرارة لشهر سبتمبر (°C)</t>
         </is>
       </c>
     </row>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>T_NovMean</t>
+          <t>T_OctMean</t>
         </is>
       </c>
       <c r="C35" s="31" t="inlineStr">
         <is>
-          <t>T_November_Mean</t>
+          <t>T_October_Mean</t>
         </is>
       </c>
       <c r="D35" s="15" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>المتوسط الحسابي لدرجة حرارة الهواء عند ارتفاع 2 متر لشهر نوفمبر عبر فترة الرصد 1996–2025.</t>
+          <t>المتوسط الحسابي لدرجة حرارة الهواء عند ارتفاع 2 متر لشهر أكتوبر عبر فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F35" s="16" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="G35" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط درجة الحرارة لشهر نوفمبر (°C)</t>
+          <t>خريطة متوسط درجة الحرارة لشهر أكتوبر (°C)</t>
         </is>
       </c>
     </row>
@@ -2920,12 +2920,12 @@
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>T_DecMean</t>
+          <t>T_NovMean</t>
         </is>
       </c>
       <c r="C36" s="29" t="inlineStr">
         <is>
-          <t>T_December_Mean</t>
+          <t>T_November_Mean</t>
         </is>
       </c>
       <c r="D36" s="18" t="inlineStr">
@@ -2935,7 +2935,7 @@
       </c>
       <c r="E36" s="12" t="inlineStr">
         <is>
-          <t>المتوسط الحسابي لدرجة حرارة الهواء عند ارتفاع 2 متر لشهر ديسمبر عبر فترة الرصد 1996–2025.</t>
+          <t>المتوسط الحسابي لدرجة حرارة الهواء عند ارتفاع 2 متر لشهر نوفمبر عبر فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F36" s="19" t="inlineStr">
@@ -2945,7 +2945,7 @@
       </c>
       <c r="G36" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط درجة الحرارة لشهر ديسمبر (°C)</t>
+          <t>خريطة متوسط درجة الحرارة لشهر نوفمبر (°C)</t>
         </is>
       </c>
     </row>
@@ -2955,22 +2955,22 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>HI_AnnMean</t>
+          <t>T_DecMean</t>
         </is>
       </c>
       <c r="C37" s="31" t="inlineStr">
         <is>
-          <t>HI_Annual_Mean</t>
+          <t>T_December_Mean</t>
         </is>
       </c>
       <c r="D37" s="15" t="inlineStr">
         <is>
-          <t>11_Heat_Index (مؤشر الحرارة)</t>
+          <t>01_Temperature (درجة الحرارة)</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>المتوسط السنوي لمؤشر الحرارة المحسوسة المحسوب بمعادلة روتفوش وستيدمان للحرارة والرطوبة.</t>
+          <t>المتوسط الحسابي لدرجة حرارة الهواء عند ارتفاع 2 متر لشهر ديسمبر عبر فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F37" s="16" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="G37" s="32" t="inlineStr">
         <is>
-          <t>خريطة المتوسط السنوي لمؤشر الحرارة المحسوسة (°C)</t>
+          <t>خريطة متوسط درجة الحرارة لشهر ديسمبر (°C)</t>
         </is>
       </c>
     </row>
@@ -2990,12 +2990,12 @@
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>HI_SumMean</t>
+          <t>HI_AnnMean</t>
         </is>
       </c>
       <c r="C38" s="29" t="inlineStr">
         <is>
-          <t>HI_Summer_Mean</t>
+          <t>HI_Annual_Mean</t>
         </is>
       </c>
       <c r="D38" s="18" t="inlineStr">
@@ -3005,7 +3005,7 @@
       </c>
       <c r="E38" s="12" t="inlineStr">
         <is>
-          <t>متوسط مؤشر الحرارة المحسوسة خلال فصل الصيف (مقياس الإجهاد الحراري الفعلي).</t>
+          <t>المتوسط السنوي لمؤشر الحرارة المحسوسة المحسوب بمعادلة روتفوش وستيدمان للحرارة والرطوبة.</t>
         </is>
       </c>
       <c r="F38" s="19" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="G38" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط مؤشر الحرارة المحسوسة خلال فصل الصيف (°C)</t>
+          <t>خريطة المتوسط السنوي لمؤشر الحرارة المحسوسة (°C)</t>
         </is>
       </c>
     </row>
@@ -3025,12 +3025,12 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>HI_WinMean</t>
+          <t>HI_SumMean</t>
         </is>
       </c>
       <c r="C39" s="31" t="inlineStr">
         <is>
-          <t>HI_Winter_Mean</t>
+          <t>HI_Summer_Mean</t>
         </is>
       </c>
       <c r="D39" s="15" t="inlineStr">
@@ -3040,7 +3040,7 @@
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>متوسط مؤشر الحرارة الظاهرية/الهيوميدكس خلال فصل الشتاء في الأجواء الباردة والرطبة.</t>
+          <t>متوسط مؤشر الحرارة المحسوسة خلال فصل الصيف (مقياس الإجهاد الحراري الفعلي).</t>
         </is>
       </c>
       <c r="F39" s="16" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="G39" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط درجة الحرارة المحسوسة خلال فصل الشتاء (°C)</t>
+          <t>خريطة متوسط مؤشر الحرارة المحسوسة خلال فصل الصيف (°C)</t>
         </is>
       </c>
     </row>
@@ -3060,12 +3060,12 @@
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>HI_AnRng</t>
+          <t>HI_WinMean</t>
         </is>
       </c>
       <c r="C40" s="29" t="inlineStr">
         <is>
-          <t>HI_Annual_Range</t>
+          <t>HI_Winter_Mean</t>
         </is>
       </c>
       <c r="D40" s="18" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
-          <t>المدى السنوي لمؤشر الحرارة المحسوسة (الفارق بين أعلى شهر إجهاد حراري وأدنى شهر).</t>
+          <t>متوسط مؤشر الحرارة الظاهرية/الهيوميدكس خلال فصل الشتاء في الأجواء الباردة والرطبة.</t>
         </is>
       </c>
       <c r="F40" s="19" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="G40" s="30" t="inlineStr">
         <is>
-          <t>خريطة المدى السنوي لمؤشر الحرارة المحسوسة (°C)</t>
+          <t>خريطة متوسط درجة الحرارة المحسوسة خلال فصل الشتاء (°C)</t>
         </is>
       </c>
     </row>
@@ -3095,12 +3095,12 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>WBGT_SuMn</t>
+          <t>HI_AnRng</t>
         </is>
       </c>
       <c r="C41" s="31" t="inlineStr">
         <is>
-          <t>WBGT_Summer_Mean</t>
+          <t>HI_Annual_Range</t>
         </is>
       </c>
       <c r="D41" s="15" t="inlineStr">
@@ -3110,7 +3110,7 @@
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>متوسط درجة حرارة البصيلة الرطبة الكروية الصيفي في الظل (معيار ISO 7243 للإجهاد المهني والرياضي).</t>
+          <t>المدى السنوي لمؤشر الحرارة المحسوسة (الفارق بين أعلى شهر إجهاد حراري وأدنى شهر).</t>
         </is>
       </c>
       <c r="F41" s="16" t="inlineStr">
@@ -3120,7 +3120,7 @@
       </c>
       <c r="G41" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط مؤشر الإجهاد الحراري الصيفي (WBGT) (°C)</t>
+          <t>خريطة المدى السنوي لمؤشر الحرارة المحسوسة (°C)</t>
         </is>
       </c>
     </row>
@@ -3130,22 +3130,22 @@
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>Td_AnnMean</t>
+          <t>WBGT_SuMn</t>
         </is>
       </c>
       <c r="C42" s="29" t="inlineStr">
         <is>
-          <t>Td_Annual_Mean</t>
+          <t>WBGT_Summer_Mean</t>
         </is>
       </c>
       <c r="D42" s="18" t="inlineStr">
         <is>
-          <t>07_Dew_Point (نقطة الندى)</t>
+          <t>11_Heat_Index (مؤشر الحرارة)</t>
         </is>
       </c>
       <c r="E42" s="12" t="inlineStr">
         <is>
-          <t>المتوسط الحسابي السنوي لدرجة حرارة نقطة الندى عند ارتفاع 2 متر.</t>
+          <t>متوسط درجة حرارة البصيلة الرطبة الكروية الصيفي في الظل (معيار ISO 7243 للإجهاد المهني والرياضي).</t>
         </is>
       </c>
       <c r="F42" s="19" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="G42" s="30" t="inlineStr">
         <is>
-          <t>خريطة المتوسط السنوي لدرجة حرارة نقطة الندى (°C)</t>
+          <t>خريطة متوسط مؤشر الإجهاد الحراري الصيفي (WBGT) (°C)</t>
         </is>
       </c>
     </row>
@@ -3165,22 +3165,22 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Td_MonMean</t>
+          <t>Td_AnnMean</t>
         </is>
       </c>
       <c r="C43" s="31" t="inlineStr">
         <is>
-          <t>Td_Month_Mean</t>
+          <t>Td_Annual_Mean</t>
         </is>
       </c>
       <c r="D43" s="15" t="inlineStr">
         <is>
-          <t>07_Dew_Point (درجة حرارة نقطة الندى)</t>
+          <t>07_Dew_Point (نقطة الندى)</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>المتوسط الشهري لدرجة حرارة نقطة الندى عند ارتفاع 2 متر (متوسط الـ 12 شهراً).</t>
+          <t>المتوسط الحسابي السنوي لدرجة حرارة نقطة الندى عند ارتفاع 2 متر.</t>
         </is>
       </c>
       <c r="F43" s="16" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="G43" s="32" t="inlineStr">
         <is>
-          <t>خريطة المتوسط الشهري لنقطة الندى (°C)</t>
+          <t>خريطة المتوسط السنوي لدرجة حرارة نقطة الندى (°C)</t>
         </is>
       </c>
     </row>
@@ -3200,22 +3200,22 @@
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>Td_WinMean</t>
+          <t>Td_MonMean</t>
         </is>
       </c>
       <c r="C44" s="29" t="inlineStr">
         <is>
-          <t>Td_Winter_Mean</t>
+          <t>Td_Month_Mean</t>
         </is>
       </c>
       <c r="D44" s="18" t="inlineStr">
         <is>
-          <t>07_Dew_Point (نقطة الندى)</t>
+          <t>07_Dew_Point (درجة حرارة نقطة الندى)</t>
         </is>
       </c>
       <c r="E44" s="12" t="inlineStr">
         <is>
-          <t>متوسط درجة حرارة نقطة الندى خلال فصل الشتاء الأرصادي (DJF).</t>
+          <t>المتوسط الشهري لدرجة حرارة نقطة الندى عند ارتفاع 2 متر (متوسط الـ 12 شهراً).</t>
         </is>
       </c>
       <c r="F44" s="19" t="inlineStr">
@@ -3225,7 +3225,7 @@
       </c>
       <c r="G44" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط درجة حرارة نقطة الندى خلال فصل الشتاء (°C)</t>
+          <t>خريطة المتوسط الشهري لنقطة الندى (°C)</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Td_SprMean</t>
+          <t>Td_WinMean</t>
         </is>
       </c>
       <c r="C45" s="31" t="inlineStr">
         <is>
-          <t>Td_Spring_Mean</t>
+          <t>Td_Winter_Mean</t>
         </is>
       </c>
       <c r="D45" s="15" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>متوسط درجة حرارة نقطة الندى خلال فصل الربيع الأرصادي (MAM).</t>
+          <t>متوسط درجة حرارة نقطة الندى خلال فصل الشتاء الأرصادي (DJF).</t>
         </is>
       </c>
       <c r="F45" s="16" t="inlineStr">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="G45" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط درجة حرارة نقطة الندى خلال فصل الربيع (°C)</t>
+          <t>خريطة متوسط درجة حرارة نقطة الندى خلال فصل الشتاء (°C)</t>
         </is>
       </c>
     </row>
@@ -3270,12 +3270,12 @@
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>Td_SumMean</t>
+          <t>Td_SprMean</t>
         </is>
       </c>
       <c r="C46" s="29" t="inlineStr">
         <is>
-          <t>Td_Summer_Mean</t>
+          <t>Td_Spring_Mean</t>
         </is>
       </c>
       <c r="D46" s="18" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="E46" s="12" t="inlineStr">
         <is>
-          <t>متوسط درجة حرارة نقطة الندى خلال فصل الصيف الأرصادي (JJA - مؤشر مباشر للرطوبة الخانقة والكتمة).</t>
+          <t>متوسط درجة حرارة نقطة الندى خلال فصل الربيع الأرصادي (MAM).</t>
         </is>
       </c>
       <c r="F46" s="19" t="inlineStr">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="G46" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط درجة حرارة نقطة الندى خلال فصل الصيف (°C)</t>
+          <t>خريطة متوسط درجة حرارة نقطة الندى خلال فصل الربيع (°C)</t>
         </is>
       </c>
     </row>
@@ -3305,12 +3305,12 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Td_AutMean</t>
+          <t>Td_SumMean</t>
         </is>
       </c>
       <c r="C47" s="31" t="inlineStr">
         <is>
-          <t>Td_Autumn_Mean</t>
+          <t>Td_Summer_Mean</t>
         </is>
       </c>
       <c r="D47" s="15" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>متوسط درجة حرارة نقطة الندى خلال فصل الخريف الأرصادي (SON).</t>
+          <t>متوسط درجة حرارة نقطة الندى خلال فصل الصيف الأرصادي (JJA - مؤشر مباشر للرطوبة الخانقة والكتمة).</t>
         </is>
       </c>
       <c r="F47" s="16" t="inlineStr">
@@ -3330,7 +3330,7 @@
       </c>
       <c r="G47" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط درجة حرارة نقطة الندى خلال فصل الخريف (°C)</t>
+          <t>خريطة متوسط درجة حرارة نقطة الندى خلال فصل الصيف (°C)</t>
         </is>
       </c>
     </row>
@@ -3340,12 +3340,12 @@
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>Td_AnnRng</t>
+          <t>Td_AutMean</t>
         </is>
       </c>
       <c r="C48" s="29" t="inlineStr">
         <is>
-          <t>Td_Annual_Range</t>
+          <t>Td_Autumn_Mean</t>
         </is>
       </c>
       <c r="D48" s="18" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="E48" s="12" t="inlineStr">
         <is>
-          <t>المدى السنوي لدرجة حرارة نقطة الندى (الفارق بين أعلى وأدنى متوسط شهري لنقطة الندى).</t>
+          <t>متوسط درجة حرارة نقطة الندى خلال فصل الخريف الأرصادي (SON).</t>
         </is>
       </c>
       <c r="F48" s="19" t="inlineStr">
@@ -3365,7 +3365,7 @@
       </c>
       <c r="G48" s="30" t="inlineStr">
         <is>
-          <t>خريطة المدى السنوي لدرجة حرارة نقطة الندى (°C)</t>
+          <t>خريطة متوسط درجة حرارة نقطة الندى خلال فصل الخريف (°C)</t>
         </is>
       </c>
     </row>
@@ -3375,12 +3375,12 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Td_JanMean</t>
+          <t>Td_AnnRng</t>
         </is>
       </c>
       <c r="C49" s="31" t="inlineStr">
         <is>
-          <t>Td_January_Mean</t>
+          <t>Td_Annual_Range</t>
         </is>
       </c>
       <c r="D49" s="15" t="inlineStr">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>متوسط درجة حرارة نقطة الندى عند ارتفاع 2 متر لشهر يناير.</t>
+          <t>المدى السنوي لدرجة حرارة نقطة الندى (الفارق بين أعلى وأدنى متوسط شهري لنقطة الندى).</t>
         </is>
       </c>
       <c r="F49" s="16" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="G49" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط درجة حرارة نقطة الندى لشهر يناير (°C)</t>
+          <t>خريطة المدى السنوي لدرجة حرارة نقطة الندى (°C)</t>
         </is>
       </c>
     </row>
@@ -3410,12 +3410,12 @@
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>Td_FebMean</t>
+          <t>Td_SeaRng</t>
         </is>
       </c>
       <c r="C50" s="29" t="inlineStr">
         <is>
-          <t>Td_February_Mean</t>
+          <t>Td_Seasonal_Range</t>
         </is>
       </c>
       <c r="D50" s="18" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="E50" s="12" t="inlineStr">
         <is>
-          <t>متوسط درجة حرارة نقطة الندى عند ارتفاع 2 متر لشهر فبراير.</t>
+          <t>المدى الفصلي لنقطة الندى (الفارق بين أعلى وأدنى فصول السنة).</t>
         </is>
       </c>
       <c r="F50" s="19" t="inlineStr">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="G50" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط درجة حرارة نقطة الندى لشهر فبراير (°C)</t>
+          <t>خريطة المدى الفصلي لنقطة الندى (°C)</t>
         </is>
       </c>
     </row>
@@ -3445,12 +3445,12 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Td_MarMean</t>
+          <t>Td_JanMean</t>
         </is>
       </c>
       <c r="C51" s="31" t="inlineStr">
         <is>
-          <t>Td_March_Mean</t>
+          <t>Td_January_Mean</t>
         </is>
       </c>
       <c r="D51" s="15" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>متوسط درجة حرارة نقطة الندى عند ارتفاع 2 متر لشهر مارس.</t>
+          <t>متوسط درجة حرارة نقطة الندى عند ارتفاع 2 متر لشهر يناير.</t>
         </is>
       </c>
       <c r="F51" s="16" t="inlineStr">
@@ -3470,7 +3470,7 @@
       </c>
       <c r="G51" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط درجة حرارة نقطة الندى لشهر مارس (°C)</t>
+          <t>خريطة متوسط درجة حرارة نقطة الندى لشهر يناير (°C)</t>
         </is>
       </c>
     </row>
@@ -3480,12 +3480,12 @@
       </c>
       <c r="B52" s="10" t="inlineStr">
         <is>
-          <t>Td_AprMean</t>
+          <t>Td_FebMean</t>
         </is>
       </c>
       <c r="C52" s="29" t="inlineStr">
         <is>
-          <t>Td_April_Mean</t>
+          <t>Td_February_Mean</t>
         </is>
       </c>
       <c r="D52" s="18" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="E52" s="12" t="inlineStr">
         <is>
-          <t>متوسط درجة حرارة نقطة الندى عند ارتفاع 2 متر لشهر أبريل.</t>
+          <t>متوسط درجة حرارة نقطة الندى عند ارتفاع 2 متر لشهر فبراير.</t>
         </is>
       </c>
       <c r="F52" s="19" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="G52" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط درجة حرارة نقطة الندى لشهر أبريل (°C)</t>
+          <t>خريطة متوسط درجة حرارة نقطة الندى لشهر فبراير (°C)</t>
         </is>
       </c>
     </row>
@@ -3515,12 +3515,12 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Td_MayMean</t>
+          <t>Td_MarMean</t>
         </is>
       </c>
       <c r="C53" s="31" t="inlineStr">
         <is>
-          <t>Td_May_Mean</t>
+          <t>Td_March_Mean</t>
         </is>
       </c>
       <c r="D53" s="15" t="inlineStr">
@@ -3530,7 +3530,7 @@
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>متوسط درجة حرارة نقطة الندى عند ارتفاع 2 متر لشهر مايو.</t>
+          <t>متوسط درجة حرارة نقطة الندى عند ارتفاع 2 متر لشهر مارس.</t>
         </is>
       </c>
       <c r="F53" s="16" t="inlineStr">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="G53" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط درجة حرارة نقطة الندى لشهر مايو (°C)</t>
+          <t>خريطة متوسط درجة حرارة نقطة الندى لشهر مارس (°C)</t>
         </is>
       </c>
     </row>
@@ -3550,12 +3550,12 @@
       </c>
       <c r="B54" s="10" t="inlineStr">
         <is>
-          <t>Td_JunMean</t>
+          <t>Td_AprMean</t>
         </is>
       </c>
       <c r="C54" s="29" t="inlineStr">
         <is>
-          <t>Td_June_Mean</t>
+          <t>Td_April_Mean</t>
         </is>
       </c>
       <c r="D54" s="18" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="E54" s="12" t="inlineStr">
         <is>
-          <t>متوسط درجة حرارة نقطة الندى عند ارتفاع 2 متر لشهر يونيو.</t>
+          <t>متوسط درجة حرارة نقطة الندى عند ارتفاع 2 متر لشهر أبريل.</t>
         </is>
       </c>
       <c r="F54" s="19" t="inlineStr">
@@ -3575,7 +3575,7 @@
       </c>
       <c r="G54" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط درجة حرارة نقطة الندى لشهر يونيو (°C)</t>
+          <t>خريطة متوسط درجة حرارة نقطة الندى لشهر أبريل (°C)</t>
         </is>
       </c>
     </row>
@@ -3585,12 +3585,12 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Td_JulMean</t>
+          <t>Td_MayMean</t>
         </is>
       </c>
       <c r="C55" s="31" t="inlineStr">
         <is>
-          <t>Td_July_Mean</t>
+          <t>Td_May_Mean</t>
         </is>
       </c>
       <c r="D55" s="15" t="inlineStr">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>متوسط درجة حرارة نقطة الندى عند ارتفاع 2 متر لشهر يوليو.</t>
+          <t>متوسط درجة حرارة نقطة الندى عند ارتفاع 2 متر لشهر مايو.</t>
         </is>
       </c>
       <c r="F55" s="16" t="inlineStr">
@@ -3610,7 +3610,7 @@
       </c>
       <c r="G55" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط درجة حرارة نقطة الندى لشهر يوليو (°C)</t>
+          <t>خريطة متوسط درجة حرارة نقطة الندى لشهر مايو (°C)</t>
         </is>
       </c>
     </row>
@@ -3620,12 +3620,12 @@
       </c>
       <c r="B56" s="10" t="inlineStr">
         <is>
-          <t>Td_AugMean</t>
+          <t>Td_JunMean</t>
         </is>
       </c>
       <c r="C56" s="29" t="inlineStr">
         <is>
-          <t>Td_August_Mean</t>
+          <t>Td_June_Mean</t>
         </is>
       </c>
       <c r="D56" s="18" t="inlineStr">
@@ -3635,7 +3635,7 @@
       </c>
       <c r="E56" s="12" t="inlineStr">
         <is>
-          <t>متوسط درجة حرارة نقطة الندى عند ارتفاع 2 متر لشهر أغسطس.</t>
+          <t>متوسط درجة حرارة نقطة الندى عند ارتفاع 2 متر لشهر يونيو.</t>
         </is>
       </c>
       <c r="F56" s="19" t="inlineStr">
@@ -3645,7 +3645,7 @@
       </c>
       <c r="G56" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط درجة حرارة نقطة الندى لشهر أغسطس (°C)</t>
+          <t>خريطة متوسط درجة حرارة نقطة الندى لشهر يونيو (°C)</t>
         </is>
       </c>
     </row>
@@ -3655,12 +3655,12 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Td_SepMean</t>
+          <t>Td_JulMean</t>
         </is>
       </c>
       <c r="C57" s="31" t="inlineStr">
         <is>
-          <t>Td_September_Mean</t>
+          <t>Td_July_Mean</t>
         </is>
       </c>
       <c r="D57" s="15" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
-          <t>متوسط درجة حرارة نقطة الندى عند ارتفاع 2 متر لشهر سبتمبر.</t>
+          <t>متوسط درجة حرارة نقطة الندى عند ارتفاع 2 متر لشهر يوليو.</t>
         </is>
       </c>
       <c r="F57" s="16" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="G57" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط درجة حرارة نقطة الندى لشهر سبتمبر (°C)</t>
+          <t>خريطة متوسط درجة حرارة نقطة الندى لشهر يوليو (°C)</t>
         </is>
       </c>
     </row>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="B58" s="10" t="inlineStr">
         <is>
-          <t>Td_OctMean</t>
+          <t>Td_AugMean</t>
         </is>
       </c>
       <c r="C58" s="29" t="inlineStr">
         <is>
-          <t>Td_October_Mean</t>
+          <t>Td_August_Mean</t>
         </is>
       </c>
       <c r="D58" s="18" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="E58" s="12" t="inlineStr">
         <is>
-          <t>متوسط درجة حرارة نقطة الندى عند ارتفاع 2 متر لشهر أكتوبر.</t>
+          <t>متوسط درجة حرارة نقطة الندى عند ارتفاع 2 متر لشهر أغسطس.</t>
         </is>
       </c>
       <c r="F58" s="19" t="inlineStr">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="G58" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط درجة حرارة نقطة الندى لشهر أكتوبر (°C)</t>
+          <t>خريطة متوسط درجة حرارة نقطة الندى لشهر أغسطس (°C)</t>
         </is>
       </c>
     </row>
@@ -3725,12 +3725,12 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>Td_NovMean</t>
+          <t>Td_SepMean</t>
         </is>
       </c>
       <c r="C59" s="31" t="inlineStr">
         <is>
-          <t>Td_November_Mean</t>
+          <t>Td_September_Mean</t>
         </is>
       </c>
       <c r="D59" s="15" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>متوسط درجة حرارة نقطة الندى عند ارتفاع 2 متر لشهر نوفمبر.</t>
+          <t>متوسط درجة حرارة نقطة الندى عند ارتفاع 2 متر لشهر سبتمبر.</t>
         </is>
       </c>
       <c r="F59" s="16" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="G59" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط درجة حرارة نقطة الندى لشهر نوفمبر (°C)</t>
+          <t>خريطة متوسط درجة حرارة نقطة الندى لشهر سبتمبر (°C)</t>
         </is>
       </c>
     </row>
@@ -3760,12 +3760,12 @@
       </c>
       <c r="B60" s="10" t="inlineStr">
         <is>
-          <t>Td_DecMean</t>
+          <t>Td_OctMean</t>
         </is>
       </c>
       <c r="C60" s="29" t="inlineStr">
         <is>
-          <t>Td_December_Mean</t>
+          <t>Td_October_Mean</t>
         </is>
       </c>
       <c r="D60" s="18" t="inlineStr">
@@ -3775,7 +3775,7 @@
       </c>
       <c r="E60" s="12" t="inlineStr">
         <is>
-          <t>متوسط درجة حرارة نقطة الندى عند ارتفاع 2 متر لشهر ديسمبر.</t>
+          <t>متوسط درجة حرارة نقطة الندى عند ارتفاع 2 متر لشهر أكتوبر.</t>
         </is>
       </c>
       <c r="F60" s="19" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="G60" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط درجة حرارة نقطة الندى لشهر ديسمبر (°C)</t>
+          <t>خريطة متوسط درجة حرارة نقطة الندى لشهر أكتوبر (°C)</t>
         </is>
       </c>
     </row>
@@ -3795,32 +3795,32 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>R_AnnMean</t>
+          <t>Td_NovMean</t>
         </is>
       </c>
       <c r="C61" s="31" t="inlineStr">
         <is>
-          <t>R_Annual_Mean</t>
+          <t>Td_November_Mean</t>
         </is>
       </c>
       <c r="D61" s="15" t="inlineStr">
         <is>
-          <t>02_Precipitation (الأمطار)</t>
+          <t>07_Dew_Point (نقطة الندى)</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>المتوسط السنوي لتساقط الأمطار (متوسط مجاميع السنين على مدار فترة الرصد 1996–2025).</t>
+          <t>متوسط درجة حرارة نقطة الندى عند ارتفاع 2 متر لشهر نوفمبر.</t>
         </is>
       </c>
       <c r="F61" s="16" t="inlineStr">
         <is>
-          <t>ملم (mm)</t>
+          <t>°C</t>
         </is>
       </c>
       <c r="G61" s="32" t="inlineStr">
         <is>
-          <t>خريطة المتوسط السنوي لتساقط الأمطار (ملم)</t>
+          <t>خريطة متوسط درجة حرارة نقطة الندى لشهر نوفمبر (°C)</t>
         </is>
       </c>
     </row>
@@ -3830,32 +3830,32 @@
       </c>
       <c r="B62" s="10" t="inlineStr">
         <is>
-          <t>R_MonMean</t>
+          <t>Td_DecMean</t>
         </is>
       </c>
       <c r="C62" s="29" t="inlineStr">
         <is>
-          <t>R_Month_Mean</t>
+          <t>Td_December_Mean</t>
         </is>
       </c>
       <c r="D62" s="18" t="inlineStr">
         <is>
-          <t>02_Precipitation (الأمطار)</t>
+          <t>07_Dew_Point (نقطة الندى)</t>
         </is>
       </c>
       <c r="E62" s="12" t="inlineStr">
         <is>
-          <t>المتوسط الشهري لتساقط الأمطار (المتوسط السنوي مقسوماً على 12 شهراً).</t>
+          <t>متوسط درجة حرارة نقطة الندى عند ارتفاع 2 متر لشهر ديسمبر.</t>
         </is>
       </c>
       <c r="F62" s="19" t="inlineStr">
         <is>
-          <t>ملم (mm)</t>
+          <t>°C</t>
         </is>
       </c>
       <c r="G62" s="30" t="inlineStr">
         <is>
-          <t>خريطة المتوسط الشهري لتساقط الأمطار (ملم)</t>
+          <t>خريطة متوسط درجة حرارة نقطة الندى لشهر ديسمبر (°C)</t>
         </is>
       </c>
     </row>
@@ -3865,12 +3865,12 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>R_AnnRng</t>
+          <t>R_AnnMean</t>
         </is>
       </c>
       <c r="C63" s="31" t="inlineStr">
         <is>
-          <t>R_Annual_Range</t>
+          <t>R_Annual_Mean</t>
         </is>
       </c>
       <c r="D63" s="15" t="inlineStr">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>المدى السنوي لتساقط الأمطار (الفارق بين أعلى شهر مطراً وأقل شهر مطراً في السنة).</t>
+          <t>المتوسط السنوي لتساقط الأمطار (متوسط مجاميع السنين على مدار فترة الرصد 1996–2025).</t>
         </is>
       </c>
       <c r="F63" s="16" t="inlineStr">
@@ -3890,7 +3890,7 @@
       </c>
       <c r="G63" s="32" t="inlineStr">
         <is>
-          <t>خريطة المدى السنوي لتساقط الأمطار (ملم)</t>
+          <t>خريطة المتوسط السنوي لتساقط الأمطار (ملم)</t>
         </is>
       </c>
     </row>
@@ -3900,12 +3900,12 @@
       </c>
       <c r="B64" s="10" t="inlineStr">
         <is>
-          <t>R_SeaRng</t>
+          <t>R_MonMean</t>
         </is>
       </c>
       <c r="C64" s="29" t="inlineStr">
         <is>
-          <t>R_Seasonal_Range</t>
+          <t>R_Month_Mean</t>
         </is>
       </c>
       <c r="D64" s="18" t="inlineStr">
@@ -3915,7 +3915,7 @@
       </c>
       <c r="E64" s="12" t="inlineStr">
         <is>
-          <t>المدى الفصلي لتساقط الأمطار (الفارق بين مجموع أعلى فصول السنة مطراً ومجموع أقلها مطراً).</t>
+          <t>المتوسط الشهري لتساقط الأمطار (المتوسط السنوي مقسوماً على 12 شهراً).</t>
         </is>
       </c>
       <c r="F64" s="19" t="inlineStr">
@@ -3925,7 +3925,7 @@
       </c>
       <c r="G64" s="30" t="inlineStr">
         <is>
-          <t>خريطة المدى الفصلي لتساقط الأمطار (ملم)</t>
+          <t>خريطة المتوسط الشهري لتساقط الأمطار (ملم)</t>
         </is>
       </c>
     </row>
@@ -3935,12 +3935,12 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>R_WinMean</t>
+          <t>R_AnnRng</t>
         </is>
       </c>
       <c r="C65" s="31" t="inlineStr">
         <is>
-          <t>R_Winter_Mean</t>
+          <t>R_Annual_Range</t>
         </is>
       </c>
       <c r="D65" s="15" t="inlineStr">
@@ -3950,17 +3950,17 @@
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>متوسط هطول الأمطار خلال فصل الشتاء (شهور ديسمبر، يناير، فبراير - DJF).</t>
+          <t>المدى السنوي لتساقط الأمطار (الفارق بين أعلى شهر مطراً وأقل شهر مطراً في السنة).</t>
         </is>
       </c>
       <c r="F65" s="16" t="inlineStr">
         <is>
-          <t>مم/فصل (mm/season)</t>
+          <t>ملم (mm)</t>
         </is>
       </c>
       <c r="G65" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط هطول الأمطار خلال فصل الشتاء (مم/فصل)</t>
+          <t>خريطة المدى السنوي لتساقط الأمطار (ملم)</t>
         </is>
       </c>
     </row>
@@ -3970,12 +3970,12 @@
       </c>
       <c r="B66" s="10" t="inlineStr">
         <is>
-          <t>R_SprMean</t>
+          <t>R_SeaRng</t>
         </is>
       </c>
       <c r="C66" s="29" t="inlineStr">
         <is>
-          <t>R_Spring_Mean</t>
+          <t>R_Seasonal_Range</t>
         </is>
       </c>
       <c r="D66" s="18" t="inlineStr">
@@ -3985,17 +3985,17 @@
       </c>
       <c r="E66" s="12" t="inlineStr">
         <is>
-          <t>متوسط هطول الأمطار خلال فصل الربيع (شهور مارس، أبريل، مايو - MAM).</t>
+          <t>المدى الفصلي لتساقط الأمطار (الفارق بين مجموع أعلى فصول السنة مطراً ومجموع أقلها مطراً).</t>
         </is>
       </c>
       <c r="F66" s="19" t="inlineStr">
         <is>
-          <t>مم/فصل (mm/season)</t>
+          <t>ملم (mm)</t>
         </is>
       </c>
       <c r="G66" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط هطول الأمطار خلال فصل الربيع (مم/فصل)</t>
+          <t>خريطة المدى الفصلي لتساقط الأمطار (ملم)</t>
         </is>
       </c>
     </row>
@@ -4005,12 +4005,12 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>R_SumMean</t>
+          <t>R_WinMean</t>
         </is>
       </c>
       <c r="C67" s="31" t="inlineStr">
         <is>
-          <t>R_Summer_Mean</t>
+          <t>R_Winter_Mean</t>
         </is>
       </c>
       <c r="D67" s="15" t="inlineStr">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>متوسط هطول الأمطار خلال فصل الصيف (شهور يونيو، يوليو، أغسطس - JJA).</t>
+          <t>متوسط هطول الأمطار خلال فصل الشتاء (شهور ديسمبر، يناير، فبراير - DJF).</t>
         </is>
       </c>
       <c r="F67" s="16" t="inlineStr">
@@ -4030,7 +4030,7 @@
       </c>
       <c r="G67" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط هطول الأمطار خلال فصل الصيف (مم/فصل)</t>
+          <t>خريطة متوسط هطول الأمطار خلال فصل الشتاء (مم/فصل)</t>
         </is>
       </c>
     </row>
@@ -4040,12 +4040,12 @@
       </c>
       <c r="B68" s="10" t="inlineStr">
         <is>
-          <t>R_AutMean</t>
+          <t>R_SprMean</t>
         </is>
       </c>
       <c r="C68" s="29" t="inlineStr">
         <is>
-          <t>R_Autumn_Mean</t>
+          <t>R_Spring_Mean</t>
         </is>
       </c>
       <c r="D68" s="18" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="E68" s="12" t="inlineStr">
         <is>
-          <t>متوسط هطول الأمطار خلال فصل الخريف (شهور سبتمبر، أكتوبر، نوفمبر - SON).</t>
+          <t>متوسط هطول الأمطار خلال فصل الربيع (شهور مارس، أبريل، مايو - MAM).</t>
         </is>
       </c>
       <c r="F68" s="19" t="inlineStr">
@@ -4065,7 +4065,7 @@
       </c>
       <c r="G68" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط هطول الأمطار خلال فصل الخريف (مم/فصل)</t>
+          <t>خريطة متوسط هطول الأمطار خلال فصل الربيع (مم/فصل)</t>
         </is>
       </c>
     </row>
@@ -4075,12 +4075,12 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>R_JanMean</t>
+          <t>R_SumMean</t>
         </is>
       </c>
       <c r="C69" s="31" t="inlineStr">
         <is>
-          <t>R_January_Mean</t>
+          <t>R_Summer_Mean</t>
         </is>
       </c>
       <c r="D69" s="15" t="inlineStr">
@@ -4090,17 +4090,17 @@
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>متوسط مجموع كميات الأمطار التراكمية لشهر يناير عبر سنوات فترة الرصد 1996–2025.</t>
+          <t>متوسط هطول الأمطار خلال فصل الصيف (شهور يونيو، يوليو، أغسطس - JJA).</t>
         </is>
       </c>
       <c r="F69" s="16" t="inlineStr">
         <is>
-          <t>ملم/شهر (mm/month)</t>
+          <t>مم/فصل (mm/season)</t>
         </is>
       </c>
       <c r="G69" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط مجموع أمطار شهر يناير (ملم/شهر)</t>
+          <t>خريطة متوسط هطول الأمطار خلال فصل الصيف (مم/فصل)</t>
         </is>
       </c>
     </row>
@@ -4110,12 +4110,12 @@
       </c>
       <c r="B70" s="10" t="inlineStr">
         <is>
-          <t>R_FebMean</t>
+          <t>R_AutMean</t>
         </is>
       </c>
       <c r="C70" s="29" t="inlineStr">
         <is>
-          <t>R_February_Mean</t>
+          <t>R_Autumn_Mean</t>
         </is>
       </c>
       <c r="D70" s="18" t="inlineStr">
@@ -4125,17 +4125,17 @@
       </c>
       <c r="E70" s="12" t="inlineStr">
         <is>
-          <t>متوسط مجموع كميات الأمطار التراكمية لشهر فبراير عبر سنوات فترة الرصد 1996–2025.</t>
+          <t>متوسط هطول الأمطار خلال فصل الخريف (شهور سبتمبر، أكتوبر، نوفمبر - SON).</t>
         </is>
       </c>
       <c r="F70" s="19" t="inlineStr">
         <is>
-          <t>ملم/شهر (mm/month)</t>
+          <t>مم/فصل (mm/season)</t>
         </is>
       </c>
       <c r="G70" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط مجموع أمطار شهر فبراير (ملم/شهر)</t>
+          <t>خريطة متوسط هطول الأمطار خلال فصل الخريف (مم/فصل)</t>
         </is>
       </c>
     </row>
@@ -4145,12 +4145,12 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>R_MarMean</t>
+          <t>R_JanMean</t>
         </is>
       </c>
       <c r="C71" s="31" t="inlineStr">
         <is>
-          <t>R_March_Mean</t>
+          <t>R_January_Mean</t>
         </is>
       </c>
       <c r="D71" s="15" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>متوسط مجموع كميات الأمطار التراكمية لشهر مارس عبر سنوات فترة الرصد 1996–2025.</t>
+          <t>متوسط مجموع كميات الأمطار التراكمية لشهر يناير عبر سنوات فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F71" s="16" t="inlineStr">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="G71" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط مجموع أمطار شهر مارس (ملم/شهر)</t>
+          <t>خريطة متوسط مجموع أمطار شهر يناير (ملم/شهر)</t>
         </is>
       </c>
     </row>
@@ -4180,12 +4180,12 @@
       </c>
       <c r="B72" s="10" t="inlineStr">
         <is>
-          <t>R_AprMean</t>
+          <t>R_FebMean</t>
         </is>
       </c>
       <c r="C72" s="29" t="inlineStr">
         <is>
-          <t>R_April_Mean</t>
+          <t>R_February_Mean</t>
         </is>
       </c>
       <c r="D72" s="18" t="inlineStr">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="E72" s="12" t="inlineStr">
         <is>
-          <t>متوسط مجموع كميات الأمطار التراكمية لشهر أبريل عبر سنوات فترة الرصد 1996–2025.</t>
+          <t>متوسط مجموع كميات الأمطار التراكمية لشهر فبراير عبر سنوات فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F72" s="19" t="inlineStr">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="G72" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط مجموع أمطار شهر أبريل (ملم/شهر)</t>
+          <t>خريطة متوسط مجموع أمطار شهر فبراير (ملم/شهر)</t>
         </is>
       </c>
     </row>
@@ -4215,12 +4215,12 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>R_MayMean</t>
+          <t>R_MarMean</t>
         </is>
       </c>
       <c r="C73" s="31" t="inlineStr">
         <is>
-          <t>R_May_Mean</t>
+          <t>R_March_Mean</t>
         </is>
       </c>
       <c r="D73" s="15" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>متوسط مجموع كميات الأمطار التراكمية لشهر مايو عبر سنوات فترة الرصد 1996–2025.</t>
+          <t>متوسط مجموع كميات الأمطار التراكمية لشهر مارس عبر سنوات فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F73" s="16" t="inlineStr">
@@ -4240,7 +4240,7 @@
       </c>
       <c r="G73" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط مجموع أمطار شهر مايو (ملم/شهر)</t>
+          <t>خريطة متوسط مجموع أمطار شهر مارس (ملم/شهر)</t>
         </is>
       </c>
     </row>
@@ -4250,12 +4250,12 @@
       </c>
       <c r="B74" s="10" t="inlineStr">
         <is>
-          <t>R_JunMean</t>
+          <t>R_AprMean</t>
         </is>
       </c>
       <c r="C74" s="29" t="inlineStr">
         <is>
-          <t>R_June_Mean</t>
+          <t>R_April_Mean</t>
         </is>
       </c>
       <c r="D74" s="18" t="inlineStr">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="E74" s="12" t="inlineStr">
         <is>
-          <t>متوسط مجموع كميات الأمطار التراكمية لشهر يونيو عبر سنوات فترة الرصد 1996–2025.</t>
+          <t>متوسط مجموع كميات الأمطار التراكمية لشهر أبريل عبر سنوات فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F74" s="19" t="inlineStr">
@@ -4275,7 +4275,7 @@
       </c>
       <c r="G74" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط مجموع أمطار شهر يونيو (ملم/شهر)</t>
+          <t>خريطة متوسط مجموع أمطار شهر أبريل (ملم/شهر)</t>
         </is>
       </c>
     </row>
@@ -4285,12 +4285,12 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>R_JulMean</t>
+          <t>R_MayMean</t>
         </is>
       </c>
       <c r="C75" s="31" t="inlineStr">
         <is>
-          <t>R_July_Mean</t>
+          <t>R_May_Mean</t>
         </is>
       </c>
       <c r="D75" s="15" t="inlineStr">
@@ -4300,7 +4300,7 @@
       </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
-          <t>متوسط مجموع كميات الأمطار التراكمية لشهر يوليو عبر سنوات فترة الرصد 1996–2025.</t>
+          <t>متوسط مجموع كميات الأمطار التراكمية لشهر مايو عبر سنوات فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F75" s="16" t="inlineStr">
@@ -4310,7 +4310,7 @@
       </c>
       <c r="G75" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط مجموع أمطار شهر يوليو (ملم/شهر)</t>
+          <t>خريطة متوسط مجموع أمطار شهر مايو (ملم/شهر)</t>
         </is>
       </c>
     </row>
@@ -4320,12 +4320,12 @@
       </c>
       <c r="B76" s="10" t="inlineStr">
         <is>
-          <t>R_AugMean</t>
+          <t>R_JunMean</t>
         </is>
       </c>
       <c r="C76" s="29" t="inlineStr">
         <is>
-          <t>R_August_Mean</t>
+          <t>R_June_Mean</t>
         </is>
       </c>
       <c r="D76" s="18" t="inlineStr">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="E76" s="12" t="inlineStr">
         <is>
-          <t>متوسط مجموع كميات الأمطار التراكمية لشهر أغسطس عبر سنوات فترة الرصد 1996–2025.</t>
+          <t>متوسط مجموع كميات الأمطار التراكمية لشهر يونيو عبر سنوات فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F76" s="19" t="inlineStr">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="G76" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط مجموع أمطار شهر أغسطس (ملم/شهر)</t>
+          <t>خريطة متوسط مجموع أمطار شهر يونيو (ملم/شهر)</t>
         </is>
       </c>
     </row>
@@ -4355,12 +4355,12 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>R_SepMean</t>
+          <t>R_JulMean</t>
         </is>
       </c>
       <c r="C77" s="31" t="inlineStr">
         <is>
-          <t>R_September_Mean</t>
+          <t>R_July_Mean</t>
         </is>
       </c>
       <c r="D77" s="15" t="inlineStr">
@@ -4370,7 +4370,7 @@
       </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
-          <t>متوسط مجموع كميات الأمطار التراكمية لشهر سبتمبر عبر سنوات فترة الرصد 1996–2025.</t>
+          <t>متوسط مجموع كميات الأمطار التراكمية لشهر يوليو عبر سنوات فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F77" s="16" t="inlineStr">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="G77" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط مجموع أمطار شهر سبتمبر (ملم/شهر)</t>
+          <t>خريطة متوسط مجموع أمطار شهر يوليو (ملم/شهر)</t>
         </is>
       </c>
     </row>
@@ -4390,12 +4390,12 @@
       </c>
       <c r="B78" s="10" t="inlineStr">
         <is>
-          <t>R_OctMean</t>
+          <t>R_AugMean</t>
         </is>
       </c>
       <c r="C78" s="29" t="inlineStr">
         <is>
-          <t>R_October_Mean</t>
+          <t>R_August_Mean</t>
         </is>
       </c>
       <c r="D78" s="18" t="inlineStr">
@@ -4405,7 +4405,7 @@
       </c>
       <c r="E78" s="12" t="inlineStr">
         <is>
-          <t>متوسط مجموع كميات الأمطار التراكمية لشهر أكتوبر عبر سنوات فترة الرصد 1996–2025.</t>
+          <t>متوسط مجموع كميات الأمطار التراكمية لشهر أغسطس عبر سنوات فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F78" s="19" t="inlineStr">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="G78" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط مجموع أمطار شهر أكتوبر (ملم/شهر)</t>
+          <t>خريطة متوسط مجموع أمطار شهر أغسطس (ملم/شهر)</t>
         </is>
       </c>
     </row>
@@ -4425,12 +4425,12 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>R_NovMean</t>
+          <t>R_SepMean</t>
         </is>
       </c>
       <c r="C79" s="31" t="inlineStr">
         <is>
-          <t>R_November_Mean</t>
+          <t>R_September_Mean</t>
         </is>
       </c>
       <c r="D79" s="15" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>متوسط مجموع كميات الأمطار التراكمية لشهر نوفمبر عبر سنوات فترة الرصد 1996–2025.</t>
+          <t>متوسط مجموع كميات الأمطار التراكمية لشهر سبتمبر عبر سنوات فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F79" s="16" t="inlineStr">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="G79" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط مجموع أمطار شهر نوفمبر (ملم/شهر)</t>
+          <t>خريطة متوسط مجموع أمطار شهر سبتمبر (ملم/شهر)</t>
         </is>
       </c>
     </row>
@@ -4460,12 +4460,12 @@
       </c>
       <c r="B80" s="10" t="inlineStr">
         <is>
-          <t>R_DecMean</t>
+          <t>R_OctMean</t>
         </is>
       </c>
       <c r="C80" s="29" t="inlineStr">
         <is>
-          <t>R_December_Mean</t>
+          <t>R_October_Mean</t>
         </is>
       </c>
       <c r="D80" s="18" t="inlineStr">
@@ -4475,7 +4475,7 @@
       </c>
       <c r="E80" s="12" t="inlineStr">
         <is>
-          <t>متوسط مجموع كميات الأمطار التراكمية لشهر ديسمبر عبر سنوات فترة الرصد 1996–2025.</t>
+          <t>متوسط مجموع كميات الأمطار التراكمية لشهر أكتوبر عبر سنوات فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F80" s="19" t="inlineStr">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="G80" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط مجموع أمطار شهر ديسمبر (ملم/شهر)</t>
+          <t>خريطة متوسط مجموع أمطار شهر أكتوبر (ملم/شهر)</t>
         </is>
       </c>
     </row>
@@ -4495,32 +4495,32 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>PSL_AnMean</t>
+          <t>R_NovMean</t>
         </is>
       </c>
       <c r="C81" s="31" t="inlineStr">
         <is>
-          <t>PSL_Annual_Mean</t>
+          <t>R_November_Mean</t>
         </is>
       </c>
       <c r="D81" s="15" t="inlineStr">
         <is>
-          <t>03_Sea_Level_Pressure (ضغط مستوى البحر)</t>
+          <t>02_Precipitation (الأمطار)</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي السنوي المصحح عند مستوى سطح البحر القياسي (Sea Level Pressure).</t>
+          <t>متوسط مجموع كميات الأمطار التراكمية لشهر نوفمبر عبر سنوات فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F81" s="16" t="inlineStr">
         <is>
-          <t>hPa / mbar</t>
+          <t>ملم/شهر (mm/month)</t>
         </is>
       </c>
       <c r="G81" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط الضغط الجوي عند مستوى سطح البحر (hPa)</t>
+          <t>خريطة متوسط مجموع أمطار شهر نوفمبر (ملم/شهر)</t>
         </is>
       </c>
     </row>
@@ -4530,32 +4530,32 @@
       </c>
       <c r="B82" s="10" t="inlineStr">
         <is>
-          <t>PSL_MonMea</t>
+          <t>R_DecMean</t>
         </is>
       </c>
       <c r="C82" s="29" t="inlineStr">
         <is>
-          <t>PSL_Month_Mean</t>
+          <t>R_December_Mean</t>
         </is>
       </c>
       <c r="D82" s="18" t="inlineStr">
         <is>
-          <t>03_Sea_Level_Pressure (ضغط مستوى البحر)</t>
+          <t>02_Precipitation (الأمطار)</t>
         </is>
       </c>
       <c r="E82" s="12" t="inlineStr">
         <is>
-          <t>المتوسط الشهري للضغط الجوي المصحح عند مستوى سطح البحر القياسي (متوسط الـ 12 شهراً).</t>
+          <t>متوسط مجموع كميات الأمطار التراكمية لشهر ديسمبر عبر سنوات فترة الرصد 1996–2025.</t>
         </is>
       </c>
       <c r="F82" s="19" t="inlineStr">
         <is>
-          <t>hPa / mbar</t>
+          <t>ملم/شهر (mm/month)</t>
         </is>
       </c>
       <c r="G82" s="30" t="inlineStr">
         <is>
-          <t>خريطة المتوسط الشهري لضغط مستوى سطح البحر (hPa)</t>
+          <t>خريطة متوسط مجموع أمطار شهر ديسمبر (ملم/شهر)</t>
         </is>
       </c>
     </row>
@@ -4565,12 +4565,12 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>PSL_WnMean</t>
+          <t>PSL_AnMean</t>
         </is>
       </c>
       <c r="C83" s="31" t="inlineStr">
         <is>
-          <t>PSL_Winter_Mean</t>
+          <t>PSL_Annual_Mean</t>
         </is>
       </c>
       <c r="D83" s="15" t="inlineStr">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي عند مستوى سطح البحر لفصل الشتاء الأرصادي (DJF).</t>
+          <t>متوسط الضغط الجوي السنوي المصحح عند مستوى سطح البحر القياسي (Sea Level Pressure).</t>
         </is>
       </c>
       <c r="F83" s="16" t="inlineStr">
@@ -4590,7 +4590,7 @@
       </c>
       <c r="G83" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط ضغط مستوى سطح البحر خلال فصل الشتاء (hPa)</t>
+          <t>خريطة متوسط الضغط الجوي عند مستوى سطح البحر (hPa)</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="B84" s="10" t="inlineStr">
         <is>
-          <t>PSL_SpMean</t>
+          <t>PSL_MonMea</t>
         </is>
       </c>
       <c r="C84" s="29" t="inlineStr">
         <is>
-          <t>PSL_Spring_Mean</t>
+          <t>PSL_Month_Mean</t>
         </is>
       </c>
       <c r="D84" s="18" t="inlineStr">
@@ -4615,7 +4615,7 @@
       </c>
       <c r="E84" s="12" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي عند مستوى سطح البحر لفصل الربيع الأرصادي (MAM).</t>
+          <t>المتوسط الشهري للضغط الجوي المصحح عند مستوى سطح البحر القياسي (متوسط الـ 12 شهراً).</t>
         </is>
       </c>
       <c r="F84" s="19" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="G84" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط ضغط مستوى سطح البحر خلال فصل الربيع (hPa)</t>
+          <t>خريطة المتوسط الشهري لضغط مستوى سطح البحر (hPa)</t>
         </is>
       </c>
     </row>
@@ -4635,12 +4635,12 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>PSL_SuMean</t>
+          <t>PSL_WnMean</t>
         </is>
       </c>
       <c r="C85" s="31" t="inlineStr">
         <is>
-          <t>PSL_Summer_Mean</t>
+          <t>PSL_Winter_Mean</t>
         </is>
       </c>
       <c r="D85" s="15" t="inlineStr">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي عند مستوى سطح البحر لفصل الصيف الأرصادي (JJA).</t>
+          <t>متوسط الضغط الجوي عند مستوى سطح البحر لفصل الشتاء الأرصادي (DJF).</t>
         </is>
       </c>
       <c r="F85" s="16" t="inlineStr">
@@ -4660,7 +4660,7 @@
       </c>
       <c r="G85" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط ضغط مستوى سطح البحر خلال فصل الصيف (hPa)</t>
+          <t>خريطة متوسط ضغط مستوى سطح البحر خلال فصل الشتاء (hPa)</t>
         </is>
       </c>
     </row>
@@ -4670,12 +4670,12 @@
       </c>
       <c r="B86" s="10" t="inlineStr">
         <is>
-          <t>PSL_AuMean</t>
+          <t>PSL_SpMean</t>
         </is>
       </c>
       <c r="C86" s="29" t="inlineStr">
         <is>
-          <t>PSL_Autumn_Mean</t>
+          <t>PSL_Spring_Mean</t>
         </is>
       </c>
       <c r="D86" s="18" t="inlineStr">
@@ -4685,7 +4685,7 @@
       </c>
       <c r="E86" s="12" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي عند مستوى سطح البحر لفصل الخريف الأرصادي (SON).</t>
+          <t>متوسط الضغط الجوي عند مستوى سطح البحر لفصل الربيع الأرصادي (MAM).</t>
         </is>
       </c>
       <c r="F86" s="19" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="G86" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط ضغط مستوى سطح البحر خلال فصل الخريف (hPa)</t>
+          <t>خريطة متوسط ضغط مستوى سطح البحر خلال فصل الربيع (hPa)</t>
         </is>
       </c>
     </row>
@@ -4705,12 +4705,12 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>PSL_AnRng</t>
+          <t>PSL_SuMean</t>
         </is>
       </c>
       <c r="C87" s="31" t="inlineStr">
         <is>
-          <t>PSL_Annual_Range</t>
+          <t>PSL_Summer_Mean</t>
         </is>
       </c>
       <c r="D87" s="15" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="E87" s="7" t="inlineStr">
         <is>
-          <t>المدى البارومتري السنوي لضغط مستوى البحر (الفارق بين أعلى وأدنى متوسط شهري للضغط).</t>
+          <t>متوسط الضغط الجوي عند مستوى سطح البحر لفصل الصيف الأرصادي (JJA).</t>
         </is>
       </c>
       <c r="F87" s="16" t="inlineStr">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="G87" s="32" t="inlineStr">
         <is>
-          <t>خريطة المدى السنوي لضغط مستوى سطح البحر (hPa)</t>
+          <t>خريطة متوسط ضغط مستوى سطح البحر خلال فصل الصيف (hPa)</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="B88" s="10" t="inlineStr">
         <is>
-          <t>PSL_JanMn</t>
+          <t>PSL_AuMean</t>
         </is>
       </c>
       <c r="C88" s="29" t="inlineStr">
         <is>
-          <t>PSL_January_Mean</t>
+          <t>PSL_Autumn_Mean</t>
         </is>
       </c>
       <c r="D88" s="18" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="E88" s="12" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي المصحح لمستوى سطح البحر القياسي لشهر يناير (SLP).</t>
+          <t>متوسط الضغط الجوي عند مستوى سطح البحر لفصل الخريف الأرصادي (SON).</t>
         </is>
       </c>
       <c r="F88" s="19" t="inlineStr">
@@ -4765,7 +4765,7 @@
       </c>
       <c r="G88" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط ضغط مستوى سطح البحر لشهر يناير (hPa)</t>
+          <t>خريطة متوسط ضغط مستوى سطح البحر خلال فصل الخريف (hPa)</t>
         </is>
       </c>
     </row>
@@ -4775,12 +4775,12 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>PSL_FebMn</t>
+          <t>PSL_AnRng</t>
         </is>
       </c>
       <c r="C89" s="31" t="inlineStr">
         <is>
-          <t>PSL_February_Mean</t>
+          <t>PSL_Annual_Range</t>
         </is>
       </c>
       <c r="D89" s="15" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي المصحح لمستوى سطح البحر القياسي لشهر فبراير (SLP).</t>
+          <t>المدى البارومتري السنوي لضغط مستوى البحر (الفارق بين أعلى وأدنى متوسط شهري للضغط).</t>
         </is>
       </c>
       <c r="F89" s="16" t="inlineStr">
@@ -4800,7 +4800,7 @@
       </c>
       <c r="G89" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط ضغط مستوى سطح البحر لشهر فبراير (hPa)</t>
+          <t>خريطة المدى السنوي لضغط مستوى سطح البحر (hPa)</t>
         </is>
       </c>
     </row>
@@ -4810,12 +4810,12 @@
       </c>
       <c r="B90" s="10" t="inlineStr">
         <is>
-          <t>PSL_MarMn</t>
+          <t>PSL_SeaRng</t>
         </is>
       </c>
       <c r="C90" s="29" t="inlineStr">
         <is>
-          <t>PSL_March_Mean</t>
+          <t>PSL_Seasonal_Range</t>
         </is>
       </c>
       <c r="D90" s="18" t="inlineStr">
@@ -4825,17 +4825,17 @@
       </c>
       <c r="E90" s="12" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي المصحح لمستوى سطح البحر القياسي لشهر مارس (SLP).</t>
+          <t>المدى الفصلي لضغط مستوى البحر (الفارق بين أعلى وأدنى فصول السنة ضغطاً).</t>
         </is>
       </c>
       <c r="F90" s="19" t="inlineStr">
         <is>
-          <t>hPa / mbar</t>
+          <t>hPa</t>
         </is>
       </c>
       <c r="G90" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط ضغط مستوى سطح البحر لشهر مارس (hPa)</t>
+          <t>خريطة المدى الفصلي لضغط مستوى البحر (hPa)</t>
         </is>
       </c>
     </row>
@@ -4845,12 +4845,12 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>PSL_AprMn</t>
+          <t>PSL_JanMn</t>
         </is>
       </c>
       <c r="C91" s="31" t="inlineStr">
         <is>
-          <t>PSL_April_Mean</t>
+          <t>PSL_January_Mean</t>
         </is>
       </c>
       <c r="D91" s="15" t="inlineStr">
@@ -4860,7 +4860,7 @@
       </c>
       <c r="E91" s="7" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي المصحح لمستوى سطح البحر القياسي لشهر أبريل (SLP).</t>
+          <t>متوسط الضغط الجوي المصحح لمستوى سطح البحر القياسي لشهر يناير (SLP).</t>
         </is>
       </c>
       <c r="F91" s="16" t="inlineStr">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="G91" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط ضغط مستوى سطح البحر لشهر أبريل (hPa)</t>
+          <t>خريطة متوسط ضغط مستوى سطح البحر لشهر يناير (hPa)</t>
         </is>
       </c>
     </row>
@@ -4880,12 +4880,12 @@
       </c>
       <c r="B92" s="10" t="inlineStr">
         <is>
-          <t>PSL_MayMn</t>
+          <t>PSL_FebMn</t>
         </is>
       </c>
       <c r="C92" s="29" t="inlineStr">
         <is>
-          <t>PSL_May_Mean</t>
+          <t>PSL_February_Mean</t>
         </is>
       </c>
       <c r="D92" s="18" t="inlineStr">
@@ -4895,7 +4895,7 @@
       </c>
       <c r="E92" s="12" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي المصحح لمستوى سطح البحر القياسي لشهر مايو (SLP).</t>
+          <t>متوسط الضغط الجوي المصحح لمستوى سطح البحر القياسي لشهر فبراير (SLP).</t>
         </is>
       </c>
       <c r="F92" s="19" t="inlineStr">
@@ -4905,7 +4905,7 @@
       </c>
       <c r="G92" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط ضغط مستوى سطح البحر لشهر مايو (hPa)</t>
+          <t>خريطة متوسط ضغط مستوى سطح البحر لشهر فبراير (hPa)</t>
         </is>
       </c>
     </row>
@@ -4915,12 +4915,12 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>PSL_JunMn</t>
+          <t>PSL_MarMn</t>
         </is>
       </c>
       <c r="C93" s="31" t="inlineStr">
         <is>
-          <t>PSL_June_Mean</t>
+          <t>PSL_March_Mean</t>
         </is>
       </c>
       <c r="D93" s="15" t="inlineStr">
@@ -4930,7 +4930,7 @@
       </c>
       <c r="E93" s="7" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي المصحح لمستوى سطح البحر القياسي لشهر يونيو (SLP).</t>
+          <t>متوسط الضغط الجوي المصحح لمستوى سطح البحر القياسي لشهر مارس (SLP).</t>
         </is>
       </c>
       <c r="F93" s="16" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="G93" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط ضغط مستوى سطح البحر لشهر يونيو (hPa)</t>
+          <t>خريطة متوسط ضغط مستوى سطح البحر لشهر مارس (hPa)</t>
         </is>
       </c>
     </row>
@@ -4950,12 +4950,12 @@
       </c>
       <c r="B94" s="10" t="inlineStr">
         <is>
-          <t>PSL_JulMn</t>
+          <t>PSL_AprMn</t>
         </is>
       </c>
       <c r="C94" s="29" t="inlineStr">
         <is>
-          <t>PSL_July_Mean</t>
+          <t>PSL_April_Mean</t>
         </is>
       </c>
       <c r="D94" s="18" t="inlineStr">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="E94" s="12" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي المصحح لمستوى سطح البحر القياسي لشهر يوليو (SLP).</t>
+          <t>متوسط الضغط الجوي المصحح لمستوى سطح البحر القياسي لشهر أبريل (SLP).</t>
         </is>
       </c>
       <c r="F94" s="19" t="inlineStr">
@@ -4975,7 +4975,7 @@
       </c>
       <c r="G94" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط ضغط مستوى سطح البحر لشهر يوليو (hPa)</t>
+          <t>خريطة متوسط ضغط مستوى سطح البحر لشهر أبريل (hPa)</t>
         </is>
       </c>
     </row>
@@ -4985,12 +4985,12 @@
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>PSL_AugMn</t>
+          <t>PSL_MayMn</t>
         </is>
       </c>
       <c r="C95" s="31" t="inlineStr">
         <is>
-          <t>PSL_August_Mean</t>
+          <t>PSL_May_Mean</t>
         </is>
       </c>
       <c r="D95" s="15" t="inlineStr">
@@ -5000,7 +5000,7 @@
       </c>
       <c r="E95" s="7" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي المصحح لمستوى سطح البحر القياسي لشهر أغسطس (SLP).</t>
+          <t>متوسط الضغط الجوي المصحح لمستوى سطح البحر القياسي لشهر مايو (SLP).</t>
         </is>
       </c>
       <c r="F95" s="16" t="inlineStr">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="G95" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط ضغط مستوى سطح البحر لشهر أغسطس (hPa)</t>
+          <t>خريطة متوسط ضغط مستوى سطح البحر لشهر مايو (hPa)</t>
         </is>
       </c>
     </row>
@@ -5020,12 +5020,12 @@
       </c>
       <c r="B96" s="10" t="inlineStr">
         <is>
-          <t>PSL_SepMn</t>
+          <t>PSL_JunMn</t>
         </is>
       </c>
       <c r="C96" s="29" t="inlineStr">
         <is>
-          <t>PSL_September_Mean</t>
+          <t>PSL_June_Mean</t>
         </is>
       </c>
       <c r="D96" s="18" t="inlineStr">
@@ -5035,7 +5035,7 @@
       </c>
       <c r="E96" s="12" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي المصحح لمستوى سطح البحر القياسي لشهر سبتمبر (SLP).</t>
+          <t>متوسط الضغط الجوي المصحح لمستوى سطح البحر القياسي لشهر يونيو (SLP).</t>
         </is>
       </c>
       <c r="F96" s="19" t="inlineStr">
@@ -5045,7 +5045,7 @@
       </c>
       <c r="G96" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط ضغط مستوى سطح البحر لشهر سبتمبر (hPa)</t>
+          <t>خريطة متوسط ضغط مستوى سطح البحر لشهر يونيو (hPa)</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>PSL_OctMn</t>
+          <t>PSL_JulMn</t>
         </is>
       </c>
       <c r="C97" s="31" t="inlineStr">
         <is>
-          <t>PSL_October_Mean</t>
+          <t>PSL_July_Mean</t>
         </is>
       </c>
       <c r="D97" s="15" t="inlineStr">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="E97" s="7" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي المصحح لمستوى سطح البحر القياسي لشهر أكتوبر (SLP).</t>
+          <t>متوسط الضغط الجوي المصحح لمستوى سطح البحر القياسي لشهر يوليو (SLP).</t>
         </is>
       </c>
       <c r="F97" s="16" t="inlineStr">
@@ -5080,7 +5080,7 @@
       </c>
       <c r="G97" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط ضغط مستوى سطح البحر لشهر أكتوبر (hPa)</t>
+          <t>خريطة متوسط ضغط مستوى سطح البحر لشهر يوليو (hPa)</t>
         </is>
       </c>
     </row>
@@ -5090,12 +5090,12 @@
       </c>
       <c r="B98" s="10" t="inlineStr">
         <is>
-          <t>PSL_NovMn</t>
+          <t>PSL_AugMn</t>
         </is>
       </c>
       <c r="C98" s="29" t="inlineStr">
         <is>
-          <t>PSL_November_Mean</t>
+          <t>PSL_August_Mean</t>
         </is>
       </c>
       <c r="D98" s="18" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="E98" s="12" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي المصحح لمستوى سطح البحر القياسي لشهر نوفمبر (SLP).</t>
+          <t>متوسط الضغط الجوي المصحح لمستوى سطح البحر القياسي لشهر أغسطس (SLP).</t>
         </is>
       </c>
       <c r="F98" s="19" t="inlineStr">
@@ -5115,7 +5115,7 @@
       </c>
       <c r="G98" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط ضغط مستوى سطح البحر لشهر نوفمبر (hPa)</t>
+          <t>خريطة متوسط ضغط مستوى سطح البحر لشهر أغسطس (hPa)</t>
         </is>
       </c>
     </row>
@@ -5125,12 +5125,12 @@
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>PSL_DecMn</t>
+          <t>PSL_SepMn</t>
         </is>
       </c>
       <c r="C99" s="31" t="inlineStr">
         <is>
-          <t>PSL_December_Mean</t>
+          <t>PSL_September_Mean</t>
         </is>
       </c>
       <c r="D99" s="15" t="inlineStr">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="E99" s="7" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي المصحح لمستوى سطح البحر القياسي لشهر ديسمبر (SLP).</t>
+          <t>متوسط الضغط الجوي المصحح لمستوى سطح البحر القياسي لشهر سبتمبر (SLP).</t>
         </is>
       </c>
       <c r="F99" s="16" t="inlineStr">
@@ -5150,7 +5150,7 @@
       </c>
       <c r="G99" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط ضغط مستوى سطح البحر لشهر ديسمبر (hPa)</t>
+          <t>خريطة متوسط ضغط مستوى سطح البحر لشهر سبتمبر (hPa)</t>
         </is>
       </c>
     </row>
@@ -5160,22 +5160,22 @@
       </c>
       <c r="B100" s="10" t="inlineStr">
         <is>
-          <t>PS_AnnMean</t>
+          <t>PSL_OctMn</t>
         </is>
       </c>
       <c r="C100" s="29" t="inlineStr">
         <is>
-          <t>PS_Annual_Mean</t>
+          <t>PSL_October_Mean</t>
         </is>
       </c>
       <c r="D100" s="18" t="inlineStr">
         <is>
-          <t>04_Surface_Pressure (الضغط السطحي)</t>
+          <t>03_Sea_Level_Pressure (ضغط مستوى البحر)</t>
         </is>
       </c>
       <c r="E100" s="12" t="inlineStr">
         <is>
-          <t>المتوسط السنوي للضغط الجوي السطحي الفعلي الحقيقي عند منسوب تضاريس المحطة.</t>
+          <t>متوسط الضغط الجوي المصحح لمستوى سطح البحر القياسي لشهر أكتوبر (SLP).</t>
         </is>
       </c>
       <c r="F100" s="19" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="G100" s="30" t="inlineStr">
         <is>
-          <t>خريطة المتوسط السنوي للضغط الجوي السطحي (hPa)</t>
+          <t>خريطة متوسط ضغط مستوى سطح البحر لشهر أكتوبر (hPa)</t>
         </is>
       </c>
     </row>
@@ -5195,22 +5195,22 @@
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>PS_MonMean</t>
+          <t>PSL_NovMn</t>
         </is>
       </c>
       <c r="C101" s="31" t="inlineStr">
         <is>
-          <t>PS_Month_Mean</t>
+          <t>PSL_November_Mean</t>
         </is>
       </c>
       <c r="D101" s="15" t="inlineStr">
         <is>
-          <t>04_Surface_Pressure (الضغط السطحي)</t>
+          <t>03_Sea_Level_Pressure (ضغط مستوى البحر)</t>
         </is>
       </c>
       <c r="E101" s="7" t="inlineStr">
         <is>
-          <t>المتوسط الشهري للضغط الجوي السطحي الفعلي للمحطة (متوسط الـ 12 شهراً).</t>
+          <t>متوسط الضغط الجوي المصحح لمستوى سطح البحر القياسي لشهر نوفمبر (SLP).</t>
         </is>
       </c>
       <c r="F101" s="16" t="inlineStr">
@@ -5220,7 +5220,7 @@
       </c>
       <c r="G101" s="32" t="inlineStr">
         <is>
-          <t>خريطة المتوسط الشهري للضغط الجوي السطحي (hPa)</t>
+          <t>خريطة متوسط ضغط مستوى سطح البحر لشهر نوفمبر (hPa)</t>
         </is>
       </c>
     </row>
@@ -5230,22 +5230,22 @@
       </c>
       <c r="B102" s="10" t="inlineStr">
         <is>
-          <t>PS_WinMean</t>
+          <t>PSL_DecMn</t>
         </is>
       </c>
       <c r="C102" s="29" t="inlineStr">
         <is>
-          <t>PS_Winter_Mean</t>
+          <t>PSL_December_Mean</t>
         </is>
       </c>
       <c r="D102" s="18" t="inlineStr">
         <is>
-          <t>04_Surface_Pressure (الضغط السطحي)</t>
+          <t>03_Sea_Level_Pressure (ضغط مستوى البحر)</t>
         </is>
       </c>
       <c r="E102" s="12" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي السطحي الفعلي لفصل الشتاء الأرصادي (DJF).</t>
+          <t>متوسط الضغط الجوي المصحح لمستوى سطح البحر القياسي لشهر ديسمبر (SLP).</t>
         </is>
       </c>
       <c r="F102" s="19" t="inlineStr">
@@ -5255,7 +5255,7 @@
       </c>
       <c r="G102" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط الضغط السطحي خلال فصل الشتاء (hPa)</t>
+          <t>خريطة متوسط ضغط مستوى سطح البحر لشهر ديسمبر (hPa)</t>
         </is>
       </c>
     </row>
@@ -5265,12 +5265,12 @@
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>PS_SprMean</t>
+          <t>PS_AnnMean</t>
         </is>
       </c>
       <c r="C103" s="31" t="inlineStr">
         <is>
-          <t>PS_Spring_Mean</t>
+          <t>PS_Annual_Mean</t>
         </is>
       </c>
       <c r="D103" s="15" t="inlineStr">
@@ -5280,7 +5280,7 @@
       </c>
       <c r="E103" s="7" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي السطحي الفعلي لفصل الربيع الأرصادي (MAM).</t>
+          <t>المتوسط السنوي للضغط الجوي السطحي الفعلي الحقيقي عند منسوب تضاريس المحطة.</t>
         </is>
       </c>
       <c r="F103" s="16" t="inlineStr">
@@ -5290,7 +5290,7 @@
       </c>
       <c r="G103" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط الضغط السطحي خلال فصل الربيع (hPa)</t>
+          <t>خريطة المتوسط السنوي للضغط الجوي السطحي (hPa)</t>
         </is>
       </c>
     </row>
@@ -5300,12 +5300,12 @@
       </c>
       <c r="B104" s="10" t="inlineStr">
         <is>
-          <t>PS_SumMean</t>
+          <t>PS_MonMean</t>
         </is>
       </c>
       <c r="C104" s="29" t="inlineStr">
         <is>
-          <t>PS_Summer_Mean</t>
+          <t>PS_Month_Mean</t>
         </is>
       </c>
       <c r="D104" s="18" t="inlineStr">
@@ -5315,7 +5315,7 @@
       </c>
       <c r="E104" s="12" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي السطحي الفعلي لفصل الصيف الأرصادي (JJA).</t>
+          <t>المتوسط الشهري للضغط الجوي السطحي الفعلي للمحطة (متوسط الـ 12 شهراً).</t>
         </is>
       </c>
       <c r="F104" s="19" t="inlineStr">
@@ -5325,7 +5325,7 @@
       </c>
       <c r="G104" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط الضغط السطحي خلال فصل الصيف (hPa)</t>
+          <t>خريطة المتوسط الشهري للضغط الجوي السطحي (hPa)</t>
         </is>
       </c>
     </row>
@@ -5335,12 +5335,12 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>PS_AutMean</t>
+          <t>PS_WinMean</t>
         </is>
       </c>
       <c r="C105" s="31" t="inlineStr">
         <is>
-          <t>PS_Autumn_Mean</t>
+          <t>PS_Winter_Mean</t>
         </is>
       </c>
       <c r="D105" s="15" t="inlineStr">
@@ -5350,7 +5350,7 @@
       </c>
       <c r="E105" s="7" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي السطحي الفعلي لفصل الخريف الأرصادي (SON).</t>
+          <t>متوسط الضغط الجوي السطحي الفعلي لفصل الشتاء الأرصادي (DJF).</t>
         </is>
       </c>
       <c r="F105" s="16" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="G105" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط الضغط السطحي خلال فصل الخريف (hPa)</t>
+          <t>خريطة متوسط الضغط السطحي خلال فصل الشتاء (hPa)</t>
         </is>
       </c>
     </row>
@@ -5370,12 +5370,12 @@
       </c>
       <c r="B106" s="10" t="inlineStr">
         <is>
-          <t>PS_AnnRng</t>
+          <t>PS_SprMean</t>
         </is>
       </c>
       <c r="C106" s="29" t="inlineStr">
         <is>
-          <t>PS_Annual_Range</t>
+          <t>PS_Spring_Mean</t>
         </is>
       </c>
       <c r="D106" s="18" t="inlineStr">
@@ -5385,7 +5385,7 @@
       </c>
       <c r="E106" s="12" t="inlineStr">
         <is>
-          <t>المدى البارومتري السنوي للضغط السطحي (الفارق بين أعلى وأدنى متوسط شهري للضغط السطحي).</t>
+          <t>متوسط الضغط الجوي السطحي الفعلي لفصل الربيع الأرصادي (MAM).</t>
         </is>
       </c>
       <c r="F106" s="19" t="inlineStr">
@@ -5395,7 +5395,7 @@
       </c>
       <c r="G106" s="30" t="inlineStr">
         <is>
-          <t>خريطة المدى السنوي للضغط الجوي السطحي (hPa)</t>
+          <t>خريطة متوسط الضغط السطحي خلال فصل الربيع (hPa)</t>
         </is>
       </c>
     </row>
@@ -5405,12 +5405,12 @@
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>PS_JanMean</t>
+          <t>PS_SumMean</t>
         </is>
       </c>
       <c r="C107" s="31" t="inlineStr">
         <is>
-          <t>PS_January_Mean</t>
+          <t>PS_Summer_Mean</t>
         </is>
       </c>
       <c r="D107" s="15" t="inlineStr">
@@ -5420,7 +5420,7 @@
       </c>
       <c r="E107" s="7" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي السطحي الفعلي الحقيقي عند منسوب المحطة لشهر يناير.</t>
+          <t>متوسط الضغط الجوي السطحي الفعلي لفصل الصيف الأرصادي (JJA).</t>
         </is>
       </c>
       <c r="F107" s="16" t="inlineStr">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="G107" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط الضغط السطحي الفعلي لشهر يناير (hPa)</t>
+          <t>خريطة متوسط الضغط السطحي خلال فصل الصيف (hPa)</t>
         </is>
       </c>
     </row>
@@ -5440,12 +5440,12 @@
       </c>
       <c r="B108" s="10" t="inlineStr">
         <is>
-          <t>PS_FebMean</t>
+          <t>PS_AutMean</t>
         </is>
       </c>
       <c r="C108" s="29" t="inlineStr">
         <is>
-          <t>PS_February_Mean</t>
+          <t>PS_Autumn_Mean</t>
         </is>
       </c>
       <c r="D108" s="18" t="inlineStr">
@@ -5455,7 +5455,7 @@
       </c>
       <c r="E108" s="12" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي السطحي الفعلي الحقيقي عند منسوب المحطة لشهر فبراير.</t>
+          <t>متوسط الضغط الجوي السطحي الفعلي لفصل الخريف الأرصادي (SON).</t>
         </is>
       </c>
       <c r="F108" s="19" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="G108" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط الضغط السطحي الفعلي لشهر فبراير (hPa)</t>
+          <t>خريطة متوسط الضغط السطحي خلال فصل الخريف (hPa)</t>
         </is>
       </c>
     </row>
@@ -5475,12 +5475,12 @@
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>PS_MarMean</t>
+          <t>PS_AnnRng</t>
         </is>
       </c>
       <c r="C109" s="31" t="inlineStr">
         <is>
-          <t>PS_March_Mean</t>
+          <t>PS_Annual_Range</t>
         </is>
       </c>
       <c r="D109" s="15" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="E109" s="7" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي السطحي الفعلي الحقيقي عند منسوب المحطة لشهر مارس.</t>
+          <t>المدى البارومتري السنوي للضغط السطحي (الفارق بين أعلى وأدنى متوسط شهري للضغط السطحي).</t>
         </is>
       </c>
       <c r="F109" s="16" t="inlineStr">
@@ -5500,7 +5500,7 @@
       </c>
       <c r="G109" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط الضغط السطحي الفعلي لشهر مارس (hPa)</t>
+          <t>خريطة المدى السنوي للضغط الجوي السطحي (hPa)</t>
         </is>
       </c>
     </row>
@@ -5510,12 +5510,12 @@
       </c>
       <c r="B110" s="10" t="inlineStr">
         <is>
-          <t>PS_AprMean</t>
+          <t>PS_SeaRng</t>
         </is>
       </c>
       <c r="C110" s="29" t="inlineStr">
         <is>
-          <t>PS_April_Mean</t>
+          <t>PS_Seasonal_Range</t>
         </is>
       </c>
       <c r="D110" s="18" t="inlineStr">
@@ -5525,17 +5525,17 @@
       </c>
       <c r="E110" s="12" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي السطحي الفعلي الحقيقي عند منسوب المحطة لشهر أبريل.</t>
+          <t>المدى الفصلي للضغط السطحي (الفارق بين فصول السنة).</t>
         </is>
       </c>
       <c r="F110" s="19" t="inlineStr">
         <is>
-          <t>hPa / mbar</t>
+          <t>hPa</t>
         </is>
       </c>
       <c r="G110" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط الضغط السطحي الفعلي لشهر أبريل (hPa)</t>
+          <t>خريطة المدى الفصلي للضغط السطحي (hPa)</t>
         </is>
       </c>
     </row>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>PS_MayMean</t>
+          <t>PS_JanMean</t>
         </is>
       </c>
       <c r="C111" s="31" t="inlineStr">
         <is>
-          <t>PS_May_Mean</t>
+          <t>PS_January_Mean</t>
         </is>
       </c>
       <c r="D111" s="15" t="inlineStr">
@@ -5560,7 +5560,7 @@
       </c>
       <c r="E111" s="7" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي السطحي الفعلي الحقيقي عند منسوب المحطة لشهر مايو.</t>
+          <t>متوسط الضغط الجوي السطحي الفعلي الحقيقي عند منسوب المحطة لشهر يناير.</t>
         </is>
       </c>
       <c r="F111" s="16" t="inlineStr">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="G111" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط الضغط السطحي الفعلي لشهر مايو (hPa)</t>
+          <t>خريطة متوسط الضغط السطحي الفعلي لشهر يناير (hPa)</t>
         </is>
       </c>
     </row>
@@ -5580,12 +5580,12 @@
       </c>
       <c r="B112" s="10" t="inlineStr">
         <is>
-          <t>PS_JunMean</t>
+          <t>PS_FebMean</t>
         </is>
       </c>
       <c r="C112" s="29" t="inlineStr">
         <is>
-          <t>PS_June_Mean</t>
+          <t>PS_February_Mean</t>
         </is>
       </c>
       <c r="D112" s="18" t="inlineStr">
@@ -5595,7 +5595,7 @@
       </c>
       <c r="E112" s="12" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي السطحي الفعلي الحقيقي عند منسوب المحطة لشهر يونيو.</t>
+          <t>متوسط الضغط الجوي السطحي الفعلي الحقيقي عند منسوب المحطة لشهر فبراير.</t>
         </is>
       </c>
       <c r="F112" s="19" t="inlineStr">
@@ -5605,7 +5605,7 @@
       </c>
       <c r="G112" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط الضغط السطحي الفعلي لشهر يونيو (hPa)</t>
+          <t>خريطة متوسط الضغط السطحي الفعلي لشهر فبراير (hPa)</t>
         </is>
       </c>
     </row>
@@ -5615,12 +5615,12 @@
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>PS_JulMean</t>
+          <t>PS_MarMean</t>
         </is>
       </c>
       <c r="C113" s="31" t="inlineStr">
         <is>
-          <t>PS_July_Mean</t>
+          <t>PS_March_Mean</t>
         </is>
       </c>
       <c r="D113" s="15" t="inlineStr">
@@ -5630,7 +5630,7 @@
       </c>
       <c r="E113" s="7" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي السطحي الفعلي الحقيقي عند منسوب المحطة لشهر يوليو.</t>
+          <t>متوسط الضغط الجوي السطحي الفعلي الحقيقي عند منسوب المحطة لشهر مارس.</t>
         </is>
       </c>
       <c r="F113" s="16" t="inlineStr">
@@ -5640,7 +5640,7 @@
       </c>
       <c r="G113" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط الضغط السطحي الفعلي لشهر يوليو (hPa)</t>
+          <t>خريطة متوسط الضغط السطحي الفعلي لشهر مارس (hPa)</t>
         </is>
       </c>
     </row>
@@ -5650,12 +5650,12 @@
       </c>
       <c r="B114" s="10" t="inlineStr">
         <is>
-          <t>PS_AugMean</t>
+          <t>PS_AprMean</t>
         </is>
       </c>
       <c r="C114" s="29" t="inlineStr">
         <is>
-          <t>PS_August_Mean</t>
+          <t>PS_April_Mean</t>
         </is>
       </c>
       <c r="D114" s="18" t="inlineStr">
@@ -5665,7 +5665,7 @@
       </c>
       <c r="E114" s="12" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي السطحي الفعلي الحقيقي عند منسوب المحطة لشهر أغسطس.</t>
+          <t>متوسط الضغط الجوي السطحي الفعلي الحقيقي عند منسوب المحطة لشهر أبريل.</t>
         </is>
       </c>
       <c r="F114" s="19" t="inlineStr">
@@ -5675,7 +5675,7 @@
       </c>
       <c r="G114" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط الضغط السطحي الفعلي لشهر أغسطس (hPa)</t>
+          <t>خريطة متوسط الضغط السطحي الفعلي لشهر أبريل (hPa)</t>
         </is>
       </c>
     </row>
@@ -5685,12 +5685,12 @@
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>PS_SepMean</t>
+          <t>PS_MayMean</t>
         </is>
       </c>
       <c r="C115" s="31" t="inlineStr">
         <is>
-          <t>PS_September_Mean</t>
+          <t>PS_May_Mean</t>
         </is>
       </c>
       <c r="D115" s="15" t="inlineStr">
@@ -5700,7 +5700,7 @@
       </c>
       <c r="E115" s="7" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي السطحي الفعلي الحقيقي عند منسوب المحطة لشهر سبتمبر.</t>
+          <t>متوسط الضغط الجوي السطحي الفعلي الحقيقي عند منسوب المحطة لشهر مايو.</t>
         </is>
       </c>
       <c r="F115" s="16" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="G115" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط الضغط السطحي الفعلي لشهر سبتمبر (hPa)</t>
+          <t>خريطة متوسط الضغط السطحي الفعلي لشهر مايو (hPa)</t>
         </is>
       </c>
     </row>
@@ -5720,12 +5720,12 @@
       </c>
       <c r="B116" s="10" t="inlineStr">
         <is>
-          <t>PS_OctMean</t>
+          <t>PS_JunMean</t>
         </is>
       </c>
       <c r="C116" s="29" t="inlineStr">
         <is>
-          <t>PS_October_Mean</t>
+          <t>PS_June_Mean</t>
         </is>
       </c>
       <c r="D116" s="18" t="inlineStr">
@@ -5735,7 +5735,7 @@
       </c>
       <c r="E116" s="12" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي السطحي الفعلي الحقيقي عند منسوب المحطة لشهر أكتوبر.</t>
+          <t>متوسط الضغط الجوي السطحي الفعلي الحقيقي عند منسوب المحطة لشهر يونيو.</t>
         </is>
       </c>
       <c r="F116" s="19" t="inlineStr">
@@ -5745,7 +5745,7 @@
       </c>
       <c r="G116" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط الضغط السطحي الفعلي لشهر أكتوبر (hPa)</t>
+          <t>خريطة متوسط الضغط السطحي الفعلي لشهر يونيو (hPa)</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>PS_NovMean</t>
+          <t>PS_JulMean</t>
         </is>
       </c>
       <c r="C117" s="31" t="inlineStr">
         <is>
-          <t>PS_November_Mean</t>
+          <t>PS_July_Mean</t>
         </is>
       </c>
       <c r="D117" s="15" t="inlineStr">
@@ -5770,7 +5770,7 @@
       </c>
       <c r="E117" s="7" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي السطحي الفعلي الحقيقي عند منسوب المحطة لشهر نوفمبر.</t>
+          <t>متوسط الضغط الجوي السطحي الفعلي الحقيقي عند منسوب المحطة لشهر يوليو.</t>
         </is>
       </c>
       <c r="F117" s="16" t="inlineStr">
@@ -5780,7 +5780,7 @@
       </c>
       <c r="G117" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط الضغط السطحي الفعلي لشهر نوفمبر (hPa)</t>
+          <t>خريطة متوسط الضغط السطحي الفعلي لشهر يوليو (hPa)</t>
         </is>
       </c>
     </row>
@@ -5790,12 +5790,12 @@
       </c>
       <c r="B118" s="10" t="inlineStr">
         <is>
-          <t>PS_DecMean</t>
+          <t>PS_AugMean</t>
         </is>
       </c>
       <c r="C118" s="29" t="inlineStr">
         <is>
-          <t>PS_December_Mean</t>
+          <t>PS_August_Mean</t>
         </is>
       </c>
       <c r="D118" s="18" t="inlineStr">
@@ -5805,7 +5805,7 @@
       </c>
       <c r="E118" s="12" t="inlineStr">
         <is>
-          <t>متوسط الضغط الجوي السطحي الفعلي الحقيقي عند منسوب المحطة لشهر ديسمبر.</t>
+          <t>متوسط الضغط الجوي السطحي الفعلي الحقيقي عند منسوب المحطة لشهر أغسطس.</t>
         </is>
       </c>
       <c r="F118" s="19" t="inlineStr">
@@ -5815,7 +5815,7 @@
       </c>
       <c r="G118" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط الضغط السطحي الفعلي لشهر ديسمبر (hPa)</t>
+          <t>خريطة متوسط الضغط السطحي الفعلي لشهر أغسطس (hPa)</t>
         </is>
       </c>
     </row>
@@ -5825,32 +5825,32 @@
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>WSp_AnMean</t>
+          <t>PS_SepMean</t>
         </is>
       </c>
       <c r="C119" s="31" t="inlineStr">
         <is>
-          <t>W_Spd_Annual_Mean</t>
+          <t>PS_September_Mean</t>
         </is>
       </c>
       <c r="D119" s="15" t="inlineStr">
         <is>
-          <t>05_Wind (الرياح)</t>
+          <t>04_Surface_Pressure (الضغط السطحي)</t>
         </is>
       </c>
       <c r="E119" s="7" t="inlineStr">
         <is>
-          <t>المتوسط السنوي لسرعة الرياح عند ارتفاع 10 أمتار فوق سطح الأرض.</t>
+          <t>متوسط الضغط الجوي السطحي الفعلي الحقيقي عند منسوب المحطة لشهر سبتمبر.</t>
         </is>
       </c>
       <c r="F119" s="16" t="inlineStr">
         <is>
-          <t>م/ث (m/s)</t>
+          <t>hPa / mbar</t>
         </is>
       </c>
       <c r="G119" s="32" t="inlineStr">
         <is>
-          <t>خريطة المتوسط السنوي لسرعة الرياح (م/ث)</t>
+          <t>خريطة متوسط الضغط السطحي الفعلي لشهر سبتمبر (hPa)</t>
         </is>
       </c>
     </row>
@@ -5860,32 +5860,32 @@
       </c>
       <c r="B120" s="10" t="inlineStr">
         <is>
-          <t>WSp_MonMea</t>
+          <t>PS_OctMean</t>
         </is>
       </c>
       <c r="C120" s="29" t="inlineStr">
         <is>
-          <t>W_Spd_Month_Mean</t>
+          <t>PS_October_Mean</t>
         </is>
       </c>
       <c r="D120" s="18" t="inlineStr">
         <is>
-          <t>05_Wind (الرياح السطحية)</t>
+          <t>04_Surface_Pressure (الضغط السطحي)</t>
         </is>
       </c>
       <c r="E120" s="12" t="inlineStr">
         <is>
-          <t>المتوسط الشهري لسرعة الرياح على ارتفاع 10 أمتار (متوسط الـ 12 شهراً).</t>
+          <t>متوسط الضغط الجوي السطحي الفعلي الحقيقي عند منسوب المحطة لشهر أكتوبر.</t>
         </is>
       </c>
       <c r="F120" s="19" t="inlineStr">
         <is>
-          <t>m/s</t>
+          <t>hPa / mbar</t>
         </is>
       </c>
       <c r="G120" s="30" t="inlineStr">
         <is>
-          <t>خريطة المتوسط الشهري لسرعة الرياح (m/s)</t>
+          <t>خريطة متوسط الضغط السطحي الفعلي لشهر أكتوبر (hPa)</t>
         </is>
       </c>
     </row>
@@ -5895,32 +5895,32 @@
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>WSp_WnMean</t>
+          <t>PS_NovMean</t>
         </is>
       </c>
       <c r="C121" s="31" t="inlineStr">
         <is>
-          <t>W_Spd_Winter_Mean</t>
+          <t>PS_November_Mean</t>
         </is>
       </c>
       <c r="D121" s="15" t="inlineStr">
         <is>
-          <t>05_Wind (الرياح)</t>
+          <t>04_Surface_Pressure (الضغط السطحي)</t>
         </is>
       </c>
       <c r="E121" s="7" t="inlineStr">
         <is>
-          <t>متوسط سرعة الرياح لفصل الشتاء الأرصادي عند ارتفاع 10 أمتار (DJF).</t>
+          <t>متوسط الضغط الجوي السطحي الفعلي الحقيقي عند منسوب المحطة لشهر نوفمبر.</t>
         </is>
       </c>
       <c r="F121" s="16" t="inlineStr">
         <is>
-          <t>م/ث (m/s)</t>
+          <t>hPa / mbar</t>
         </is>
       </c>
       <c r="G121" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط سرعة الرياح خلال فصل الشتاء (م/ث)</t>
+          <t>خريطة متوسط الضغط السطحي الفعلي لشهر نوفمبر (hPa)</t>
         </is>
       </c>
     </row>
@@ -5930,32 +5930,32 @@
       </c>
       <c r="B122" s="10" t="inlineStr">
         <is>
-          <t>WSp_SpMean</t>
+          <t>PS_DecMean</t>
         </is>
       </c>
       <c r="C122" s="29" t="inlineStr">
         <is>
-          <t>W_Spd_Spring_Mean</t>
+          <t>PS_December_Mean</t>
         </is>
       </c>
       <c r="D122" s="18" t="inlineStr">
         <is>
-          <t>05_Wind (الرياح)</t>
+          <t>04_Surface_Pressure (الضغط السطحي)</t>
         </is>
       </c>
       <c r="E122" s="12" t="inlineStr">
         <is>
-          <t>متوسط سرعة الرياح لفصل الربيع الأرصادي عند ارتفاع 10 أمتار (MAM).</t>
+          <t>متوسط الضغط الجوي السطحي الفعلي الحقيقي عند منسوب المحطة لشهر ديسمبر.</t>
         </is>
       </c>
       <c r="F122" s="19" t="inlineStr">
         <is>
-          <t>م/ث (m/s)</t>
+          <t>hPa / mbar</t>
         </is>
       </c>
       <c r="G122" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط سرعة الرياح خلال فصل الربيع (م/ث)</t>
+          <t>خريطة متوسط الضغط السطحي الفعلي لشهر ديسمبر (hPa)</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>WSp_SuMean</t>
+          <t>WSp_AnMean</t>
         </is>
       </c>
       <c r="C123" s="31" t="inlineStr">
         <is>
-          <t>W_Spd_Summer_Mean</t>
+          <t>W_Spd_Annual_Mean</t>
         </is>
       </c>
       <c r="D123" s="15" t="inlineStr">
@@ -5980,7 +5980,7 @@
       </c>
       <c r="E123" s="7" t="inlineStr">
         <is>
-          <t>متوسط سرعة الرياح لفصل الصيف الأرصادي عند ارتفاع 10 أمتار (JJA).</t>
+          <t>المتوسط السنوي لسرعة الرياح عند ارتفاع 10 أمتار فوق سطح الأرض.</t>
         </is>
       </c>
       <c r="F123" s="16" t="inlineStr">
@@ -5990,7 +5990,7 @@
       </c>
       <c r="G123" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط سرعة الرياح خلال فصل الصيف (م/ث)</t>
+          <t>خريطة المتوسط السنوي لسرعة الرياح (م/ث)</t>
         </is>
       </c>
     </row>
@@ -6000,32 +6000,32 @@
       </c>
       <c r="B124" s="10" t="inlineStr">
         <is>
-          <t>WSp_AuMean</t>
+          <t>WSp_MonMea</t>
         </is>
       </c>
       <c r="C124" s="29" t="inlineStr">
         <is>
-          <t>W_Spd_Autumn_Mean</t>
+          <t>W_Spd_Month_Mean</t>
         </is>
       </c>
       <c r="D124" s="18" t="inlineStr">
         <is>
-          <t>05_Wind (الرياح)</t>
+          <t>05_Wind (الرياح السطحية)</t>
         </is>
       </c>
       <c r="E124" s="12" t="inlineStr">
         <is>
-          <t>متوسط سرعة الرياح لفصل الخريف الأرصادي عند ارتفاع 10 أمتار (SON).</t>
+          <t>المتوسط الشهري لسرعة الرياح على ارتفاع 10 أمتار (متوسط الـ 12 شهراً).</t>
         </is>
       </c>
       <c r="F124" s="19" t="inlineStr">
         <is>
-          <t>م/ث (m/s)</t>
+          <t>m/s</t>
         </is>
       </c>
       <c r="G124" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط سرعة الرياح خلال فصل الخريف (م/ث)</t>
+          <t>خريطة المتوسط الشهري لسرعة الرياح (m/s)</t>
         </is>
       </c>
     </row>
@@ -6035,12 +6035,12 @@
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>WSp_MaxMo</t>
+          <t>WSp_WnMean</t>
         </is>
       </c>
       <c r="C125" s="31" t="inlineStr">
         <is>
-          <t>W_Spd_Annual_Max_Month</t>
+          <t>W_Spd_Winter_Mean</t>
         </is>
       </c>
       <c r="D125" s="15" t="inlineStr">
@@ -6050,7 +6050,7 @@
       </c>
       <c r="E125" s="7" t="inlineStr">
         <is>
-          <t>أقصى متوسط شهري مسجل لسرعة الرياح في السنة (ذروة النشاط الريحي).</t>
+          <t>متوسط سرعة الرياح لفصل الشتاء الأرصادي عند ارتفاع 10 أمتار (DJF).</t>
         </is>
       </c>
       <c r="F125" s="16" t="inlineStr">
@@ -6060,7 +6060,7 @@
       </c>
       <c r="G125" s="32" t="inlineStr">
         <is>
-          <t>خريطة أقصى متوسط شهري لسرعة الرياح (م/ث)</t>
+          <t>خريطة متوسط سرعة الرياح خلال فصل الشتاء (م/ث)</t>
         </is>
       </c>
     </row>
@@ -6070,12 +6070,12 @@
       </c>
       <c r="B126" s="10" t="inlineStr">
         <is>
-          <t>WSp_MinMo</t>
+          <t>WSp_SpMean</t>
         </is>
       </c>
       <c r="C126" s="29" t="inlineStr">
         <is>
-          <t>W_Spd_Annual_Min_Month</t>
+          <t>W_Spd_Spring_Mean</t>
         </is>
       </c>
       <c r="D126" s="18" t="inlineStr">
@@ -6085,7 +6085,7 @@
       </c>
       <c r="E126" s="12" t="inlineStr">
         <is>
-          <t>أدنى متوسط شهري مسجل لسرعة الرياح في السنة (فترة الهدوء الريحي).</t>
+          <t>متوسط سرعة الرياح لفصل الربيع الأرصادي عند ارتفاع 10 أمتار (MAM).</t>
         </is>
       </c>
       <c r="F126" s="19" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="G126" s="30" t="inlineStr">
         <is>
-          <t>خريطة أدنى متوسط شهري لسرعة الرياح (م/ث)</t>
+          <t>خريطة متوسط سرعة الرياح خلال فصل الربيع (م/ث)</t>
         </is>
       </c>
     </row>
@@ -6105,12 +6105,12 @@
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>WSp_AnRng</t>
+          <t>WSp_SuMean</t>
         </is>
       </c>
       <c r="C127" s="31" t="inlineStr">
         <is>
-          <t>W_Spd_Annual_Range</t>
+          <t>W_Spd_Summer_Mean</t>
         </is>
       </c>
       <c r="D127" s="15" t="inlineStr">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="E127" s="7" t="inlineStr">
         <is>
-          <t>المدى السنوي لسرعة الرياح (الفارق بين أشد شهور السنة رياحاً وأهدأها سرعة).</t>
+          <t>متوسط سرعة الرياح لفصل الصيف الأرصادي عند ارتفاع 10 أمتار (JJA).</t>
         </is>
       </c>
       <c r="F127" s="16" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="G127" s="32" t="inlineStr">
         <is>
-          <t>خريطة المدى السنوي لسرعة الرياح (م/ث)</t>
+          <t>خريطة متوسط سرعة الرياح خلال فصل الصيف (م/ث)</t>
         </is>
       </c>
     </row>
@@ -6140,12 +6140,12 @@
       </c>
       <c r="B128" s="10" t="inlineStr">
         <is>
-          <t>WDr_AnMean</t>
+          <t>WSp_AuMean</t>
         </is>
       </c>
       <c r="C128" s="29" t="inlineStr">
         <is>
-          <t>W_Dir_Annual_Mean</t>
+          <t>W_Spd_Autumn_Mean</t>
         </is>
       </c>
       <c r="D128" s="18" t="inlineStr">
@@ -6155,17 +6155,17 @@
       </c>
       <c r="E128" s="12" t="inlineStr">
         <is>
-          <t>الاتجاه السائد السنوي للرياح بالدرجات الزاوية (محسوب بالمتوسط الدائري للمتجهات الدائرية atan2).</t>
+          <t>متوسط سرعة الرياح لفصل الخريف الأرصادي عند ارتفاع 10 أمتار (SON).</t>
         </is>
       </c>
       <c r="F128" s="19" t="inlineStr">
         <is>
-          <t>درجة (°)</t>
+          <t>م/ث (m/s)</t>
         </is>
       </c>
       <c r="G128" s="30" t="inlineStr">
         <is>
-          <t>خريطة الاتجاه السائد السنوي للرياح (درجات)</t>
+          <t>خريطة متوسط سرعة الرياح خلال فصل الخريف (م/ث)</t>
         </is>
       </c>
     </row>
@@ -6175,32 +6175,32 @@
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>WDr_MonMea</t>
+          <t>WSp_MaxMo</t>
         </is>
       </c>
       <c r="C129" s="31" t="inlineStr">
         <is>
-          <t>W_Dir_Month_Mean</t>
+          <t>W_Spd_Annual_Max_Month</t>
         </is>
       </c>
       <c r="D129" s="15" t="inlineStr">
         <is>
-          <t>05_Wind (الرياح السطحية)</t>
+          <t>05_Wind (الرياح)</t>
         </is>
       </c>
       <c r="E129" s="7" t="inlineStr">
         <is>
-          <t>المتوسط الشهري لاتجاه الرياح السائدة (المتوسط الدائري للشهور الـ 12).</t>
+          <t>أقصى متوسط شهري مسجل لسرعة الرياح في السنة (ذروة النشاط الريحي).</t>
         </is>
       </c>
       <c r="F129" s="16" t="inlineStr">
         <is>
-          <t>°</t>
+          <t>م/ث (m/s)</t>
         </is>
       </c>
       <c r="G129" s="32" t="inlineStr">
         <is>
-          <t>خريطة المتوسط الشهري لاتجاه الرياح السائدة (°)</t>
+          <t>خريطة أقصى متوسط شهري لسرعة الرياح (م/ث)</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="B130" s="10" t="inlineStr">
         <is>
-          <t>WDr_WnMean</t>
+          <t>WSp_MinMo</t>
         </is>
       </c>
       <c r="C130" s="29" t="inlineStr">
         <is>
-          <t>W_Dir_Winter_Mean</t>
+          <t>W_Spd_Annual_Min_Month</t>
         </is>
       </c>
       <c r="D130" s="18" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="E130" s="12" t="inlineStr">
         <is>
-          <t>اتجاه الرياح السائد خلال فصل الشتاء الأرصادي بالدرجات الزاوية (DJF).</t>
+          <t>أدنى متوسط شهري مسجل لسرعة الرياح في السنة (فترة الهدوء الريحي).</t>
         </is>
       </c>
       <c r="F130" s="19" t="inlineStr">
         <is>
-          <t>درجة (°)</t>
+          <t>م/ث (m/s)</t>
         </is>
       </c>
       <c r="G130" s="30" t="inlineStr">
         <is>
-          <t>خريطة اتجاه الرياح السائد خلال فصل الشتاء (درجات)</t>
+          <t>خريطة أدنى متوسط شهري لسرعة الرياح (م/ث)</t>
         </is>
       </c>
     </row>
@@ -6245,12 +6245,12 @@
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>WDr_SpMean</t>
+          <t>WSp_AnRng</t>
         </is>
       </c>
       <c r="C131" s="31" t="inlineStr">
         <is>
-          <t>W_Dir_Spring_Mean</t>
+          <t>W_Spd_Annual_Range</t>
         </is>
       </c>
       <c r="D131" s="15" t="inlineStr">
@@ -6260,17 +6260,17 @@
       </c>
       <c r="E131" s="7" t="inlineStr">
         <is>
-          <t>اتجاه الرياح السائد خلال فصل الربيع الأرصادي بالدرجات الزاوية (MAM).</t>
+          <t>المدى السنوي لسرعة الرياح (الفارق بين أشد شهور السنة رياحاً وأهدأها سرعة).</t>
         </is>
       </c>
       <c r="F131" s="16" t="inlineStr">
         <is>
-          <t>درجة (°)</t>
+          <t>م/ث (m/s)</t>
         </is>
       </c>
       <c r="G131" s="32" t="inlineStr">
         <is>
-          <t>خريطة اتجاه الرياح السائد خلال فصل الربيع (درجات)</t>
+          <t>خريطة المدى السنوي لسرعة الرياح (م/ث)</t>
         </is>
       </c>
     </row>
@@ -6280,12 +6280,12 @@
       </c>
       <c r="B132" s="10" t="inlineStr">
         <is>
-          <t>WDr_SuMean</t>
+          <t>WSp_SeaRng</t>
         </is>
       </c>
       <c r="C132" s="29" t="inlineStr">
         <is>
-          <t>W_Dir_Summer_Mean</t>
+          <t>W_Spd_Seasonal_Range</t>
         </is>
       </c>
       <c r="D132" s="18" t="inlineStr">
@@ -6295,17 +6295,17 @@
       </c>
       <c r="E132" s="12" t="inlineStr">
         <is>
-          <t>اتجاه الرياح السائد خلال فصل الصيف الأرصادي بالدرجات الزاوية (JJA).</t>
+          <t>المدى الفصلي لسرعة الرياح (الفارق بين أشد فصول السنة ريحاً وأهدأها).</t>
         </is>
       </c>
       <c r="F132" s="19" t="inlineStr">
         <is>
-          <t>درجة (°)</t>
+          <t>م/ث (m/s)</t>
         </is>
       </c>
       <c r="G132" s="30" t="inlineStr">
         <is>
-          <t>خريطة اتجاه الرياح السائد خلال فصل الصيف (درجات)</t>
+          <t>خريطة المدى الفصلي لسرعة الرياح (م/ث)</t>
         </is>
       </c>
     </row>
@@ -6315,12 +6315,12 @@
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>WDr_AuMean</t>
+          <t>WDr_AnMean</t>
         </is>
       </c>
       <c r="C133" s="31" t="inlineStr">
         <is>
-          <t>W_Dir_Autumn_Mean</t>
+          <t>W_Dir_Annual_Mean</t>
         </is>
       </c>
       <c r="D133" s="15" t="inlineStr">
@@ -6330,7 +6330,7 @@
       </c>
       <c r="E133" s="7" t="inlineStr">
         <is>
-          <t>اتجاه الرياح السائد خلال فصل الخريف الأرصادي بالدرجات الزاوية (SON).</t>
+          <t>الاتجاه السائد السنوي للرياح بالدرجات الزاوية (محسوب بالمتوسط الدائري للمتجهات الدائرية atan2).</t>
         </is>
       </c>
       <c r="F133" s="16" t="inlineStr">
@@ -6340,7 +6340,7 @@
       </c>
       <c r="G133" s="32" t="inlineStr">
         <is>
-          <t>خريطة اتجاه الرياح السائد خلال فصل الخريف (درجات)</t>
+          <t>خريطة الاتجاه السائد السنوي للرياح (درجات)</t>
         </is>
       </c>
     </row>
@@ -6350,32 +6350,32 @@
       </c>
       <c r="B134" s="10" t="inlineStr">
         <is>
-          <t>WSp_JanMn</t>
+          <t>WDr_MonMea</t>
         </is>
       </c>
       <c r="C134" s="29" t="inlineStr">
         <is>
-          <t>W_Spd_January_Mean</t>
+          <t>W_Dir_Month_Mean</t>
         </is>
       </c>
       <c r="D134" s="18" t="inlineStr">
         <is>
-          <t>05_Wind (الرياح)</t>
+          <t>05_Wind (الرياح السطحية)</t>
         </is>
       </c>
       <c r="E134" s="12" t="inlineStr">
         <is>
-          <t>متوسط سرعة الرياح على ارتفاع 10 أمتار لشهر يناير عبر فترة الرصد.</t>
+          <t>المتوسط الشهري لاتجاه الرياح السائدة (المتوسط الدائري للشهور الـ 12).</t>
         </is>
       </c>
       <c r="F134" s="19" t="inlineStr">
         <is>
-          <t>م/ث (m/s)</t>
+          <t>°</t>
         </is>
       </c>
       <c r="G134" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط سرعة الرياح لشهر يناير (م/ث)</t>
+          <t>خريطة المتوسط الشهري لاتجاه الرياح السائدة (°)</t>
         </is>
       </c>
     </row>
@@ -6385,12 +6385,12 @@
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>WSp_FebMn</t>
+          <t>WDr_WnMean</t>
         </is>
       </c>
       <c r="C135" s="31" t="inlineStr">
         <is>
-          <t>W_Spd_February_Mean</t>
+          <t>W_Dir_Winter_Mean</t>
         </is>
       </c>
       <c r="D135" s="15" t="inlineStr">
@@ -6400,17 +6400,17 @@
       </c>
       <c r="E135" s="7" t="inlineStr">
         <is>
-          <t>متوسط سرعة الرياح على ارتفاع 10 أمتار لشهر فبراير عبر فترة الرصد.</t>
+          <t>اتجاه الرياح السائد خلال فصل الشتاء الأرصادي بالدرجات الزاوية (DJF).</t>
         </is>
       </c>
       <c r="F135" s="16" t="inlineStr">
         <is>
-          <t>م/ث (m/s)</t>
+          <t>درجة (°)</t>
         </is>
       </c>
       <c r="G135" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط سرعة الرياح لشهر فبراير (م/ث)</t>
+          <t>خريطة اتجاه الرياح السائد خلال فصل الشتاء (درجات)</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="B136" s="10" t="inlineStr">
         <is>
-          <t>WSp_MarMn</t>
+          <t>WDr_SpMean</t>
         </is>
       </c>
       <c r="C136" s="29" t="inlineStr">
         <is>
-          <t>W_Spd_March_Mean</t>
+          <t>W_Dir_Spring_Mean</t>
         </is>
       </c>
       <c r="D136" s="18" t="inlineStr">
@@ -6435,17 +6435,17 @@
       </c>
       <c r="E136" s="12" t="inlineStr">
         <is>
-          <t>متوسط سرعة الرياح على ارتفاع 10 أمتار لشهر مارس عبر فترة الرصد.</t>
+          <t>اتجاه الرياح السائد خلال فصل الربيع الأرصادي بالدرجات الزاوية (MAM).</t>
         </is>
       </c>
       <c r="F136" s="19" t="inlineStr">
         <is>
-          <t>م/ث (m/s)</t>
+          <t>درجة (°)</t>
         </is>
       </c>
       <c r="G136" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط سرعة الرياح لشهر مارس (م/ث)</t>
+          <t>خريطة اتجاه الرياح السائد خلال فصل الربيع (درجات)</t>
         </is>
       </c>
     </row>
@@ -6455,12 +6455,12 @@
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>WSp_AprMn</t>
+          <t>WDr_SuMean</t>
         </is>
       </c>
       <c r="C137" s="31" t="inlineStr">
         <is>
-          <t>W_Spd_April_Mean</t>
+          <t>W_Dir_Summer_Mean</t>
         </is>
       </c>
       <c r="D137" s="15" t="inlineStr">
@@ -6470,17 +6470,17 @@
       </c>
       <c r="E137" s="7" t="inlineStr">
         <is>
-          <t>متوسط سرعة الرياح على ارتفاع 10 أمتار لشهر أبريل عبر فترة الرصد.</t>
+          <t>اتجاه الرياح السائد خلال فصل الصيف الأرصادي بالدرجات الزاوية (JJA).</t>
         </is>
       </c>
       <c r="F137" s="16" t="inlineStr">
         <is>
-          <t>م/ث (m/s)</t>
+          <t>درجة (°)</t>
         </is>
       </c>
       <c r="G137" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط سرعة الرياح لشهر أبريل (م/ث)</t>
+          <t>خريطة اتجاه الرياح السائد خلال فصل الصيف (درجات)</t>
         </is>
       </c>
     </row>
@@ -6490,12 +6490,12 @@
       </c>
       <c r="B138" s="10" t="inlineStr">
         <is>
-          <t>WSp_MayMn</t>
+          <t>WDr_AuMean</t>
         </is>
       </c>
       <c r="C138" s="29" t="inlineStr">
         <is>
-          <t>W_Spd_May_Mean</t>
+          <t>W_Dir_Autumn_Mean</t>
         </is>
       </c>
       <c r="D138" s="18" t="inlineStr">
@@ -6505,17 +6505,17 @@
       </c>
       <c r="E138" s="12" t="inlineStr">
         <is>
-          <t>متوسط سرعة الرياح على ارتفاع 10 أمتار لشهر مايو عبر فترة الرصد.</t>
+          <t>اتجاه الرياح السائد خلال فصل الخريف الأرصادي بالدرجات الزاوية (SON).</t>
         </is>
       </c>
       <c r="F138" s="19" t="inlineStr">
         <is>
-          <t>م/ث (m/s)</t>
+          <t>درجة (°)</t>
         </is>
       </c>
       <c r="G138" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط سرعة الرياح لشهر مايو (م/ث)</t>
+          <t>خريطة اتجاه الرياح السائد خلال فصل الخريف (درجات)</t>
         </is>
       </c>
     </row>
@@ -6525,12 +6525,12 @@
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>WSp_JunMn</t>
+          <t>WSp_JanMn</t>
         </is>
       </c>
       <c r="C139" s="31" t="inlineStr">
         <is>
-          <t>W_Spd_June_Mean</t>
+          <t>W_Spd_January_Mean</t>
         </is>
       </c>
       <c r="D139" s="15" t="inlineStr">
@@ -6540,7 +6540,7 @@
       </c>
       <c r="E139" s="7" t="inlineStr">
         <is>
-          <t>متوسط سرعة الرياح على ارتفاع 10 أمتار لشهر يونيو عبر فترة الرصد.</t>
+          <t>متوسط سرعة الرياح على ارتفاع 10 أمتار لشهر يناير عبر فترة الرصد.</t>
         </is>
       </c>
       <c r="F139" s="16" t="inlineStr">
@@ -6550,7 +6550,7 @@
       </c>
       <c r="G139" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط سرعة الرياح لشهر يونيو (م/ث)</t>
+          <t>خريطة متوسط سرعة الرياح لشهر يناير (م/ث)</t>
         </is>
       </c>
     </row>
@@ -6560,12 +6560,12 @@
       </c>
       <c r="B140" s="10" t="inlineStr">
         <is>
-          <t>WSp_JulMn</t>
+          <t>WSp_FebMn</t>
         </is>
       </c>
       <c r="C140" s="29" t="inlineStr">
         <is>
-          <t>W_Spd_July_Mean</t>
+          <t>W_Spd_February_Mean</t>
         </is>
       </c>
       <c r="D140" s="18" t="inlineStr">
@@ -6575,7 +6575,7 @@
       </c>
       <c r="E140" s="12" t="inlineStr">
         <is>
-          <t>متوسط سرعة الرياح على ارتفاع 10 أمتار لشهر يوليو عبر فترة الرصد.</t>
+          <t>متوسط سرعة الرياح على ارتفاع 10 أمتار لشهر فبراير عبر فترة الرصد.</t>
         </is>
       </c>
       <c r="F140" s="19" t="inlineStr">
@@ -6585,7 +6585,7 @@
       </c>
       <c r="G140" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط سرعة الرياح لشهر يوليو (م/ث)</t>
+          <t>خريطة متوسط سرعة الرياح لشهر فبراير (م/ث)</t>
         </is>
       </c>
     </row>
@@ -6595,12 +6595,12 @@
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>WSp_AugMn</t>
+          <t>WSp_MarMn</t>
         </is>
       </c>
       <c r="C141" s="31" t="inlineStr">
         <is>
-          <t>W_Spd_August_Mean</t>
+          <t>W_Spd_March_Mean</t>
         </is>
       </c>
       <c r="D141" s="15" t="inlineStr">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="E141" s="7" t="inlineStr">
         <is>
-          <t>متوسط سرعة الرياح على ارتفاع 10 أمتار لشهر أغسطس عبر فترة الرصد.</t>
+          <t>متوسط سرعة الرياح على ارتفاع 10 أمتار لشهر مارس عبر فترة الرصد.</t>
         </is>
       </c>
       <c r="F141" s="16" t="inlineStr">
@@ -6620,7 +6620,7 @@
       </c>
       <c r="G141" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط سرعة الرياح لشهر أغسطس (م/ث)</t>
+          <t>خريطة متوسط سرعة الرياح لشهر مارس (م/ث)</t>
         </is>
       </c>
     </row>
@@ -6630,12 +6630,12 @@
       </c>
       <c r="B142" s="10" t="inlineStr">
         <is>
-          <t>WSp_SepMn</t>
+          <t>WSp_AprMn</t>
         </is>
       </c>
       <c r="C142" s="29" t="inlineStr">
         <is>
-          <t>W_Spd_September_Mean</t>
+          <t>W_Spd_April_Mean</t>
         </is>
       </c>
       <c r="D142" s="18" t="inlineStr">
@@ -6645,7 +6645,7 @@
       </c>
       <c r="E142" s="12" t="inlineStr">
         <is>
-          <t>متوسط سرعة الرياح على ارتفاع 10 أمتار لشهر سبتمبر عبر فترة الرصد.</t>
+          <t>متوسط سرعة الرياح على ارتفاع 10 أمتار لشهر أبريل عبر فترة الرصد.</t>
         </is>
       </c>
       <c r="F142" s="19" t="inlineStr">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="G142" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط سرعة الرياح لشهر سبتمبر (م/ث)</t>
+          <t>خريطة متوسط سرعة الرياح لشهر أبريل (م/ث)</t>
         </is>
       </c>
     </row>
@@ -6665,12 +6665,12 @@
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>WSp_OctMn</t>
+          <t>WSp_MayMn</t>
         </is>
       </c>
       <c r="C143" s="31" t="inlineStr">
         <is>
-          <t>W_Spd_October_Mean</t>
+          <t>W_Spd_May_Mean</t>
         </is>
       </c>
       <c r="D143" s="15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="E143" s="7" t="inlineStr">
         <is>
-          <t>متوسط سرعة الرياح على ارتفاع 10 أمتار لشهر أكتوبر عبر فترة الرصد.</t>
+          <t>متوسط سرعة الرياح على ارتفاع 10 أمتار لشهر مايو عبر فترة الرصد.</t>
         </is>
       </c>
       <c r="F143" s="16" t="inlineStr">
@@ -6690,7 +6690,7 @@
       </c>
       <c r="G143" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط سرعة الرياح لشهر أكتوبر (م/ث)</t>
+          <t>خريطة متوسط سرعة الرياح لشهر مايو (م/ث)</t>
         </is>
       </c>
     </row>
@@ -6700,12 +6700,12 @@
       </c>
       <c r="B144" s="10" t="inlineStr">
         <is>
-          <t>WSp_NovMn</t>
+          <t>WSp_JunMn</t>
         </is>
       </c>
       <c r="C144" s="29" t="inlineStr">
         <is>
-          <t>W_Spd_November_Mean</t>
+          <t>W_Spd_June_Mean</t>
         </is>
       </c>
       <c r="D144" s="18" t="inlineStr">
@@ -6715,7 +6715,7 @@
       </c>
       <c r="E144" s="12" t="inlineStr">
         <is>
-          <t>متوسط سرعة الرياح على ارتفاع 10 أمتار لشهر نوفمبر عبر فترة الرصد.</t>
+          <t>متوسط سرعة الرياح على ارتفاع 10 أمتار لشهر يونيو عبر فترة الرصد.</t>
         </is>
       </c>
       <c r="F144" s="19" t="inlineStr">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="G144" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط سرعة الرياح لشهر نوفمبر (م/ث)</t>
+          <t>خريطة متوسط سرعة الرياح لشهر يونيو (م/ث)</t>
         </is>
       </c>
     </row>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>WSp_DecMn</t>
+          <t>WSp_JulMn</t>
         </is>
       </c>
       <c r="C145" s="31" t="inlineStr">
         <is>
-          <t>W_Spd_December_Mean</t>
+          <t>W_Spd_July_Mean</t>
         </is>
       </c>
       <c r="D145" s="15" t="inlineStr">
@@ -6750,7 +6750,7 @@
       </c>
       <c r="E145" s="7" t="inlineStr">
         <is>
-          <t>متوسط سرعة الرياح على ارتفاع 10 أمتار لشهر ديسمبر عبر فترة الرصد.</t>
+          <t>متوسط سرعة الرياح على ارتفاع 10 أمتار لشهر يوليو عبر فترة الرصد.</t>
         </is>
       </c>
       <c r="F145" s="16" t="inlineStr">
@@ -6760,7 +6760,7 @@
       </c>
       <c r="G145" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط سرعة الرياح لشهر ديسمبر (م/ث)</t>
+          <t>خريطة متوسط سرعة الرياح لشهر يوليو (م/ث)</t>
         </is>
       </c>
     </row>
@@ -6770,12 +6770,12 @@
       </c>
       <c r="B146" s="10" t="inlineStr">
         <is>
-          <t>WDr_JanMn</t>
+          <t>WSp_AugMn</t>
         </is>
       </c>
       <c r="C146" s="29" t="inlineStr">
         <is>
-          <t>W_Dir_January_Mean</t>
+          <t>W_Spd_August_Mean</t>
         </is>
       </c>
       <c r="D146" s="18" t="inlineStr">
@@ -6785,17 +6785,17 @@
       </c>
       <c r="E146" s="12" t="inlineStr">
         <is>
-          <t>متوسط اتجاه الرياح السائد لشهر يناير محسوب بالمتوسط الدائري المتجهي (atan2).</t>
+          <t>متوسط سرعة الرياح على ارتفاع 10 أمتار لشهر أغسطس عبر فترة الرصد.</t>
         </is>
       </c>
       <c r="F146" s="19" t="inlineStr">
         <is>
-          <t>درجة (°) / Degree</t>
+          <t>م/ث (m/s)</t>
         </is>
       </c>
       <c r="G146" s="30" t="inlineStr">
         <is>
-          <t>خريطة اتجاه الرياح السائد لشهر يناير (°)</t>
+          <t>خريطة متوسط سرعة الرياح لشهر أغسطس (م/ث)</t>
         </is>
       </c>
     </row>
@@ -6805,12 +6805,12 @@
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>WDr_FebMn</t>
+          <t>WSp_SepMn</t>
         </is>
       </c>
       <c r="C147" s="31" t="inlineStr">
         <is>
-          <t>W_Dir_February_Mean</t>
+          <t>W_Spd_September_Mean</t>
         </is>
       </c>
       <c r="D147" s="15" t="inlineStr">
@@ -6820,17 +6820,17 @@
       </c>
       <c r="E147" s="7" t="inlineStr">
         <is>
-          <t>متوسط اتجاه الرياح السائد لشهر فبراير محسوب بالمتوسط الدائري المتجهي (atan2).</t>
+          <t>متوسط سرعة الرياح على ارتفاع 10 أمتار لشهر سبتمبر عبر فترة الرصد.</t>
         </is>
       </c>
       <c r="F147" s="16" t="inlineStr">
         <is>
-          <t>درجة (°) / Degree</t>
+          <t>م/ث (m/s)</t>
         </is>
       </c>
       <c r="G147" s="32" t="inlineStr">
         <is>
-          <t>خريطة اتجاه الرياح السائد لشهر فبراير (°)</t>
+          <t>خريطة متوسط سرعة الرياح لشهر سبتمبر (م/ث)</t>
         </is>
       </c>
     </row>
@@ -6840,12 +6840,12 @@
       </c>
       <c r="B148" s="10" t="inlineStr">
         <is>
-          <t>WDr_MarMn</t>
+          <t>WSp_OctMn</t>
         </is>
       </c>
       <c r="C148" s="29" t="inlineStr">
         <is>
-          <t>W_Dir_March_Mean</t>
+          <t>W_Spd_October_Mean</t>
         </is>
       </c>
       <c r="D148" s="18" t="inlineStr">
@@ -6855,17 +6855,17 @@
       </c>
       <c r="E148" s="12" t="inlineStr">
         <is>
-          <t>متوسط اتجاه الرياح السائد لشهر مارس محسوب بالمتوسط الدائري المتجهي (atan2).</t>
+          <t>متوسط سرعة الرياح على ارتفاع 10 أمتار لشهر أكتوبر عبر فترة الرصد.</t>
         </is>
       </c>
       <c r="F148" s="19" t="inlineStr">
         <is>
-          <t>درجة (°) / Degree</t>
+          <t>م/ث (m/s)</t>
         </is>
       </c>
       <c r="G148" s="30" t="inlineStr">
         <is>
-          <t>خريطة اتجاه الرياح السائد لشهر مارس (°)</t>
+          <t>خريطة متوسط سرعة الرياح لشهر أكتوبر (م/ث)</t>
         </is>
       </c>
     </row>
@@ -6875,12 +6875,12 @@
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>WDr_AprMn</t>
+          <t>WSp_NovMn</t>
         </is>
       </c>
       <c r="C149" s="31" t="inlineStr">
         <is>
-          <t>W_Dir_April_Mean</t>
+          <t>W_Spd_November_Mean</t>
         </is>
       </c>
       <c r="D149" s="15" t="inlineStr">
@@ -6890,17 +6890,17 @@
       </c>
       <c r="E149" s="7" t="inlineStr">
         <is>
-          <t>متوسط اتجاه الرياح السائد لشهر أبريل محسوب بالمتوسط الدائري المتجهي (atan2).</t>
+          <t>متوسط سرعة الرياح على ارتفاع 10 أمتار لشهر نوفمبر عبر فترة الرصد.</t>
         </is>
       </c>
       <c r="F149" s="16" t="inlineStr">
         <is>
-          <t>درجة (°) / Degree</t>
+          <t>م/ث (m/s)</t>
         </is>
       </c>
       <c r="G149" s="32" t="inlineStr">
         <is>
-          <t>خريطة اتجاه الرياح السائد لشهر أبريل (°)</t>
+          <t>خريطة متوسط سرعة الرياح لشهر نوفمبر (م/ث)</t>
         </is>
       </c>
     </row>
@@ -6910,12 +6910,12 @@
       </c>
       <c r="B150" s="10" t="inlineStr">
         <is>
-          <t>WDr_MayMn</t>
+          <t>WSp_DecMn</t>
         </is>
       </c>
       <c r="C150" s="29" t="inlineStr">
         <is>
-          <t>W_Dir_May_Mean</t>
+          <t>W_Spd_December_Mean</t>
         </is>
       </c>
       <c r="D150" s="18" t="inlineStr">
@@ -6925,17 +6925,17 @@
       </c>
       <c r="E150" s="12" t="inlineStr">
         <is>
-          <t>متوسط اتجاه الرياح السائد لشهر مايو محسوب بالمتوسط الدائري المتجهي (atan2).</t>
+          <t>متوسط سرعة الرياح على ارتفاع 10 أمتار لشهر ديسمبر عبر فترة الرصد.</t>
         </is>
       </c>
       <c r="F150" s="19" t="inlineStr">
         <is>
-          <t>درجة (°) / Degree</t>
+          <t>م/ث (m/s)</t>
         </is>
       </c>
       <c r="G150" s="30" t="inlineStr">
         <is>
-          <t>خريطة اتجاه الرياح السائد لشهر مايو (°)</t>
+          <t>خريطة متوسط سرعة الرياح لشهر ديسمبر (م/ث)</t>
         </is>
       </c>
     </row>
@@ -6945,12 +6945,12 @@
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>WDr_JunMn</t>
+          <t>WDr_JanMn</t>
         </is>
       </c>
       <c r="C151" s="31" t="inlineStr">
         <is>
-          <t>W_Dir_June_Mean</t>
+          <t>W_Dir_January_Mean</t>
         </is>
       </c>
       <c r="D151" s="15" t="inlineStr">
@@ -6960,7 +6960,7 @@
       </c>
       <c r="E151" s="7" t="inlineStr">
         <is>
-          <t>متوسط اتجاه الرياح السائد لشهر يونيو محسوب بالمتوسط الدائري المتجهي (atan2).</t>
+          <t>متوسط اتجاه الرياح السائد لشهر يناير محسوب بالمتوسط الدائري المتجهي (atan2).</t>
         </is>
       </c>
       <c r="F151" s="16" t="inlineStr">
@@ -6970,7 +6970,7 @@
       </c>
       <c r="G151" s="32" t="inlineStr">
         <is>
-          <t>خريطة اتجاه الرياح السائد لشهر يونيو (°)</t>
+          <t>خريطة اتجاه الرياح السائد لشهر يناير (°)</t>
         </is>
       </c>
     </row>
@@ -6980,12 +6980,12 @@
       </c>
       <c r="B152" s="10" t="inlineStr">
         <is>
-          <t>WDr_JulMn</t>
+          <t>WDr_FebMn</t>
         </is>
       </c>
       <c r="C152" s="29" t="inlineStr">
         <is>
-          <t>W_Dir_July_Mean</t>
+          <t>W_Dir_February_Mean</t>
         </is>
       </c>
       <c r="D152" s="18" t="inlineStr">
@@ -6995,7 +6995,7 @@
       </c>
       <c r="E152" s="12" t="inlineStr">
         <is>
-          <t>متوسط اتجاه الرياح السائد لشهر يوليو محسوب بالمتوسط الدائري المتجهي (atan2).</t>
+          <t>متوسط اتجاه الرياح السائد لشهر فبراير محسوب بالمتوسط الدائري المتجهي (atan2).</t>
         </is>
       </c>
       <c r="F152" s="19" t="inlineStr">
@@ -7005,7 +7005,7 @@
       </c>
       <c r="G152" s="30" t="inlineStr">
         <is>
-          <t>خريطة اتجاه الرياح السائد لشهر يوليو (°)</t>
+          <t>خريطة اتجاه الرياح السائد لشهر فبراير (°)</t>
         </is>
       </c>
     </row>
@@ -7015,12 +7015,12 @@
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>WDr_AugMn</t>
+          <t>WDr_MarMn</t>
         </is>
       </c>
       <c r="C153" s="31" t="inlineStr">
         <is>
-          <t>W_Dir_August_Mean</t>
+          <t>W_Dir_March_Mean</t>
         </is>
       </c>
       <c r="D153" s="15" t="inlineStr">
@@ -7030,7 +7030,7 @@
       </c>
       <c r="E153" s="7" t="inlineStr">
         <is>
-          <t>متوسط اتجاه الرياح السائد لشهر أغسطس محسوب بالمتوسط الدائري المتجهي (atan2).</t>
+          <t>متوسط اتجاه الرياح السائد لشهر مارس محسوب بالمتوسط الدائري المتجهي (atan2).</t>
         </is>
       </c>
       <c r="F153" s="16" t="inlineStr">
@@ -7040,7 +7040,7 @@
       </c>
       <c r="G153" s="32" t="inlineStr">
         <is>
-          <t>خريطة اتجاه الرياح السائد لشهر أغسطس (°)</t>
+          <t>خريطة اتجاه الرياح السائد لشهر مارس (°)</t>
         </is>
       </c>
     </row>
@@ -7050,12 +7050,12 @@
       </c>
       <c r="B154" s="10" t="inlineStr">
         <is>
-          <t>WDr_SepMn</t>
+          <t>WDr_AprMn</t>
         </is>
       </c>
       <c r="C154" s="29" t="inlineStr">
         <is>
-          <t>W_Dir_September_Mean</t>
+          <t>W_Dir_April_Mean</t>
         </is>
       </c>
       <c r="D154" s="18" t="inlineStr">
@@ -7065,7 +7065,7 @@
       </c>
       <c r="E154" s="12" t="inlineStr">
         <is>
-          <t>متوسط اتجاه الرياح السائد لشهر سبتمبر محسوب بالمتوسط الدائري المتجهي (atan2).</t>
+          <t>متوسط اتجاه الرياح السائد لشهر أبريل محسوب بالمتوسط الدائري المتجهي (atan2).</t>
         </is>
       </c>
       <c r="F154" s="19" t="inlineStr">
@@ -7075,7 +7075,7 @@
       </c>
       <c r="G154" s="30" t="inlineStr">
         <is>
-          <t>خريطة اتجاه الرياح السائد لشهر سبتمبر (°)</t>
+          <t>خريطة اتجاه الرياح السائد لشهر أبريل (°)</t>
         </is>
       </c>
     </row>
@@ -7085,12 +7085,12 @@
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
-          <t>WDr_OctMn</t>
+          <t>WDr_MayMn</t>
         </is>
       </c>
       <c r="C155" s="31" t="inlineStr">
         <is>
-          <t>W_Dir_October_Mean</t>
+          <t>W_Dir_May_Mean</t>
         </is>
       </c>
       <c r="D155" s="15" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="E155" s="7" t="inlineStr">
         <is>
-          <t>متوسط اتجاه الرياح السائد لشهر أكتوبر محسوب بالمتوسط الدائري المتجهي (atan2).</t>
+          <t>متوسط اتجاه الرياح السائد لشهر مايو محسوب بالمتوسط الدائري المتجهي (atan2).</t>
         </is>
       </c>
       <c r="F155" s="16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="G155" s="32" t="inlineStr">
         <is>
-          <t>خريطة اتجاه الرياح السائد لشهر أكتوبر (°)</t>
+          <t>خريطة اتجاه الرياح السائد لشهر مايو (°)</t>
         </is>
       </c>
     </row>
@@ -7120,12 +7120,12 @@
       </c>
       <c r="B156" s="10" t="inlineStr">
         <is>
-          <t>WDr_NovMn</t>
+          <t>WDr_JunMn</t>
         </is>
       </c>
       <c r="C156" s="29" t="inlineStr">
         <is>
-          <t>W_Dir_November_Mean</t>
+          <t>W_Dir_June_Mean</t>
         </is>
       </c>
       <c r="D156" s="18" t="inlineStr">
@@ -7135,7 +7135,7 @@
       </c>
       <c r="E156" s="12" t="inlineStr">
         <is>
-          <t>متوسط اتجاه الرياح السائد لشهر نوفمبر محسوب بالمتوسط الدائري المتجهي (atan2).</t>
+          <t>متوسط اتجاه الرياح السائد لشهر يونيو محسوب بالمتوسط الدائري المتجهي (atan2).</t>
         </is>
       </c>
       <c r="F156" s="19" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="G156" s="30" t="inlineStr">
         <is>
-          <t>خريطة اتجاه الرياح السائد لشهر نوفمبر (°)</t>
+          <t>خريطة اتجاه الرياح السائد لشهر يونيو (°)</t>
         </is>
       </c>
     </row>
@@ -7155,12 +7155,12 @@
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>WDr_DecMn</t>
+          <t>WDr_JulMn</t>
         </is>
       </c>
       <c r="C157" s="31" t="inlineStr">
         <is>
-          <t>W_Dir_December_Mean</t>
+          <t>W_Dir_July_Mean</t>
         </is>
       </c>
       <c r="D157" s="15" t="inlineStr">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="E157" s="7" t="inlineStr">
         <is>
-          <t>متوسط اتجاه الرياح السائد لشهر ديسمبر محسوب بالمتوسط الدائري المتجهي (atan2).</t>
+          <t>متوسط اتجاه الرياح السائد لشهر يوليو محسوب بالمتوسط الدائري المتجهي (atan2).</t>
         </is>
       </c>
       <c r="F157" s="16" t="inlineStr">
@@ -7180,7 +7180,7 @@
       </c>
       <c r="G157" s="32" t="inlineStr">
         <is>
-          <t>خريطة اتجاه الرياح السائد لشهر ديسمبر (°)</t>
+          <t>خريطة اتجاه الرياح السائد لشهر يوليو (°)</t>
         </is>
       </c>
     </row>
@@ -7190,32 +7190,32 @@
       </c>
       <c r="B158" s="10" t="inlineStr">
         <is>
-          <t>RH_AnMean</t>
+          <t>WDr_AugMn</t>
         </is>
       </c>
       <c r="C158" s="29" t="inlineStr">
         <is>
-          <t>RH_Annual_Mean</t>
+          <t>W_Dir_August_Mean</t>
         </is>
       </c>
       <c r="D158" s="18" t="inlineStr">
         <is>
-          <t>06_Relative_Humidity (الرطوبة النسبية)</t>
+          <t>05_Wind (الرياح)</t>
         </is>
       </c>
       <c r="E158" s="12" t="inlineStr">
         <is>
-          <t>المتوسط الحسابي السنوي للرطوبة النسبية للهواء عند ارتفاع 2 متر كنسبة مئوية.</t>
+          <t>متوسط اتجاه الرياح السائد لشهر أغسطس محسوب بالمتوسط الدائري المتجهي (atan2).</t>
         </is>
       </c>
       <c r="F158" s="19" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>درجة (°) / Degree</t>
         </is>
       </c>
       <c r="G158" s="30" t="inlineStr">
         <is>
-          <t>خريطة المتوسط السنوي للرطوبة النسبية (%)</t>
+          <t>خريطة اتجاه الرياح السائد لشهر أغسطس (°)</t>
         </is>
       </c>
     </row>
@@ -7225,32 +7225,32 @@
       </c>
       <c r="B159" s="5" t="inlineStr">
         <is>
-          <t>RH_MonMean</t>
+          <t>WDr_SepMn</t>
         </is>
       </c>
       <c r="C159" s="31" t="inlineStr">
         <is>
-          <t>RH_Month_Mean</t>
+          <t>W_Dir_September_Mean</t>
         </is>
       </c>
       <c r="D159" s="15" t="inlineStr">
         <is>
-          <t>06_Relative_Humidity (الرطوبة النسبية)</t>
+          <t>05_Wind (الرياح)</t>
         </is>
       </c>
       <c r="E159" s="7" t="inlineStr">
         <is>
-          <t>المتوسط الشهري للرطوبة النسبية عند ارتفاع 2 متر (متوسط الـ 12 شهراً).</t>
+          <t>متوسط اتجاه الرياح السائد لشهر سبتمبر محسوب بالمتوسط الدائري المتجهي (atan2).</t>
         </is>
       </c>
       <c r="F159" s="16" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>درجة (°) / Degree</t>
         </is>
       </c>
       <c r="G159" s="32" t="inlineStr">
         <is>
-          <t>خريطة المتوسط الشهري للرطوبة النسبية (%)</t>
+          <t>خريطة اتجاه الرياح السائد لشهر سبتمبر (°)</t>
         </is>
       </c>
     </row>
@@ -7260,32 +7260,32 @@
       </c>
       <c r="B160" s="10" t="inlineStr">
         <is>
-          <t>RH_WnMean</t>
+          <t>WDr_OctMn</t>
         </is>
       </c>
       <c r="C160" s="29" t="inlineStr">
         <is>
-          <t>RH_Winter_Mean</t>
+          <t>W_Dir_October_Mean</t>
         </is>
       </c>
       <c r="D160" s="18" t="inlineStr">
         <is>
-          <t>06_Relative_Humidity (الرطوبة النسبية)</t>
+          <t>05_Wind (الرياح)</t>
         </is>
       </c>
       <c r="E160" s="12" t="inlineStr">
         <is>
-          <t>متوسط الرطوبة النسبية لفصل الشتاء الأرصادي (DJF).</t>
+          <t>متوسط اتجاه الرياح السائد لشهر أكتوبر محسوب بالمتوسط الدائري المتجهي (atan2).</t>
         </is>
       </c>
       <c r="F160" s="19" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>درجة (°) / Degree</t>
         </is>
       </c>
       <c r="G160" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط الرطوبة النسبية خلال فصل الشتاء (%)</t>
+          <t>خريطة اتجاه الرياح السائد لشهر أكتوبر (°)</t>
         </is>
       </c>
     </row>
@@ -7295,32 +7295,32 @@
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
-          <t>RH_SpMean</t>
+          <t>WDr_NovMn</t>
         </is>
       </c>
       <c r="C161" s="31" t="inlineStr">
         <is>
-          <t>RH_Spring_Mean</t>
+          <t>W_Dir_November_Mean</t>
         </is>
       </c>
       <c r="D161" s="15" t="inlineStr">
         <is>
-          <t>06_Relative_Humidity (الرطوبة النسبية)</t>
+          <t>05_Wind (الرياح)</t>
         </is>
       </c>
       <c r="E161" s="7" t="inlineStr">
         <is>
-          <t>متوسط الرطوبة النسبية لفصل الربيع الأرصادي (MAM).</t>
+          <t>متوسط اتجاه الرياح السائد لشهر نوفمبر محسوب بالمتوسط الدائري المتجهي (atan2).</t>
         </is>
       </c>
       <c r="F161" s="16" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>درجة (°) / Degree</t>
         </is>
       </c>
       <c r="G161" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط الرطوبة النسبية خلال فصل الربيع (%)</t>
+          <t>خريطة اتجاه الرياح السائد لشهر نوفمبر (°)</t>
         </is>
       </c>
     </row>
@@ -7330,32 +7330,32 @@
       </c>
       <c r="B162" s="10" t="inlineStr">
         <is>
-          <t>RH_SuMean</t>
+          <t>WDr_DecMn</t>
         </is>
       </c>
       <c r="C162" s="29" t="inlineStr">
         <is>
-          <t>RH_Summer_Mean</t>
+          <t>W_Dir_December_Mean</t>
         </is>
       </c>
       <c r="D162" s="18" t="inlineStr">
         <is>
-          <t>06_Relative_Humidity (الرطوبة النسبية)</t>
+          <t>05_Wind (الرياح)</t>
         </is>
       </c>
       <c r="E162" s="12" t="inlineStr">
         <is>
-          <t>متوسط الرطوبة النسبية لفصل الصيف الأرصادي (JJA).</t>
+          <t>متوسط اتجاه الرياح السائد لشهر ديسمبر محسوب بالمتوسط الدائري المتجهي (atan2).</t>
         </is>
       </c>
       <c r="F162" s="19" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>درجة (°) / Degree</t>
         </is>
       </c>
       <c r="G162" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط الرطوبة النسبية خلال فصل الصيف (%)</t>
+          <t>خريطة اتجاه الرياح السائد لشهر ديسمبر (°)</t>
         </is>
       </c>
     </row>
@@ -7365,12 +7365,12 @@
       </c>
       <c r="B163" s="5" t="inlineStr">
         <is>
-          <t>RH_AuMean</t>
+          <t>RH_AnMean</t>
         </is>
       </c>
       <c r="C163" s="31" t="inlineStr">
         <is>
-          <t>RH_Autumn_Mean</t>
+          <t>RH_Annual_Mean</t>
         </is>
       </c>
       <c r="D163" s="15" t="inlineStr">
@@ -7380,7 +7380,7 @@
       </c>
       <c r="E163" s="7" t="inlineStr">
         <is>
-          <t>متوسط الرطوبة النسبية لفصل الخريف الأرصادي (SON).</t>
+          <t>المتوسط الحسابي السنوي للرطوبة النسبية للهواء عند ارتفاع 2 متر كنسبة مئوية.</t>
         </is>
       </c>
       <c r="F163" s="16" t="inlineStr">
@@ -7390,7 +7390,7 @@
       </c>
       <c r="G163" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط الرطوبة النسبية خلال فصل الخريف (%)</t>
+          <t>خريطة المتوسط السنوي للرطوبة النسبية (%)</t>
         </is>
       </c>
     </row>
@@ -7400,12 +7400,12 @@
       </c>
       <c r="B164" s="10" t="inlineStr">
         <is>
-          <t>RH_AnRng</t>
+          <t>RH_MonMean</t>
         </is>
       </c>
       <c r="C164" s="29" t="inlineStr">
         <is>
-          <t>RH_Annual_Range</t>
+          <t>RH_Month_Mean</t>
         </is>
       </c>
       <c r="D164" s="18" t="inlineStr">
@@ -7415,7 +7415,7 @@
       </c>
       <c r="E164" s="12" t="inlineStr">
         <is>
-          <t>المدى السنوي للرطوبة النسبية (الفارق بين أعلى شهر رطوبة وأدنى شهر رطوبة).</t>
+          <t>المتوسط الشهري للرطوبة النسبية عند ارتفاع 2 متر (متوسط الـ 12 شهراً).</t>
         </is>
       </c>
       <c r="F164" s="19" t="inlineStr">
@@ -7425,7 +7425,7 @@
       </c>
       <c r="G164" s="30" t="inlineStr">
         <is>
-          <t>خريطة المدى السنوي للرطوبة النسبية (%)</t>
+          <t>خريطة المتوسط الشهري للرطوبة النسبية (%)</t>
         </is>
       </c>
     </row>
@@ -7435,12 +7435,12 @@
       </c>
       <c r="B165" s="5" t="inlineStr">
         <is>
-          <t>RH_JanMean</t>
+          <t>RH_WnMean</t>
         </is>
       </c>
       <c r="C165" s="31" t="inlineStr">
         <is>
-          <t>RH_January_Mean</t>
+          <t>RH_Winter_Mean</t>
         </is>
       </c>
       <c r="D165" s="15" t="inlineStr">
@@ -7450,7 +7450,7 @@
       </c>
       <c r="E165" s="7" t="inlineStr">
         <is>
-          <t>متوسط الرطوبة النسبية عند ارتفاع 2 متر لشهر يناير عبر فترة الرصد.</t>
+          <t>متوسط الرطوبة النسبية لفصل الشتاء الأرصادي (DJF).</t>
         </is>
       </c>
       <c r="F165" s="16" t="inlineStr">
@@ -7460,7 +7460,7 @@
       </c>
       <c r="G165" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط الرطوبة النسبية لشهر يناير (%)</t>
+          <t>خريطة متوسط الرطوبة النسبية خلال فصل الشتاء (%)</t>
         </is>
       </c>
     </row>
@@ -7470,12 +7470,12 @@
       </c>
       <c r="B166" s="10" t="inlineStr">
         <is>
-          <t>RH_FebMean</t>
+          <t>RH_SpMean</t>
         </is>
       </c>
       <c r="C166" s="29" t="inlineStr">
         <is>
-          <t>RH_February_Mean</t>
+          <t>RH_Spring_Mean</t>
         </is>
       </c>
       <c r="D166" s="18" t="inlineStr">
@@ -7485,7 +7485,7 @@
       </c>
       <c r="E166" s="12" t="inlineStr">
         <is>
-          <t>متوسط الرطوبة النسبية عند ارتفاع 2 متر لشهر فبراير عبر فترة الرصد.</t>
+          <t>متوسط الرطوبة النسبية لفصل الربيع الأرصادي (MAM).</t>
         </is>
       </c>
       <c r="F166" s="19" t="inlineStr">
@@ -7495,7 +7495,7 @@
       </c>
       <c r="G166" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط الرطوبة النسبية لشهر فبراير (%)</t>
+          <t>خريطة متوسط الرطوبة النسبية خلال فصل الربيع (%)</t>
         </is>
       </c>
     </row>
@@ -7505,12 +7505,12 @@
       </c>
       <c r="B167" s="5" t="inlineStr">
         <is>
-          <t>RH_MarMean</t>
+          <t>RH_SuMean</t>
         </is>
       </c>
       <c r="C167" s="31" t="inlineStr">
         <is>
-          <t>RH_March_Mean</t>
+          <t>RH_Summer_Mean</t>
         </is>
       </c>
       <c r="D167" s="15" t="inlineStr">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="E167" s="7" t="inlineStr">
         <is>
-          <t>متوسط الرطوبة النسبية عند ارتفاع 2 متر لشهر مارس عبر فترة الرصد.</t>
+          <t>متوسط الرطوبة النسبية لفصل الصيف الأرصادي (JJA).</t>
         </is>
       </c>
       <c r="F167" s="16" t="inlineStr">
@@ -7530,7 +7530,7 @@
       </c>
       <c r="G167" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط الرطوبة النسبية لشهر مارس (%)</t>
+          <t>خريطة متوسط الرطوبة النسبية خلال فصل الصيف (%)</t>
         </is>
       </c>
     </row>
@@ -7540,12 +7540,12 @@
       </c>
       <c r="B168" s="10" t="inlineStr">
         <is>
-          <t>RH_AprMean</t>
+          <t>RH_AuMean</t>
         </is>
       </c>
       <c r="C168" s="29" t="inlineStr">
         <is>
-          <t>RH_April_Mean</t>
+          <t>RH_Autumn_Mean</t>
         </is>
       </c>
       <c r="D168" s="18" t="inlineStr">
@@ -7555,7 +7555,7 @@
       </c>
       <c r="E168" s="12" t="inlineStr">
         <is>
-          <t>متوسط الرطوبة النسبية عند ارتفاع 2 متر لشهر أبريل عبر فترة الرصد.</t>
+          <t>متوسط الرطوبة النسبية لفصل الخريف الأرصادي (SON).</t>
         </is>
       </c>
       <c r="F168" s="19" t="inlineStr">
@@ -7565,7 +7565,7 @@
       </c>
       <c r="G168" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط الرطوبة النسبية لشهر أبريل (%)</t>
+          <t>خريطة متوسط الرطوبة النسبية خلال فصل الخريف (%)</t>
         </is>
       </c>
     </row>
@@ -7575,12 +7575,12 @@
       </c>
       <c r="B169" s="5" t="inlineStr">
         <is>
-          <t>RH_MayMean</t>
+          <t>RH_AnRng</t>
         </is>
       </c>
       <c r="C169" s="31" t="inlineStr">
         <is>
-          <t>RH_May_Mean</t>
+          <t>RH_Annual_Range</t>
         </is>
       </c>
       <c r="D169" s="15" t="inlineStr">
@@ -7590,7 +7590,7 @@
       </c>
       <c r="E169" s="7" t="inlineStr">
         <is>
-          <t>متوسط الرطوبة النسبية عند ارتفاع 2 متر لشهر مايو عبر فترة الرصد.</t>
+          <t>المدى السنوي للرطوبة النسبية (الفارق بين أعلى شهر رطوبة وأدنى شهر رطوبة).</t>
         </is>
       </c>
       <c r="F169" s="16" t="inlineStr">
@@ -7600,7 +7600,7 @@
       </c>
       <c r="G169" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط الرطوبة النسبية لشهر مايو (%)</t>
+          <t>خريطة المدى السنوي للرطوبة النسبية (%)</t>
         </is>
       </c>
     </row>
@@ -7610,12 +7610,12 @@
       </c>
       <c r="B170" s="10" t="inlineStr">
         <is>
-          <t>RH_JunMean</t>
+          <t>RH_SeaRng</t>
         </is>
       </c>
       <c r="C170" s="29" t="inlineStr">
         <is>
-          <t>RH_June_Mean</t>
+          <t>RH_Seasonal_Range</t>
         </is>
       </c>
       <c r="D170" s="18" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="E170" s="12" t="inlineStr">
         <is>
-          <t>متوسط الرطوبة النسبية عند ارتفاع 2 متر لشهر يونيو عبر فترة الرصد.</t>
+          <t>المدى الفصلي للرطوبة النسبية (الفارق بين أكثر فصول السنة رطوبة وأجفها).</t>
         </is>
       </c>
       <c r="F170" s="19" t="inlineStr">
@@ -7635,7 +7635,7 @@
       </c>
       <c r="G170" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط الرطوبة النسبية لشهر يونيو (%)</t>
+          <t>خريطة المدى الفصلي للرطوبة النسبية (%)</t>
         </is>
       </c>
     </row>
@@ -7645,12 +7645,12 @@
       </c>
       <c r="B171" s="5" t="inlineStr">
         <is>
-          <t>RH_JulMean</t>
+          <t>RH_JanMean</t>
         </is>
       </c>
       <c r="C171" s="31" t="inlineStr">
         <is>
-          <t>RH_July_Mean</t>
+          <t>RH_January_Mean</t>
         </is>
       </c>
       <c r="D171" s="15" t="inlineStr">
@@ -7660,7 +7660,7 @@
       </c>
       <c r="E171" s="7" t="inlineStr">
         <is>
-          <t>متوسط الرطوبة النسبية عند ارتفاع 2 متر لشهر يوليو عبر فترة الرصد.</t>
+          <t>متوسط الرطوبة النسبية عند ارتفاع 2 متر لشهر يناير عبر فترة الرصد.</t>
         </is>
       </c>
       <c r="F171" s="16" t="inlineStr">
@@ -7670,7 +7670,7 @@
       </c>
       <c r="G171" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط الرطوبة النسبية لشهر يوليو (%)</t>
+          <t>خريطة متوسط الرطوبة النسبية لشهر يناير (%)</t>
         </is>
       </c>
     </row>
@@ -7680,12 +7680,12 @@
       </c>
       <c r="B172" s="10" t="inlineStr">
         <is>
-          <t>RH_AugMean</t>
+          <t>RH_FebMean</t>
         </is>
       </c>
       <c r="C172" s="29" t="inlineStr">
         <is>
-          <t>RH_August_Mean</t>
+          <t>RH_February_Mean</t>
         </is>
       </c>
       <c r="D172" s="18" t="inlineStr">
@@ -7695,7 +7695,7 @@
       </c>
       <c r="E172" s="12" t="inlineStr">
         <is>
-          <t>متوسط الرطوبة النسبية عند ارتفاع 2 متر لشهر أغسطس عبر فترة الرصد.</t>
+          <t>متوسط الرطوبة النسبية عند ارتفاع 2 متر لشهر فبراير عبر فترة الرصد.</t>
         </is>
       </c>
       <c r="F172" s="19" t="inlineStr">
@@ -7705,7 +7705,7 @@
       </c>
       <c r="G172" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط الرطوبة النسبية لشهر أغسطس (%)</t>
+          <t>خريطة متوسط الرطوبة النسبية لشهر فبراير (%)</t>
         </is>
       </c>
     </row>
@@ -7715,12 +7715,12 @@
       </c>
       <c r="B173" s="5" t="inlineStr">
         <is>
-          <t>RH_SepMean</t>
+          <t>RH_MarMean</t>
         </is>
       </c>
       <c r="C173" s="31" t="inlineStr">
         <is>
-          <t>RH_September_Mean</t>
+          <t>RH_March_Mean</t>
         </is>
       </c>
       <c r="D173" s="15" t="inlineStr">
@@ -7730,7 +7730,7 @@
       </c>
       <c r="E173" s="7" t="inlineStr">
         <is>
-          <t>متوسط الرطوبة النسبية عند ارتفاع 2 متر لشهر سبتمبر عبر فترة الرصد.</t>
+          <t>متوسط الرطوبة النسبية عند ارتفاع 2 متر لشهر مارس عبر فترة الرصد.</t>
         </is>
       </c>
       <c r="F173" s="16" t="inlineStr">
@@ -7740,7 +7740,7 @@
       </c>
       <c r="G173" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط الرطوبة النسبية لشهر سبتمبر (%)</t>
+          <t>خريطة متوسط الرطوبة النسبية لشهر مارس (%)</t>
         </is>
       </c>
     </row>
@@ -7750,12 +7750,12 @@
       </c>
       <c r="B174" s="10" t="inlineStr">
         <is>
-          <t>RH_OctMean</t>
+          <t>RH_AprMean</t>
         </is>
       </c>
       <c r="C174" s="29" t="inlineStr">
         <is>
-          <t>RH_October_Mean</t>
+          <t>RH_April_Mean</t>
         </is>
       </c>
       <c r="D174" s="18" t="inlineStr">
@@ -7765,7 +7765,7 @@
       </c>
       <c r="E174" s="12" t="inlineStr">
         <is>
-          <t>متوسط الرطوبة النسبية عند ارتفاع 2 متر لشهر أكتوبر عبر فترة الرصد.</t>
+          <t>متوسط الرطوبة النسبية عند ارتفاع 2 متر لشهر أبريل عبر فترة الرصد.</t>
         </is>
       </c>
       <c r="F174" s="19" t="inlineStr">
@@ -7775,7 +7775,7 @@
       </c>
       <c r="G174" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط الرطوبة النسبية لشهر أكتوبر (%)</t>
+          <t>خريطة متوسط الرطوبة النسبية لشهر أبريل (%)</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="B175" s="5" t="inlineStr">
         <is>
-          <t>RH_NovMean</t>
+          <t>RH_MayMean</t>
         </is>
       </c>
       <c r="C175" s="31" t="inlineStr">
         <is>
-          <t>RH_November_Mean</t>
+          <t>RH_May_Mean</t>
         </is>
       </c>
       <c r="D175" s="15" t="inlineStr">
@@ -7800,7 +7800,7 @@
       </c>
       <c r="E175" s="7" t="inlineStr">
         <is>
-          <t>متوسط الرطوبة النسبية عند ارتفاع 2 متر لشهر نوفمبر عبر فترة الرصد.</t>
+          <t>متوسط الرطوبة النسبية عند ارتفاع 2 متر لشهر مايو عبر فترة الرصد.</t>
         </is>
       </c>
       <c r="F175" s="16" t="inlineStr">
@@ -7810,7 +7810,7 @@
       </c>
       <c r="G175" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط الرطوبة النسبية لشهر نوفمبر (%)</t>
+          <t>خريطة متوسط الرطوبة النسبية لشهر مايو (%)</t>
         </is>
       </c>
     </row>
@@ -7820,12 +7820,12 @@
       </c>
       <c r="B176" s="10" t="inlineStr">
         <is>
-          <t>RH_DecMean</t>
+          <t>RH_JunMean</t>
         </is>
       </c>
       <c r="C176" s="29" t="inlineStr">
         <is>
-          <t>RH_December_Mean</t>
+          <t>RH_June_Mean</t>
         </is>
       </c>
       <c r="D176" s="18" t="inlineStr">
@@ -7835,7 +7835,7 @@
       </c>
       <c r="E176" s="12" t="inlineStr">
         <is>
-          <t>متوسط الرطوبة النسبية عند ارتفاع 2 متر لشهر ديسمبر عبر فترة الرصد.</t>
+          <t>متوسط الرطوبة النسبية عند ارتفاع 2 متر لشهر يونيو عبر فترة الرصد.</t>
         </is>
       </c>
       <c r="F176" s="19" t="inlineStr">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="G176" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط الرطوبة النسبية لشهر ديسمبر (%)</t>
+          <t>خريطة متوسط الرطوبة النسبية لشهر يونيو (%)</t>
         </is>
       </c>
     </row>
@@ -7855,32 +7855,32 @@
       </c>
       <c r="B177" s="5" t="inlineStr">
         <is>
-          <t>Sol_AnMean</t>
+          <t>RH_JulMean</t>
         </is>
       </c>
       <c r="C177" s="31" t="inlineStr">
         <is>
-          <t>Sol_Annual_Mean</t>
+          <t>RH_July_Mean</t>
         </is>
       </c>
       <c r="D177" s="15" t="inlineStr">
         <is>
-          <t>08_Solar_Radiation (الإشعاع الشمسي)</t>
+          <t>06_Relative_Humidity (الرطوبة النسبية)</t>
         </is>
       </c>
       <c r="E177" s="7" t="inlineStr">
         <is>
-          <t>المتوسط اليومي السنوي للإشعاع الشمسي الكلي السطحي الواصل لسطح الأرض في كافة ظروف السماء.</t>
+          <t>متوسط الرطوبة النسبية عند ارتفاع 2 متر لشهر يوليو عبر فترة الرصد.</t>
         </is>
       </c>
       <c r="F177" s="16" t="inlineStr">
         <is>
-          <t>kWh/m²/day</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G177" s="32" t="inlineStr">
         <is>
-          <t>خريطة المتوسط اليومي السنوي للإشعاع الشمسي (kWh/m²/day)</t>
+          <t>خريطة متوسط الرطوبة النسبية لشهر يوليو (%)</t>
         </is>
       </c>
     </row>
@@ -7890,32 +7890,32 @@
       </c>
       <c r="B178" s="10" t="inlineStr">
         <is>
-          <t>Sol_MonMea</t>
+          <t>RH_AugMean</t>
         </is>
       </c>
       <c r="C178" s="29" t="inlineStr">
         <is>
-          <t>Sol_Month_Mean</t>
+          <t>RH_August_Mean</t>
         </is>
       </c>
       <c r="D178" s="18" t="inlineStr">
         <is>
-          <t>08_Solar_Radiation (الإشعاع الشمسي)</t>
+          <t>06_Relative_Humidity (الرطوبة النسبية)</t>
         </is>
       </c>
       <c r="E178" s="12" t="inlineStr">
         <is>
-          <t>المتوسط الشهري للإشعاع الشمسي اليومي الساقط على السطح الأفقي (متوسط الـ 12 شهراً).</t>
+          <t>متوسط الرطوبة النسبية عند ارتفاع 2 متر لشهر أغسطس عبر فترة الرصد.</t>
         </is>
       </c>
       <c r="F178" s="19" t="inlineStr">
         <is>
-          <t>kWh/m²/day</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G178" s="30" t="inlineStr">
         <is>
-          <t>خريطة المتوسط الشهري للإشعاع الشمسي اليومي (kWh/m²/day)</t>
+          <t>خريطة متوسط الرطوبة النسبية لشهر أغسطس (%)</t>
         </is>
       </c>
     </row>
@@ -7925,32 +7925,32 @@
       </c>
       <c r="B179" s="5" t="inlineStr">
         <is>
-          <t>Sol_AnTot</t>
+          <t>RH_SepMean</t>
         </is>
       </c>
       <c r="C179" s="31" t="inlineStr">
         <is>
-          <t>Sol_Annual_Total</t>
+          <t>RH_September_Mean</t>
         </is>
       </c>
       <c r="D179" s="15" t="inlineStr">
         <is>
-          <t>08_Solar_Radiation (الإشعاع الشمسي)</t>
+          <t>06_Relative_Humidity (الرطوبة النسبية)</t>
         </is>
       </c>
       <c r="E179" s="7" t="inlineStr">
         <is>
-          <t>إجمالي الطاقة الشمسية السنوية التراكمية الساقطة على المتر المربع في السنة كاملة.</t>
+          <t>متوسط الرطوبة النسبية عند ارتفاع 2 متر لشهر سبتمبر عبر فترة الرصد.</t>
         </is>
       </c>
       <c r="F179" s="16" t="inlineStr">
         <is>
-          <t>kWh/m²/year</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G179" s="32" t="inlineStr">
         <is>
-          <t>خريطة إجمالي الطاقة الشمسية السنوية التراكمية (kWh/m²/year)</t>
+          <t>خريطة متوسط الرطوبة النسبية لشهر سبتمبر (%)</t>
         </is>
       </c>
     </row>
@@ -7960,32 +7960,32 @@
       </c>
       <c r="B180" s="10" t="inlineStr">
         <is>
-          <t>Sol_WnMean</t>
+          <t>RH_OctMean</t>
         </is>
       </c>
       <c r="C180" s="29" t="inlineStr">
         <is>
-          <t>Sol_Winter_Mean</t>
+          <t>RH_October_Mean</t>
         </is>
       </c>
       <c r="D180" s="18" t="inlineStr">
         <is>
-          <t>08_Solar_Radiation (الإشعاع الشمسي)</t>
+          <t>06_Relative_Humidity (الرطوبة النسبية)</t>
         </is>
       </c>
       <c r="E180" s="12" t="inlineStr">
         <is>
-          <t>متوسط الإشعاع الشمسي اليومي لفصل الشتاء الأرصادي (DJF).</t>
+          <t>متوسط الرطوبة النسبية عند ارتفاع 2 متر لشهر أكتوبر عبر فترة الرصد.</t>
         </is>
       </c>
       <c r="F180" s="19" t="inlineStr">
         <is>
-          <t>kWh/m²/day</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G180" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط الإشعاع الشمسي خلال فصل الشتاء (kWh/m²/day)</t>
+          <t>خريطة متوسط الرطوبة النسبية لشهر أكتوبر (%)</t>
         </is>
       </c>
     </row>
@@ -7995,32 +7995,32 @@
       </c>
       <c r="B181" s="5" t="inlineStr">
         <is>
-          <t>Sol_SpMean</t>
+          <t>RH_NovMean</t>
         </is>
       </c>
       <c r="C181" s="31" t="inlineStr">
         <is>
-          <t>Sol_Spring_Mean</t>
+          <t>RH_November_Mean</t>
         </is>
       </c>
       <c r="D181" s="15" t="inlineStr">
         <is>
-          <t>08_Solar_Radiation (الإشعاع الشمسي)</t>
+          <t>06_Relative_Humidity (الرطوبة النسبية)</t>
         </is>
       </c>
       <c r="E181" s="7" t="inlineStr">
         <is>
-          <t>متوسط الإشعاع الشمسي اليومي لفصل الربيع الأرصادي (MAM).</t>
+          <t>متوسط الرطوبة النسبية عند ارتفاع 2 متر لشهر نوفمبر عبر فترة الرصد.</t>
         </is>
       </c>
       <c r="F181" s="16" t="inlineStr">
         <is>
-          <t>kWh/m²/day</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G181" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط الإشعاع الشمسي خلال فصل الربيع (kWh/m²/day)</t>
+          <t>خريطة متوسط الرطوبة النسبية لشهر نوفمبر (%)</t>
         </is>
       </c>
     </row>
@@ -8030,32 +8030,32 @@
       </c>
       <c r="B182" s="10" t="inlineStr">
         <is>
-          <t>Sol_SuMean</t>
+          <t>RH_DecMean</t>
         </is>
       </c>
       <c r="C182" s="29" t="inlineStr">
         <is>
-          <t>Sol_Summer_Mean</t>
+          <t>RH_December_Mean</t>
         </is>
       </c>
       <c r="D182" s="18" t="inlineStr">
         <is>
-          <t>08_Solar_Radiation (الإشعاع الشمسي)</t>
+          <t>06_Relative_Humidity (الرطوبة النسبية)</t>
         </is>
       </c>
       <c r="E182" s="12" t="inlineStr">
         <is>
-          <t>متوسط الإشعاع الشمسي اليومي لفصل الصيف الأرصادي (JJA).</t>
+          <t>متوسط الرطوبة النسبية عند ارتفاع 2 متر لشهر ديسمبر عبر فترة الرصد.</t>
         </is>
       </c>
       <c r="F182" s="19" t="inlineStr">
         <is>
-          <t>kWh/m²/day</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G182" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط الإشعاع الشمسي خلال فصل الصيف (kWh/m²/day)</t>
+          <t>خريطة متوسط الرطوبة النسبية لشهر ديسمبر (%)</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="B183" s="5" t="inlineStr">
         <is>
-          <t>Sol_AuMean</t>
+          <t>Sol_AnMean</t>
         </is>
       </c>
       <c r="C183" s="31" t="inlineStr">
         <is>
-          <t>Sol_Autumn_Mean</t>
+          <t>Sol_Annual_Mean</t>
         </is>
       </c>
       <c r="D183" s="15" t="inlineStr">
@@ -8080,7 +8080,7 @@
       </c>
       <c r="E183" s="7" t="inlineStr">
         <is>
-          <t>متوسط الإشعاع الشمسي اليومي لفصل الخريف الأرصادي (SON).</t>
+          <t>المتوسط اليومي السنوي للإشعاع الشمسي الكلي السطحي الواصل لسطح الأرض في كافة ظروف السماء.</t>
         </is>
       </c>
       <c r="F183" s="16" t="inlineStr">
@@ -8090,7 +8090,7 @@
       </c>
       <c r="G183" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط الإشعاع الشمسي خلال فصل الخريف (kWh/m²/day)</t>
+          <t>خريطة المتوسط اليومي السنوي للإشعاع الشمسي (kWh/m²/day)</t>
         </is>
       </c>
     </row>
@@ -8100,12 +8100,12 @@
       </c>
       <c r="B184" s="10" t="inlineStr">
         <is>
-          <t>Sol_AnRng</t>
+          <t>Sol_MonMea</t>
         </is>
       </c>
       <c r="C184" s="29" t="inlineStr">
         <is>
-          <t>Sol_Annual_Range</t>
+          <t>Sol_Month_Mean</t>
         </is>
       </c>
       <c r="D184" s="18" t="inlineStr">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="E184" s="12" t="inlineStr">
         <is>
-          <t>المدى السنوي للإشعاع الشمسي (الفارق بين ذروة الإشعاع في الصيف وأدناه في الشتاء).</t>
+          <t>المتوسط الشهري للإشعاع الشمسي اليومي الساقط على السطح الأفقي (متوسط الـ 12 شهراً).</t>
         </is>
       </c>
       <c r="F184" s="19" t="inlineStr">
@@ -8125,7 +8125,7 @@
       </c>
       <c r="G184" s="30" t="inlineStr">
         <is>
-          <t>خريطة المدى السنوي للإشعاع الشمسي (kWh/m²/day)</t>
+          <t>خريطة المتوسط الشهري للإشعاع الشمسي اليومي (kWh/m²/day)</t>
         </is>
       </c>
     </row>
@@ -8135,12 +8135,12 @@
       </c>
       <c r="B185" s="5" t="inlineStr">
         <is>
-          <t>Sol_JanMn</t>
+          <t>Sol_AnTot</t>
         </is>
       </c>
       <c r="C185" s="31" t="inlineStr">
         <is>
-          <t>Sol_January_Mean</t>
+          <t>Sol_Annual_Total</t>
         </is>
       </c>
       <c r="D185" s="15" t="inlineStr">
@@ -8150,17 +8150,17 @@
       </c>
       <c r="E185" s="7" t="inlineStr">
         <is>
-          <t>المعدل اليومي للإشعاع الشمسي الكلي الساقط على السطح الأفقي لشهر يناير.</t>
+          <t>إجمالي الطاقة الشمسية السنوية التراكمية الساقطة على المتر المربع في السنة كاملة.</t>
         </is>
       </c>
       <c r="F185" s="16" t="inlineStr">
         <is>
-          <t>kWh/m²/day</t>
+          <t>kWh/m²/year</t>
         </is>
       </c>
       <c r="G185" s="32" t="inlineStr">
         <is>
-          <t>خريطة المعدل اليومي للإشعاع الشمسي لشهر يناير (kWh/m²/day)</t>
+          <t>خريطة إجمالي الطاقة الشمسية السنوية التراكمية (kWh/m²/year)</t>
         </is>
       </c>
     </row>
@@ -8170,12 +8170,12 @@
       </c>
       <c r="B186" s="10" t="inlineStr">
         <is>
-          <t>Sol_FebMn</t>
+          <t>Sol_WnMean</t>
         </is>
       </c>
       <c r="C186" s="29" t="inlineStr">
         <is>
-          <t>Sol_February_Mean</t>
+          <t>Sol_Winter_Mean</t>
         </is>
       </c>
       <c r="D186" s="18" t="inlineStr">
@@ -8185,7 +8185,7 @@
       </c>
       <c r="E186" s="12" t="inlineStr">
         <is>
-          <t>المعدل اليومي للإشعاع الشمسي الكلي الساقط على السطح الأفقي لشهر فبراير.</t>
+          <t>متوسط الإشعاع الشمسي اليومي لفصل الشتاء الأرصادي (DJF).</t>
         </is>
       </c>
       <c r="F186" s="19" t="inlineStr">
@@ -8195,7 +8195,7 @@
       </c>
       <c r="G186" s="30" t="inlineStr">
         <is>
-          <t>خريطة المعدل اليومي للإشعاع الشمسي لشهر فبراير (kWh/m²/day)</t>
+          <t>خريطة متوسط الإشعاع الشمسي خلال فصل الشتاء (kWh/m²/day)</t>
         </is>
       </c>
     </row>
@@ -8205,12 +8205,12 @@
       </c>
       <c r="B187" s="5" t="inlineStr">
         <is>
-          <t>Sol_MarMn</t>
+          <t>Sol_SpMean</t>
         </is>
       </c>
       <c r="C187" s="31" t="inlineStr">
         <is>
-          <t>Sol_March_Mean</t>
+          <t>Sol_Spring_Mean</t>
         </is>
       </c>
       <c r="D187" s="15" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="E187" s="7" t="inlineStr">
         <is>
-          <t>المعدل اليومي للإشعاع الشمسي الكلي الساقط على السطح الأفقي لشهر مارس.</t>
+          <t>متوسط الإشعاع الشمسي اليومي لفصل الربيع الأرصادي (MAM).</t>
         </is>
       </c>
       <c r="F187" s="16" t="inlineStr">
@@ -8230,7 +8230,7 @@
       </c>
       <c r="G187" s="32" t="inlineStr">
         <is>
-          <t>خريطة المعدل اليومي للإشعاع الشمسي لشهر مارس (kWh/m²/day)</t>
+          <t>خريطة متوسط الإشعاع الشمسي خلال فصل الربيع (kWh/m²/day)</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="B188" s="10" t="inlineStr">
         <is>
-          <t>Sol_AprMn</t>
+          <t>Sol_SuMean</t>
         </is>
       </c>
       <c r="C188" s="29" t="inlineStr">
         <is>
-          <t>Sol_April_Mean</t>
+          <t>Sol_Summer_Mean</t>
         </is>
       </c>
       <c r="D188" s="18" t="inlineStr">
@@ -8255,7 +8255,7 @@
       </c>
       <c r="E188" s="12" t="inlineStr">
         <is>
-          <t>المعدل اليومي للإشعاع الشمسي الكلي الساقط على السطح الأفقي لشهر أبريل.</t>
+          <t>متوسط الإشعاع الشمسي اليومي لفصل الصيف الأرصادي (JJA).</t>
         </is>
       </c>
       <c r="F188" s="19" t="inlineStr">
@@ -8265,7 +8265,7 @@
       </c>
       <c r="G188" s="30" t="inlineStr">
         <is>
-          <t>خريطة المعدل اليومي للإشعاع الشمسي لشهر أبريل (kWh/m²/day)</t>
+          <t>خريطة متوسط الإشعاع الشمسي خلال فصل الصيف (kWh/m²/day)</t>
         </is>
       </c>
     </row>
@@ -8275,12 +8275,12 @@
       </c>
       <c r="B189" s="5" t="inlineStr">
         <is>
-          <t>Sol_MayMn</t>
+          <t>Sol_AuMean</t>
         </is>
       </c>
       <c r="C189" s="31" t="inlineStr">
         <is>
-          <t>Sol_May_Mean</t>
+          <t>Sol_Autumn_Mean</t>
         </is>
       </c>
       <c r="D189" s="15" t="inlineStr">
@@ -8290,7 +8290,7 @@
       </c>
       <c r="E189" s="7" t="inlineStr">
         <is>
-          <t>المعدل اليومي للإشعاع الشمسي الكلي الساقط على السطح الأفقي لشهر مايو.</t>
+          <t>متوسط الإشعاع الشمسي اليومي لفصل الخريف الأرصادي (SON).</t>
         </is>
       </c>
       <c r="F189" s="16" t="inlineStr">
@@ -8300,7 +8300,7 @@
       </c>
       <c r="G189" s="32" t="inlineStr">
         <is>
-          <t>خريطة المعدل اليومي للإشعاع الشمسي لشهر مايو (kWh/m²/day)</t>
+          <t>خريطة متوسط الإشعاع الشمسي خلال فصل الخريف (kWh/m²/day)</t>
         </is>
       </c>
     </row>
@@ -8310,12 +8310,12 @@
       </c>
       <c r="B190" s="10" t="inlineStr">
         <is>
-          <t>Sol_JunMn</t>
+          <t>Sol_AnRng</t>
         </is>
       </c>
       <c r="C190" s="29" t="inlineStr">
         <is>
-          <t>Sol_June_Mean</t>
+          <t>Sol_Annual_Range</t>
         </is>
       </c>
       <c r="D190" s="18" t="inlineStr">
@@ -8325,7 +8325,7 @@
       </c>
       <c r="E190" s="12" t="inlineStr">
         <is>
-          <t>المعدل اليومي للإشعاع الشمسي الكلي الساقط على السطح الأفقي لشهر يونيو.</t>
+          <t>المدى السنوي للإشعاع الشمسي (الفارق بين ذروة الإشعاع في الصيف وأدناه في الشتاء).</t>
         </is>
       </c>
       <c r="F190" s="19" t="inlineStr">
@@ -8335,7 +8335,7 @@
       </c>
       <c r="G190" s="30" t="inlineStr">
         <is>
-          <t>خريطة المعدل اليومي للإشعاع الشمسي لشهر يونيو (kWh/m²/day)</t>
+          <t>خريطة المدى السنوي للإشعاع الشمسي (kWh/m²/day)</t>
         </is>
       </c>
     </row>
@@ -8345,12 +8345,12 @@
       </c>
       <c r="B191" s="5" t="inlineStr">
         <is>
-          <t>Sol_JulMn</t>
+          <t>Sol_SeaRng</t>
         </is>
       </c>
       <c r="C191" s="31" t="inlineStr">
         <is>
-          <t>Sol_July_Mean</t>
+          <t>Sol_Seasonal_Range</t>
         </is>
       </c>
       <c r="D191" s="15" t="inlineStr">
@@ -8360,7 +8360,7 @@
       </c>
       <c r="E191" s="7" t="inlineStr">
         <is>
-          <t>المعدل اليومي للإشعاع الشمسي الكلي الساقط على السطح الأفقي لشهر يوليو.</t>
+          <t>المدى الفصلي للإشعاع الشمسي اليومي (الفارق بين فصول السنة).</t>
         </is>
       </c>
       <c r="F191" s="16" t="inlineStr">
@@ -8370,7 +8370,7 @@
       </c>
       <c r="G191" s="32" t="inlineStr">
         <is>
-          <t>خريطة المعدل اليومي للإشعاع الشمسي لشهر يوليو (kWh/m²/day)</t>
+          <t>خريطة المدى الفصلي للإشعاع الشمسي (kWh/m²/day)</t>
         </is>
       </c>
     </row>
@@ -8380,12 +8380,12 @@
       </c>
       <c r="B192" s="10" t="inlineStr">
         <is>
-          <t>Sol_AugMn</t>
+          <t>Sol_JanMn</t>
         </is>
       </c>
       <c r="C192" s="29" t="inlineStr">
         <is>
-          <t>Sol_August_Mean</t>
+          <t>Sol_January_Mean</t>
         </is>
       </c>
       <c r="D192" s="18" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="E192" s="12" t="inlineStr">
         <is>
-          <t>المعدل اليومي للإشعاع الشمسي الكلي الساقط على السطح الأفقي لشهر أغسطس.</t>
+          <t>المعدل اليومي للإشعاع الشمسي الكلي الساقط على السطح الأفقي لشهر يناير.</t>
         </is>
       </c>
       <c r="F192" s="19" t="inlineStr">
@@ -8405,7 +8405,7 @@
       </c>
       <c r="G192" s="30" t="inlineStr">
         <is>
-          <t>خريطة المعدل اليومي للإشعاع الشمسي لشهر أغسطس (kWh/m²/day)</t>
+          <t>خريطة المعدل اليومي للإشعاع الشمسي لشهر يناير (kWh/m²/day)</t>
         </is>
       </c>
     </row>
@@ -8415,12 +8415,12 @@
       </c>
       <c r="B193" s="5" t="inlineStr">
         <is>
-          <t>Sol_SepMn</t>
+          <t>Sol_FebMn</t>
         </is>
       </c>
       <c r="C193" s="31" t="inlineStr">
         <is>
-          <t>Sol_September_Mean</t>
+          <t>Sol_February_Mean</t>
         </is>
       </c>
       <c r="D193" s="15" t="inlineStr">
@@ -8430,7 +8430,7 @@
       </c>
       <c r="E193" s="7" t="inlineStr">
         <is>
-          <t>المعدل اليومي للإشعاع الشمسي الكلي الساقط على السطح الأفقي لشهر سبتمبر.</t>
+          <t>المعدل اليومي للإشعاع الشمسي الكلي الساقط على السطح الأفقي لشهر فبراير.</t>
         </is>
       </c>
       <c r="F193" s="16" t="inlineStr">
@@ -8440,7 +8440,7 @@
       </c>
       <c r="G193" s="32" t="inlineStr">
         <is>
-          <t>خريطة المعدل اليومي للإشعاع الشمسي لشهر سبتمبر (kWh/m²/day)</t>
+          <t>خريطة المعدل اليومي للإشعاع الشمسي لشهر فبراير (kWh/m²/day)</t>
         </is>
       </c>
     </row>
@@ -8450,12 +8450,12 @@
       </c>
       <c r="B194" s="10" t="inlineStr">
         <is>
-          <t>Sol_OctMn</t>
+          <t>Sol_MarMn</t>
         </is>
       </c>
       <c r="C194" s="29" t="inlineStr">
         <is>
-          <t>Sol_October_Mean</t>
+          <t>Sol_March_Mean</t>
         </is>
       </c>
       <c r="D194" s="18" t="inlineStr">
@@ -8465,7 +8465,7 @@
       </c>
       <c r="E194" s="12" t="inlineStr">
         <is>
-          <t>المعدل اليومي للإشعاع الشمسي الكلي الساقط على السطح الأفقي لشهر أكتوبر.</t>
+          <t>المعدل اليومي للإشعاع الشمسي الكلي الساقط على السطح الأفقي لشهر مارس.</t>
         </is>
       </c>
       <c r="F194" s="19" t="inlineStr">
@@ -8475,7 +8475,7 @@
       </c>
       <c r="G194" s="30" t="inlineStr">
         <is>
-          <t>خريطة المعدل اليومي للإشعاع الشمسي لشهر أكتوبر (kWh/m²/day)</t>
+          <t>خريطة المعدل اليومي للإشعاع الشمسي لشهر مارس (kWh/m²/day)</t>
         </is>
       </c>
     </row>
@@ -8485,12 +8485,12 @@
       </c>
       <c r="B195" s="5" t="inlineStr">
         <is>
-          <t>Sol_NovMn</t>
+          <t>Sol_AprMn</t>
         </is>
       </c>
       <c r="C195" s="31" t="inlineStr">
         <is>
-          <t>Sol_November_Mean</t>
+          <t>Sol_April_Mean</t>
         </is>
       </c>
       <c r="D195" s="15" t="inlineStr">
@@ -8500,7 +8500,7 @@
       </c>
       <c r="E195" s="7" t="inlineStr">
         <is>
-          <t>المعدل اليومي للإشعاع الشمسي الكلي الساقط على السطح الأفقي لشهر نوفمبر.</t>
+          <t>المعدل اليومي للإشعاع الشمسي الكلي الساقط على السطح الأفقي لشهر أبريل.</t>
         </is>
       </c>
       <c r="F195" s="16" t="inlineStr">
@@ -8510,7 +8510,7 @@
       </c>
       <c r="G195" s="32" t="inlineStr">
         <is>
-          <t>خريطة المعدل اليومي للإشعاع الشمسي لشهر نوفمبر (kWh/m²/day)</t>
+          <t>خريطة المعدل اليومي للإشعاع الشمسي لشهر أبريل (kWh/m²/day)</t>
         </is>
       </c>
     </row>
@@ -8520,12 +8520,12 @@
       </c>
       <c r="B196" s="10" t="inlineStr">
         <is>
-          <t>Sol_DecMn</t>
+          <t>Sol_MayMn</t>
         </is>
       </c>
       <c r="C196" s="29" t="inlineStr">
         <is>
-          <t>Sol_December_Mean</t>
+          <t>Sol_May_Mean</t>
         </is>
       </c>
       <c r="D196" s="18" t="inlineStr">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="E196" s="12" t="inlineStr">
         <is>
-          <t>المعدل اليومي للإشعاع الشمسي الكلي الساقط على السطح الأفقي لشهر ديسمبر.</t>
+          <t>المعدل اليومي للإشعاع الشمسي الكلي الساقط على السطح الأفقي لشهر مايو.</t>
         </is>
       </c>
       <c r="F196" s="19" t="inlineStr">
@@ -8545,7 +8545,7 @@
       </c>
       <c r="G196" s="30" t="inlineStr">
         <is>
-          <t>خريطة المعدل اليومي للإشعاع الشمسي لشهر ديسمبر (kWh/m²/day)</t>
+          <t>خريطة المعدل اليومي للإشعاع الشمسي لشهر مايو (kWh/m²/day)</t>
         </is>
       </c>
     </row>
@@ -8555,32 +8555,32 @@
       </c>
       <c r="B197" s="5" t="inlineStr">
         <is>
-          <t>UV_AnMean</t>
+          <t>Sol_JunMn</t>
         </is>
       </c>
       <c r="C197" s="31" t="inlineStr">
         <is>
-          <t>UV_Annual_Mean</t>
+          <t>Sol_June_Mean</t>
         </is>
       </c>
       <c r="D197" s="15" t="inlineStr">
         <is>
-          <t>09_UV_Index (الأشعة فوق البنفسجية)</t>
+          <t>08_Solar_Radiation (الإشعاع الشمسي)</t>
         </is>
       </c>
       <c r="E197" s="7" t="inlineStr">
         <is>
-          <t>المتوسط السنوي لمؤشر الأشعة فوق البنفسجية عند الظهيرة وفق منظومة منظمة الصحة العالمية.</t>
+          <t>المعدل اليومي للإشعاع الشمسي الكلي الساقط على السطح الأفقي لشهر يونيو.</t>
         </is>
       </c>
       <c r="F197" s="16" t="inlineStr">
         <is>
-          <t>مؤشر (0-16+)</t>
+          <t>kWh/m²/day</t>
         </is>
       </c>
       <c r="G197" s="32" t="inlineStr">
         <is>
-          <t>خريطة المتوسط السنوي لمؤشر الأشعة فوق البنفسجية (UV)</t>
+          <t>خريطة المعدل اليومي للإشعاع الشمسي لشهر يونيو (kWh/m²/day)</t>
         </is>
       </c>
     </row>
@@ -8590,32 +8590,32 @@
       </c>
       <c r="B198" s="10" t="inlineStr">
         <is>
-          <t>UV_MonMean</t>
+          <t>Sol_JulMn</t>
         </is>
       </c>
       <c r="C198" s="29" t="inlineStr">
         <is>
-          <t>UV_Month_Mean</t>
+          <t>Sol_July_Mean</t>
         </is>
       </c>
       <c r="D198" s="18" t="inlineStr">
         <is>
-          <t>09_UV_Index (مؤشر الأشعة فوق البنفسجية)</t>
+          <t>08_Solar_Radiation (الإشعاع الشمسي)</t>
         </is>
       </c>
       <c r="E198" s="12" t="inlineStr">
         <is>
-          <t>المتوسط الشهري لمؤشر الأشعة فوق البنفسجية في سماء صافية (متوسط الـ 12 شهراً).</t>
+          <t>المعدل اليومي للإشعاع الشمسي الكلي الساقط على السطح الأفقي لشهر يوليو.</t>
         </is>
       </c>
       <c r="F198" s="19" t="inlineStr">
         <is>
-          <t>Index</t>
+          <t>kWh/m²/day</t>
         </is>
       </c>
       <c r="G198" s="30" t="inlineStr">
         <is>
-          <t>خريطة المتوسط الشهري لمؤشر الأشعة فوق البنفسجية</t>
+          <t>خريطة المعدل اليومي للإشعاع الشمسي لشهر يوليو (kWh/m²/day)</t>
         </is>
       </c>
     </row>
@@ -8625,32 +8625,32 @@
       </c>
       <c r="B199" s="5" t="inlineStr">
         <is>
-          <t>UV_WnMean</t>
+          <t>Sol_AugMn</t>
         </is>
       </c>
       <c r="C199" s="31" t="inlineStr">
         <is>
-          <t>UV_Winter_Mean</t>
+          <t>Sol_August_Mean</t>
         </is>
       </c>
       <c r="D199" s="15" t="inlineStr">
         <is>
-          <t>09_UV_Index (الأشعة فوق البنفسجية)</t>
+          <t>08_Solar_Radiation (الإشعاع الشمسي)</t>
         </is>
       </c>
       <c r="E199" s="7" t="inlineStr">
         <is>
-          <t>متوسط مؤشر الأشعة فوق البنفسجية لفصل الشتاء الأرصادي (DJF).</t>
+          <t>المعدل اليومي للإشعاع الشمسي الكلي الساقط على السطح الأفقي لشهر أغسطس.</t>
         </is>
       </c>
       <c r="F199" s="16" t="inlineStr">
         <is>
-          <t>مؤشر (0-16+)</t>
+          <t>kWh/m²/day</t>
         </is>
       </c>
       <c r="G199" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية خلال فصل الشتاء</t>
+          <t>خريطة المعدل اليومي للإشعاع الشمسي لشهر أغسطس (kWh/m²/day)</t>
         </is>
       </c>
     </row>
@@ -8660,32 +8660,32 @@
       </c>
       <c r="B200" s="10" t="inlineStr">
         <is>
-          <t>UV_SpMean</t>
+          <t>Sol_SepMn</t>
         </is>
       </c>
       <c r="C200" s="29" t="inlineStr">
         <is>
-          <t>UV_Spring_Mean</t>
+          <t>Sol_September_Mean</t>
         </is>
       </c>
       <c r="D200" s="18" t="inlineStr">
         <is>
-          <t>09_UV_Index (الأشعة فوق البنفسجية)</t>
+          <t>08_Solar_Radiation (الإشعاع الشمسي)</t>
         </is>
       </c>
       <c r="E200" s="12" t="inlineStr">
         <is>
-          <t>متوسط مؤشر الأشعة فوق البنفسجية لفصل الربيع الأرصادي (MAM).</t>
+          <t>المعدل اليومي للإشعاع الشمسي الكلي الساقط على السطح الأفقي لشهر سبتمبر.</t>
         </is>
       </c>
       <c r="F200" s="19" t="inlineStr">
         <is>
-          <t>مؤشر (0-16+)</t>
+          <t>kWh/m²/day</t>
         </is>
       </c>
       <c r="G200" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية خلال فصل الربيع</t>
+          <t>خريطة المعدل اليومي للإشعاع الشمسي لشهر سبتمبر (kWh/m²/day)</t>
         </is>
       </c>
     </row>
@@ -8695,32 +8695,32 @@
       </c>
       <c r="B201" s="5" t="inlineStr">
         <is>
-          <t>UV_SuMean</t>
+          <t>Sol_OctMn</t>
         </is>
       </c>
       <c r="C201" s="31" t="inlineStr">
         <is>
-          <t>UV_Summer_Mean</t>
+          <t>Sol_October_Mean</t>
         </is>
       </c>
       <c r="D201" s="15" t="inlineStr">
         <is>
-          <t>09_UV_Index (الأشعة فوق البنفسجية)</t>
+          <t>08_Solar_Radiation (الإشعاع الشمسي)</t>
         </is>
       </c>
       <c r="E201" s="7" t="inlineStr">
         <is>
-          <t>متوسط مؤشر الأشعة فوق البنفسجية لفصل الصيف الأرصادي (JJA - ذروة مخاطر الحروق الشمسية).</t>
+          <t>المعدل اليومي للإشعاع الشمسي الكلي الساقط على السطح الأفقي لشهر أكتوبر.</t>
         </is>
       </c>
       <c r="F201" s="16" t="inlineStr">
         <is>
-          <t>مؤشر (0-16+)</t>
+          <t>kWh/m²/day</t>
         </is>
       </c>
       <c r="G201" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية خلال فصل الصيف</t>
+          <t>خريطة المعدل اليومي للإشعاع الشمسي لشهر أكتوبر (kWh/m²/day)</t>
         </is>
       </c>
     </row>
@@ -8730,32 +8730,32 @@
       </c>
       <c r="B202" s="10" t="inlineStr">
         <is>
-          <t>UV_AuMean</t>
+          <t>Sol_NovMn</t>
         </is>
       </c>
       <c r="C202" s="29" t="inlineStr">
         <is>
-          <t>UV_Autumn_Mean</t>
+          <t>Sol_November_Mean</t>
         </is>
       </c>
       <c r="D202" s="18" t="inlineStr">
         <is>
-          <t>09_UV_Index (الأشعة فوق البنفسجية)</t>
+          <t>08_Solar_Radiation (الإشعاع الشمسي)</t>
         </is>
       </c>
       <c r="E202" s="12" t="inlineStr">
         <is>
-          <t>متوسط مؤشر الأشعة فوق البنفسجية لفصل الخريف الأرصادي (SON).</t>
+          <t>المعدل اليومي للإشعاع الشمسي الكلي الساقط على السطح الأفقي لشهر نوفمبر.</t>
         </is>
       </c>
       <c r="F202" s="19" t="inlineStr">
         <is>
-          <t>مؤشر (0-16+)</t>
+          <t>kWh/m²/day</t>
         </is>
       </c>
       <c r="G202" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية خلال فصل الخريف</t>
+          <t>خريطة المعدل اليومي للإشعاع الشمسي لشهر نوفمبر (kWh/m²/day)</t>
         </is>
       </c>
     </row>
@@ -8765,32 +8765,32 @@
       </c>
       <c r="B203" s="5" t="inlineStr">
         <is>
-          <t>UV_AnRng</t>
+          <t>Sol_DecMn</t>
         </is>
       </c>
       <c r="C203" s="31" t="inlineStr">
         <is>
-          <t>UV_Annual_Range</t>
+          <t>Sol_December_Mean</t>
         </is>
       </c>
       <c r="D203" s="15" t="inlineStr">
         <is>
-          <t>09_UV_Index (الأشعة فوق البنفسجية)</t>
+          <t>08_Solar_Radiation (الإشعاع الشمسي)</t>
         </is>
       </c>
       <c r="E203" s="7" t="inlineStr">
         <is>
-          <t>المدى السنوي لمؤشر الأشعة فوق البنفسجية (الفارق بين ذروة الصيف وأدنى مستويات الشتاء).</t>
+          <t>المعدل اليومي للإشعاع الشمسي الكلي الساقط على السطح الأفقي لشهر ديسمبر.</t>
         </is>
       </c>
       <c r="F203" s="16" t="inlineStr">
         <is>
-          <t>مؤشر (0-16+)</t>
+          <t>kWh/m²/day</t>
         </is>
       </c>
       <c r="G203" s="32" t="inlineStr">
         <is>
-          <t>خريطة المدى السنوي لمؤشر الأشعة فوق البنفسجية</t>
+          <t>خريطة المعدل اليومي للإشعاع الشمسي لشهر ديسمبر (kWh/m²/day)</t>
         </is>
       </c>
     </row>
@@ -8800,12 +8800,12 @@
       </c>
       <c r="B204" s="10" t="inlineStr">
         <is>
-          <t>UV_JanMean</t>
+          <t>UV_AnMean</t>
         </is>
       </c>
       <c r="C204" s="29" t="inlineStr">
         <is>
-          <t>UV_January_Mean</t>
+          <t>UV_Annual_Mean</t>
         </is>
       </c>
       <c r="D204" s="18" t="inlineStr">
@@ -8815,7 +8815,7 @@
       </c>
       <c r="E204" s="12" t="inlineStr">
         <is>
-          <t>متوسط مؤشر الأشعة فوق البنفسجية القصوى لشهر يناير وفق معيار WHO.</t>
+          <t>المتوسط السنوي لمؤشر الأشعة فوق البنفسجية عند الظهيرة وفق منظومة منظمة الصحة العالمية.</t>
         </is>
       </c>
       <c r="F204" s="19" t="inlineStr">
@@ -8825,7 +8825,7 @@
       </c>
       <c r="G204" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية لشهر يناير</t>
+          <t>خريطة المتوسط السنوي لمؤشر الأشعة فوق البنفسجية (UV)</t>
         </is>
       </c>
     </row>
@@ -8835,32 +8835,32 @@
       </c>
       <c r="B205" s="5" t="inlineStr">
         <is>
-          <t>UV_FebMean</t>
+          <t>UV_MonMean</t>
         </is>
       </c>
       <c r="C205" s="31" t="inlineStr">
         <is>
-          <t>UV_February_Mean</t>
+          <t>UV_Month_Mean</t>
         </is>
       </c>
       <c r="D205" s="15" t="inlineStr">
         <is>
-          <t>09_UV_Index (الأشعة فوق البنفسجية)</t>
+          <t>09_UV_Index (مؤشر الأشعة فوق البنفسجية)</t>
         </is>
       </c>
       <c r="E205" s="7" t="inlineStr">
         <is>
-          <t>متوسط مؤشر الأشعة فوق البنفسجية القصوى لشهر فبراير وفق معيار WHO.</t>
+          <t>المتوسط الشهري لمؤشر الأشعة فوق البنفسجية في سماء صافية (متوسط الـ 12 شهراً).</t>
         </is>
       </c>
       <c r="F205" s="16" t="inlineStr">
         <is>
-          <t>مؤشر (0-16+)</t>
+          <t>Index</t>
         </is>
       </c>
       <c r="G205" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية لشهر فبراير</t>
+          <t>خريطة المتوسط الشهري لمؤشر الأشعة فوق البنفسجية</t>
         </is>
       </c>
     </row>
@@ -8870,12 +8870,12 @@
       </c>
       <c r="B206" s="10" t="inlineStr">
         <is>
-          <t>UV_MarMean</t>
+          <t>UV_WnMean</t>
         </is>
       </c>
       <c r="C206" s="29" t="inlineStr">
         <is>
-          <t>UV_March_Mean</t>
+          <t>UV_Winter_Mean</t>
         </is>
       </c>
       <c r="D206" s="18" t="inlineStr">
@@ -8885,7 +8885,7 @@
       </c>
       <c r="E206" s="12" t="inlineStr">
         <is>
-          <t>متوسط مؤشر الأشعة فوق البنفسجية القصوى لشهر مارس وفق معيار WHO.</t>
+          <t>متوسط مؤشر الأشعة فوق البنفسجية لفصل الشتاء الأرصادي (DJF).</t>
         </is>
       </c>
       <c r="F206" s="19" t="inlineStr">
@@ -8895,7 +8895,7 @@
       </c>
       <c r="G206" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية لشهر مارس</t>
+          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية خلال فصل الشتاء</t>
         </is>
       </c>
     </row>
@@ -8905,12 +8905,12 @@
       </c>
       <c r="B207" s="5" t="inlineStr">
         <is>
-          <t>UV_AprMean</t>
+          <t>UV_SpMean</t>
         </is>
       </c>
       <c r="C207" s="31" t="inlineStr">
         <is>
-          <t>UV_April_Mean</t>
+          <t>UV_Spring_Mean</t>
         </is>
       </c>
       <c r="D207" s="15" t="inlineStr">
@@ -8920,7 +8920,7 @@
       </c>
       <c r="E207" s="7" t="inlineStr">
         <is>
-          <t>متوسط مؤشر الأشعة فوق البنفسجية القصوى لشهر أبريل وفق معيار WHO.</t>
+          <t>متوسط مؤشر الأشعة فوق البنفسجية لفصل الربيع الأرصادي (MAM).</t>
         </is>
       </c>
       <c r="F207" s="16" t="inlineStr">
@@ -8930,7 +8930,7 @@
       </c>
       <c r="G207" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية لشهر أبريل</t>
+          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية خلال فصل الربيع</t>
         </is>
       </c>
     </row>
@@ -8940,12 +8940,12 @@
       </c>
       <c r="B208" s="10" t="inlineStr">
         <is>
-          <t>UV_MayMean</t>
+          <t>UV_SuMean</t>
         </is>
       </c>
       <c r="C208" s="29" t="inlineStr">
         <is>
-          <t>UV_May_Mean</t>
+          <t>UV_Summer_Mean</t>
         </is>
       </c>
       <c r="D208" s="18" t="inlineStr">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="E208" s="12" t="inlineStr">
         <is>
-          <t>متوسط مؤشر الأشعة فوق البنفسجية القصوى لشهر مايو وفق معيار WHO.</t>
+          <t>متوسط مؤشر الأشعة فوق البنفسجية لفصل الصيف الأرصادي (JJA - ذروة مخاطر الحروق الشمسية).</t>
         </is>
       </c>
       <c r="F208" s="19" t="inlineStr">
@@ -8965,7 +8965,7 @@
       </c>
       <c r="G208" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية لشهر مايو</t>
+          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية خلال فصل الصيف</t>
         </is>
       </c>
     </row>
@@ -8975,12 +8975,12 @@
       </c>
       <c r="B209" s="5" t="inlineStr">
         <is>
-          <t>UV_JunMean</t>
+          <t>UV_AuMean</t>
         </is>
       </c>
       <c r="C209" s="31" t="inlineStr">
         <is>
-          <t>UV_June_Mean</t>
+          <t>UV_Autumn_Mean</t>
         </is>
       </c>
       <c r="D209" s="15" t="inlineStr">
@@ -8990,7 +8990,7 @@
       </c>
       <c r="E209" s="7" t="inlineStr">
         <is>
-          <t>متوسط مؤشر الأشعة فوق البنفسجية القصوى لشهر يونيو وفق معيار WHO.</t>
+          <t>متوسط مؤشر الأشعة فوق البنفسجية لفصل الخريف الأرصادي (SON).</t>
         </is>
       </c>
       <c r="F209" s="16" t="inlineStr">
@@ -9000,7 +9000,7 @@
       </c>
       <c r="G209" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية لشهر يونيو</t>
+          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية خلال فصل الخريف</t>
         </is>
       </c>
     </row>
@@ -9010,12 +9010,12 @@
       </c>
       <c r="B210" s="10" t="inlineStr">
         <is>
-          <t>UV_JulMean</t>
+          <t>UV_AnRng</t>
         </is>
       </c>
       <c r="C210" s="29" t="inlineStr">
         <is>
-          <t>UV_July_Mean</t>
+          <t>UV_Annual_Range</t>
         </is>
       </c>
       <c r="D210" s="18" t="inlineStr">
@@ -9025,7 +9025,7 @@
       </c>
       <c r="E210" s="12" t="inlineStr">
         <is>
-          <t>متوسط مؤشر الأشعة فوق البنفسجية القصوى لشهر يوليو وفق معيار WHO.</t>
+          <t>المدى السنوي لمؤشر الأشعة فوق البنفسجية (الفارق بين ذروة الصيف وأدنى مستويات الشتاء).</t>
         </is>
       </c>
       <c r="F210" s="19" t="inlineStr">
@@ -9035,7 +9035,7 @@
       </c>
       <c r="G210" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية لشهر يوليو</t>
+          <t>خريطة المدى السنوي لمؤشر الأشعة فوق البنفسجية</t>
         </is>
       </c>
     </row>
@@ -9045,12 +9045,12 @@
       </c>
       <c r="B211" s="5" t="inlineStr">
         <is>
-          <t>UV_AugMean</t>
+          <t>UV_SeaRng</t>
         </is>
       </c>
       <c r="C211" s="31" t="inlineStr">
         <is>
-          <t>UV_August_Mean</t>
+          <t>UV_Seasonal_Range</t>
         </is>
       </c>
       <c r="D211" s="15" t="inlineStr">
@@ -9060,17 +9060,17 @@
       </c>
       <c r="E211" s="7" t="inlineStr">
         <is>
-          <t>متوسط مؤشر الأشعة فوق البنفسجية القصوى لشهر أغسطس وفق معيار WHO.</t>
+          <t>المدى الفصلي لمؤشر الأشعة فوق البنفسجية (الفارق بين فصول السنة).</t>
         </is>
       </c>
       <c r="F211" s="16" t="inlineStr">
         <is>
-          <t>مؤشر (0-16+)</t>
+          <t>مؤشر (Index)</t>
         </is>
       </c>
       <c r="G211" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية لشهر أغسطس</t>
+          <t>خريطة المدى الفصلي لمؤشر الأشعة فوق البنفسجية</t>
         </is>
       </c>
     </row>
@@ -9080,12 +9080,12 @@
       </c>
       <c r="B212" s="10" t="inlineStr">
         <is>
-          <t>UV_SepMean</t>
+          <t>UV_JanMean</t>
         </is>
       </c>
       <c r="C212" s="29" t="inlineStr">
         <is>
-          <t>UV_September_Mean</t>
+          <t>UV_January_Mean</t>
         </is>
       </c>
       <c r="D212" s="18" t="inlineStr">
@@ -9095,7 +9095,7 @@
       </c>
       <c r="E212" s="12" t="inlineStr">
         <is>
-          <t>متوسط مؤشر الأشعة فوق البنفسجية القصوى لشهر سبتمبر وفق معيار WHO.</t>
+          <t>متوسط مؤشر الأشعة فوق البنفسجية القصوى لشهر يناير وفق معيار WHO.</t>
         </is>
       </c>
       <c r="F212" s="19" t="inlineStr">
@@ -9105,7 +9105,7 @@
       </c>
       <c r="G212" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية لشهر سبتمبر</t>
+          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية لشهر يناير</t>
         </is>
       </c>
     </row>
@@ -9115,12 +9115,12 @@
       </c>
       <c r="B213" s="5" t="inlineStr">
         <is>
-          <t>UV_OctMean</t>
+          <t>UV_FebMean</t>
         </is>
       </c>
       <c r="C213" s="31" t="inlineStr">
         <is>
-          <t>UV_October_Mean</t>
+          <t>UV_February_Mean</t>
         </is>
       </c>
       <c r="D213" s="15" t="inlineStr">
@@ -9130,7 +9130,7 @@
       </c>
       <c r="E213" s="7" t="inlineStr">
         <is>
-          <t>متوسط مؤشر الأشعة فوق البنفسجية القصوى لشهر أكتوبر وفق معيار WHO.</t>
+          <t>متوسط مؤشر الأشعة فوق البنفسجية القصوى لشهر فبراير وفق معيار WHO.</t>
         </is>
       </c>
       <c r="F213" s="16" t="inlineStr">
@@ -9140,7 +9140,7 @@
       </c>
       <c r="G213" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية لشهر أكتوبر</t>
+          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية لشهر فبراير</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="B214" s="10" t="inlineStr">
         <is>
-          <t>UV_NovMean</t>
+          <t>UV_MarMean</t>
         </is>
       </c>
       <c r="C214" s="29" t="inlineStr">
         <is>
-          <t>UV_November_Mean</t>
+          <t>UV_March_Mean</t>
         </is>
       </c>
       <c r="D214" s="18" t="inlineStr">
@@ -9165,7 +9165,7 @@
       </c>
       <c r="E214" s="12" t="inlineStr">
         <is>
-          <t>متوسط مؤشر الأشعة فوق البنفسجية القصوى لشهر نوفمبر وفق معيار WHO.</t>
+          <t>متوسط مؤشر الأشعة فوق البنفسجية القصوى لشهر مارس وفق معيار WHO.</t>
         </is>
       </c>
       <c r="F214" s="19" t="inlineStr">
@@ -9175,7 +9175,7 @@
       </c>
       <c r="G214" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية لشهر نوفمبر</t>
+          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية لشهر مارس</t>
         </is>
       </c>
     </row>
@@ -9185,12 +9185,12 @@
       </c>
       <c r="B215" s="5" t="inlineStr">
         <is>
-          <t>UV_DecMean</t>
+          <t>UV_AprMean</t>
         </is>
       </c>
       <c r="C215" s="31" t="inlineStr">
         <is>
-          <t>UV_December_Mean</t>
+          <t>UV_April_Mean</t>
         </is>
       </c>
       <c r="D215" s="15" t="inlineStr">
@@ -9200,7 +9200,7 @@
       </c>
       <c r="E215" s="7" t="inlineStr">
         <is>
-          <t>متوسط مؤشر الأشعة فوق البنفسجية القصوى لشهر ديسمبر وفق معيار WHO.</t>
+          <t>متوسط مؤشر الأشعة فوق البنفسجية القصوى لشهر أبريل وفق معيار WHO.</t>
         </is>
       </c>
       <c r="F215" s="16" t="inlineStr">
@@ -9210,7 +9210,7 @@
       </c>
       <c r="G215" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية لشهر ديسمبر</t>
+          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية لشهر أبريل</t>
         </is>
       </c>
     </row>
@@ -9220,32 +9220,32 @@
       </c>
       <c r="B216" s="10" t="inlineStr">
         <is>
-          <t>Cld_AnMean</t>
+          <t>UV_MayMean</t>
         </is>
       </c>
       <c r="C216" s="29" t="inlineStr">
         <is>
-          <t>Cld_Annual_Mean</t>
+          <t>UV_May_Mean</t>
         </is>
       </c>
       <c r="D216" s="18" t="inlineStr">
         <is>
-          <t>10_Cloud_Cover (الغطاء السحابي)</t>
+          <t>09_UV_Index (الأشعة فوق البنفسجية)</t>
         </is>
       </c>
       <c r="E216" s="12" t="inlineStr">
         <is>
-          <t>المتوسط السنوي لنسبة تغطية السماء بالغيوم والسحب كنسبة مئوية.</t>
+          <t>متوسط مؤشر الأشعة فوق البنفسجية القصوى لشهر مايو وفق معيار WHO.</t>
         </is>
       </c>
       <c r="F216" s="19" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>مؤشر (0-16+)</t>
         </is>
       </c>
       <c r="G216" s="30" t="inlineStr">
         <is>
-          <t>خريطة المتوسط السنوي لنسبة الغطاء السحابي (%)</t>
+          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية لشهر مايو</t>
         </is>
       </c>
     </row>
@@ -9255,32 +9255,32 @@
       </c>
       <c r="B217" s="5" t="inlineStr">
         <is>
-          <t>Cld_MonMea</t>
+          <t>UV_JunMean</t>
         </is>
       </c>
       <c r="C217" s="31" t="inlineStr">
         <is>
-          <t>Cld_Month_Mean</t>
+          <t>UV_June_Mean</t>
         </is>
       </c>
       <c r="D217" s="15" t="inlineStr">
         <is>
-          <t>10_Cloud_Cover (الغطاء السحابي)</t>
+          <t>09_UV_Index (الأشعة فوق البنفسجية)</t>
         </is>
       </c>
       <c r="E217" s="7" t="inlineStr">
         <is>
-          <t>المتوسط الشهري لكمية الغطاء السحابي الكلي (متوسط الـ 12 شهراً).</t>
+          <t>متوسط مؤشر الأشعة فوق البنفسجية القصوى لشهر يونيو وفق معيار WHO.</t>
         </is>
       </c>
       <c r="F217" s="16" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>مؤشر (0-16+)</t>
         </is>
       </c>
       <c r="G217" s="32" t="inlineStr">
         <is>
-          <t>خريطة المتوسط الشهري للغطاء السحابي (%)</t>
+          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية لشهر يونيو</t>
         </is>
       </c>
     </row>
@@ -9290,32 +9290,32 @@
       </c>
       <c r="B218" s="10" t="inlineStr">
         <is>
-          <t>Cld_WnMean</t>
+          <t>UV_JulMean</t>
         </is>
       </c>
       <c r="C218" s="29" t="inlineStr">
         <is>
-          <t>Cld_Winter_Mean</t>
+          <t>UV_July_Mean</t>
         </is>
       </c>
       <c r="D218" s="18" t="inlineStr">
         <is>
-          <t>10_Cloud_Cover (الغطاء السحابي)</t>
+          <t>09_UV_Index (الأشعة فوق البنفسجية)</t>
         </is>
       </c>
       <c r="E218" s="12" t="inlineStr">
         <is>
-          <t>متوسط نسبة تغطية السحب لفصل الشتاء الأرصادي (DJF).</t>
+          <t>متوسط مؤشر الأشعة فوق البنفسجية القصوى لشهر يوليو وفق معيار WHO.</t>
         </is>
       </c>
       <c r="F218" s="19" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>مؤشر (0-16+)</t>
         </is>
       </c>
       <c r="G218" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط الغطاء السحابي خلال فصل الشتاء (%)</t>
+          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية لشهر يوليو</t>
         </is>
       </c>
     </row>
@@ -9325,32 +9325,32 @@
       </c>
       <c r="B219" s="5" t="inlineStr">
         <is>
-          <t>Cld_SpMean</t>
+          <t>UV_AugMean</t>
         </is>
       </c>
       <c r="C219" s="31" t="inlineStr">
         <is>
-          <t>Cld_Spring_Mean</t>
+          <t>UV_August_Mean</t>
         </is>
       </c>
       <c r="D219" s="15" t="inlineStr">
         <is>
-          <t>10_Cloud_Cover (الغطاء السحابي)</t>
+          <t>09_UV_Index (الأشعة فوق البنفسجية)</t>
         </is>
       </c>
       <c r="E219" s="7" t="inlineStr">
         <is>
-          <t>متوسط نسبة تغطية السحب لفصل الربيع الأرصادي (MAM).</t>
+          <t>متوسط مؤشر الأشعة فوق البنفسجية القصوى لشهر أغسطس وفق معيار WHO.</t>
         </is>
       </c>
       <c r="F219" s="16" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>مؤشر (0-16+)</t>
         </is>
       </c>
       <c r="G219" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط الغطاء السحابي خلال فصل الربيع (%)</t>
+          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية لشهر أغسطس</t>
         </is>
       </c>
     </row>
@@ -9360,32 +9360,32 @@
       </c>
       <c r="B220" s="10" t="inlineStr">
         <is>
-          <t>Cld_SuMean</t>
+          <t>UV_SepMean</t>
         </is>
       </c>
       <c r="C220" s="29" t="inlineStr">
         <is>
-          <t>Cld_Summer_Mean</t>
+          <t>UV_September_Mean</t>
         </is>
       </c>
       <c r="D220" s="18" t="inlineStr">
         <is>
-          <t>10_Cloud_Cover (الغطاء السحابي)</t>
+          <t>09_UV_Index (الأشعة فوق البنفسجية)</t>
         </is>
       </c>
       <c r="E220" s="12" t="inlineStr">
         <is>
-          <t>متوسط نسبة تغطية السحب لفصل الصيف الأرصادي (JJA).</t>
+          <t>متوسط مؤشر الأشعة فوق البنفسجية القصوى لشهر سبتمبر وفق معيار WHO.</t>
         </is>
       </c>
       <c r="F220" s="19" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>مؤشر (0-16+)</t>
         </is>
       </c>
       <c r="G220" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط الغطاء السحابي خلال فصل الصيف (%)</t>
+          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية لشهر سبتمبر</t>
         </is>
       </c>
     </row>
@@ -9395,32 +9395,32 @@
       </c>
       <c r="B221" s="5" t="inlineStr">
         <is>
-          <t>Cld_AuMean</t>
+          <t>UV_OctMean</t>
         </is>
       </c>
       <c r="C221" s="31" t="inlineStr">
         <is>
-          <t>Cld_Autumn_Mean</t>
+          <t>UV_October_Mean</t>
         </is>
       </c>
       <c r="D221" s="15" t="inlineStr">
         <is>
-          <t>10_Cloud_Cover (الغطاء السحابي)</t>
+          <t>09_UV_Index (الأشعة فوق البنفسجية)</t>
         </is>
       </c>
       <c r="E221" s="7" t="inlineStr">
         <is>
-          <t>متوسط نسبة تغطية السحب لفصل الخريف الأرصادي (SON).</t>
+          <t>متوسط مؤشر الأشعة فوق البنفسجية القصوى لشهر أكتوبر وفق معيار WHO.</t>
         </is>
       </c>
       <c r="F221" s="16" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>مؤشر (0-16+)</t>
         </is>
       </c>
       <c r="G221" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط الغطاء السحابي خلال فصل الخريف (%)</t>
+          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية لشهر أكتوبر</t>
         </is>
       </c>
     </row>
@@ -9430,32 +9430,32 @@
       </c>
       <c r="B222" s="10" t="inlineStr">
         <is>
-          <t>Cld_AnRng</t>
+          <t>UV_NovMean</t>
         </is>
       </c>
       <c r="C222" s="29" t="inlineStr">
         <is>
-          <t>Cld_Annual_Range</t>
+          <t>UV_November_Mean</t>
         </is>
       </c>
       <c r="D222" s="18" t="inlineStr">
         <is>
-          <t>10_Cloud_Cover (الغطاء السحابي)</t>
+          <t>09_UV_Index (الأشعة فوق البنفسجية)</t>
         </is>
       </c>
       <c r="E222" s="12" t="inlineStr">
         <is>
-          <t>المدى السنوي لتغطية السحب (الفارق بين أكثر شهور السنة غيوماً وأكثرها صفاءً).</t>
+          <t>متوسط مؤشر الأشعة فوق البنفسجية القصوى لشهر نوفمبر وفق معيار WHO.</t>
         </is>
       </c>
       <c r="F222" s="19" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>مؤشر (0-16+)</t>
         </is>
       </c>
       <c r="G222" s="30" t="inlineStr">
         <is>
-          <t>خريطة المدى السنوي لنسبة الغطاء السحابي (%)</t>
+          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية لشهر نوفمبر</t>
         </is>
       </c>
     </row>
@@ -9465,32 +9465,32 @@
       </c>
       <c r="B223" s="5" t="inlineStr">
         <is>
-          <t>Cld_JanMn</t>
+          <t>UV_DecMean</t>
         </is>
       </c>
       <c r="C223" s="31" t="inlineStr">
         <is>
-          <t>Cld_January_Mean</t>
+          <t>UV_December_Mean</t>
         </is>
       </c>
       <c r="D223" s="15" t="inlineStr">
         <is>
-          <t>10_Cloud_Cover (الغطاء السحابي)</t>
+          <t>09_UV_Index (الأشعة فوق البنفسجية)</t>
         </is>
       </c>
       <c r="E223" s="7" t="inlineStr">
         <is>
-          <t>متوسط نسبة الغطاء السحابي الكلي للسماء لشهر يناير.</t>
+          <t>متوسط مؤشر الأشعة فوق البنفسجية القصوى لشهر ديسمبر وفق معيار WHO.</t>
         </is>
       </c>
       <c r="F223" s="16" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>مؤشر (0-16+)</t>
         </is>
       </c>
       <c r="G223" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط الغطاء السحابي لشهر يناير (%)</t>
+          <t>خريطة متوسط مؤشر الأشعة فوق البنفسجية لشهر ديسمبر</t>
         </is>
       </c>
     </row>
@@ -9500,12 +9500,12 @@
       </c>
       <c r="B224" s="10" t="inlineStr">
         <is>
-          <t>Cld_FebMn</t>
+          <t>Cld_AnMean</t>
         </is>
       </c>
       <c r="C224" s="29" t="inlineStr">
         <is>
-          <t>Cld_February_Mean</t>
+          <t>Cld_Annual_Mean</t>
         </is>
       </c>
       <c r="D224" s="18" t="inlineStr">
@@ -9515,7 +9515,7 @@
       </c>
       <c r="E224" s="12" t="inlineStr">
         <is>
-          <t>متوسط نسبة الغطاء السحابي الكلي للسماء لشهر فبراير.</t>
+          <t>المتوسط السنوي لنسبة تغطية السماء بالغيوم والسحب كنسبة مئوية.</t>
         </is>
       </c>
       <c r="F224" s="19" t="inlineStr">
@@ -9525,7 +9525,7 @@
       </c>
       <c r="G224" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط الغطاء السحابي لشهر فبراير (%)</t>
+          <t>خريطة المتوسط السنوي لنسبة الغطاء السحابي (%)</t>
         </is>
       </c>
     </row>
@@ -9535,12 +9535,12 @@
       </c>
       <c r="B225" s="5" t="inlineStr">
         <is>
-          <t>Cld_MarMn</t>
+          <t>Cld_MonMea</t>
         </is>
       </c>
       <c r="C225" s="31" t="inlineStr">
         <is>
-          <t>Cld_March_Mean</t>
+          <t>Cld_Month_Mean</t>
         </is>
       </c>
       <c r="D225" s="15" t="inlineStr">
@@ -9550,7 +9550,7 @@
       </c>
       <c r="E225" s="7" t="inlineStr">
         <is>
-          <t>متوسط نسبة الغطاء السحابي الكلي للسماء لشهر مارس.</t>
+          <t>المتوسط الشهري لكمية الغطاء السحابي الكلي (متوسط الـ 12 شهراً).</t>
         </is>
       </c>
       <c r="F225" s="16" t="inlineStr">
@@ -9560,7 +9560,7 @@
       </c>
       <c r="G225" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط الغطاء السحابي لشهر مارس (%)</t>
+          <t>خريطة المتوسط الشهري للغطاء السحابي (%)</t>
         </is>
       </c>
     </row>
@@ -9570,12 +9570,12 @@
       </c>
       <c r="B226" s="10" t="inlineStr">
         <is>
-          <t>Cld_AprMn</t>
+          <t>Cld_WnMean</t>
         </is>
       </c>
       <c r="C226" s="29" t="inlineStr">
         <is>
-          <t>Cld_April_Mean</t>
+          <t>Cld_Winter_Mean</t>
         </is>
       </c>
       <c r="D226" s="18" t="inlineStr">
@@ -9585,7 +9585,7 @@
       </c>
       <c r="E226" s="12" t="inlineStr">
         <is>
-          <t>متوسط نسبة الغطاء السحابي الكلي للسماء لشهر أبريل.</t>
+          <t>متوسط نسبة تغطية السحب لفصل الشتاء الأرصادي (DJF).</t>
         </is>
       </c>
       <c r="F226" s="19" t="inlineStr">
@@ -9595,7 +9595,7 @@
       </c>
       <c r="G226" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط الغطاء السحابي لشهر أبريل (%)</t>
+          <t>خريطة متوسط الغطاء السحابي خلال فصل الشتاء (%)</t>
         </is>
       </c>
     </row>
@@ -9605,12 +9605,12 @@
       </c>
       <c r="B227" s="5" t="inlineStr">
         <is>
-          <t>Cld_MayMn</t>
+          <t>Cld_SpMean</t>
         </is>
       </c>
       <c r="C227" s="31" t="inlineStr">
         <is>
-          <t>Cld_May_Mean</t>
+          <t>Cld_Spring_Mean</t>
         </is>
       </c>
       <c r="D227" s="15" t="inlineStr">
@@ -9620,7 +9620,7 @@
       </c>
       <c r="E227" s="7" t="inlineStr">
         <is>
-          <t>متوسط نسبة الغطاء السحابي الكلي للسماء لشهر مايو.</t>
+          <t>متوسط نسبة تغطية السحب لفصل الربيع الأرصادي (MAM).</t>
         </is>
       </c>
       <c r="F227" s="16" t="inlineStr">
@@ -9630,7 +9630,7 @@
       </c>
       <c r="G227" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط الغطاء السحابي لشهر مايو (%)</t>
+          <t>خريطة متوسط الغطاء السحابي خلال فصل الربيع (%)</t>
         </is>
       </c>
     </row>
@@ -9640,12 +9640,12 @@
       </c>
       <c r="B228" s="10" t="inlineStr">
         <is>
-          <t>Cld_JunMn</t>
+          <t>Cld_SuMean</t>
         </is>
       </c>
       <c r="C228" s="29" t="inlineStr">
         <is>
-          <t>Cld_June_Mean</t>
+          <t>Cld_Summer_Mean</t>
         </is>
       </c>
       <c r="D228" s="18" t="inlineStr">
@@ -9655,7 +9655,7 @@
       </c>
       <c r="E228" s="12" t="inlineStr">
         <is>
-          <t>متوسط نسبة الغطاء السحابي الكلي للسماء لشهر يونيو.</t>
+          <t>متوسط نسبة تغطية السحب لفصل الصيف الأرصادي (JJA).</t>
         </is>
       </c>
       <c r="F228" s="19" t="inlineStr">
@@ -9665,7 +9665,7 @@
       </c>
       <c r="G228" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط الغطاء السحابي لشهر يونيو (%)</t>
+          <t>خريطة متوسط الغطاء السحابي خلال فصل الصيف (%)</t>
         </is>
       </c>
     </row>
@@ -9675,12 +9675,12 @@
       </c>
       <c r="B229" s="5" t="inlineStr">
         <is>
-          <t>Cld_JulMn</t>
+          <t>Cld_AuMean</t>
         </is>
       </c>
       <c r="C229" s="31" t="inlineStr">
         <is>
-          <t>Cld_July_Mean</t>
+          <t>Cld_Autumn_Mean</t>
         </is>
       </c>
       <c r="D229" s="15" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="E229" s="7" t="inlineStr">
         <is>
-          <t>متوسط نسبة الغطاء السحابي الكلي للسماء لشهر يوليو.</t>
+          <t>متوسط نسبة تغطية السحب لفصل الخريف الأرصادي (SON).</t>
         </is>
       </c>
       <c r="F229" s="16" t="inlineStr">
@@ -9700,7 +9700,7 @@
       </c>
       <c r="G229" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط الغطاء السحابي لشهر يوليو (%)</t>
+          <t>خريطة متوسط الغطاء السحابي خلال فصل الخريف (%)</t>
         </is>
       </c>
     </row>
@@ -9710,12 +9710,12 @@
       </c>
       <c r="B230" s="10" t="inlineStr">
         <is>
-          <t>Cld_AugMn</t>
+          <t>Cld_AnRng</t>
         </is>
       </c>
       <c r="C230" s="29" t="inlineStr">
         <is>
-          <t>Cld_August_Mean</t>
+          <t>Cld_Annual_Range</t>
         </is>
       </c>
       <c r="D230" s="18" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="E230" s="12" t="inlineStr">
         <is>
-          <t>متوسط نسبة الغطاء السحابي الكلي للسماء لشهر أغسطس.</t>
+          <t>المدى السنوي لتغطية السحب (الفارق بين أكثر شهور السنة غيوماً وأكثرها صفاءً).</t>
         </is>
       </c>
       <c r="F230" s="19" t="inlineStr">
@@ -9735,7 +9735,7 @@
       </c>
       <c r="G230" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط الغطاء السحابي لشهر أغسطس (%)</t>
+          <t>خريطة المدى السنوي لنسبة الغطاء السحابي (%)</t>
         </is>
       </c>
     </row>
@@ -9745,12 +9745,12 @@
       </c>
       <c r="B231" s="5" t="inlineStr">
         <is>
-          <t>Cld_SepMn</t>
+          <t>Cld_SeaRng</t>
         </is>
       </c>
       <c r="C231" s="31" t="inlineStr">
         <is>
-          <t>Cld_September_Mean</t>
+          <t>Cld_Seasonal_Range</t>
         </is>
       </c>
       <c r="D231" s="15" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="E231" s="7" t="inlineStr">
         <is>
-          <t>متوسط نسبة الغطاء السحابي الكلي للسماء لشهر سبتمبر.</t>
+          <t>المدى الفصلي للغطاء السحابي (الفارق بين أعلى فصول السنة غيوماً وأصفاها).</t>
         </is>
       </c>
       <c r="F231" s="16" t="inlineStr">
@@ -9770,7 +9770,7 @@
       </c>
       <c r="G231" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط الغطاء السحابي لشهر سبتمبر (%)</t>
+          <t>خريطة المدى الفصلي للغطاء السحابي (%)</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="B232" s="10" t="inlineStr">
         <is>
-          <t>Cld_OctMn</t>
+          <t>Cld_JanMn</t>
         </is>
       </c>
       <c r="C232" s="29" t="inlineStr">
         <is>
-          <t>Cld_October_Mean</t>
+          <t>Cld_January_Mean</t>
         </is>
       </c>
       <c r="D232" s="18" t="inlineStr">
@@ -9795,7 +9795,7 @@
       </c>
       <c r="E232" s="12" t="inlineStr">
         <is>
-          <t>متوسط نسبة الغطاء السحابي الكلي للسماء لشهر أكتوبر.</t>
+          <t>متوسط نسبة الغطاء السحابي الكلي للسماء لشهر يناير.</t>
         </is>
       </c>
       <c r="F232" s="19" t="inlineStr">
@@ -9805,7 +9805,7 @@
       </c>
       <c r="G232" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط الغطاء السحابي لشهر أكتوبر (%)</t>
+          <t>خريطة متوسط الغطاء السحابي لشهر يناير (%)</t>
         </is>
       </c>
     </row>
@@ -9815,12 +9815,12 @@
       </c>
       <c r="B233" s="5" t="inlineStr">
         <is>
-          <t>Cld_NovMn</t>
+          <t>Cld_FebMn</t>
         </is>
       </c>
       <c r="C233" s="31" t="inlineStr">
         <is>
-          <t>Cld_November_Mean</t>
+          <t>Cld_February_Mean</t>
         </is>
       </c>
       <c r="D233" s="15" t="inlineStr">
@@ -9830,7 +9830,7 @@
       </c>
       <c r="E233" s="7" t="inlineStr">
         <is>
-          <t>متوسط نسبة الغطاء السحابي الكلي للسماء لشهر نوفمبر.</t>
+          <t>متوسط نسبة الغطاء السحابي الكلي للسماء لشهر فبراير.</t>
         </is>
       </c>
       <c r="F233" s="16" t="inlineStr">
@@ -9840,7 +9840,7 @@
       </c>
       <c r="G233" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط الغطاء السحابي لشهر نوفمبر (%)</t>
+          <t>خريطة متوسط الغطاء السحابي لشهر فبراير (%)</t>
         </is>
       </c>
     </row>
@@ -9850,12 +9850,12 @@
       </c>
       <c r="B234" s="10" t="inlineStr">
         <is>
-          <t>Cld_DecMn</t>
+          <t>Cld_MarMn</t>
         </is>
       </c>
       <c r="C234" s="29" t="inlineStr">
         <is>
-          <t>Cld_December_Mean</t>
+          <t>Cld_March_Mean</t>
         </is>
       </c>
       <c r="D234" s="18" t="inlineStr">
@@ -9865,7 +9865,7 @@
       </c>
       <c r="E234" s="12" t="inlineStr">
         <is>
-          <t>متوسط نسبة الغطاء السحابي الكلي للسماء لشهر ديسمبر.</t>
+          <t>متوسط نسبة الغطاء السحابي الكلي للسماء لشهر مارس.</t>
         </is>
       </c>
       <c r="F234" s="19" t="inlineStr">
@@ -9875,7 +9875,7 @@
       </c>
       <c r="G234" s="30" t="inlineStr">
         <is>
-          <t>خريطة متوسط الغطاء السحابي لشهر ديسمبر (%)</t>
+          <t>خريطة متوسط الغطاء السحابي لشهر مارس (%)</t>
         </is>
       </c>
     </row>
@@ -9885,32 +9885,32 @@
       </c>
       <c r="B235" s="5" t="inlineStr">
         <is>
-          <t>WC_WinMean</t>
+          <t>Cld_AprMn</t>
         </is>
       </c>
       <c r="C235" s="31" t="inlineStr">
         <is>
-          <t>WC_Winter_Mean</t>
+          <t>Cld_April_Mean</t>
         </is>
       </c>
       <c r="D235" s="15" t="inlineStr">
         <is>
-          <t>12_Wind_Chill (مبرد الرياح)</t>
+          <t>10_Cloud_Cover (الغطاء السحابي)</t>
         </is>
       </c>
       <c r="E235" s="7" t="inlineStr">
         <is>
-          <t>متوسط درجة البرودة الريحية لفصل الشتاء المحسوبة بمعادلة NWS لخفض الحرارة بفعل سرعة الرياح.</t>
+          <t>متوسط نسبة الغطاء السحابي الكلي للسماء لشهر أبريل.</t>
         </is>
       </c>
       <c r="F235" s="16" t="inlineStr">
         <is>
-          <t>°C</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G235" s="32" t="inlineStr">
         <is>
-          <t>خريطة متوسط مبرد الرياح خلال فصل الشتاء (°C)</t>
+          <t>خريطة متوسط الغطاء السحابي لشهر أبريل (%)</t>
         </is>
       </c>
     </row>
@@ -9920,32 +9920,32 @@
       </c>
       <c r="B236" s="10" t="inlineStr">
         <is>
-          <t>WC_AnnMean</t>
+          <t>Cld_MayMn</t>
         </is>
       </c>
       <c r="C236" s="29" t="inlineStr">
         <is>
-          <t>WC_Annual_Mean</t>
+          <t>Cld_May_Mean</t>
         </is>
       </c>
       <c r="D236" s="18" t="inlineStr">
         <is>
-          <t>12_Wind_Chill (مبرد الرياح)</t>
+          <t>10_Cloud_Cover (الغطاء السحابي)</t>
         </is>
       </c>
       <c r="E236" s="12" t="inlineStr">
         <is>
-          <t>المتوسط الحسابي السنوي لتأثير البرودة الريحية على حرارة الهواء المحسوسة.</t>
+          <t>متوسط نسبة الغطاء السحابي الكلي للسماء لشهر مايو.</t>
         </is>
       </c>
       <c r="F236" s="19" t="inlineStr">
         <is>
-          <t>°C</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G236" s="30" t="inlineStr">
         <is>
-          <t>خريطة المتوسط السنوي لمبرد الرياح (°C)</t>
+          <t>خريطة متوسط الغطاء السحابي لشهر مايو (%)</t>
         </is>
       </c>
     </row>
@@ -9955,32 +9955,32 @@
       </c>
       <c r="B237" s="5" t="inlineStr">
         <is>
-          <t>DM_AridAnn</t>
+          <t>Cld_JunMn</t>
         </is>
       </c>
       <c r="C237" s="31" t="inlineStr">
         <is>
-          <t>DM_Aridity_Annual</t>
+          <t>Cld_June_Mean</t>
         </is>
       </c>
       <c r="D237" s="15" t="inlineStr">
         <is>
-          <t>13_De_Martonne_Aridity (دليل دي مارتون)</t>
+          <t>10_Cloud_Cover (الغطاء السحابي)</t>
         </is>
       </c>
       <c r="E237" s="7" t="inlineStr">
         <is>
-          <t>دليل القحولة والجفاف السنوي لدي مارتون I = P / (T + 10) لتصنيف الأقاليم من القاحل فائق الجفاف إلى الرطب.</t>
+          <t>متوسط نسبة الغطاء السحابي الكلي للسماء لشهر يونيو.</t>
         </is>
       </c>
       <c r="F237" s="16" t="inlineStr">
         <is>
-          <t>مؤشر (Index)</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G237" s="32" t="inlineStr">
         <is>
-          <t>خريطة دليل دي مارتون السنوي للقحولة والجفاف</t>
+          <t>خريطة متوسط الغطاء السحابي لشهر يونيو (%)</t>
         </is>
       </c>
     </row>
@@ -9990,32 +9990,32 @@
       </c>
       <c r="B238" s="10" t="inlineStr">
         <is>
-          <t>ET_AnnTot</t>
+          <t>Cld_JulMn</t>
         </is>
       </c>
       <c r="C238" s="29" t="inlineStr">
         <is>
-          <t>ET_Annual_Total</t>
+          <t>Cld_July_Mean</t>
         </is>
       </c>
       <c r="D238" s="18" t="inlineStr">
         <is>
-          <t>14_Evapotranspiration (البخر والنتح)</t>
+          <t>10_Cloud_Cover (الغطاء السحابي)</t>
         </is>
       </c>
       <c r="E238" s="12" t="inlineStr">
         <is>
-          <t>المجموع التراكمي السنوي للبخر والنتح المرجعي الكامن المحسوب بمعادلة Hargreaves-Samani (FAO-56).</t>
+          <t>متوسط نسبة الغطاء السحابي الكلي للسماء لشهر يوليو.</t>
         </is>
       </c>
       <c r="F238" s="19" t="inlineStr">
         <is>
-          <t>ملم (mm)</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G238" s="30" t="inlineStr">
         <is>
-          <t>خريطة المجموع السنوي للبخر والنتح (ملم)</t>
+          <t>خريطة متوسط الغطاء السحابي لشهر يوليو (%)</t>
         </is>
       </c>
     </row>
@@ -10025,32 +10025,32 @@
       </c>
       <c r="B239" s="5" t="inlineStr">
         <is>
-          <t>ET_AnnMean</t>
+          <t>Cld_AugMn</t>
         </is>
       </c>
       <c r="C239" s="31" t="inlineStr">
         <is>
-          <t>ET_Annual_Mean</t>
+          <t>Cld_August_Mean</t>
         </is>
       </c>
       <c r="D239" s="15" t="inlineStr">
         <is>
-          <t>14_Evapotranspiration (البخر والنتح)</t>
+          <t>10_Cloud_Cover (الغطاء السحابي)</t>
         </is>
       </c>
       <c r="E239" s="7" t="inlineStr">
         <is>
-          <t>المعدل الشهري للبخر والنتح المرجعي (المجموع التراكمي السنوي مقسوماً على 12 شهراً).</t>
+          <t>متوسط نسبة الغطاء السحابي الكلي للسماء لشهر أغسطس.</t>
         </is>
       </c>
       <c r="F239" s="16" t="inlineStr">
         <is>
-          <t>ملم (mm)</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G239" s="32" t="inlineStr">
         <is>
-          <t>خريطة المعدل الشهري للبخر والنتح (ملم)</t>
+          <t>خريطة متوسط الغطاء السحابي لشهر أغسطس (%)</t>
         </is>
       </c>
     </row>
@@ -10060,32 +10060,32 @@
       </c>
       <c r="B240" s="10" t="inlineStr">
         <is>
-          <t>ET_MonMean</t>
+          <t>Cld_SepMn</t>
         </is>
       </c>
       <c r="C240" s="29" t="inlineStr">
         <is>
-          <t>ET_Month_Mean</t>
+          <t>Cld_September_Mean</t>
         </is>
       </c>
       <c r="D240" s="18" t="inlineStr">
         <is>
-          <t>14_Evapotranspiration (البخر-نتح المرجعي)</t>
+          <t>10_Cloud_Cover (الغطاء السحابي)</t>
         </is>
       </c>
       <c r="E240" s="12" t="inlineStr">
         <is>
-          <t>المعدل الشهري للبخر-نتح المرجعي المحسوب بطريقة هارجريفز (متوسط الشهور = المجموع السنوي / 12).</t>
+          <t>متوسط نسبة الغطاء السحابي الكلي للسماء لشهر سبتمبر.</t>
         </is>
       </c>
       <c r="F240" s="19" t="inlineStr">
         <is>
-          <t>mm/month</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G240" s="30" t="inlineStr">
         <is>
-          <t>خريطة المتوسط الشهري للبخر والنتح المرجعي (mm/month)</t>
+          <t>خريطة متوسط الغطاء السحابي لشهر سبتمبر (%)</t>
         </is>
       </c>
     </row>
@@ -10095,32 +10095,32 @@
       </c>
       <c r="B241" s="5" t="inlineStr">
         <is>
-          <t>ET_AnnRng</t>
+          <t>Cld_OctMn</t>
         </is>
       </c>
       <c r="C241" s="31" t="inlineStr">
         <is>
-          <t>ET_Annual_Range</t>
+          <t>Cld_October_Mean</t>
         </is>
       </c>
       <c r="D241" s="15" t="inlineStr">
         <is>
-          <t>14_Evapotranspiration (البخر والنتح)</t>
+          <t>10_Cloud_Cover (الغطاء السحابي)</t>
         </is>
       </c>
       <c r="E241" s="7" t="inlineStr">
         <is>
-          <t>المدى السنوي للبخر والنتح (الفارق بين أعلى شهور السنة فقداً للماء بالبخر والنتح وأدناها).</t>
+          <t>متوسط نسبة الغطاء السحابي الكلي للسماء لشهر أكتوبر.</t>
         </is>
       </c>
       <c r="F241" s="16" t="inlineStr">
         <is>
-          <t>ملم (mm)</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G241" s="32" t="inlineStr">
         <is>
-          <t>خريطة المدى السنوي للبخر والنتح (ملم)</t>
+          <t>خريطة متوسط الغطاء السحابي لشهر أكتوبر (%)</t>
         </is>
       </c>
     </row>
@@ -10130,32 +10130,32 @@
       </c>
       <c r="B242" s="10" t="inlineStr">
         <is>
-          <t>ET_SeaRng</t>
+          <t>Cld_NovMn</t>
         </is>
       </c>
       <c r="C242" s="29" t="inlineStr">
         <is>
-          <t>ET_Seasonal_Range</t>
+          <t>Cld_November_Mean</t>
         </is>
       </c>
       <c r="D242" s="18" t="inlineStr">
         <is>
-          <t>14_Evapotranspiration (البخر والنتح)</t>
+          <t>10_Cloud_Cover (الغطاء السحابي)</t>
         </is>
       </c>
       <c r="E242" s="12" t="inlineStr">
         <is>
-          <t>المدى الفصلي للبخر والنتح (الفارق بين مجموع أعلى فصول السنة في البخر والنتح ومجموع أقلها).</t>
+          <t>متوسط نسبة الغطاء السحابي الكلي للسماء لشهر نوفمبر.</t>
         </is>
       </c>
       <c r="F242" s="19" t="inlineStr">
         <is>
-          <t>ملم (mm)</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G242" s="30" t="inlineStr">
         <is>
-          <t>خريطة المدى الفصلي للبخر والنتح (ملم)</t>
+          <t>خريطة متوسط الغطاء السحابي لشهر نوفمبر (%)</t>
         </is>
       </c>
     </row>
@@ -10165,32 +10165,32 @@
       </c>
       <c r="B243" s="5" t="inlineStr">
         <is>
-          <t>ET_WinTot</t>
+          <t>Cld_DecMn</t>
         </is>
       </c>
       <c r="C243" s="31" t="inlineStr">
         <is>
-          <t>ET_Winter_Total</t>
+          <t>Cld_December_Mean</t>
         </is>
       </c>
       <c r="D243" s="15" t="inlineStr">
         <is>
-          <t>14_Evapotranspiration (البخر والنتح)</t>
+          <t>10_Cloud_Cover (الغطاء السحابي)</t>
         </is>
       </c>
       <c r="E243" s="7" t="inlineStr">
         <is>
-          <t>مجموع البخر والنتح لفصل الشتاء الأرصادي (شهور ديسمبر، يناير، فبراير - DJF).</t>
+          <t>متوسط نسبة الغطاء السحابي الكلي للسماء لشهر ديسمبر.</t>
         </is>
       </c>
       <c r="F243" s="16" t="inlineStr">
         <is>
-          <t>ملم (mm)</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G243" s="32" t="inlineStr">
         <is>
-          <t>خريطة مجموع البخر والنتح خلال فصل الشتاء (ملم)</t>
+          <t>خريطة متوسط الغطاء السحابي لشهر ديسمبر (%)</t>
         </is>
       </c>
     </row>
@@ -10200,32 +10200,32 @@
       </c>
       <c r="B244" s="10" t="inlineStr">
         <is>
-          <t>ET_SprTot</t>
+          <t>WC_WinMean</t>
         </is>
       </c>
       <c r="C244" s="29" t="inlineStr">
         <is>
-          <t>ET_Spring_Total</t>
+          <t>WC_Winter_Mean</t>
         </is>
       </c>
       <c r="D244" s="18" t="inlineStr">
         <is>
-          <t>14_Evapotranspiration (البخر والنتح)</t>
+          <t>12_Wind_Chill (مبرد الرياح)</t>
         </is>
       </c>
       <c r="E244" s="12" t="inlineStr">
         <is>
-          <t>مجموع البخر والنتح لفصل الربيع الأرصادي (شهور مارس، أبريل، مايو - MAM).</t>
+          <t>متوسط درجة البرودة الريحية لفصل الشتاء المحسوبة بمعادلة NWS لخفض الحرارة بفعل سرعة الرياح.</t>
         </is>
       </c>
       <c r="F244" s="19" t="inlineStr">
         <is>
-          <t>ملم (mm)</t>
+          <t>°C</t>
         </is>
       </c>
       <c r="G244" s="30" t="inlineStr">
         <is>
-          <t>خريطة مجموع البخر والنتح خلال فصل الربيع (ملم)</t>
+          <t>خريطة متوسط مبرد الرياح خلال فصل الشتاء (°C)</t>
         </is>
       </c>
     </row>
@@ -10235,32 +10235,32 @@
       </c>
       <c r="B245" s="5" t="inlineStr">
         <is>
-          <t>ET_SumTot</t>
+          <t>WC_AnnMean</t>
         </is>
       </c>
       <c r="C245" s="31" t="inlineStr">
         <is>
-          <t>ET_Summer_Total</t>
+          <t>WC_Annual_Mean</t>
         </is>
       </c>
       <c r="D245" s="15" t="inlineStr">
         <is>
-          <t>14_Evapotranspiration (البخر والنتح)</t>
+          <t>12_Wind_Chill (مبرد الرياح)</t>
         </is>
       </c>
       <c r="E245" s="7" t="inlineStr">
         <is>
-          <t>مجموع البخر والنتح لفصل الصيف الأرصادي (شهور يونيو، يوليو، أغسطس - JJA).</t>
+          <t>المتوسط الحسابي السنوي لتأثير البرودة الريحية على حرارة الهواء المحسوسة.</t>
         </is>
       </c>
       <c r="F245" s="16" t="inlineStr">
         <is>
-          <t>ملم (mm)</t>
+          <t>°C</t>
         </is>
       </c>
       <c r="G245" s="32" t="inlineStr">
         <is>
-          <t>خريطة مجموع البخر والنتح خلال فصل الصيف (ملم)</t>
+          <t>خريطة المتوسط السنوي لمبرد الرياح (°C)</t>
         </is>
       </c>
     </row>
@@ -10270,32 +10270,32 @@
       </c>
       <c r="B246" s="10" t="inlineStr">
         <is>
-          <t>ET_AutTot</t>
+          <t>DM_AridAnn</t>
         </is>
       </c>
       <c r="C246" s="29" t="inlineStr">
         <is>
-          <t>ET_Autumn_Total</t>
+          <t>DM_Aridity_Annual</t>
         </is>
       </c>
       <c r="D246" s="18" t="inlineStr">
         <is>
-          <t>14_Evapotranspiration (البخر والنتح)</t>
+          <t>13_De_Martonne_Aridity (دليل دي مارتون)</t>
         </is>
       </c>
       <c r="E246" s="12" t="inlineStr">
         <is>
-          <t>مجموع البخر والنتح لفصل الخريف الأرصادي (شهور سبتمبر، أكتوبر، نوفمبر - SON).</t>
+          <t>دليل القحولة والجفاف السنوي لدي مارتون I = P / (T + 10) لتصنيف الأقاليم من القاحل فائق الجفاف إلى الرطب.</t>
         </is>
       </c>
       <c r="F246" s="19" t="inlineStr">
         <is>
-          <t>ملم (mm)</t>
+          <t>مؤشر (Index)</t>
         </is>
       </c>
       <c r="G246" s="30" t="inlineStr">
         <is>
-          <t>خريطة مجموع البخر والنتح خلال فصل الخريف (ملم)</t>
+          <t>خريطة دليل دي مارتون السنوي للقحولة والجفاف</t>
         </is>
       </c>
     </row>
@@ -10305,12 +10305,12 @@
       </c>
       <c r="B247" s="5" t="inlineStr">
         <is>
-          <t>PET_HarAnn</t>
+          <t>ET_AnnTot</t>
         </is>
       </c>
       <c r="C247" s="31" t="inlineStr">
         <is>
-          <t>PET_Hargreaves_Annual</t>
+          <t>ET_Annual_Total</t>
         </is>
       </c>
       <c r="D247" s="15" t="inlineStr">
@@ -10320,7 +10320,7 @@
       </c>
       <c r="E247" s="7" t="inlineStr">
         <is>
-          <t>التبخر-نتح الكامن السنوي بهارجريفز (حقل رديف مطابق تماماً لـ ET_Annual_Total للتوافقية العكسية).</t>
+          <t>المجموع التراكمي السنوي للبخر والنتح المرجعي الكامن المحسوب بمعادلة Hargreaves-Samani (FAO-56).</t>
         </is>
       </c>
       <c r="F247" s="16" t="inlineStr">
@@ -10330,7 +10330,7 @@
       </c>
       <c r="G247" s="32" t="inlineStr">
         <is>
-          <t>خريطة التبخر والنتح الكامن السنوي بهارجريفز (ملم)</t>
+          <t>خريطة المجموع السنوي للبخر والنتح (ملم)</t>
         </is>
       </c>
     </row>
@@ -10340,12 +10340,12 @@
       </c>
       <c r="B248" s="10" t="inlineStr">
         <is>
-          <t>ET_JanTot</t>
+          <t>ET_AnnMean</t>
         </is>
       </c>
       <c r="C248" s="29" t="inlineStr">
         <is>
-          <t>ET_January_Total</t>
+          <t>ET_Annual_Mean</t>
         </is>
       </c>
       <c r="D248" s="18" t="inlineStr">
@@ -10355,17 +10355,17 @@
       </c>
       <c r="E248" s="12" t="inlineStr">
         <is>
-          <t>متوسط مجموع البخر والنتح المرجعي الكامن لشهر يناير بطريقة هارجريفز-ساماني FAO-56.</t>
+          <t>المعدل الشهري للبخر والنتح المرجعي (المجموع التراكمي السنوي مقسوماً على 12 شهراً).</t>
         </is>
       </c>
       <c r="F248" s="19" t="inlineStr">
         <is>
-          <t>ملم/شهر (mm/month)</t>
+          <t>ملم (mm)</t>
         </is>
       </c>
       <c r="G248" s="30" t="inlineStr">
         <is>
-          <t>خريطة مجموع البخر والنتح لشهر يناير (ملم/شهر)</t>
+          <t>خريطة المعدل الشهري للبخر والنتح (ملم)</t>
         </is>
       </c>
     </row>
@@ -10375,32 +10375,32 @@
       </c>
       <c r="B249" s="5" t="inlineStr">
         <is>
-          <t>ET_FebTot</t>
+          <t>ET_MonMean</t>
         </is>
       </c>
       <c r="C249" s="31" t="inlineStr">
         <is>
-          <t>ET_February_Total</t>
+          <t>ET_Month_Mean</t>
         </is>
       </c>
       <c r="D249" s="15" t="inlineStr">
         <is>
-          <t>14_Evapotranspiration (البخر والنتح)</t>
+          <t>14_Evapotranspiration (البخر-نتح المرجعي)</t>
         </is>
       </c>
       <c r="E249" s="7" t="inlineStr">
         <is>
-          <t>متوسط مجموع البخر والنتح المرجعي الكامن لشهر فبراير بطريقة هارجريفز-ساماني FAO-56.</t>
+          <t>المعدل الشهري للبخر-نتح المرجعي المحسوب بطريقة هارجريفز (متوسط الشهور = المجموع السنوي / 12).</t>
         </is>
       </c>
       <c r="F249" s="16" t="inlineStr">
         <is>
-          <t>ملم/شهر (mm/month)</t>
+          <t>mm/month</t>
         </is>
       </c>
       <c r="G249" s="32" t="inlineStr">
         <is>
-          <t>خريطة مجموع البخر والنتح لشهر فبراير (ملم/شهر)</t>
+          <t>خريطة المتوسط الشهري للبخر والنتح المرجعي (mm/month)</t>
         </is>
       </c>
     </row>
@@ -10410,12 +10410,12 @@
       </c>
       <c r="B250" s="10" t="inlineStr">
         <is>
-          <t>ET_MarTot</t>
+          <t>ET_AnnRng</t>
         </is>
       </c>
       <c r="C250" s="29" t="inlineStr">
         <is>
-          <t>ET_March_Total</t>
+          <t>ET_Annual_Range</t>
         </is>
       </c>
       <c r="D250" s="18" t="inlineStr">
@@ -10425,17 +10425,17 @@
       </c>
       <c r="E250" s="12" t="inlineStr">
         <is>
-          <t>متوسط مجموع البخر والنتح المرجعي الكامن لشهر مارس بطريقة هارجريفز-ساماني FAO-56.</t>
+          <t>المدى السنوي للبخر والنتح (الفارق بين أعلى شهور السنة فقداً للماء بالبخر والنتح وأدناها).</t>
         </is>
       </c>
       <c r="F250" s="19" t="inlineStr">
         <is>
-          <t>ملم/شهر (mm/month)</t>
+          <t>ملم (mm)</t>
         </is>
       </c>
       <c r="G250" s="30" t="inlineStr">
         <is>
-          <t>خريطة مجموع البخر والنتح لشهر مارس (ملم/شهر)</t>
+          <t>خريطة المدى السنوي للبخر والنتح (ملم)</t>
         </is>
       </c>
     </row>
@@ -10445,12 +10445,12 @@
       </c>
       <c r="B251" s="5" t="inlineStr">
         <is>
-          <t>ET_AprTot</t>
+          <t>ET_SeaRng</t>
         </is>
       </c>
       <c r="C251" s="31" t="inlineStr">
         <is>
-          <t>ET_April_Total</t>
+          <t>ET_Seasonal_Range</t>
         </is>
       </c>
       <c r="D251" s="15" t="inlineStr">
@@ -10460,17 +10460,17 @@
       </c>
       <c r="E251" s="7" t="inlineStr">
         <is>
-          <t>متوسط مجموع البخر والنتح المرجعي الكامن لشهر أبريل بطريقة هارجريفز-ساماني FAO-56.</t>
+          <t>المدى الفصلي للبخر والنتح (الفارق بين مجموع أعلى فصول السنة في البخر والنتح ومجموع أقلها).</t>
         </is>
       </c>
       <c r="F251" s="16" t="inlineStr">
         <is>
-          <t>ملم/شهر (mm/month)</t>
+          <t>ملم (mm)</t>
         </is>
       </c>
       <c r="G251" s="32" t="inlineStr">
         <is>
-          <t>خريطة مجموع البخر والنتح لشهر أبريل (ملم/شهر)</t>
+          <t>خريطة المدى الفصلي للبخر والنتح (ملم)</t>
         </is>
       </c>
     </row>
@@ -10480,12 +10480,12 @@
       </c>
       <c r="B252" s="10" t="inlineStr">
         <is>
-          <t>ET_MayTot</t>
+          <t>ET_WinTot</t>
         </is>
       </c>
       <c r="C252" s="29" t="inlineStr">
         <is>
-          <t>ET_May_Total</t>
+          <t>ET_Winter_Total</t>
         </is>
       </c>
       <c r="D252" s="18" t="inlineStr">
@@ -10495,17 +10495,17 @@
       </c>
       <c r="E252" s="12" t="inlineStr">
         <is>
-          <t>متوسط مجموع البخر والنتح المرجعي الكامن لشهر مايو بطريقة هارجريفز-ساماني FAO-56.</t>
+          <t>مجموع البخر والنتح لفصل الشتاء الأرصادي (شهور ديسمبر، يناير، فبراير - DJF).</t>
         </is>
       </c>
       <c r="F252" s="19" t="inlineStr">
         <is>
-          <t>ملم/شهر (mm/month)</t>
+          <t>ملم (mm)</t>
         </is>
       </c>
       <c r="G252" s="30" t="inlineStr">
         <is>
-          <t>خريطة مجموع البخر والنتح لشهر مايو (ملم/شهر)</t>
+          <t>خريطة مجموع البخر والنتح خلال فصل الشتاء (ملم)</t>
         </is>
       </c>
     </row>
@@ -10515,12 +10515,12 @@
       </c>
       <c r="B253" s="5" t="inlineStr">
         <is>
-          <t>ET_JunTot</t>
+          <t>ET_SprTot</t>
         </is>
       </c>
       <c r="C253" s="31" t="inlineStr">
         <is>
-          <t>ET_June_Total</t>
+          <t>ET_Spring_Total</t>
         </is>
       </c>
       <c r="D253" s="15" t="inlineStr">
@@ -10530,17 +10530,17 @@
       </c>
       <c r="E253" s="7" t="inlineStr">
         <is>
-          <t>متوسط مجموع البخر والنتح المرجعي الكامن لشهر يونيو بطريقة هارجريفز-ساماني FAO-56.</t>
+          <t>مجموع البخر والنتح لفصل الربيع الأرصادي (شهور مارس، أبريل، مايو - MAM).</t>
         </is>
       </c>
       <c r="F253" s="16" t="inlineStr">
         <is>
-          <t>ملم/شهر (mm/month)</t>
+          <t>ملم (mm)</t>
         </is>
       </c>
       <c r="G253" s="32" t="inlineStr">
         <is>
-          <t>خريطة مجموع البخر والنتح لشهر يونيو (ملم/شهر)</t>
+          <t>خريطة مجموع البخر والنتح خلال فصل الربيع (ملم)</t>
         </is>
       </c>
     </row>
@@ -10550,12 +10550,12 @@
       </c>
       <c r="B254" s="10" t="inlineStr">
         <is>
-          <t>ET_JulTot</t>
+          <t>ET_SumTot</t>
         </is>
       </c>
       <c r="C254" s="29" t="inlineStr">
         <is>
-          <t>ET_July_Total</t>
+          <t>ET_Summer_Total</t>
         </is>
       </c>
       <c r="D254" s="18" t="inlineStr">
@@ -10565,17 +10565,17 @@
       </c>
       <c r="E254" s="12" t="inlineStr">
         <is>
-          <t>متوسط مجموع البخر والنتح المرجعي الكامن لشهر يوليو بطريقة هارجريفز-ساماني FAO-56.</t>
+          <t>مجموع البخر والنتح لفصل الصيف الأرصادي (شهور يونيو، يوليو، أغسطس - JJA).</t>
         </is>
       </c>
       <c r="F254" s="19" t="inlineStr">
         <is>
-          <t>ملم/شهر (mm/month)</t>
+          <t>ملم (mm)</t>
         </is>
       </c>
       <c r="G254" s="30" t="inlineStr">
         <is>
-          <t>خريطة مجموع البخر والنتح لشهر يوليو (ملم/شهر)</t>
+          <t>خريطة مجموع البخر والنتح خلال فصل الصيف (ملم)</t>
         </is>
       </c>
     </row>
@@ -10585,12 +10585,12 @@
       </c>
       <c r="B255" s="5" t="inlineStr">
         <is>
-          <t>ET_AugTot</t>
+          <t>ET_AutTot</t>
         </is>
       </c>
       <c r="C255" s="31" t="inlineStr">
         <is>
-          <t>ET_August_Total</t>
+          <t>ET_Autumn_Total</t>
         </is>
       </c>
       <c r="D255" s="15" t="inlineStr">
@@ -10600,17 +10600,17 @@
       </c>
       <c r="E255" s="7" t="inlineStr">
         <is>
-          <t>متوسط مجموع البخر والنتح المرجعي الكامن لشهر أغسطس بطريقة هارجريفز-ساماني FAO-56.</t>
+          <t>مجموع البخر والنتح لفصل الخريف الأرصادي (شهور سبتمبر، أكتوبر، نوفمبر - SON).</t>
         </is>
       </c>
       <c r="F255" s="16" t="inlineStr">
         <is>
-          <t>ملم/شهر (mm/month)</t>
+          <t>ملم (mm)</t>
         </is>
       </c>
       <c r="G255" s="32" t="inlineStr">
         <is>
-          <t>خريطة مجموع البخر والنتح لشهر أغسطس (ملم/شهر)</t>
+          <t>خريطة مجموع البخر والنتح خلال فصل الخريف (ملم)</t>
         </is>
       </c>
     </row>
@@ -10620,12 +10620,12 @@
       </c>
       <c r="B256" s="10" t="inlineStr">
         <is>
-          <t>ET_SepTot</t>
+          <t>PET_HarAnn</t>
         </is>
       </c>
       <c r="C256" s="29" t="inlineStr">
         <is>
-          <t>ET_September_Total</t>
+          <t>PET_Hargreaves_Annual</t>
         </is>
       </c>
       <c r="D256" s="18" t="inlineStr">
@@ -10635,17 +10635,17 @@
       </c>
       <c r="E256" s="12" t="inlineStr">
         <is>
-          <t>متوسط مجموع البخر والنتح المرجعي الكامن لشهر سبتمبر بطريقة هارجريفز-ساماني FAO-56.</t>
+          <t>التبخر-نتح الكامن السنوي بهارجريفز (حقل رديف مطابق تماماً لـ ET_Annual_Total للتوافقية العكسية).</t>
         </is>
       </c>
       <c r="F256" s="19" t="inlineStr">
         <is>
-          <t>ملم/شهر (mm/month)</t>
+          <t>ملم (mm)</t>
         </is>
       </c>
       <c r="G256" s="30" t="inlineStr">
         <is>
-          <t>خريطة مجموع البخر والنتح لشهر سبتمبر (ملم/شهر)</t>
+          <t>خريطة التبخر والنتح الكامن السنوي بهارجريفز (ملم)</t>
         </is>
       </c>
     </row>
@@ -10655,12 +10655,12 @@
       </c>
       <c r="B257" s="5" t="inlineStr">
         <is>
-          <t>ET_OctTot</t>
+          <t>ET_JanTot</t>
         </is>
       </c>
       <c r="C257" s="31" t="inlineStr">
         <is>
-          <t>ET_October_Total</t>
+          <t>ET_January_Total</t>
         </is>
       </c>
       <c r="D257" s="15" t="inlineStr">
@@ -10670,7 +10670,7 @@
       </c>
       <c r="E257" s="7" t="inlineStr">
         <is>
-          <t>متوسط مجموع البخر والنتح المرجعي الكامن لشهر أكتوبر بطريقة هارجريفز-ساماني FAO-56.</t>
+          <t>متوسط مجموع البخر والنتح المرجعي الكامن لشهر يناير بطريقة هارجريفز-ساماني FAO-56.</t>
         </is>
       </c>
       <c r="F257" s="16" t="inlineStr">
@@ -10680,7 +10680,7 @@
       </c>
       <c r="G257" s="32" t="inlineStr">
         <is>
-          <t>خريطة مجموع البخر والنتح لشهر أكتوبر (ملم/شهر)</t>
+          <t>خريطة مجموع البخر والنتح لشهر يناير (ملم/شهر)</t>
         </is>
       </c>
     </row>
@@ -10690,12 +10690,12 @@
       </c>
       <c r="B258" s="10" t="inlineStr">
         <is>
-          <t>ET_NovTot</t>
+          <t>ET_FebTot</t>
         </is>
       </c>
       <c r="C258" s="29" t="inlineStr">
         <is>
-          <t>ET_November_Total</t>
+          <t>ET_February_Total</t>
         </is>
       </c>
       <c r="D258" s="18" t="inlineStr">
@@ -10705,7 +10705,7 @@
       </c>
       <c r="E258" s="12" t="inlineStr">
         <is>
-          <t>متوسط مجموع البخر والنتح المرجعي الكامن لشهر نوفمبر بطريقة هارجريفز-ساماني FAO-56.</t>
+          <t>متوسط مجموع البخر والنتح المرجعي الكامن لشهر فبراير بطريقة هارجريفز-ساماني FAO-56.</t>
         </is>
       </c>
       <c r="F258" s="19" t="inlineStr">
@@ -10715,7 +10715,7 @@
       </c>
       <c r="G258" s="30" t="inlineStr">
         <is>
-          <t>خريطة مجموع البخر والنتح لشهر نوفمبر (ملم/شهر)</t>
+          <t>خريطة مجموع البخر والنتح لشهر فبراير (ملم/شهر)</t>
         </is>
       </c>
     </row>
@@ -10725,12 +10725,12 @@
       </c>
       <c r="B259" s="5" t="inlineStr">
         <is>
-          <t>ET_DecTot</t>
+          <t>ET_MarTot</t>
         </is>
       </c>
       <c r="C259" s="31" t="inlineStr">
         <is>
-          <t>ET_December_Total</t>
+          <t>ET_March_Total</t>
         </is>
       </c>
       <c r="D259" s="15" t="inlineStr">
@@ -10740,7 +10740,7 @@
       </c>
       <c r="E259" s="7" t="inlineStr">
         <is>
-          <t>متوسط مجموع البخر والنتح المرجعي الكامن لشهر ديسمبر بطريقة هارجريفز-ساماني FAO-56.</t>
+          <t>متوسط مجموع البخر والنتح المرجعي الكامن لشهر مارس بطريقة هارجريفز-ساماني FAO-56.</t>
         </is>
       </c>
       <c r="F259" s="16" t="inlineStr">
@@ -10750,7 +10750,7 @@
       </c>
       <c r="G259" s="32" t="inlineStr">
         <is>
-          <t>خريطة مجموع البخر والنتح لشهر ديسمبر (ملم/شهر)</t>
+          <t>خريطة مجموع البخر والنتح لشهر مارس (ملم/شهر)</t>
         </is>
       </c>
     </row>
@@ -10760,32 +10760,32 @@
       </c>
       <c r="B260" s="10" t="inlineStr">
         <is>
-          <t>UNEP_Arid</t>
+          <t>ET_AprTot</t>
         </is>
       </c>
       <c r="C260" s="29" t="inlineStr">
         <is>
-          <t>UNEP_Aridity_Annual</t>
+          <t>ET_April_Total</t>
         </is>
       </c>
       <c r="D260" s="18" t="inlineStr">
         <is>
-          <t>15_UNEP_Aridity (مؤشر UNEP)</t>
+          <t>14_Evapotranspiration (البخر والنتح)</t>
         </is>
       </c>
       <c r="E260" s="12" t="inlineStr">
         <is>
-          <t>مؤشر القحولة العالمي لبرنامج الأمم المتحدة للبيئة AI = P / ET_ann لتحديد المناطق القاحلة وشبه القاحلة.</t>
+          <t>متوسط مجموع البخر والنتح المرجعي الكامن لشهر أبريل بطريقة هارجريفز-ساماني FAO-56.</t>
         </is>
       </c>
       <c r="F260" s="19" t="inlineStr">
         <is>
-          <t>نسبة (Ratio)</t>
+          <t>ملم/شهر (mm/month)</t>
         </is>
       </c>
       <c r="G260" s="30" t="inlineStr">
         <is>
-          <t>خريطة مؤشر القحولة العالمي لبرنامج الأمم المتحدة للبيئة</t>
+          <t>خريطة مجموع البخر والنتح لشهر أبريل (ملم/شهر)</t>
         </is>
       </c>
     </row>
@@ -10795,32 +10795,32 @@
       </c>
       <c r="B261" s="5" t="inlineStr">
         <is>
-          <t>WatDefAnn</t>
+          <t>ET_MayTot</t>
         </is>
       </c>
       <c r="C261" s="31" t="inlineStr">
         <is>
-          <t>Water_Deficit_Annual</t>
+          <t>ET_May_Total</t>
         </is>
       </c>
       <c r="D261" s="15" t="inlineStr">
         <is>
-          <t>16_Water_Deficit (العجز المائي)</t>
+          <t>14_Evapotranspiration (البخر والنتح)</t>
         </is>
       </c>
       <c r="E261" s="7" t="inlineStr">
         <is>
-          <t>الموازنة المائية المناخية السنوية الصافية WD = P - ET_ann (القيم السالبة تعبر عن عجز مائي والموجبة فائض مائي).</t>
+          <t>متوسط مجموع البخر والنتح المرجعي الكامن لشهر مايو بطريقة هارجريفز-ساماني FAO-56.</t>
         </is>
       </c>
       <c r="F261" s="16" t="inlineStr">
         <is>
-          <t>ملم (mm)</t>
+          <t>ملم/شهر (mm/month)</t>
         </is>
       </c>
       <c r="G261" s="32" t="inlineStr">
         <is>
-          <t>خريطة الموازنة والعجز المائي المناخي السنوي (ملم)</t>
+          <t>خريطة مجموع البخر والنتح لشهر مايو (ملم/شهر)</t>
         </is>
       </c>
     </row>
@@ -10830,32 +10830,32 @@
       </c>
       <c r="B262" s="10" t="inlineStr">
         <is>
-          <t>Dry_Months</t>
+          <t>ET_JunTot</t>
         </is>
       </c>
       <c r="C262" s="29" t="inlineStr">
         <is>
-          <t>Dry_Months_Count</t>
+          <t>ET_June_Total</t>
         </is>
       </c>
       <c r="D262" s="18" t="inlineStr">
         <is>
-          <t>17_Dry_Months (الأشهر الجافة)</t>
+          <t>14_Evapotranspiration (البخر والنتح)</t>
         </is>
       </c>
       <c r="E262" s="12" t="inlineStr">
         <is>
-          <t>عدد أشهر السنة الجافة بيولوجياً ومناخياً وفق معيار والتر-ليث البيومناخي الشهير (P &lt; 2T).</t>
+          <t>متوسط مجموع البخر والنتح المرجعي الكامن لشهر يونيو بطريقة هارجريفز-ساماني FAO-56.</t>
         </is>
       </c>
       <c r="F262" s="19" t="inlineStr">
         <is>
-          <t>شهر (0-12)</t>
+          <t>ملم/شهر (mm/month)</t>
         </is>
       </c>
       <c r="G262" s="30" t="inlineStr">
         <is>
-          <t>خريطة عدد الأشهر الجافة بيولوجياً في السنة</t>
+          <t>خريطة مجموع البخر والنتح لشهر يونيو (ملم/شهر)</t>
         </is>
       </c>
     </row>
@@ -10865,32 +10865,32 @@
       </c>
       <c r="B263" s="5" t="inlineStr">
         <is>
-          <t>T_TrendDec</t>
+          <t>ET_JulTot</t>
         </is>
       </c>
       <c r="C263" s="31" t="inlineStr">
         <is>
-          <t>T_Trend_Decade</t>
+          <t>ET_July_Total</t>
         </is>
       </c>
       <c r="D263" s="15" t="inlineStr">
         <is>
-          <t>18_Trends_And_Anomalies (الاتجاهات والشذوذ)</t>
+          <t>14_Evapotranspiration (البخر والنتح)</t>
         </is>
       </c>
       <c r="E263" s="7" t="inlineStr">
         <is>
-          <t>معدل تغير واتجاه درجة الحرارة لكل عقد زمني (10 سنوات) باستخدام انحدار المربعات الصغرى الخطي.</t>
+          <t>متوسط مجموع البخر والنتح المرجعي الكامن لشهر يوليو بطريقة هارجريفز-ساماني FAO-56.</t>
         </is>
       </c>
       <c r="F263" s="16" t="inlineStr">
         <is>
-          <t>°C/decade</t>
+          <t>ملم/شهر (mm/month)</t>
         </is>
       </c>
       <c r="G263" s="32" t="inlineStr">
         <is>
-          <t>خريطة اتجاه تغير درجة الحرارة في العقد الزمني (°C/decade)</t>
+          <t>خريطة مجموع البخر والنتح لشهر يوليو (ملم/شهر)</t>
         </is>
       </c>
     </row>
@@ -10900,32 +10900,32 @@
       </c>
       <c r="B264" s="10" t="inlineStr">
         <is>
-          <t>R_TrendDec</t>
+          <t>ET_AugTot</t>
         </is>
       </c>
       <c r="C264" s="29" t="inlineStr">
         <is>
-          <t>R_Trend_Decade</t>
+          <t>ET_August_Total</t>
         </is>
       </c>
       <c r="D264" s="18" t="inlineStr">
         <is>
-          <t>18_Trends_And_Anomalies (الاتجاهات والشذوذ)</t>
+          <t>14_Evapotranspiration (البخر والنتح)</t>
         </is>
       </c>
       <c r="E264" s="12" t="inlineStr">
         <is>
-          <t>معدل تغير واتجاه تساقط الأمطار لكل عقد زمني (10 سنوات) باستخدام انحدار المربعات الصغرى الخطي.</t>
+          <t>متوسط مجموع البخر والنتح المرجعي الكامن لشهر أغسطس بطريقة هارجريفز-ساماني FAO-56.</t>
         </is>
       </c>
       <c r="F264" s="19" t="inlineStr">
         <is>
-          <t>mm/decade</t>
+          <t>ملم/شهر (mm/month)</t>
         </is>
       </c>
       <c r="G264" s="30" t="inlineStr">
         <is>
-          <t>خريطة اتجاه تغير تساقط الأمطار في العقد الزمني (mm/decade)</t>
+          <t>خريطة مجموع البخر والنتح لشهر أغسطس (ملم/شهر)</t>
         </is>
       </c>
     </row>
@@ -10935,32 +10935,32 @@
       </c>
       <c r="B265" s="5" t="inlineStr">
         <is>
-          <t>T_AnomAnn</t>
+          <t>ET_SepTot</t>
         </is>
       </c>
       <c r="C265" s="31" t="inlineStr">
         <is>
-          <t>T_Anom_Annual</t>
+          <t>ET_September_Total</t>
         </is>
       </c>
       <c r="D265" s="15" t="inlineStr">
         <is>
-          <t>18_Trends_And_Anomalies (الاتجاهات والشذوذ)</t>
+          <t>14_Evapotranspiration (البخر والنتح)</t>
         </is>
       </c>
       <c r="E265" s="7" t="inlineStr">
         <is>
-          <t>الشذوذ الحراري السنوي لدرجة الحرارة مقارنة بخط الأساس المناخي العالمي 1991–2020.</t>
+          <t>متوسط مجموع البخر والنتح المرجعي الكامن لشهر سبتمبر بطريقة هارجريفز-ساماني FAO-56.</t>
         </is>
       </c>
       <c r="F265" s="16" t="inlineStr">
         <is>
-          <t>°C</t>
+          <t>ملم/شهر (mm/month)</t>
         </is>
       </c>
       <c r="G265" s="32" t="inlineStr">
         <is>
-          <t>خريطة الشذوذ الحراري السنوي مقارنة بخط أساس 1991–2020 (°C)</t>
+          <t>خريطة مجموع البخر والنتح لشهر سبتمبر (ملم/شهر)</t>
         </is>
       </c>
     </row>
@@ -10970,32 +10970,32 @@
       </c>
       <c r="B266" s="10" t="inlineStr">
         <is>
-          <t>T_AnomWin</t>
+          <t>ET_OctTot</t>
         </is>
       </c>
       <c r="C266" s="29" t="inlineStr">
         <is>
-          <t>T_Anom_Winter</t>
+          <t>ET_October_Total</t>
         </is>
       </c>
       <c r="D266" s="18" t="inlineStr">
         <is>
-          <t>18_Trends_And_Anomalies (الاتجاهات والشذوذ)</t>
+          <t>14_Evapotranspiration (البخر والنتح)</t>
         </is>
       </c>
       <c r="E266" s="12" t="inlineStr">
         <is>
-          <t>الشذوذ الحراري لفصل الشتاء مقارنة بمتوسط شهور الشتاء لخط الأساس المناخي 1991–2020.</t>
+          <t>متوسط مجموع البخر والنتح المرجعي الكامن لشهر أكتوبر بطريقة هارجريفز-ساماني FAO-56.</t>
         </is>
       </c>
       <c r="F266" s="19" t="inlineStr">
         <is>
-          <t>°C</t>
+          <t>ملم/شهر (mm/month)</t>
         </is>
       </c>
       <c r="G266" s="30" t="inlineStr">
         <is>
-          <t>خريطة الشذوذ الحراري لفصل الشتاء مقارنة بخط أساس 1991–2020 (°C)</t>
+          <t>خريطة مجموع البخر والنتح لشهر أكتوبر (ملم/شهر)</t>
         </is>
       </c>
     </row>
@@ -11005,32 +11005,32 @@
       </c>
       <c r="B267" s="5" t="inlineStr">
         <is>
-          <t>T_AnomSum</t>
+          <t>ET_NovTot</t>
         </is>
       </c>
       <c r="C267" s="31" t="inlineStr">
         <is>
-          <t>T_Anom_Summer</t>
+          <t>ET_November_Total</t>
         </is>
       </c>
       <c r="D267" s="15" t="inlineStr">
         <is>
-          <t>18_Trends_And_Anomalies (الاتجاهات والشذوذ)</t>
+          <t>14_Evapotranspiration (البخر والنتح)</t>
         </is>
       </c>
       <c r="E267" s="7" t="inlineStr">
         <is>
-          <t>الشذوذ الحراري لفصل الصيف مقارنة بمتوسط شهور الصيف لخط الأساس المناخي 1991–2020.</t>
+          <t>متوسط مجموع البخر والنتح المرجعي الكامن لشهر نوفمبر بطريقة هارجريفز-ساماني FAO-56.</t>
         </is>
       </c>
       <c r="F267" s="16" t="inlineStr">
         <is>
-          <t>°C</t>
+          <t>ملم/شهر (mm/month)</t>
         </is>
       </c>
       <c r="G267" s="32" t="inlineStr">
         <is>
-          <t>خريطة الشذوذ الحراري لفصل الصيف مقارنة بخط أساس 1991–2020 (°C)</t>
+          <t>خريطة مجموع البخر والنتح لشهر نوفمبر (ملم/شهر)</t>
         </is>
       </c>
     </row>
@@ -11040,32 +11040,32 @@
       </c>
       <c r="B268" s="10" t="inlineStr">
         <is>
-          <t>R_AnomAnn</t>
+          <t>ET_DecTot</t>
         </is>
       </c>
       <c r="C268" s="29" t="inlineStr">
         <is>
-          <t>R_Anom_Annual</t>
+          <t>ET_December_Total</t>
         </is>
       </c>
       <c r="D268" s="18" t="inlineStr">
         <is>
-          <t>18_Trends_And_Anomalies (الاتجاهات والشذوذ)</t>
+          <t>14_Evapotranspiration (البخر والنتح)</t>
         </is>
       </c>
       <c r="E268" s="12" t="inlineStr">
         <is>
-          <t>شذوذ الأمطار السنوي المطلق مقارنة بمتوسط الأمطار لخط الأساس المناخي 1991–2020.</t>
+          <t>متوسط مجموع البخر والنتح المرجعي الكامن لشهر ديسمبر بطريقة هارجريفز-ساماني FAO-56.</t>
         </is>
       </c>
       <c r="F268" s="19" t="inlineStr">
         <is>
-          <t>ملم (mm)</t>
+          <t>ملم/شهر (mm/month)</t>
         </is>
       </c>
       <c r="G268" s="30" t="inlineStr">
         <is>
-          <t>خريطة شذوذ تساقط الأمطار السنوي مقارنة بخط أساس 1991–2020 (ملم)</t>
+          <t>خريطة مجموع البخر والنتح لشهر ديسمبر (ملم/شهر)</t>
         </is>
       </c>
     </row>
@@ -11075,32 +11075,32 @@
       </c>
       <c r="B269" s="5" t="inlineStr">
         <is>
-          <t>R_AnomPct</t>
+          <t>UNEP_Arid</t>
         </is>
       </c>
       <c r="C269" s="31" t="inlineStr">
         <is>
-          <t>R_Anom_Annual_Pct</t>
+          <t>UNEP_Aridity_Annual</t>
         </is>
       </c>
       <c r="D269" s="15" t="inlineStr">
         <is>
-          <t>18_Trends_And_Anomalies (الاتجاهات والشذوذ)</t>
+          <t>15_UNEP_Aridity (مؤشر UNEP)</t>
         </is>
       </c>
       <c r="E269" s="7" t="inlineStr">
         <is>
-          <t>شذوذ الأمطار السنوي كنسبة مئوية من خط الأساس المناخي 1991–2020 (فرق نسبي مئوي).</t>
+          <t>مؤشر القحولة العالمي لبرنامج الأمم المتحدة للبيئة AI = P / ET_ann لتحديد المناطق القاحلة وشبه القاحلة.</t>
         </is>
       </c>
       <c r="F269" s="16" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>نسبة (Ratio)</t>
         </is>
       </c>
       <c r="G269" s="32" t="inlineStr">
         <is>
-          <t>خريطة الشذوذ النسبي المئوي للأمطار مقارنة بخط أساس 1991–2020 (%)</t>
+          <t>خريطة مؤشر القحولة العالمي لبرنامج الأمم المتحدة للبيئة</t>
         </is>
       </c>
     </row>
@@ -11110,22 +11110,22 @@
       </c>
       <c r="B270" s="10" t="inlineStr">
         <is>
-          <t>R_AnomWin</t>
+          <t>WatDefAnn</t>
         </is>
       </c>
       <c r="C270" s="29" t="inlineStr">
         <is>
-          <t>R_Anom_Winter</t>
+          <t>Water_Deficit_Annual</t>
         </is>
       </c>
       <c r="D270" s="18" t="inlineStr">
         <is>
-          <t>18_Trends_And_Anomalies (الاتجاهات والشذوذ)</t>
+          <t>16_Water_Deficit (العجز المائي)</t>
         </is>
       </c>
       <c r="E270" s="12" t="inlineStr">
         <is>
-          <t>شذوذ أمطار فصل الشتاء المطلق مقارنة بأمطار شتاء خط الأساس المناخي 1991–2020.</t>
+          <t>الموازنة المائية المناخية السنوية الصافية WD = P - ET_ann (القيم السالبة تعبر عن عجز مائي والموجبة فائض مائي).</t>
         </is>
       </c>
       <c r="F270" s="19" t="inlineStr">
@@ -11135,7 +11135,7 @@
       </c>
       <c r="G270" s="30" t="inlineStr">
         <is>
-          <t>خريطة شذوذ أمطار الشتاء مقارنة بخط أساس 1991–2020 (ملم)</t>
+          <t>خريطة الموازنة والعجز المائي المناخي السنوي (ملم)</t>
         </is>
       </c>
     </row>
@@ -11145,37 +11145,352 @@
       </c>
       <c r="B271" s="5" t="inlineStr">
         <is>
+          <t>Dry_Months</t>
+        </is>
+      </c>
+      <c r="C271" s="31" t="inlineStr">
+        <is>
+          <t>Dry_Months_Count</t>
+        </is>
+      </c>
+      <c r="D271" s="15" t="inlineStr">
+        <is>
+          <t>17_Dry_Months (الأشهر الجافة)</t>
+        </is>
+      </c>
+      <c r="E271" s="7" t="inlineStr">
+        <is>
+          <t>عدد أشهر السنة الجافة بيولوجياً ومناخياً وفق معيار والتر-ليث البيومناخي الشهير (P &lt; 2T).</t>
+        </is>
+      </c>
+      <c r="F271" s="16" t="inlineStr">
+        <is>
+          <t>شهر (0-12)</t>
+        </is>
+      </c>
+      <c r="G271" s="32" t="inlineStr">
+        <is>
+          <t>خريطة عدد الأشهر الجافة بيولوجياً في السنة</t>
+        </is>
+      </c>
+    </row>
+    <row r="272" ht="24" customHeight="1">
+      <c r="A272" s="8" t="n">
+        <v>271</v>
+      </c>
+      <c r="B272" s="10" t="inlineStr">
+        <is>
+          <t>T_TrendDec</t>
+        </is>
+      </c>
+      <c r="C272" s="29" t="inlineStr">
+        <is>
+          <t>T_Trend_Decade</t>
+        </is>
+      </c>
+      <c r="D272" s="18" t="inlineStr">
+        <is>
+          <t>18_Trends_And_Anomalies (الاتجاهات والشذوذ)</t>
+        </is>
+      </c>
+      <c r="E272" s="12" t="inlineStr">
+        <is>
+          <t>معدل تغير واتجاه درجة الحرارة لكل عقد زمني (10 سنوات) باستخدام انحدار المربعات الصغرى الخطي.</t>
+        </is>
+      </c>
+      <c r="F272" s="19" t="inlineStr">
+        <is>
+          <t>°C/decade</t>
+        </is>
+      </c>
+      <c r="G272" s="30" t="inlineStr">
+        <is>
+          <t>خريطة اتجاه تغير درجة الحرارة في العقد الزمني (°C/decade)</t>
+        </is>
+      </c>
+    </row>
+    <row r="273" ht="24" customHeight="1">
+      <c r="A273" s="3" t="n">
+        <v>272</v>
+      </c>
+      <c r="B273" s="5" t="inlineStr">
+        <is>
+          <t>R_TrendDec</t>
+        </is>
+      </c>
+      <c r="C273" s="31" t="inlineStr">
+        <is>
+          <t>R_Trend_Decade</t>
+        </is>
+      </c>
+      <c r="D273" s="15" t="inlineStr">
+        <is>
+          <t>18_Trends_And_Anomalies (الاتجاهات والشذوذ)</t>
+        </is>
+      </c>
+      <c r="E273" s="7" t="inlineStr">
+        <is>
+          <t>معدل تغير واتجاه تساقط الأمطار لكل عقد زمني (10 سنوات) باستخدام انحدار المربعات الصغرى الخطي.</t>
+        </is>
+      </c>
+      <c r="F273" s="16" t="inlineStr">
+        <is>
+          <t>mm/decade</t>
+        </is>
+      </c>
+      <c r="G273" s="32" t="inlineStr">
+        <is>
+          <t>خريطة اتجاه تغير تساقط الأمطار في العقد الزمني (mm/decade)</t>
+        </is>
+      </c>
+    </row>
+    <row r="274" ht="24" customHeight="1">
+      <c r="A274" s="8" t="n">
+        <v>273</v>
+      </c>
+      <c r="B274" s="10" t="inlineStr">
+        <is>
+          <t>T_AnomAnn</t>
+        </is>
+      </c>
+      <c r="C274" s="29" t="inlineStr">
+        <is>
+          <t>T_Anom_Annual</t>
+        </is>
+      </c>
+      <c r="D274" s="18" t="inlineStr">
+        <is>
+          <t>18_Trends_And_Anomalies (الاتجاهات والشذوذ)</t>
+        </is>
+      </c>
+      <c r="E274" s="12" t="inlineStr">
+        <is>
+          <t>الشذوذ الحراري السنوي لدرجة الحرارة مقارنة بخط الأساس المناخي العالمي 1991–2020.</t>
+        </is>
+      </c>
+      <c r="F274" s="19" t="inlineStr">
+        <is>
+          <t>°C</t>
+        </is>
+      </c>
+      <c r="G274" s="30" t="inlineStr">
+        <is>
+          <t>خريطة الشذوذ الحراري السنوي مقارنة بخط أساس 1991–2020 (°C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="275" ht="24" customHeight="1">
+      <c r="A275" s="3" t="n">
+        <v>274</v>
+      </c>
+      <c r="B275" s="5" t="inlineStr">
+        <is>
+          <t>T_AnomWin</t>
+        </is>
+      </c>
+      <c r="C275" s="31" t="inlineStr">
+        <is>
+          <t>T_Anom_Winter</t>
+        </is>
+      </c>
+      <c r="D275" s="15" t="inlineStr">
+        <is>
+          <t>18_Trends_And_Anomalies (الاتجاهات والشذوذ)</t>
+        </is>
+      </c>
+      <c r="E275" s="7" t="inlineStr">
+        <is>
+          <t>الشذوذ الحراري لفصل الشتاء مقارنة بمتوسط شهور الشتاء لخط الأساس المناخي 1991–2020.</t>
+        </is>
+      </c>
+      <c r="F275" s="16" t="inlineStr">
+        <is>
+          <t>°C</t>
+        </is>
+      </c>
+      <c r="G275" s="32" t="inlineStr">
+        <is>
+          <t>خريطة الشذوذ الحراري لفصل الشتاء مقارنة بخط أساس 1991–2020 (°C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="276" ht="24" customHeight="1">
+      <c r="A276" s="8" t="n">
+        <v>275</v>
+      </c>
+      <c r="B276" s="10" t="inlineStr">
+        <is>
+          <t>T_AnomSum</t>
+        </is>
+      </c>
+      <c r="C276" s="29" t="inlineStr">
+        <is>
+          <t>T_Anom_Summer</t>
+        </is>
+      </c>
+      <c r="D276" s="18" t="inlineStr">
+        <is>
+          <t>18_Trends_And_Anomalies (الاتجاهات والشذوذ)</t>
+        </is>
+      </c>
+      <c r="E276" s="12" t="inlineStr">
+        <is>
+          <t>الشذوذ الحراري لفصل الصيف مقارنة بمتوسط شهور الصيف لخط الأساس المناخي 1991–2020.</t>
+        </is>
+      </c>
+      <c r="F276" s="19" t="inlineStr">
+        <is>
+          <t>°C</t>
+        </is>
+      </c>
+      <c r="G276" s="30" t="inlineStr">
+        <is>
+          <t>خريطة الشذوذ الحراري لفصل الصيف مقارنة بخط أساس 1991–2020 (°C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="277" ht="24" customHeight="1">
+      <c r="A277" s="3" t="n">
+        <v>276</v>
+      </c>
+      <c r="B277" s="5" t="inlineStr">
+        <is>
+          <t>R_AnomAnn</t>
+        </is>
+      </c>
+      <c r="C277" s="31" t="inlineStr">
+        <is>
+          <t>R_Anom_Annual</t>
+        </is>
+      </c>
+      <c r="D277" s="15" t="inlineStr">
+        <is>
+          <t>18_Trends_And_Anomalies (الاتجاهات والشذوذ)</t>
+        </is>
+      </c>
+      <c r="E277" s="7" t="inlineStr">
+        <is>
+          <t>شذوذ الأمطار السنوي المطلق مقارنة بمتوسط الأمطار لخط الأساس المناخي 1991–2020.</t>
+        </is>
+      </c>
+      <c r="F277" s="16" t="inlineStr">
+        <is>
+          <t>ملم (mm)</t>
+        </is>
+      </c>
+      <c r="G277" s="32" t="inlineStr">
+        <is>
+          <t>خريطة شذوذ تساقط الأمطار السنوي مقارنة بخط أساس 1991–2020 (ملم)</t>
+        </is>
+      </c>
+    </row>
+    <row r="278" ht="24" customHeight="1">
+      <c r="A278" s="8" t="n">
+        <v>277</v>
+      </c>
+      <c r="B278" s="10" t="inlineStr">
+        <is>
+          <t>R_AnomPct</t>
+        </is>
+      </c>
+      <c r="C278" s="29" t="inlineStr">
+        <is>
+          <t>R_Anom_Annual_Pct</t>
+        </is>
+      </c>
+      <c r="D278" s="18" t="inlineStr">
+        <is>
+          <t>18_Trends_And_Anomalies (الاتجاهات والشذوذ)</t>
+        </is>
+      </c>
+      <c r="E278" s="12" t="inlineStr">
+        <is>
+          <t>شذوذ الأمطار السنوي كنسبة مئوية من خط الأساس المناخي 1991–2020 (فرق نسبي مئوي).</t>
+        </is>
+      </c>
+      <c r="F278" s="19" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="G278" s="30" t="inlineStr">
+        <is>
+          <t>خريطة الشذوذ النسبي المئوي للأمطار مقارنة بخط أساس 1991–2020 (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="279" ht="24" customHeight="1">
+      <c r="A279" s="3" t="n">
+        <v>278</v>
+      </c>
+      <c r="B279" s="5" t="inlineStr">
+        <is>
+          <t>R_AnomWin</t>
+        </is>
+      </c>
+      <c r="C279" s="31" t="inlineStr">
+        <is>
+          <t>R_Anom_Winter</t>
+        </is>
+      </c>
+      <c r="D279" s="15" t="inlineStr">
+        <is>
+          <t>18_Trends_And_Anomalies (الاتجاهات والشذوذ)</t>
+        </is>
+      </c>
+      <c r="E279" s="7" t="inlineStr">
+        <is>
+          <t>شذوذ أمطار فصل الشتاء المطلق مقارنة بأمطار شتاء خط الأساس المناخي 1991–2020.</t>
+        </is>
+      </c>
+      <c r="F279" s="16" t="inlineStr">
+        <is>
+          <t>ملم (mm)</t>
+        </is>
+      </c>
+      <c r="G279" s="32" t="inlineStr">
+        <is>
+          <t>خريطة شذوذ أمطار الشتاء مقارنة بخط أساس 1991–2020 (ملم)</t>
+        </is>
+      </c>
+    </row>
+    <row r="280" ht="24" customHeight="1">
+      <c r="A280" s="8" t="n">
+        <v>279</v>
+      </c>
+      <c r="B280" s="10" t="inlineStr">
+        <is>
           <t>R_AnomWPct</t>
         </is>
       </c>
-      <c r="C271" s="31" t="inlineStr">
+      <c r="C280" s="29" t="inlineStr">
         <is>
           <t>R_Anom_Winter_Pct</t>
         </is>
       </c>
-      <c r="D271" s="15" t="inlineStr">
+      <c r="D280" s="18" t="inlineStr">
         <is>
           <t>18_Trends_And_Anomalies (الاتجاهات والشذوذ)</t>
         </is>
       </c>
-      <c r="E271" s="7" t="inlineStr">
+      <c r="E280" s="12" t="inlineStr">
         <is>
           <t>شذوذ أمطار فصل الشتاء كنسبة مئوية مقارنة بأمطار شتاء خط الأساس المناخي 1991–2020.</t>
         </is>
       </c>
-      <c r="F271" s="16" t="inlineStr">
+      <c r="F280" s="19" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="G271" s="32" t="inlineStr">
+      <c r="G280" s="30" t="inlineStr">
         <is>
           <t>خريطة الشذوذ النسبي المئوي لأمطار الشتاء مقارنة بخط أساس 1991–2020 (%)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G271"/>
+  <autoFilter ref="A1:G280"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
